--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3988" uniqueCount="1774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3989" uniqueCount="1774">
   <si>
     <t>Status</t>
   </si>
@@ -14693,7 +14693,9 @@
         <v>615</v>
       </c>
       <c r="O213" s="14"/>
-      <c r="P213" s="14"/>
+      <c r="P213" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q213" s="18" t="s">
         <v>16</v>
       </c>
@@ -33282,301 +33284,302 @@
     <hyperlink ref="B213" r:id="rId207"/>
     <hyperlink ref="L213" r:id="rId208"/>
     <hyperlink ref="N213" r:id="rId209"/>
-    <hyperlink ref="Q213" r:id="rId210"/>
-    <hyperlink ref="B218" r:id="rId211"/>
-    <hyperlink ref="L218" r:id="rId212"/>
-    <hyperlink ref="N218" r:id="rId213"/>
-    <hyperlink ref="P218" r:id="rId214"/>
-    <hyperlink ref="Q218" r:id="rId215"/>
-    <hyperlink ref="B223" r:id="rId216"/>
-    <hyperlink ref="L223" r:id="rId217"/>
-    <hyperlink ref="N223" r:id="rId218"/>
-    <hyperlink ref="P223" r:id="rId219"/>
-    <hyperlink ref="Q223" r:id="rId220"/>
-    <hyperlink ref="R223" r:id="rId221"/>
-    <hyperlink ref="B229" r:id="rId222"/>
-    <hyperlink ref="L229" r:id="rId223"/>
-    <hyperlink ref="N229" r:id="rId224"/>
-    <hyperlink ref="P229" r:id="rId225"/>
-    <hyperlink ref="B236" r:id="rId226"/>
-    <hyperlink ref="L236" r:id="rId227"/>
-    <hyperlink ref="N236" r:id="rId228"/>
-    <hyperlink ref="P236" r:id="rId229"/>
-    <hyperlink ref="B245" r:id="rId230"/>
-    <hyperlink ref="L245" r:id="rId231"/>
-    <hyperlink ref="N245" r:id="rId232"/>
-    <hyperlink ref="P245" r:id="rId233"/>
-    <hyperlink ref="Q245" r:id="rId234"/>
-    <hyperlink ref="B251" r:id="rId235"/>
-    <hyperlink ref="L251" r:id="rId236"/>
-    <hyperlink ref="N251" r:id="rId237"/>
-    <hyperlink ref="P251" r:id="rId238"/>
-    <hyperlink ref="Q251" r:id="rId239"/>
-    <hyperlink ref="B255" r:id="rId240"/>
-    <hyperlink ref="L255" r:id="rId241"/>
-    <hyperlink ref="N255" r:id="rId242"/>
-    <hyperlink ref="B277" r:id="rId243"/>
-    <hyperlink ref="L277" r:id="rId244"/>
-    <hyperlink ref="N277" r:id="rId245"/>
-    <hyperlink ref="P277" r:id="rId246"/>
-    <hyperlink ref="Q277" r:id="rId247"/>
-    <hyperlink ref="B285" r:id="rId248"/>
-    <hyperlink ref="L285" r:id="rId249"/>
-    <hyperlink ref="N285" r:id="rId250"/>
-    <hyperlink ref="P285" r:id="rId251"/>
-    <hyperlink ref="Q285" r:id="rId252"/>
-    <hyperlink ref="B296" r:id="rId253"/>
-    <hyperlink ref="L296" r:id="rId254"/>
-    <hyperlink ref="N296" r:id="rId255"/>
-    <hyperlink ref="P296" r:id="rId256"/>
-    <hyperlink ref="Q296" r:id="rId257"/>
-    <hyperlink ref="B304" r:id="rId258"/>
-    <hyperlink ref="L304" r:id="rId259"/>
-    <hyperlink ref="N304" r:id="rId260"/>
-    <hyperlink ref="P304" r:id="rId261"/>
-    <hyperlink ref="Q304" r:id="rId262"/>
-    <hyperlink ref="B326" r:id="rId263"/>
-    <hyperlink ref="L326" r:id="rId264"/>
-    <hyperlink ref="N326" r:id="rId265"/>
-    <hyperlink ref="P326" r:id="rId266"/>
-    <hyperlink ref="B328" r:id="rId267"/>
-    <hyperlink ref="L328" r:id="rId268"/>
-    <hyperlink ref="N328" r:id="rId269"/>
-    <hyperlink ref="P328" r:id="rId270"/>
-    <hyperlink ref="Q328" r:id="rId271"/>
-    <hyperlink ref="B332" r:id="rId272"/>
-    <hyperlink ref="L332" r:id="rId273"/>
-    <hyperlink ref="N332" r:id="rId274"/>
-    <hyperlink ref="B335" r:id="rId275"/>
-    <hyperlink ref="L335" r:id="rId276"/>
-    <hyperlink ref="N335" r:id="rId277"/>
-    <hyperlink ref="P335" r:id="rId278"/>
-    <hyperlink ref="Q335" r:id="rId279"/>
-    <hyperlink ref="B337" r:id="rId280"/>
-    <hyperlink ref="L337" r:id="rId281"/>
-    <hyperlink ref="N337" r:id="rId282"/>
-    <hyperlink ref="P337" r:id="rId283"/>
-    <hyperlink ref="Q337" r:id="rId284"/>
-    <hyperlink ref="B343" r:id="rId285"/>
-    <hyperlink ref="L343" r:id="rId286"/>
-    <hyperlink ref="N343" r:id="rId287"/>
-    <hyperlink ref="P343" r:id="rId288"/>
-    <hyperlink ref="Q343" r:id="rId289"/>
-    <hyperlink ref="B344" r:id="rId290"/>
-    <hyperlink ref="L344" r:id="rId291"/>
-    <hyperlink ref="N344" r:id="rId292"/>
-    <hyperlink ref="Q344" r:id="rId293"/>
-    <hyperlink ref="B347" r:id="rId294"/>
-    <hyperlink ref="L347" r:id="rId295"/>
-    <hyperlink ref="N347" r:id="rId296"/>
-    <hyperlink ref="P347" r:id="rId297"/>
-    <hyperlink ref="Q347" r:id="rId298"/>
-    <hyperlink ref="B350" r:id="rId299"/>
-    <hyperlink ref="L350" r:id="rId300"/>
-    <hyperlink ref="N350" r:id="rId301"/>
-    <hyperlink ref="P350" r:id="rId302"/>
-    <hyperlink ref="Q350" r:id="rId303"/>
-    <hyperlink ref="B352" r:id="rId304"/>
-    <hyperlink ref="L352" r:id="rId305"/>
-    <hyperlink ref="N352" r:id="rId306"/>
-    <hyperlink ref="P352" r:id="rId307"/>
-    <hyperlink ref="Q352" r:id="rId308"/>
-    <hyperlink ref="R352" r:id="rId309"/>
-    <hyperlink ref="B391" r:id="rId310"/>
-    <hyperlink ref="L391" r:id="rId311"/>
-    <hyperlink ref="N391" r:id="rId312"/>
-    <hyperlink ref="P391" r:id="rId313"/>
-    <hyperlink ref="B393" r:id="rId314"/>
-    <hyperlink ref="L393" r:id="rId315"/>
-    <hyperlink ref="N393" r:id="rId316"/>
-    <hyperlink ref="P393" r:id="rId317"/>
-    <hyperlink ref="B394" r:id="rId318"/>
-    <hyperlink ref="L394" r:id="rId319"/>
-    <hyperlink ref="N394" r:id="rId320"/>
-    <hyperlink ref="Q394" r:id="rId321"/>
-    <hyperlink ref="B395" r:id="rId322"/>
-    <hyperlink ref="L395" r:id="rId323"/>
-    <hyperlink ref="N395" r:id="rId324"/>
-    <hyperlink ref="P395" r:id="rId325"/>
-    <hyperlink ref="B406" r:id="rId326"/>
-    <hyperlink ref="L406" r:id="rId327"/>
-    <hyperlink ref="N406" r:id="rId328"/>
-    <hyperlink ref="P406" r:id="rId329"/>
-    <hyperlink ref="B407" r:id="rId330"/>
-    <hyperlink ref="L407" r:id="rId331"/>
-    <hyperlink ref="N407" r:id="rId332"/>
-    <hyperlink ref="P407" r:id="rId333"/>
-    <hyperlink ref="B408" r:id="rId334"/>
-    <hyperlink ref="L408" r:id="rId335"/>
-    <hyperlink ref="N408" r:id="rId336"/>
-    <hyperlink ref="Q408" r:id="rId337"/>
-    <hyperlink ref="B410" r:id="rId338"/>
-    <hyperlink ref="L410" r:id="rId339"/>
-    <hyperlink ref="N410" r:id="rId340"/>
-    <hyperlink ref="P410" r:id="rId341"/>
-    <hyperlink ref="B411" r:id="rId342"/>
-    <hyperlink ref="L411" r:id="rId343"/>
-    <hyperlink ref="N411" r:id="rId344"/>
-    <hyperlink ref="Q411" r:id="rId345"/>
-    <hyperlink ref="B417" r:id="rId346"/>
-    <hyperlink ref="L417" r:id="rId347"/>
-    <hyperlink ref="N417" r:id="rId348"/>
-    <hyperlink ref="P417" r:id="rId349"/>
-    <hyperlink ref="B424" r:id="rId350"/>
-    <hyperlink ref="L424" r:id="rId351"/>
-    <hyperlink ref="N424" r:id="rId352"/>
-    <hyperlink ref="P424" r:id="rId353"/>
-    <hyperlink ref="B429" r:id="rId354"/>
-    <hyperlink ref="L429" r:id="rId355"/>
-    <hyperlink ref="N429" r:id="rId356"/>
-    <hyperlink ref="P429" r:id="rId357"/>
-    <hyperlink ref="B430" r:id="rId358"/>
-    <hyperlink ref="L430" r:id="rId359"/>
-    <hyperlink ref="N430" r:id="rId360"/>
-    <hyperlink ref="P430" r:id="rId361"/>
-    <hyperlink ref="B442" r:id="rId362"/>
-    <hyperlink ref="L442" r:id="rId363"/>
-    <hyperlink ref="N442" r:id="rId364"/>
-    <hyperlink ref="P442" r:id="rId365"/>
-    <hyperlink ref="Q442" r:id="rId366"/>
-    <hyperlink ref="B459" r:id="rId367"/>
-    <hyperlink ref="L459" r:id="rId368"/>
-    <hyperlink ref="N459" r:id="rId369"/>
-    <hyperlink ref="P459" r:id="rId370"/>
-    <hyperlink ref="Q459" r:id="rId371"/>
-    <hyperlink ref="N464" r:id="rId372"/>
-    <hyperlink ref="B475" r:id="rId373"/>
-    <hyperlink ref="L475" r:id="rId374"/>
-    <hyperlink ref="N475" r:id="rId375"/>
-    <hyperlink ref="P475" r:id="rId376"/>
-    <hyperlink ref="R475" r:id="rId377"/>
-    <hyperlink ref="B481" r:id="rId378"/>
-    <hyperlink ref="L481" r:id="rId379"/>
-    <hyperlink ref="N481" r:id="rId380"/>
-    <hyperlink ref="P481" r:id="rId381"/>
-    <hyperlink ref="B483" r:id="rId382"/>
-    <hyperlink ref="L483" r:id="rId383"/>
-    <hyperlink ref="N483" r:id="rId384"/>
-    <hyperlink ref="B486" r:id="rId385"/>
-    <hyperlink ref="L486" r:id="rId386"/>
-    <hyperlink ref="N486" r:id="rId387"/>
-    <hyperlink ref="B489" r:id="rId388"/>
-    <hyperlink ref="L489" r:id="rId389"/>
-    <hyperlink ref="N489" r:id="rId390"/>
-    <hyperlink ref="P489" r:id="rId391"/>
-    <hyperlink ref="B493" r:id="rId392"/>
-    <hyperlink ref="L493" r:id="rId393"/>
-    <hyperlink ref="N493" r:id="rId394"/>
-    <hyperlink ref="P493" r:id="rId395"/>
-    <hyperlink ref="B494" r:id="rId396"/>
-    <hyperlink ref="L494" r:id="rId397"/>
-    <hyperlink ref="N494" r:id="rId398"/>
-    <hyperlink ref="P494" r:id="rId399"/>
-    <hyperlink ref="B497" r:id="rId400"/>
-    <hyperlink ref="L497" r:id="rId401"/>
-    <hyperlink ref="N497" r:id="rId402"/>
-    <hyperlink ref="P497" r:id="rId403"/>
-    <hyperlink ref="B508" r:id="rId404"/>
-    <hyperlink ref="L508" r:id="rId405"/>
-    <hyperlink ref="N508" r:id="rId406"/>
-    <hyperlink ref="P508" r:id="rId407"/>
-    <hyperlink ref="B511" r:id="rId408"/>
-    <hyperlink ref="L511" r:id="rId409"/>
-    <hyperlink ref="N511" r:id="rId410"/>
-    <hyperlink ref="P511" r:id="rId411"/>
-    <hyperlink ref="R511" r:id="rId412"/>
-    <hyperlink ref="B522" r:id="rId413"/>
-    <hyperlink ref="L522" r:id="rId414"/>
-    <hyperlink ref="N522" r:id="rId415"/>
-    <hyperlink ref="P522" r:id="rId416"/>
-    <hyperlink ref="Q522" r:id="rId417"/>
-    <hyperlink ref="R522" r:id="rId418"/>
-    <hyperlink ref="B525" r:id="rId419"/>
-    <hyperlink ref="L525" r:id="rId420"/>
-    <hyperlink ref="N525" r:id="rId421"/>
-    <hyperlink ref="P525" r:id="rId422"/>
-    <hyperlink ref="B526" r:id="rId423"/>
-    <hyperlink ref="L526" r:id="rId424"/>
-    <hyperlink ref="N526" r:id="rId425"/>
-    <hyperlink ref="Q526" r:id="rId426"/>
-    <hyperlink ref="B528" r:id="rId427"/>
-    <hyperlink ref="L528" r:id="rId428"/>
-    <hyperlink ref="N528" r:id="rId429"/>
-    <hyperlink ref="P528" r:id="rId430"/>
-    <hyperlink ref="B530" r:id="rId431"/>
-    <hyperlink ref="L530" r:id="rId432"/>
-    <hyperlink ref="N530" r:id="rId433"/>
-    <hyperlink ref="P530" r:id="rId434"/>
-    <hyperlink ref="B531" r:id="rId435"/>
-    <hyperlink ref="L531" r:id="rId436"/>
-    <hyperlink ref="N531" r:id="rId437"/>
-    <hyperlink ref="P531" r:id="rId438"/>
-    <hyperlink ref="B532" r:id="rId439"/>
-    <hyperlink ref="L532" r:id="rId440"/>
-    <hyperlink ref="N532" r:id="rId441"/>
-    <hyperlink ref="Q532" r:id="rId442"/>
-    <hyperlink ref="B533" r:id="rId443"/>
-    <hyperlink ref="L533" r:id="rId444"/>
-    <hyperlink ref="N533" r:id="rId445"/>
-    <hyperlink ref="Q533" r:id="rId446"/>
-    <hyperlink ref="B534" r:id="rId447"/>
-    <hyperlink ref="L534" r:id="rId448"/>
-    <hyperlink ref="N534" r:id="rId449"/>
-    <hyperlink ref="Q534" r:id="rId450"/>
-    <hyperlink ref="B545" r:id="rId451"/>
-    <hyperlink ref="L545" r:id="rId452"/>
-    <hyperlink ref="N545" r:id="rId453"/>
-    <hyperlink ref="P545" r:id="rId454"/>
-    <hyperlink ref="Q545" r:id="rId455"/>
-    <hyperlink ref="N553" r:id="rId456"/>
-    <hyperlink ref="B554" r:id="rId457"/>
-    <hyperlink ref="L554" r:id="rId458"/>
-    <hyperlink ref="N554" r:id="rId459"/>
-    <hyperlink ref="P554" r:id="rId460"/>
-    <hyperlink ref="Q554" r:id="rId461"/>
-    <hyperlink ref="B561" r:id="rId462"/>
-    <hyperlink ref="L561" r:id="rId463"/>
-    <hyperlink ref="N561" r:id="rId464"/>
-    <hyperlink ref="P561" r:id="rId465"/>
-    <hyperlink ref="Q561" r:id="rId466"/>
-    <hyperlink ref="B562" r:id="rId467"/>
-    <hyperlink ref="L562" r:id="rId468"/>
-    <hyperlink ref="N562" r:id="rId469"/>
-    <hyperlink ref="Q562" r:id="rId470"/>
-    <hyperlink ref="B563" r:id="rId471"/>
-    <hyperlink ref="L563" r:id="rId472"/>
-    <hyperlink ref="N563" r:id="rId473"/>
-    <hyperlink ref="Q563" r:id="rId474"/>
-    <hyperlink ref="B584" r:id="rId475"/>
-    <hyperlink ref="L584" r:id="rId476"/>
-    <hyperlink ref="N584" r:id="rId477"/>
-    <hyperlink ref="P584" r:id="rId478"/>
-    <hyperlink ref="R584" r:id="rId479"/>
-    <hyperlink ref="B594" r:id="rId480"/>
-    <hyperlink ref="L594" r:id="rId481"/>
-    <hyperlink ref="N594" r:id="rId482"/>
-    <hyperlink ref="P594" r:id="rId483"/>
-    <hyperlink ref="Q594" r:id="rId484"/>
-    <hyperlink ref="B620" r:id="rId485"/>
-    <hyperlink ref="L620" r:id="rId486"/>
-    <hyperlink ref="N620" r:id="rId487"/>
-    <hyperlink ref="P620" r:id="rId488"/>
-    <hyperlink ref="Q620" r:id="rId489"/>
-    <hyperlink ref="B621" r:id="rId490"/>
-    <hyperlink ref="L621" r:id="rId491"/>
-    <hyperlink ref="N621" r:id="rId492"/>
-    <hyperlink ref="O621" r:id="rId493"/>
-    <hyperlink ref="Q621" r:id="rId494"/>
-    <hyperlink ref="B630" r:id="rId495"/>
-    <hyperlink ref="N630" r:id="rId496"/>
-    <hyperlink ref="P630" r:id="rId497"/>
-    <hyperlink ref="B639" r:id="rId498"/>
-    <hyperlink ref="L639" r:id="rId499"/>
-    <hyperlink ref="N639" r:id="rId500"/>
-    <hyperlink ref="P639" r:id="rId501"/>
-    <hyperlink ref="B646" r:id="rId502"/>
-    <hyperlink ref="L646" r:id="rId503"/>
-    <hyperlink ref="N646" r:id="rId504"/>
+    <hyperlink ref="P213" r:id="rId210"/>
+    <hyperlink ref="Q213" r:id="rId211"/>
+    <hyperlink ref="B218" r:id="rId212"/>
+    <hyperlink ref="L218" r:id="rId213"/>
+    <hyperlink ref="N218" r:id="rId214"/>
+    <hyperlink ref="P218" r:id="rId215"/>
+    <hyperlink ref="Q218" r:id="rId216"/>
+    <hyperlink ref="B223" r:id="rId217"/>
+    <hyperlink ref="L223" r:id="rId218"/>
+    <hyperlink ref="N223" r:id="rId219"/>
+    <hyperlink ref="P223" r:id="rId220"/>
+    <hyperlink ref="Q223" r:id="rId221"/>
+    <hyperlink ref="R223" r:id="rId222"/>
+    <hyperlink ref="B229" r:id="rId223"/>
+    <hyperlink ref="L229" r:id="rId224"/>
+    <hyperlink ref="N229" r:id="rId225"/>
+    <hyperlink ref="P229" r:id="rId226"/>
+    <hyperlink ref="B236" r:id="rId227"/>
+    <hyperlink ref="L236" r:id="rId228"/>
+    <hyperlink ref="N236" r:id="rId229"/>
+    <hyperlink ref="P236" r:id="rId230"/>
+    <hyperlink ref="B245" r:id="rId231"/>
+    <hyperlink ref="L245" r:id="rId232"/>
+    <hyperlink ref="N245" r:id="rId233"/>
+    <hyperlink ref="P245" r:id="rId234"/>
+    <hyperlink ref="Q245" r:id="rId235"/>
+    <hyperlink ref="B251" r:id="rId236"/>
+    <hyperlink ref="L251" r:id="rId237"/>
+    <hyperlink ref="N251" r:id="rId238"/>
+    <hyperlink ref="P251" r:id="rId239"/>
+    <hyperlink ref="Q251" r:id="rId240"/>
+    <hyperlink ref="B255" r:id="rId241"/>
+    <hyperlink ref="L255" r:id="rId242"/>
+    <hyperlink ref="N255" r:id="rId243"/>
+    <hyperlink ref="B277" r:id="rId244"/>
+    <hyperlink ref="L277" r:id="rId245"/>
+    <hyperlink ref="N277" r:id="rId246"/>
+    <hyperlink ref="P277" r:id="rId247"/>
+    <hyperlink ref="Q277" r:id="rId248"/>
+    <hyperlink ref="B285" r:id="rId249"/>
+    <hyperlink ref="L285" r:id="rId250"/>
+    <hyperlink ref="N285" r:id="rId251"/>
+    <hyperlink ref="P285" r:id="rId252"/>
+    <hyperlink ref="Q285" r:id="rId253"/>
+    <hyperlink ref="B296" r:id="rId254"/>
+    <hyperlink ref="L296" r:id="rId255"/>
+    <hyperlink ref="N296" r:id="rId256"/>
+    <hyperlink ref="P296" r:id="rId257"/>
+    <hyperlink ref="Q296" r:id="rId258"/>
+    <hyperlink ref="B304" r:id="rId259"/>
+    <hyperlink ref="L304" r:id="rId260"/>
+    <hyperlink ref="N304" r:id="rId261"/>
+    <hyperlink ref="P304" r:id="rId262"/>
+    <hyperlink ref="Q304" r:id="rId263"/>
+    <hyperlink ref="B326" r:id="rId264"/>
+    <hyperlink ref="L326" r:id="rId265"/>
+    <hyperlink ref="N326" r:id="rId266"/>
+    <hyperlink ref="P326" r:id="rId267"/>
+    <hyperlink ref="B328" r:id="rId268"/>
+    <hyperlink ref="L328" r:id="rId269"/>
+    <hyperlink ref="N328" r:id="rId270"/>
+    <hyperlink ref="P328" r:id="rId271"/>
+    <hyperlink ref="Q328" r:id="rId272"/>
+    <hyperlink ref="B332" r:id="rId273"/>
+    <hyperlink ref="L332" r:id="rId274"/>
+    <hyperlink ref="N332" r:id="rId275"/>
+    <hyperlink ref="B335" r:id="rId276"/>
+    <hyperlink ref="L335" r:id="rId277"/>
+    <hyperlink ref="N335" r:id="rId278"/>
+    <hyperlink ref="P335" r:id="rId279"/>
+    <hyperlink ref="Q335" r:id="rId280"/>
+    <hyperlink ref="B337" r:id="rId281"/>
+    <hyperlink ref="L337" r:id="rId282"/>
+    <hyperlink ref="N337" r:id="rId283"/>
+    <hyperlink ref="P337" r:id="rId284"/>
+    <hyperlink ref="Q337" r:id="rId285"/>
+    <hyperlink ref="B343" r:id="rId286"/>
+    <hyperlink ref="L343" r:id="rId287"/>
+    <hyperlink ref="N343" r:id="rId288"/>
+    <hyperlink ref="P343" r:id="rId289"/>
+    <hyperlink ref="Q343" r:id="rId290"/>
+    <hyperlink ref="B344" r:id="rId291"/>
+    <hyperlink ref="L344" r:id="rId292"/>
+    <hyperlink ref="N344" r:id="rId293"/>
+    <hyperlink ref="Q344" r:id="rId294"/>
+    <hyperlink ref="B347" r:id="rId295"/>
+    <hyperlink ref="L347" r:id="rId296"/>
+    <hyperlink ref="N347" r:id="rId297"/>
+    <hyperlink ref="P347" r:id="rId298"/>
+    <hyperlink ref="Q347" r:id="rId299"/>
+    <hyperlink ref="B350" r:id="rId300"/>
+    <hyperlink ref="L350" r:id="rId301"/>
+    <hyperlink ref="N350" r:id="rId302"/>
+    <hyperlink ref="P350" r:id="rId303"/>
+    <hyperlink ref="Q350" r:id="rId304"/>
+    <hyperlink ref="B352" r:id="rId305"/>
+    <hyperlink ref="L352" r:id="rId306"/>
+    <hyperlink ref="N352" r:id="rId307"/>
+    <hyperlink ref="P352" r:id="rId308"/>
+    <hyperlink ref="Q352" r:id="rId309"/>
+    <hyperlink ref="R352" r:id="rId310"/>
+    <hyperlink ref="B391" r:id="rId311"/>
+    <hyperlink ref="L391" r:id="rId312"/>
+    <hyperlink ref="N391" r:id="rId313"/>
+    <hyperlink ref="P391" r:id="rId314"/>
+    <hyperlink ref="B393" r:id="rId315"/>
+    <hyperlink ref="L393" r:id="rId316"/>
+    <hyperlink ref="N393" r:id="rId317"/>
+    <hyperlink ref="P393" r:id="rId318"/>
+    <hyperlink ref="B394" r:id="rId319"/>
+    <hyperlink ref="L394" r:id="rId320"/>
+    <hyperlink ref="N394" r:id="rId321"/>
+    <hyperlink ref="Q394" r:id="rId322"/>
+    <hyperlink ref="B395" r:id="rId323"/>
+    <hyperlink ref="L395" r:id="rId324"/>
+    <hyperlink ref="N395" r:id="rId325"/>
+    <hyperlink ref="P395" r:id="rId326"/>
+    <hyperlink ref="B406" r:id="rId327"/>
+    <hyperlink ref="L406" r:id="rId328"/>
+    <hyperlink ref="N406" r:id="rId329"/>
+    <hyperlink ref="P406" r:id="rId330"/>
+    <hyperlink ref="B407" r:id="rId331"/>
+    <hyperlink ref="L407" r:id="rId332"/>
+    <hyperlink ref="N407" r:id="rId333"/>
+    <hyperlink ref="P407" r:id="rId334"/>
+    <hyperlink ref="B408" r:id="rId335"/>
+    <hyperlink ref="L408" r:id="rId336"/>
+    <hyperlink ref="N408" r:id="rId337"/>
+    <hyperlink ref="Q408" r:id="rId338"/>
+    <hyperlink ref="B410" r:id="rId339"/>
+    <hyperlink ref="L410" r:id="rId340"/>
+    <hyperlink ref="N410" r:id="rId341"/>
+    <hyperlink ref="P410" r:id="rId342"/>
+    <hyperlink ref="B411" r:id="rId343"/>
+    <hyperlink ref="L411" r:id="rId344"/>
+    <hyperlink ref="N411" r:id="rId345"/>
+    <hyperlink ref="Q411" r:id="rId346"/>
+    <hyperlink ref="B417" r:id="rId347"/>
+    <hyperlink ref="L417" r:id="rId348"/>
+    <hyperlink ref="N417" r:id="rId349"/>
+    <hyperlink ref="P417" r:id="rId350"/>
+    <hyperlink ref="B424" r:id="rId351"/>
+    <hyperlink ref="L424" r:id="rId352"/>
+    <hyperlink ref="N424" r:id="rId353"/>
+    <hyperlink ref="P424" r:id="rId354"/>
+    <hyperlink ref="B429" r:id="rId355"/>
+    <hyperlink ref="L429" r:id="rId356"/>
+    <hyperlink ref="N429" r:id="rId357"/>
+    <hyperlink ref="P429" r:id="rId358"/>
+    <hyperlink ref="B430" r:id="rId359"/>
+    <hyperlink ref="L430" r:id="rId360"/>
+    <hyperlink ref="N430" r:id="rId361"/>
+    <hyperlink ref="P430" r:id="rId362"/>
+    <hyperlink ref="B442" r:id="rId363"/>
+    <hyperlink ref="L442" r:id="rId364"/>
+    <hyperlink ref="N442" r:id="rId365"/>
+    <hyperlink ref="P442" r:id="rId366"/>
+    <hyperlink ref="Q442" r:id="rId367"/>
+    <hyperlink ref="B459" r:id="rId368"/>
+    <hyperlink ref="L459" r:id="rId369"/>
+    <hyperlink ref="N459" r:id="rId370"/>
+    <hyperlink ref="P459" r:id="rId371"/>
+    <hyperlink ref="Q459" r:id="rId372"/>
+    <hyperlink ref="N464" r:id="rId373"/>
+    <hyperlink ref="B475" r:id="rId374"/>
+    <hyperlink ref="L475" r:id="rId375"/>
+    <hyperlink ref="N475" r:id="rId376"/>
+    <hyperlink ref="P475" r:id="rId377"/>
+    <hyperlink ref="R475" r:id="rId378"/>
+    <hyperlink ref="B481" r:id="rId379"/>
+    <hyperlink ref="L481" r:id="rId380"/>
+    <hyperlink ref="N481" r:id="rId381"/>
+    <hyperlink ref="P481" r:id="rId382"/>
+    <hyperlink ref="B483" r:id="rId383"/>
+    <hyperlink ref="L483" r:id="rId384"/>
+    <hyperlink ref="N483" r:id="rId385"/>
+    <hyperlink ref="B486" r:id="rId386"/>
+    <hyperlink ref="L486" r:id="rId387"/>
+    <hyperlink ref="N486" r:id="rId388"/>
+    <hyperlink ref="B489" r:id="rId389"/>
+    <hyperlink ref="L489" r:id="rId390"/>
+    <hyperlink ref="N489" r:id="rId391"/>
+    <hyperlink ref="P489" r:id="rId392"/>
+    <hyperlink ref="B493" r:id="rId393"/>
+    <hyperlink ref="L493" r:id="rId394"/>
+    <hyperlink ref="N493" r:id="rId395"/>
+    <hyperlink ref="P493" r:id="rId396"/>
+    <hyperlink ref="B494" r:id="rId397"/>
+    <hyperlink ref="L494" r:id="rId398"/>
+    <hyperlink ref="N494" r:id="rId399"/>
+    <hyperlink ref="P494" r:id="rId400"/>
+    <hyperlink ref="B497" r:id="rId401"/>
+    <hyperlink ref="L497" r:id="rId402"/>
+    <hyperlink ref="N497" r:id="rId403"/>
+    <hyperlink ref="P497" r:id="rId404"/>
+    <hyperlink ref="B508" r:id="rId405"/>
+    <hyperlink ref="L508" r:id="rId406"/>
+    <hyperlink ref="N508" r:id="rId407"/>
+    <hyperlink ref="P508" r:id="rId408"/>
+    <hyperlink ref="B511" r:id="rId409"/>
+    <hyperlink ref="L511" r:id="rId410"/>
+    <hyperlink ref="N511" r:id="rId411"/>
+    <hyperlink ref="P511" r:id="rId412"/>
+    <hyperlink ref="R511" r:id="rId413"/>
+    <hyperlink ref="B522" r:id="rId414"/>
+    <hyperlink ref="L522" r:id="rId415"/>
+    <hyperlink ref="N522" r:id="rId416"/>
+    <hyperlink ref="P522" r:id="rId417"/>
+    <hyperlink ref="Q522" r:id="rId418"/>
+    <hyperlink ref="R522" r:id="rId419"/>
+    <hyperlink ref="B525" r:id="rId420"/>
+    <hyperlink ref="L525" r:id="rId421"/>
+    <hyperlink ref="N525" r:id="rId422"/>
+    <hyperlink ref="P525" r:id="rId423"/>
+    <hyperlink ref="B526" r:id="rId424"/>
+    <hyperlink ref="L526" r:id="rId425"/>
+    <hyperlink ref="N526" r:id="rId426"/>
+    <hyperlink ref="Q526" r:id="rId427"/>
+    <hyperlink ref="B528" r:id="rId428"/>
+    <hyperlink ref="L528" r:id="rId429"/>
+    <hyperlink ref="N528" r:id="rId430"/>
+    <hyperlink ref="P528" r:id="rId431"/>
+    <hyperlink ref="B530" r:id="rId432"/>
+    <hyperlink ref="L530" r:id="rId433"/>
+    <hyperlink ref="N530" r:id="rId434"/>
+    <hyperlink ref="P530" r:id="rId435"/>
+    <hyperlink ref="B531" r:id="rId436"/>
+    <hyperlink ref="L531" r:id="rId437"/>
+    <hyperlink ref="N531" r:id="rId438"/>
+    <hyperlink ref="P531" r:id="rId439"/>
+    <hyperlink ref="B532" r:id="rId440"/>
+    <hyperlink ref="L532" r:id="rId441"/>
+    <hyperlink ref="N532" r:id="rId442"/>
+    <hyperlink ref="Q532" r:id="rId443"/>
+    <hyperlink ref="B533" r:id="rId444"/>
+    <hyperlink ref="L533" r:id="rId445"/>
+    <hyperlink ref="N533" r:id="rId446"/>
+    <hyperlink ref="Q533" r:id="rId447"/>
+    <hyperlink ref="B534" r:id="rId448"/>
+    <hyperlink ref="L534" r:id="rId449"/>
+    <hyperlink ref="N534" r:id="rId450"/>
+    <hyperlink ref="Q534" r:id="rId451"/>
+    <hyperlink ref="B545" r:id="rId452"/>
+    <hyperlink ref="L545" r:id="rId453"/>
+    <hyperlink ref="N545" r:id="rId454"/>
+    <hyperlink ref="P545" r:id="rId455"/>
+    <hyperlink ref="Q545" r:id="rId456"/>
+    <hyperlink ref="N553" r:id="rId457"/>
+    <hyperlink ref="B554" r:id="rId458"/>
+    <hyperlink ref="L554" r:id="rId459"/>
+    <hyperlink ref="N554" r:id="rId460"/>
+    <hyperlink ref="P554" r:id="rId461"/>
+    <hyperlink ref="Q554" r:id="rId462"/>
+    <hyperlink ref="B561" r:id="rId463"/>
+    <hyperlink ref="L561" r:id="rId464"/>
+    <hyperlink ref="N561" r:id="rId465"/>
+    <hyperlink ref="P561" r:id="rId466"/>
+    <hyperlink ref="Q561" r:id="rId467"/>
+    <hyperlink ref="B562" r:id="rId468"/>
+    <hyperlink ref="L562" r:id="rId469"/>
+    <hyperlink ref="N562" r:id="rId470"/>
+    <hyperlink ref="Q562" r:id="rId471"/>
+    <hyperlink ref="B563" r:id="rId472"/>
+    <hyperlink ref="L563" r:id="rId473"/>
+    <hyperlink ref="N563" r:id="rId474"/>
+    <hyperlink ref="Q563" r:id="rId475"/>
+    <hyperlink ref="B584" r:id="rId476"/>
+    <hyperlink ref="L584" r:id="rId477"/>
+    <hyperlink ref="N584" r:id="rId478"/>
+    <hyperlink ref="P584" r:id="rId479"/>
+    <hyperlink ref="R584" r:id="rId480"/>
+    <hyperlink ref="B594" r:id="rId481"/>
+    <hyperlink ref="L594" r:id="rId482"/>
+    <hyperlink ref="N594" r:id="rId483"/>
+    <hyperlink ref="P594" r:id="rId484"/>
+    <hyperlink ref="Q594" r:id="rId485"/>
+    <hyperlink ref="B620" r:id="rId486"/>
+    <hyperlink ref="L620" r:id="rId487"/>
+    <hyperlink ref="N620" r:id="rId488"/>
+    <hyperlink ref="P620" r:id="rId489"/>
+    <hyperlink ref="Q620" r:id="rId490"/>
+    <hyperlink ref="B621" r:id="rId491"/>
+    <hyperlink ref="L621" r:id="rId492"/>
+    <hyperlink ref="N621" r:id="rId493"/>
+    <hyperlink ref="O621" r:id="rId494"/>
+    <hyperlink ref="Q621" r:id="rId495"/>
+    <hyperlink ref="B630" r:id="rId496"/>
+    <hyperlink ref="N630" r:id="rId497"/>
+    <hyperlink ref="P630" r:id="rId498"/>
+    <hyperlink ref="B639" r:id="rId499"/>
+    <hyperlink ref="L639" r:id="rId500"/>
+    <hyperlink ref="N639" r:id="rId501"/>
+    <hyperlink ref="P639" r:id="rId502"/>
+    <hyperlink ref="B646" r:id="rId503"/>
+    <hyperlink ref="L646" r:id="rId504"/>
+    <hyperlink ref="N646" r:id="rId505"/>
   </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3989" uniqueCount="1774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="1774">
   <si>
     <t>Status</t>
   </si>
@@ -26161,6 +26161,7 @@
         <v>1370</v>
       </c>
       <c r="O486" s="9"/>
+      <c r="P486" s="9"/>
       <c r="Q486" s="7"/>
       <c r="R486" s="7"/>
     </row>
@@ -31912,7 +31913,9 @@
       <c r="O621" s="25" t="s">
         <v>1711</v>
       </c>
-      <c r="P621" s="14"/>
+      <c r="P621" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q621" s="18" t="s">
         <v>16</v>
       </c>
@@ -33569,17 +33572,18 @@
     <hyperlink ref="L621" r:id="rId492"/>
     <hyperlink ref="N621" r:id="rId493"/>
     <hyperlink ref="O621" r:id="rId494"/>
-    <hyperlink ref="Q621" r:id="rId495"/>
-    <hyperlink ref="B630" r:id="rId496"/>
-    <hyperlink ref="N630" r:id="rId497"/>
-    <hyperlink ref="P630" r:id="rId498"/>
-    <hyperlink ref="B639" r:id="rId499"/>
-    <hyperlink ref="L639" r:id="rId500"/>
-    <hyperlink ref="N639" r:id="rId501"/>
-    <hyperlink ref="P639" r:id="rId502"/>
-    <hyperlink ref="B646" r:id="rId503"/>
-    <hyperlink ref="L646" r:id="rId504"/>
-    <hyperlink ref="N646" r:id="rId505"/>
+    <hyperlink ref="P621" r:id="rId495"/>
+    <hyperlink ref="Q621" r:id="rId496"/>
+    <hyperlink ref="B630" r:id="rId497"/>
+    <hyperlink ref="N630" r:id="rId498"/>
+    <hyperlink ref="P630" r:id="rId499"/>
+    <hyperlink ref="B639" r:id="rId500"/>
+    <hyperlink ref="L639" r:id="rId501"/>
+    <hyperlink ref="N639" r:id="rId502"/>
+    <hyperlink ref="P639" r:id="rId503"/>
+    <hyperlink ref="B646" r:id="rId504"/>
+    <hyperlink ref="L646" r:id="rId505"/>
+    <hyperlink ref="N646" r:id="rId506"/>
   </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="1774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3991" uniqueCount="1774">
   <si>
     <t>Status</t>
   </si>
@@ -22831,7 +22831,9 @@
       <c r="G408" s="8"/>
       <c r="H408" s="8"/>
       <c r="I408" s="8"/>
-      <c r="J408" s="9"/>
+      <c r="J408" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="K408" s="8"/>
       <c r="L408" s="15" t="s">
         <v>11</v>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4000" uniqueCount="1778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4000" uniqueCount="1779">
   <si>
     <t>Status</t>
   </si>
@@ -3464,7 +3464,13 @@
     <t>To verify and validate that the dynamic models and associated parameters used to assess Bulk Electric System (BES) reliability represent the in-service equipment of Bulk Power System (BPS) facilities including generating facilities, transmission connected dynamic reactive resources, and high-voltage direct current (HVDC) systems.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD26-3-000</t>
+    <t xml:space="preserve">Filing/Order Docket No. RD26-3-000
+Additional Effective Date Details
+Requirements R1 and R7 -   April 1, 2027
+Entities shall not be required to comply with Requirement R1 relating to the jointly developed dynamic model requirements between the Planning Coordinator and Transmission Planner and Requirement R7 relating to the provision of the current (in-use) models until twelve (12) months after the effective date of the Reliability Standard MOD-026-2.
+Requirements R2, R3, R4, R5, and R6 - April 1, 2029
+Entities shall not be required to comply with Requirements R2, R3, R4, R5, and R6 until thirty-six (36) months after the effective date of Reliability Standard MOD-026-2.
+See the Implementation Plan for additional information on Initial Performance Dates for periodic requirements, newly commissioned and newly applicable facilities, and early compliance.  </t>
   </si>
   <si>
     <t>Project 2020-06</t>
@@ -3602,6 +3608,13 @@
 procedures for development of planning horizon cases necessary to 
 support analysis of the reliability of the interconnected transmission 
 system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filing/Order Docket No. RD26-1-000
+Additional Effective Date Details
+Requirements R2, R3, and R4 - April 1, 2029
+Entities shall not be required to comply with Requirements R2, R3, and R4 relating to revised Planning Coordinator and Transmission Planner data requirements and reporting procedures developed under MOD-032-2 Requirement R1 and Attachment 1 until 12 months after the effective date of Reliability Standard MOD-032-2.
+During the phased-in compliance period, entities shall continue to comply with Requirements R2, R3, and R4 related to Planning Coordinator / Transmission Planner data requirements and reporting procedures developed under MOD-032-1 Requirement R1 and Attachment 1 unless they are compliant with revised Planning Coordinator / Transmission Planner data requirements and reporting procedures under Reliability Standard MOD-032-2 Requirement R1.</t>
   </si>
   <si>
     <t>MOD-033-1</t>
@@ -20192,7 +20205,9 @@
         <v>45839</v>
       </c>
       <c r="J344" s="9"/>
-      <c r="K344" s="8"/>
+      <c r="K344" s="8">
+        <v>47208</v>
+      </c>
       <c r="L344" s="15" t="s">
         <v>11</v>
       </c>
@@ -20213,7 +20228,7 @@
     </row>
     <row r="345" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A345" s="11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B345" s="18" t="s">
         <v>966</v>
@@ -20230,9 +20245,15 @@
       <c r="F345" s="13">
         <v>45965</v>
       </c>
-      <c r="G345" s="13"/>
-      <c r="H345" s="13"/>
-      <c r="I345" s="13"/>
+      <c r="G345" s="13">
+        <v>46072</v>
+      </c>
+      <c r="H345" s="13">
+        <v>46072</v>
+      </c>
+      <c r="I345" s="13">
+        <v>47209</v>
+      </c>
       <c r="J345" s="14"/>
       <c r="K345" s="13"/>
       <c r="L345" s="18" t="s">
@@ -22232,7 +22253,9 @@
       <c r="J394" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K394" s="8"/>
+      <c r="K394" s="8">
+        <v>46112</v>
+      </c>
       <c r="L394" s="15" t="s">
         <v>11</v>
       </c>
@@ -22249,9 +22272,9 @@
       <c r="Q394" s="7"/>
       <c r="R394" s="7"/>
     </row>
-    <row r="395" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="395" s="1" customFormat="1" ht="289.0486" customHeight="1">
       <c r="A395" s="11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B395" s="18" t="s">
         <v>1117</v>
@@ -22268,9 +22291,15 @@
       <c r="F395" s="13">
         <v>45965</v>
       </c>
-      <c r="G395" s="13"/>
-      <c r="H395" s="13"/>
-      <c r="I395" s="13"/>
+      <c r="G395" s="13">
+        <v>46072</v>
+      </c>
+      <c r="H395" s="13">
+        <v>46072</v>
+      </c>
+      <c r="I395" s="13">
+        <v>46113</v>
+      </c>
       <c r="J395" s="14" t="s">
         <v>86</v>
       </c>
@@ -22278,7 +22307,7 @@
       <c r="L395" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M395" s="11" t="s">
+      <c r="M395" s="17" t="s">
         <v>1120</v>
       </c>
       <c r="N395" s="18" t="s">
@@ -22322,7 +22351,9 @@
       <c r="J396" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K396" s="8"/>
+      <c r="K396" s="8">
+        <v>46112</v>
+      </c>
       <c r="L396" s="15" t="s">
         <v>11</v>
       </c>
@@ -22842,7 +22873,9 @@
       <c r="J408" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K408" s="8"/>
+      <c r="K408" s="8">
+        <v>46843</v>
+      </c>
       <c r="L408" s="15" t="s">
         <v>11</v>
       </c>
@@ -22859,9 +22892,9 @@
       <c r="Q408" s="7"/>
       <c r="R408" s="7"/>
     </row>
-    <row r="409" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="409" s="1" customFormat="1" ht="245.8513" customHeight="1">
       <c r="A409" s="11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B409" s="18" t="s">
         <v>1161</v>
@@ -22878,9 +22911,15 @@
       <c r="F409" s="13">
         <v>45965</v>
       </c>
-      <c r="G409" s="13"/>
-      <c r="H409" s="13"/>
-      <c r="I409" s="13"/>
+      <c r="G409" s="13">
+        <v>46072</v>
+      </c>
+      <c r="H409" s="13">
+        <v>46072</v>
+      </c>
+      <c r="I409" s="13">
+        <v>46844</v>
+      </c>
       <c r="J409" s="14" t="s">
         <v>86</v>
       </c>
@@ -22888,8 +22927,8 @@
       <c r="L409" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M409" s="11" t="s">
-        <v>969</v>
+      <c r="M409" s="17" t="s">
+        <v>1163</v>
       </c>
       <c r="N409" s="18" t="s">
         <v>970</v>
@@ -22906,13 +22945,13 @@
         <v>18</v>
       </c>
       <c r="B410" s="7" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E410" s="8">
         <v>41676</v>
@@ -22935,7 +22974,7 @@
       </c>
       <c r="L410" s="7"/>
       <c r="M410" s="6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="N410" s="7" t="s">
         <v>1160</v>
@@ -22950,13 +22989,13 @@
         <v>30</v>
       </c>
       <c r="B411" s="18" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C411" s="12" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D411" s="11" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E411" s="13">
         <v>43867</v>
@@ -22974,7 +23013,9 @@
         <v>44287</v>
       </c>
       <c r="J411" s="14"/>
-      <c r="K411" s="13"/>
+      <c r="K411" s="13">
+        <v>46112</v>
+      </c>
       <c r="L411" s="18" t="s">
         <v>11</v>
       </c>
@@ -22991,18 +23032,18 @@
       <c r="Q411" s="12"/>
       <c r="R411" s="12"/>
     </row>
-    <row r="412" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="412" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A412" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B412" s="15" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D412" s="10" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="E412" s="8">
         <v>45961</v>
@@ -23010,19 +23051,25 @@
       <c r="F412" s="8">
         <v>45965</v>
       </c>
-      <c r="G412" s="8"/>
-      <c r="H412" s="8"/>
-      <c r="I412" s="8"/>
+      <c r="G412" s="8">
+        <v>46072</v>
+      </c>
+      <c r="H412" s="8">
+        <v>46072</v>
+      </c>
+      <c r="I412" s="8">
+        <v>46113</v>
+      </c>
       <c r="J412" s="9"/>
       <c r="K412" s="8"/>
       <c r="L412" s="15" t="s">
         <v>11</v>
       </c>
       <c r="M412" s="6" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N412" s="15" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="O412" s="9"/>
       <c r="P412" s="9"/>
@@ -23036,13 +23083,13 @@
         <v>18</v>
       </c>
       <c r="B413" s="12" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C413" s="12" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D413" s="11" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E413" s="13">
         <v>39204</v>
@@ -23063,7 +23110,7 @@
       </c>
       <c r="L413" s="12"/>
       <c r="M413" s="11" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N413" s="12"/>
       <c r="O413" s="14"/>
@@ -23076,13 +23123,13 @@
         <v>18</v>
       </c>
       <c r="B414" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D414" s="6" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E414" s="8">
         <v>40030</v>
@@ -23105,7 +23152,7 @@
       </c>
       <c r="L414" s="7"/>
       <c r="M414" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N414" s="7"/>
       <c r="O414" s="9"/>
@@ -23118,13 +23165,13 @@
         <v>18</v>
       </c>
       <c r="B415" s="12" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C415" s="12" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D415" s="11" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E415" s="13">
         <v>41010</v>
@@ -23145,10 +23192,10 @@
       </c>
       <c r="L415" s="12"/>
       <c r="M415" s="11" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N415" s="12" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="O415" s="14"/>
       <c r="P415" s="14"/>
@@ -23160,13 +23207,13 @@
         <v>18</v>
       </c>
       <c r="B416" s="7" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D416" s="6" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E416" s="8">
         <v>41956</v>
@@ -23194,13 +23241,13 @@
         <v>18</v>
       </c>
       <c r="B417" s="12" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C417" s="12" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D417" s="11" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E417" s="13">
         <v>41865</v>
@@ -23223,10 +23270,10 @@
       </c>
       <c r="L417" s="12"/>
       <c r="M417" s="11" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N417" s="12" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="O417" s="14"/>
       <c r="P417" s="14"/>
@@ -23238,13 +23285,13 @@
         <v>30</v>
       </c>
       <c r="B418" s="15" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D418" s="6" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E418" s="8">
         <v>43867</v>
@@ -23284,13 +23331,13 @@
         <v>18</v>
       </c>
       <c r="B419" s="12" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C419" s="12" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D419" s="11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E419" s="13">
         <v>38391</v>
@@ -23316,7 +23363,7 @@
         <v>45</v>
       </c>
       <c r="N419" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O419" s="14"/>
       <c r="P419" s="14"/>
@@ -23328,13 +23375,13 @@
         <v>18</v>
       </c>
       <c r="B420" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C420" s="7" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D420" s="6" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E420" s="8">
         <v>39918</v>
@@ -23370,13 +23417,13 @@
         <v>18</v>
       </c>
       <c r="B421" s="12" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C421" s="12" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D421" s="11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E421" s="13">
         <v>40976</v>
@@ -23402,7 +23449,7 @@
         <v>118</v>
       </c>
       <c r="N421" s="12" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="O421" s="14"/>
       <c r="P421" s="14"/>
@@ -23414,13 +23461,13 @@
         <v>18</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C422" s="7" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D422" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E422" s="8">
         <v>38391</v>
@@ -23456,13 +23503,13 @@
         <v>18</v>
       </c>
       <c r="B423" s="12" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C423" s="12" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D423" s="11" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E423" s="13">
         <v>38391</v>
@@ -23488,7 +23535,7 @@
         <v>45</v>
       </c>
       <c r="N423" s="12" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="O423" s="14"/>
       <c r="P423" s="14"/>
@@ -23500,13 +23547,13 @@
         <v>18</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C424" s="7" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D424" s="10" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="E424" s="8">
         <v>40591</v>
@@ -23529,10 +23576,10 @@
       </c>
       <c r="L424" s="7"/>
       <c r="M424" s="6" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="N424" s="7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="O424" s="9"/>
       <c r="P424" s="9"/>
@@ -23544,13 +23591,13 @@
         <v>30</v>
       </c>
       <c r="B425" s="18" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C425" s="12" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D425" s="17" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="E425" s="13">
         <v>43230</v>
@@ -23573,10 +23620,10 @@
         <v>11</v>
       </c>
       <c r="M425" s="11" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N425" s="18" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="O425" s="14"/>
       <c r="P425" s="19" t="s">
@@ -23590,13 +23637,13 @@
         <v>18</v>
       </c>
       <c r="B426" s="7" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C426" s="7" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D426" s="6" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E426" s="8">
         <v>38391</v>
@@ -23613,7 +23660,7 @@
       </c>
       <c r="L426" s="7"/>
       <c r="M426" s="10" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="N426" s="7"/>
       <c r="O426" s="9"/>
@@ -23626,13 +23673,13 @@
         <v>18</v>
       </c>
       <c r="B427" s="12" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C427" s="12" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D427" s="11" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E427" s="13">
         <v>39022</v>
@@ -23668,13 +23715,13 @@
         <v>18</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C428" s="7" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D428" s="6" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E428" s="8">
         <v>39854</v>
@@ -23697,10 +23744,10 @@
       </c>
       <c r="L428" s="7"/>
       <c r="M428" s="6" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N428" s="7" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="O428" s="9"/>
       <c r="P428" s="9"/>
@@ -23712,13 +23759,13 @@
         <v>18</v>
       </c>
       <c r="B429" s="12" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C429" s="12" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D429" s="17" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E429" s="13">
         <v>39854</v>
@@ -23741,10 +23788,10 @@
       </c>
       <c r="L429" s="12"/>
       <c r="M429" s="11" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="N429" s="12" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="O429" s="14"/>
       <c r="P429" s="14"/>
@@ -23756,13 +23803,13 @@
         <v>30</v>
       </c>
       <c r="B430" s="15" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C430" s="7" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D430" s="6" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="E430" s="8">
         <v>41676</v>
@@ -23785,10 +23832,10 @@
         <v>11</v>
       </c>
       <c r="M430" s="6" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="N430" s="15" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="O430" s="9"/>
       <c r="P430" s="16" t="s">
@@ -23802,13 +23849,13 @@
         <v>30</v>
       </c>
       <c r="B431" s="18" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C431" s="12" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D431" s="11" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E431" s="13">
         <v>42593</v>
@@ -23831,10 +23878,10 @@
         <v>11</v>
       </c>
       <c r="M431" s="11" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N431" s="18" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="O431" s="14"/>
       <c r="P431" s="19" t="s">
@@ -23848,13 +23895,13 @@
         <v>18</v>
       </c>
       <c r="B432" s="7" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C432" s="7" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D432" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E432" s="8">
         <v>38391</v>
@@ -23871,10 +23918,10 @@
       </c>
       <c r="L432" s="7"/>
       <c r="M432" s="10" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="N432" s="7" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="O432" s="9"/>
       <c r="P432" s="9"/>
@@ -23886,13 +23933,13 @@
         <v>18</v>
       </c>
       <c r="B433" s="12" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C433" s="12" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D433" s="11" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E433" s="13">
         <v>39022</v>
@@ -23918,7 +23965,7 @@
         <v>471</v>
       </c>
       <c r="N433" s="12" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="O433" s="14"/>
       <c r="P433" s="14"/>
@@ -23930,13 +23977,13 @@
         <v>18</v>
       </c>
       <c r="B434" s="7" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C434" s="7" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D434" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E434" s="8">
         <v>41010</v>
@@ -23957,10 +24004,10 @@
       </c>
       <c r="L434" s="7"/>
       <c r="M434" s="6" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N434" s="7" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="O434" s="9"/>
       <c r="P434" s="9"/>
@@ -23972,13 +24019,13 @@
         <v>18</v>
       </c>
       <c r="B435" s="12" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C435" s="12" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D435" s="11" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E435" s="13">
         <v>41956</v>
@@ -24016,13 +24063,13 @@
         <v>18</v>
       </c>
       <c r="B436" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C436" s="7" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D436" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E436" s="8">
         <v>42047</v>
@@ -24047,10 +24094,10 @@
       </c>
       <c r="L436" s="7"/>
       <c r="M436" s="6" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="N436" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O436" s="9"/>
       <c r="P436" s="9"/>
@@ -24062,13 +24109,13 @@
         <v>18</v>
       </c>
       <c r="B437" s="12" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C437" s="12" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D437" s="11" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E437" s="13">
         <v>41038</v>
@@ -24085,10 +24132,10 @@
       </c>
       <c r="L437" s="12"/>
       <c r="M437" s="11" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N437" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O437" s="14"/>
       <c r="P437" s="14"/>
@@ -24100,13 +24147,13 @@
         <v>18</v>
       </c>
       <c r="B438" s="7" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C438" s="7" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D438" s="6" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E438" s="8">
         <v>38391</v>
@@ -24123,10 +24170,10 @@
       </c>
       <c r="L438" s="7"/>
       <c r="M438" s="10" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N438" s="7" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="O438" s="9"/>
       <c r="P438" s="9"/>
@@ -24138,13 +24185,13 @@
         <v>18</v>
       </c>
       <c r="B439" s="12" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C439" s="12" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D439" s="11" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="E439" s="13">
         <v>38931</v>
@@ -24161,7 +24208,7 @@
       </c>
       <c r="L439" s="12"/>
       <c r="M439" s="17" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N439" s="12" t="s">
         <v>1060</v>
@@ -24176,13 +24223,13 @@
         <v>18</v>
       </c>
       <c r="B440" s="7" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C440" s="7" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D440" s="6" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E440" s="8">
         <v>41956</v>
@@ -24207,10 +24254,10 @@
       </c>
       <c r="L440" s="7"/>
       <c r="M440" s="10" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N440" s="7" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="O440" s="9"/>
       <c r="P440" s="9"/>
@@ -24222,13 +24269,13 @@
         <v>18</v>
       </c>
       <c r="B441" s="12" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C441" s="12" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D441" s="11" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E441" s="13">
         <v>44329</v>
@@ -24251,7 +24298,7 @@
       </c>
       <c r="L441" s="12"/>
       <c r="M441" s="11" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N441" s="12" t="s">
         <v>459</v>
@@ -24266,13 +24313,13 @@
         <v>18</v>
       </c>
       <c r="B442" s="7" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C442" s="7" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D442" s="10" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E442" s="8">
         <v>44973</v>
@@ -24295,10 +24342,10 @@
       </c>
       <c r="L442" s="7"/>
       <c r="M442" s="6" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="N442" s="7" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="O442" s="9"/>
       <c r="P442" s="9"/>
@@ -24310,13 +24357,13 @@
         <v>30</v>
       </c>
       <c r="B443" s="18" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C443" s="12" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D443" s="11" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E443" s="13">
         <v>45573</v>
@@ -24339,10 +24386,10 @@
         <v>11</v>
       </c>
       <c r="M443" s="11" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="N443" s="18" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="O443" s="14"/>
       <c r="P443" s="19" t="s">
@@ -24358,13 +24405,13 @@
         <v>18</v>
       </c>
       <c r="B444" s="7" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C444" s="7" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D444" s="6" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="E444" s="8">
         <v>40486</v>
@@ -24387,7 +24434,7 @@
       </c>
       <c r="L444" s="7"/>
       <c r="M444" s="6" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N444" s="7"/>
       <c r="O444" s="9"/>
@@ -24400,13 +24447,13 @@
         <v>18</v>
       </c>
       <c r="B445" s="12" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C445" s="12" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D445" s="11" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E445" s="13">
         <v>38391</v>
@@ -24421,7 +24468,7 @@
       </c>
       <c r="L445" s="12"/>
       <c r="M445" s="11" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N445" s="12"/>
       <c r="O445" s="14"/>
@@ -24434,13 +24481,13 @@
         <v>18</v>
       </c>
       <c r="B446" s="7" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C446" s="7" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D446" s="6" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="E446" s="8">
         <v>38755</v>
@@ -24472,13 +24519,13 @@
         <v>18</v>
       </c>
       <c r="B447" s="12" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C447" s="12" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D447" s="11" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E447" s="13">
         <v>38391</v>
@@ -24508,13 +24555,13 @@
         <v>18</v>
       </c>
       <c r="B448" s="7" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C448" s="7" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D448" s="6" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E448" s="8">
         <v>38755</v>
@@ -24540,7 +24587,7 @@
         <v>45</v>
       </c>
       <c r="N448" s="7" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="O448" s="9"/>
       <c r="P448" s="9"/>
@@ -24552,13 +24599,13 @@
         <v>18</v>
       </c>
       <c r="B449" s="12" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C449" s="12" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D449" s="11" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E449" s="13">
         <v>40591</v>
@@ -24581,10 +24628,10 @@
       </c>
       <c r="L449" s="12"/>
       <c r="M449" s="11" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N449" s="12" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="O449" s="14"/>
       <c r="P449" s="14"/>
@@ -24596,13 +24643,13 @@
         <v>18</v>
       </c>
       <c r="B450" s="7" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C450" s="7" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D450" s="6" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E450" s="8">
         <v>40395</v>
@@ -24626,7 +24673,7 @@
         <v>47</v>
       </c>
       <c r="N450" s="7" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O450" s="9"/>
       <c r="P450" s="9"/>
@@ -24638,13 +24685,13 @@
         <v>18</v>
       </c>
       <c r="B451" s="12" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C451" s="12" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D451" s="11" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E451" s="13">
         <v>40948</v>
@@ -24667,10 +24714,10 @@
       </c>
       <c r="L451" s="12"/>
       <c r="M451" s="11" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N451" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O451" s="14"/>
       <c r="P451" s="14"/>
@@ -24682,13 +24729,13 @@
         <v>18</v>
       </c>
       <c r="B452" s="7" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C452" s="7" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D452" s="6" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E452" s="8">
         <v>41956</v>
@@ -24711,10 +24758,10 @@
       </c>
       <c r="L452" s="7"/>
       <c r="M452" s="6" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N452" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O452" s="9"/>
       <c r="P452" s="9"/>
@@ -24726,13 +24773,13 @@
         <v>18</v>
       </c>
       <c r="B453" s="12" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="C453" s="12" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D453" s="11" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E453" s="13">
         <v>40591</v>
@@ -24755,7 +24802,7 @@
       </c>
       <c r="L453" s="12"/>
       <c r="M453" s="11" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N453" s="12" t="s">
         <v>48</v>
@@ -24770,13 +24817,13 @@
         <v>18</v>
       </c>
       <c r="B454" s="7" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C454" s="7" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D454" s="6" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E454" s="8">
         <v>41865</v>
@@ -24799,10 +24846,10 @@
       </c>
       <c r="L454" s="7"/>
       <c r="M454" s="10" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="N454" s="7" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="O454" s="9"/>
       <c r="P454" s="9"/>
@@ -24814,13 +24861,13 @@
         <v>18</v>
       </c>
       <c r="B455" s="12" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C455" s="12" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D455" s="11" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E455" s="13">
         <v>42177</v>
@@ -24843,7 +24890,7 @@
       </c>
       <c r="L455" s="12"/>
       <c r="M455" s="17" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="N455" s="12" t="s">
         <v>13</v>
@@ -24858,13 +24905,13 @@
         <v>18</v>
       </c>
       <c r="B456" s="7" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C456" s="7" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D456" s="6" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E456" s="8">
         <v>41956</v>
@@ -24885,10 +24932,10 @@
       </c>
       <c r="L456" s="7"/>
       <c r="M456" s="10" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N456" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O456" s="9"/>
       <c r="P456" s="9"/>
@@ -24900,13 +24947,13 @@
         <v>18</v>
       </c>
       <c r="B457" s="12" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C457" s="12" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D457" s="11" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E457" s="13">
         <v>42177</v>
@@ -24929,10 +24976,10 @@
       </c>
       <c r="L457" s="12"/>
       <c r="M457" s="11" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N457" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O457" s="14"/>
       <c r="P457" s="14"/>
@@ -24944,13 +24991,13 @@
         <v>18</v>
       </c>
       <c r="B458" s="7" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="C458" s="7" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D458" s="6" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E458" s="8">
         <v>42131</v>
@@ -24973,10 +25020,10 @@
       </c>
       <c r="L458" s="7"/>
       <c r="M458" s="10" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N458" s="7" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="O458" s="9"/>
       <c r="P458" s="9"/>
@@ -24988,13 +25035,13 @@
         <v>18</v>
       </c>
       <c r="B459" s="12" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C459" s="12" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D459" s="11" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E459" s="13">
         <v>42177</v>
@@ -25017,10 +25064,10 @@
       </c>
       <c r="L459" s="12"/>
       <c r="M459" s="11" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N459" s="12" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="O459" s="14"/>
       <c r="P459" s="14"/>
@@ -25032,13 +25079,13 @@
         <v>30</v>
       </c>
       <c r="B460" s="15" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C460" s="7" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D460" s="6" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E460" s="8">
         <v>43594</v>
@@ -25061,7 +25108,7 @@
         <v>11</v>
       </c>
       <c r="M460" s="6" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N460" s="15" t="s">
         <v>692</v>
@@ -25080,13 +25127,13 @@
         <v>18</v>
       </c>
       <c r="B461" s="12" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C461" s="12" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D461" s="11" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="E461" s="13">
         <v>39750</v>
@@ -25124,13 +25171,13 @@
         <v>18</v>
       </c>
       <c r="B462" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C462" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D462" s="6" t="s">
         <v>1311</v>
-      </c>
-      <c r="C462" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D462" s="6" t="s">
-        <v>1310</v>
       </c>
       <c r="E462" s="8">
         <v>41956</v>
@@ -25168,13 +25215,13 @@
         <v>18</v>
       </c>
       <c r="B463" s="12" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C463" s="12" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D463" s="17" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E463" s="13">
         <v>38391</v>
@@ -25189,7 +25236,7 @@
       </c>
       <c r="L463" s="12"/>
       <c r="M463" s="11" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="N463" s="12"/>
       <c r="O463" s="14"/>
@@ -25202,13 +25249,13 @@
         <v>18</v>
       </c>
       <c r="B464" s="7" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C464" s="7" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D464" s="6" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E464" s="8">
         <v>38755</v>
@@ -25244,13 +25291,13 @@
         <v>18</v>
       </c>
       <c r="B465" s="12" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C465" s="12" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D465" s="11" t="s">
         <v>1319</v>
-      </c>
-      <c r="C465" s="12" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D465" s="11" t="s">
-        <v>1318</v>
       </c>
       <c r="E465" s="13">
         <v>41038</v>
@@ -25273,10 +25320,10 @@
       </c>
       <c r="L465" s="12"/>
       <c r="M465" s="11" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N465" s="18" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="O465" s="14"/>
       <c r="P465" s="14"/>
@@ -25288,13 +25335,13 @@
         <v>18</v>
       </c>
       <c r="B466" s="7" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C466" s="7" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E466" s="8">
         <v>40591</v>
@@ -25317,7 +25364,7 @@
       </c>
       <c r="L466" s="7"/>
       <c r="M466" s="6" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N466" s="7"/>
       <c r="O466" s="9"/>
@@ -25330,13 +25377,13 @@
         <v>18</v>
       </c>
       <c r="B467" s="12" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C467" s="12" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D467" s="11" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E467" s="13">
         <v>40122</v>
@@ -25359,7 +25406,7 @@
       </c>
       <c r="L467" s="12"/>
       <c r="M467" s="11" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="N467" s="12"/>
       <c r="O467" s="14"/>
@@ -25372,13 +25419,13 @@
         <v>18</v>
       </c>
       <c r="B468" s="7" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C468" s="7" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D468" s="6" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E468" s="8">
         <v>41220</v>
@@ -25401,10 +25448,10 @@
       </c>
       <c r="L468" s="7"/>
       <c r="M468" s="6" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="N468" s="7" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="O468" s="9"/>
       <c r="P468" s="9"/>
@@ -25416,13 +25463,13 @@
         <v>18</v>
       </c>
       <c r="B469" s="12" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C469" s="12" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D469" s="11" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E469" s="13">
         <v>41956</v>
@@ -25445,10 +25492,10 @@
       </c>
       <c r="L469" s="12"/>
       <c r="M469" s="11" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="N469" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O469" s="14"/>
       <c r="P469" s="14"/>
@@ -25460,13 +25507,13 @@
         <v>18</v>
       </c>
       <c r="B470" s="7" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C470" s="7" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D470" s="6" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E470" s="8">
         <v>41956</v>
@@ -25487,7 +25534,7 @@
       </c>
       <c r="L470" s="7"/>
       <c r="M470" s="10" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="N470" s="7" t="s">
         <v>191</v>
@@ -25502,13 +25549,13 @@
         <v>18</v>
       </c>
       <c r="B471" s="12" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C471" s="12" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D471" s="11" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E471" s="13">
         <v>41585</v>
@@ -25525,10 +25572,10 @@
       </c>
       <c r="L471" s="12"/>
       <c r="M471" s="11" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N471" s="12" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="O471" s="14"/>
       <c r="P471" s="14"/>
@@ -25540,13 +25587,13 @@
         <v>18</v>
       </c>
       <c r="B472" s="7" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C472" s="7" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D472" s="6" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E472" s="8">
         <v>41956</v>
@@ -25563,10 +25610,10 @@
       </c>
       <c r="L472" s="7"/>
       <c r="M472" s="10" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N472" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O472" s="9"/>
       <c r="P472" s="9"/>
@@ -25578,13 +25625,13 @@
         <v>18</v>
       </c>
       <c r="B473" s="12" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C473" s="12" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D473" s="11" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E473" s="13">
         <v>41956</v>
@@ -25605,10 +25652,10 @@
       </c>
       <c r="L473" s="12"/>
       <c r="M473" s="17" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="N473" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O473" s="14"/>
       <c r="P473" s="14"/>
@@ -25620,13 +25667,13 @@
         <v>18</v>
       </c>
       <c r="B474" s="7" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C474" s="7" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D474" s="6" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E474" s="8">
         <v>41956</v>
@@ -25643,10 +25690,10 @@
       </c>
       <c r="L474" s="7"/>
       <c r="M474" s="6" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="N474" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O474" s="9"/>
       <c r="P474" s="9"/>
@@ -25658,13 +25705,13 @@
         <v>18</v>
       </c>
       <c r="B475" s="12" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C475" s="12" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D475" s="11" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E475" s="13">
         <v>42131</v>
@@ -25683,10 +25730,10 @@
       </c>
       <c r="L475" s="12"/>
       <c r="M475" s="11" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="N475" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O475" s="14"/>
       <c r="P475" s="14"/>
@@ -25698,13 +25745,13 @@
         <v>30</v>
       </c>
       <c r="B476" s="15" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C476" s="7" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D476" s="6" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E476" s="8">
         <v>42313</v>
@@ -25729,10 +25776,10 @@
         <v>11</v>
       </c>
       <c r="M476" s="10" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="N476" s="15" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="O476" s="9"/>
       <c r="P476" s="16" t="s">
@@ -25748,13 +25795,13 @@
         <v>18</v>
       </c>
       <c r="B477" s="12" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C477" s="12" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D477" s="11" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E477" s="13">
         <v>38391</v>
@@ -25784,13 +25831,13 @@
         <v>18</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C478" s="7" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D478" s="6" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E478" s="8">
         <v>40486</v>
@@ -25828,13 +25875,13 @@
         <v>18</v>
       </c>
       <c r="B479" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C479" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D479" s="11" t="s">
         <v>1356</v>
-      </c>
-      <c r="C479" s="12" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D479" s="11" t="s">
-        <v>1355</v>
       </c>
       <c r="E479" s="13">
         <v>41956</v>
@@ -25857,10 +25904,10 @@
       </c>
       <c r="L479" s="12"/>
       <c r="M479" s="11" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="N479" s="12" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="O479" s="14"/>
       <c r="P479" s="14"/>
@@ -25872,13 +25919,13 @@
         <v>18</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C480" s="7" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D480" s="6" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E480" s="8">
         <v>42957</v>
@@ -25901,7 +25948,7 @@
       </c>
       <c r="L480" s="7"/>
       <c r="M480" s="10" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="N480" s="7" t="s">
         <v>68</v>
@@ -25916,13 +25963,13 @@
         <v>18</v>
       </c>
       <c r="B481" s="12" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C481" s="12" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D481" s="11" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E481" s="13">
         <v>43867</v>
@@ -25954,13 +26001,13 @@
         <v>30</v>
       </c>
       <c r="B482" s="15" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C482" s="7" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D482" s="6" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E482" s="8">
         <v>44063</v>
@@ -25983,7 +26030,7 @@
         <v>11</v>
       </c>
       <c r="M482" s="6" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="N482" s="15" t="s">
         <v>68</v>
@@ -26000,13 +26047,13 @@
         <v>18</v>
       </c>
       <c r="B483" s="12" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C483" s="12" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D483" s="17" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E483" s="13">
         <v>40948</v>
@@ -26032,7 +26079,7 @@
       <c r="L483" s="12"/>
       <c r="M483" s="11"/>
       <c r="N483" s="12" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O483" s="14"/>
       <c r="P483" s="14"/>
@@ -26044,13 +26091,13 @@
         <v>30</v>
       </c>
       <c r="B484" s="15" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C484" s="7" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D484" s="10" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="E484" s="8">
         <v>43785</v>
@@ -26075,10 +26122,10 @@
         <v>11</v>
       </c>
       <c r="M484" s="6" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="N484" s="15" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O484" s="9"/>
       <c r="P484" s="9"/>
@@ -26090,13 +26137,13 @@
         <v>18</v>
       </c>
       <c r="B485" s="12" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C485" s="12" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D485" s="11" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="E485" s="13">
         <v>40850</v>
@@ -26119,10 +26166,10 @@
       </c>
       <c r="L485" s="12"/>
       <c r="M485" s="11" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="N485" s="12" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="O485" s="14"/>
       <c r="P485" s="14"/>
@@ -26134,13 +26181,13 @@
         <v>18</v>
       </c>
       <c r="B486" s="7" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="C486" s="7" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D486" s="6" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="E486" s="8">
         <v>42957</v>
@@ -26163,10 +26210,10 @@
       </c>
       <c r="L486" s="7"/>
       <c r="M486" s="6" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="N486" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="O486" s="9"/>
       <c r="P486" s="9"/>
@@ -26178,13 +26225,13 @@
         <v>30</v>
       </c>
       <c r="B487" s="18" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C487" s="12" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D487" s="17" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E487" s="13">
         <v>44504</v>
@@ -26207,10 +26254,10 @@
         <v>11</v>
       </c>
       <c r="M487" s="11" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="N487" s="18" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="O487" s="14"/>
       <c r="P487" s="14"/>
@@ -26222,13 +26269,13 @@
         <v>18</v>
       </c>
       <c r="B488" s="7" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C488" s="7" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D488" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="E488" s="8">
         <v>41220</v>
@@ -26245,10 +26292,10 @@
       </c>
       <c r="L488" s="7"/>
       <c r="M488" s="10" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="N488" s="7" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="O488" s="9"/>
       <c r="P488" s="9"/>
@@ -26260,13 +26307,13 @@
         <v>18</v>
       </c>
       <c r="B489" s="12" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C489" s="12" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="D489" s="11" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="E489" s="13">
         <v>38391</v>
@@ -26304,13 +26351,13 @@
         <v>30</v>
       </c>
       <c r="B490" s="15" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C490" s="7" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D490" s="6" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E490" s="8">
         <v>38391</v>
@@ -26352,13 +26399,13 @@
         <v>18</v>
       </c>
       <c r="B491" s="12" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="C491" s="12" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="D491" s="11" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="E491" s="13">
         <v>38391</v>
@@ -26396,13 +26443,13 @@
         <v>18</v>
       </c>
       <c r="B492" s="7" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C492" s="7" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="D492" s="6" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="E492" s="8">
         <v>38391</v>
@@ -26440,13 +26487,13 @@
         <v>18</v>
       </c>
       <c r="B493" s="12" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="C493" s="12" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="D493" s="11" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E493" s="13">
         <v>41956</v>
@@ -26469,10 +26516,10 @@
       </c>
       <c r="L493" s="12"/>
       <c r="M493" s="11" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="N493" s="12" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="O493" s="14"/>
       <c r="P493" s="14"/>
@@ -26484,13 +26531,13 @@
         <v>30</v>
       </c>
       <c r="B494" s="15" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C494" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="D494" s="6" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E494" s="8">
         <v>42131</v>
@@ -26513,10 +26560,10 @@
         <v>11</v>
       </c>
       <c r="M494" s="6" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="N494" s="15" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="O494" s="9"/>
       <c r="P494" s="16" t="s">
@@ -26530,13 +26577,13 @@
         <v>30</v>
       </c>
       <c r="B495" s="18" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C495" s="12" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D495" s="11" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="E495" s="13">
         <v>38391</v>
@@ -26578,13 +26625,13 @@
         <v>18</v>
       </c>
       <c r="B496" s="7" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C496" s="7" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D496" s="10" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E496" s="8">
         <v>38391</v>
@@ -26616,13 +26663,13 @@
         <v>18</v>
       </c>
       <c r="B497" s="12" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C497" s="12" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D497" s="17" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E497" s="13">
         <v>41956</v>
@@ -26654,13 +26701,13 @@
         <v>30</v>
       </c>
       <c r="B498" s="15" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="C498" s="7" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="D498" s="6" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E498" s="8">
         <v>42495</v>
@@ -26683,10 +26730,10 @@
         <v>11</v>
       </c>
       <c r="M498" s="6" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="N498" s="15" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="O498" s="9"/>
       <c r="P498" s="16" t="s">
@@ -26700,13 +26747,13 @@
         <v>18</v>
       </c>
       <c r="B499" s="12" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C499" s="12" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D499" s="11" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E499" s="13">
         <v>38391</v>
@@ -26738,13 +26785,13 @@
         <v>18</v>
       </c>
       <c r="B500" s="7" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C500" s="7" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D500" s="6" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E500" s="8">
         <v>41956</v>
@@ -26776,13 +26823,13 @@
         <v>18</v>
       </c>
       <c r="B501" s="12" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C501" s="12" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D501" s="17" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="E501" s="13">
         <v>38391</v>
@@ -26814,13 +26861,13 @@
         <v>18</v>
       </c>
       <c r="B502" s="7" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C502" s="7" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D502" s="10" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E502" s="8">
         <v>41956</v>
@@ -26852,13 +26899,13 @@
         <v>18</v>
       </c>
       <c r="B503" s="12" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C503" s="12" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D503" s="17" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E503" s="13">
         <v>38391</v>
@@ -26896,13 +26943,13 @@
         <v>18</v>
       </c>
       <c r="B504" s="7" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C504" s="7" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="D504" s="10" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E504" s="8">
         <v>41956</v>
@@ -26940,13 +26987,13 @@
         <v>18</v>
       </c>
       <c r="B505" s="12" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C505" s="12" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D505" s="17" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E505" s="13">
         <v>38391</v>
@@ -26982,13 +27029,13 @@
         <v>18</v>
       </c>
       <c r="B506" s="7" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C506" s="7" t="s">
         <v>1433</v>
       </c>
-      <c r="C506" s="7" t="s">
-        <v>1432</v>
-      </c>
       <c r="D506" s="10" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E506" s="8">
         <v>39750</v>
@@ -27026,13 +27073,13 @@
         <v>18</v>
       </c>
       <c r="B507" s="12" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C507" s="12" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D507" s="17" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E507" s="13">
         <v>41956</v>
@@ -27070,13 +27117,13 @@
         <v>18</v>
       </c>
       <c r="B508" s="7" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C508" s="7" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D508" s="10" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E508" s="8">
         <v>38391</v>
@@ -27114,13 +27161,13 @@
         <v>30</v>
       </c>
       <c r="B509" s="18" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="C509" s="12" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D509" s="17" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E509" s="13">
         <v>41956</v>
@@ -27162,13 +27209,13 @@
         <v>18</v>
       </c>
       <c r="B510" s="7" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C510" s="7" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D510" s="6" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E510" s="8">
         <v>38931</v>
@@ -27194,7 +27241,7 @@
         <v>260</v>
       </c>
       <c r="N510" s="7" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="O510" s="9"/>
       <c r="P510" s="9"/>
@@ -27206,13 +27253,13 @@
         <v>18</v>
       </c>
       <c r="B511" s="12" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C511" s="12" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="D511" s="11" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="E511" s="13">
         <v>41312</v>
@@ -27235,7 +27282,7 @@
       </c>
       <c r="L511" s="12"/>
       <c r="M511" s="17" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="N511" s="12" t="s">
         <v>1108</v>
@@ -27250,13 +27297,13 @@
         <v>30</v>
       </c>
       <c r="B512" s="15" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C512" s="7" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="D512" s="6" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="E512" s="8">
         <v>42047</v>
@@ -27279,10 +27326,10 @@
         <v>11</v>
       </c>
       <c r="M512" s="10" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="N512" s="15" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O512" s="9"/>
       <c r="P512" s="16" t="s">
@@ -27298,13 +27345,13 @@
         <v>18</v>
       </c>
       <c r="B513" s="12" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C513" s="12" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D513" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="E513" s="13">
         <v>38755</v>
@@ -27324,7 +27371,7 @@
         <v>45</v>
       </c>
       <c r="N513" s="12" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="O513" s="14"/>
       <c r="P513" s="14"/>
@@ -27336,13 +27383,13 @@
         <v>18</v>
       </c>
       <c r="B514" s="7" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C514" s="7" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D514" s="10" t="s">
         <v>1454</v>
-      </c>
-      <c r="C514" s="7" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D514" s="10" t="s">
-        <v>1453</v>
       </c>
       <c r="E514" s="8">
         <v>41956</v>
@@ -27372,13 +27419,13 @@
         <v>18</v>
       </c>
       <c r="B515" s="12" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C515" s="12" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="D515" s="11" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="E515" s="13">
         <v>38755</v>
@@ -27416,13 +27463,13 @@
         <v>18</v>
       </c>
       <c r="B516" s="7" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C516" s="7" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D516" s="6" t="s">
         <v>1458</v>
-      </c>
-      <c r="C516" s="7" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D516" s="6" t="s">
-        <v>1457</v>
       </c>
       <c r="E516" s="8">
         <v>41956</v>
@@ -27452,13 +27499,13 @@
         <v>18</v>
       </c>
       <c r="B517" s="12" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C517" s="12" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D517" s="11" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="E517" s="13">
         <v>38755</v>
@@ -27496,13 +27543,13 @@
         <v>18</v>
       </c>
       <c r="B518" s="7" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C518" s="7" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D518" s="10" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E518" s="8">
         <v>39490</v>
@@ -27525,10 +27572,10 @@
       </c>
       <c r="L518" s="7"/>
       <c r="M518" s="6" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="N518" s="7" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="O518" s="9"/>
       <c r="P518" s="9"/>
@@ -27540,13 +27587,13 @@
         <v>18</v>
       </c>
       <c r="B519" s="12" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C519" s="12" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D519" s="17" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E519" s="13">
         <v>40612</v>
@@ -27569,10 +27616,10 @@
       </c>
       <c r="L519" s="12"/>
       <c r="M519" s="11" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="N519" s="12" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="O519" s="14"/>
       <c r="P519" s="14"/>
@@ -27584,13 +27631,13 @@
         <v>18</v>
       </c>
       <c r="B520" s="7" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C520" s="7" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D520" s="10" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E520" s="8">
         <v>41585</v>
@@ -27613,10 +27660,10 @@
       </c>
       <c r="L520" s="7"/>
       <c r="M520" s="6" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="N520" s="7" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="O520" s="9"/>
       <c r="P520" s="9"/>
@@ -27628,13 +27675,13 @@
         <v>18</v>
       </c>
       <c r="B521" s="12" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C521" s="12" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D521" s="17" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E521" s="13">
         <v>41956</v>
@@ -27672,13 +27719,13 @@
         <v>18</v>
       </c>
       <c r="B522" s="7" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C522" s="7" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D522" s="10" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E522" s="8">
         <v>44329</v>
@@ -27701,7 +27748,7 @@
       </c>
       <c r="L522" s="7"/>
       <c r="M522" s="6" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N522" s="7" t="s">
         <v>459</v>
@@ -27716,13 +27763,13 @@
         <v>30</v>
       </c>
       <c r="B523" s="18" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C523" s="12" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D523" s="17" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="E523" s="13">
         <v>44973</v>
@@ -27745,10 +27792,10 @@
         <v>11</v>
       </c>
       <c r="M523" s="17" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="N523" s="18" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="O523" s="14"/>
       <c r="P523" s="19" t="s">
@@ -27766,13 +27813,13 @@
         <v>18</v>
       </c>
       <c r="B524" s="7" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C524" s="7" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="D524" s="6" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E524" s="8">
         <v>41403</v>
@@ -27795,10 +27842,10 @@
       </c>
       <c r="L524" s="7"/>
       <c r="M524" s="10" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="N524" s="7" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="O524" s="9"/>
       <c r="P524" s="9"/>
@@ -27810,13 +27857,13 @@
         <v>18</v>
       </c>
       <c r="B525" s="12" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C525" s="12" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="D525" s="11" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E525" s="13">
         <v>42047</v>
@@ -27839,10 +27886,10 @@
       </c>
       <c r="L525" s="12"/>
       <c r="M525" s="17" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="N525" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O525" s="14"/>
       <c r="P525" s="14"/>
@@ -27854,13 +27901,13 @@
         <v>30</v>
       </c>
       <c r="B526" s="15" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C526" s="7" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="D526" s="6" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E526" s="8">
         <v>43867</v>
@@ -27885,10 +27932,10 @@
         <v>11</v>
       </c>
       <c r="M526" s="6" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="N526" s="15" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="O526" s="9"/>
       <c r="P526" s="16" t="s">
@@ -27902,13 +27949,13 @@
         <v>139</v>
       </c>
       <c r="B527" s="18" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C527" s="12" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D527" s="11" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="E527" s="13">
         <v>45573</v>
@@ -27931,10 +27978,10 @@
         <v>11</v>
       </c>
       <c r="M527" s="17" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="N527" s="18" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="O527" s="14"/>
       <c r="P527" s="14"/>
@@ -27948,13 +27995,13 @@
         <v>18</v>
       </c>
       <c r="B528" s="7" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C528" s="7" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="D528" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="E528" s="8">
         <v>41501</v>
@@ -27977,10 +28024,10 @@
       </c>
       <c r="L528" s="7"/>
       <c r="M528" s="10" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="N528" s="7" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="O528" s="9"/>
       <c r="P528" s="9"/>
@@ -27992,13 +28039,13 @@
         <v>30</v>
       </c>
       <c r="B529" s="18" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C529" s="12" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="D529" s="11" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="E529" s="13">
         <v>43139</v>
@@ -28023,10 +28070,10 @@
         <v>11</v>
       </c>
       <c r="M529" s="11" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="N529" s="18" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="O529" s="14"/>
       <c r="P529" s="19" t="s">
@@ -28040,13 +28087,13 @@
         <v>18</v>
       </c>
       <c r="B530" s="7" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C530" s="7" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="D530" s="6" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="E530" s="8">
         <v>41990</v>
@@ -28071,10 +28118,10 @@
       </c>
       <c r="L530" s="7"/>
       <c r="M530" s="10" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="N530" s="7" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="O530" s="9"/>
       <c r="P530" s="9"/>
@@ -28086,13 +28133,13 @@
         <v>30</v>
       </c>
       <c r="B531" s="18" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C531" s="12" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="D531" s="11" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="E531" s="13">
         <v>44329</v>
@@ -28117,7 +28164,7 @@
         <v>11</v>
       </c>
       <c r="M531" s="11" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N531" s="18" t="s">
         <v>459</v>
@@ -28134,13 +28181,13 @@
         <v>30</v>
       </c>
       <c r="B532" s="15" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C532" s="7" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="D532" s="6" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="E532" s="8">
         <v>42313</v>
@@ -28163,10 +28210,10 @@
         <v>11</v>
       </c>
       <c r="M532" s="6" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N532" s="15" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="O532" s="9"/>
       <c r="P532" s="16" t="s">
@@ -28180,13 +28227,13 @@
         <v>30</v>
       </c>
       <c r="B533" s="18" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C533" s="12" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D533" s="11" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="E533" s="13">
         <v>45573</v>
@@ -28211,10 +28258,10 @@
         <v>11</v>
       </c>
       <c r="M533" s="11" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="N533" s="18" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="O533" s="14"/>
       <c r="P533" s="19" t="s">
@@ -28230,13 +28277,13 @@
         <v>139</v>
       </c>
       <c r="B534" s="15" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C534" s="7" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="D534" s="6" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="E534" s="8">
         <v>45573</v>
@@ -28261,10 +28308,10 @@
         <v>11</v>
       </c>
       <c r="M534" s="10" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="N534" s="15" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="O534" s="9"/>
       <c r="P534" s="9"/>
@@ -28278,13 +28325,13 @@
         <v>139</v>
       </c>
       <c r="B535" s="18" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C535" s="12" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D535" s="11" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="E535" s="13">
         <v>45573</v>
@@ -28309,10 +28356,10 @@
         <v>11</v>
       </c>
       <c r="M535" s="17" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="N535" s="18" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="O535" s="14"/>
       <c r="P535" s="14"/>
@@ -28326,13 +28373,13 @@
         <v>18</v>
       </c>
       <c r="B536" s="7" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C536" s="7" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="D536" s="6" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="E536" s="8">
         <v>39153</v>
@@ -28368,13 +28415,13 @@
         <v>18</v>
       </c>
       <c r="B537" s="12" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="C537" s="12" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D537" s="17" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="E537" s="13">
         <v>39153</v>
@@ -28410,13 +28457,13 @@
         <v>18</v>
       </c>
       <c r="B538" s="7" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C538" s="7" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D538" s="6" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="E538" s="8">
         <v>39153</v>
@@ -28452,13 +28499,13 @@
         <v>18</v>
       </c>
       <c r="B539" s="12" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="C539" s="12" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D539" s="11" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="E539" s="13">
         <v>38391</v>
@@ -28488,13 +28535,13 @@
         <v>18</v>
       </c>
       <c r="B540" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C540" s="7" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D540" s="6" t="s">
         <v>1534</v>
-      </c>
-      <c r="C540" s="7" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D540" s="6" t="s">
-        <v>1533</v>
       </c>
       <c r="E540" s="8">
         <v>39022</v>
@@ -28530,13 +28577,13 @@
         <v>18</v>
       </c>
       <c r="B541" s="12" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="C541" s="12" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="D541" s="11" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="E541" s="13">
         <v>40310</v>
@@ -28559,10 +28606,10 @@
       </c>
       <c r="L541" s="12"/>
       <c r="M541" s="11" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="N541" s="12" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="O541" s="14"/>
       <c r="P541" s="14"/>
@@ -28574,13 +28621,13 @@
         <v>18</v>
       </c>
       <c r="B542" s="7" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="C542" s="7" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D542" s="6" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="E542" s="8">
         <v>41038</v>
@@ -28597,10 +28644,10 @@
       </c>
       <c r="L542" s="7"/>
       <c r="M542" s="6" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N542" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O542" s="9"/>
       <c r="P542" s="9"/>
@@ -28612,13 +28659,13 @@
         <v>18</v>
       </c>
       <c r="B543" s="12" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="C543" s="12" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D543" s="11" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="E543" s="13">
         <v>42047</v>
@@ -28656,13 +28703,13 @@
         <v>18</v>
       </c>
       <c r="B544" s="7" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C544" s="7" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D544" s="6" t="s">
         <v>1543</v>
-      </c>
-      <c r="C544" s="7" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D544" s="6" t="s">
-        <v>1542</v>
       </c>
       <c r="E544" s="8">
         <v>42775</v>
@@ -28685,7 +28732,7 @@
       </c>
       <c r="L544" s="7"/>
       <c r="M544" s="6" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="N544" s="7" t="s">
         <v>861</v>
@@ -28700,13 +28747,13 @@
         <v>18</v>
       </c>
       <c r="B545" s="12" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C545" s="12" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D545" s="11" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="E545" s="13">
         <v>43594</v>
@@ -28729,7 +28776,7 @@
       </c>
       <c r="L545" s="12"/>
       <c r="M545" s="11" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="N545" s="12" t="s">
         <v>692</v>
@@ -28744,13 +28791,13 @@
         <v>30</v>
       </c>
       <c r="B546" s="15" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="C546" s="7" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D546" s="6" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="E546" s="8">
         <v>44329</v>
@@ -28773,7 +28820,7 @@
         <v>11</v>
       </c>
       <c r="M546" s="6" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N546" s="15" t="s">
         <v>459</v>
@@ -28792,13 +28839,13 @@
         <v>18</v>
       </c>
       <c r="B547" s="12" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="C547" s="12" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D547" s="11" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E547" s="13">
         <v>38391</v>
@@ -28828,13 +28875,13 @@
         <v>18</v>
       </c>
       <c r="B548" s="7" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C548" s="7" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D548" s="6" t="s">
         <v>1551</v>
-      </c>
-      <c r="C548" s="7" t="s">
-        <v>1549</v>
-      </c>
-      <c r="D548" s="6" t="s">
-        <v>1550</v>
       </c>
       <c r="E548" s="8">
         <v>38931</v>
@@ -28849,7 +28896,7 @@
       </c>
       <c r="L548" s="7"/>
       <c r="M548" s="6" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="N548" s="7"/>
       <c r="O548" s="9"/>
@@ -28862,13 +28909,13 @@
         <v>18</v>
       </c>
       <c r="B549" s="12" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C549" s="12" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D549" s="11" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E549" s="13">
         <v>39022</v>
@@ -28904,13 +28951,13 @@
         <v>18</v>
       </c>
       <c r="B550" s="7" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="C550" s="7" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D550" s="6" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E550" s="8">
         <v>41010</v>
@@ -28936,7 +28983,7 @@
         <v>118</v>
       </c>
       <c r="N550" s="7" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="O550" s="9"/>
       <c r="P550" s="9"/>
@@ -28948,13 +28995,13 @@
         <v>18</v>
       </c>
       <c r="B551" s="12" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="C551" s="12" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D551" s="11" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E551" s="13">
         <v>39854</v>
@@ -28990,13 +29037,13 @@
         <v>18</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C552" s="7" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D552" s="6" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E552" s="8">
         <v>40486</v>
@@ -29019,7 +29066,7 @@
       </c>
       <c r="L552" s="7"/>
       <c r="M552" s="6" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="N552" s="7"/>
       <c r="O552" s="9"/>
@@ -29032,13 +29079,13 @@
         <v>18</v>
       </c>
       <c r="B553" s="12" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="C553" s="12" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="D553" s="11" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="E553" s="13">
         <v>41038</v>
@@ -29055,10 +29102,10 @@
       </c>
       <c r="L553" s="12"/>
       <c r="M553" s="11" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N553" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O553" s="14"/>
       <c r="P553" s="14"/>
@@ -29070,13 +29117,13 @@
         <v>18</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="C554" s="7" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="D554" s="6" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="E554" s="8">
         <v>41956</v>
@@ -29114,13 +29161,13 @@
         <v>30</v>
       </c>
       <c r="B555" s="18" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C555" s="12" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D555" s="11" t="s">
         <v>1563</v>
-      </c>
-      <c r="C555" s="12" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D555" s="11" t="s">
-        <v>1562</v>
       </c>
       <c r="E555" s="13">
         <v>45222</v>
@@ -29143,7 +29190,7 @@
         <v>11</v>
       </c>
       <c r="M555" s="11" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="N555" s="18" t="s">
         <v>607</v>
@@ -29162,13 +29209,13 @@
         <v>18</v>
       </c>
       <c r="B556" s="7" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="C556" s="7" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="D556" s="6" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="E556" s="8">
         <v>38391</v>
@@ -29204,13 +29251,13 @@
         <v>18</v>
       </c>
       <c r="B557" s="12" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C557" s="12" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D557" s="11" t="s">
         <v>1568</v>
-      </c>
-      <c r="C557" s="12" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D557" s="11" t="s">
-        <v>1567</v>
       </c>
       <c r="E557" s="13">
         <v>39738</v>
@@ -29248,13 +29295,13 @@
         <v>18</v>
       </c>
       <c r="B558" s="7" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C558" s="7" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="D558" s="6" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E558" s="8">
         <v>41038</v>
@@ -29271,10 +29318,10 @@
       </c>
       <c r="L558" s="7"/>
       <c r="M558" s="6" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N558" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O558" s="9"/>
       <c r="P558" s="9"/>
@@ -29286,13 +29333,13 @@
         <v>18</v>
       </c>
       <c r="B559" s="12" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="C559" s="12" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="D559" s="11" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E559" s="13">
         <v>41956</v>
@@ -29317,7 +29364,7 @@
       </c>
       <c r="L559" s="12"/>
       <c r="M559" s="17" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="N559" s="12" t="s">
         <v>842</v>
@@ -29332,13 +29379,13 @@
         <v>18</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C560" s="7" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="D560" s="6" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E560" s="8">
         <v>43867</v>
@@ -29376,13 +29423,13 @@
         <v>18</v>
       </c>
       <c r="B561" s="12" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C561" s="12" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="D561" s="11" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E561" s="13">
         <v>44358</v>
@@ -29420,13 +29467,13 @@
         <v>30</v>
       </c>
       <c r="B562" s="15" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="C562" s="7" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D562" s="10" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="E562" s="8">
         <v>45161</v>
@@ -29451,7 +29498,7 @@
         <v>11</v>
       </c>
       <c r="M562" s="6" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="N562" s="15" t="s">
         <v>965</v>
@@ -29467,16 +29514,16 @@
     </row>
     <row r="563" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A563" s="11" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="B563" s="18" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="C563" s="12" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="D563" s="11" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="E563" s="13">
         <v>45636</v>
@@ -29494,12 +29541,14 @@
         <v>46296</v>
       </c>
       <c r="J563" s="14"/>
-      <c r="K563" s="13"/>
+      <c r="K563" s="13">
+        <v>47208</v>
+      </c>
       <c r="L563" s="18" t="s">
         <v>11</v>
       </c>
       <c r="M563" s="11" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="N563" s="18" t="s">
         <v>144</v>
@@ -29513,16 +29562,16 @@
     </row>
     <row r="564" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A564" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B564" s="15" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C564" s="7" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="D564" s="10" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="E564" s="8">
         <v>45961</v>
@@ -29530,9 +29579,15 @@
       <c r="F564" s="8">
         <v>45965</v>
       </c>
-      <c r="G564" s="8"/>
-      <c r="H564" s="8"/>
-      <c r="I564" s="8"/>
+      <c r="G564" s="8">
+        <v>46072</v>
+      </c>
+      <c r="H564" s="8">
+        <v>46072</v>
+      </c>
+      <c r="I564" s="8">
+        <v>47209</v>
+      </c>
       <c r="J564" s="9"/>
       <c r="K564" s="8"/>
       <c r="L564" s="15" t="s">
@@ -29556,13 +29611,13 @@
         <v>18</v>
       </c>
       <c r="B565" s="12" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C565" s="12" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D565" s="11" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E565" s="13">
         <v>38391</v>
@@ -29579,7 +29634,7 @@
       </c>
       <c r="L565" s="12"/>
       <c r="M565" s="17" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="N565" s="12"/>
       <c r="O565" s="14"/>
@@ -29592,13 +29647,13 @@
         <v>18</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="C566" s="7" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D566" s="6" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E566" s="8">
         <v>39022</v>
@@ -29634,13 +29689,13 @@
         <v>18</v>
       </c>
       <c r="B567" s="12" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C567" s="12" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="D567" s="11" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E567" s="13">
         <v>39022</v>
@@ -29664,7 +29719,7 @@
       <c r="L567" s="12"/>
       <c r="M567" s="11"/>
       <c r="N567" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="O567" s="14"/>
       <c r="P567" s="14"/>
@@ -29676,13 +29731,13 @@
         <v>18</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="C568" s="7" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D568" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E568" s="8">
         <v>38391</v>
@@ -29697,7 +29752,7 @@
       </c>
       <c r="L568" s="7"/>
       <c r="M568" s="6" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="N568" s="7"/>
       <c r="O568" s="9"/>
@@ -29710,13 +29765,13 @@
         <v>18</v>
       </c>
       <c r="B569" s="12" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="C569" s="12" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D569" s="11" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E569" s="13">
         <v>38755</v>
@@ -29752,13 +29807,13 @@
         <v>18</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C570" s="7" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D570" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E570" s="8">
         <v>39750</v>
@@ -29794,13 +29849,13 @@
         <v>18</v>
       </c>
       <c r="B571" s="12" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="C571" s="12" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D571" s="11" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E571" s="13">
         <v>40122</v>
@@ -29836,13 +29891,13 @@
         <v>18</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="C572" s="7" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D572" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E572" s="8">
         <v>39738</v>
@@ -29876,13 +29931,13 @@
         <v>18</v>
       </c>
       <c r="B573" s="12" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C573" s="12" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D573" s="11" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E573" s="13">
         <v>39738</v>
@@ -29920,13 +29975,13 @@
         <v>18</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C574" s="7" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D574" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E574" s="8">
         <v>41956</v>
@@ -29956,13 +30011,13 @@
         <v>18</v>
       </c>
       <c r="B575" s="12" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="C575" s="12" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="D575" s="11" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E575" s="13">
         <v>38391</v>
@@ -29979,7 +30034,7 @@
       </c>
       <c r="L575" s="12"/>
       <c r="M575" s="17" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="N575" s="12"/>
       <c r="O575" s="14"/>
@@ -29992,13 +30047,13 @@
         <v>18</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C576" s="7" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="D576" s="6" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E576" s="8">
         <v>39022</v>
@@ -30024,7 +30079,7 @@
         <v>471</v>
       </c>
       <c r="N576" s="7" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="O576" s="9"/>
       <c r="P576" s="9"/>
@@ -30036,13 +30091,13 @@
         <v>18</v>
       </c>
       <c r="B577" s="12" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="C577" s="12" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="D577" s="11" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E577" s="13">
         <v>39738</v>
@@ -30080,13 +30135,13 @@
         <v>18</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="C578" s="7" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="D578" s="6" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="E578" s="8">
         <v>41220</v>
@@ -30103,10 +30158,10 @@
       </c>
       <c r="L578" s="7"/>
       <c r="M578" s="6" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="N578" s="7" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="O578" s="9"/>
       <c r="P578" s="9"/>
@@ -30118,13 +30173,13 @@
         <v>18</v>
       </c>
       <c r="B579" s="12" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="C579" s="12" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="D579" s="11" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="E579" s="13">
         <v>38391</v>
@@ -30150,7 +30205,7 @@
         <v>45</v>
       </c>
       <c r="N579" s="12" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="O579" s="14"/>
       <c r="P579" s="14"/>
@@ -30162,13 +30217,13 @@
         <v>18</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="C580" s="7" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D580" s="6" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="E580" s="8">
         <v>39750</v>
@@ -30191,7 +30246,7 @@
       </c>
       <c r="L580" s="7"/>
       <c r="M580" s="6" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="N580" s="7"/>
       <c r="O580" s="9"/>
@@ -30204,13 +30259,13 @@
         <v>18</v>
       </c>
       <c r="B581" s="12" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="C581" s="12" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D581" s="11" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="E581" s="13">
         <v>41676</v>
@@ -30233,7 +30288,7 @@
       </c>
       <c r="L581" s="12"/>
       <c r="M581" s="11" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="N581" s="12" t="s">
         <v>68</v>
@@ -30248,13 +30303,13 @@
         <v>18</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="C582" s="7" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D582" s="6" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="E582" s="8">
         <v>38391</v>
@@ -30274,7 +30329,7 @@
         <v>45</v>
       </c>
       <c r="N582" s="7" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="O582" s="9"/>
       <c r="P582" s="9"/>
@@ -30286,13 +30341,13 @@
         <v>18</v>
       </c>
       <c r="B583" s="12" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="C583" s="12" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D583" s="11" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="E583" s="13">
         <v>39022</v>
@@ -30328,10 +30383,10 @@
         <v>18</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="C584" s="7" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="D584" s="6" t="s">
         <v>989</v>
@@ -30355,7 +30410,7 @@
       </c>
       <c r="L584" s="7"/>
       <c r="M584" s="10" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="N584" s="7" t="s">
         <v>991</v>
@@ -30370,10 +30425,10 @@
         <v>30</v>
       </c>
       <c r="B585" s="18" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="C585" s="12" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="D585" s="11" t="s">
         <v>989</v>
@@ -30399,7 +30454,7 @@
         <v>11</v>
       </c>
       <c r="M585" s="11" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N585" s="18" t="s">
         <v>991</v>
@@ -30418,13 +30473,13 @@
         <v>18</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="C586" s="7" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="D586" s="6" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="E586" s="8">
         <v>39153</v>
@@ -30460,13 +30515,13 @@
         <v>18</v>
       </c>
       <c r="B587" s="12" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="C587" s="12" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D587" s="17" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E587" s="13">
         <v>38391</v>
@@ -30502,13 +30557,13 @@
         <v>18</v>
       </c>
       <c r="B588" s="7" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C588" s="7" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D588" s="10" t="s">
         <v>1638</v>
-      </c>
-      <c r="C588" s="7" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D588" s="10" t="s">
-        <v>1637</v>
       </c>
       <c r="E588" s="8">
         <v>39750</v>
@@ -30546,13 +30601,13 @@
         <v>18</v>
       </c>
       <c r="B589" s="12" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="C589" s="12" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D589" s="17" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E589" s="13">
         <v>41956</v>
@@ -30588,13 +30643,13 @@
         <v>18</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C590" s="7" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D590" s="10" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E590" s="8">
         <v>40591</v>
@@ -30615,7 +30670,7 @@
       </c>
       <c r="L590" s="7"/>
       <c r="M590" s="6" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="N590" s="7"/>
       <c r="O590" s="9"/>
@@ -30628,13 +30683,13 @@
         <v>18</v>
       </c>
       <c r="B591" s="12" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="C591" s="12" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D591" s="11" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E591" s="13">
         <v>40759</v>
@@ -30651,7 +30706,7 @@
       </c>
       <c r="L591" s="12"/>
       <c r="M591" s="11" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="N591" s="12" t="s">
         <v>13</v>
@@ -30666,13 +30721,13 @@
         <v>18</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="C592" s="7" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D592" s="10" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E592" s="8">
         <v>41312</v>
@@ -30689,7 +30744,7 @@
       </c>
       <c r="L592" s="7"/>
       <c r="M592" s="6" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="N592" s="7" t="s">
         <v>13</v>
@@ -30704,13 +30759,13 @@
         <v>18</v>
       </c>
       <c r="B593" s="12" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="C593" s="12" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D593" s="11" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E593" s="13">
         <v>41312</v>
@@ -30733,10 +30788,10 @@
       </c>
       <c r="L593" s="12"/>
       <c r="M593" s="11" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="N593" s="12" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="O593" s="14"/>
       <c r="P593" s="14"/>
@@ -30748,13 +30803,13 @@
         <v>18</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C594" s="7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D594" s="6" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E594" s="8">
         <v>43411</v>
@@ -30775,10 +30830,10 @@
       </c>
       <c r="L594" s="7"/>
       <c r="M594" s="6" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="N594" s="7" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="O594" s="9"/>
       <c r="P594" s="9"/>
@@ -30790,13 +30845,13 @@
         <v>30</v>
       </c>
       <c r="B595" s="18" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="C595" s="12" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D595" s="11" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E595" s="13">
         <v>43411</v>
@@ -30821,10 +30876,10 @@
         <v>11</v>
       </c>
       <c r="M595" s="11" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="N595" s="18" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="O595" s="14"/>
       <c r="P595" s="19" t="s">
@@ -30840,13 +30895,13 @@
         <v>18</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="C596" s="7" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D596" s="10" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E596" s="8">
         <v>38391</v>
@@ -30884,13 +30939,13 @@
         <v>18</v>
       </c>
       <c r="B597" s="12" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C597" s="12" t="s">
         <v>1658</v>
       </c>
-      <c r="C597" s="12" t="s">
-        <v>1657</v>
-      </c>
       <c r="D597" s="17" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E597" s="13">
         <v>39659</v>
@@ -30913,7 +30968,7 @@
       </c>
       <c r="L597" s="12"/>
       <c r="M597" s="11" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="N597" s="12"/>
       <c r="O597" s="14"/>
@@ -30926,13 +30981,13 @@
         <v>18</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C598" s="7" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D598" s="10" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E598" s="8">
         <v>40122</v>
@@ -30955,10 +31010,10 @@
       </c>
       <c r="L598" s="7"/>
       <c r="M598" s="6" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="N598" s="7" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="O598" s="9"/>
       <c r="P598" s="9"/>
@@ -30970,13 +31025,13 @@
         <v>18</v>
       </c>
       <c r="B599" s="12" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="C599" s="12" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D599" s="17" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E599" s="13">
         <v>41956</v>
@@ -31012,13 +31067,13 @@
         <v>18</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="C600" s="7" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D600" s="10" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E600" s="8">
         <v>40591</v>
@@ -31039,10 +31094,10 @@
       </c>
       <c r="L600" s="7"/>
       <c r="M600" s="6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="N600" s="7" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="O600" s="9"/>
       <c r="P600" s="9"/>
@@ -31054,13 +31109,13 @@
         <v>18</v>
       </c>
       <c r="B601" s="12" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C601" s="12" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D601" s="17" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E601" s="13">
         <v>41312</v>
@@ -31077,10 +31132,10 @@
       </c>
       <c r="L601" s="12"/>
       <c r="M601" s="11" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="N601" s="12" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="O601" s="14"/>
       <c r="P601" s="14"/>
@@ -31092,13 +31147,13 @@
         <v>18</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="C602" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D602" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E602" s="8">
         <v>38391</v>
@@ -31124,7 +31179,7 @@
         <v>45</v>
       </c>
       <c r="N602" s="7" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="O602" s="9"/>
       <c r="P602" s="9"/>
@@ -31136,13 +31191,13 @@
         <v>18</v>
       </c>
       <c r="B603" s="12" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C603" s="12" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D603" s="17" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E603" s="13">
         <v>39659</v>
@@ -31165,10 +31220,10 @@
       </c>
       <c r="L603" s="12"/>
       <c r="M603" s="11" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="N603" s="12" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="O603" s="14"/>
       <c r="P603" s="14"/>
@@ -31180,13 +31235,13 @@
         <v>18</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="C604" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D604" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E604" s="8">
         <v>41312</v>
@@ -31209,7 +31264,7 @@
       </c>
       <c r="L604" s="7"/>
       <c r="M604" s="10" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="N604" s="7" t="s">
         <v>1066</v>
@@ -31224,13 +31279,13 @@
         <v>18</v>
       </c>
       <c r="B605" s="12" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="C605" s="12" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D605" s="17" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E605" s="13">
         <v>41956</v>
@@ -31266,13 +31321,13 @@
         <v>18</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="C606" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D606" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E606" s="8">
         <v>40591</v>
@@ -31293,10 +31348,10 @@
       </c>
       <c r="L606" s="7"/>
       <c r="M606" s="6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="N606" s="7" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="O606" s="9"/>
       <c r="P606" s="9"/>
@@ -31308,13 +31363,13 @@
         <v>18</v>
       </c>
       <c r="B607" s="12" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="C607" s="12" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D607" s="17" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E607" s="13">
         <v>41312</v>
@@ -31331,10 +31386,10 @@
       </c>
       <c r="L607" s="12"/>
       <c r="M607" s="11" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="N607" s="12" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="O607" s="14"/>
       <c r="P607" s="14"/>
@@ -31346,13 +31401,13 @@
         <v>18</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="C608" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D608" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E608" s="8">
         <v>41312</v>
@@ -31369,10 +31424,10 @@
       </c>
       <c r="L608" s="7"/>
       <c r="M608" s="10" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="N608" s="7" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="O608" s="9"/>
       <c r="P608" s="9"/>
@@ -31384,13 +31439,13 @@
         <v>18</v>
       </c>
       <c r="B609" s="12" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="C609" s="12" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D609" s="17" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E609" s="13">
         <v>38391</v>
@@ -31416,7 +31471,7 @@
         <v>45</v>
       </c>
       <c r="N609" s="12" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="O609" s="14"/>
       <c r="P609" s="14"/>
@@ -31428,13 +31483,13 @@
         <v>18</v>
       </c>
       <c r="B610" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C610" s="7" t="s">
         <v>1685</v>
       </c>
-      <c r="C610" s="7" t="s">
-        <v>1684</v>
-      </c>
       <c r="D610" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E610" s="8">
         <v>41312</v>
@@ -31457,7 +31512,7 @@
       </c>
       <c r="L610" s="7"/>
       <c r="M610" s="10" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="N610" s="7" t="s">
         <v>1066</v>
@@ -31472,13 +31527,13 @@
         <v>18</v>
       </c>
       <c r="B611" s="12" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="C611" s="12" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D611" s="17" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E611" s="13">
         <v>41956</v>
@@ -31514,13 +31569,13 @@
         <v>18</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C612" s="7" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D612" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E612" s="8">
         <v>40591</v>
@@ -31541,7 +31596,7 @@
       </c>
       <c r="L612" s="7"/>
       <c r="M612" s="6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="N612" s="7"/>
       <c r="O612" s="9"/>
@@ -31554,13 +31609,13 @@
         <v>18</v>
       </c>
       <c r="B613" s="12" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="C613" s="12" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D613" s="17" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E613" s="13">
         <v>41312</v>
@@ -31577,7 +31632,7 @@
       </c>
       <c r="L613" s="12"/>
       <c r="M613" s="11" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="N613" s="12"/>
       <c r="O613" s="14"/>
@@ -31590,13 +31645,13 @@
         <v>18</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="C614" s="7" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D614" s="10" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E614" s="8">
         <v>41312</v>
@@ -31613,10 +31668,10 @@
       </c>
       <c r="L614" s="7"/>
       <c r="M614" s="10" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="N614" s="7" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="O614" s="9"/>
       <c r="P614" s="9"/>
@@ -31628,13 +31683,13 @@
         <v>18</v>
       </c>
       <c r="B615" s="12" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="C615" s="12" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D615" s="11" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="E615" s="13">
         <v>38391</v>
@@ -31666,13 +31721,13 @@
         <v>18</v>
       </c>
       <c r="B616" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C616" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D616" s="6" t="s">
         <v>1694</v>
-      </c>
-      <c r="C616" s="7" t="s">
-        <v>1695</v>
-      </c>
-      <c r="D616" s="6" t="s">
-        <v>1693</v>
       </c>
       <c r="E616" s="8">
         <v>38391</v>
@@ -31704,13 +31759,13 @@
         <v>18</v>
       </c>
       <c r="B617" s="12" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C617" s="12" t="s">
         <v>1696</v>
       </c>
-      <c r="C617" s="12" t="s">
-        <v>1695</v>
-      </c>
       <c r="D617" s="11" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="E617" s="13">
         <v>39918</v>
@@ -31725,10 +31780,10 @@
       </c>
       <c r="L617" s="12"/>
       <c r="M617" s="11" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="N617" s="12" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="O617" s="14"/>
       <c r="P617" s="14"/>
@@ -31740,13 +31795,13 @@
         <v>18</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C618" s="7" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D618" s="6" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E618" s="8">
         <v>41990</v>
@@ -31771,7 +31826,7 @@
       </c>
       <c r="L618" s="7"/>
       <c r="M618" s="6" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="N618" s="7" t="s">
         <v>593</v>
@@ -31786,13 +31841,13 @@
         <v>18</v>
       </c>
       <c r="B619" s="12" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="C619" s="12" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D619" s="11" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E619" s="13">
         <v>43048</v>
@@ -31817,7 +31872,7 @@
       </c>
       <c r="L619" s="12"/>
       <c r="M619" s="17" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="N619" s="12" t="s">
         <v>593</v>
@@ -31832,13 +31887,13 @@
         <v>18</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="C620" s="7" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D620" s="6" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E620" s="8">
         <v>43503</v>
@@ -31863,10 +31918,10 @@
       </c>
       <c r="L620" s="7"/>
       <c r="M620" s="10" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="N620" s="7" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="O620" s="9"/>
       <c r="P620" s="9"/>
@@ -31878,13 +31933,13 @@
         <v>30</v>
       </c>
       <c r="B621" s="18" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="C621" s="12" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D621" s="11" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E621" s="13">
         <v>43867</v>
@@ -31909,10 +31964,10 @@
         <v>11</v>
       </c>
       <c r="M621" s="17" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="N621" s="18" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="O621" s="14"/>
       <c r="P621" s="19" t="s">
@@ -31928,13 +31983,13 @@
         <v>139</v>
       </c>
       <c r="B622" s="15" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="C622" s="7" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="D622" s="6" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="E622" s="8">
         <v>45636</v>
@@ -31959,13 +32014,13 @@
         <v>11</v>
       </c>
       <c r="M622" s="6" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="N622" s="15" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="O622" s="25" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="P622" s="16" t="s">
         <v>34</v>
@@ -31980,13 +32035,13 @@
         <v>18</v>
       </c>
       <c r="B623" s="12" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="C623" s="12" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D623" s="11" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="E623" s="13">
         <v>38391</v>
@@ -32003,7 +32058,7 @@
       </c>
       <c r="L623" s="12"/>
       <c r="M623" s="17" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="N623" s="12"/>
       <c r="O623" s="14"/>
@@ -32016,13 +32071,13 @@
         <v>18</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C624" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D624" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E624" s="8">
         <v>38931</v>
@@ -32058,13 +32113,13 @@
         <v>18</v>
       </c>
       <c r="B625" s="12" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C625" s="12" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D625" s="11" t="s">
         <v>1722</v>
-      </c>
-      <c r="C625" s="12" t="s">
-        <v>1717</v>
-      </c>
-      <c r="D625" s="11" t="s">
-        <v>1721</v>
       </c>
       <c r="E625" s="13">
         <v>39533</v>
@@ -32079,7 +32134,7 @@
       </c>
       <c r="L625" s="12"/>
       <c r="M625" s="11" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="N625" s="12"/>
       <c r="O625" s="14"/>
@@ -32092,13 +32147,13 @@
         <v>18</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C626" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D626" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E626" s="8">
         <v>40395</v>
@@ -32136,13 +32191,13 @@
         <v>18</v>
       </c>
       <c r="B627" s="12" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="C627" s="12" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D627" s="11" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E627" s="13">
         <v>41038</v>
@@ -32165,7 +32220,7 @@
       </c>
       <c r="L627" s="12"/>
       <c r="M627" s="11" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="N627" s="12" t="s">
         <v>48</v>
@@ -32180,13 +32235,13 @@
         <v>18</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="C628" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D628" s="6" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E628" s="8">
         <v>41676</v>
@@ -32209,10 +32264,10 @@
       </c>
       <c r="L628" s="7"/>
       <c r="M628" s="6" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="N628" s="7" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="O628" s="9"/>
       <c r="P628" s="9"/>
@@ -32224,13 +32279,13 @@
         <v>18</v>
       </c>
       <c r="B629" s="12" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="C629" s="12" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D629" s="11" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E629" s="13">
         <v>41676</v>
@@ -32256,7 +32311,7 @@
         <v>479</v>
       </c>
       <c r="N629" s="12" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="O629" s="14"/>
       <c r="P629" s="14"/>
@@ -32268,13 +32323,13 @@
         <v>18</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="C630" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D630" s="6" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E630" s="8">
         <v>42957</v>
@@ -32297,10 +32352,10 @@
       </c>
       <c r="L630" s="7"/>
       <c r="M630" s="10" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="N630" s="7" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="O630" s="9"/>
       <c r="P630" s="9"/>
@@ -32312,13 +32367,13 @@
         <v>30</v>
       </c>
       <c r="B631" s="18" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="C631" s="12" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D631" s="11" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E631" s="13">
         <v>43328</v>
@@ -32339,7 +32394,7 @@
       <c r="K631" s="13"/>
       <c r="L631" s="12"/>
       <c r="M631" s="11" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="N631" s="18" t="s">
         <v>68</v>
@@ -32356,13 +32411,13 @@
         <v>18</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C632" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D632" s="6" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E632" s="8">
         <v>43594</v>
@@ -32379,7 +32434,7 @@
       </c>
       <c r="L632" s="7"/>
       <c r="M632" s="10" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="N632" s="7" t="s">
         <v>692</v>
@@ -32394,13 +32449,13 @@
         <v>18</v>
       </c>
       <c r="B633" s="12" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C633" s="12" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D633" s="11" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="E633" s="13">
         <v>38931</v>
@@ -32436,13 +32491,13 @@
         <v>18</v>
       </c>
       <c r="B634" s="7" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C634" s="7" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D634" s="6" t="s">
         <v>1742</v>
-      </c>
-      <c r="C634" s="7" t="s">
-        <v>1740</v>
-      </c>
-      <c r="D634" s="6" t="s">
-        <v>1741</v>
       </c>
       <c r="E634" s="8">
         <v>39750</v>
@@ -32478,13 +32533,13 @@
         <v>18</v>
       </c>
       <c r="B635" s="12" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="C635" s="12" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D635" s="11" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="E635" s="13">
         <v>39854</v>
@@ -32507,10 +32562,10 @@
       </c>
       <c r="L635" s="12"/>
       <c r="M635" s="11" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="N635" s="12" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="O635" s="14"/>
       <c r="P635" s="14"/>
@@ -32522,13 +32577,13 @@
         <v>18</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C636" s="7" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D636" s="6" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="E636" s="8">
         <v>39295</v>
@@ -32551,7 +32606,7 @@
       </c>
       <c r="L636" s="7"/>
       <c r="M636" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N636" s="7"/>
       <c r="O636" s="9"/>
@@ -32564,13 +32619,13 @@
         <v>18</v>
       </c>
       <c r="B637" s="12" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="C637" s="12" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D637" s="11" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="E637" s="13">
         <v>41137</v>
@@ -32593,10 +32648,10 @@
       </c>
       <c r="L637" s="12"/>
       <c r="M637" s="11" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="N637" s="12" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="O637" s="14"/>
       <c r="P637" s="14"/>
@@ -32608,13 +32663,13 @@
         <v>18</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="C638" s="7" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D638" s="6" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="E638" s="8">
         <v>41765</v>
@@ -32637,10 +32692,10 @@
       </c>
       <c r="L638" s="7"/>
       <c r="M638" s="6" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="N638" s="7" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="O638" s="9"/>
       <c r="P638" s="9"/>
@@ -32652,13 +32707,13 @@
         <v>18</v>
       </c>
       <c r="B639" s="12" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C639" s="12" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D639" s="11" t="s">
         <v>1752</v>
-      </c>
-      <c r="C639" s="12" t="s">
-        <v>1740</v>
-      </c>
-      <c r="D639" s="11" t="s">
-        <v>1751</v>
       </c>
       <c r="E639" s="13">
         <v>41956</v>
@@ -32681,10 +32736,10 @@
       </c>
       <c r="L639" s="12"/>
       <c r="M639" s="11" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N639" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="O639" s="14"/>
       <c r="P639" s="14"/>
@@ -32696,13 +32751,13 @@
         <v>30</v>
       </c>
       <c r="B640" s="15" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C640" s="7" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D640" s="6" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="E640" s="8">
         <v>42957</v>
@@ -32725,10 +32780,10 @@
         <v>11</v>
       </c>
       <c r="M640" s="10" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="N640" s="15" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="O640" s="9"/>
       <c r="P640" s="16" t="s">
@@ -32742,13 +32797,13 @@
         <v>18</v>
       </c>
       <c r="B641" s="12" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="C641" s="12" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="D641" s="11" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="E641" s="13">
         <v>39750</v>
@@ -32786,13 +32841,13 @@
         <v>18</v>
       </c>
       <c r="B642" s="7" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C642" s="7" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D642" s="6" t="s">
         <v>1758</v>
-      </c>
-      <c r="C642" s="7" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D642" s="6" t="s">
-        <v>1757</v>
       </c>
       <c r="E642" s="8">
         <v>41956</v>
@@ -32815,7 +32870,7 @@
       </c>
       <c r="L642" s="7"/>
       <c r="M642" s="6" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="N642" s="7" t="s">
         <v>68</v>
@@ -32830,13 +32885,13 @@
         <v>18</v>
       </c>
       <c r="B643" s="12" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="C643" s="12" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D643" s="11" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="E643" s="13">
         <v>39750</v>
@@ -32874,13 +32929,13 @@
         <v>18</v>
       </c>
       <c r="B644" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C644" s="7" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D644" s="6" t="s">
         <v>1763</v>
-      </c>
-      <c r="C644" s="7" t="s">
-        <v>1761</v>
-      </c>
-      <c r="D644" s="6" t="s">
-        <v>1762</v>
       </c>
       <c r="E644" s="8">
         <v>41956</v>
@@ -32903,7 +32958,7 @@
       </c>
       <c r="L644" s="7"/>
       <c r="M644" s="6" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="N644" s="7" t="s">
         <v>68</v>
@@ -32918,13 +32973,13 @@
         <v>18</v>
       </c>
       <c r="B645" s="12" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="C645" s="12" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D645" s="11" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E645" s="13">
         <v>42775</v>
@@ -32947,10 +33002,10 @@
       </c>
       <c r="L645" s="12"/>
       <c r="M645" s="17" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="N645" s="12" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="O645" s="14"/>
       <c r="P645" s="14"/>
@@ -32962,13 +33017,13 @@
         <v>18</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="C646" s="7" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D646" s="6" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E646" s="8">
         <v>42957</v>
@@ -32991,7 +33046,7 @@
       </c>
       <c r="L646" s="7"/>
       <c r="M646" s="6" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="N646" s="7" t="s">
         <v>68</v>
@@ -33006,13 +33061,13 @@
         <v>30</v>
       </c>
       <c r="B647" s="18" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C647" s="12" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D647" s="11" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E647" s="13">
         <v>45272</v>
@@ -33035,7 +33090,7 @@
         <v>11</v>
       </c>
       <c r="M647" s="11" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="N647" s="18" t="s">
         <v>68</v>
@@ -33050,13 +33105,13 @@
         <v>18</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C648" s="7" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="D648" s="10" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E648" s="8">
         <v>39153</v>
@@ -33092,13 +33147,13 @@
         <v>18</v>
       </c>
       <c r="B649" s="12" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C649" s="12" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D649" s="17" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E649" s="13">
         <v>39153</v>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -1,9 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mullerw\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5E6C47-6FFD-425B-AC5E-3B9B03912F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="One Stop Shop" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -76,7 +88,9 @@
     <t>To maintain Interconnection steady-state frequency within defined limits by balancing real power demand and supply in real-time.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 WECC Request for Interpretation of BAL-001-0, Requirement 1</t>
   </si>
   <si>
@@ -89,7 +103,9 @@
     <t>BAL-001-0a</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM08-7-000 
+    <t>Filing/Order Docket No. RM08-7-000 _x000D_
+_x000D_
+_x000D_
 WECC Request for Interpretation of BAL-001-0, Requirement 1 and Errata change</t>
   </si>
   <si>
@@ -126,7 +142,9 @@
     <t>To maintain Interconnection steady-state frequency within defined limits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. ​RD13-12-000​ ​
+    <t>Filing/Order Docket No. ​RD13-12-000​ ​_x000D_
+_x000D_
+_x000D_
 Refer to the implementation plan for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -202,7 +220,9 @@
     <t>Contingency Reserve is required for the reliable operation of the interconnected power system. Adequate generating capacity must be available at all times to maintain scheduled frequency, and avoid loss of firm load following transmission or generation contingencies. This generating capacity is necessary to replace generating capacity and energy lost due to forced outages of generation or transmission equipment.</t>
   </si>
   <si>
-    <t xml:space="preserve">Docket No. RM09-15-000; Order No. 740
+    <t>Docket No. RM09-15-000; Order No. 740_x000D_
+_x000D_
+_x000D_
 Remanded by FERC in an October 21, 2010 Order, effective November 26, 2010.</t>
   </si>
   <si>
@@ -275,7 +295,9 @@
     <t>X</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. ​RM13-11-000 ​
+    <t>Filing/Order Docket No. ​RM13-11-000 ​_x000D_
+_x000D_
+_x000D_
 See the implementation plan for guidance on phased-in enforcement dates. Requirement R1 will never become enforceable.. Disregard the dates for R1 it is non enforceable.</t>
   </si>
   <si>
@@ -306,14 +328,18 @@
     <t>The purpose of this standard is to ensure that Time Error Corrections are conducted in a manner that does not adversely affect the reliability of the Interconnection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 The retirement of BAL-004-0 is contingent upon the retirement of NAESB WEQ-006 Manual Time Error Correction Business Practice Standard.</t>
   </si>
   <si>
     <t>BAL-004-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM09-13-000
+    <t>Filing/Order Docket No. RM09-13-000_x000D_
+_x000D_
+_x000D_
 The NERC BOT withdrew its approval of this standard at its meeting on August 16, 2012.</t>
   </si>
   <si>
@@ -509,7 +535,7 @@
     <t>Sabotage Reporting</t>
   </si>
   <si>
-    <t xml:space="preserve">Disturbances or unusual occurrences, suspected or determined to be caused by sabotage, shall be reported to the appropriate systems, governmental agencies, and regulatory
+    <t>Disturbances or unusual occurrences, suspected or determined to be caused by sabotage, shall be reported to the appropriate systems, governmental agencies, and regulatory_x000D_
 bodies.</t>
   </si>
   <si>
@@ -576,7 +602,9 @@
     <t>CIP-002-3a</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-5-000
+    <t>Filing/Order Docket No. RD12-5-000_x000D_
+_x000D_
+_x000D_
 FERC remanded the interpretation of R3 in an order issued on 3/21/13</t>
   </si>
   <si>
@@ -586,9 +614,12 @@
     <t>CIP-002-3(i)</t>
   </si>
   <si>
-    <t xml:space="preserve">NERC Standards CIP-002-3(i) through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System.
-These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. 
-Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets.
+    <t>NERC Standards CIP-002-3(i) through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System._x000D_
+_x000D_
+These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. _x000D_
+_x000D_
+Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets._x000D_
+_x000D_
 Standard CIP-002-3(i) requires the identification and documentation of the Critical Cyber Assets associated with the Critical Assets that support the reliable operation of the Bulk Electric System. These Critical Assets are to be identified through the application of a risk-based assessment.</t>
   </si>
   <si>
@@ -601,9 +632,12 @@
     <t>CIP-002-3(i)b</t>
   </si>
   <si>
-    <t xml:space="preserve">NERC Standards CIP-002-3(i)b through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System.
-These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. 
-Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets.
+    <t>NERC Standards CIP-002-3(i)b through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System._x000D_
+_x000D_
+These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. _x000D_
+_x000D_
+Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets._x000D_
+_x000D_
 Standard CIP-002-3(i)b requires the identification and documentation of the Critical Cyber Assets associated with the Critical Assets that support the reliable operation of the Bulk Electric System. These Critical Assets are to be identified through the application of a risk-based assessment.</t>
   </si>
   <si>
@@ -640,14 +674,18 @@
     <t>CIP-002-5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-5-000
+    <t>Filing/Order Docket No. RM13-5-000_x000D_
+_x000D_
+_x000D_
 Errata approved by the SC on 9/27/2013</t>
   </si>
   <si>
     <t>CIP-002-5.1a</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-2-000
+    <t>Filing/Order Docket No. RD17-2-000_x000D_
+_x000D_
+_x000D_
 CIP-002-5.1a replaced CIP-002-5.1</t>
   </si>
   <si>
@@ -660,7 +698,7 @@
     <t>Cyber Security – BES Cyber System Categorization</t>
   </si>
   <si>
-    <t xml:space="preserve">To identify and categorize BES Cyber Systems and their associated BES 
+    <t>To identify and categorize BES Cyber Systems and their associated BES _x000D_
 Cyber Assets for the application of cyber security requirements commensurate with the adverse impact that loss, compromise, or misuse of those BES Cyber Systems could have on the reliable operation of the BES. Identification and categorization of BES Cyber Systems support appropriate protection against compromises that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
@@ -703,7 +741,9 @@
     <t>Standard CIP-003 requires that Responsible Entities have minimum security management controls in place to protect Critical Cyber Assets. Standard CIP-003 should be read as part of a group of standards numbered Standards CIP-002 through CIP-009. Responsible Entities should interpret and apply Standards CIP-002 through CIP-009 using reasonable business judgment.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000,  RM06-22-000
+    <t>Filing/Order Docket No. RM06-16-000,  RM06-22-000_x000D_
+_x000D_
+_x000D_
 Replaced with CIP-003-2</t>
   </si>
   <si>
@@ -731,7 +771,9 @@
     <t>Standard CIP-003-2 requires that Responsible Entities have minimum security management controls in place to protect Critical Cyber Assets. Standard CIP-003-2 should be read as part of a group of standards numbered Standards CIP-002-2 through CIP-009-2.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-22-000, RD09-7-000
+    <t>Filing/Order Docket No. RM06-22-000, RD09-7-000_x000D_
+_x000D_
+_x000D_
 Replaced with CIP-003-3</t>
   </si>
   <si>
@@ -762,7 +804,9 @@
     <t>To specify consistent and sustainable security management controls that establish responsibility and accountability to protect BES Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-5-000
+    <t>Filing/Order Docket No. RM13-5-000_x000D_
+_x000D_
+_x000D_
 CIP-003-5 will be superseded by CIP-003-6.</t>
   </si>
   <si>
@@ -772,8 +816,12 @@
     <t>To specify consistent and sustainable security management controls that establish responsibility and accountability to protect Bulk Electric System (BES) Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
-With the approval of CIP-003-7 and its associated Implementation Plan, entities will not be required to implement CIP-003-6, Requirement R2, Attachment 1, Sections 2 and 3. Instead, entities will implement CIP-003-7, Requirement R2, Attachment 1 Sections 2 and 3 on January 1, 2020. See Implementation Plan for CIP-003-7.
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000_x000D_
+_x000D_
+_x000D_
+With the approval of CIP-003-7 and its associated Implementation Plan, entities will not be required to implement CIP-003-6, Requirement R2, Attachment 1, Sections 2 and 3. Instead, entities will implement CIP-003-7, Requirement R2, Attachment 1 Sections 2 and 3 on January 1, 2020. See Implementation Plan for CIP-003-7._x000D_
+_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -861,7 +909,11 @@
     <t>CIP-004-5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-5-000
+    <t>Filing/Order Docket No. RM13-5-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
 CIP-004-5.1 will be superseded by CIP-004-6.</t>
   </si>
   <si>
@@ -976,8 +1028,8 @@
     <t xml:space="preserve">Cyber Security — Electronic Security Perimeter(s) </t>
   </si>
   <si>
-    <t xml:space="preserve">To protect BES Cyber Systems (BCS) against compromise by permitting
-only known and controlled communication to reduce the likelihood of
+    <t>To protect BES Cyber Systems (BCS) against compromise by permitting_x000D_
+only known and controlled communication to reduce the likelihood of_x000D_
 misoperation or instability in the Bulk Electric System (BES).</t>
   </si>
   <si>
@@ -1065,7 +1117,8 @@
     <t>CIP-006-4d</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-3-000
+    <t xml:space="preserve">Filing/Order Docket No. RD12-3-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1084,7 +1137,11 @@
     <t>To manage physical access to Bulk Electric System (BES) Cyber Systems by specifying a physical security plan in support of protecting BES Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
+    <t>Filing/Order Docket No. RM15-14-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
 See Implementation Plan for Compliance dates.</t>
   </si>
   <si>
@@ -1121,10 +1178,10 @@
     <t>CIP-007-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard CIP-007-3 requires Responsible Entities to define methods, processes,
-and procedures for securing those systems determined to be Critical Cyber Assets, as well as
-the other (non-critical) Cyber Assets within the Electronic Security Perimeter(s). Standard
-CIP-007-3 should be read as part of a group of standards numbered Standards CIP-002-3
+    <t>Standard CIP-007-3 requires Responsible Entities to define methods, processes,_x000D_
+and procedures for securing those systems determined to be Critical Cyber Assets, as well as_x000D_
+the other (non-critical) Cyber Assets within the Electronic Security Perimeter(s). Standard_x000D_
+CIP-007-3 should be read as part of a group of standards numbered Standards CIP-002-3_x000D_
 through CIP-009-3.</t>
   </si>
   <si>
@@ -1137,7 +1194,11 @@
     <t>Standard CIP-007-3 requires Responsible Entities to define methods, processes, and procedures for securing those systems determined to be Critical Cyber Assets, as well as the other (non-critical) Cyber Assets within the Electronic Security Perimeter(s). Standard CIP-007-3 should be read as part of a group of standards numbered Standards CIP-002-3 through CIP-009-3.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD09-7-002
+    <t>Filing/Order Docket No. RD09-7-002_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
 The version number was updated from CIP-007-3 to CIP-007-3a to incorporate the approved interpretation that should have previously been appended.</t>
   </si>
   <si>
@@ -1168,7 +1229,10 @@
     <t>To manage system security by specifying select technical, operational, and procedural requirements in support of protecting Bulk Electric System (BES) Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000_x000D_
+_x000D_
+_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1265,7 +1329,8 @@
     <t>CIP-009-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1419,7 +1484,8 @@
     <t>CIP-014-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD22-3-000
+    <t xml:space="preserve">Filing/Order Docket No. RD22-3-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1453,7 +1519,9 @@
     <t>Each Reliability Coordinator, Transmission Operator and Balancing Authority needs adequate and reliable telecommunications facilities internally and with others for the exchange of Interconnection and operating information necessary to maintain reliability.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 COM-001-0 was never enforceable</t>
   </si>
   <si>
@@ -1511,12 +1579,14 @@
     <t>COM-002-1</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure Balancing Authorities, Transmission Operators, and Generator Operators have adequate communications and that these communications capabilities are
-staffed and available for addressing a real-time emergency condition. To ensure
+    <t>To ensure Balancing Authorities, Transmission Operators, and Generator Operators have adequate communications and that these communications capabilities are_x000D_
+staffed and available for addressing a real-time emergency condition. To ensure_x000D_
 communications by operating personnel are effective.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 COM-002-1 was never enforceable</t>
   </si>
   <si>
@@ -1574,7 +1644,11 @@
     <t>EOP-001-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM10-15-000, RM10-16-000
+    <t>Filing/Order Docket No. RM10-15-000, RM10-16-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
 Replaced with EOP-001-2 (EOP-001-1 was not enforceable)</t>
   </si>
   <si>
@@ -1584,7 +1658,11 @@
     <t>EOP-001-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM10-15-000, RM10-16-000
+    <t>Filing/Order Docket No. RM10-15-000, RM10-16-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
 Replaced with EOP-001-2b (Interpretation of R1 and R2.2)--(EOP-001-2 was not enforceable)</t>
   </si>
   <si>
@@ -1594,7 +1672,8 @@
     <t>EOP-001-2.1b</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-4-000
+    <t xml:space="preserve">Filing/Order Docket No. RD12-4-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1616,7 +1695,9 @@
     <t>EOP-002-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 EOP-002-1 was never enforceable</t>
   </si>
   <si>
@@ -1644,7 +1725,9 @@
     <t>A Balancing Authority and Transmission Operator operating with insufficient generation or transmission capacity must have the capability and authority to shed load rather than risk an uncontrolled failure of the Interconnection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 EOP-003-0 was never enforceable</t>
   </si>
   <si>
@@ -1687,7 +1770,8 @@
     <t>EOP-004-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000
+    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1709,7 +1793,9 @@
     <t>To ensure plans, procedures, and resources are available to restore the electric system to a normal condition in the event of a partial or total shut down of the system</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 EOP-005-0 was never enforceable</t>
   </si>
   <si>
@@ -1752,7 +1838,9 @@
     <t>The Reliability Coordinator must have a coordinating role in system restoration to ensure reliability is maintained during restoration and priority is placed on restoring the Interconnection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 EOP-006-0 was never enforceable</t>
   </si>
   <si>
@@ -1780,7 +1868,9 @@
     <t>A system Blackstart Capability Plan (BCP) is necessary to ensure that the quantity and location of system blackstart generators are sufficient and that they can perform their expected functions as specified in overall coordinated Regional System Restoration Plans (SRP).</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 FERC approved withdrawal of standard</t>
   </si>
   <si>
@@ -1835,7 +1925,9 @@
     <t>To mitigate the effects of geomagnetic disturbance (GMD) events by implementing Operating Plans, Processes, and Procedures.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM14-1-000
+    <t>Filing/Order Docket No. RM14-1-000_x000D_
+_x000D_
+_x000D_
 A FERC order was issued on June 19, 2014, approving EOP-010-1. Requirement 2 of Reliability Standard EOP-010-1 will not become effective until the first day following retirement of Reliability Standard IRO-005-3.1a.</t>
   </si>
   <si>
@@ -1851,7 +1943,8 @@
     <t>To address the effects of operating Emergencies by ensuring each Transmission Operator and Balancing Authority has developed Operating Plan(s) to mitigate operating Emergencies, and that those plans are coordinated within a Reliability Coordinator Area.</t>
   </si>
   <si>
-    <t xml:space="preserve">RM15-7-000
+    <t xml:space="preserve">RM15-7-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1867,7 +1960,10 @@
     <t>To address the effects of operating emergencies by ensuring each Transmission Operator, Balancing Authority, and Generator Owner has developed plan(s) to mitigate operating Emergencies and that those plans are implemented and coordinated within the Reliability Coordinator Area as specified within the requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD21-5-000
+    <t xml:space="preserve">Filing/Order Docket No. RD21-5-000_x000D_
+_x000D_
+_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1940,7 +2036,8 @@
     <t>To avoid adverse impacts on reliability, Transmission Owners and Generator Owners must establish Facility connection and performance requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM12-16-000
+    <t xml:space="preserve">Filing/Order Docket No. RM12-16-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -1968,7 +2065,9 @@
     <t>FAC-001-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD22-5-000
+    <t>Filing/Order Docket No. RD22-5-000_x000D_
+_x000D_
+_x000D_
 See Implementation Plan for additional compliance information</t>
   </si>
   <si>
@@ -2050,7 +2149,8 @@
     <t>To maintain a reliable electric transmission system by using a defense-in-depth strategy to manage vegetation located on transmission rights of way (ROW) and minimize encroachments from vegetation located adjacent to the ROW, thus preventing the risk of those vegetation-related outages that could lead to Cascading.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM12-4-000
+    <t xml:space="preserve">Filing/Order Docket No. RM12-4-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -2138,7 +2238,9 @@
     <t>FAC-008-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM19-17-000
+    <t>Filing/Order Docket No. RM19-17-000_x000D_
+_x000D_
+_x000D_
 Withdrawn 2/4/2021 Replaced by FAC-008-5</t>
   </si>
   <si>
@@ -2292,7 +2394,9 @@
     <t>FAC-501-WECC-4</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure the Transmission Owner of a path identified in the Table Revision Process, Attachment A, Major WECC Transfer Paths in the Bulk Electric System (Table), has a Transmission Maintenance and Inspection Plan (TMIP) for those paths, annually updates its TMIP, and adheres to the TMIP.
+    <t>To ensure the Transmission Owner of a path identified in the Table Revision Process, Attachment A, Major WECC Transfer Paths in the Bulk Electric System (Table), has a Transmission Maintenance and Inspection Plan (TMIP) for those paths, annually updates its TMIP, and adheres to the TMIP._x000D_
+_x000D_
+_x000D_
  </t>
   </si>
   <si>
@@ -2308,7 +2412,9 @@
     <t>To ensure that Interchange Transactions, certain Interchange Schedules, and intra-Balancing Authority Area transfers using Point-to-Point Transmission Service are Tagged in adequate time to allow the transactions to be assessed for reliability impacts by the affected Reliability Coordinators, Transmission Service Providers, and Balancing Authorities, and to allow adequate time for implementation.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 INT-001-0 was never enforceable</t>
   </si>
   <si>
@@ -2339,7 +2445,9 @@
     <t>To ensure that Interchange Transaction information is provided to all entities needing to make reliability assessments and to ensure all affected reliability entities assess the reliability impacts of Interchange Transactions before approving or denying a Tag. To communicate the approvals and denials of the Tag and the final composite status of the Tag.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 This standard was never enforceable</t>
   </si>
   <si>
@@ -2352,7 +2460,9 @@
     <t>To ensure Balancing Authorities confirm Interchange Schedules with Adjacent Balancing Authorities prior to implementing the schedules in their Area Control Error (ACE) equations. To ensure Balancing Authorities incorporate all confirmed Schedules into their ACE equations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 INT-003-0 was never enforceable</t>
   </si>
   <si>
@@ -2362,7 +2472,9 @@
     <t>To ensure Balancing Authorities confirm Interchange Schedules with Adjacent Balancing Authorities prior to implementing the schedules in their Area Control Error (ACE) equations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 INT-003-1 was never enforceable</t>
   </si>
   <si>
@@ -2501,7 +2613,8 @@
     <t>To ensure that Balancing Authorities implement the Interchange as agreed upon in the Interchange confirmation process.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-4-000
+    <t xml:space="preserve">Filing/Order Docket No. RD14-4-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -2550,13 +2663,15 @@
     <t>Reliability Coordination – Responsibilities and Authorities</t>
   </si>
   <si>
-    <t xml:space="preserve">Reliability Coordinators must have the authority, plans, and agreements in place to immediately direct reliability entities within their Reliability Coordinator Areas to redispatch generation, reconfigure transmission, or reduce load to mitigate critical conditions to rn the system to a reliable state. If a Reliability Coordinator delegates tasks to others, the
-Reliability Coordinator retains its responsibilities for complying with NERC and regional
-standards. Standards of conduct are necessary to ensure the Reliability Coordinator does not
+    <t>Reliability Coordinators must have the authority, plans, and agreements in place to immediately direct reliability entities within their Reliability Coordinator Areas to redispatch generation, reconfigure transmission, or reduce load to mitigate critical conditions to rn the system to a reliable state. If a Reliability Coordinator delegates tasks to others, the_x000D_
+Reliability Coordinator retains its responsibilities for complying with NERC and regional_x000D_
+standards. Standards of conduct are necessary to ensure the Reliability Coordinator does not_x000D_
 act in a manner that favors one market participant over another.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 IRO-001-0 was never enforceable</t>
   </si>
   <si>
@@ -2611,11 +2726,13 @@
     <t>Reliability Coordination – Facilities</t>
   </si>
   <si>
-    <t xml:space="preserve">Reliability Coordinators need information, tools and other capabilities to perform
+    <t>Reliability Coordinators need information, tools and other capabilities to perform_x000D_
 their responsibilities.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 IRO-002-0 was never enforceable</t>
   </si>
   <si>
@@ -2682,7 +2799,7 @@
     <t>Reliability Coordination – Wide-Area View</t>
   </si>
   <si>
-    <t xml:space="preserve">The Reliability Coordinator must have a wide area view of its own Reliability
+    <t>The Reliability Coordinator must have a wide area view of its own Reliability_x000D_
 Coordinator Area and that of neighboring Reliability Coordinators.</t>
   </si>
   <si>
@@ -2710,11 +2827,11 @@
     <t>Reliability Coordination — Operations Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">Each Reliability Coordinator must conduct next-day reliability analyses for its
-Reliability Coordinator Area to ensure the Bulk Electric System can be operated reliably in
-anticipated normal and Contingency conditions. System studies must be conducted to
-highlight potential interface and other operating limits, including overloaded transmission lines
-and transformers, voltage and stability limits, etc. Plans must be developed to alleviate System
+    <t>Each Reliability Coordinator must conduct next-day reliability analyses for its_x000D_
+Reliability Coordinator Area to ensure the Bulk Electric System can be operated reliably in_x000D_
+anticipated normal and Contingency conditions. System studies must be conducted to_x000D_
+highlight potential interface and other operating limits, including overloaded transmission lines_x000D_
+and transformers, voltage and stability limits, etc. Plans must be developed to alleviate System_x000D_
 Operating Limit (SOL) and Interconnection Reliability Operating Limit (IROL) violations.</t>
   </si>
   <si>
@@ -2736,7 +2853,7 @@
     <t>Reliability Coordination — Current Day Operations</t>
   </si>
   <si>
-    <t xml:space="preserve">The Reliability Coordinator must be continuously aware of conditions within its Reliability Coordinator Area and include this information in its reliability assessments. The Reliability Coordinator must monitor Bulk Electric System parameters that may have significant impacts upon the Reliability Coordinator Area and neighboring Reliability
+    <t>The Reliability Coordinator must be continuously aware of conditions within its Reliability Coordinator Area and include this information in its reliability assessments. The Reliability Coordinator must monitor Bulk Electric System parameters that may have significant impacts upon the Reliability Coordinator Area and neighboring Reliability_x000D_
 Coordinator Areas.</t>
   </si>
   <si>
@@ -2788,8 +2905,8 @@
     <t>Reliability Coordination — Transmission Loading Relief</t>
   </si>
   <si>
-    <t xml:space="preserve">Regardless of the process it uses, the Reliability Coordinator must direct its Balancing Authorities and Transmission Operators to return the transmission system to within its Interconnection Reliability Operating Limits as soon as possible, but no longer than 30 minutes. The Reliability Coordinator needs to direct Balancing Authorities and Transmission
-Operators to execute actions such as reconfiguration, redispatch, or load shedding until relief
+    <t>Regardless of the process it uses, the Reliability Coordinator must direct its Balancing Authorities and Transmission Operators to return the transmission system to within its Interconnection Reliability Operating Limits as soon as possible, but no longer than 30 minutes. The Reliability Coordinator needs to direct Balancing Authorities and Transmission_x000D_
+Operators to execute actions such as reconfiguration, redispatch, or load shedding until relief_x000D_
 requested by the TLR process is achieved.</t>
   </si>
   <si>
@@ -2802,7 +2919,9 @@
     <t>Regardless of the process it uses, the Reliability Coordinator must direct its Balancing Authorities and Transmission Operators to return the transmission system to within its Interconnection Reliability Operating Limits as soon as possible, but no longer than 30 minutes. The Reliability Coordinator needs to direct Balancing Authorities and Transmission Operators to execute actions such as reconfiguration, redispatch, or load shedding until relief requested by the TLR process is achieved.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 IRO-006-1 was never enforceable</t>
   </si>
   <si>
@@ -2872,7 +2991,8 @@
     <t>To provide and execute transmission loading relief procedures that can be used to mitigate SOL or IROL exceedances for the purpose of maintaining reliable operation of the bulk electric system in the ERCOT Region.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-1-000
+    <t xml:space="preserve">Filing/Order Docket No. RD12-1-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -2993,9 +3113,9 @@
     <t>Reliability Coordinator Data and Information Specification and Collection</t>
   </si>
   <si>
-    <t xml:space="preserve">To prevent instability, uncontrolled separation, or Cascading outages that 
-adversely impact reliability, by ensuring each Reliability Coordinator has the data and 
-information it needs to plan, monitor and assess the operation of its Reliability
+    <t>To prevent instability, uncontrolled separation, or Cascading outages that _x000D_
+adversely impact reliability, by ensuring each Reliability Coordinator has the data and _x000D_
+information it needs to plan, monitor and assess the operation of its Reliability_x000D_
 Coordinator Area.</t>
   </si>
   <si>
@@ -3113,7 +3233,10 @@
     <t>MOD-001-1a</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD10-5-000
+    <t xml:space="preserve">Filing/Order Docket No. RD10-5-000_x000D_
+_x000D_
+_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -3123,11 +3246,13 @@
     <t>MOD-001-2</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure that determinations of available transmission system capability are determined in a manner that supports the reliable operation of the Bulk-Power System (BPS) and that the methodology and data underlying those determinations are
+    <t>To ensure that determinations of available transmission system capability are determined in a manner that supports the reliable operation of the Bulk-Power System (BPS) and that the methodology and data underlying those determinations are_x000D_
 disclosed to those registered entities that need such information for reliability purposes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM14-7-000
+    <t>Filing/Order Docket No. RM14-7-000_x000D_
+_x000D_
+_x000D_
 Petition for approval was withdrawn as part of Project 2018-03 SER Retirements.</t>
   </si>
   <si>
@@ -3167,7 +3292,9 @@
     <t>To promote the consistent and reliable calculation, verification, preservation, and use of Capacity Benefit Margin (CBM) to support analysis and system operations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM05-17-000, RM05-25-000
+    <t>Filing/Order Docket No. RM05-17-000, RM05-25-000_x000D_
+_x000D_
+_x000D_
  </t>
   </si>
   <si>
@@ -3225,7 +3352,9 @@
     <t>To promote the consistent and reliable calculation, verification, preservation, and use of Transmission Reliability Margin (TRM) to support analysis and system operations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM08-19-000
+    <t>Filing/Order Docket No. RM08-19-000_x000D_
+_x000D_
+_x000D_
  </t>
   </si>
   <si>
@@ -3271,7 +3400,9 @@
     <t>Maintenance and Distribution of Dynamics Data Requirements and Reporting Procedures</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 MOD-013-0 was never enforceable</t>
   </si>
   <si>
@@ -3419,7 +3550,9 @@
     <t>To ensure that accurate information on generator gross and net Real and Reactive Power capability and synchronous condenser Reactive Power capability is available for planning models used to assess Bulk Electric System (BES) reliability.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
+    <t>Filing/Order Docket No. RM13-16-000_x000D_
+_x000D_
+_x000D_
 Please see the Implementation Plan for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -3444,14 +3577,19 @@
     <t>Verification of Models and Data for Generator Excitation Control System or Plant Volt/Var Control Functions</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify that the generator excitation control system or plant volt/var control function model (including the power system stabilizer model and the impedance compensator model) and the model parameters used in dynamic simulations accurately represent the generator excitation control system or plant volt/var control function behavior when assessing Bulk Electric System (BES) reliability.
-Footnote: Excitation control system or plant volt/var control function:
-a.    For individual synchronous machines, the generator excitation control system includes the generator, exciter, voltage regulator, impedance compensation and power system stabilizer.
-b.    For an aggregate generating plant, the volt/var control system includes the voltage regulator &amp; reactive power control system controlling and coordinating plant voltage and associated reactive capable resources.
+    <t xml:space="preserve">To verify that the generator excitation control system or plant volt/var control function model (including the power system stabilizer model and the impedance compensator model) and the model parameters used in dynamic simulations accurately represent the generator excitation control system or plant volt/var control function behavior when assessing Bulk Electric System (BES) reliability._x000D_
+ _x000D_
+Footnote: Excitation control system or plant volt/var control function:_x000D_
+ _x000D_
+a.    For individual synchronous machines, the generator excitation control system includes the generator, exciter, voltage regulator, impedance compensation and power system stabilizer._x000D_
+ _x000D_
+b.    For an aggregate generating plant, the volt/var control system includes the voltage regulator &amp; reactive power control system controlling and coordinating plant voltage and associated reactive capable resources._x000D_
  </t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
+    <t>Filing/Order Docket No. RM13-16-000_x000D_
+_x000D_
+_x000D_
 See Implementation Plan for additional compliance information</t>
   </si>
   <si>
@@ -3464,12 +3602,20 @@
     <t>To verify and validate that the dynamic models and associated parameters used to assess Bulk Electric System (BES) reliability represent the in-service equipment of Bulk Power System (BPS) facilities including generating facilities, transmission connected dynamic reactive resources, and high-voltage direct current (HVDC) systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD26-3-000
-Additional Effective Date Details
-Requirements R1 and R7 -   April 1, 2027
-Entities shall not be required to comply with Requirement R1 relating to the jointly developed dynamic model requirements between the Planning Coordinator and Transmission Planner and Requirement R7 relating to the provision of the current (in-use) models until twelve (12) months after the effective date of the Reliability Standard MOD-026-2.
-Requirements R2, R3, R4, R5, and R6 - April 1, 2029
-Entities shall not be required to comply with Requirements R2, R3, R4, R5, and R6 until thirty-six (36) months after the effective date of Reliability Standard MOD-026-2.
+    <t>Filing/Order Docket No. RD26-3-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+Additional Effective Date Details_x000D_
+Requirements R1 and R7 -   April 1, 2027_x000D_
+Entities shall not be required to comply with Requirement R1 relating to the jointly developed dynamic model requirements between the Planning Coordinator and Transmission Planner and Requirement R7 relating to the provision of the current (in-use) models until twelve (12) months after the effective date of the Reliability Standard MOD-026-2._x000D_
+_x000D_
+_x000D_
+Requirements R2, R3, R4, R5, and R6 - April 1, 2029_x000D_
+Entities shall not be required to comply with Requirements R2, R3, R4, R5, and R6 until thirty-six (36) months after the effective date of Reliability Standard MOD-026-2._x000D_
+_x000D_
+_x000D_
 See the Implementation Plan for additional information on Initial Performance Dates for periodic requirements, newly commissioned and newly applicable facilities, and early compliance.  </t>
   </si>
   <si>
@@ -3482,10 +3628,13 @@
     <t>Verification of Models and Data for Turbine/Governor and Load Control or Active Power/Frequency Control Functions</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify that the turbine/governor and load control or active power/frequency control model and the model parameters, used in dynamic simulations that assess Bulk Electric System (BES) reliability, accurately represent generator unit real power response to system frequency variations.
-Footnote: Turbine/governor and load control or active power/frequency control:
-a.     Turbine/governor and load control applies to conventional synchronous generation.
-b.     Active power/frequency control applies to inverter connected generators (often found at variable energy plants).
+    <t xml:space="preserve">To verify that the turbine/governor and load control or active power/frequency control model and the model parameters, used in dynamic simulations that assess Bulk Electric System (BES) reliability, accurately represent generator unit real power response to system frequency variations._x000D_
+ _x000D_
+Footnote: Turbine/governor and load control or active power/frequency control:_x000D_
+ _x000D_
+a.     Turbine/governor and load control applies to conventional synchronous generation._x000D_
+ _x000D_
+b.     Active power/frequency control applies to inverter connected generators (often found at variable energy plants)._x000D_
  </t>
   </si>
   <si>
@@ -3504,7 +3653,11 @@
     <t>MOD-028-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM12-19-000
+    <t>Filing/Order Docket No. RM12-19-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
  </t>
   </si>
   <si>
@@ -3538,7 +3691,9 @@
     <t>To increase consistency and reliability in the development and documentation of transfer capability calculations for short-term use performed by entities using the Flowgate Methodology to support analysis and system operations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM08-19-000
+    <t>Filing/Order Docket No. RM08-19-000_x000D_
+_x000D_
+_x000D_
 Withdrawn. FERC approved NERC's petition to withdraw its request for approval (Order 729)</t>
   </si>
   <si>
@@ -3551,7 +3706,11 @@
     <t>MOD-030-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000
+    <t>Filing/Order Docket No. RM15-13-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
  </t>
   </si>
   <si>
@@ -3594,7 +3753,9 @@
     <t>To establish consistent modeling data requirements and reporting procedures for development of planning horizon cases necessary to support analysis of the reliability of the interconnected transmission system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-5-000
+    <t>Filing/Order Docket No. RD14-5-000_x000D_
+_x000D_
+_x000D_
 Please see the implementation plan for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -3604,16 +3765,20 @@
     <t>MOD-032-2</t>
   </si>
   <si>
-    <t xml:space="preserve">To establish consistent modeling data requirements and reporting 
-procedures for development of planning horizon cases necessary to 
-support analysis of the reliability of the interconnected transmission 
+    <t>To establish consistent modeling data requirements and reporting _x000D_
+procedures for development of planning horizon cases necessary to _x000D_
+support analysis of the reliability of the interconnected transmission _x000D_
 system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD26-1-000
-Additional Effective Date Details
-Requirements R2, R3, and R4 - April 1, 2029
-Entities shall not be required to comply with Requirements R2, R3, and R4 relating to revised Planning Coordinator and Transmission Planner data requirements and reporting procedures developed under MOD-032-2 Requirement R1 and Attachment 1 until 12 months after the effective date of Reliability Standard MOD-032-2.
+    <t>Filing/Order Docket No. RD26-1-000_x000D_
+_x000D_
+_x000D_
+Additional Effective Date Details_x000D_
+Requirements R2, R3, and R4 - April 1, 2029_x000D_
+Entities shall not be required to comply with Requirements R2, R3, and R4 relating to revised Planning Coordinator and Transmission Planner data requirements and reporting procedures developed under MOD-032-2 Requirement R1 and Attachment 1 until 12 months after the effective date of Reliability Standard MOD-032-2._x000D_
+_x000D_
+_x000D_
 During the phased-in compliance period, entities shall continue to comply with Requirements R2, R3, and R4 related to Planning Coordinator / Transmission Planner data requirements and reporting procedures developed under MOD-032-1 Requirement R1 and Attachment 1 unless they are compliant with revised Planning Coordinator / Transmission Planner data requirements and reporting procedures under Reliability Standard MOD-032-2 Requirement R1.</t>
   </si>
   <si>
@@ -3635,7 +3800,7 @@
     <t>MOD-033-3</t>
   </si>
   <si>
-    <t xml:space="preserve">To establish a process for system model validation to facilitate achieving 
+    <t>To establish a process for system model validation to facilitate achieving _x000D_
 and maintaining model accuracy.</t>
   </si>
   <si>
@@ -3753,7 +3918,9 @@
     <t>Reliability Coordinators must have sufficient, competent staff to perform the Reliability Coordinator functions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 PER-004-0 was never enforceable</t>
   </si>
   <si>
@@ -3820,7 +3987,9 @@
     <t>To ensure system protection is coordinated among operating entities.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 PRC-001-0 was never enforceable</t>
   </si>
   <si>
@@ -3860,7 +4029,9 @@
     <t>To ensure that Disturbance monitoring equipment is installed in a uniform manner to facilitate development of models and analyses of events.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 PRC-002-0 was never enforceable</t>
   </si>
   <si>
@@ -3876,7 +4047,9 @@
     <t>Ensure that Regional Reliability Organizations establish requirements for installation of Disturbance Monitoring Equipment (DME) and reporting of Disturbance data to facilitate analyses of events and verify system models.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000,  RM06-22-000
+    <t>Filing/Order Docket No. RM06-16-000,  RM06-22-000_x000D_
+_x000D_
+_x000D_
 This Standard was not approved by FERC in Order 693. See Standards Under Development page or Reliability Standards Development Plan for more information.</t>
   </si>
   <si>
@@ -3889,7 +4062,8 @@
     <t>To have adequate data available to facilitate analysis of Bulk Electric System (BES) Disturbances.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-4-000
+    <t xml:space="preserve">Filing/Order Docket No. RM15-4-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -3905,7 +4079,7 @@
     <t>PRC-002-4</t>
   </si>
   <si>
-    <t xml:space="preserve">To have adequate data available to facilitate analysis of Bulk Electric
+    <t>To have adequate data available to facilitate analysis of Bulk Electric_x000D_
 System (BES) Disturbances.</t>
   </si>
   <si>
@@ -4014,7 +4188,8 @@
     <t>Identify and correct the causes of Misoperations of Protection Systems for Bulk Electric System (BES) Elements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-14-000
+    <t xml:space="preserve">Filing/Order Docket No. RD14-14-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4024,14 +4199,16 @@
     <t>PRC-004-3(i)</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-14-001, RD15-3-001 and RD15-5-001
+    <t xml:space="preserve">Filing/Order Docket No. RD14-14-001, RD15-3-001 and RD15-5-001_x000D_
+_x000D_
 </t>
   </si>
   <si>
     <t>PRC-004-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000
+    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4044,7 +4221,8 @@
     <t>PRC-004-5</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-5-000
+    <t xml:space="preserve">Filing/Order Docket No. RD15-5-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4081,8 +4259,8 @@
     <t>Transmission Protection System Maintenance and Testing</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure all transmission protection system misoperations are analyzed for
-cause and corrective action, and maintenance and testing programs are developed and
+    <t>To ensure all transmission protection system misoperations are analyzed for_x000D_
+cause and corrective action, and maintenance and testing programs are developed and_x000D_
 implemented.</t>
   </si>
   <si>
@@ -4134,7 +4312,9 @@
     <t>PRC-005-2(ii)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entities with newly classified “Remedial Action Scheme” (RAS) resulting from the application of the revised definition must be fully compliant with all Reliability Standards applicable RAS twenty-four (24) months from the Effective Date of the revised definition. PRC-004-WECC-2 replaces PRC-004-WECC-1. NERC filed a joint petition March 9, 2018 for approval of retirement of PRC-004-WECC-2.
+    <t>Entities with newly classified “Remedial Action Scheme” (RAS) resulting from the application of the revised definition must be fully compliant with all Reliability Standards applicable RAS twenty-four (24) months from the Effective Date of the revised definition. PRC-004-WECC-2 replaces PRC-004-WECC-1. NERC filed a joint petition March 9, 2018 for approval of retirement of PRC-004-WECC-2._x000D_
+_x000D_
+_x000D_
 Retired by PRC-005-6; PRC-005-2(ii) was never enforceable</t>
   </si>
   <si>
@@ -4159,7 +4339,9 @@
     <t>PRC-005-3(ii)</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000
+    <t>Filing/Order Docket No. RM15-13-000_x000D_
+_x000D_
+_x000D_
 Retired by PRC-005-6; PRC-005-3(ii) was never enforceable.</t>
   </si>
   <si>
@@ -4187,7 +4369,9 @@
     <t>PRC-005-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD16-2-000
+    <t>Filing/Order Docket No. RD16-2-000_x000D_
+_x000D_
+_x000D_
 Due to the complex compliance requirements, please refer to the implementation plan for the phased-in details.</t>
   </si>
   <si>
@@ -4224,7 +4408,8 @@
     <t>PRC-006-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-2-000
+    <t xml:space="preserve">Filing/Order Docket No. RD15-2-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4279,8 +4464,10 @@
     <t>PRC-006-SERC-03</t>
   </si>
   <si>
-    <t xml:space="preserve">To establish consistent and coordinated requirements for the design,
-implementation, and analysis of automatic underfrequency load shedding (UFLS)
+    <t>To establish consistent and coordinated requirements for the design,_x000D_
+ _x000D_
+implementation, and analysis of automatic underfrequency load shedding (UFLS)_x000D_
+ _x000D_
 programs among all SERC applicable entities.</t>
   </si>
   <si>
@@ -4296,7 +4483,10 @@
     <t>To develop, coordinate and document requirements for automatic underfrequency load shedding (UFLS) programs to arrest declining frequency and assist recovery of frequency following underfrequency events.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD13-9-000
+    <t xml:space="preserve">Filing/Order Docket No. RD13-9-000_x000D_
+_x000D_
+_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4366,7 +4556,7 @@
     <t>Special Protection System Review Procedure</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure that all Special Protection Systems (SPS) are properly designed, meet
+    <t>To ensure that all Special Protection Systems (SPS) are properly designed, meet_x000D_
 performance requirements, and are coordinated with other protection systems. To ensure that maintenance and testing programs are developed and misoperations are analyzed and corrected.</t>
   </si>
   <si>
@@ -4418,8 +4608,8 @@
     <t>Special Protection System Assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure that all Special Protection Systems (SPS) are properly designed, meet
-performance requirements, and are coordinated with other protection systems. To ensure that
+    <t>To ensure that all Special Protection Systems (SPS) are properly designed, meet_x000D_
+performance requirements, and are coordinated with other protection systems. To ensure that_x000D_
 maintenance and testing programs are developed and misoperations are analyzed and corrected.</t>
   </si>
   <si>
@@ -4492,7 +4682,9 @@
     <t>To verify coordination of generating unit Facility or synchronous condenser voltage regulating controls, limit functions, equipment capabilities and Protection System settings.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
+    <t>Filing/Order Docket No. RM13-16-000_x000D_
+_x000D_
+_x000D_
 Please see the Implementation Plan for specific compliance dates and timeframes. The standard will become inactive 6/30/16.</t>
   </si>
   <si>
@@ -4502,7 +4694,9 @@
     <t>Coordination of Generating Unit or Plant Capabilities, Voltage Regulating Controls, and Protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000
+    <t>Filing/Order Docket No. RD15-3-000_x000D_
+_x000D_
+_x000D_
 Please see the Implementation Plan for Version 1 for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -4581,13 +4775,14 @@
     <t>PRC-023-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Protective relay settings shall not limit transmission loadability; not interfere
-with system operators’ ability to take remedial action to protect system reliability and; be
-set to reliably detect all fault conditions and protect the electrical network from these
+    <t>Protective relay settings shall not limit transmission loadability; not interfere_x000D_
+with system operators’ ability to take remedial action to protect system reliability and; be_x000D_
+set to reliably detect all fault conditions and protect the electrical network from these_x000D_
 faults.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD23-5-000
+    <t xml:space="preserve">Filing/Order Docket No. RD23-5-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4603,14 +4798,16 @@
     <t>Ensure Generator Owners set their generator protective relays such that generating units remain connected during defined frequency and voltage excursions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
+    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
     <t>PRC-024-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000
+    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4638,7 +4835,9 @@
     <t>To assure that protection of synchronous generators, type 1 and type 2 wind resources, and synchronous condensers do not cause tripping during defined frequency and voltage excursions in support of the Bulk Power System (BPS).</t>
   </si>
   <si>
-    <t xml:space="preserve">Docket No. RM25-3-000
+    <t>Docket No. RM25-3-000_x000D_
+_x000D_
+_x000D_
 See Implementation Plan for more information on effective/compliance dates</t>
   </si>
   <si>
@@ -4654,7 +4853,11 @@
     <t>To set load-responsive protective relays associated with generation Facilities at a level to prevent unnecessary tripping of generators during a system disturbance for conditions that do not pose a risk of damage to the associated equipment.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-19-000
+    <t>Filing/Order Docket No. RM13-19-000_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
 See Implementation Plan. For applicable relays where the entity has determined replacement or removal is not necessary, the entity shall be compliant by 10/1/2019. For applicable relays where the entity has determined replacement or removal is necessary, the entity shall be compliant by 10/1/2021.</t>
   </si>
   <si>
@@ -4676,7 +4879,8 @@
     <t>To ensure that load-responsive protective relays are expected to not trip in response to stable power swings during non-Fault conditions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-8-000
+    <t xml:space="preserve">Filing/Order Docket No. RM15-8-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4722,7 +4926,9 @@
     <t>Identify, analyze, and mitigate unexpected Inverter-Based Resource (IBR) change of power output.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD25-3-000
+    <t>Filing/Order Docket No. RD25-3-000_x000D_
+_x000D_
+_x000D_
 See Implementation Plan for more effective/compliance date information</t>
   </si>
   <si>
@@ -4885,7 +5091,8 @@
     <t>To ensure that the Transmission Operator and Balancing Authority have data needed to fulfill their operational and planning responsibilities.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-16-000
+    <t xml:space="preserve">Filing/Order Docket No. RM15-16-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -4901,7 +5108,9 @@
     <t>Transmission Operator and Balancing Authority Data and Information  Specification and Collection</t>
   </si>
   <si>
-    <t xml:space="preserve"> To ensure that each Transmission Operator and Balancing Authority has the data and information it needs to plan, monitor, and assess the operation of its
+    <t> To ensure that each Transmission Operator and Balancing Authority has the data and information it needs to plan, monitor, and assess the operation of its_x000D_
+_x000D_
+_x000D_
   Transmission Operator Area or Balancing Authority Area.</t>
   </si>
   <si>
@@ -4923,9 +5132,9 @@
     <t>TOP-003-8</t>
   </si>
   <si>
-    <t xml:space="preserve">To ensure that each Transmission Operator and Balancing Authority has 
-the data and information it needs to plan, monitor, and assess the 
-operation of its Transmission Operator Area or Balancing Authority 
+    <t>To ensure that each Transmission Operator and Balancing Authority has _x000D_
+the data and information it needs to plan, monitor, and assess the _x000D_
+operation of its Transmission Operator Area or Balancing Authority _x000D_
 Area.</t>
   </si>
   <si>
@@ -4935,7 +5144,9 @@
     <t>To ensure that the transmission system is operated so that instability, uncontrolled separation, or cascading outages will not occur as a result of the most severe single Contingency and specified multiple Contingencies.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 TOP-004-0 was never enforceable</t>
   </si>
   <si>
@@ -4984,7 +5195,9 @@
     <t>To ensure critical reliability parameters are monitored in real-time.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 TOP-006-0 was never enforceable</t>
   </si>
   <si>
@@ -5057,7 +5270,8 @@
     <t>Real-time Reliability Monitoring and Analysis Capabilities</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD16-6-000
+    <t xml:space="preserve">Filing/Order Docket No. RD16-6-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -5199,7 +5413,8 @@
     <t>TPL-003-0b</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD13-8-000
+    <t xml:space="preserve">Filing/Order Docket No. RD13-8-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -5284,7 +5499,8 @@
     <t>TPL-007-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM18-8-000
+    <t xml:space="preserve">Filing/Order Docket No. RM18-8-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -5297,7 +5513,9 @@
     <t>TPL-007-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD20-3-000
+    <t>Filing/Order Docket No. RD20-3-000_x000D_
+_x000D_
+_x000D_
 This Variance shall be applicable in those Canadian jurisdictions where the Variance has been approved for use by the applicable governmental authority or has otherwise become effective in the jurisdiction.</t>
   </si>
   <si>
@@ -5331,7 +5549,9 @@
     <t>To ensure voltage levels, reactive flows, and reactive resources are monitored, controlled, and maintained within limits in real time to protect equipment and the reliable operation of the Interconnection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
+    <t>Filing/Order Docket No. RM06-16-000_x000D_
+_x000D_
+_x000D_
 VAR-001-0 was never enforceable</t>
   </si>
   <si>
@@ -5374,7 +5594,8 @@
     <t>VAR-001-4.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000
+    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -5390,7 +5611,9 @@
     <t>VAR-001-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM19-16-000
+    <t>Filing/Order Docket No. RM19-16-000_x000D_
+_x000D_
+_x000D_
 Standard withdrawn on 5/14/2020.</t>
   </si>
   <si>
@@ -5439,7 +5662,8 @@
     <t>VAR-002-4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000
+    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -5476,7 +5700,8 @@
     <t>To ensure the Western Interconnection is operated in a coordinated manner under normal and abnormal conditions by establishing the performance criteria for WECC power system stabilizers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-5-000
+    <t xml:space="preserve">Filing/Order Docket No. RD17-5-000_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -5516,11 +5741,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="m\/d\/yyyy"/>
+    <numFmt numFmtId="164" formatCode="m\/d\/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -5528,19 +5753,19 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="00333333"/>
+      <color rgb="FF333333"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
       <sz val="9"/>
-      <color rgb="000000FF"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -5549,10 +5774,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="00000000"/>
-        <bgColor rgb="00000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -5583,31 +5805,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="003877A6"/>
+        <color rgb="FF3877A6"/>
       </left>
       <right style="thin">
-        <color rgb="003877A6"/>
+        <color rgb="FF3877A6"/>
       </right>
       <top style="thin">
-        <color rgb="003877A6"/>
+        <color rgb="FF3877A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00A5A5B1"/>
+        <color rgb="FFA5A5B1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00EBEBEB"/>
+        <color rgb="FFEBEBEB"/>
       </left>
       <right style="thin">
-        <color rgb="00EBEBEB"/>
+        <color rgb="FFEBEBEB"/>
       </right>
       <top style="thin">
-        <color rgb="00EBEBEB"/>
+        <color rgb="FFEBEBEB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00EBEBEB"/>
+        <color rgb="FFEBEBEB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5615,108 +5837,428 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="bottom"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R650"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.9715986666667" customWidth="1"/>
-    <col min="2" max="3" width="24.1017" customWidth="1"/>
-    <col min="4" max="4" width="47.9139986666667" customWidth="1"/>
-    <col min="5" max="7" width="10.7163133333333" customWidth="1"/>
-    <col min="8" max="8" width="12.5491986666667" customWidth="1"/>
-    <col min="9" max="9" width="10.7163133333333" customWidth="1"/>
-    <col min="10" max="10" width="16.1161" customWidth="1"/>
-    <col min="11" max="11" width="10.7163133333333" customWidth="1"/>
-    <col min="12" max="12" width="19.002324" customWidth="1"/>
-    <col min="13" max="13" width="49.1993" customWidth="1"/>
-    <col min="14" max="16" width="14.1158973333333" customWidth="1"/>
-    <col min="17" max="17" width="15.4011986666667" customWidth="1"/>
-    <col min="18" max="18" width="16.5419986666667" customWidth="1"/>
-    <col min="19" max="19" width="4.67767866666667" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="3" width="24.08984375" customWidth="1"/>
+    <col min="4" max="4" width="47.90625" customWidth="1"/>
+    <col min="5" max="7" width="10.7265625" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="49.1796875" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" customWidth="1"/>
+    <col min="17" max="17" width="15.36328125" customWidth="1"/>
+    <col min="18" max="18" width="16.54296875" customWidth="1"/>
+    <col min="19" max="19" width="4.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="55.9965" customHeight="1">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="37.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5772,7 +6314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="2" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
@@ -5814,7 +6356,7 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="3" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -5856,7 +6398,7 @@
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="4" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
@@ -5898,7 +6440,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="5" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
@@ -5942,7 +6484,7 @@
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="6" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
@@ -5988,7 +6530,7 @@
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="7" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
@@ -6032,7 +6574,7 @@
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="8" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
@@ -6076,7 +6618,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="9" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>18</v>
       </c>
@@ -6118,7 +6660,7 @@
       <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="10" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -6162,7 +6704,7 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="11" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>18</v>
       </c>
@@ -6200,7 +6742,7 @@
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="12" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
@@ -6242,7 +6784,7 @@
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="13" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>18</v>
       </c>
@@ -6284,7 +6826,7 @@
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="14" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>30</v>
       </c>
@@ -6332,7 +6874,7 @@
       </c>
       <c r="R14" s="7"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="15" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6368,7 +6910,7 @@
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="16" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
@@ -6412,7 +6954,7 @@
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="17" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>18</v>
       </c>
@@ -6456,7 +6998,7 @@
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="18" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
@@ -6500,7 +7042,7 @@
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="19" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>18</v>
       </c>
@@ -6542,7 +7084,7 @@
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="20" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
@@ -6584,7 +7126,7 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="21" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>18</v>
       </c>
@@ -6626,7 +7168,7 @@
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="22" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
@@ -6668,7 +7210,7 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="23" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>18</v>
       </c>
@@ -6708,7 +7250,7 @@
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="24" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>18</v>
       </c>
@@ -6752,7 +7294,7 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="25" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>18</v>
       </c>
@@ -6798,7 +7340,7 @@
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="26" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>30</v>
       </c>
@@ -6844,7 +7386,7 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="27" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>18</v>
       </c>
@@ -6888,7 +7430,7 @@
       <c r="Q27" s="12"/>
       <c r="R27" s="12"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="28" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>18</v>
       </c>
@@ -6924,7 +7466,7 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
     </row>
-    <row r="29" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="29" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>18</v>
       </c>
@@ -6968,7 +7510,7 @@
       <c r="Q29" s="12"/>
       <c r="R29" s="12"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="30" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>18</v>
       </c>
@@ -7012,7 +7554,7 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="31" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>18</v>
       </c>
@@ -7056,7 +7598,7 @@
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="32" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>30</v>
       </c>
@@ -7100,7 +7642,7 @@
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="33" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>18</v>
       </c>
@@ -7142,7 +7684,7 @@
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="34" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>18</v>
       </c>
@@ -7184,7 +7726,7 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="35" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>18</v>
       </c>
@@ -7228,7 +7770,7 @@
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="36" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>18</v>
       </c>
@@ -7264,7 +7806,7 @@
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="37" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>18</v>
       </c>
@@ -7306,7 +7848,7 @@
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="38" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>30</v>
       </c>
@@ -7354,7 +7896,7 @@
       </c>
       <c r="R38" s="7"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="39" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>18</v>
       </c>
@@ -7390,7 +7932,7 @@
       <c r="Q39" s="12"/>
       <c r="R39" s="12"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="40" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>18</v>
       </c>
@@ -7432,7 +7974,7 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="41" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>18</v>
       </c>
@@ -7474,7 +8016,7 @@
       <c r="Q41" s="12"/>
       <c r="R41" s="12"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="42" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
@@ -7518,7 +8060,7 @@
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="43" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>139</v>
       </c>
@@ -7564,7 +8106,7 @@
       </c>
       <c r="R43" s="12"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="44" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>145</v>
       </c>
@@ -7602,7 +8144,7 @@
       </c>
       <c r="R44" s="7"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="45" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>30</v>
       </c>
@@ -7646,7 +8188,7 @@
       <c r="Q45" s="12"/>
       <c r="R45" s="12"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="46" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>18</v>
       </c>
@@ -7688,7 +8230,7 @@
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="47" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>18</v>
       </c>
@@ -7730,7 +8272,7 @@
       <c r="Q47" s="12"/>
       <c r="R47" s="12"/>
     </row>
-    <row r="48" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="48" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>18</v>
       </c>
@@ -7766,7 +8308,7 @@
       <c r="Q48" s="7"/>
       <c r="R48" s="7"/>
     </row>
-    <row r="49" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="49" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>18</v>
       </c>
@@ -7808,7 +8350,7 @@
       <c r="Q49" s="12"/>
       <c r="R49" s="12"/>
     </row>
-    <row r="50" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="50" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>18</v>
       </c>
@@ -7850,7 +8392,7 @@
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
     </row>
-    <row r="51" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="51" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>18</v>
       </c>
@@ -7894,7 +8436,7 @@
       <c r="Q51" s="12"/>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" s="1" customFormat="1" ht="245.8513" customHeight="1">
+    <row r="52" spans="1:18" s="1" customFormat="1" ht="163.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>18</v>
       </c>
@@ -7936,7 +8478,7 @@
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="53" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>18</v>
       </c>
@@ -7978,7 +8520,7 @@
       <c r="Q53" s="12"/>
       <c r="R53" s="12"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="54" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>18</v>
       </c>
@@ -8022,7 +8564,7 @@
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="55" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>18</v>
       </c>
@@ -8058,7 +8600,7 @@
       <c r="Q55" s="12"/>
       <c r="R55" s="12"/>
     </row>
-    <row r="56" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="56" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>18</v>
       </c>
@@ -8092,7 +8634,7 @@
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="278.3826" customHeight="1">
+    <row r="57" spans="1:18" s="1" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -8128,7 +8670,7 @@
       <c r="Q57" s="12"/>
       <c r="R57" s="12"/>
     </row>
-    <row r="58" s="1" customFormat="1" ht="278.3826" customHeight="1">
+    <row r="58" spans="1:18" s="1" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>18</v>
       </c>
@@ -8164,7 +8706,7 @@
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
     </row>
-    <row r="59" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="59" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>18</v>
       </c>
@@ -8208,7 +8750,7 @@
       <c r="Q59" s="12"/>
       <c r="R59" s="12"/>
     </row>
-    <row r="60" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="60" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>18</v>
       </c>
@@ -8246,7 +8788,7 @@
       <c r="Q60" s="7"/>
       <c r="R60" s="7"/>
     </row>
-    <row r="61" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="61" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>18</v>
       </c>
@@ -8284,7 +8826,7 @@
       <c r="Q61" s="12"/>
       <c r="R61" s="12"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="62" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>18</v>
       </c>
@@ -8328,7 +8870,7 @@
       <c r="Q62" s="7"/>
       <c r="R62" s="7"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="63" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>30</v>
       </c>
@@ -8376,7 +8918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="64" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>18</v>
       </c>
@@ -8414,7 +8956,7 @@
       <c r="Q64" s="7"/>
       <c r="R64" s="7"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="65" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>145</v>
       </c>
@@ -8454,7 +8996,7 @@
       </c>
       <c r="R65" s="12"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="66" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>145</v>
       </c>
@@ -8494,7 +9036,7 @@
       </c>
       <c r="R66" s="7"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="67" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>18</v>
       </c>
@@ -8536,7 +9078,7 @@
       <c r="Q67" s="12"/>
       <c r="R67" s="12"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="68" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>145</v>
       </c>
@@ -8576,7 +9118,7 @@
       </c>
       <c r="R68" s="7"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="69" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>145</v>
       </c>
@@ -8616,7 +9158,7 @@
       </c>
       <c r="R69" s="12"/>
     </row>
-    <row r="70" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="70" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>18</v>
       </c>
@@ -8658,7 +9200,7 @@
       <c r="Q70" s="7"/>
       <c r="R70" s="7"/>
     </row>
-    <row r="71" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="71" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>18</v>
       </c>
@@ -8702,7 +9244,7 @@
       <c r="Q71" s="12"/>
       <c r="R71" s="12"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="72" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>18</v>
       </c>
@@ -8736,7 +9278,7 @@
       <c r="Q72" s="7"/>
       <c r="R72" s="7"/>
     </row>
-    <row r="73" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="73" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>18</v>
       </c>
@@ -8780,7 +9322,7 @@
       <c r="Q73" s="12"/>
       <c r="R73" s="12"/>
     </row>
-    <row r="74" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="74" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>18</v>
       </c>
@@ -8814,7 +9356,7 @@
       <c r="Q74" s="7"/>
       <c r="R74" s="7"/>
     </row>
-    <row r="75" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="75" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>18</v>
       </c>
@@ -8856,7 +9398,7 @@
       <c r="Q75" s="12"/>
       <c r="R75" s="12"/>
     </row>
-    <row r="76" s="1" customFormat="1" ht="138.1247" customHeight="1">
+    <row r="76" spans="1:18" s="1" customFormat="1" ht="92.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>18</v>
       </c>
@@ -8902,7 +9444,7 @@
       <c r="Q76" s="7"/>
       <c r="R76" s="7"/>
     </row>
-    <row r="77" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="77" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>18</v>
       </c>
@@ -8946,7 +9488,7 @@
       <c r="Q77" s="12"/>
       <c r="R77" s="12"/>
     </row>
-    <row r="78" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="78" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>30</v>
       </c>
@@ -8994,7 +9536,7 @@
       <c r="Q78" s="7"/>
       <c r="R78" s="7"/>
     </row>
-    <row r="79" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="79" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>139</v>
       </c>
@@ -9042,7 +9584,7 @@
       </c>
       <c r="R79" s="12"/>
     </row>
-    <row r="80" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="80" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>18</v>
       </c>
@@ -9084,7 +9626,7 @@
       <c r="Q80" s="7"/>
       <c r="R80" s="7"/>
     </row>
-    <row r="81" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="81" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>18</v>
       </c>
@@ -9126,7 +9668,7 @@
       <c r="Q81" s="12"/>
       <c r="R81" s="12"/>
     </row>
-    <row r="82" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="82" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>18</v>
       </c>
@@ -9170,7 +9712,7 @@
       <c r="Q82" s="7"/>
       <c r="R82" s="7"/>
     </row>
-    <row r="83" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="83" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>18</v>
       </c>
@@ -9214,7 +9756,7 @@
       <c r="Q83" s="12"/>
       <c r="R83" s="12"/>
     </row>
-    <row r="84" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="84" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>18</v>
       </c>
@@ -9256,7 +9798,7 @@
       <c r="Q84" s="7"/>
       <c r="R84" s="7"/>
     </row>
-    <row r="85" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="85" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>18</v>
       </c>
@@ -9300,7 +9842,7 @@
       <c r="Q85" s="12"/>
       <c r="R85" s="12"/>
     </row>
-    <row r="86" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="86" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>18</v>
       </c>
@@ -9336,7 +9878,7 @@
       <c r="Q86" s="7"/>
       <c r="R86" s="7"/>
     </row>
-    <row r="87" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="87" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>18</v>
       </c>
@@ -9378,7 +9920,7 @@
       <c r="Q87" s="12"/>
       <c r="R87" s="12"/>
     </row>
-    <row r="88" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="88" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>18</v>
       </c>
@@ -9424,7 +9966,7 @@
       <c r="Q88" s="7"/>
       <c r="R88" s="7"/>
     </row>
-    <row r="89" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="89" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>30</v>
       </c>
@@ -9474,7 +10016,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="90" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>145</v>
       </c>
@@ -9514,7 +10056,7 @@
       </c>
       <c r="R90" s="7"/>
     </row>
-    <row r="91" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="91" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>18</v>
       </c>
@@ -9556,7 +10098,7 @@
       <c r="Q91" s="12"/>
       <c r="R91" s="12"/>
     </row>
-    <row r="92" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="92" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>18</v>
       </c>
@@ -9590,7 +10132,7 @@
       <c r="Q92" s="7"/>
       <c r="R92" s="7"/>
     </row>
-    <row r="93" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="93" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>18</v>
       </c>
@@ -9632,7 +10174,7 @@
       <c r="Q93" s="12"/>
       <c r="R93" s="12"/>
     </row>
-    <row r="94" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="94" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>18</v>
       </c>
@@ -9672,7 +10214,7 @@
       <c r="Q94" s="7"/>
       <c r="R94" s="7"/>
     </row>
-    <row r="95" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="95" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>18</v>
       </c>
@@ -9714,7 +10256,7 @@
       <c r="Q95" s="12"/>
       <c r="R95" s="12"/>
     </row>
-    <row r="96" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="96" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>18</v>
       </c>
@@ -9758,7 +10300,7 @@
       <c r="Q96" s="7"/>
       <c r="R96" s="7"/>
     </row>
-    <row r="97" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="97" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>18</v>
       </c>
@@ -9802,7 +10344,7 @@
       <c r="Q97" s="12"/>
       <c r="R97" s="12"/>
     </row>
-    <row r="98" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="98" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>18</v>
       </c>
@@ -9846,7 +10388,7 @@
       <c r="Q98" s="7"/>
       <c r="R98" s="7"/>
     </row>
-    <row r="99" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="99" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>18</v>
       </c>
@@ -9890,7 +10432,7 @@
       <c r="Q99" s="12"/>
       <c r="R99" s="12"/>
     </row>
-    <row r="100" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="100" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>30</v>
       </c>
@@ -9938,7 +10480,7 @@
       </c>
       <c r="R100" s="7"/>
     </row>
-    <row r="101" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="101" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>145</v>
       </c>
@@ -9978,7 +10520,7 @@
       </c>
       <c r="R101" s="12"/>
     </row>
-    <row r="102" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="102" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>18</v>
       </c>
@@ -10020,7 +10562,7 @@
       <c r="Q102" s="7"/>
       <c r="R102" s="7"/>
     </row>
-    <row r="103" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="103" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>18</v>
       </c>
@@ -10054,7 +10596,7 @@
       <c r="Q103" s="12"/>
       <c r="R103" s="12"/>
     </row>
-    <row r="104" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="104" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>18</v>
       </c>
@@ -10088,7 +10630,7 @@
       <c r="Q104" s="7"/>
       <c r="R104" s="7"/>
     </row>
-    <row r="105" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="105" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>18</v>
       </c>
@@ -10122,7 +10664,7 @@
       <c r="Q105" s="12"/>
       <c r="R105" s="12"/>
     </row>
-    <row r="106" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="106" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>18</v>
       </c>
@@ -10164,7 +10706,7 @@
       <c r="Q106" s="7"/>
       <c r="R106" s="7"/>
     </row>
-    <row r="107" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="107" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>18</v>
       </c>
@@ -10206,7 +10748,7 @@
       <c r="Q107" s="12"/>
       <c r="R107" s="12"/>
     </row>
-    <row r="108" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="108" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>18</v>
       </c>
@@ -10244,7 +10786,7 @@
       <c r="Q108" s="7"/>
       <c r="R108" s="7"/>
     </row>
-    <row r="109" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="109" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>18</v>
       </c>
@@ -10284,7 +10826,7 @@
       <c r="Q109" s="12"/>
       <c r="R109" s="12"/>
     </row>
-    <row r="110" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="110" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>18</v>
       </c>
@@ -10324,7 +10866,7 @@
       <c r="Q110" s="7"/>
       <c r="R110" s="7"/>
     </row>
-    <row r="111" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="111" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>18</v>
       </c>
@@ -10366,7 +10908,7 @@
       <c r="Q111" s="12"/>
       <c r="R111" s="12"/>
     </row>
-    <row r="112" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="112" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>18</v>
       </c>
@@ -10410,7 +10952,7 @@
       <c r="Q112" s="7"/>
       <c r="R112" s="7"/>
     </row>
-    <row r="113" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="113" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>18</v>
       </c>
@@ -10448,7 +10990,7 @@
       <c r="Q113" s="12"/>
       <c r="R113" s="12"/>
     </row>
-    <row r="114" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="114" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>18</v>
       </c>
@@ -10492,7 +11034,7 @@
       <c r="Q114" s="7"/>
       <c r="R114" s="7"/>
     </row>
-    <row r="115" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="115" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>18</v>
       </c>
@@ -10530,7 +11072,7 @@
       <c r="Q115" s="12"/>
       <c r="R115" s="12"/>
     </row>
-    <row r="116" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="116" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>18</v>
       </c>
@@ -10572,7 +11114,7 @@
       <c r="Q116" s="7"/>
       <c r="R116" s="7"/>
     </row>
-    <row r="117" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="117" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>30</v>
       </c>
@@ -10618,11 +11160,11 @@
         <v>34</v>
       </c>
       <c r="Q117" s="12"/>
-      <c r="R117" s="21" t="s">
+      <c r="R117" s="20" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="118" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>145</v>
       </c>
@@ -10662,7 +11204,7 @@
       </c>
       <c r="R118" s="7"/>
     </row>
-    <row r="119" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="119" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>18</v>
       </c>
@@ -10704,7 +11246,7 @@
       <c r="Q119" s="12"/>
       <c r="R119" s="12"/>
     </row>
-    <row r="120" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="120" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>18</v>
       </c>
@@ -10744,7 +11286,7 @@
       <c r="Q120" s="7"/>
       <c r="R120" s="7"/>
     </row>
-    <row r="121" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="121" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>18</v>
       </c>
@@ -10786,7 +11328,7 @@
       <c r="Q121" s="12"/>
       <c r="R121" s="12"/>
     </row>
-    <row r="122" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="122" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>18</v>
       </c>
@@ -10820,7 +11362,7 @@
       <c r="Q122" s="7"/>
       <c r="R122" s="7"/>
     </row>
-    <row r="123" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="123" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>18</v>
       </c>
@@ -10864,7 +11406,7 @@
       <c r="Q123" s="12"/>
       <c r="R123" s="12"/>
     </row>
-    <row r="124" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="124" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>18</v>
       </c>
@@ -10898,7 +11440,7 @@
       <c r="Q124" s="7"/>
       <c r="R124" s="7"/>
     </row>
-    <row r="125" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="125" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>18</v>
       </c>
@@ -10942,7 +11484,7 @@
       <c r="Q125" s="12"/>
       <c r="R125" s="12"/>
     </row>
-    <row r="126" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="126" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>18</v>
       </c>
@@ -10976,7 +11518,7 @@
       <c r="Q126" s="7"/>
       <c r="R126" s="7"/>
     </row>
-    <row r="127" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="127" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>18</v>
       </c>
@@ -11018,7 +11560,7 @@
       <c r="Q127" s="12"/>
       <c r="R127" s="12"/>
     </row>
-    <row r="128" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="128" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>30</v>
       </c>
@@ -11068,7 +11610,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="129" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="129" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>145</v>
       </c>
@@ -11108,7 +11650,7 @@
       </c>
       <c r="R129" s="12"/>
     </row>
-    <row r="130" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="130" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>18</v>
       </c>
@@ -11150,7 +11692,7 @@
       <c r="Q130" s="7"/>
       <c r="R130" s="7"/>
     </row>
-    <row r="131" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="131" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>18</v>
       </c>
@@ -11192,7 +11734,7 @@
       <c r="Q131" s="12"/>
       <c r="R131" s="12"/>
     </row>
-    <row r="132" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="132" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>18</v>
       </c>
@@ -11236,7 +11778,7 @@
       <c r="Q132" s="7"/>
       <c r="R132" s="7"/>
     </row>
-    <row r="133" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="133" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>18</v>
       </c>
@@ -11278,7 +11820,7 @@
       <c r="Q133" s="12"/>
       <c r="R133" s="12"/>
     </row>
-    <row r="134" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="134" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>18</v>
       </c>
@@ -11324,7 +11866,7 @@
       <c r="Q134" s="7"/>
       <c r="R134" s="7"/>
     </row>
-    <row r="135" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="135" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>30</v>
       </c>
@@ -11372,7 +11914,7 @@
       </c>
       <c r="R135" s="12"/>
     </row>
-    <row r="136" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="136" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>145</v>
       </c>
@@ -11412,7 +11954,7 @@
       </c>
       <c r="R136" s="7"/>
     </row>
-    <row r="137" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="137" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>18</v>
       </c>
@@ -11454,7 +11996,7 @@
       <c r="Q137" s="12"/>
       <c r="R137" s="12"/>
     </row>
-    <row r="138" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="138" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>18</v>
       </c>
@@ -11496,7 +12038,7 @@
       <c r="Q138" s="7"/>
       <c r="R138" s="7"/>
     </row>
-    <row r="139" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="139" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>18</v>
       </c>
@@ -11540,7 +12082,7 @@
       <c r="Q139" s="12"/>
       <c r="R139" s="12"/>
     </row>
-    <row r="140" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="140" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>18</v>
       </c>
@@ -11582,7 +12124,7 @@
       <c r="Q140" s="7"/>
       <c r="R140" s="7"/>
     </row>
-    <row r="141" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="141" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
         <v>18</v>
       </c>
@@ -11624,7 +12166,7 @@
       <c r="Q141" s="12"/>
       <c r="R141" s="12"/>
     </row>
-    <row r="142" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="142" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>30</v>
       </c>
@@ -11674,7 +12216,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="143" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>145</v>
       </c>
@@ -11714,7 +12256,7 @@
       </c>
       <c r="R143" s="12"/>
     </row>
-    <row r="144" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="144" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>18</v>
       </c>
@@ -11756,7 +12298,7 @@
       <c r="Q144" s="7"/>
       <c r="R144" s="7"/>
     </row>
-    <row r="145" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="145" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>18</v>
       </c>
@@ -11800,7 +12342,7 @@
       <c r="Q145" s="12"/>
       <c r="R145" s="12"/>
     </row>
-    <row r="146" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="146" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>18</v>
       </c>
@@ -11844,7 +12386,7 @@
       <c r="Q146" s="7"/>
       <c r="R146" s="7"/>
     </row>
-    <row r="147" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="147" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>30</v>
       </c>
@@ -11894,7 +12436,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="148" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="148" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>145</v>
       </c>
@@ -11934,7 +12476,7 @@
       </c>
       <c r="R148" s="7"/>
     </row>
-    <row r="149" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="149" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>18</v>
       </c>
@@ -11976,7 +12518,7 @@
       <c r="Q149" s="12"/>
       <c r="R149" s="12"/>
     </row>
-    <row r="150" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="150" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>18</v>
       </c>
@@ -12022,7 +12564,7 @@
       <c r="Q150" s="7"/>
       <c r="R150" s="7"/>
     </row>
-    <row r="151" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="151" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
         <v>30</v>
       </c>
@@ -12072,7 +12614,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="152" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="152" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>145</v>
       </c>
@@ -12112,7 +12654,7 @@
       </c>
       <c r="R152" s="7"/>
     </row>
-    <row r="153" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="153" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
         <v>30</v>
       </c>
@@ -12164,7 +12706,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="154" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>139</v>
       </c>
@@ -12212,7 +12754,7 @@
       </c>
       <c r="R154" s="7"/>
     </row>
-    <row r="155" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="155" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
         <v>18</v>
       </c>
@@ -12256,7 +12798,7 @@
       <c r="Q155" s="12"/>
       <c r="R155" s="12"/>
     </row>
-    <row r="156" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="156" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>30</v>
       </c>
@@ -12302,11 +12844,11 @@
       <c r="Q156" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R156" s="23" t="s">
+      <c r="R156" s="21" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="157" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>145</v>
       </c>
@@ -12346,7 +12888,7 @@
       </c>
       <c r="R157" s="12"/>
     </row>
-    <row r="158" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="158" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>18</v>
       </c>
@@ -12390,7 +12932,7 @@
       <c r="Q158" s="7"/>
       <c r="R158" s="7"/>
     </row>
-    <row r="159" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="159" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>18</v>
       </c>
@@ -12436,7 +12978,7 @@
       <c r="Q159" s="12"/>
       <c r="R159" s="12"/>
     </row>
-    <row r="160" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="160" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>30</v>
       </c>
@@ -12484,7 +13026,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="161" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
         <v>139</v>
       </c>
@@ -12530,7 +13072,7 @@
       </c>
       <c r="R161" s="12"/>
     </row>
-    <row r="162" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="162" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>18</v>
       </c>
@@ -12566,7 +13108,7 @@
       <c r="Q162" s="7"/>
       <c r="R162" s="7"/>
     </row>
-    <row r="163" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="163" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
         <v>18</v>
       </c>
@@ -12608,7 +13150,7 @@
       <c r="Q163" s="12"/>
       <c r="R163" s="12"/>
     </row>
-    <row r="164" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="164" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>18</v>
       </c>
@@ -12650,7 +13192,7 @@
       <c r="Q164" s="7"/>
       <c r="R164" s="7"/>
     </row>
-    <row r="165" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="165" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>18</v>
       </c>
@@ -12694,7 +13236,7 @@
       <c r="Q165" s="12"/>
       <c r="R165" s="12"/>
     </row>
-    <row r="166" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="166" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>18</v>
       </c>
@@ -12738,7 +13280,7 @@
       <c r="Q166" s="7"/>
       <c r="R166" s="7"/>
     </row>
-    <row r="167" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="167" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>30</v>
       </c>
@@ -12784,7 +13326,7 @@
       <c r="Q167" s="12"/>
       <c r="R167" s="12"/>
     </row>
-    <row r="168" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="168" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>18</v>
       </c>
@@ -12818,7 +13360,7 @@
       <c r="Q168" s="7"/>
       <c r="R168" s="7"/>
     </row>
-    <row r="169" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="169" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>18</v>
       </c>
@@ -12854,7 +13396,7 @@
       <c r="Q169" s="12"/>
       <c r="R169" s="12"/>
     </row>
-    <row r="170" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="170" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>18</v>
       </c>
@@ -12898,7 +13440,7 @@
       <c r="Q170" s="7"/>
       <c r="R170" s="7"/>
     </row>
-    <row r="171" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="171" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
         <v>18</v>
       </c>
@@ -12932,7 +13474,7 @@
       <c r="Q171" s="12"/>
       <c r="R171" s="12"/>
     </row>
-    <row r="172" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="172" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>18</v>
       </c>
@@ -12964,7 +13506,7 @@
       <c r="Q172" s="7"/>
       <c r="R172" s="7"/>
     </row>
-    <row r="173" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="173" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
         <v>30</v>
       </c>
@@ -13012,7 +13554,7 @@
       </c>
       <c r="R173" s="12"/>
     </row>
-    <row r="174" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="174" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>18</v>
       </c>
@@ -13054,7 +13596,7 @@
       <c r="Q174" s="7"/>
       <c r="R174" s="7"/>
     </row>
-    <row r="175" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="175" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
         <v>18</v>
       </c>
@@ -13096,7 +13638,7 @@
       <c r="Q175" s="12"/>
       <c r="R175" s="12"/>
     </row>
-    <row r="176" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="176" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>18</v>
       </c>
@@ -13138,7 +13680,7 @@
       <c r="Q176" s="7"/>
       <c r="R176" s="7"/>
     </row>
-    <row r="177" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="177" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
         <v>18</v>
       </c>
@@ -13176,7 +13718,7 @@
       <c r="Q177" s="12"/>
       <c r="R177" s="12"/>
     </row>
-    <row r="178" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="178" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>18</v>
       </c>
@@ -13218,7 +13760,7 @@
       <c r="Q178" s="7"/>
       <c r="R178" s="7"/>
     </row>
-    <row r="179" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="179" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>18</v>
       </c>
@@ -13260,7 +13802,7 @@
       <c r="Q179" s="12"/>
       <c r="R179" s="12"/>
     </row>
-    <row r="180" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="180" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>18</v>
       </c>
@@ -13300,7 +13842,7 @@
       <c r="Q180" s="7"/>
       <c r="R180" s="7"/>
     </row>
-    <row r="181" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="181" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>18</v>
       </c>
@@ -13334,7 +13876,7 @@
       <c r="Q181" s="12"/>
       <c r="R181" s="12"/>
     </row>
-    <row r="182" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="182" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>18</v>
       </c>
@@ -13370,7 +13912,7 @@
       <c r="Q182" s="7"/>
       <c r="R182" s="7"/>
     </row>
-    <row r="183" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="183" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
         <v>18</v>
       </c>
@@ -13412,7 +13954,7 @@
       <c r="Q183" s="12"/>
       <c r="R183" s="12"/>
     </row>
-    <row r="184" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="184" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>18</v>
       </c>
@@ -13454,7 +13996,7 @@
       <c r="Q184" s="7"/>
       <c r="R184" s="7"/>
     </row>
-    <row r="185" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="185" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
         <v>18</v>
       </c>
@@ -13496,7 +14038,7 @@
       <c r="Q185" s="12"/>
       <c r="R185" s="12"/>
     </row>
-    <row r="186" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="186" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>18</v>
       </c>
@@ -13540,7 +14082,7 @@
       <c r="Q186" s="7"/>
       <c r="R186" s="7"/>
     </row>
-    <row r="187" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="187" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>18</v>
       </c>
@@ -13576,7 +14118,7 @@
       <c r="Q187" s="12"/>
       <c r="R187" s="12"/>
     </row>
-    <row r="188" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="188" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>18</v>
       </c>
@@ -13620,7 +14162,7 @@
       <c r="Q188" s="7"/>
       <c r="R188" s="7"/>
     </row>
-    <row r="189" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="189" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>18</v>
       </c>
@@ -13664,7 +14206,7 @@
       <c r="Q189" s="12"/>
       <c r="R189" s="12"/>
     </row>
-    <row r="190" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="190" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>18</v>
       </c>
@@ -13708,7 +14250,7 @@
       <c r="Q190" s="7"/>
       <c r="R190" s="7"/>
     </row>
-    <row r="191" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="191" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
         <v>18</v>
       </c>
@@ -13752,7 +14294,7 @@
       <c r="Q191" s="12"/>
       <c r="R191" s="12"/>
     </row>
-    <row r="192" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="192" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>18</v>
       </c>
@@ -13796,7 +14338,7 @@
       <c r="Q192" s="7"/>
       <c r="R192" s="7"/>
     </row>
-    <row r="193" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="193" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
         <v>30</v>
       </c>
@@ -13842,7 +14384,7 @@
       <c r="Q193" s="12"/>
       <c r="R193" s="12"/>
     </row>
-    <row r="194" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="194" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>18</v>
       </c>
@@ -13878,7 +14420,7 @@
       <c r="Q194" s="7"/>
       <c r="R194" s="7"/>
     </row>
-    <row r="195" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="195" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
         <v>18</v>
       </c>
@@ -13922,7 +14464,7 @@
       <c r="Q195" s="12"/>
       <c r="R195" s="12"/>
     </row>
-    <row r="196" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="196" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>18</v>
       </c>
@@ -13966,7 +14508,7 @@
       <c r="Q196" s="7"/>
       <c r="R196" s="7"/>
     </row>
-    <row r="197" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="197" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>30</v>
       </c>
@@ -14012,7 +14554,7 @@
       <c r="Q197" s="12"/>
       <c r="R197" s="12"/>
     </row>
-    <row r="198" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="198" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>18</v>
       </c>
@@ -14048,7 +14590,7 @@
       <c r="Q198" s="7"/>
       <c r="R198" s="7"/>
     </row>
-    <row r="199" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="199" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
         <v>18</v>
       </c>
@@ -14090,7 +14632,7 @@
       <c r="Q199" s="12"/>
       <c r="R199" s="12"/>
     </row>
-    <row r="200" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="200" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>18</v>
       </c>
@@ -14134,7 +14676,7 @@
       <c r="Q200" s="7"/>
       <c r="R200" s="7"/>
     </row>
-    <row r="201" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="201" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
         <v>30</v>
       </c>
@@ -14180,7 +14722,7 @@
       <c r="Q201" s="12"/>
       <c r="R201" s="12"/>
     </row>
-    <row r="202" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="202" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
         <v>18</v>
       </c>
@@ -14220,7 +14762,7 @@
       <c r="Q202" s="7"/>
       <c r="R202" s="7"/>
     </row>
-    <row r="203" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="203" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
         <v>18</v>
       </c>
@@ -14264,7 +14806,7 @@
       <c r="Q203" s="12"/>
       <c r="R203" s="12"/>
     </row>
-    <row r="204" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="204" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
         <v>18</v>
       </c>
@@ -14308,7 +14850,7 @@
       <c r="Q204" s="7"/>
       <c r="R204" s="7"/>
     </row>
-    <row r="205" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="205" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
         <v>30</v>
       </c>
@@ -14356,7 +14898,7 @@
       </c>
       <c r="R205" s="12"/>
     </row>
-    <row r="206" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="206" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>18</v>
       </c>
@@ -14400,7 +14942,7 @@
       <c r="Q206" s="7"/>
       <c r="R206" s="7"/>
     </row>
-    <row r="207" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="207" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>30</v>
       </c>
@@ -14448,7 +14990,7 @@
       <c r="Q207" s="12"/>
       <c r="R207" s="12"/>
     </row>
-    <row r="208" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="208" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
         <v>18</v>
       </c>
@@ -14492,7 +15034,7 @@
       <c r="Q208" s="7"/>
       <c r="R208" s="7"/>
     </row>
-    <row r="209" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="209" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>18</v>
       </c>
@@ -14536,7 +15078,7 @@
       <c r="Q209" s="12"/>
       <c r="R209" s="12"/>
     </row>
-    <row r="210" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="210" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
         <v>18</v>
       </c>
@@ -14578,7 +15120,7 @@
       <c r="Q210" s="7"/>
       <c r="R210" s="7"/>
     </row>
-    <row r="211" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="211" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
         <v>30</v>
       </c>
@@ -14628,7 +15170,7 @@
       </c>
       <c r="R211" s="12"/>
     </row>
-    <row r="212" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="212" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
         <v>18</v>
       </c>
@@ -14670,7 +15212,7 @@
       <c r="Q212" s="7"/>
       <c r="R212" s="7"/>
     </row>
-    <row r="213" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="213" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>18</v>
       </c>
@@ -14716,7 +15258,7 @@
       <c r="Q213" s="12"/>
       <c r="R213" s="12"/>
     </row>
-    <row r="214" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="214" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
         <v>30</v>
       </c>
@@ -14764,7 +15306,7 @@
       </c>
       <c r="R214" s="7"/>
     </row>
-    <row r="215" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="215" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
         <v>18</v>
       </c>
@@ -14808,7 +15350,7 @@
       <c r="Q215" s="12"/>
       <c r="R215" s="12"/>
     </row>
-    <row r="216" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="216" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>18</v>
       </c>
@@ -14852,7 +15394,7 @@
       <c r="Q216" s="7"/>
       <c r="R216" s="7"/>
     </row>
-    <row r="217" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="217" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>18</v>
       </c>
@@ -14896,7 +15438,7 @@
       <c r="Q217" s="12"/>
       <c r="R217" s="12"/>
     </row>
-    <row r="218" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="218" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
         <v>18</v>
       </c>
@@ -14940,7 +15482,7 @@
       <c r="Q218" s="7"/>
       <c r="R218" s="7"/>
     </row>
-    <row r="219" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="219" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>30</v>
       </c>
@@ -14990,7 +15532,7 @@
       </c>
       <c r="R219" s="12"/>
     </row>
-    <row r="220" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="220" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
         <v>18</v>
       </c>
@@ -15032,7 +15574,7 @@
       <c r="Q220" s="7"/>
       <c r="R220" s="7"/>
     </row>
-    <row r="221" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="221" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
         <v>18</v>
       </c>
@@ -15076,7 +15618,7 @@
       <c r="Q221" s="12"/>
       <c r="R221" s="12"/>
     </row>
-    <row r="222" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="222" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
         <v>18</v>
       </c>
@@ -15120,7 +15662,7 @@
       <c r="Q222" s="7"/>
       <c r="R222" s="7"/>
     </row>
-    <row r="223" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="223" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
         <v>18</v>
       </c>
@@ -15164,7 +15706,7 @@
       <c r="Q223" s="12"/>
       <c r="R223" s="12"/>
     </row>
-    <row r="224" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="224" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>30</v>
       </c>
@@ -15216,7 +15758,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="225" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>18</v>
       </c>
@@ -15250,7 +15792,7 @@
       <c r="Q225" s="12"/>
       <c r="R225" s="12"/>
     </row>
-    <row r="226" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="226" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>18</v>
       </c>
@@ -15294,7 +15836,7 @@
       <c r="Q226" s="7"/>
       <c r="R226" s="7"/>
     </row>
-    <row r="227" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="227" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>18</v>
       </c>
@@ -15338,7 +15880,7 @@
       <c r="Q227" s="12"/>
       <c r="R227" s="12"/>
     </row>
-    <row r="228" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="228" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
         <v>18</v>
       </c>
@@ -15382,7 +15924,7 @@
       <c r="Q228" s="7"/>
       <c r="R228" s="7"/>
     </row>
-    <row r="229" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="229" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
         <v>18</v>
       </c>
@@ -15426,7 +15968,7 @@
       <c r="Q229" s="12"/>
       <c r="R229" s="12"/>
     </row>
-    <row r="230" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="230" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
         <v>30</v>
       </c>
@@ -15472,7 +16014,7 @@
       <c r="Q230" s="7"/>
       <c r="R230" s="7"/>
     </row>
-    <row r="231" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="231" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
         <v>18</v>
       </c>
@@ -15506,7 +16048,7 @@
       <c r="Q231" s="12"/>
       <c r="R231" s="12"/>
     </row>
-    <row r="232" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="232" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
         <v>18</v>
       </c>
@@ -15540,7 +16082,7 @@
       <c r="Q232" s="7"/>
       <c r="R232" s="7"/>
     </row>
-    <row r="233" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="233" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
         <v>18</v>
       </c>
@@ -15582,7 +16124,7 @@
       <c r="Q233" s="12"/>
       <c r="R233" s="12"/>
     </row>
-    <row r="234" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="234" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
         <v>18</v>
       </c>
@@ -15616,7 +16158,7 @@
       <c r="Q234" s="7"/>
       <c r="R234" s="7"/>
     </row>
-    <row r="235" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="235" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
         <v>18</v>
       </c>
@@ -15660,7 +16202,7 @@
       <c r="Q235" s="12"/>
       <c r="R235" s="12"/>
     </row>
-    <row r="236" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="236" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>18</v>
       </c>
@@ -15698,7 +16240,7 @@
       <c r="Q236" s="7"/>
       <c r="R236" s="7"/>
     </row>
-    <row r="237" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="237" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
         <v>30</v>
       </c>
@@ -15744,7 +16286,7 @@
       <c r="Q237" s="12"/>
       <c r="R237" s="12"/>
     </row>
-    <row r="238" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="238" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
         <v>18</v>
       </c>
@@ -15786,7 +16328,7 @@
       <c r="Q238" s="7"/>
       <c r="R238" s="7"/>
     </row>
-    <row r="239" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="239" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>18</v>
       </c>
@@ -15828,7 +16370,7 @@
       <c r="Q239" s="12"/>
       <c r="R239" s="12"/>
     </row>
-    <row r="240" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="240" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
         <v>18</v>
       </c>
@@ -15870,7 +16412,7 @@
       <c r="Q240" s="7"/>
       <c r="R240" s="7"/>
     </row>
-    <row r="241" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="241" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
         <v>18</v>
       </c>
@@ -15914,7 +16456,7 @@
       <c r="Q241" s="12"/>
       <c r="R241" s="12"/>
     </row>
-    <row r="242" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="242" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
         <v>18</v>
       </c>
@@ -15960,7 +16502,7 @@
       <c r="Q242" s="7"/>
       <c r="R242" s="7"/>
     </row>
-    <row r="243" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="243" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="11" t="s">
         <v>18</v>
       </c>
@@ -16002,7 +16544,7 @@
       <c r="Q243" s="12"/>
       <c r="R243" s="12"/>
     </row>
-    <row r="244" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="244" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
         <v>18</v>
       </c>
@@ -16046,7 +16588,7 @@
       <c r="Q244" s="7"/>
       <c r="R244" s="7"/>
     </row>
-    <row r="245" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="245" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="11" t="s">
         <v>18</v>
       </c>
@@ -16090,7 +16632,7 @@
       <c r="Q245" s="12"/>
       <c r="R245" s="12"/>
     </row>
-    <row r="246" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="246" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
         <v>30</v>
       </c>
@@ -16138,7 +16680,7 @@
       </c>
       <c r="R246" s="7"/>
     </row>
-    <row r="247" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="247" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>18</v>
       </c>
@@ -16174,7 +16716,7 @@
       <c r="Q247" s="12"/>
       <c r="R247" s="12"/>
     </row>
-    <row r="248" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="248" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
         <v>18</v>
       </c>
@@ -16216,7 +16758,7 @@
       <c r="Q248" s="7"/>
       <c r="R248" s="7"/>
     </row>
-    <row r="249" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="249" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>18</v>
       </c>
@@ -16262,7 +16804,7 @@
       <c r="Q249" s="12"/>
       <c r="R249" s="12"/>
     </row>
-    <row r="250" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="250" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
         <v>18</v>
       </c>
@@ -16304,7 +16846,7 @@
       <c r="Q250" s="7"/>
       <c r="R250" s="7"/>
     </row>
-    <row r="251" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="251" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="11" t="s">
         <v>18</v>
       </c>
@@ -16348,7 +16890,7 @@
       <c r="Q251" s="12"/>
       <c r="R251" s="12"/>
     </row>
-    <row r="252" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="252" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
         <v>30</v>
       </c>
@@ -16396,7 +16938,7 @@
       </c>
       <c r="R252" s="7"/>
     </row>
-    <row r="253" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="253" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="11" t="s">
         <v>18</v>
       </c>
@@ -16440,7 +16982,7 @@
       <c r="Q253" s="12"/>
       <c r="R253" s="12"/>
     </row>
-    <row r="254" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="254" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
         <v>18</v>
       </c>
@@ -16484,7 +17026,7 @@
       <c r="Q254" s="7"/>
       <c r="R254" s="7"/>
     </row>
-    <row r="255" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="255" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>18</v>
       </c>
@@ -16518,7 +17060,7 @@
       <c r="Q255" s="12"/>
       <c r="R255" s="12"/>
     </row>
-    <row r="256" s="1" customFormat="1" ht="106.1267" customHeight="1">
+    <row r="256" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>30</v>
       </c>
@@ -16562,7 +17104,7 @@
       <c r="Q256" s="7"/>
       <c r="R256" s="7"/>
     </row>
-    <row r="257" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="257" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>18</v>
       </c>
@@ -16598,7 +17140,7 @@
       <c r="Q257" s="12"/>
       <c r="R257" s="12"/>
     </row>
-    <row r="258" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="258" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
         <v>18</v>
       </c>
@@ -16632,7 +17174,7 @@
       <c r="Q258" s="7"/>
       <c r="R258" s="7"/>
     </row>
-    <row r="259" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="259" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>18</v>
       </c>
@@ -16674,7 +17216,7 @@
       <c r="Q259" s="12"/>
       <c r="R259" s="12"/>
     </row>
-    <row r="260" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="260" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
         <v>18</v>
       </c>
@@ -16716,7 +17258,7 @@
       <c r="Q260" s="7"/>
       <c r="R260" s="7"/>
     </row>
-    <row r="261" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="261" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>18</v>
       </c>
@@ -16752,7 +17294,7 @@
       <c r="Q261" s="12"/>
       <c r="R261" s="12"/>
     </row>
-    <row r="262" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="262" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
         <v>18</v>
       </c>
@@ -16788,7 +17330,7 @@
       <c r="Q262" s="7"/>
       <c r="R262" s="7"/>
     </row>
-    <row r="263" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="263" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
         <v>18</v>
       </c>
@@ -16824,7 +17366,7 @@
       <c r="Q263" s="12"/>
       <c r="R263" s="12"/>
     </row>
-    <row r="264" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="264" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
         <v>18</v>
       </c>
@@ -16866,7 +17408,7 @@
       <c r="Q264" s="7"/>
       <c r="R264" s="7"/>
     </row>
-    <row r="265" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="265" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="11" t="s">
         <v>18</v>
       </c>
@@ -16908,7 +17450,7 @@
       <c r="Q265" s="12"/>
       <c r="R265" s="12"/>
     </row>
-    <row r="266" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="266" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
         <v>18</v>
       </c>
@@ -16942,7 +17484,7 @@
       <c r="Q266" s="7"/>
       <c r="R266" s="7"/>
     </row>
-    <row r="267" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="267" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>18</v>
       </c>
@@ -16984,7 +17526,7 @@
       <c r="Q267" s="12"/>
       <c r="R267" s="12"/>
     </row>
-    <row r="268" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="268" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
         <v>18</v>
       </c>
@@ -17026,7 +17568,7 @@
       <c r="Q268" s="7"/>
       <c r="R268" s="7"/>
     </row>
-    <row r="269" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="269" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>18</v>
       </c>
@@ -17068,7 +17610,7 @@
       <c r="Q269" s="12"/>
       <c r="R269" s="12"/>
     </row>
-    <row r="270" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="270" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>18</v>
       </c>
@@ -17112,7 +17654,7 @@
       <c r="Q270" s="7"/>
       <c r="R270" s="7"/>
     </row>
-    <row r="271" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="271" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="11" t="s">
         <v>18</v>
       </c>
@@ -17154,7 +17696,7 @@
       <c r="Q271" s="12"/>
       <c r="R271" s="12"/>
     </row>
-    <row r="272" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="272" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>18</v>
       </c>
@@ -17196,7 +17738,7 @@
       <c r="Q272" s="7"/>
       <c r="R272" s="7"/>
     </row>
-    <row r="273" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="273" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="11" t="s">
         <v>18</v>
       </c>
@@ -17238,7 +17780,7 @@
       <c r="Q273" s="12"/>
       <c r="R273" s="12"/>
     </row>
-    <row r="274" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="274" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>18</v>
       </c>
@@ -17280,7 +17822,7 @@
       <c r="Q274" s="7"/>
       <c r="R274" s="7"/>
     </row>
-    <row r="275" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="275" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="11" t="s">
         <v>18</v>
       </c>
@@ -17322,7 +17864,7 @@
       <c r="Q275" s="12"/>
       <c r="R275" s="12"/>
     </row>
-    <row r="276" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="276" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>18</v>
       </c>
@@ -17364,7 +17906,7 @@
       <c r="Q276" s="7"/>
       <c r="R276" s="7"/>
     </row>
-    <row r="277" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="277" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="11" t="s">
         <v>18</v>
       </c>
@@ -17408,7 +17950,7 @@
       <c r="Q277" s="12"/>
       <c r="R277" s="12"/>
     </row>
-    <row r="278" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="278" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
         <v>30</v>
       </c>
@@ -17456,7 +17998,7 @@
       </c>
       <c r="R278" s="7"/>
     </row>
-    <row r="279" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="279" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="11" t="s">
         <v>18</v>
       </c>
@@ -17498,7 +18040,7 @@
       <c r="Q279" s="12"/>
       <c r="R279" s="12"/>
     </row>
-    <row r="280" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="280" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
         <v>18</v>
       </c>
@@ -17540,7 +18082,7 @@
       <c r="Q280" s="7"/>
       <c r="R280" s="7"/>
     </row>
-    <row r="281" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="281" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="11" t="s">
         <v>18</v>
       </c>
@@ -17582,7 +18124,7 @@
       <c r="Q281" s="12"/>
       <c r="R281" s="12"/>
     </row>
-    <row r="282" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="282" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
         <v>18</v>
       </c>
@@ -17624,7 +18166,7 @@
       <c r="Q282" s="7"/>
       <c r="R282" s="7"/>
     </row>
-    <row r="283" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="283" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="11" t="s">
         <v>18</v>
       </c>
@@ -17666,7 +18208,7 @@
       <c r="Q283" s="12"/>
       <c r="R283" s="12"/>
     </row>
-    <row r="284" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="284" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
         <v>18</v>
       </c>
@@ -17708,7 +18250,7 @@
       <c r="Q284" s="7"/>
       <c r="R284" s="7"/>
     </row>
-    <row r="285" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="285" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="11" t="s">
         <v>18</v>
       </c>
@@ -17752,7 +18294,7 @@
       <c r="Q285" s="12"/>
       <c r="R285" s="12"/>
     </row>
-    <row r="286" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="286" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
         <v>30</v>
       </c>
@@ -17800,7 +18342,7 @@
       </c>
       <c r="R286" s="7"/>
     </row>
-    <row r="287" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="287" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="11" t="s">
         <v>18</v>
       </c>
@@ -17842,7 +18384,7 @@
       <c r="Q287" s="12"/>
       <c r="R287" s="12"/>
     </row>
-    <row r="288" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="288" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
         <v>18</v>
       </c>
@@ -17884,7 +18426,7 @@
       <c r="Q288" s="7"/>
       <c r="R288" s="7"/>
     </row>
-    <row r="289" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="289" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="11" t="s">
         <v>18</v>
       </c>
@@ -17928,7 +18470,7 @@
       <c r="Q289" s="12"/>
       <c r="R289" s="12"/>
     </row>
-    <row r="290" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="290" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
         <v>18</v>
       </c>
@@ -17970,7 +18512,7 @@
       <c r="Q290" s="7"/>
       <c r="R290" s="7"/>
     </row>
-    <row r="291" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="291" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="11" t="s">
         <v>18</v>
       </c>
@@ -18014,7 +18556,7 @@
       <c r="Q291" s="12"/>
       <c r="R291" s="12"/>
     </row>
-    <row r="292" s="1" customFormat="1" ht="148.7907" customHeight="1">
+    <row r="292" spans="1:18" s="1" customFormat="1" ht="99.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
         <v>18</v>
       </c>
@@ -18050,7 +18592,7 @@
       <c r="Q292" s="7"/>
       <c r="R292" s="7"/>
     </row>
-    <row r="293" s="1" customFormat="1" ht="127.4587" customHeight="1">
+    <row r="293" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="11" t="s">
         <v>18</v>
       </c>
@@ -18092,7 +18634,7 @@
       <c r="Q293" s="12"/>
       <c r="R293" s="12"/>
     </row>
-    <row r="294" s="1" customFormat="1" ht="127.4587" customHeight="1">
+    <row r="294" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
         <v>18</v>
       </c>
@@ -18136,7 +18678,7 @@
       <c r="Q294" s="7"/>
       <c r="R294" s="7"/>
     </row>
-    <row r="295" s="1" customFormat="1" ht="127.4587" customHeight="1">
+    <row r="295" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="11" t="s">
         <v>18</v>
       </c>
@@ -18170,7 +18712,7 @@
       <c r="Q295" s="12"/>
       <c r="R295" s="12"/>
     </row>
-    <row r="296" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="296" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
         <v>18</v>
       </c>
@@ -18208,7 +18750,7 @@
       <c r="Q296" s="7"/>
       <c r="R296" s="7"/>
     </row>
-    <row r="297" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="297" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="11" t="s">
         <v>30</v>
       </c>
@@ -18256,7 +18798,7 @@
       </c>
       <c r="R297" s="12"/>
     </row>
-    <row r="298" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="298" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
         <v>18</v>
       </c>
@@ -18292,7 +18834,7 @@
       <c r="Q298" s="7"/>
       <c r="R298" s="7"/>
     </row>
-    <row r="299" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="299" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="11" t="s">
         <v>18</v>
       </c>
@@ -18334,7 +18876,7 @@
       <c r="Q299" s="12"/>
       <c r="R299" s="12"/>
     </row>
-    <row r="300" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="300" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
         <v>18</v>
       </c>
@@ -18378,7 +18920,7 @@
       <c r="Q300" s="7"/>
       <c r="R300" s="7"/>
     </row>
-    <row r="301" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="301" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="11" t="s">
         <v>18</v>
       </c>
@@ -18416,7 +18958,7 @@
       <c r="Q301" s="12"/>
       <c r="R301" s="12"/>
     </row>
-    <row r="302" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="302" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6" t="s">
         <v>18</v>
       </c>
@@ -18460,7 +19002,7 @@
       <c r="Q302" s="7"/>
       <c r="R302" s="7"/>
     </row>
-    <row r="303" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="303" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="11" t="s">
         <v>18</v>
       </c>
@@ -18504,7 +19046,7 @@
       <c r="Q303" s="12"/>
       <c r="R303" s="12"/>
     </row>
-    <row r="304" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="304" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
         <v>18</v>
       </c>
@@ -18548,7 +19090,7 @@
       <c r="Q304" s="7"/>
       <c r="R304" s="7"/>
     </row>
-    <row r="305" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="305" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="11" t="s">
         <v>30</v>
       </c>
@@ -18596,7 +19138,7 @@
       </c>
       <c r="R305" s="12"/>
     </row>
-    <row r="306" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="306" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
         <v>18</v>
       </c>
@@ -18630,7 +19172,7 @@
       <c r="Q306" s="7"/>
       <c r="R306" s="7"/>
     </row>
-    <row r="307" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="307" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="11" t="s">
         <v>18</v>
       </c>
@@ -18666,7 +19208,7 @@
       <c r="Q307" s="12"/>
       <c r="R307" s="12"/>
     </row>
-    <row r="308" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="308" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
         <v>18</v>
       </c>
@@ -18710,7 +19252,7 @@
       <c r="Q308" s="7"/>
       <c r="R308" s="7"/>
     </row>
-    <row r="309" s="1" customFormat="1" ht="138.1247" customHeight="1">
+    <row r="309" spans="1:18" s="1" customFormat="1" ht="92.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="11" t="s">
         <v>18</v>
       </c>
@@ -18744,7 +19286,7 @@
       <c r="Q309" s="12"/>
       <c r="R309" s="12"/>
     </row>
-    <row r="310" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="310" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6" t="s">
         <v>18</v>
       </c>
@@ -18786,7 +19328,7 @@
       <c r="Q310" s="7"/>
       <c r="R310" s="7"/>
     </row>
-    <row r="311" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="311" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="11" t="s">
         <v>18</v>
       </c>
@@ -18830,7 +19372,7 @@
       <c r="Q311" s="12"/>
       <c r="R311" s="12"/>
     </row>
-    <row r="312" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="312" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
         <v>18</v>
       </c>
@@ -18864,7 +19406,7 @@
       <c r="Q312" s="7"/>
       <c r="R312" s="7"/>
     </row>
-    <row r="313" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="313" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="11" t="s">
         <v>18</v>
       </c>
@@ -18906,7 +19448,7 @@
       <c r="Q313" s="12"/>
       <c r="R313" s="12"/>
     </row>
-    <row r="314" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="314" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
         <v>18</v>
       </c>
@@ -18948,7 +19490,7 @@
       <c r="Q314" s="7"/>
       <c r="R314" s="7"/>
     </row>
-    <row r="315" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="315" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="11" t="s">
         <v>18</v>
       </c>
@@ -18990,7 +19532,7 @@
       <c r="Q315" s="12"/>
       <c r="R315" s="12"/>
     </row>
-    <row r="316" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="316" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
         <v>18</v>
       </c>
@@ -19030,7 +19572,7 @@
       <c r="Q316" s="7"/>
       <c r="R316" s="7"/>
     </row>
-    <row r="317" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="317" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="11" t="s">
         <v>18</v>
       </c>
@@ -19074,7 +19616,7 @@
       <c r="Q317" s="12"/>
       <c r="R317" s="12"/>
     </row>
-    <row r="318" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="318" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
         <v>18</v>
       </c>
@@ -19108,7 +19650,7 @@
       <c r="Q318" s="7"/>
       <c r="R318" s="7"/>
     </row>
-    <row r="319" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="319" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="11" t="s">
         <v>18</v>
       </c>
@@ -19150,7 +19692,7 @@
       <c r="Q319" s="12"/>
       <c r="R319" s="12"/>
     </row>
-    <row r="320" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="320" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
         <v>18</v>
       </c>
@@ -19188,7 +19730,7 @@
       <c r="Q320" s="7"/>
       <c r="R320" s="7"/>
     </row>
-    <row r="321" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="321" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="11" t="s">
         <v>18</v>
       </c>
@@ -19222,7 +19764,7 @@
       <c r="Q321" s="12"/>
       <c r="R321" s="12"/>
     </row>
-    <row r="322" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="322" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6" t="s">
         <v>18</v>
       </c>
@@ -19258,7 +19800,7 @@
       <c r="Q322" s="7"/>
       <c r="R322" s="7"/>
     </row>
-    <row r="323" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="323" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="11" t="s">
         <v>18</v>
       </c>
@@ -19292,7 +19834,7 @@
       <c r="Q323" s="12"/>
       <c r="R323" s="12"/>
     </row>
-    <row r="324" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="324" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
         <v>18</v>
       </c>
@@ -19334,7 +19876,7 @@
       <c r="Q324" s="7"/>
       <c r="R324" s="7"/>
     </row>
-    <row r="325" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="325" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="11" t="s">
         <v>18</v>
       </c>
@@ -19376,7 +19918,7 @@
       <c r="Q325" s="12"/>
       <c r="R325" s="12"/>
     </row>
-    <row r="326" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="326" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6" t="s">
         <v>18</v>
       </c>
@@ -19418,7 +19960,7 @@
       <c r="Q326" s="7"/>
       <c r="R326" s="7"/>
     </row>
-    <row r="327" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="327" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="11" t="s">
         <v>30</v>
       </c>
@@ -19464,7 +20006,7 @@
       <c r="Q327" s="12"/>
       <c r="R327" s="12"/>
     </row>
-    <row r="328" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="328" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6" t="s">
         <v>18</v>
       </c>
@@ -19508,7 +20050,7 @@
       <c r="Q328" s="7"/>
       <c r="R328" s="7"/>
     </row>
-    <row r="329" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="329" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="11" t="s">
         <v>30</v>
       </c>
@@ -19556,7 +20098,7 @@
       </c>
       <c r="R329" s="12"/>
     </row>
-    <row r="330" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="330" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6" t="s">
         <v>18</v>
       </c>
@@ -19600,7 +20142,7 @@
       <c r="Q330" s="7"/>
       <c r="R330" s="7"/>
     </row>
-    <row r="331" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="331" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="11" t="s">
         <v>18</v>
       </c>
@@ -19642,7 +20184,7 @@
       <c r="Q331" s="12"/>
       <c r="R331" s="12"/>
     </row>
-    <row r="332" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="332" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6" t="s">
         <v>18</v>
       </c>
@@ -19686,7 +20228,7 @@
       <c r="Q332" s="7"/>
       <c r="R332" s="7"/>
     </row>
-    <row r="333" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="333" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="11" t="s">
         <v>30</v>
       </c>
@@ -19730,7 +20272,7 @@
       <c r="Q333" s="12"/>
       <c r="R333" s="12"/>
     </row>
-    <row r="334" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="334" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6" t="s">
         <v>18</v>
       </c>
@@ -19774,7 +20316,7 @@
       <c r="Q334" s="7"/>
       <c r="R334" s="7"/>
     </row>
-    <row r="335" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="335" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="11" t="s">
         <v>18</v>
       </c>
@@ -19818,7 +20360,7 @@
       <c r="Q335" s="12"/>
       <c r="R335" s="12"/>
     </row>
-    <row r="336" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="336" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6" t="s">
         <v>30</v>
       </c>
@@ -19866,7 +20408,7 @@
       </c>
       <c r="R336" s="7"/>
     </row>
-    <row r="337" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="337" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="11" t="s">
         <v>18</v>
       </c>
@@ -19910,7 +20452,7 @@
       <c r="Q337" s="12"/>
       <c r="R337" s="12"/>
     </row>
-    <row r="338" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="338" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6" t="s">
         <v>30</v>
       </c>
@@ -19958,7 +20500,7 @@
       </c>
       <c r="R338" s="7"/>
     </row>
-    <row r="339" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="339" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="11" t="s">
         <v>18</v>
       </c>
@@ -19998,7 +20540,7 @@
       <c r="Q339" s="12"/>
       <c r="R339" s="12"/>
     </row>
-    <row r="340" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="340" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6" t="s">
         <v>18</v>
       </c>
@@ -20042,7 +20584,7 @@
       <c r="Q340" s="7"/>
       <c r="R340" s="7"/>
     </row>
-    <row r="341" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="341" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
         <v>18</v>
       </c>
@@ -20088,7 +20630,7 @@
       <c r="Q341" s="12"/>
       <c r="R341" s="12"/>
     </row>
-    <row r="342" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="342" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6" t="s">
         <v>18</v>
       </c>
@@ -20132,7 +20674,7 @@
       <c r="Q342" s="7"/>
       <c r="R342" s="7"/>
     </row>
-    <row r="343" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="343" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="11" t="s">
         <v>18</v>
       </c>
@@ -20176,7 +20718,7 @@
       <c r="Q343" s="12"/>
       <c r="R343" s="12"/>
     </row>
-    <row r="344" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="344" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6" t="s">
         <v>30</v>
       </c>
@@ -20226,7 +20768,7 @@
       </c>
       <c r="R344" s="7"/>
     </row>
-    <row r="345" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="345" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="11" t="s">
         <v>139</v>
       </c>
@@ -20272,7 +20814,7 @@
       </c>
       <c r="R345" s="12"/>
     </row>
-    <row r="346" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="346" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6" t="s">
         <v>18</v>
       </c>
@@ -20316,7 +20858,7 @@
       <c r="Q346" s="7"/>
       <c r="R346" s="7"/>
     </row>
-    <row r="347" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="347" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="11" t="s">
         <v>18</v>
       </c>
@@ -20354,7 +20896,7 @@
       <c r="Q347" s="12"/>
       <c r="R347" s="12"/>
     </row>
-    <row r="348" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="348" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6" t="s">
         <v>30</v>
       </c>
@@ -20402,7 +20944,7 @@
       </c>
       <c r="R348" s="7"/>
     </row>
-    <row r="349" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="349" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="11" t="s">
         <v>18</v>
       </c>
@@ -20446,7 +20988,7 @@
       <c r="Q349" s="12"/>
       <c r="R349" s="12"/>
     </row>
-    <row r="350" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="350" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6" t="s">
         <v>18</v>
       </c>
@@ -20490,7 +21032,7 @@
       <c r="Q350" s="7"/>
       <c r="R350" s="7"/>
     </row>
-    <row r="351" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="351" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
         <v>30</v>
       </c>
@@ -20538,7 +21080,7 @@
       </c>
       <c r="R351" s="12"/>
     </row>
-    <row r="352" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="352" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6" t="s">
         <v>18</v>
       </c>
@@ -20580,7 +21122,7 @@
       <c r="Q352" s="7"/>
       <c r="R352" s="7"/>
     </row>
-    <row r="353" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="353" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="11" t="s">
         <v>30</v>
       </c>
@@ -20630,7 +21172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="354" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="354" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6" t="s">
         <v>18</v>
       </c>
@@ -20672,7 +21214,7 @@
       <c r="Q354" s="7"/>
       <c r="R354" s="7"/>
     </row>
-    <row r="355" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="355" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="11" t="s">
         <v>18</v>
       </c>
@@ -20706,7 +21248,7 @@
       <c r="Q355" s="12"/>
       <c r="R355" s="12"/>
     </row>
-    <row r="356" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="356" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6" t="s">
         <v>18</v>
       </c>
@@ -20746,7 +21288,7 @@
       <c r="Q356" s="7"/>
       <c r="R356" s="7"/>
     </row>
-    <row r="357" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="357" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="11" t="s">
         <v>18</v>
       </c>
@@ -20790,7 +21332,7 @@
       <c r="Q357" s="12"/>
       <c r="R357" s="12"/>
     </row>
-    <row r="358" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="358" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
         <v>18</v>
       </c>
@@ -20828,7 +21370,7 @@
       <c r="Q358" s="7"/>
       <c r="R358" s="7"/>
     </row>
-    <row r="359" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="359" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="11" t="s">
         <v>18</v>
       </c>
@@ -20862,7 +21404,7 @@
       <c r="Q359" s="12"/>
       <c r="R359" s="12"/>
     </row>
-    <row r="360" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="360" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6" t="s">
         <v>18</v>
       </c>
@@ -20896,7 +21438,7 @@
       <c r="Q360" s="7"/>
       <c r="R360" s="7"/>
     </row>
-    <row r="361" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="361" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="11" t="s">
         <v>18</v>
       </c>
@@ -20930,7 +21472,7 @@
       <c r="Q361" s="12"/>
       <c r="R361" s="12"/>
     </row>
-    <row r="362" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="362" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6" t="s">
         <v>18</v>
       </c>
@@ -20974,7 +21516,7 @@
       <c r="Q362" s="7"/>
       <c r="R362" s="7"/>
     </row>
-    <row r="363" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="363" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="11" t="s">
         <v>18</v>
       </c>
@@ -21008,7 +21550,7 @@
       <c r="Q363" s="12"/>
       <c r="R363" s="12"/>
     </row>
-    <row r="364" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="364" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6" t="s">
         <v>18</v>
       </c>
@@ -21050,7 +21592,7 @@
       <c r="Q364" s="7"/>
       <c r="R364" s="7"/>
     </row>
-    <row r="365" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="365" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="11" t="s">
         <v>18</v>
       </c>
@@ -21092,7 +21634,7 @@
       <c r="Q365" s="12"/>
       <c r="R365" s="12"/>
     </row>
-    <row r="366" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="366" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6" t="s">
         <v>18</v>
       </c>
@@ -21134,7 +21676,7 @@
       <c r="Q366" s="7"/>
       <c r="R366" s="7"/>
     </row>
-    <row r="367" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="367" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="11" t="s">
         <v>18</v>
       </c>
@@ -21168,7 +21710,7 @@
       <c r="Q367" s="12"/>
       <c r="R367" s="12"/>
     </row>
-    <row r="368" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="368" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6" t="s">
         <v>18</v>
       </c>
@@ -21212,7 +21754,7 @@
       <c r="Q368" s="7"/>
       <c r="R368" s="7"/>
     </row>
-    <row r="369" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="369" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="11" t="s">
         <v>18</v>
       </c>
@@ -21246,7 +21788,7 @@
       <c r="Q369" s="12"/>
       <c r="R369" s="12"/>
     </row>
-    <row r="370" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="370" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6" t="s">
         <v>18</v>
       </c>
@@ -21290,7 +21832,7 @@
       <c r="Q370" s="7"/>
       <c r="R370" s="7"/>
     </row>
-    <row r="371" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="371" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="11" t="s">
         <v>18</v>
       </c>
@@ -21328,7 +21870,7 @@
       <c r="Q371" s="12"/>
       <c r="R371" s="12"/>
     </row>
-    <row r="372" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="372" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6" t="s">
         <v>18</v>
       </c>
@@ -21372,7 +21914,7 @@
       <c r="Q372" s="7"/>
       <c r="R372" s="7"/>
     </row>
-    <row r="373" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="373" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="11" t="s">
         <v>18</v>
       </c>
@@ -21408,7 +21950,7 @@
       <c r="Q373" s="12"/>
       <c r="R373" s="12"/>
     </row>
-    <row r="374" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="374" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6" t="s">
         <v>18</v>
       </c>
@@ -21446,7 +21988,7 @@
       <c r="Q374" s="7"/>
       <c r="R374" s="7"/>
     </row>
-    <row r="375" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="375" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="11" t="s">
         <v>18</v>
       </c>
@@ -21484,7 +22026,7 @@
       <c r="Q375" s="12"/>
       <c r="R375" s="12"/>
     </row>
-    <row r="376" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="376" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6" t="s">
         <v>18</v>
       </c>
@@ -21522,7 +22064,7 @@
       <c r="Q376" s="7"/>
       <c r="R376" s="7"/>
     </row>
-    <row r="377" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="377" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="11" t="s">
         <v>18</v>
       </c>
@@ -21558,7 +22100,7 @@
       <c r="Q377" s="12"/>
       <c r="R377" s="12"/>
     </row>
-    <row r="378" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="378" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6" t="s">
         <v>18</v>
       </c>
@@ -21592,7 +22134,7 @@
       <c r="Q378" s="7"/>
       <c r="R378" s="7"/>
     </row>
-    <row r="379" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="379" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="11" t="s">
         <v>18</v>
       </c>
@@ -21634,7 +22176,7 @@
       <c r="Q379" s="12"/>
       <c r="R379" s="12"/>
     </row>
-    <row r="380" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="380" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6" t="s">
         <v>18</v>
       </c>
@@ -21678,7 +22220,7 @@
       <c r="Q380" s="7"/>
       <c r="R380" s="7"/>
     </row>
-    <row r="381" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="381" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="11" t="s">
         <v>18</v>
       </c>
@@ -21720,7 +22262,7 @@
       <c r="Q381" s="12"/>
       <c r="R381" s="12"/>
     </row>
-    <row r="382" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="382" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6" t="s">
         <v>18</v>
       </c>
@@ -21764,7 +22306,7 @@
       <c r="Q382" s="7"/>
       <c r="R382" s="7"/>
     </row>
-    <row r="383" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="383" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="11" t="s">
         <v>18</v>
       </c>
@@ -21808,7 +22350,7 @@
       <c r="Q383" s="12"/>
       <c r="R383" s="12"/>
     </row>
-    <row r="384" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="384" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6" t="s">
         <v>18</v>
       </c>
@@ -21850,7 +22392,7 @@
       <c r="Q384" s="7"/>
       <c r="R384" s="7"/>
     </row>
-    <row r="385" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="385" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="11" t="s">
         <v>18</v>
       </c>
@@ -21894,7 +22436,7 @@
       <c r="Q385" s="12"/>
       <c r="R385" s="12"/>
     </row>
-    <row r="386" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="386" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6" t="s">
         <v>18</v>
       </c>
@@ -21938,7 +22480,7 @@
       <c r="Q386" s="7"/>
       <c r="R386" s="7"/>
     </row>
-    <row r="387" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="387" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="11" t="s">
         <v>18</v>
       </c>
@@ -21980,7 +22522,7 @@
       <c r="Q387" s="12"/>
       <c r="R387" s="12"/>
     </row>
-    <row r="388" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="388" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6" t="s">
         <v>18</v>
       </c>
@@ -22022,7 +22564,7 @@
       <c r="Q388" s="7"/>
       <c r="R388" s="7"/>
     </row>
-    <row r="389" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="389" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="11" t="s">
         <v>18</v>
       </c>
@@ -22066,7 +22608,7 @@
       <c r="Q389" s="12"/>
       <c r="R389" s="12"/>
     </row>
-    <row r="390" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="390" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6" t="s">
         <v>18</v>
       </c>
@@ -22104,7 +22646,7 @@
       <c r="Q390" s="7"/>
       <c r="R390" s="7"/>
     </row>
-    <row r="391" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="391" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="11" t="s">
         <v>18</v>
       </c>
@@ -22142,7 +22684,7 @@
       <c r="Q391" s="12"/>
       <c r="R391" s="12"/>
     </row>
-    <row r="392" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="392" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6" t="s">
         <v>30</v>
       </c>
@@ -22188,7 +22730,7 @@
       <c r="Q392" s="7"/>
       <c r="R392" s="7"/>
     </row>
-    <row r="393" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="393" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="11" t="s">
         <v>18</v>
       </c>
@@ -22222,7 +22764,7 @@
       <c r="Q393" s="12"/>
       <c r="R393" s="12"/>
     </row>
-    <row r="394" s="1" customFormat="1" ht="235.1853" customHeight="1">
+    <row r="394" spans="1:18" s="1" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6" t="s">
         <v>30</v>
       </c>
@@ -22272,7 +22814,7 @@
       <c r="Q394" s="7"/>
       <c r="R394" s="7"/>
     </row>
-    <row r="395" s="1" customFormat="1" ht="289.0486" customHeight="1">
+    <row r="395" spans="1:18" s="1" customFormat="1" ht="192.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="11" t="s">
         <v>139</v>
       </c>
@@ -22320,7 +22862,7 @@
       </c>
       <c r="R395" s="12"/>
     </row>
-    <row r="396" s="1" customFormat="1" ht="191.988" customHeight="1">
+    <row r="396" spans="1:18" s="1" customFormat="1" ht="128" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6" t="s">
         <v>30</v>
       </c>
@@ -22370,7 +22912,7 @@
       <c r="Q396" s="7"/>
       <c r="R396" s="7"/>
     </row>
-    <row r="397" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="397" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="11" t="s">
         <v>18</v>
       </c>
@@ -22412,7 +22954,7 @@
       <c r="Q397" s="12"/>
       <c r="R397" s="12"/>
     </row>
-    <row r="398" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="398" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6" t="s">
         <v>18</v>
       </c>
@@ -22456,7 +22998,7 @@
       <c r="Q398" s="7"/>
       <c r="R398" s="7"/>
     </row>
-    <row r="399" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="399" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="11" t="s">
         <v>18</v>
       </c>
@@ -22496,7 +23038,7 @@
       <c r="Q399" s="12"/>
       <c r="R399" s="12"/>
     </row>
-    <row r="400" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="400" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6" t="s">
         <v>18</v>
       </c>
@@ -22540,7 +23082,7 @@
       <c r="Q400" s="7"/>
       <c r="R400" s="7"/>
     </row>
-    <row r="401" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="401" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="11" t="s">
         <v>18</v>
       </c>
@@ -22584,7 +23126,7 @@
       <c r="Q401" s="12"/>
       <c r="R401" s="12"/>
     </row>
-    <row r="402" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="402" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6" t="s">
         <v>18</v>
       </c>
@@ -22620,7 +23162,7 @@
       <c r="Q402" s="7"/>
       <c r="R402" s="7"/>
     </row>
-    <row r="403" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="403" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="11" t="s">
         <v>18</v>
       </c>
@@ -22664,7 +23206,7 @@
       <c r="Q403" s="12"/>
       <c r="R403" s="12"/>
     </row>
-    <row r="404" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="404" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6" t="s">
         <v>18</v>
       </c>
@@ -22708,7 +23250,7 @@
       <c r="Q404" s="7"/>
       <c r="R404" s="7"/>
     </row>
-    <row r="405" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="405" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="11" t="s">
         <v>18</v>
       </c>
@@ -22752,7 +23294,7 @@
       <c r="Q405" s="12"/>
       <c r="R405" s="12"/>
     </row>
-    <row r="406" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="406" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6" t="s">
         <v>18</v>
       </c>
@@ -22796,7 +23338,7 @@
       <c r="Q406" s="7"/>
       <c r="R406" s="7"/>
     </row>
-    <row r="407" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="407" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="11" t="s">
         <v>30</v>
       </c>
@@ -22842,7 +23384,7 @@
       <c r="Q407" s="12"/>
       <c r="R407" s="12"/>
     </row>
-    <row r="408" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="408" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6" t="s">
         <v>30</v>
       </c>
@@ -22892,7 +23434,7 @@
       <c r="Q408" s="7"/>
       <c r="R408" s="7"/>
     </row>
-    <row r="409" s="1" customFormat="1" ht="245.8513" customHeight="1">
+    <row r="409" spans="1:18" s="1" customFormat="1" ht="163.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="11" t="s">
         <v>139</v>
       </c>
@@ -22940,7 +23482,7 @@
       </c>
       <c r="R409" s="12"/>
     </row>
-    <row r="410" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="410" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6" t="s">
         <v>18</v>
       </c>
@@ -22984,7 +23526,7 @@
       <c r="Q410" s="7"/>
       <c r="R410" s="7"/>
     </row>
-    <row r="411" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="411" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="11" t="s">
         <v>30</v>
       </c>
@@ -23032,7 +23574,7 @@
       <c r="Q411" s="12"/>
       <c r="R411" s="12"/>
     </row>
-    <row r="412" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="412" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6" t="s">
         <v>139</v>
       </c>
@@ -23078,7 +23620,7 @@
       </c>
       <c r="R412" s="7"/>
     </row>
-    <row r="413" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="413" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="11" t="s">
         <v>18</v>
       </c>
@@ -23118,7 +23660,7 @@
       <c r="Q413" s="12"/>
       <c r="R413" s="12"/>
     </row>
-    <row r="414" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="414" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6" t="s">
         <v>18</v>
       </c>
@@ -23160,7 +23702,7 @@
       <c r="Q414" s="7"/>
       <c r="R414" s="7"/>
     </row>
-    <row r="415" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="415" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="11" t="s">
         <v>18</v>
       </c>
@@ -23202,7 +23744,7 @@
       <c r="Q415" s="12"/>
       <c r="R415" s="12"/>
     </row>
-    <row r="416" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="416" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6" t="s">
         <v>18</v>
       </c>
@@ -23236,7 +23778,7 @@
       <c r="Q416" s="7"/>
       <c r="R416" s="7"/>
     </row>
-    <row r="417" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="417" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="11" t="s">
         <v>18</v>
       </c>
@@ -23280,7 +23822,7 @@
       <c r="Q417" s="12"/>
       <c r="R417" s="12"/>
     </row>
-    <row r="418" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="418" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6" t="s">
         <v>30</v>
       </c>
@@ -23326,7 +23868,7 @@
       <c r="Q418" s="7"/>
       <c r="R418" s="7"/>
     </row>
-    <row r="419" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="419" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="11" t="s">
         <v>18</v>
       </c>
@@ -23370,7 +23912,7 @@
       <c r="Q419" s="12"/>
       <c r="R419" s="12"/>
     </row>
-    <row r="420" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="420" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6" t="s">
         <v>18</v>
       </c>
@@ -23412,7 +23954,7 @@
       <c r="Q420" s="7"/>
       <c r="R420" s="7"/>
     </row>
-    <row r="421" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="421" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="11" t="s">
         <v>18</v>
       </c>
@@ -23456,7 +23998,7 @@
       <c r="Q421" s="12"/>
       <c r="R421" s="12"/>
     </row>
-    <row r="422" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="422" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6" t="s">
         <v>18</v>
       </c>
@@ -23498,7 +24040,7 @@
       <c r="Q422" s="7"/>
       <c r="R422" s="7"/>
     </row>
-    <row r="423" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="423" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="11" t="s">
         <v>18</v>
       </c>
@@ -23542,7 +24084,7 @@
       <c r="Q423" s="12"/>
       <c r="R423" s="12"/>
     </row>
-    <row r="424" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="424" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6" t="s">
         <v>18</v>
       </c>
@@ -23586,7 +24128,7 @@
       <c r="Q424" s="7"/>
       <c r="R424" s="7"/>
     </row>
-    <row r="425" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="425" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="11" t="s">
         <v>30</v>
       </c>
@@ -23632,7 +24174,7 @@
       <c r="Q425" s="12"/>
       <c r="R425" s="12"/>
     </row>
-    <row r="426" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="426" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6" t="s">
         <v>18</v>
       </c>
@@ -23668,7 +24210,7 @@
       <c r="Q426" s="7"/>
       <c r="R426" s="7"/>
     </row>
-    <row r="427" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="427" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="11" t="s">
         <v>18</v>
       </c>
@@ -23710,7 +24252,7 @@
       <c r="Q427" s="12"/>
       <c r="R427" s="12"/>
     </row>
-    <row r="428" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="428" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6" t="s">
         <v>18</v>
       </c>
@@ -23754,7 +24296,7 @@
       <c r="Q428" s="7"/>
       <c r="R428" s="7"/>
     </row>
-    <row r="429" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="429" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="11" t="s">
         <v>18</v>
       </c>
@@ -23798,7 +24340,7 @@
       <c r="Q429" s="12"/>
       <c r="R429" s="12"/>
     </row>
-    <row r="430" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="430" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6" t="s">
         <v>30</v>
       </c>
@@ -23844,7 +24386,7 @@
       <c r="Q430" s="7"/>
       <c r="R430" s="7"/>
     </row>
-    <row r="431" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="431" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="11" t="s">
         <v>30</v>
       </c>
@@ -23890,7 +24432,7 @@
       <c r="Q431" s="12"/>
       <c r="R431" s="12"/>
     </row>
-    <row r="432" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="432" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6" t="s">
         <v>18</v>
       </c>
@@ -23928,7 +24470,7 @@
       <c r="Q432" s="7"/>
       <c r="R432" s="7"/>
     </row>
-    <row r="433" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="433" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="11" t="s">
         <v>18</v>
       </c>
@@ -23972,7 +24514,7 @@
       <c r="Q433" s="12"/>
       <c r="R433" s="12"/>
     </row>
-    <row r="434" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="434" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6" t="s">
         <v>18</v>
       </c>
@@ -24014,7 +24556,7 @@
       <c r="Q434" s="7"/>
       <c r="R434" s="7"/>
     </row>
-    <row r="435" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="435" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="11" t="s">
         <v>18</v>
       </c>
@@ -24058,7 +24600,7 @@
       <c r="Q435" s="12"/>
       <c r="R435" s="12"/>
     </row>
-    <row r="436" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="436" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6" t="s">
         <v>18</v>
       </c>
@@ -24104,7 +24646,7 @@
       <c r="Q436" s="7"/>
       <c r="R436" s="7"/>
     </row>
-    <row r="437" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="437" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="11" t="s">
         <v>18</v>
       </c>
@@ -24142,7 +24684,7 @@
       <c r="Q437" s="12"/>
       <c r="R437" s="12"/>
     </row>
-    <row r="438" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="438" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6" t="s">
         <v>18</v>
       </c>
@@ -24180,7 +24722,7 @@
       <c r="Q438" s="7"/>
       <c r="R438" s="7"/>
     </row>
-    <row r="439" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="439" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="11" t="s">
         <v>18</v>
       </c>
@@ -24218,7 +24760,7 @@
       <c r="Q439" s="12"/>
       <c r="R439" s="12"/>
     </row>
-    <row r="440" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="440" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6" t="s">
         <v>18</v>
       </c>
@@ -24264,7 +24806,7 @@
       <c r="Q440" s="7"/>
       <c r="R440" s="7"/>
     </row>
-    <row r="441" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="441" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="11" t="s">
         <v>18</v>
       </c>
@@ -24308,7 +24850,7 @@
       <c r="Q441" s="12"/>
       <c r="R441" s="12"/>
     </row>
-    <row r="442" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="442" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6" t="s">
         <v>18</v>
       </c>
@@ -24352,7 +24894,7 @@
       <c r="Q442" s="7"/>
       <c r="R442" s="7"/>
     </row>
-    <row r="443" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="443" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="11" t="s">
         <v>30</v>
       </c>
@@ -24400,7 +24942,7 @@
       </c>
       <c r="R443" s="12"/>
     </row>
-    <row r="444" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="444" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6" t="s">
         <v>18</v>
       </c>
@@ -24442,7 +24984,7 @@
       <c r="Q444" s="7"/>
       <c r="R444" s="7"/>
     </row>
-    <row r="445" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="445" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="11" t="s">
         <v>18</v>
       </c>
@@ -24476,7 +25018,7 @@
       <c r="Q445" s="12"/>
       <c r="R445" s="12"/>
     </row>
-    <row r="446" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="446" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6" t="s">
         <v>18</v>
       </c>
@@ -24514,7 +25056,7 @@
       <c r="Q446" s="7"/>
       <c r="R446" s="7"/>
     </row>
-    <row r="447" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="447" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="11" t="s">
         <v>18</v>
       </c>
@@ -24550,7 +25092,7 @@
       <c r="Q447" s="12"/>
       <c r="R447" s="12"/>
     </row>
-    <row r="448" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="448" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6" t="s">
         <v>18</v>
       </c>
@@ -24594,7 +25136,7 @@
       <c r="Q448" s="7"/>
       <c r="R448" s="7"/>
     </row>
-    <row r="449" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="449" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="11" t="s">
         <v>18</v>
       </c>
@@ -24638,7 +25180,7 @@
       <c r="Q449" s="12"/>
       <c r="R449" s="12"/>
     </row>
-    <row r="450" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="450" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6" t="s">
         <v>18</v>
       </c>
@@ -24680,7 +25222,7 @@
       <c r="Q450" s="7"/>
       <c r="R450" s="7"/>
     </row>
-    <row r="451" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="451" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="11" t="s">
         <v>18</v>
       </c>
@@ -24724,7 +25266,7 @@
       <c r="Q451" s="12"/>
       <c r="R451" s="12"/>
     </row>
-    <row r="452" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="452" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6" t="s">
         <v>18</v>
       </c>
@@ -24768,7 +25310,7 @@
       <c r="Q452" s="7"/>
       <c r="R452" s="7"/>
     </row>
-    <row r="453" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="453" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="11" t="s">
         <v>18</v>
       </c>
@@ -24812,7 +25354,7 @@
       <c r="Q453" s="12"/>
       <c r="R453" s="12"/>
     </row>
-    <row r="454" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="454" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6" t="s">
         <v>18</v>
       </c>
@@ -24856,7 +25398,7 @@
       <c r="Q454" s="7"/>
       <c r="R454" s="7"/>
     </row>
-    <row r="455" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="455" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="11" t="s">
         <v>18</v>
       </c>
@@ -24900,7 +25442,7 @@
       <c r="Q455" s="12"/>
       <c r="R455" s="12"/>
     </row>
-    <row r="456" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="456" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6" t="s">
         <v>18</v>
       </c>
@@ -24942,7 +25484,7 @@
       <c r="Q456" s="7"/>
       <c r="R456" s="7"/>
     </row>
-    <row r="457" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="457" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="11" t="s">
         <v>18</v>
       </c>
@@ -24986,7 +25528,7 @@
       <c r="Q457" s="12"/>
       <c r="R457" s="12"/>
     </row>
-    <row r="458" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="458" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6" t="s">
         <v>18</v>
       </c>
@@ -25030,7 +25572,7 @@
       <c r="Q458" s="7"/>
       <c r="R458" s="7"/>
     </row>
-    <row r="459" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="459" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="11" t="s">
         <v>18</v>
       </c>
@@ -25074,7 +25616,7 @@
       <c r="Q459" s="12"/>
       <c r="R459" s="12"/>
     </row>
-    <row r="460" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="460" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6" t="s">
         <v>30</v>
       </c>
@@ -25122,7 +25664,7 @@
       </c>
       <c r="R460" s="7"/>
     </row>
-    <row r="461" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="461" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="11" t="s">
         <v>18</v>
       </c>
@@ -25166,7 +25708,7 @@
       <c r="Q461" s="12"/>
       <c r="R461" s="12"/>
     </row>
-    <row r="462" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="462" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6" t="s">
         <v>18</v>
       </c>
@@ -25210,7 +25752,7 @@
       <c r="Q462" s="7"/>
       <c r="R462" s="7"/>
     </row>
-    <row r="463" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="463" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="11" t="s">
         <v>18</v>
       </c>
@@ -25244,7 +25786,7 @@
       <c r="Q463" s="12"/>
       <c r="R463" s="12"/>
     </row>
-    <row r="464" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="464" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6" t="s">
         <v>18</v>
       </c>
@@ -25286,7 +25828,7 @@
       <c r="Q464" s="7"/>
       <c r="R464" s="7"/>
     </row>
-    <row r="465" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="465" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="11" t="s">
         <v>18</v>
       </c>
@@ -25330,7 +25872,7 @@
       <c r="Q465" s="12"/>
       <c r="R465" s="12"/>
     </row>
-    <row r="466" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="466" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6" t="s">
         <v>18</v>
       </c>
@@ -25372,7 +25914,7 @@
       <c r="Q466" s="7"/>
       <c r="R466" s="7"/>
     </row>
-    <row r="467" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="467" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="11" t="s">
         <v>18</v>
       </c>
@@ -25414,7 +25956,7 @@
       <c r="Q467" s="12"/>
       <c r="R467" s="12"/>
     </row>
-    <row r="468" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="468" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6" t="s">
         <v>18</v>
       </c>
@@ -25458,7 +26000,7 @@
       <c r="Q468" s="7"/>
       <c r="R468" s="7"/>
     </row>
-    <row r="469" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="469" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="11" t="s">
         <v>18</v>
       </c>
@@ -25502,7 +26044,7 @@
       <c r="Q469" s="12"/>
       <c r="R469" s="12"/>
     </row>
-    <row r="470" s="1" customFormat="1" ht="138.1247" customHeight="1">
+    <row r="470" spans="1:18" s="1" customFormat="1" ht="92.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6" t="s">
         <v>18</v>
       </c>
@@ -25544,7 +26086,7 @@
       <c r="Q470" s="7"/>
       <c r="R470" s="7"/>
     </row>
-    <row r="471" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="471" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="11" t="s">
         <v>18</v>
       </c>
@@ -25582,7 +26124,7 @@
       <c r="Q471" s="12"/>
       <c r="R471" s="12"/>
     </row>
-    <row r="472" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="472" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6" t="s">
         <v>18</v>
       </c>
@@ -25620,7 +26162,7 @@
       <c r="Q472" s="7"/>
       <c r="R472" s="7"/>
     </row>
-    <row r="473" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="473" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="11" t="s">
         <v>18</v>
       </c>
@@ -25662,7 +26204,7 @@
       <c r="Q473" s="12"/>
       <c r="R473" s="12"/>
     </row>
-    <row r="474" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="474" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6" t="s">
         <v>18</v>
       </c>
@@ -25700,7 +26242,7 @@
       <c r="Q474" s="7"/>
       <c r="R474" s="7"/>
     </row>
-    <row r="475" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="475" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="11" t="s">
         <v>18</v>
       </c>
@@ -25740,7 +26282,7 @@
       <c r="Q475" s="12"/>
       <c r="R475" s="12"/>
     </row>
-    <row r="476" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="476" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
         <v>30</v>
       </c>
@@ -25790,7 +26332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="477" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="477" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="11" t="s">
         <v>18</v>
       </c>
@@ -25826,7 +26368,7 @@
       <c r="Q477" s="12"/>
       <c r="R477" s="12"/>
     </row>
-    <row r="478" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="478" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6" t="s">
         <v>18</v>
       </c>
@@ -25870,7 +26412,7 @@
       <c r="Q478" s="7"/>
       <c r="R478" s="7"/>
     </row>
-    <row r="479" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="479" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="11" t="s">
         <v>18</v>
       </c>
@@ -25914,7 +26456,7 @@
       <c r="Q479" s="12"/>
       <c r="R479" s="12"/>
     </row>
-    <row r="480" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="480" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6" t="s">
         <v>18</v>
       </c>
@@ -25958,7 +26500,7 @@
       <c r="Q480" s="7"/>
       <c r="R480" s="7"/>
     </row>
-    <row r="481" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="481" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="11" t="s">
         <v>18</v>
       </c>
@@ -25996,7 +26538,7 @@
       <c r="Q481" s="12"/>
       <c r="R481" s="12"/>
     </row>
-    <row r="482" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="482" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6" t="s">
         <v>30</v>
       </c>
@@ -26042,7 +26584,7 @@
       <c r="Q482" s="7"/>
       <c r="R482" s="7"/>
     </row>
-    <row r="483" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="483" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="11" t="s">
         <v>18</v>
       </c>
@@ -26086,7 +26628,7 @@
       <c r="Q483" s="12"/>
       <c r="R483" s="12"/>
     </row>
-    <row r="484" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="484" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6" t="s">
         <v>30</v>
       </c>
@@ -26132,7 +26674,7 @@
       <c r="Q484" s="7"/>
       <c r="R484" s="7"/>
     </row>
-    <row r="485" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="485" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="11" t="s">
         <v>18</v>
       </c>
@@ -26176,7 +26718,7 @@
       <c r="Q485" s="12"/>
       <c r="R485" s="12"/>
     </row>
-    <row r="486" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="486" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6" t="s">
         <v>18</v>
       </c>
@@ -26220,7 +26762,7 @@
       <c r="Q486" s="7"/>
       <c r="R486" s="7"/>
     </row>
-    <row r="487" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="487" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="11" t="s">
         <v>30</v>
       </c>
@@ -26264,7 +26806,7 @@
       <c r="Q487" s="12"/>
       <c r="R487" s="12"/>
     </row>
-    <row r="488" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="488" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6" t="s">
         <v>18</v>
       </c>
@@ -26302,7 +26844,7 @@
       <c r="Q488" s="7"/>
       <c r="R488" s="7"/>
     </row>
-    <row r="489" s="1" customFormat="1" ht="94.9274" customHeight="1">
+    <row r="489" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="11" t="s">
         <v>18</v>
       </c>
@@ -26346,7 +26888,7 @@
       <c r="Q489" s="12"/>
       <c r="R489" s="12"/>
     </row>
-    <row r="490" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="490" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6" t="s">
         <v>30</v>
       </c>
@@ -26394,7 +26936,7 @@
       <c r="Q490" s="7"/>
       <c r="R490" s="7"/>
     </row>
-    <row r="491" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="491" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="11" t="s">
         <v>18</v>
       </c>
@@ -26438,7 +26980,7 @@
       <c r="Q491" s="12"/>
       <c r="R491" s="12"/>
     </row>
-    <row r="492" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="492" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6" t="s">
         <v>18</v>
       </c>
@@ -26482,7 +27024,7 @@
       <c r="Q492" s="7"/>
       <c r="R492" s="7"/>
     </row>
-    <row r="493" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="493" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="11" t="s">
         <v>18</v>
       </c>
@@ -26526,7 +27068,7 @@
       <c r="Q493" s="12"/>
       <c r="R493" s="12"/>
     </row>
-    <row r="494" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="494" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6" t="s">
         <v>30</v>
       </c>
@@ -26572,7 +27114,7 @@
       <c r="Q494" s="7"/>
       <c r="R494" s="7"/>
     </row>
-    <row r="495" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="495" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="11" t="s">
         <v>30</v>
       </c>
@@ -26620,7 +27162,7 @@
       <c r="Q495" s="12"/>
       <c r="R495" s="12"/>
     </row>
-    <row r="496" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="496" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6" t="s">
         <v>18</v>
       </c>
@@ -26658,7 +27200,7 @@
       <c r="Q496" s="7"/>
       <c r="R496" s="7"/>
     </row>
-    <row r="497" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="497" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="11" t="s">
         <v>18</v>
       </c>
@@ -26696,7 +27238,7 @@
       <c r="Q497" s="12"/>
       <c r="R497" s="12"/>
     </row>
-    <row r="498" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="498" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6" t="s">
         <v>30</v>
       </c>
@@ -26742,7 +27284,7 @@
       <c r="Q498" s="7"/>
       <c r="R498" s="7"/>
     </row>
-    <row r="499" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="499" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="11" t="s">
         <v>18</v>
       </c>
@@ -26780,7 +27322,7 @@
       <c r="Q499" s="12"/>
       <c r="R499" s="12"/>
     </row>
-    <row r="500" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="500" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6" t="s">
         <v>18</v>
       </c>
@@ -26818,7 +27360,7 @@
       <c r="Q500" s="7"/>
       <c r="R500" s="7"/>
     </row>
-    <row r="501" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="501" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="11" t="s">
         <v>18</v>
       </c>
@@ -26856,7 +27398,7 @@
       <c r="Q501" s="12"/>
       <c r="R501" s="12"/>
     </row>
-    <row r="502" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="502" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="6" t="s">
         <v>18</v>
       </c>
@@ -26894,7 +27436,7 @@
       <c r="Q502" s="7"/>
       <c r="R502" s="7"/>
     </row>
-    <row r="503" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="503" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="11" t="s">
         <v>18</v>
       </c>
@@ -26938,7 +27480,7 @@
       <c r="Q503" s="12"/>
       <c r="R503" s="12"/>
     </row>
-    <row r="504" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="504" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="6" t="s">
         <v>18</v>
       </c>
@@ -26982,7 +27524,7 @@
       <c r="Q504" s="7"/>
       <c r="R504" s="7"/>
     </row>
-    <row r="505" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="505" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="11" t="s">
         <v>18</v>
       </c>
@@ -27024,7 +27566,7 @@
       <c r="Q505" s="12"/>
       <c r="R505" s="12"/>
     </row>
-    <row r="506" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="506" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="6" t="s">
         <v>18</v>
       </c>
@@ -27068,7 +27610,7 @@
       <c r="Q506" s="7"/>
       <c r="R506" s="7"/>
     </row>
-    <row r="507" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="507" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="11" t="s">
         <v>18</v>
       </c>
@@ -27112,7 +27654,7 @@
       <c r="Q507" s="12"/>
       <c r="R507" s="12"/>
     </row>
-    <row r="508" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="508" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="6" t="s">
         <v>18</v>
       </c>
@@ -27156,7 +27698,7 @@
       <c r="Q508" s="7"/>
       <c r="R508" s="7"/>
     </row>
-    <row r="509" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="509" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="11" t="s">
         <v>30</v>
       </c>
@@ -27204,7 +27746,7 @@
       <c r="Q509" s="12"/>
       <c r="R509" s="12"/>
     </row>
-    <row r="510" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="510" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="6" t="s">
         <v>18</v>
       </c>
@@ -27248,7 +27790,7 @@
       <c r="Q510" s="7"/>
       <c r="R510" s="7"/>
     </row>
-    <row r="511" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="511" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="11" t="s">
         <v>18</v>
       </c>
@@ -27292,7 +27834,7 @@
       <c r="Q511" s="12"/>
       <c r="R511" s="12"/>
     </row>
-    <row r="512" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="512" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="6" t="s">
         <v>30</v>
       </c>
@@ -27340,7 +27882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="513" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="513" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="11" t="s">
         <v>18</v>
       </c>
@@ -27378,7 +27920,7 @@
       <c r="Q513" s="12"/>
       <c r="R513" s="12"/>
     </row>
-    <row r="514" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="514" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="6" t="s">
         <v>18</v>
       </c>
@@ -27414,7 +27956,7 @@
       <c r="Q514" s="7"/>
       <c r="R514" s="7"/>
     </row>
-    <row r="515" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="515" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="11" t="s">
         <v>18</v>
       </c>
@@ -27458,7 +28000,7 @@
       <c r="Q515" s="12"/>
       <c r="R515" s="12"/>
     </row>
-    <row r="516" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="516" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="6" t="s">
         <v>18</v>
       </c>
@@ -27494,7 +28036,7 @@
       <c r="Q516" s="7"/>
       <c r="R516" s="7"/>
     </row>
-    <row r="517" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="517" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="11" t="s">
         <v>18</v>
       </c>
@@ -27538,7 +28080,7 @@
       <c r="Q517" s="12"/>
       <c r="R517" s="12"/>
     </row>
-    <row r="518" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="518" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="6" t="s">
         <v>18</v>
       </c>
@@ -27582,7 +28124,7 @@
       <c r="Q518" s="7"/>
       <c r="R518" s="7"/>
     </row>
-    <row r="519" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="519" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="11" t="s">
         <v>18</v>
       </c>
@@ -27626,7 +28168,7 @@
       <c r="Q519" s="12"/>
       <c r="R519" s="12"/>
     </row>
-    <row r="520" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="520" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="6" t="s">
         <v>18</v>
       </c>
@@ -27670,7 +28212,7 @@
       <c r="Q520" s="7"/>
       <c r="R520" s="7"/>
     </row>
-    <row r="521" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="521" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="11" t="s">
         <v>18</v>
       </c>
@@ -27714,7 +28256,7 @@
       <c r="Q521" s="12"/>
       <c r="R521" s="12"/>
     </row>
-    <row r="522" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="522" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="6" t="s">
         <v>18</v>
       </c>
@@ -27758,7 +28300,7 @@
       <c r="Q522" s="7"/>
       <c r="R522" s="7"/>
     </row>
-    <row r="523" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="523" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="11" t="s">
         <v>30</v>
       </c>
@@ -27804,11 +28346,11 @@
       <c r="Q523" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="R523" s="21" t="s">
+      <c r="R523" s="20" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="524" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="524" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="6" t="s">
         <v>18</v>
       </c>
@@ -27852,7 +28394,7 @@
       <c r="Q524" s="7"/>
       <c r="R524" s="7"/>
     </row>
-    <row r="525" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="525" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="11" t="s">
         <v>18</v>
       </c>
@@ -27896,7 +28438,7 @@
       <c r="Q525" s="12"/>
       <c r="R525" s="12"/>
     </row>
-    <row r="526" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="526" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="6" t="s">
         <v>30</v>
       </c>
@@ -27944,7 +28486,7 @@
       <c r="Q526" s="7"/>
       <c r="R526" s="7"/>
     </row>
-    <row r="527" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="527" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="11" t="s">
         <v>139</v>
       </c>
@@ -27990,7 +28532,7 @@
       </c>
       <c r="R527" s="12"/>
     </row>
-    <row r="528" s="1" customFormat="1" ht="127.4587" customHeight="1">
+    <row r="528" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="6" t="s">
         <v>18</v>
       </c>
@@ -28034,7 +28576,7 @@
       <c r="Q528" s="7"/>
       <c r="R528" s="7"/>
     </row>
-    <row r="529" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="529" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="11" t="s">
         <v>30</v>
       </c>
@@ -28082,7 +28624,7 @@
       <c r="Q529" s="12"/>
       <c r="R529" s="12"/>
     </row>
-    <row r="530" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="530" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="6" t="s">
         <v>18</v>
       </c>
@@ -28128,7 +28670,7 @@
       <c r="Q530" s="7"/>
       <c r="R530" s="7"/>
     </row>
-    <row r="531" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="531" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="11" t="s">
         <v>30</v>
       </c>
@@ -28176,7 +28718,7 @@
       <c r="Q531" s="12"/>
       <c r="R531" s="12"/>
     </row>
-    <row r="532" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="532" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="6" t="s">
         <v>30</v>
       </c>
@@ -28222,7 +28764,7 @@
       <c r="Q532" s="7"/>
       <c r="R532" s="7"/>
     </row>
-    <row r="533" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="533" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="11" t="s">
         <v>30</v>
       </c>
@@ -28272,7 +28814,7 @@
       </c>
       <c r="R533" s="12"/>
     </row>
-    <row r="534" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="534" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="6" t="s">
         <v>139</v>
       </c>
@@ -28320,7 +28862,7 @@
       </c>
       <c r="R534" s="7"/>
     </row>
-    <row r="535" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="535" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="11" t="s">
         <v>139</v>
       </c>
@@ -28368,7 +28910,7 @@
       </c>
       <c r="R535" s="12"/>
     </row>
-    <row r="536" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="536" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="6" t="s">
         <v>18</v>
       </c>
@@ -28410,7 +28952,7 @@
       <c r="Q536" s="7"/>
       <c r="R536" s="7"/>
     </row>
-    <row r="537" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="537" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="11" t="s">
         <v>18</v>
       </c>
@@ -28452,7 +28994,7 @@
       <c r="Q537" s="12"/>
       <c r="R537" s="12"/>
     </row>
-    <row r="538" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="538" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="6" t="s">
         <v>18</v>
       </c>
@@ -28494,7 +29036,7 @@
       <c r="Q538" s="7"/>
       <c r="R538" s="7"/>
     </row>
-    <row r="539" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="539" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="11" t="s">
         <v>18</v>
       </c>
@@ -28530,7 +29072,7 @@
       <c r="Q539" s="12"/>
       <c r="R539" s="12"/>
     </row>
-    <row r="540" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="540" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="6" t="s">
         <v>18</v>
       </c>
@@ -28572,7 +29114,7 @@
       <c r="Q540" s="7"/>
       <c r="R540" s="7"/>
     </row>
-    <row r="541" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="541" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="11" t="s">
         <v>18</v>
       </c>
@@ -28616,7 +29158,7 @@
       <c r="Q541" s="12"/>
       <c r="R541" s="12"/>
     </row>
-    <row r="542" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="542" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="6" t="s">
         <v>18</v>
       </c>
@@ -28654,7 +29196,7 @@
       <c r="Q542" s="7"/>
       <c r="R542" s="7"/>
     </row>
-    <row r="543" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="543" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="11" t="s">
         <v>18</v>
       </c>
@@ -28698,7 +29240,7 @@
       <c r="Q543" s="12"/>
       <c r="R543" s="12"/>
     </row>
-    <row r="544" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="544" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="6" t="s">
         <v>18</v>
       </c>
@@ -28742,7 +29284,7 @@
       <c r="Q544" s="7"/>
       <c r="R544" s="7"/>
     </row>
-    <row r="545" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="545" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="11" t="s">
         <v>18</v>
       </c>
@@ -28786,7 +29328,7 @@
       <c r="Q545" s="12"/>
       <c r="R545" s="12"/>
     </row>
-    <row r="546" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="546" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="6" t="s">
         <v>30</v>
       </c>
@@ -28834,7 +29376,7 @@
       </c>
       <c r="R546" s="7"/>
     </row>
-    <row r="547" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="547" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="11" t="s">
         <v>18</v>
       </c>
@@ -28870,7 +29412,7 @@
       <c r="Q547" s="12"/>
       <c r="R547" s="12"/>
     </row>
-    <row r="548" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="548" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="6" t="s">
         <v>18</v>
       </c>
@@ -28904,7 +29446,7 @@
       <c r="Q548" s="7"/>
       <c r="R548" s="7"/>
     </row>
-    <row r="549" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="549" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="11" t="s">
         <v>18</v>
       </c>
@@ -28946,7 +29488,7 @@
       <c r="Q549" s="12"/>
       <c r="R549" s="12"/>
     </row>
-    <row r="550" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="550" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="6" t="s">
         <v>18</v>
       </c>
@@ -28990,7 +29532,7 @@
       <c r="Q550" s="7"/>
       <c r="R550" s="7"/>
     </row>
-    <row r="551" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="551" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="11" t="s">
         <v>18</v>
       </c>
@@ -29032,7 +29574,7 @@
       <c r="Q551" s="12"/>
       <c r="R551" s="12"/>
     </row>
-    <row r="552" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="552" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="6" t="s">
         <v>18</v>
       </c>
@@ -29074,7 +29616,7 @@
       <c r="Q552" s="7"/>
       <c r="R552" s="7"/>
     </row>
-    <row r="553" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="553" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="11" t="s">
         <v>18</v>
       </c>
@@ -29112,7 +29654,7 @@
       <c r="Q553" s="12"/>
       <c r="R553" s="12"/>
     </row>
-    <row r="554" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="554" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="6" t="s">
         <v>18</v>
       </c>
@@ -29156,7 +29698,7 @@
       <c r="Q554" s="7"/>
       <c r="R554" s="7"/>
     </row>
-    <row r="555" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="555" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="11" t="s">
         <v>30</v>
       </c>
@@ -29204,7 +29746,7 @@
       </c>
       <c r="R555" s="12"/>
     </row>
-    <row r="556" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="556" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="6" t="s">
         <v>18</v>
       </c>
@@ -29246,7 +29788,7 @@
       <c r="Q556" s="7"/>
       <c r="R556" s="7"/>
     </row>
-    <row r="557" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="557" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="11" t="s">
         <v>18</v>
       </c>
@@ -29290,7 +29832,7 @@
       <c r="Q557" s="12"/>
       <c r="R557" s="12"/>
     </row>
-    <row r="558" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="558" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="6" t="s">
         <v>18</v>
       </c>
@@ -29328,7 +29870,7 @@
       <c r="Q558" s="7"/>
       <c r="R558" s="7"/>
     </row>
-    <row r="559" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="559" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="11" t="s">
         <v>18</v>
       </c>
@@ -29374,7 +29916,7 @@
       <c r="Q559" s="12"/>
       <c r="R559" s="12"/>
     </row>
-    <row r="560" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="560" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="6" t="s">
         <v>18</v>
       </c>
@@ -29418,7 +29960,7 @@
       <c r="Q560" s="7"/>
       <c r="R560" s="7"/>
     </row>
-    <row r="561" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="561" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="11" t="s">
         <v>18</v>
       </c>
@@ -29462,7 +30004,7 @@
       <c r="Q561" s="12"/>
       <c r="R561" s="12"/>
     </row>
-    <row r="562" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="562" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="6" t="s">
         <v>30</v>
       </c>
@@ -29512,7 +30054,7 @@
       </c>
       <c r="R562" s="7"/>
     </row>
-    <row r="563" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="563" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="11" t="s">
         <v>30</v>
       </c>
@@ -29560,7 +30102,7 @@
       </c>
       <c r="R563" s="12"/>
     </row>
-    <row r="564" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="564" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="6" t="s">
         <v>139</v>
       </c>
@@ -29606,7 +30148,7 @@
       </c>
       <c r="R564" s="7"/>
     </row>
-    <row r="565" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="565" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="11" t="s">
         <v>18</v>
       </c>
@@ -29642,7 +30184,7 @@
       <c r="Q565" s="12"/>
       <c r="R565" s="12"/>
     </row>
-    <row r="566" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="566" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="6" t="s">
         <v>18</v>
       </c>
@@ -29684,7 +30226,7 @@
       <c r="Q566" s="7"/>
       <c r="R566" s="7"/>
     </row>
-    <row r="567" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="567" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="11" t="s">
         <v>18</v>
       </c>
@@ -29726,7 +30268,7 @@
       <c r="Q567" s="12"/>
       <c r="R567" s="12"/>
     </row>
-    <row r="568" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="568" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="6" t="s">
         <v>18</v>
       </c>
@@ -29760,7 +30302,7 @@
       <c r="Q568" s="7"/>
       <c r="R568" s="7"/>
     </row>
-    <row r="569" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="569" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="11" t="s">
         <v>18</v>
       </c>
@@ -29802,7 +30344,7 @@
       <c r="Q569" s="12"/>
       <c r="R569" s="12"/>
     </row>
-    <row r="570" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="570" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="6" t="s">
         <v>18</v>
       </c>
@@ -29844,7 +30386,7 @@
       <c r="Q570" s="7"/>
       <c r="R570" s="7"/>
     </row>
-    <row r="571" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="571" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="11" t="s">
         <v>18</v>
       </c>
@@ -29886,7 +30428,7 @@
       <c r="Q571" s="12"/>
       <c r="R571" s="12"/>
     </row>
-    <row r="572" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="572" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="6" t="s">
         <v>18</v>
       </c>
@@ -29926,7 +30468,7 @@
       <c r="Q572" s="7"/>
       <c r="R572" s="7"/>
     </row>
-    <row r="573" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="573" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="11" t="s">
         <v>18</v>
       </c>
@@ -29970,7 +30512,7 @@
       <c r="Q573" s="12"/>
       <c r="R573" s="12"/>
     </row>
-    <row r="574" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="574" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="6" t="s">
         <v>18</v>
       </c>
@@ -30006,7 +30548,7 @@
       <c r="Q574" s="7"/>
       <c r="R574" s="7"/>
     </row>
-    <row r="575" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="575" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="11" t="s">
         <v>18</v>
       </c>
@@ -30042,7 +30584,7 @@
       <c r="Q575" s="12"/>
       <c r="R575" s="12"/>
     </row>
-    <row r="576" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="576" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="6" t="s">
         <v>18</v>
       </c>
@@ -30086,7 +30628,7 @@
       <c r="Q576" s="7"/>
       <c r="R576" s="7"/>
     </row>
-    <row r="577" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="577" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="11" t="s">
         <v>18</v>
       </c>
@@ -30130,7 +30672,7 @@
       <c r="Q577" s="12"/>
       <c r="R577" s="12"/>
     </row>
-    <row r="578" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="578" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="6" t="s">
         <v>18</v>
       </c>
@@ -30168,7 +30710,7 @@
       <c r="Q578" s="7"/>
       <c r="R578" s="7"/>
     </row>
-    <row r="579" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="579" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="11" t="s">
         <v>18</v>
       </c>
@@ -30212,7 +30754,7 @@
       <c r="Q579" s="12"/>
       <c r="R579" s="12"/>
     </row>
-    <row r="580" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="580" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="6" t="s">
         <v>18</v>
       </c>
@@ -30254,7 +30796,7 @@
       <c r="Q580" s="7"/>
       <c r="R580" s="7"/>
     </row>
-    <row r="581" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="581" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="11" t="s">
         <v>18</v>
       </c>
@@ -30298,7 +30840,7 @@
       <c r="Q581" s="12"/>
       <c r="R581" s="12"/>
     </row>
-    <row r="582" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="582" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="6" t="s">
         <v>18</v>
       </c>
@@ -30336,7 +30878,7 @@
       <c r="Q582" s="7"/>
       <c r="R582" s="7"/>
     </row>
-    <row r="583" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="583" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="11" t="s">
         <v>18</v>
       </c>
@@ -30378,7 +30920,7 @@
       <c r="Q583" s="12"/>
       <c r="R583" s="12"/>
     </row>
-    <row r="584" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="584" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="6" t="s">
         <v>18</v>
       </c>
@@ -30420,7 +30962,7 @@
       <c r="Q584" s="7"/>
       <c r="R584" s="7"/>
     </row>
-    <row r="585" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="585" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="11" t="s">
         <v>30</v>
       </c>
@@ -30468,7 +31010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="586" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="586" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="6" t="s">
         <v>18</v>
       </c>
@@ -30510,7 +31052,7 @@
       <c r="Q586" s="7"/>
       <c r="R586" s="7"/>
     </row>
-    <row r="587" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="587" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="11" t="s">
         <v>18</v>
       </c>
@@ -30552,7 +31094,7 @@
       <c r="Q587" s="12"/>
       <c r="R587" s="12"/>
     </row>
-    <row r="588" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="588" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="6" t="s">
         <v>18</v>
       </c>
@@ -30596,7 +31138,7 @@
       <c r="Q588" s="7"/>
       <c r="R588" s="7"/>
     </row>
-    <row r="589" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="589" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="11" t="s">
         <v>18</v>
       </c>
@@ -30638,7 +31180,7 @@
       <c r="Q589" s="12"/>
       <c r="R589" s="12"/>
     </row>
-    <row r="590" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="590" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="6" t="s">
         <v>18</v>
       </c>
@@ -30678,7 +31220,7 @@
       <c r="Q590" s="7"/>
       <c r="R590" s="7"/>
     </row>
-    <row r="591" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="591" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="11" t="s">
         <v>18</v>
       </c>
@@ -30716,7 +31258,7 @@
       <c r="Q591" s="12"/>
       <c r="R591" s="12"/>
     </row>
-    <row r="592" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="592" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="6" t="s">
         <v>18</v>
       </c>
@@ -30754,7 +31296,7 @@
       <c r="Q592" s="7"/>
       <c r="R592" s="7"/>
     </row>
-    <row r="593" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="593" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="11" t="s">
         <v>18</v>
       </c>
@@ -30798,7 +31340,7 @@
       <c r="Q593" s="12"/>
       <c r="R593" s="12"/>
     </row>
-    <row r="594" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="594" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6" t="s">
         <v>18</v>
       </c>
@@ -30840,7 +31382,7 @@
       <c r="Q594" s="7"/>
       <c r="R594" s="7"/>
     </row>
-    <row r="595" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="595" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="11" t="s">
         <v>30</v>
       </c>
@@ -30890,7 +31432,7 @@
       </c>
       <c r="R595" s="12"/>
     </row>
-    <row r="596" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="596" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="6" t="s">
         <v>18</v>
       </c>
@@ -30934,7 +31476,7 @@
       <c r="Q596" s="7"/>
       <c r="R596" s="7"/>
     </row>
-    <row r="597" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="597" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="11" t="s">
         <v>18</v>
       </c>
@@ -30976,7 +31518,7 @@
       <c r="Q597" s="12"/>
       <c r="R597" s="12"/>
     </row>
-    <row r="598" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="598" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="6" t="s">
         <v>18</v>
       </c>
@@ -31020,7 +31562,7 @@
       <c r="Q598" s="7"/>
       <c r="R598" s="7"/>
     </row>
-    <row r="599" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="599" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="11" t="s">
         <v>18</v>
       </c>
@@ -31062,7 +31604,7 @@
       <c r="Q599" s="12"/>
       <c r="R599" s="12"/>
     </row>
-    <row r="600" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="600" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="6" t="s">
         <v>18</v>
       </c>
@@ -31104,7 +31646,7 @@
       <c r="Q600" s="7"/>
       <c r="R600" s="7"/>
     </row>
-    <row r="601" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="601" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="11" t="s">
         <v>18</v>
       </c>
@@ -31142,7 +31684,7 @@
       <c r="Q601" s="12"/>
       <c r="R601" s="12"/>
     </row>
-    <row r="602" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="602" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="6" t="s">
         <v>18</v>
       </c>
@@ -31186,7 +31728,7 @@
       <c r="Q602" s="7"/>
       <c r="R602" s="7"/>
     </row>
-    <row r="603" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="603" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="11" t="s">
         <v>18</v>
       </c>
@@ -31230,7 +31772,7 @@
       <c r="Q603" s="12"/>
       <c r="R603" s="12"/>
     </row>
-    <row r="604" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="604" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="6" t="s">
         <v>18</v>
       </c>
@@ -31274,7 +31816,7 @@
       <c r="Q604" s="7"/>
       <c r="R604" s="7"/>
     </row>
-    <row r="605" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="605" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="11" t="s">
         <v>18</v>
       </c>
@@ -31316,7 +31858,7 @@
       <c r="Q605" s="12"/>
       <c r="R605" s="12"/>
     </row>
-    <row r="606" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="606" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="6" t="s">
         <v>18</v>
       </c>
@@ -31358,7 +31900,7 @@
       <c r="Q606" s="7"/>
       <c r="R606" s="7"/>
     </row>
-    <row r="607" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="607" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="11" t="s">
         <v>18</v>
       </c>
@@ -31396,7 +31938,7 @@
       <c r="Q607" s="12"/>
       <c r="R607" s="12"/>
     </row>
-    <row r="608" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="608" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="6" t="s">
         <v>18</v>
       </c>
@@ -31434,7 +31976,7 @@
       <c r="Q608" s="7"/>
       <c r="R608" s="7"/>
     </row>
-    <row r="609" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="609" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="11" t="s">
         <v>18</v>
       </c>
@@ -31478,7 +32020,7 @@
       <c r="Q609" s="12"/>
       <c r="R609" s="12"/>
     </row>
-    <row r="610" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="610" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="6" t="s">
         <v>18</v>
       </c>
@@ -31522,7 +32064,7 @@
       <c r="Q610" s="7"/>
       <c r="R610" s="7"/>
     </row>
-    <row r="611" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="611" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="11" t="s">
         <v>18</v>
       </c>
@@ -31564,7 +32106,7 @@
       <c r="Q611" s="12"/>
       <c r="R611" s="12"/>
     </row>
-    <row r="612" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="612" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="6" t="s">
         <v>18</v>
       </c>
@@ -31604,7 +32146,7 @@
       <c r="Q612" s="7"/>
       <c r="R612" s="7"/>
     </row>
-    <row r="613" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="613" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="11" t="s">
         <v>18</v>
       </c>
@@ -31640,7 +32182,7 @@
       <c r="Q613" s="12"/>
       <c r="R613" s="12"/>
     </row>
-    <row r="614" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="614" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="6" t="s">
         <v>18</v>
       </c>
@@ -31678,7 +32220,7 @@
       <c r="Q614" s="7"/>
       <c r="R614" s="7"/>
     </row>
-    <row r="615" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="615" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="11" t="s">
         <v>18</v>
       </c>
@@ -31716,7 +32258,7 @@
       <c r="Q615" s="12"/>
       <c r="R615" s="12"/>
     </row>
-    <row r="616" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="616" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="6" t="s">
         <v>18</v>
       </c>
@@ -31754,7 +32296,7 @@
       <c r="Q616" s="7"/>
       <c r="R616" s="7"/>
     </row>
-    <row r="617" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="617" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="11" t="s">
         <v>18</v>
       </c>
@@ -31790,7 +32332,7 @@
       <c r="Q617" s="12"/>
       <c r="R617" s="12"/>
     </row>
-    <row r="618" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="618" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="6" t="s">
         <v>18</v>
       </c>
@@ -31836,7 +32378,7 @@
       <c r="Q618" s="7"/>
       <c r="R618" s="7"/>
     </row>
-    <row r="619" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="619" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="11" t="s">
         <v>18</v>
       </c>
@@ -31882,7 +32424,7 @@
       <c r="Q619" s="12"/>
       <c r="R619" s="12"/>
     </row>
-    <row r="620" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="620" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="6" t="s">
         <v>18</v>
       </c>
@@ -31928,7 +32470,7 @@
       <c r="Q620" s="7"/>
       <c r="R620" s="7"/>
     </row>
-    <row r="621" s="1" customFormat="1" ht="84.2614" customHeight="1">
+    <row r="621" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="11" t="s">
         <v>30</v>
       </c>
@@ -31978,7 +32520,7 @@
       </c>
       <c r="R621" s="12"/>
     </row>
-    <row r="622" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="622" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="6" t="s">
         <v>139</v>
       </c>
@@ -32019,7 +32561,7 @@
       <c r="N622" s="15" t="s">
         <v>1715</v>
       </c>
-      <c r="O622" s="25" t="s">
+      <c r="O622" s="22" t="s">
         <v>1716</v>
       </c>
       <c r="P622" s="16" t="s">
@@ -32030,7 +32572,7 @@
       </c>
       <c r="R622" s="7"/>
     </row>
-    <row r="623" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="623" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="11" t="s">
         <v>18</v>
       </c>
@@ -32066,7 +32608,7 @@
       <c r="Q623" s="12"/>
       <c r="R623" s="12"/>
     </row>
-    <row r="624" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="624" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="6" t="s">
         <v>18</v>
       </c>
@@ -32108,7 +32650,7 @@
       <c r="Q624" s="7"/>
       <c r="R624" s="7"/>
     </row>
-    <row r="625" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="625" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="11" t="s">
         <v>18</v>
       </c>
@@ -32142,7 +32684,7 @@
       <c r="Q625" s="12"/>
       <c r="R625" s="12"/>
     </row>
-    <row r="626" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="626" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="6" t="s">
         <v>18</v>
       </c>
@@ -32186,7 +32728,7 @@
       <c r="Q626" s="7"/>
       <c r="R626" s="7"/>
     </row>
-    <row r="627" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="627" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="11" t="s">
         <v>18</v>
       </c>
@@ -32230,7 +32772,7 @@
       <c r="Q627" s="12"/>
       <c r="R627" s="12"/>
     </row>
-    <row r="628" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="628" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="6" t="s">
         <v>18</v>
       </c>
@@ -32274,7 +32816,7 @@
       <c r="Q628" s="7"/>
       <c r="R628" s="7"/>
     </row>
-    <row r="629" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="629" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="11" t="s">
         <v>18</v>
       </c>
@@ -32318,7 +32860,7 @@
       <c r="Q629" s="12"/>
       <c r="R629" s="12"/>
     </row>
-    <row r="630" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="630" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="6" t="s">
         <v>18</v>
       </c>
@@ -32362,7 +32904,7 @@
       <c r="Q630" s="7"/>
       <c r="R630" s="7"/>
     </row>
-    <row r="631" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="631" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="11" t="s">
         <v>30</v>
       </c>
@@ -32406,7 +32948,7 @@
       <c r="Q631" s="12"/>
       <c r="R631" s="12"/>
     </row>
-    <row r="632" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="632" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="6" t="s">
         <v>18</v>
       </c>
@@ -32444,7 +32986,7 @@
       <c r="Q632" s="7"/>
       <c r="R632" s="7"/>
     </row>
-    <row r="633" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="633" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="11" t="s">
         <v>18</v>
       </c>
@@ -32486,7 +33028,7 @@
       <c r="Q633" s="12"/>
       <c r="R633" s="12"/>
     </row>
-    <row r="634" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="634" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="6" t="s">
         <v>18</v>
       </c>
@@ -32528,7 +33070,7 @@
       <c r="Q634" s="7"/>
       <c r="R634" s="7"/>
     </row>
-    <row r="635" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="635" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="11" t="s">
         <v>18</v>
       </c>
@@ -32572,7 +33114,7 @@
       <c r="Q635" s="12"/>
       <c r="R635" s="12"/>
     </row>
-    <row r="636" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="636" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="6" t="s">
         <v>18</v>
       </c>
@@ -32614,7 +33156,7 @@
       <c r="Q636" s="7"/>
       <c r="R636" s="7"/>
     </row>
-    <row r="637" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="637" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="11" t="s">
         <v>18</v>
       </c>
@@ -32658,7 +33200,7 @@
       <c r="Q637" s="12"/>
       <c r="R637" s="12"/>
     </row>
-    <row r="638" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="638" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="6" t="s">
         <v>18</v>
       </c>
@@ -32702,7 +33244,7 @@
       <c r="Q638" s="7"/>
       <c r="R638" s="7"/>
     </row>
-    <row r="639" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="639" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="11" t="s">
         <v>18</v>
       </c>
@@ -32746,7 +33288,7 @@
       <c r="Q639" s="12"/>
       <c r="R639" s="12"/>
     </row>
-    <row r="640" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="640" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="6" t="s">
         <v>30</v>
       </c>
@@ -32792,7 +33334,7 @@
       <c r="Q640" s="7"/>
       <c r="R640" s="7"/>
     </row>
-    <row r="641" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="641" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="11" t="s">
         <v>18</v>
       </c>
@@ -32836,7 +33378,7 @@
       <c r="Q641" s="12"/>
       <c r="R641" s="12"/>
     </row>
-    <row r="642" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="642" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="6" t="s">
         <v>18</v>
       </c>
@@ -32880,7 +33422,7 @@
       <c r="Q642" s="7"/>
       <c r="R642" s="7"/>
     </row>
-    <row r="643" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="643" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="11" t="s">
         <v>18</v>
       </c>
@@ -32924,7 +33466,7 @@
       <c r="Q643" s="12"/>
       <c r="R643" s="12"/>
     </row>
-    <row r="644" s="1" customFormat="1" ht="30.3981" customHeight="1">
+    <row r="644" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="6" t="s">
         <v>18</v>
       </c>
@@ -32968,7 +33510,7 @@
       <c r="Q644" s="7"/>
       <c r="R644" s="7"/>
     </row>
-    <row r="645" s="1" customFormat="1" ht="62.9294" customHeight="1">
+    <row r="645" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="11" t="s">
         <v>18</v>
       </c>
@@ -33012,7 +33554,7 @@
       <c r="Q645" s="12"/>
       <c r="R645" s="12"/>
     </row>
-    <row r="646" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="646" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="6" t="s">
         <v>18</v>
       </c>
@@ -33056,7 +33598,7 @@
       <c r="Q646" s="7"/>
       <c r="R646" s="7"/>
     </row>
-    <row r="647" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="647" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="11" t="s">
         <v>30</v>
       </c>
@@ -33100,7 +33642,7 @@
       <c r="Q647" s="12"/>
       <c r="R647" s="12"/>
     </row>
-    <row r="648" s="1" customFormat="1" ht="116.7927" customHeight="1">
+    <row r="648" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="6" t="s">
         <v>18</v>
       </c>
@@ -33142,7 +33684,7 @@
       <c r="Q648" s="7"/>
       <c r="R648" s="7"/>
     </row>
-    <row r="649" s="1" customFormat="1" ht="73.5954" customHeight="1">
+    <row r="649" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="11" t="s">
         <v>18</v>
       </c>
@@ -33184,522 +33726,529 @@
       <c r="Q649" s="12"/>
       <c r="R649" s="12"/>
     </row>
-    <row r="650" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
+    <row r="650" spans="1:18" s="1" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-    <hyperlink ref="L6" r:id="rId2"/>
-    <hyperlink ref="N6" r:id="rId3"/>
-    <hyperlink ref="P6" r:id="rId4"/>
-    <hyperlink ref="B8" r:id="rId5"/>
-    <hyperlink ref="L8" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="B14" r:id="rId8"/>
-    <hyperlink ref="L14" r:id="rId9"/>
-    <hyperlink ref="N14" r:id="rId10"/>
-    <hyperlink ref="P14" r:id="rId11"/>
-    <hyperlink ref="Q14" r:id="rId12"/>
-    <hyperlink ref="B18" r:id="rId13"/>
-    <hyperlink ref="L18" r:id="rId14"/>
-    <hyperlink ref="N18" r:id="rId15"/>
-    <hyperlink ref="B26" r:id="rId16"/>
-    <hyperlink ref="L26" r:id="rId17"/>
-    <hyperlink ref="N26" r:id="rId18"/>
-    <hyperlink ref="P26" r:id="rId19"/>
-    <hyperlink ref="N31" r:id="rId20"/>
-    <hyperlink ref="B32" r:id="rId21"/>
-    <hyperlink ref="L32" r:id="rId22"/>
-    <hyperlink ref="N32" r:id="rId23"/>
-    <hyperlink ref="B38" r:id="rId24"/>
-    <hyperlink ref="L38" r:id="rId25"/>
-    <hyperlink ref="N38" r:id="rId26"/>
-    <hyperlink ref="P38" r:id="rId27"/>
-    <hyperlink ref="Q38" r:id="rId28"/>
-    <hyperlink ref="B43" r:id="rId29"/>
-    <hyperlink ref="L43" r:id="rId30"/>
-    <hyperlink ref="N43" r:id="rId31"/>
-    <hyperlink ref="Q43" r:id="rId32"/>
-    <hyperlink ref="B44" r:id="rId33"/>
-    <hyperlink ref="L44" r:id="rId34"/>
-    <hyperlink ref="N44" r:id="rId35"/>
-    <hyperlink ref="Q44" r:id="rId36"/>
-    <hyperlink ref="B45" r:id="rId37"/>
-    <hyperlink ref="L45" r:id="rId38"/>
-    <hyperlink ref="N45" r:id="rId39"/>
-    <hyperlink ref="B63" r:id="rId40"/>
-    <hyperlink ref="L63" r:id="rId41"/>
-    <hyperlink ref="N63" r:id="rId42"/>
-    <hyperlink ref="P63" r:id="rId43"/>
-    <hyperlink ref="R63" r:id="rId44"/>
-    <hyperlink ref="B65" r:id="rId45"/>
-    <hyperlink ref="L65" r:id="rId46"/>
-    <hyperlink ref="N65" r:id="rId47"/>
-    <hyperlink ref="Q65" r:id="rId48"/>
-    <hyperlink ref="B66" r:id="rId49"/>
-    <hyperlink ref="L66" r:id="rId50"/>
-    <hyperlink ref="N66" r:id="rId51"/>
-    <hyperlink ref="Q66" r:id="rId52"/>
-    <hyperlink ref="B68" r:id="rId53"/>
-    <hyperlink ref="L68" r:id="rId54"/>
-    <hyperlink ref="N68" r:id="rId55"/>
-    <hyperlink ref="Q68" r:id="rId56"/>
-    <hyperlink ref="B69" r:id="rId57"/>
-    <hyperlink ref="L69" r:id="rId58"/>
-    <hyperlink ref="N69" r:id="rId59"/>
-    <hyperlink ref="Q69" r:id="rId60"/>
-    <hyperlink ref="B78" r:id="rId61"/>
-    <hyperlink ref="L78" r:id="rId62"/>
-    <hyperlink ref="N78" r:id="rId63"/>
-    <hyperlink ref="P78" r:id="rId64"/>
-    <hyperlink ref="B79" r:id="rId65"/>
-    <hyperlink ref="L79" r:id="rId66"/>
-    <hyperlink ref="N79" r:id="rId67"/>
-    <hyperlink ref="P79" r:id="rId68"/>
-    <hyperlink ref="Q79" r:id="rId69"/>
-    <hyperlink ref="B89" r:id="rId70"/>
-    <hyperlink ref="L89" r:id="rId71"/>
-    <hyperlink ref="N89" r:id="rId72"/>
-    <hyperlink ref="P89" r:id="rId73"/>
-    <hyperlink ref="Q89" r:id="rId74"/>
-    <hyperlink ref="R89" r:id="rId75"/>
-    <hyperlink ref="B90" r:id="rId76"/>
-    <hyperlink ref="L90" r:id="rId77"/>
-    <hyperlink ref="N90" r:id="rId78"/>
-    <hyperlink ref="Q90" r:id="rId79"/>
-    <hyperlink ref="B100" r:id="rId80"/>
-    <hyperlink ref="L100" r:id="rId81"/>
-    <hyperlink ref="N100" r:id="rId82"/>
-    <hyperlink ref="P100" r:id="rId83"/>
-    <hyperlink ref="Q100" r:id="rId84"/>
-    <hyperlink ref="B101" r:id="rId85"/>
-    <hyperlink ref="L101" r:id="rId86"/>
-    <hyperlink ref="N101" r:id="rId87"/>
-    <hyperlink ref="Q101" r:id="rId88"/>
-    <hyperlink ref="B117" r:id="rId89"/>
-    <hyperlink ref="L117" r:id="rId90"/>
-    <hyperlink ref="N117" r:id="rId91"/>
-    <hyperlink ref="P117" r:id="rId92"/>
-    <hyperlink ref="R117" r:id="rId93"/>
-    <hyperlink ref="B118" r:id="rId94"/>
-    <hyperlink ref="L118" r:id="rId95"/>
-    <hyperlink ref="N118" r:id="rId96"/>
-    <hyperlink ref="Q118" r:id="rId97"/>
-    <hyperlink ref="B128" r:id="rId98"/>
-    <hyperlink ref="L128" r:id="rId99"/>
-    <hyperlink ref="N128" r:id="rId100"/>
-    <hyperlink ref="P128" r:id="rId101"/>
-    <hyperlink ref="R128" r:id="rId102"/>
-    <hyperlink ref="B129" r:id="rId103"/>
-    <hyperlink ref="L129" r:id="rId104"/>
-    <hyperlink ref="N129" r:id="rId105"/>
-    <hyperlink ref="Q129" r:id="rId106"/>
-    <hyperlink ref="B135" r:id="rId107"/>
-    <hyperlink ref="L135" r:id="rId108"/>
-    <hyperlink ref="N135" r:id="rId109"/>
-    <hyperlink ref="P135" r:id="rId110"/>
-    <hyperlink ref="Q135" r:id="rId111"/>
-    <hyperlink ref="B136" r:id="rId112"/>
-    <hyperlink ref="L136" r:id="rId113"/>
-    <hyperlink ref="N136" r:id="rId114"/>
-    <hyperlink ref="Q136" r:id="rId115"/>
-    <hyperlink ref="B142" r:id="rId116"/>
-    <hyperlink ref="L142" r:id="rId117"/>
-    <hyperlink ref="N142" r:id="rId118"/>
-    <hyperlink ref="P142" r:id="rId119"/>
-    <hyperlink ref="R142" r:id="rId120"/>
-    <hyperlink ref="B143" r:id="rId121"/>
-    <hyperlink ref="L143" r:id="rId122"/>
-    <hyperlink ref="N143" r:id="rId123"/>
-    <hyperlink ref="Q143" r:id="rId124"/>
-    <hyperlink ref="B147" r:id="rId125"/>
-    <hyperlink ref="L147" r:id="rId126"/>
-    <hyperlink ref="N147" r:id="rId127"/>
-    <hyperlink ref="P147" r:id="rId128"/>
-    <hyperlink ref="Q147" r:id="rId129"/>
-    <hyperlink ref="R147" r:id="rId130"/>
-    <hyperlink ref="B148" r:id="rId131"/>
-    <hyperlink ref="L148" r:id="rId132"/>
-    <hyperlink ref="N148" r:id="rId133"/>
-    <hyperlink ref="Q148" r:id="rId134"/>
-    <hyperlink ref="B151" r:id="rId135"/>
-    <hyperlink ref="L151" r:id="rId136"/>
-    <hyperlink ref="N151" r:id="rId137"/>
-    <hyperlink ref="P151" r:id="rId138"/>
-    <hyperlink ref="Q151" r:id="rId139"/>
-    <hyperlink ref="R151" r:id="rId140"/>
-    <hyperlink ref="B152" r:id="rId141"/>
-    <hyperlink ref="L152" r:id="rId142"/>
-    <hyperlink ref="N152" r:id="rId143"/>
-    <hyperlink ref="Q152" r:id="rId144"/>
-    <hyperlink ref="B153" r:id="rId145"/>
-    <hyperlink ref="L153" r:id="rId146"/>
-    <hyperlink ref="N153" r:id="rId147"/>
-    <hyperlink ref="P153" r:id="rId148"/>
-    <hyperlink ref="Q153" r:id="rId149"/>
-    <hyperlink ref="R153" r:id="rId150"/>
-    <hyperlink ref="B154" r:id="rId151"/>
-    <hyperlink ref="L154" r:id="rId152"/>
-    <hyperlink ref="N154" r:id="rId153"/>
-    <hyperlink ref="P154" r:id="rId154"/>
-    <hyperlink ref="Q154" r:id="rId155"/>
-    <hyperlink ref="B156" r:id="rId156"/>
-    <hyperlink ref="L156" r:id="rId157"/>
-    <hyperlink ref="N156" r:id="rId158"/>
-    <hyperlink ref="P156" r:id="rId159"/>
-    <hyperlink ref="Q156" r:id="rId160"/>
-    <hyperlink ref="R156" r:id="rId161"/>
-    <hyperlink ref="B157" r:id="rId162"/>
-    <hyperlink ref="L157" r:id="rId163"/>
-    <hyperlink ref="N157" r:id="rId164"/>
-    <hyperlink ref="Q157" r:id="rId165"/>
-    <hyperlink ref="B160" r:id="rId166"/>
-    <hyperlink ref="L160" r:id="rId167"/>
-    <hyperlink ref="N160" r:id="rId168"/>
-    <hyperlink ref="P160" r:id="rId169"/>
-    <hyperlink ref="R160" r:id="rId170"/>
-    <hyperlink ref="B161" r:id="rId171"/>
-    <hyperlink ref="L161" r:id="rId172"/>
-    <hyperlink ref="N161" r:id="rId173"/>
-    <hyperlink ref="Q161" r:id="rId174"/>
-    <hyperlink ref="B167" r:id="rId175"/>
-    <hyperlink ref="L167" r:id="rId176"/>
-    <hyperlink ref="N167" r:id="rId177"/>
-    <hyperlink ref="P167" r:id="rId178"/>
-    <hyperlink ref="B173" r:id="rId179"/>
-    <hyperlink ref="L173" r:id="rId180"/>
-    <hyperlink ref="N173" r:id="rId181"/>
-    <hyperlink ref="P173" r:id="rId182"/>
-    <hyperlink ref="Q173" r:id="rId183"/>
-    <hyperlink ref="B193" r:id="rId184"/>
-    <hyperlink ref="L193" r:id="rId185"/>
-    <hyperlink ref="N193" r:id="rId186"/>
-    <hyperlink ref="P193" r:id="rId187"/>
-    <hyperlink ref="B197" r:id="rId188"/>
-    <hyperlink ref="L197" r:id="rId189"/>
-    <hyperlink ref="N197" r:id="rId190"/>
-    <hyperlink ref="P197" r:id="rId191"/>
-    <hyperlink ref="B201" r:id="rId192"/>
-    <hyperlink ref="L201" r:id="rId193"/>
-    <hyperlink ref="N201" r:id="rId194"/>
-    <hyperlink ref="P201" r:id="rId195"/>
-    <hyperlink ref="B205" r:id="rId196"/>
-    <hyperlink ref="L205" r:id="rId197"/>
-    <hyperlink ref="N205" r:id="rId198"/>
-    <hyperlink ref="P205" r:id="rId199"/>
-    <hyperlink ref="Q205" r:id="rId200"/>
-    <hyperlink ref="B207" r:id="rId201"/>
-    <hyperlink ref="L207" r:id="rId202"/>
-    <hyperlink ref="N207" r:id="rId203"/>
-    <hyperlink ref="P207" r:id="rId204"/>
-    <hyperlink ref="B211" r:id="rId205"/>
-    <hyperlink ref="L211" r:id="rId206"/>
-    <hyperlink ref="N211" r:id="rId207"/>
-    <hyperlink ref="P211" r:id="rId208"/>
-    <hyperlink ref="Q211" r:id="rId209"/>
-    <hyperlink ref="N213" r:id="rId210"/>
-    <hyperlink ref="B214" r:id="rId211"/>
-    <hyperlink ref="L214" r:id="rId212"/>
-    <hyperlink ref="N214" r:id="rId213"/>
-    <hyperlink ref="P214" r:id="rId214"/>
-    <hyperlink ref="Q214" r:id="rId215"/>
-    <hyperlink ref="B219" r:id="rId216"/>
-    <hyperlink ref="L219" r:id="rId217"/>
-    <hyperlink ref="N219" r:id="rId218"/>
-    <hyperlink ref="P219" r:id="rId219"/>
-    <hyperlink ref="Q219" r:id="rId220"/>
-    <hyperlink ref="B224" r:id="rId221"/>
-    <hyperlink ref="L224" r:id="rId222"/>
-    <hyperlink ref="N224" r:id="rId223"/>
-    <hyperlink ref="P224" r:id="rId224"/>
-    <hyperlink ref="Q224" r:id="rId225"/>
-    <hyperlink ref="R224" r:id="rId226"/>
-    <hyperlink ref="B230" r:id="rId227"/>
-    <hyperlink ref="L230" r:id="rId228"/>
-    <hyperlink ref="N230" r:id="rId229"/>
-    <hyperlink ref="P230" r:id="rId230"/>
-    <hyperlink ref="B237" r:id="rId231"/>
-    <hyperlink ref="L237" r:id="rId232"/>
-    <hyperlink ref="N237" r:id="rId233"/>
-    <hyperlink ref="P237" r:id="rId234"/>
-    <hyperlink ref="B246" r:id="rId235"/>
-    <hyperlink ref="L246" r:id="rId236"/>
-    <hyperlink ref="N246" r:id="rId237"/>
-    <hyperlink ref="P246" r:id="rId238"/>
-    <hyperlink ref="Q246" r:id="rId239"/>
-    <hyperlink ref="B252" r:id="rId240"/>
-    <hyperlink ref="L252" r:id="rId241"/>
-    <hyperlink ref="N252" r:id="rId242"/>
-    <hyperlink ref="P252" r:id="rId243"/>
-    <hyperlink ref="Q252" r:id="rId244"/>
-    <hyperlink ref="B256" r:id="rId245"/>
-    <hyperlink ref="L256" r:id="rId246"/>
-    <hyperlink ref="N256" r:id="rId247"/>
-    <hyperlink ref="B278" r:id="rId248"/>
-    <hyperlink ref="L278" r:id="rId249"/>
-    <hyperlink ref="N278" r:id="rId250"/>
-    <hyperlink ref="P278" r:id="rId251"/>
-    <hyperlink ref="Q278" r:id="rId252"/>
-    <hyperlink ref="B286" r:id="rId253"/>
-    <hyperlink ref="L286" r:id="rId254"/>
-    <hyperlink ref="N286" r:id="rId255"/>
-    <hyperlink ref="P286" r:id="rId256"/>
-    <hyperlink ref="Q286" r:id="rId257"/>
-    <hyperlink ref="B297" r:id="rId258"/>
-    <hyperlink ref="L297" r:id="rId259"/>
-    <hyperlink ref="N297" r:id="rId260"/>
-    <hyperlink ref="P297" r:id="rId261"/>
-    <hyperlink ref="Q297" r:id="rId262"/>
-    <hyperlink ref="B305" r:id="rId263"/>
-    <hyperlink ref="L305" r:id="rId264"/>
-    <hyperlink ref="N305" r:id="rId265"/>
-    <hyperlink ref="P305" r:id="rId266"/>
-    <hyperlink ref="Q305" r:id="rId267"/>
-    <hyperlink ref="B327" r:id="rId268"/>
-    <hyperlink ref="L327" r:id="rId269"/>
-    <hyperlink ref="N327" r:id="rId270"/>
-    <hyperlink ref="P327" r:id="rId271"/>
-    <hyperlink ref="B329" r:id="rId272"/>
-    <hyperlink ref="L329" r:id="rId273"/>
-    <hyperlink ref="N329" r:id="rId274"/>
-    <hyperlink ref="P329" r:id="rId275"/>
-    <hyperlink ref="Q329" r:id="rId276"/>
-    <hyperlink ref="B333" r:id="rId277"/>
-    <hyperlink ref="L333" r:id="rId278"/>
-    <hyperlink ref="N333" r:id="rId279"/>
-    <hyperlink ref="B336" r:id="rId280"/>
-    <hyperlink ref="L336" r:id="rId281"/>
-    <hyperlink ref="N336" r:id="rId282"/>
-    <hyperlink ref="P336" r:id="rId283"/>
-    <hyperlink ref="Q336" r:id="rId284"/>
-    <hyperlink ref="B338" r:id="rId285"/>
-    <hyperlink ref="L338" r:id="rId286"/>
-    <hyperlink ref="N338" r:id="rId287"/>
-    <hyperlink ref="P338" r:id="rId288"/>
-    <hyperlink ref="Q338" r:id="rId289"/>
-    <hyperlink ref="B344" r:id="rId290"/>
-    <hyperlink ref="L344" r:id="rId291"/>
-    <hyperlink ref="N344" r:id="rId292"/>
-    <hyperlink ref="P344" r:id="rId293"/>
-    <hyperlink ref="Q344" r:id="rId294"/>
-    <hyperlink ref="B345" r:id="rId295"/>
-    <hyperlink ref="L345" r:id="rId296"/>
-    <hyperlink ref="N345" r:id="rId297"/>
-    <hyperlink ref="Q345" r:id="rId298"/>
-    <hyperlink ref="B348" r:id="rId299"/>
-    <hyperlink ref="L348" r:id="rId300"/>
-    <hyperlink ref="N348" r:id="rId301"/>
-    <hyperlink ref="P348" r:id="rId302"/>
-    <hyperlink ref="Q348" r:id="rId303"/>
-    <hyperlink ref="B351" r:id="rId304"/>
-    <hyperlink ref="L351" r:id="rId305"/>
-    <hyperlink ref="N351" r:id="rId306"/>
-    <hyperlink ref="P351" r:id="rId307"/>
-    <hyperlink ref="Q351" r:id="rId308"/>
-    <hyperlink ref="B353" r:id="rId309"/>
-    <hyperlink ref="L353" r:id="rId310"/>
-    <hyperlink ref="N353" r:id="rId311"/>
-    <hyperlink ref="P353" r:id="rId312"/>
-    <hyperlink ref="Q353" r:id="rId313"/>
-    <hyperlink ref="R353" r:id="rId314"/>
-    <hyperlink ref="B392" r:id="rId315"/>
-    <hyperlink ref="L392" r:id="rId316"/>
-    <hyperlink ref="N392" r:id="rId317"/>
-    <hyperlink ref="P392" r:id="rId318"/>
-    <hyperlink ref="B394" r:id="rId319"/>
-    <hyperlink ref="L394" r:id="rId320"/>
-    <hyperlink ref="N394" r:id="rId321"/>
-    <hyperlink ref="P394" r:id="rId322"/>
-    <hyperlink ref="B395" r:id="rId323"/>
-    <hyperlink ref="L395" r:id="rId324"/>
-    <hyperlink ref="N395" r:id="rId325"/>
-    <hyperlink ref="Q395" r:id="rId326"/>
-    <hyperlink ref="B396" r:id="rId327"/>
-    <hyperlink ref="L396" r:id="rId328"/>
-    <hyperlink ref="N396" r:id="rId329"/>
-    <hyperlink ref="P396" r:id="rId330"/>
-    <hyperlink ref="B407" r:id="rId331"/>
-    <hyperlink ref="L407" r:id="rId332"/>
-    <hyperlink ref="N407" r:id="rId333"/>
-    <hyperlink ref="P407" r:id="rId334"/>
-    <hyperlink ref="B408" r:id="rId335"/>
-    <hyperlink ref="L408" r:id="rId336"/>
-    <hyperlink ref="N408" r:id="rId337"/>
-    <hyperlink ref="P408" r:id="rId338"/>
-    <hyperlink ref="B409" r:id="rId339"/>
-    <hyperlink ref="L409" r:id="rId340"/>
-    <hyperlink ref="N409" r:id="rId341"/>
-    <hyperlink ref="Q409" r:id="rId342"/>
-    <hyperlink ref="B411" r:id="rId343"/>
-    <hyperlink ref="L411" r:id="rId344"/>
-    <hyperlink ref="N411" r:id="rId345"/>
-    <hyperlink ref="P411" r:id="rId346"/>
-    <hyperlink ref="B412" r:id="rId347"/>
-    <hyperlink ref="L412" r:id="rId348"/>
-    <hyperlink ref="N412" r:id="rId349"/>
-    <hyperlink ref="Q412" r:id="rId350"/>
-    <hyperlink ref="B418" r:id="rId351"/>
-    <hyperlink ref="L418" r:id="rId352"/>
-    <hyperlink ref="N418" r:id="rId353"/>
-    <hyperlink ref="P418" r:id="rId354"/>
-    <hyperlink ref="B425" r:id="rId355"/>
-    <hyperlink ref="L425" r:id="rId356"/>
-    <hyperlink ref="N425" r:id="rId357"/>
-    <hyperlink ref="P425" r:id="rId358"/>
-    <hyperlink ref="B430" r:id="rId359"/>
-    <hyperlink ref="L430" r:id="rId360"/>
-    <hyperlink ref="N430" r:id="rId361"/>
-    <hyperlink ref="P430" r:id="rId362"/>
-    <hyperlink ref="B431" r:id="rId363"/>
-    <hyperlink ref="L431" r:id="rId364"/>
-    <hyperlink ref="N431" r:id="rId365"/>
-    <hyperlink ref="P431" r:id="rId366"/>
-    <hyperlink ref="B443" r:id="rId367"/>
-    <hyperlink ref="L443" r:id="rId368"/>
-    <hyperlink ref="N443" r:id="rId369"/>
-    <hyperlink ref="P443" r:id="rId370"/>
-    <hyperlink ref="Q443" r:id="rId371"/>
-    <hyperlink ref="B460" r:id="rId372"/>
-    <hyperlink ref="L460" r:id="rId373"/>
-    <hyperlink ref="N460" r:id="rId374"/>
-    <hyperlink ref="P460" r:id="rId375"/>
-    <hyperlink ref="Q460" r:id="rId376"/>
-    <hyperlink ref="N465" r:id="rId377"/>
-    <hyperlink ref="B476" r:id="rId378"/>
-    <hyperlink ref="L476" r:id="rId379"/>
-    <hyperlink ref="N476" r:id="rId380"/>
-    <hyperlink ref="P476" r:id="rId381"/>
-    <hyperlink ref="R476" r:id="rId382"/>
-    <hyperlink ref="B482" r:id="rId383"/>
-    <hyperlink ref="L482" r:id="rId384"/>
-    <hyperlink ref="N482" r:id="rId385"/>
-    <hyperlink ref="P482" r:id="rId386"/>
-    <hyperlink ref="B484" r:id="rId387"/>
-    <hyperlink ref="L484" r:id="rId388"/>
-    <hyperlink ref="N484" r:id="rId389"/>
-    <hyperlink ref="B487" r:id="rId390"/>
-    <hyperlink ref="L487" r:id="rId391"/>
-    <hyperlink ref="N487" r:id="rId392"/>
-    <hyperlink ref="B490" r:id="rId393"/>
-    <hyperlink ref="L490" r:id="rId394"/>
-    <hyperlink ref="N490" r:id="rId395"/>
-    <hyperlink ref="P490" r:id="rId396"/>
-    <hyperlink ref="B494" r:id="rId397"/>
-    <hyperlink ref="L494" r:id="rId398"/>
-    <hyperlink ref="N494" r:id="rId399"/>
-    <hyperlink ref="P494" r:id="rId400"/>
-    <hyperlink ref="B495" r:id="rId401"/>
-    <hyperlink ref="L495" r:id="rId402"/>
-    <hyperlink ref="N495" r:id="rId403"/>
-    <hyperlink ref="P495" r:id="rId404"/>
-    <hyperlink ref="B498" r:id="rId405"/>
-    <hyperlink ref="L498" r:id="rId406"/>
-    <hyperlink ref="N498" r:id="rId407"/>
-    <hyperlink ref="P498" r:id="rId408"/>
-    <hyperlink ref="B509" r:id="rId409"/>
-    <hyperlink ref="L509" r:id="rId410"/>
-    <hyperlink ref="N509" r:id="rId411"/>
-    <hyperlink ref="P509" r:id="rId412"/>
-    <hyperlink ref="B512" r:id="rId413"/>
-    <hyperlink ref="L512" r:id="rId414"/>
-    <hyperlink ref="N512" r:id="rId415"/>
-    <hyperlink ref="P512" r:id="rId416"/>
-    <hyperlink ref="R512" r:id="rId417"/>
-    <hyperlink ref="B523" r:id="rId418"/>
-    <hyperlink ref="L523" r:id="rId419"/>
-    <hyperlink ref="N523" r:id="rId420"/>
-    <hyperlink ref="P523" r:id="rId421"/>
-    <hyperlink ref="Q523" r:id="rId422"/>
-    <hyperlink ref="R523" r:id="rId423"/>
-    <hyperlink ref="B526" r:id="rId424"/>
-    <hyperlink ref="L526" r:id="rId425"/>
-    <hyperlink ref="N526" r:id="rId426"/>
-    <hyperlink ref="P526" r:id="rId427"/>
-    <hyperlink ref="B527" r:id="rId428"/>
-    <hyperlink ref="L527" r:id="rId429"/>
-    <hyperlink ref="N527" r:id="rId430"/>
-    <hyperlink ref="Q527" r:id="rId431"/>
-    <hyperlink ref="B529" r:id="rId432"/>
-    <hyperlink ref="L529" r:id="rId433"/>
-    <hyperlink ref="N529" r:id="rId434"/>
-    <hyperlink ref="P529" r:id="rId435"/>
-    <hyperlink ref="B531" r:id="rId436"/>
-    <hyperlink ref="L531" r:id="rId437"/>
-    <hyperlink ref="N531" r:id="rId438"/>
-    <hyperlink ref="P531" r:id="rId439"/>
-    <hyperlink ref="B532" r:id="rId440"/>
-    <hyperlink ref="L532" r:id="rId441"/>
-    <hyperlink ref="N532" r:id="rId442"/>
-    <hyperlink ref="P532" r:id="rId443"/>
-    <hyperlink ref="B533" r:id="rId444"/>
-    <hyperlink ref="L533" r:id="rId445"/>
-    <hyperlink ref="N533" r:id="rId446"/>
-    <hyperlink ref="P533" r:id="rId447"/>
-    <hyperlink ref="Q533" r:id="rId448"/>
-    <hyperlink ref="B534" r:id="rId449"/>
-    <hyperlink ref="L534" r:id="rId450"/>
-    <hyperlink ref="N534" r:id="rId451"/>
-    <hyperlink ref="Q534" r:id="rId452"/>
-    <hyperlink ref="B535" r:id="rId453"/>
-    <hyperlink ref="L535" r:id="rId454"/>
-    <hyperlink ref="N535" r:id="rId455"/>
-    <hyperlink ref="Q535" r:id="rId456"/>
-    <hyperlink ref="B546" r:id="rId457"/>
-    <hyperlink ref="L546" r:id="rId458"/>
-    <hyperlink ref="N546" r:id="rId459"/>
-    <hyperlink ref="P546" r:id="rId460"/>
-    <hyperlink ref="Q546" r:id="rId461"/>
-    <hyperlink ref="N554" r:id="rId462"/>
-    <hyperlink ref="B555" r:id="rId463"/>
-    <hyperlink ref="L555" r:id="rId464"/>
-    <hyperlink ref="N555" r:id="rId465"/>
-    <hyperlink ref="P555" r:id="rId466"/>
-    <hyperlink ref="Q555" r:id="rId467"/>
-    <hyperlink ref="B562" r:id="rId468"/>
-    <hyperlink ref="L562" r:id="rId469"/>
-    <hyperlink ref="N562" r:id="rId470"/>
-    <hyperlink ref="P562" r:id="rId471"/>
-    <hyperlink ref="Q562" r:id="rId472"/>
-    <hyperlink ref="B563" r:id="rId473"/>
-    <hyperlink ref="L563" r:id="rId474"/>
-    <hyperlink ref="N563" r:id="rId475"/>
-    <hyperlink ref="Q563" r:id="rId476"/>
-    <hyperlink ref="B564" r:id="rId477"/>
-    <hyperlink ref="L564" r:id="rId478"/>
-    <hyperlink ref="N564" r:id="rId479"/>
-    <hyperlink ref="Q564" r:id="rId480"/>
-    <hyperlink ref="B585" r:id="rId481"/>
-    <hyperlink ref="L585" r:id="rId482"/>
-    <hyperlink ref="N585" r:id="rId483"/>
-    <hyperlink ref="P585" r:id="rId484"/>
-    <hyperlink ref="R585" r:id="rId485"/>
-    <hyperlink ref="B595" r:id="rId486"/>
-    <hyperlink ref="L595" r:id="rId487"/>
-    <hyperlink ref="N595" r:id="rId488"/>
-    <hyperlink ref="P595" r:id="rId489"/>
-    <hyperlink ref="Q595" r:id="rId490"/>
-    <hyperlink ref="B621" r:id="rId491"/>
-    <hyperlink ref="L621" r:id="rId492"/>
-    <hyperlink ref="N621" r:id="rId493"/>
-    <hyperlink ref="P621" r:id="rId494"/>
-    <hyperlink ref="Q621" r:id="rId495"/>
-    <hyperlink ref="B622" r:id="rId496"/>
-    <hyperlink ref="L622" r:id="rId497"/>
-    <hyperlink ref="N622" r:id="rId498"/>
-    <hyperlink ref="O622" r:id="rId499"/>
-    <hyperlink ref="P622" r:id="rId500"/>
-    <hyperlink ref="Q622" r:id="rId501"/>
-    <hyperlink ref="B631" r:id="rId502"/>
-    <hyperlink ref="N631" r:id="rId503"/>
-    <hyperlink ref="P631" r:id="rId504"/>
-    <hyperlink ref="B640" r:id="rId505"/>
-    <hyperlink ref="L640" r:id="rId506"/>
-    <hyperlink ref="N640" r:id="rId507"/>
-    <hyperlink ref="P640" r:id="rId508"/>
-    <hyperlink ref="B647" r:id="rId509"/>
-    <hyperlink ref="L647" r:id="rId510"/>
-    <hyperlink ref="N647" r:id="rId511"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="P6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="L8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="L14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="P14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="Q14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="L18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B26" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="L26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="P26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N31" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B32" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="L32" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N32" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="L38" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N38" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="P38" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="Q38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B43" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="L43" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N43" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="Q43" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B44" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="L44" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N44" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="Q44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B45" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="L45" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N45" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B63" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="L63" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N63" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="P63" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="R63" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B65" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="L65" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N65" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="Q65" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B66" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="L66" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N66" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="Q66" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B68" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="L68" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N68" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="Q68" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="B69" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="L69" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N69" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="Q69" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B78" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="L78" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N78" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="P78" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B79" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="L79" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N79" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="P79" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="Q79" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B89" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="L89" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N89" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="P89" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="Q89" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="R89" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="B90" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="L90" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N90" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="Q90" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="B100" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="L100" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N100" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="P100" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="Q100" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="B101" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="L101" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N101" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="Q101" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="B117" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L117" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N117" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="P117" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="R117" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B118" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="L118" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N118" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="Q118" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="B128" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="L128" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N128" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="P128" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="R128" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="B129" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="L129" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N129" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="Q129" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="B135" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="L135" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N135" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="P135" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="Q135" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="B136" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="L136" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="N136" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="Q136" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="B142" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="L142" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="N142" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="P142" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="R142" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="B143" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="L143" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="N143" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="Q143" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="B147" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="L147" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="N147" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="P147" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="Q147" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="R147" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="B148" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="L148" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="N148" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="Q148" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="B151" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="L151" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="N151" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="P151" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="Q151" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="R151" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="B152" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="L152" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="N152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="Q152" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="B153" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="L153" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="N153" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="P153" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="Q153" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="R153" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="B154" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="L154" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="N154" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="P154" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="Q154" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="B156" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="L156" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="N156" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="P156" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="Q156" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="R156" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="B157" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="L157" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="N157" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="Q157" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="B160" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="L160" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="N160" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="P160" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="R160" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="B161" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="L161" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="N161" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="Q161" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="B167" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="L167" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="N167" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="P167" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="B173" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="L173" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="N173" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="P173" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="Q173" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="B193" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="L193" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="N193" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="P193" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="B197" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="L197" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="N197" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="P197" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="B201" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="L201" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="N201" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="P201" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="B205" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="L205" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="N205" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="P205" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="Q205" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="B207" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="L207" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="N207" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="P207" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="B211" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="L211" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="N211" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="P211" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="Q211" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="N213" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="B214" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="L214" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="N214" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="P214" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="Q214" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="B219" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="L219" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="N219" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="P219" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="Q219" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="B224" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="L224" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="N224" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="P224" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="Q224" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="R224" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="B230" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="L230" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="N230" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="P230" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="B237" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="L237" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="N237" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="P237" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="B246" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="L246" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="N246" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="P246" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="Q246" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="B252" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="L252" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="N252" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="P252" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="Q252" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="B256" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="L256" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="N256" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="B278" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="L278" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="N278" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="P278" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="Q278" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="B286" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="L286" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="N286" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="P286" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="Q286" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="B297" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="L297" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="N297" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="P297" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="Q297" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="B305" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="L305" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="N305" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="P305" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="Q305" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="B327" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="L327" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="N327" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="P327" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="B329" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="L329" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="N329" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="P329" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="Q329" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="B333" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="L333" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="N333" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="B336" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="L336" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="N336" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="P336" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="Q336" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="B338" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="L338" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="N338" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="P338" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="Q338" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="B344" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="L344" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="N344" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="P344" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="Q344" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="B345" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="L345" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="N345" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="Q345" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="B348" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="L348" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="N348" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="P348" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="Q348" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="B351" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="L351" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="N351" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="P351" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="Q351" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="B353" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="L353" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="N353" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="P353" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="Q353" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="R353" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="B392" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="L392" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="N392" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="P392" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="B394" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="L394" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="N394" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="P394" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="B395" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="L395" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="N395" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="Q395" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="B396" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="L396" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="N396" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="P396" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="B407" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="L407" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="N407" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="P407" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="B408" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="L408" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="N408" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="P408" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="B409" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="L409" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="N409" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="Q409" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="B411" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="L411" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="N411" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="P411" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="B412" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="L412" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="N412" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="Q412" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="B418" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="L418" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="N418" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="P418" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="B425" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="L425" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="N425" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="P425" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="B430" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="L430" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="N430" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="P430" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="B431" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="L431" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="N431" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="P431" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="B443" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="L443" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="N443" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="P443" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="Q443" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="B460" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="L460" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="N460" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="P460" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="Q460" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="N465" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="B476" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="L476" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="N476" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="P476" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="R476" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="B482" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="L482" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="N482" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="P482" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="B484" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="L484" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="N484" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="B487" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="L487" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="N487" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="B490" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="L490" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="N490" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="P490" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="B494" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="L494" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="N494" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="P494" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="B495" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="L495" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="N495" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="P495" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="B498" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="L498" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="N498" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="P498" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="B509" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="L509" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="N509" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="P509" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="B512" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="L512" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="N512" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="P512" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="R512" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="B523" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="L523" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="N523" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="P523" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="Q523" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="R523" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="B526" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="L526" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="N526" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="P526" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="B527" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="L527" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="N527" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="Q527" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="B529" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="L529" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="N529" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="P529" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="B531" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="L531" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="N531" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="P531" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="B532" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="L532" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="N532" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="P532" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="B533" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="L533" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="N533" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="P533" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="Q533" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="B534" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="L534" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="N534" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="Q534" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="B535" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="L535" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="N535" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="Q535" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="B546" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="L546" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="N546" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="P546" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="Q546" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="N554" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="B555" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="L555" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="N555" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="P555" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="Q555" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="B562" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="L562" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="N562" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="P562" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="Q562" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="B563" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="L563" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="N563" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="Q563" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="B564" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="L564" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="N564" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="Q564" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="B585" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="L585" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="N585" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="P585" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="R585" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="B595" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="L595" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="N595" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="P595" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="Q595" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="B621" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="L621" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="N621" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="P621" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="Q621" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="B622" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="L622" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="N622" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="O622" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="P622" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="Q622" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="B631" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="N631" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="P631" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="B640" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="L640" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="N640" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="P640" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="B647" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="L647" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="N647" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
   </hyperlinks>
-  <pageSetup paperSize="66" scale="100" orientation="landscape"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="66" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b16d0a29-7bab-41bf-9a27-8bca820ba65b}" enabled="1" method="Privileged" siteId="{a2d34bfa-bd5b-4dc3-9a2e-098f99296771}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -1,21 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mullerw\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5E6C47-6FFD-425B-AC5E-3B9B03912F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="One Stop Shop" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -88,9 +76,7 @@
     <t>To maintain Interconnection steady-state frequency within defined limits by balancing real power demand and supply in real-time.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 WECC Request for Interpretation of BAL-001-0, Requirement 1</t>
   </si>
   <si>
@@ -103,9 +89,7 @@
     <t>BAL-001-0a</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM08-7-000 _x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM08-7-000 
 WECC Request for Interpretation of BAL-001-0, Requirement 1 and Errata change</t>
   </si>
   <si>
@@ -142,9 +126,7 @@
     <t>To maintain Interconnection steady-state frequency within defined limits.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. ​RD13-12-000​ ​_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. ​RD13-12-000​ ​
 Refer to the implementation plan for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -220,9 +202,7 @@
     <t>Contingency Reserve is required for the reliable operation of the interconnected power system. Adequate generating capacity must be available at all times to maintain scheduled frequency, and avoid loss of firm load following transmission or generation contingencies. This generating capacity is necessary to replace generating capacity and energy lost due to forced outages of generation or transmission equipment.</t>
   </si>
   <si>
-    <t>Docket No. RM09-15-000; Order No. 740_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Docket No. RM09-15-000; Order No. 740
 Remanded by FERC in an October 21, 2010 Order, effective November 26, 2010.</t>
   </si>
   <si>
@@ -295,9 +275,7 @@
     <t>X</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. ​RM13-11-000 ​_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. ​RM13-11-000 ​
 See the implementation plan for guidance on phased-in enforcement dates. Requirement R1 will never become enforceable.. Disregard the dates for R1 it is non enforceable.</t>
   </si>
   <si>
@@ -328,18 +306,14 @@
     <t>The purpose of this standard is to ensure that Time Error Corrections are conducted in a manner that does not adversely affect the reliability of the Interconnection.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 The retirement of BAL-004-0 is contingent upon the retirement of NAESB WEQ-006 Manual Time Error Correction Business Practice Standard.</t>
   </si>
   <si>
     <t>BAL-004-1</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM09-13-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM09-13-000
 The NERC BOT withdrew its approval of this standard at its meeting on August 16, 2012.</t>
   </si>
   <si>
@@ -535,7 +509,7 @@
     <t>Sabotage Reporting</t>
   </si>
   <si>
-    <t>Disturbances or unusual occurrences, suspected or determined to be caused by sabotage, shall be reported to the appropriate systems, governmental agencies, and regulatory_x000D_
+    <t xml:space="preserve">Disturbances or unusual occurrences, suspected or determined to be caused by sabotage, shall be reported to the appropriate systems, governmental agencies, and regulatory
 bodies.</t>
   </si>
   <si>
@@ -602,9 +576,7 @@
     <t>CIP-002-3a</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD12-5-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD12-5-000
 FERC remanded the interpretation of R3 in an order issued on 3/21/13</t>
   </si>
   <si>
@@ -614,12 +586,9 @@
     <t>CIP-002-3(i)</t>
   </si>
   <si>
-    <t>NERC Standards CIP-002-3(i) through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System._x000D_
-_x000D_
-These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. _x000D_
-_x000D_
-Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets._x000D_
-_x000D_
+    <t xml:space="preserve">NERC Standards CIP-002-3(i) through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System.
+These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. 
+Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets.
 Standard CIP-002-3(i) requires the identification and documentation of the Critical Cyber Assets associated with the Critical Assets that support the reliable operation of the Bulk Electric System. These Critical Assets are to be identified through the application of a risk-based assessment.</t>
   </si>
   <si>
@@ -632,12 +601,9 @@
     <t>CIP-002-3(i)b</t>
   </si>
   <si>
-    <t>NERC Standards CIP-002-3(i)b through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System._x000D_
-_x000D_
-These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. _x000D_
-_x000D_
-Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets._x000D_
-_x000D_
+    <t xml:space="preserve">NERC Standards CIP-002-3(i)b through CIP-009-3 provide a cyber security framework for the identification and protection of Critical Cyber Assets to support reliable operation of the Bulk Electric System.
+These standards recognize the differing roles of each entity in the operation of the Bulk Electric System, the criticality and vulnerability of the assets needed to manage Bulk Electric System reliability, and the risks to which they are exposed. 
+Business and operational demands for managing and maintaining a reliable Bulk Electric System increasingly rely on Cyber Assets supporting critical reliability functions and processes to communicate with each other, across functions and organizations, for services and data. This results in increased risks to these Cyber Assets.
 Standard CIP-002-3(i)b requires the identification and documentation of the Critical Cyber Assets associated with the Critical Assets that support the reliable operation of the Bulk Electric System. These Critical Assets are to be identified through the application of a risk-based assessment.</t>
   </si>
   <si>
@@ -674,18 +640,14 @@
     <t>CIP-002-5.1</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-5-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-5-000
 Errata approved by the SC on 9/27/2013</t>
   </si>
   <si>
     <t>CIP-002-5.1a</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD17-2-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD17-2-000
 CIP-002-5.1a replaced CIP-002-5.1</t>
   </si>
   <si>
@@ -698,7 +660,7 @@
     <t>Cyber Security – BES Cyber System Categorization</t>
   </si>
   <si>
-    <t>To identify and categorize BES Cyber Systems and their associated BES _x000D_
+    <t xml:space="preserve">To identify and categorize BES Cyber Systems and their associated BES 
 Cyber Assets for the application of cyber security requirements commensurate with the adverse impact that loss, compromise, or misuse of those BES Cyber Systems could have on the reliable operation of the BES. Identification and categorization of BES Cyber Systems support appropriate protection against compromises that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
@@ -741,9 +703,7 @@
     <t>Standard CIP-003 requires that Responsible Entities have minimum security management controls in place to protect Critical Cyber Assets. Standard CIP-003 should be read as part of a group of standards numbered Standards CIP-002 through CIP-009. Responsible Entities should interpret and apply Standards CIP-002 through CIP-009 using reasonable business judgment.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000,  RM06-22-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000,  RM06-22-000
 Replaced with CIP-003-2</t>
   </si>
   <si>
@@ -771,9 +731,7 @@
     <t>Standard CIP-003-2 requires that Responsible Entities have minimum security management controls in place to protect Critical Cyber Assets. Standard CIP-003-2 should be read as part of a group of standards numbered Standards CIP-002-2 through CIP-009-2.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-22-000, RD09-7-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-22-000, RD09-7-000
 Replaced with CIP-003-3</t>
   </si>
   <si>
@@ -804,9 +762,7 @@
     <t>To specify consistent and sustainable security management controls that establish responsibility and accountability to protect BES Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-5-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-5-000
 CIP-003-5 will be superseded by CIP-003-6.</t>
   </si>
   <si>
@@ -816,12 +772,8 @@
     <t>To specify consistent and sustainable security management controls that establish responsibility and accountability to protect Bulk Electric System (BES) Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000_x000D_
-_x000D_
-_x000D_
-With the approval of CIP-003-7 and its associated Implementation Plan, entities will not be required to implement CIP-003-6, Requirement R2, Attachment 1, Sections 2 and 3. Instead, entities will implement CIP-003-7, Requirement R2, Attachment 1 Sections 2 and 3 on January 1, 2020. See Implementation Plan for CIP-003-7._x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
+With the approval of CIP-003-7 and its associated Implementation Plan, entities will not be required to implement CIP-003-6, Requirement R2, Attachment 1, Sections 2 and 3. Instead, entities will implement CIP-003-7, Requirement R2, Attachment 1 Sections 2 and 3 on January 1, 2020. See Implementation Plan for CIP-003-7.
 </t>
   </si>
   <si>
@@ -909,11 +861,7 @@
     <t>CIP-004-5.1</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-5-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-5-000
 CIP-004-5.1 will be superseded by CIP-004-6.</t>
   </si>
   <si>
@@ -1028,8 +976,8 @@
     <t xml:space="preserve">Cyber Security — Electronic Security Perimeter(s) </t>
   </si>
   <si>
-    <t>To protect BES Cyber Systems (BCS) against compromise by permitting_x000D_
-only known and controlled communication to reduce the likelihood of_x000D_
+    <t xml:space="preserve">To protect BES Cyber Systems (BCS) against compromise by permitting
+only known and controlled communication to reduce the likelihood of
 misoperation or instability in the Bulk Electric System (BES).</t>
   </si>
   <si>
@@ -1117,8 +1065,7 @@
     <t>CIP-006-4d</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-3-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD12-3-000
 </t>
   </si>
   <si>
@@ -1137,11 +1084,7 @@
     <t>To manage physical access to Bulk Electric System (BES) Cyber Systems by specifying a physical security plan in support of protecting BES Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM15-14-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
 See Implementation Plan for Compliance dates.</t>
   </si>
   <si>
@@ -1178,10 +1121,10 @@
     <t>CIP-007-3</t>
   </si>
   <si>
-    <t>Standard CIP-007-3 requires Responsible Entities to define methods, processes,_x000D_
-and procedures for securing those systems determined to be Critical Cyber Assets, as well as_x000D_
-the other (non-critical) Cyber Assets within the Electronic Security Perimeter(s). Standard_x000D_
-CIP-007-3 should be read as part of a group of standards numbered Standards CIP-002-3_x000D_
+    <t xml:space="preserve">Standard CIP-007-3 requires Responsible Entities to define methods, processes,
+and procedures for securing those systems determined to be Critical Cyber Assets, as well as
+the other (non-critical) Cyber Assets within the Electronic Security Perimeter(s). Standard
+CIP-007-3 should be read as part of a group of standards numbered Standards CIP-002-3
 through CIP-009-3.</t>
   </si>
   <si>
@@ -1194,11 +1137,7 @@
     <t>Standard CIP-007-3 requires Responsible Entities to define methods, processes, and procedures for securing those systems determined to be Critical Cyber Assets, as well as the other (non-critical) Cyber Assets within the Electronic Security Perimeter(s). Standard CIP-007-3 should be read as part of a group of standards numbered Standards CIP-002-3 through CIP-009-3.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD09-7-002_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD09-7-002
 The version number was updated from CIP-007-3 to CIP-007-3a to incorporate the approved interpretation that should have previously been appended.</t>
   </si>
   <si>
@@ -1229,10 +1168,7 @@
     <t>To manage system security by specifying select technical, operational, and procedural requirements in support of protecting Bulk Electric System (BES) Cyber Systems against compromise that could lead to misoperation or instability in the BES.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
 </t>
   </si>
   <si>
@@ -1329,8 +1265,7 @@
     <t>CIP-009-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-14-000
 </t>
   </si>
   <si>
@@ -1484,8 +1419,7 @@
     <t>CIP-014-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD22-3-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD22-3-000
 </t>
   </si>
   <si>
@@ -1519,9 +1453,7 @@
     <t>Each Reliability Coordinator, Transmission Operator and Balancing Authority needs adequate and reliable telecommunications facilities internally and with others for the exchange of Interconnection and operating information necessary to maintain reliability.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 COM-001-0 was never enforceable</t>
   </si>
   <si>
@@ -1579,14 +1511,12 @@
     <t>COM-002-1</t>
   </si>
   <si>
-    <t>To ensure Balancing Authorities, Transmission Operators, and Generator Operators have adequate communications and that these communications capabilities are_x000D_
-staffed and available for addressing a real-time emergency condition. To ensure_x000D_
+    <t xml:space="preserve">To ensure Balancing Authorities, Transmission Operators, and Generator Operators have adequate communications and that these communications capabilities are
+staffed and available for addressing a real-time emergency condition. To ensure
 communications by operating personnel are effective.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 COM-002-1 was never enforceable</t>
   </si>
   <si>
@@ -1644,11 +1574,7 @@
     <t>EOP-001-1</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM10-15-000, RM10-16-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM10-15-000, RM10-16-000
 Replaced with EOP-001-2 (EOP-001-1 was not enforceable)</t>
   </si>
   <si>
@@ -1658,11 +1584,7 @@
     <t>EOP-001-2</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM10-15-000, RM10-16-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM10-15-000, RM10-16-000
 Replaced with EOP-001-2b (Interpretation of R1 and R2.2)--(EOP-001-2 was not enforceable)</t>
   </si>
   <si>
@@ -1672,8 +1594,7 @@
     <t>EOP-001-2.1b</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-4-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD12-4-000
 </t>
   </si>
   <si>
@@ -1695,9 +1616,7 @@
     <t>EOP-002-1</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 EOP-002-1 was never enforceable</t>
   </si>
   <si>
@@ -1725,9 +1644,7 @@
     <t>A Balancing Authority and Transmission Operator operating with insufficient generation or transmission capacity must have the capability and authority to shed load rather than risk an uncontrolled failure of the Interconnection.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 EOP-003-0 was never enforceable</t>
   </si>
   <si>
@@ -1770,8 +1687,7 @@
     <t>EOP-004-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000
 </t>
   </si>
   <si>
@@ -1793,9 +1709,7 @@
     <t>To ensure plans, procedures, and resources are available to restore the electric system to a normal condition in the event of a partial or total shut down of the system</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 EOP-005-0 was never enforceable</t>
   </si>
   <si>
@@ -1838,9 +1752,7 @@
     <t>The Reliability Coordinator must have a coordinating role in system restoration to ensure reliability is maintained during restoration and priority is placed on restoring the Interconnection.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 EOP-006-0 was never enforceable</t>
   </si>
   <si>
@@ -1868,9 +1780,7 @@
     <t>A system Blackstart Capability Plan (BCP) is necessary to ensure that the quantity and location of system blackstart generators are sufficient and that they can perform their expected functions as specified in overall coordinated Regional System Restoration Plans (SRP).</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 FERC approved withdrawal of standard</t>
   </si>
   <si>
@@ -1925,9 +1835,7 @@
     <t>To mitigate the effects of geomagnetic disturbance (GMD) events by implementing Operating Plans, Processes, and Procedures.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM14-1-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM14-1-000
 A FERC order was issued on June 19, 2014, approving EOP-010-1. Requirement 2 of Reliability Standard EOP-010-1 will not become effective until the first day following retirement of Reliability Standard IRO-005-3.1a.</t>
   </si>
   <si>
@@ -1943,8 +1851,7 @@
     <t>To address the effects of operating Emergencies by ensuring each Transmission Operator and Balancing Authority has developed Operating Plan(s) to mitigate operating Emergencies, and that those plans are coordinated within a Reliability Coordinator Area.</t>
   </si>
   <si>
-    <t xml:space="preserve">RM15-7-000_x000D_
-_x000D_
+    <t xml:space="preserve">RM15-7-000
 </t>
   </si>
   <si>
@@ -1960,10 +1867,7 @@
     <t>To address the effects of operating emergencies by ensuring each Transmission Operator, Balancing Authority, and Generator Owner has developed plan(s) to mitigate operating Emergencies and that those plans are implemented and coordinated within the Reliability Coordinator Area as specified within the requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD21-5-000_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD21-5-000
 </t>
   </si>
   <si>
@@ -2036,8 +1940,7 @@
     <t>To avoid adverse impacts on reliability, Transmission Owners and Generator Owners must establish Facility connection and performance requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM12-16-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM12-16-000
 </t>
   </si>
   <si>
@@ -2065,9 +1968,7 @@
     <t>FAC-001-4</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD22-5-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD22-5-000
 See Implementation Plan for additional compliance information</t>
   </si>
   <si>
@@ -2149,8 +2050,7 @@
     <t>To maintain a reliable electric transmission system by using a defense-in-depth strategy to manage vegetation located on transmission rights of way (ROW) and minimize encroachments from vegetation located adjacent to the ROW, thus preventing the risk of those vegetation-related outages that could lead to Cascading.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM12-4-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM12-4-000
 </t>
   </si>
   <si>
@@ -2238,9 +2138,7 @@
     <t>FAC-008-4</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM19-17-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM19-17-000
 Withdrawn 2/4/2021 Replaced by FAC-008-5</t>
   </si>
   <si>
@@ -2394,9 +2292,7 @@
     <t>FAC-501-WECC-4</t>
   </si>
   <si>
-    <t>To ensure the Transmission Owner of a path identified in the Table Revision Process, Attachment A, Major WECC Transfer Paths in the Bulk Electric System (Table), has a Transmission Maintenance and Inspection Plan (TMIP) for those paths, annually updates its TMIP, and adheres to the TMIP._x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">To ensure the Transmission Owner of a path identified in the Table Revision Process, Attachment A, Major WECC Transfer Paths in the Bulk Electric System (Table), has a Transmission Maintenance and Inspection Plan (TMIP) for those paths, annually updates its TMIP, and adheres to the TMIP.
  </t>
   </si>
   <si>
@@ -2412,9 +2308,7 @@
     <t>To ensure that Interchange Transactions, certain Interchange Schedules, and intra-Balancing Authority Area transfers using Point-to-Point Transmission Service are Tagged in adequate time to allow the transactions to be assessed for reliability impacts by the affected Reliability Coordinators, Transmission Service Providers, and Balancing Authorities, and to allow adequate time for implementation.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 INT-001-0 was never enforceable</t>
   </si>
   <si>
@@ -2445,9 +2339,7 @@
     <t>To ensure that Interchange Transaction information is provided to all entities needing to make reliability assessments and to ensure all affected reliability entities assess the reliability impacts of Interchange Transactions before approving or denying a Tag. To communicate the approvals and denials of the Tag and the final composite status of the Tag.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 This standard was never enforceable</t>
   </si>
   <si>
@@ -2460,9 +2352,7 @@
     <t>To ensure Balancing Authorities confirm Interchange Schedules with Adjacent Balancing Authorities prior to implementing the schedules in their Area Control Error (ACE) equations. To ensure Balancing Authorities incorporate all confirmed Schedules into their ACE equations.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 INT-003-0 was never enforceable</t>
   </si>
   <si>
@@ -2472,9 +2362,7 @@
     <t>To ensure Balancing Authorities confirm Interchange Schedules with Adjacent Balancing Authorities prior to implementing the schedules in their Area Control Error (ACE) equations.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 INT-003-1 was never enforceable</t>
   </si>
   <si>
@@ -2613,8 +2501,7 @@
     <t>To ensure that Balancing Authorities implement the Interchange as agreed upon in the Interchange confirmation process.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-4-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD14-4-000
 </t>
   </si>
   <si>
@@ -2663,15 +2550,13 @@
     <t>Reliability Coordination – Responsibilities and Authorities</t>
   </si>
   <si>
-    <t>Reliability Coordinators must have the authority, plans, and agreements in place to immediately direct reliability entities within their Reliability Coordinator Areas to redispatch generation, reconfigure transmission, or reduce load to mitigate critical conditions to rn the system to a reliable state. If a Reliability Coordinator delegates tasks to others, the_x000D_
-Reliability Coordinator retains its responsibilities for complying with NERC and regional_x000D_
-standards. Standards of conduct are necessary to ensure the Reliability Coordinator does not_x000D_
+    <t xml:space="preserve">Reliability Coordinators must have the authority, plans, and agreements in place to immediately direct reliability entities within their Reliability Coordinator Areas to redispatch generation, reconfigure transmission, or reduce load to mitigate critical conditions to rn the system to a reliable state. If a Reliability Coordinator delegates tasks to others, the
+Reliability Coordinator retains its responsibilities for complying with NERC and regional
+standards. Standards of conduct are necessary to ensure the Reliability Coordinator does not
 act in a manner that favors one market participant over another.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 IRO-001-0 was never enforceable</t>
   </si>
   <si>
@@ -2726,13 +2611,11 @@
     <t>Reliability Coordination – Facilities</t>
   </si>
   <si>
-    <t>Reliability Coordinators need information, tools and other capabilities to perform_x000D_
+    <t xml:space="preserve">Reliability Coordinators need information, tools and other capabilities to perform
 their responsibilities.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 IRO-002-0 was never enforceable</t>
   </si>
   <si>
@@ -2799,7 +2682,7 @@
     <t>Reliability Coordination – Wide-Area View</t>
   </si>
   <si>
-    <t>The Reliability Coordinator must have a wide area view of its own Reliability_x000D_
+    <t xml:space="preserve">The Reliability Coordinator must have a wide area view of its own Reliability
 Coordinator Area and that of neighboring Reliability Coordinators.</t>
   </si>
   <si>
@@ -2827,11 +2710,11 @@
     <t>Reliability Coordination — Operations Planning</t>
   </si>
   <si>
-    <t>Each Reliability Coordinator must conduct next-day reliability analyses for its_x000D_
-Reliability Coordinator Area to ensure the Bulk Electric System can be operated reliably in_x000D_
-anticipated normal and Contingency conditions. System studies must be conducted to_x000D_
-highlight potential interface and other operating limits, including overloaded transmission lines_x000D_
-and transformers, voltage and stability limits, etc. Plans must be developed to alleviate System_x000D_
+    <t xml:space="preserve">Each Reliability Coordinator must conduct next-day reliability analyses for its
+Reliability Coordinator Area to ensure the Bulk Electric System can be operated reliably in
+anticipated normal and Contingency conditions. System studies must be conducted to
+highlight potential interface and other operating limits, including overloaded transmission lines
+and transformers, voltage and stability limits, etc. Plans must be developed to alleviate System
 Operating Limit (SOL) and Interconnection Reliability Operating Limit (IROL) violations.</t>
   </si>
   <si>
@@ -2853,7 +2736,7 @@
     <t>Reliability Coordination — Current Day Operations</t>
   </si>
   <si>
-    <t>The Reliability Coordinator must be continuously aware of conditions within its Reliability Coordinator Area and include this information in its reliability assessments. The Reliability Coordinator must monitor Bulk Electric System parameters that may have significant impacts upon the Reliability Coordinator Area and neighboring Reliability_x000D_
+    <t xml:space="preserve">The Reliability Coordinator must be continuously aware of conditions within its Reliability Coordinator Area and include this information in its reliability assessments. The Reliability Coordinator must monitor Bulk Electric System parameters that may have significant impacts upon the Reliability Coordinator Area and neighboring Reliability
 Coordinator Areas.</t>
   </si>
   <si>
@@ -2905,8 +2788,8 @@
     <t>Reliability Coordination — Transmission Loading Relief</t>
   </si>
   <si>
-    <t>Regardless of the process it uses, the Reliability Coordinator must direct its Balancing Authorities and Transmission Operators to return the transmission system to within its Interconnection Reliability Operating Limits as soon as possible, but no longer than 30 minutes. The Reliability Coordinator needs to direct Balancing Authorities and Transmission_x000D_
-Operators to execute actions such as reconfiguration, redispatch, or load shedding until relief_x000D_
+    <t xml:space="preserve">Regardless of the process it uses, the Reliability Coordinator must direct its Balancing Authorities and Transmission Operators to return the transmission system to within its Interconnection Reliability Operating Limits as soon as possible, but no longer than 30 minutes. The Reliability Coordinator needs to direct Balancing Authorities and Transmission
+Operators to execute actions such as reconfiguration, redispatch, or load shedding until relief
 requested by the TLR process is achieved.</t>
   </si>
   <si>
@@ -2919,9 +2802,7 @@
     <t>Regardless of the process it uses, the Reliability Coordinator must direct its Balancing Authorities and Transmission Operators to return the transmission system to within its Interconnection Reliability Operating Limits as soon as possible, but no longer than 30 minutes. The Reliability Coordinator needs to direct Balancing Authorities and Transmission Operators to execute actions such as reconfiguration, redispatch, or load shedding until relief requested by the TLR process is achieved.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 IRO-006-1 was never enforceable</t>
   </si>
   <si>
@@ -2991,8 +2872,7 @@
     <t>To provide and execute transmission loading relief procedures that can be used to mitigate SOL or IROL exceedances for the purpose of maintaining reliable operation of the bulk electric system in the ERCOT Region.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD12-1-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD12-1-000
 </t>
   </si>
   <si>
@@ -3113,9 +2993,9 @@
     <t>Reliability Coordinator Data and Information Specification and Collection</t>
   </si>
   <si>
-    <t>To prevent instability, uncontrolled separation, or Cascading outages that _x000D_
-adversely impact reliability, by ensuring each Reliability Coordinator has the data and _x000D_
-information it needs to plan, monitor and assess the operation of its Reliability_x000D_
+    <t xml:space="preserve">To prevent instability, uncontrolled separation, or Cascading outages that 
+adversely impact reliability, by ensuring each Reliability Coordinator has the data and 
+information it needs to plan, monitor and assess the operation of its Reliability
 Coordinator Area.</t>
   </si>
   <si>
@@ -3233,10 +3113,7 @@
     <t>MOD-001-1a</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD10-5-000_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD10-5-000
 </t>
   </si>
   <si>
@@ -3246,13 +3123,11 @@
     <t>MOD-001-2</t>
   </si>
   <si>
-    <t>To ensure that determinations of available transmission system capability are determined in a manner that supports the reliable operation of the Bulk-Power System (BPS) and that the methodology and data underlying those determinations are_x000D_
+    <t xml:space="preserve">To ensure that determinations of available transmission system capability are determined in a manner that supports the reliable operation of the Bulk-Power System (BPS) and that the methodology and data underlying those determinations are
 disclosed to those registered entities that need such information for reliability purposes.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM14-7-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM14-7-000
 Petition for approval was withdrawn as part of Project 2018-03 SER Retirements.</t>
   </si>
   <si>
@@ -3292,9 +3167,7 @@
     <t>To promote the consistent and reliable calculation, verification, preservation, and use of Capacity Benefit Margin (CBM) to support analysis and system operations.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM05-17-000, RM05-25-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM05-17-000, RM05-25-000
  </t>
   </si>
   <si>
@@ -3352,9 +3225,7 @@
     <t>To promote the consistent and reliable calculation, verification, preservation, and use of Transmission Reliability Margin (TRM) to support analysis and system operations.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM08-19-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM08-19-000
  </t>
   </si>
   <si>
@@ -3400,9 +3271,7 @@
     <t>Maintenance and Distribution of Dynamics Data Requirements and Reporting Procedures</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 MOD-013-0 was never enforceable</t>
   </si>
   <si>
@@ -3550,9 +3419,7 @@
     <t>To ensure that accurate information on generator gross and net Real and Reactive Power capability and synchronous condenser Reactive Power capability is available for planning models used to assess Bulk Electric System (BES) reliability.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
 Please see the Implementation Plan for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -3577,19 +3444,14 @@
     <t>Verification of Models and Data for Generator Excitation Control System or Plant Volt/Var Control Functions</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify that the generator excitation control system or plant volt/var control function model (including the power system stabilizer model and the impedance compensator model) and the model parameters used in dynamic simulations accurately represent the generator excitation control system or plant volt/var control function behavior when assessing Bulk Electric System (BES) reliability._x000D_
- _x000D_
-Footnote: Excitation control system or plant volt/var control function:_x000D_
- _x000D_
-a.    For individual synchronous machines, the generator excitation control system includes the generator, exciter, voltage regulator, impedance compensation and power system stabilizer._x000D_
- _x000D_
-b.    For an aggregate generating plant, the volt/var control system includes the voltage regulator &amp; reactive power control system controlling and coordinating plant voltage and associated reactive capable resources._x000D_
+    <t xml:space="preserve">To verify that the generator excitation control system or plant volt/var control function model (including the power system stabilizer model and the impedance compensator model) and the model parameters used in dynamic simulations accurately represent the generator excitation control system or plant volt/var control function behavior when assessing Bulk Electric System (BES) reliability.
+Footnote: Excitation control system or plant volt/var control function:
+a.    For individual synchronous machines, the generator excitation control system includes the generator, exciter, voltage regulator, impedance compensation and power system stabilizer.
+b.    For an aggregate generating plant, the volt/var control system includes the voltage regulator &amp; reactive power control system controlling and coordinating plant voltage and associated reactive capable resources.
  </t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
 See Implementation Plan for additional compliance information</t>
   </si>
   <si>
@@ -3602,20 +3464,12 @@
     <t>To verify and validate that the dynamic models and associated parameters used to assess Bulk Electric System (BES) reliability represent the in-service equipment of Bulk Power System (BPS) facilities including generating facilities, transmission connected dynamic reactive resources, and high-voltage direct current (HVDC) systems.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD26-3-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
-Additional Effective Date Details_x000D_
-Requirements R1 and R7 -   April 1, 2027_x000D_
-Entities shall not be required to comply with Requirement R1 relating to the jointly developed dynamic model requirements between the Planning Coordinator and Transmission Planner and Requirement R7 relating to the provision of the current (in-use) models until twelve (12) months after the effective date of the Reliability Standard MOD-026-2._x000D_
-_x000D_
-_x000D_
-Requirements R2, R3, R4, R5, and R6 - April 1, 2029_x000D_
-Entities shall not be required to comply with Requirements R2, R3, R4, R5, and R6 until thirty-six (36) months after the effective date of Reliability Standard MOD-026-2._x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD26-3-000
+Additional Effective Date Details
+Requirements R1 and R7 -   April 1, 2027
+Entities shall not be required to comply with Requirement R1 relating to the jointly developed dynamic model requirements between the Planning Coordinator and Transmission Planner and Requirement R7 relating to the provision of the current (in-use) models until twelve (12) months after the effective date of the Reliability Standard MOD-026-2.
+Requirements R2, R3, R4, R5, and R6 - April 1, 2029
+Entities shall not be required to comply with Requirements R2, R3, R4, R5, and R6 until thirty-six (36) months after the effective date of Reliability Standard MOD-026-2.
 See the Implementation Plan for additional information on Initial Performance Dates for periodic requirements, newly commissioned and newly applicable facilities, and early compliance.  </t>
   </si>
   <si>
@@ -3628,13 +3482,10 @@
     <t>Verification of Models and Data for Turbine/Governor and Load Control or Active Power/Frequency Control Functions</t>
   </si>
   <si>
-    <t xml:space="preserve">To verify that the turbine/governor and load control or active power/frequency control model and the model parameters, used in dynamic simulations that assess Bulk Electric System (BES) reliability, accurately represent generator unit real power response to system frequency variations._x000D_
- _x000D_
-Footnote: Turbine/governor and load control or active power/frequency control:_x000D_
- _x000D_
-a.     Turbine/governor and load control applies to conventional synchronous generation._x000D_
- _x000D_
-b.     Active power/frequency control applies to inverter connected generators (often found at variable energy plants)._x000D_
+    <t xml:space="preserve">To verify that the turbine/governor and load control or active power/frequency control model and the model parameters, used in dynamic simulations that assess Bulk Electric System (BES) reliability, accurately represent generator unit real power response to system frequency variations.
+Footnote: Turbine/governor and load control or active power/frequency control:
+a.     Turbine/governor and load control applies to conventional synchronous generation.
+b.     Active power/frequency control applies to inverter connected generators (often found at variable energy plants).
  </t>
   </si>
   <si>
@@ -3653,11 +3504,7 @@
     <t>MOD-028-2</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM12-19-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM12-19-000
  </t>
   </si>
   <si>
@@ -3691,9 +3538,7 @@
     <t>To increase consistency and reliability in the development and documentation of transfer capability calculations for short-term use performed by entities using the Flowgate Methodology to support analysis and system operations.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM08-19-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM08-19-000
 Withdrawn. FERC approved NERC's petition to withdraw its request for approval (Order 729)</t>
   </si>
   <si>
@@ -3706,11 +3551,7 @@
     <t>MOD-030-3</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM15-13-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000
  </t>
   </si>
   <si>
@@ -3753,9 +3594,7 @@
     <t>To establish consistent modeling data requirements and reporting procedures for development of planning horizon cases necessary to support analysis of the reliability of the interconnected transmission system.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD14-5-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD14-5-000
 Please see the implementation plan for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -3765,20 +3604,16 @@
     <t>MOD-032-2</t>
   </si>
   <si>
-    <t>To establish consistent modeling data requirements and reporting _x000D_
-procedures for development of planning horizon cases necessary to _x000D_
-support analysis of the reliability of the interconnected transmission _x000D_
+    <t xml:space="preserve">To establish consistent modeling data requirements and reporting 
+procedures for development of planning horizon cases necessary to 
+support analysis of the reliability of the interconnected transmission 
 system.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD26-1-000_x000D_
-_x000D_
-_x000D_
-Additional Effective Date Details_x000D_
-Requirements R2, R3, and R4 - April 1, 2029_x000D_
-Entities shall not be required to comply with Requirements R2, R3, and R4 relating to revised Planning Coordinator and Transmission Planner data requirements and reporting procedures developed under MOD-032-2 Requirement R1 and Attachment 1 until 12 months after the effective date of Reliability Standard MOD-032-2._x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD26-1-000
+Additional Effective Date Details
+Requirements R2, R3, and R4 - April 1, 2029
+Entities shall not be required to comply with Requirements R2, R3, and R4 relating to revised Planning Coordinator and Transmission Planner data requirements and reporting procedures developed under MOD-032-2 Requirement R1 and Attachment 1 until 12 months after the effective date of Reliability Standard MOD-032-2.
 During the phased-in compliance period, entities shall continue to comply with Requirements R2, R3, and R4 related to Planning Coordinator / Transmission Planner data requirements and reporting procedures developed under MOD-032-1 Requirement R1 and Attachment 1 unless they are compliant with revised Planning Coordinator / Transmission Planner data requirements and reporting procedures under Reliability Standard MOD-032-2 Requirement R1.</t>
   </si>
   <si>
@@ -3800,7 +3635,7 @@
     <t>MOD-033-3</t>
   </si>
   <si>
-    <t>To establish a process for system model validation to facilitate achieving _x000D_
+    <t xml:space="preserve">To establish a process for system model validation to facilitate achieving 
 and maintaining model accuracy.</t>
   </si>
   <si>
@@ -3918,9 +3753,7 @@
     <t>Reliability Coordinators must have sufficient, competent staff to perform the Reliability Coordinator functions.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 PER-004-0 was never enforceable</t>
   </si>
   <si>
@@ -3987,9 +3820,7 @@
     <t>To ensure system protection is coordinated among operating entities.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 PRC-001-0 was never enforceable</t>
   </si>
   <si>
@@ -4029,9 +3860,7 @@
     <t>To ensure that Disturbance monitoring equipment is installed in a uniform manner to facilitate development of models and analyses of events.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 PRC-002-0 was never enforceable</t>
   </si>
   <si>
@@ -4047,9 +3876,7 @@
     <t>Ensure that Regional Reliability Organizations establish requirements for installation of Disturbance Monitoring Equipment (DME) and reporting of Disturbance data to facilitate analyses of events and verify system models.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000,  RM06-22-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000,  RM06-22-000
 This Standard was not approved by FERC in Order 693. See Standards Under Development page or Reliability Standards Development Plan for more information.</t>
   </si>
   <si>
@@ -4062,8 +3889,7 @@
     <t>To have adequate data available to facilitate analysis of Bulk Electric System (BES) Disturbances.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-4-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-4-000
 </t>
   </si>
   <si>
@@ -4079,7 +3905,7 @@
     <t>PRC-002-4</t>
   </si>
   <si>
-    <t>To have adequate data available to facilitate analysis of Bulk Electric_x000D_
+    <t xml:space="preserve">To have adequate data available to facilitate analysis of Bulk Electric
 System (BES) Disturbances.</t>
   </si>
   <si>
@@ -4188,8 +4014,7 @@
     <t>Identify and correct the causes of Misoperations of Protection Systems for Bulk Electric System (BES) Elements.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-14-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD14-14-000
 </t>
   </si>
   <si>
@@ -4199,16 +4024,14 @@
     <t>PRC-004-3(i)</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD14-14-001, RD15-3-001 and RD15-5-001_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD14-14-001, RD15-3-001 and RD15-5-001
 </t>
   </si>
   <si>
     <t>PRC-004-4</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000
 </t>
   </si>
   <si>
@@ -4221,8 +4044,7 @@
     <t>PRC-004-5</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-5-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD15-5-000
 </t>
   </si>
   <si>
@@ -4259,8 +4081,8 @@
     <t>Transmission Protection System Maintenance and Testing</t>
   </si>
   <si>
-    <t>To ensure all transmission protection system misoperations are analyzed for_x000D_
-cause and corrective action, and maintenance and testing programs are developed and_x000D_
+    <t xml:space="preserve">To ensure all transmission protection system misoperations are analyzed for
+cause and corrective action, and maintenance and testing programs are developed and
 implemented.</t>
   </si>
   <si>
@@ -4312,9 +4134,7 @@
     <t>PRC-005-2(ii)</t>
   </si>
   <si>
-    <t>Entities with newly classified “Remedial Action Scheme” (RAS) resulting from the application of the revised definition must be fully compliant with all Reliability Standards applicable RAS twenty-four (24) months from the Effective Date of the revised definition. PRC-004-WECC-2 replaces PRC-004-WECC-1. NERC filed a joint petition March 9, 2018 for approval of retirement of PRC-004-WECC-2._x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Entities with newly classified “Remedial Action Scheme” (RAS) resulting from the application of the revised definition must be fully compliant with all Reliability Standards applicable RAS twenty-four (24) months from the Effective Date of the revised definition. PRC-004-WECC-2 replaces PRC-004-WECC-1. NERC filed a joint petition March 9, 2018 for approval of retirement of PRC-004-WECC-2.
 Retired by PRC-005-6; PRC-005-2(ii) was never enforceable</t>
   </si>
   <si>
@@ -4339,9 +4159,7 @@
     <t>PRC-005-3(ii)</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM15-13-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-13-000
 Retired by PRC-005-6; PRC-005-3(ii) was never enforceable.</t>
   </si>
   <si>
@@ -4369,9 +4187,7 @@
     <t>PRC-005-6</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD16-2-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD16-2-000
 Due to the complex compliance requirements, please refer to the implementation plan for the phased-in details.</t>
   </si>
   <si>
@@ -4408,8 +4224,7 @@
     <t>PRC-006-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-2-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD15-2-000
 </t>
   </si>
   <si>
@@ -4464,10 +4279,8 @@
     <t>PRC-006-SERC-03</t>
   </si>
   <si>
-    <t>To establish consistent and coordinated requirements for the design,_x000D_
- _x000D_
-implementation, and analysis of automatic underfrequency load shedding (UFLS)_x000D_
- _x000D_
+    <t xml:space="preserve">To establish consistent and coordinated requirements for the design,
+implementation, and analysis of automatic underfrequency load shedding (UFLS)
 programs among all SERC applicable entities.</t>
   </si>
   <si>
@@ -4483,10 +4296,7 @@
     <t>To develop, coordinate and document requirements for automatic underfrequency load shedding (UFLS) programs to arrest declining frequency and assist recovery of frequency following underfrequency events.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD13-9-000_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD13-9-000
 </t>
   </si>
   <si>
@@ -4556,7 +4366,7 @@
     <t>Special Protection System Review Procedure</t>
   </si>
   <si>
-    <t>To ensure that all Special Protection Systems (SPS) are properly designed, meet_x000D_
+    <t xml:space="preserve">To ensure that all Special Protection Systems (SPS) are properly designed, meet
 performance requirements, and are coordinated with other protection systems. To ensure that maintenance and testing programs are developed and misoperations are analyzed and corrected.</t>
   </si>
   <si>
@@ -4608,8 +4418,8 @@
     <t>Special Protection System Assessment</t>
   </si>
   <si>
-    <t>To ensure that all Special Protection Systems (SPS) are properly designed, meet_x000D_
-performance requirements, and are coordinated with other protection systems. To ensure that_x000D_
+    <t xml:space="preserve">To ensure that all Special Protection Systems (SPS) are properly designed, meet
+performance requirements, and are coordinated with other protection systems. To ensure that
 maintenance and testing programs are developed and misoperations are analyzed and corrected.</t>
   </si>
   <si>
@@ -4682,9 +4492,7 @@
     <t>To verify coordination of generating unit Facility or synchronous condenser voltage regulating controls, limit functions, equipment capabilities and Protection System settings.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
 Please see the Implementation Plan for specific compliance dates and timeframes. The standard will become inactive 6/30/16.</t>
   </si>
   <si>
@@ -4694,9 +4502,7 @@
     <t>Coordination of Generating Unit or Plant Capabilities, Voltage Regulating Controls, and Protection</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD15-3-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000
 Please see the Implementation Plan for Version 1 for specific compliance dates and timeframes.</t>
   </si>
   <si>
@@ -4775,14 +4581,13 @@
     <t>PRC-023-6</t>
   </si>
   <si>
-    <t>Protective relay settings shall not limit transmission loadability; not interfere_x000D_
-with system operators’ ability to take remedial action to protect system reliability and; be_x000D_
-set to reliably detect all fault conditions and protect the electrical network from these_x000D_
+    <t xml:space="preserve">Protective relay settings shall not limit transmission loadability; not interfere
+with system operators’ ability to take remedial action to protect system reliability and; be
+set to reliably detect all fault conditions and protect the electrical network from these
 faults.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD23-5-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD23-5-000
 </t>
   </si>
   <si>
@@ -4798,16 +4603,14 @@
     <t>Ensure Generator Owners set their generator protective relays such that generating units remain connected during defined frequency and voltage excursions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-16-000
 </t>
   </si>
   <si>
     <t>PRC-024-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD15-3-000
 </t>
   </si>
   <si>
@@ -4835,9 +4638,7 @@
     <t>To assure that protection of synchronous generators, type 1 and type 2 wind resources, and synchronous condensers do not cause tripping during defined frequency and voltage excursions in support of the Bulk Power System (BPS).</t>
   </si>
   <si>
-    <t>Docket No. RM25-3-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Docket No. RM25-3-000
 See Implementation Plan for more information on effective/compliance dates</t>
   </si>
   <si>
@@ -4853,11 +4654,7 @@
     <t>To set load-responsive protective relays associated with generation Facilities at a level to prevent unnecessary tripping of generators during a system disturbance for conditions that do not pose a risk of damage to the associated equipment.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM13-19-000_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM13-19-000
 See Implementation Plan. For applicable relays where the entity has determined replacement or removal is not necessary, the entity shall be compliant by 10/1/2019. For applicable relays where the entity has determined replacement or removal is necessary, the entity shall be compliant by 10/1/2021.</t>
   </si>
   <si>
@@ -4879,8 +4676,7 @@
     <t>To ensure that load-responsive protective relays are expected to not trip in response to stable power swings during non-Fault conditions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-8-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-8-000
 </t>
   </si>
   <si>
@@ -4926,9 +4722,7 @@
     <t>Identify, analyze, and mitigate unexpected Inverter-Based Resource (IBR) change of power output.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD25-3-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD25-3-000
 See Implementation Plan for more effective/compliance date information</t>
   </si>
   <si>
@@ -5091,8 +4885,7 @@
     <t>To ensure that the Transmission Operator and Balancing Authority have data needed to fulfill their operational and planning responsibilities.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM15-16-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM15-16-000
 </t>
   </si>
   <si>
@@ -5108,9 +4901,7 @@
     <t>Transmission Operator and Balancing Authority Data and Information  Specification and Collection</t>
   </si>
   <si>
-    <t> To ensure that each Transmission Operator and Balancing Authority has the data and information it needs to plan, monitor, and assess the operation of its_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve"> To ensure that each Transmission Operator and Balancing Authority has the data and information it needs to plan, monitor, and assess the operation of its
   Transmission Operator Area or Balancing Authority Area.</t>
   </si>
   <si>
@@ -5132,9 +4923,9 @@
     <t>TOP-003-8</t>
   </si>
   <si>
-    <t>To ensure that each Transmission Operator and Balancing Authority has _x000D_
-the data and information it needs to plan, monitor, and assess the _x000D_
-operation of its Transmission Operator Area or Balancing Authority _x000D_
+    <t xml:space="preserve">To ensure that each Transmission Operator and Balancing Authority has 
+the data and information it needs to plan, monitor, and assess the 
+operation of its Transmission Operator Area or Balancing Authority 
 Area.</t>
   </si>
   <si>
@@ -5144,9 +4935,7 @@
     <t>To ensure that the transmission system is operated so that instability, uncontrolled separation, or cascading outages will not occur as a result of the most severe single Contingency and specified multiple Contingencies.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 TOP-004-0 was never enforceable</t>
   </si>
   <si>
@@ -5195,9 +4984,7 @@
     <t>To ensure critical reliability parameters are monitored in real-time.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 TOP-006-0 was never enforceable</t>
   </si>
   <si>
@@ -5270,8 +5057,7 @@
     <t>Real-time Reliability Monitoring and Analysis Capabilities</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD16-6-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD16-6-000
 </t>
   </si>
   <si>
@@ -5413,8 +5199,7 @@
     <t>TPL-003-0b</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD13-8-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD13-8-000
 </t>
   </si>
   <si>
@@ -5499,8 +5284,7 @@
     <t>TPL-007-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RM18-8-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM18-8-000
 </t>
   </si>
   <si>
@@ -5513,9 +5297,7 @@
     <t>TPL-007-4</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD20-3-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD20-3-000
 This Variance shall be applicable in those Canadian jurisdictions where the Variance has been approved for use by the applicable governmental authority or has otherwise become effective in the jurisdiction.</t>
   </si>
   <si>
@@ -5549,9 +5331,7 @@
     <t>To ensure voltage levels, reactive flows, and reactive resources are monitored, controlled, and maintained within limits in real time to protect equipment and the reliable operation of the Interconnection.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM06-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM06-16-000
 VAR-001-0 was never enforceable</t>
   </si>
   <si>
@@ -5594,8 +5374,7 @@
     <t>VAR-001-4.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000
 </t>
   </si>
   <si>
@@ -5611,9 +5390,7 @@
     <t>VAR-001-6</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RM19-16-000_x000D_
-_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RM19-16-000
 Standard withdrawn on 5/14/2020.</t>
   </si>
   <si>
@@ -5662,8 +5439,7 @@
     <t>VAR-002-4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD17-7-000
 </t>
   </si>
   <si>
@@ -5700,8 +5476,7 @@
     <t>To ensure the Western Interconnection is operated in a coordinated manner under normal and abnormal conditions by establishing the performance criteria for WECC power system stabilizers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Filing/Order Docket No. RD17-5-000_x000D_
-_x000D_
+    <t xml:space="preserve">Filing/Order Docket No. RD17-5-000
 </t>
   </si>
   <si>
@@ -5741,11 +5516,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m\/d\/yyyy"/>
+    <numFmt numFmtId="172" formatCode="m\/d\/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -5753,19 +5528,19 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF333333"/>
+      <color rgb="00333333"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
       <sz val="9"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="000000FF"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -5774,7 +5549,10 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="00000000"/>
+        <bgColor rgb="00000000"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -5805,31 +5583,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3877A6"/>
+        <color rgb="003877A6"/>
       </left>
       <right style="thin">
-        <color rgb="FF3877A6"/>
+        <color rgb="003877A6"/>
       </right>
       <top style="thin">
-        <color rgb="FF3877A6"/>
+        <color rgb="003877A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFA5A5B1"/>
+        <color rgb="00A5A5B1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFEBEBEB"/>
+        <color rgb="00EBEBEB"/>
       </left>
       <right style="thin">
-        <color rgb="FFEBEBEB"/>
+        <color rgb="00EBEBEB"/>
       </right>
       <top style="thin">
-        <color rgb="FFEBEBEB"/>
+        <color rgb="00EBEBEB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFEBEBEB"/>
+        <color rgb="00EBEBEB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5837,428 +5615,108 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R650"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="3" width="24.08984375" customWidth="1"/>
-    <col min="4" max="4" width="47.90625" customWidth="1"/>
-    <col min="5" max="7" width="10.7265625" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="49.1796875" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" customWidth="1"/>
-    <col min="17" max="17" width="15.36328125" customWidth="1"/>
-    <col min="18" max="18" width="16.54296875" customWidth="1"/>
-    <col min="19" max="19" width="4.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.9715986666667" customWidth="1"/>
+    <col min="2" max="3" width="24.1017" customWidth="1"/>
+    <col min="4" max="4" width="47.9139986666667" customWidth="1"/>
+    <col min="5" max="7" width="10.7163133333333" customWidth="1"/>
+    <col min="8" max="8" width="12.5491986666667" customWidth="1"/>
+    <col min="9" max="9" width="10.7163133333333" customWidth="1"/>
+    <col min="10" max="10" width="16.1161" customWidth="1"/>
+    <col min="11" max="11" width="10.7163133333333" customWidth="1"/>
+    <col min="12" max="12" width="19.002324" customWidth="1"/>
+    <col min="13" max="13" width="49.1993" customWidth="1"/>
+    <col min="14" max="16" width="14.1158973333333" customWidth="1"/>
+    <col min="17" max="17" width="15.4011986666667" customWidth="1"/>
+    <col min="18" max="18" width="16.5419986666667" customWidth="1"/>
+    <col min="19" max="19" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="37.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" ht="55.9965" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6314,7 +5772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
@@ -6356,7 +5814,7 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
     </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -6398,7 +5856,7 @@
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
     </row>
-    <row r="4" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
@@ -6440,7 +5898,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
@@ -6484,7 +5942,7 @@
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
@@ -6530,7 +5988,7 @@
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
     </row>
-    <row r="7" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
@@ -6574,7 +6032,7 @@
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
     </row>
-    <row r="8" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
@@ -6618,7 +6076,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A9" s="11" t="s">
         <v>18</v>
       </c>
@@ -6660,7 +6118,7 @@
       <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
     </row>
-    <row r="10" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -6704,7 +6162,7 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>18</v>
       </c>
@@ -6742,7 +6200,7 @@
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
@@ -6784,7 +6242,7 @@
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
     </row>
-    <row r="13" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A13" s="11" t="s">
         <v>18</v>
       </c>
@@ -6826,7 +6284,7 @@
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
     </row>
-    <row r="14" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A14" s="6" t="s">
         <v>30</v>
       </c>
@@ -6874,7 +6332,7 @@
       </c>
       <c r="R14" s="7"/>
     </row>
-    <row r="15" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6910,7 +6368,7 @@
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
     </row>
-    <row r="16" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
@@ -6954,7 +6412,7 @@
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A17" s="11" t="s">
         <v>18</v>
       </c>
@@ -6998,7 +6456,7 @@
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
     </row>
-    <row r="18" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
@@ -7042,7 +6500,7 @@
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
     </row>
-    <row r="19" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>18</v>
       </c>
@@ -7084,7 +6542,7 @@
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
     </row>
-    <row r="20" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
@@ -7126,7 +6584,7 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
     </row>
-    <row r="21" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>18</v>
       </c>
@@ -7168,7 +6626,7 @@
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
-    <row r="22" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>18</v>
       </c>
@@ -7210,7 +6668,7 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A23" s="11" t="s">
         <v>18</v>
       </c>
@@ -7250,7 +6708,7 @@
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
     </row>
-    <row r="24" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A24" s="6" t="s">
         <v>18</v>
       </c>
@@ -7294,7 +6752,7 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A25" s="11" t="s">
         <v>18</v>
       </c>
@@ -7340,7 +6798,7 @@
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
     </row>
-    <row r="26" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A26" s="6" t="s">
         <v>30</v>
       </c>
@@ -7386,7 +6844,7 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
     </row>
-    <row r="27" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A27" s="11" t="s">
         <v>18</v>
       </c>
@@ -7430,7 +6888,7 @@
       <c r="Q27" s="12"/>
       <c r="R27" s="12"/>
     </row>
-    <row r="28" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A28" s="6" t="s">
         <v>18</v>
       </c>
@@ -7466,7 +6924,7 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
     </row>
-    <row r="29" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A29" s="11" t="s">
         <v>18</v>
       </c>
@@ -7510,7 +6968,7 @@
       <c r="Q29" s="12"/>
       <c r="R29" s="12"/>
     </row>
-    <row r="30" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>18</v>
       </c>
@@ -7554,7 +7012,7 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
     </row>
-    <row r="31" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A31" s="11" t="s">
         <v>18</v>
       </c>
@@ -7598,7 +7056,7 @@
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
     </row>
-    <row r="32" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>30</v>
       </c>
@@ -7642,7 +7100,7 @@
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
     </row>
-    <row r="33" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A33" s="11" t="s">
         <v>18</v>
       </c>
@@ -7684,7 +7142,7 @@
       <c r="Q33" s="12"/>
       <c r="R33" s="12"/>
     </row>
-    <row r="34" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>18</v>
       </c>
@@ -7726,7 +7184,7 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
     </row>
-    <row r="35" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A35" s="11" t="s">
         <v>18</v>
       </c>
@@ -7770,7 +7228,7 @@
       <c r="Q35" s="12"/>
       <c r="R35" s="12"/>
     </row>
-    <row r="36" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>18</v>
       </c>
@@ -7806,7 +7264,7 @@
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
-    <row r="37" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>18</v>
       </c>
@@ -7848,7 +7306,7 @@
       <c r="Q37" s="12"/>
       <c r="R37" s="12"/>
     </row>
-    <row r="38" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A38" s="6" t="s">
         <v>30</v>
       </c>
@@ -7896,7 +7354,7 @@
       </c>
       <c r="R38" s="7"/>
     </row>
-    <row r="39" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A39" s="11" t="s">
         <v>18</v>
       </c>
@@ -7932,7 +7390,7 @@
       <c r="Q39" s="12"/>
       <c r="R39" s="12"/>
     </row>
-    <row r="40" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A40" s="6" t="s">
         <v>18</v>
       </c>
@@ -7974,7 +7432,7 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
     </row>
-    <row r="41" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A41" s="11" t="s">
         <v>18</v>
       </c>
@@ -8016,7 +7474,7 @@
       <c r="Q41" s="12"/>
       <c r="R41" s="12"/>
     </row>
-    <row r="42" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
@@ -8060,7 +7518,7 @@
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
     </row>
-    <row r="43" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>139</v>
       </c>
@@ -8106,7 +7564,7 @@
       </c>
       <c r="R43" s="12"/>
     </row>
-    <row r="44" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A44" s="6" t="s">
         <v>145</v>
       </c>
@@ -8144,7 +7602,7 @@
       </c>
       <c r="R44" s="7"/>
     </row>
-    <row r="45" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A45" s="11" t="s">
         <v>30</v>
       </c>
@@ -8188,7 +7646,7 @@
       <c r="Q45" s="12"/>
       <c r="R45" s="12"/>
     </row>
-    <row r="46" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>18</v>
       </c>
@@ -8230,7 +7688,7 @@
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
     </row>
-    <row r="47" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>18</v>
       </c>
@@ -8272,7 +7730,7 @@
       <c r="Q47" s="12"/>
       <c r="R47" s="12"/>
     </row>
-    <row r="48" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A48" s="6" t="s">
         <v>18</v>
       </c>
@@ -8308,7 +7766,7 @@
       <c r="Q48" s="7"/>
       <c r="R48" s="7"/>
     </row>
-    <row r="49" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A49" s="11" t="s">
         <v>18</v>
       </c>
@@ -8350,7 +7808,7 @@
       <c r="Q49" s="12"/>
       <c r="R49" s="12"/>
     </row>
-    <row r="50" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A50" s="6" t="s">
         <v>18</v>
       </c>
@@ -8392,7 +7850,7 @@
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
     </row>
-    <row r="51" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>18</v>
       </c>
@@ -8436,7 +7894,7 @@
       <c r="Q51" s="12"/>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="1:18" s="1" customFormat="1" ht="163.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" s="1" customFormat="1" ht="245.8513" customHeight="1">
       <c r="A52" s="6" t="s">
         <v>18</v>
       </c>
@@ -8478,7 +7936,7 @@
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
     </row>
-    <row r="53" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>18</v>
       </c>
@@ -8520,7 +7978,7 @@
       <c r="Q53" s="12"/>
       <c r="R53" s="12"/>
     </row>
-    <row r="54" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A54" s="6" t="s">
         <v>18</v>
       </c>
@@ -8564,7 +8022,7 @@
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
     </row>
-    <row r="55" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A55" s="11" t="s">
         <v>18</v>
       </c>
@@ -8600,7 +8058,7 @@
       <c r="Q55" s="12"/>
       <c r="R55" s="12"/>
     </row>
-    <row r="56" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A56" s="6" t="s">
         <v>18</v>
       </c>
@@ -8634,7 +8092,7 @@
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
     </row>
-    <row r="57" spans="1:18" s="1" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" s="1" customFormat="1" ht="278.3826" customHeight="1">
       <c r="A57" s="11" t="s">
         <v>18</v>
       </c>
@@ -8670,7 +8128,7 @@
       <c r="Q57" s="12"/>
       <c r="R57" s="12"/>
     </row>
-    <row r="58" spans="1:18" s="1" customFormat="1" ht="185.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" s="1" customFormat="1" ht="278.3826" customHeight="1">
       <c r="A58" s="6" t="s">
         <v>18</v>
       </c>
@@ -8706,7 +8164,7 @@
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
     </row>
-    <row r="59" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A59" s="11" t="s">
         <v>18</v>
       </c>
@@ -8750,7 +8208,7 @@
       <c r="Q59" s="12"/>
       <c r="R59" s="12"/>
     </row>
-    <row r="60" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A60" s="6" t="s">
         <v>18</v>
       </c>
@@ -8788,7 +8246,7 @@
       <c r="Q60" s="7"/>
       <c r="R60" s="7"/>
     </row>
-    <row r="61" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A61" s="11" t="s">
         <v>18</v>
       </c>
@@ -8826,7 +8284,7 @@
       <c r="Q61" s="12"/>
       <c r="R61" s="12"/>
     </row>
-    <row r="62" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A62" s="6" t="s">
         <v>18</v>
       </c>
@@ -8870,7 +8328,7 @@
       <c r="Q62" s="7"/>
       <c r="R62" s="7"/>
     </row>
-    <row r="63" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A63" s="11" t="s">
         <v>30</v>
       </c>
@@ -8918,7 +8376,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A64" s="6" t="s">
         <v>18</v>
       </c>
@@ -8956,7 +8414,7 @@
       <c r="Q64" s="7"/>
       <c r="R64" s="7"/>
     </row>
-    <row r="65" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A65" s="11" t="s">
         <v>145</v>
       </c>
@@ -8996,7 +8454,7 @@
       </c>
       <c r="R65" s="12"/>
     </row>
-    <row r="66" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A66" s="6" t="s">
         <v>145</v>
       </c>
@@ -9036,7 +8494,7 @@
       </c>
       <c r="R66" s="7"/>
     </row>
-    <row r="67" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A67" s="11" t="s">
         <v>18</v>
       </c>
@@ -9078,7 +8536,7 @@
       <c r="Q67" s="12"/>
       <c r="R67" s="12"/>
     </row>
-    <row r="68" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A68" s="6" t="s">
         <v>145</v>
       </c>
@@ -9118,7 +8576,7 @@
       </c>
       <c r="R68" s="7"/>
     </row>
-    <row r="69" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A69" s="11" t="s">
         <v>145</v>
       </c>
@@ -9158,7 +8616,7 @@
       </c>
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A70" s="6" t="s">
         <v>18</v>
       </c>
@@ -9200,7 +8658,7 @@
       <c r="Q70" s="7"/>
       <c r="R70" s="7"/>
     </row>
-    <row r="71" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A71" s="11" t="s">
         <v>18</v>
       </c>
@@ -9244,7 +8702,7 @@
       <c r="Q71" s="12"/>
       <c r="R71" s="12"/>
     </row>
-    <row r="72" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A72" s="6" t="s">
         <v>18</v>
       </c>
@@ -9278,7 +8736,7 @@
       <c r="Q72" s="7"/>
       <c r="R72" s="7"/>
     </row>
-    <row r="73" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A73" s="11" t="s">
         <v>18</v>
       </c>
@@ -9322,7 +8780,7 @@
       <c r="Q73" s="12"/>
       <c r="R73" s="12"/>
     </row>
-    <row r="74" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A74" s="6" t="s">
         <v>18</v>
       </c>
@@ -9356,7 +8814,7 @@
       <c r="Q74" s="7"/>
       <c r="R74" s="7"/>
     </row>
-    <row r="75" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A75" s="11" t="s">
         <v>18</v>
       </c>
@@ -9398,7 +8856,7 @@
       <c r="Q75" s="12"/>
       <c r="R75" s="12"/>
     </row>
-    <row r="76" spans="1:18" s="1" customFormat="1" ht="92.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" s="1" customFormat="1" ht="138.1247" customHeight="1">
       <c r="A76" s="6" t="s">
         <v>18</v>
       </c>
@@ -9444,7 +8902,7 @@
       <c r="Q76" s="7"/>
       <c r="R76" s="7"/>
     </row>
-    <row r="77" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A77" s="11" t="s">
         <v>18</v>
       </c>
@@ -9488,7 +8946,7 @@
       <c r="Q77" s="12"/>
       <c r="R77" s="12"/>
     </row>
-    <row r="78" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A78" s="6" t="s">
         <v>30</v>
       </c>
@@ -9536,7 +8994,7 @@
       <c r="Q78" s="7"/>
       <c r="R78" s="7"/>
     </row>
-    <row r="79" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A79" s="11" t="s">
         <v>139</v>
       </c>
@@ -9584,7 +9042,7 @@
       </c>
       <c r="R79" s="12"/>
     </row>
-    <row r="80" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A80" s="6" t="s">
         <v>18</v>
       </c>
@@ -9626,7 +9084,7 @@
       <c r="Q80" s="7"/>
       <c r="R80" s="7"/>
     </row>
-    <row r="81" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A81" s="11" t="s">
         <v>18</v>
       </c>
@@ -9668,7 +9126,7 @@
       <c r="Q81" s="12"/>
       <c r="R81" s="12"/>
     </row>
-    <row r="82" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A82" s="6" t="s">
         <v>18</v>
       </c>
@@ -9712,7 +9170,7 @@
       <c r="Q82" s="7"/>
       <c r="R82" s="7"/>
     </row>
-    <row r="83" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A83" s="11" t="s">
         <v>18</v>
       </c>
@@ -9756,7 +9214,7 @@
       <c r="Q83" s="12"/>
       <c r="R83" s="12"/>
     </row>
-    <row r="84" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>18</v>
       </c>
@@ -9798,7 +9256,7 @@
       <c r="Q84" s="7"/>
       <c r="R84" s="7"/>
     </row>
-    <row r="85" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A85" s="11" t="s">
         <v>18</v>
       </c>
@@ -9842,7 +9300,7 @@
       <c r="Q85" s="12"/>
       <c r="R85" s="12"/>
     </row>
-    <row r="86" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A86" s="6" t="s">
         <v>18</v>
       </c>
@@ -9878,7 +9336,7 @@
       <c r="Q86" s="7"/>
       <c r="R86" s="7"/>
     </row>
-    <row r="87" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A87" s="11" t="s">
         <v>18</v>
       </c>
@@ -9920,7 +9378,7 @@
       <c r="Q87" s="12"/>
       <c r="R87" s="12"/>
     </row>
-    <row r="88" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A88" s="6" t="s">
         <v>18</v>
       </c>
@@ -9966,7 +9424,7 @@
       <c r="Q88" s="7"/>
       <c r="R88" s="7"/>
     </row>
-    <row r="89" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A89" s="11" t="s">
         <v>30</v>
       </c>
@@ -10016,7 +9474,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="90" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A90" s="6" t="s">
         <v>145</v>
       </c>
@@ -10056,7 +9514,7 @@
       </c>
       <c r="R90" s="7"/>
     </row>
-    <row r="91" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A91" s="11" t="s">
         <v>18</v>
       </c>
@@ -10098,7 +9556,7 @@
       <c r="Q91" s="12"/>
       <c r="R91" s="12"/>
     </row>
-    <row r="92" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A92" s="6" t="s">
         <v>18</v>
       </c>
@@ -10132,7 +9590,7 @@
       <c r="Q92" s="7"/>
       <c r="R92" s="7"/>
     </row>
-    <row r="93" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A93" s="11" t="s">
         <v>18</v>
       </c>
@@ -10174,7 +9632,7 @@
       <c r="Q93" s="12"/>
       <c r="R93" s="12"/>
     </row>
-    <row r="94" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A94" s="6" t="s">
         <v>18</v>
       </c>
@@ -10214,7 +9672,7 @@
       <c r="Q94" s="7"/>
       <c r="R94" s="7"/>
     </row>
-    <row r="95" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A95" s="11" t="s">
         <v>18</v>
       </c>
@@ -10256,7 +9714,7 @@
       <c r="Q95" s="12"/>
       <c r="R95" s="12"/>
     </row>
-    <row r="96" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A96" s="6" t="s">
         <v>18</v>
       </c>
@@ -10300,7 +9758,7 @@
       <c r="Q96" s="7"/>
       <c r="R96" s="7"/>
     </row>
-    <row r="97" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A97" s="11" t="s">
         <v>18</v>
       </c>
@@ -10344,7 +9802,7 @@
       <c r="Q97" s="12"/>
       <c r="R97" s="12"/>
     </row>
-    <row r="98" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A98" s="6" t="s">
         <v>18</v>
       </c>
@@ -10388,7 +9846,7 @@
       <c r="Q98" s="7"/>
       <c r="R98" s="7"/>
     </row>
-    <row r="99" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A99" s="11" t="s">
         <v>18</v>
       </c>
@@ -10432,7 +9890,7 @@
       <c r="Q99" s="12"/>
       <c r="R99" s="12"/>
     </row>
-    <row r="100" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A100" s="6" t="s">
         <v>30</v>
       </c>
@@ -10480,7 +9938,7 @@
       </c>
       <c r="R100" s="7"/>
     </row>
-    <row r="101" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A101" s="11" t="s">
         <v>145</v>
       </c>
@@ -10520,7 +9978,7 @@
       </c>
       <c r="R101" s="12"/>
     </row>
-    <row r="102" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A102" s="6" t="s">
         <v>18</v>
       </c>
@@ -10562,7 +10020,7 @@
       <c r="Q102" s="7"/>
       <c r="R102" s="7"/>
     </row>
-    <row r="103" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A103" s="11" t="s">
         <v>18</v>
       </c>
@@ -10596,7 +10054,7 @@
       <c r="Q103" s="12"/>
       <c r="R103" s="12"/>
     </row>
-    <row r="104" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A104" s="6" t="s">
         <v>18</v>
       </c>
@@ -10630,7 +10088,7 @@
       <c r="Q104" s="7"/>
       <c r="R104" s="7"/>
     </row>
-    <row r="105" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A105" s="11" t="s">
         <v>18</v>
       </c>
@@ -10664,7 +10122,7 @@
       <c r="Q105" s="12"/>
       <c r="R105" s="12"/>
     </row>
-    <row r="106" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A106" s="6" t="s">
         <v>18</v>
       </c>
@@ -10706,7 +10164,7 @@
       <c r="Q106" s="7"/>
       <c r="R106" s="7"/>
     </row>
-    <row r="107" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A107" s="11" t="s">
         <v>18</v>
       </c>
@@ -10748,7 +10206,7 @@
       <c r="Q107" s="12"/>
       <c r="R107" s="12"/>
     </row>
-    <row r="108" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A108" s="6" t="s">
         <v>18</v>
       </c>
@@ -10786,7 +10244,7 @@
       <c r="Q108" s="7"/>
       <c r="R108" s="7"/>
     </row>
-    <row r="109" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A109" s="11" t="s">
         <v>18</v>
       </c>
@@ -10826,7 +10284,7 @@
       <c r="Q109" s="12"/>
       <c r="R109" s="12"/>
     </row>
-    <row r="110" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A110" s="6" t="s">
         <v>18</v>
       </c>
@@ -10866,7 +10324,7 @@
       <c r="Q110" s="7"/>
       <c r="R110" s="7"/>
     </row>
-    <row r="111" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A111" s="11" t="s">
         <v>18</v>
       </c>
@@ -10908,7 +10366,7 @@
       <c r="Q111" s="12"/>
       <c r="R111" s="12"/>
     </row>
-    <row r="112" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A112" s="6" t="s">
         <v>18</v>
       </c>
@@ -10952,7 +10410,7 @@
       <c r="Q112" s="7"/>
       <c r="R112" s="7"/>
     </row>
-    <row r="113" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A113" s="11" t="s">
         <v>18</v>
       </c>
@@ -10990,7 +10448,7 @@
       <c r="Q113" s="12"/>
       <c r="R113" s="12"/>
     </row>
-    <row r="114" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A114" s="6" t="s">
         <v>18</v>
       </c>
@@ -11034,7 +10492,7 @@
       <c r="Q114" s="7"/>
       <c r="R114" s="7"/>
     </row>
-    <row r="115" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A115" s="11" t="s">
         <v>18</v>
       </c>
@@ -11072,7 +10530,7 @@
       <c r="Q115" s="12"/>
       <c r="R115" s="12"/>
     </row>
-    <row r="116" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A116" s="6" t="s">
         <v>18</v>
       </c>
@@ -11114,7 +10572,7 @@
       <c r="Q116" s="7"/>
       <c r="R116" s="7"/>
     </row>
-    <row r="117" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A117" s="11" t="s">
         <v>30</v>
       </c>
@@ -11160,11 +10618,11 @@
         <v>34</v>
       </c>
       <c r="Q117" s="12"/>
-      <c r="R117" s="20" t="s">
+      <c r="R117" s="21" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="118" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A118" s="6" t="s">
         <v>145</v>
       </c>
@@ -11204,7 +10662,7 @@
       </c>
       <c r="R118" s="7"/>
     </row>
-    <row r="119" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A119" s="11" t="s">
         <v>18</v>
       </c>
@@ -11246,7 +10704,7 @@
       <c r="Q119" s="12"/>
       <c r="R119" s="12"/>
     </row>
-    <row r="120" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A120" s="6" t="s">
         <v>18</v>
       </c>
@@ -11286,7 +10744,7 @@
       <c r="Q120" s="7"/>
       <c r="R120" s="7"/>
     </row>
-    <row r="121" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A121" s="11" t="s">
         <v>18</v>
       </c>
@@ -11328,7 +10786,7 @@
       <c r="Q121" s="12"/>
       <c r="R121" s="12"/>
     </row>
-    <row r="122" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A122" s="6" t="s">
         <v>18</v>
       </c>
@@ -11362,7 +10820,7 @@
       <c r="Q122" s="7"/>
       <c r="R122" s="7"/>
     </row>
-    <row r="123" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A123" s="11" t="s">
         <v>18</v>
       </c>
@@ -11406,7 +10864,7 @@
       <c r="Q123" s="12"/>
       <c r="R123" s="12"/>
     </row>
-    <row r="124" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A124" s="6" t="s">
         <v>18</v>
       </c>
@@ -11440,7 +10898,7 @@
       <c r="Q124" s="7"/>
       <c r="R124" s="7"/>
     </row>
-    <row r="125" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A125" s="11" t="s">
         <v>18</v>
       </c>
@@ -11484,7 +10942,7 @@
       <c r="Q125" s="12"/>
       <c r="R125" s="12"/>
     </row>
-    <row r="126" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A126" s="6" t="s">
         <v>18</v>
       </c>
@@ -11518,7 +10976,7 @@
       <c r="Q126" s="7"/>
       <c r="R126" s="7"/>
     </row>
-    <row r="127" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A127" s="11" t="s">
         <v>18</v>
       </c>
@@ -11560,7 +11018,7 @@
       <c r="Q127" s="12"/>
       <c r="R127" s="12"/>
     </row>
-    <row r="128" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A128" s="6" t="s">
         <v>30</v>
       </c>
@@ -11610,7 +11068,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="129" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A129" s="11" t="s">
         <v>145</v>
       </c>
@@ -11650,7 +11108,7 @@
       </c>
       <c r="R129" s="12"/>
     </row>
-    <row r="130" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A130" s="6" t="s">
         <v>18</v>
       </c>
@@ -11692,7 +11150,7 @@
       <c r="Q130" s="7"/>
       <c r="R130" s="7"/>
     </row>
-    <row r="131" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A131" s="11" t="s">
         <v>18</v>
       </c>
@@ -11734,7 +11192,7 @@
       <c r="Q131" s="12"/>
       <c r="R131" s="12"/>
     </row>
-    <row r="132" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A132" s="6" t="s">
         <v>18</v>
       </c>
@@ -11778,7 +11236,7 @@
       <c r="Q132" s="7"/>
       <c r="R132" s="7"/>
     </row>
-    <row r="133" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A133" s="11" t="s">
         <v>18</v>
       </c>
@@ -11820,7 +11278,7 @@
       <c r="Q133" s="12"/>
       <c r="R133" s="12"/>
     </row>
-    <row r="134" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A134" s="6" t="s">
         <v>18</v>
       </c>
@@ -11866,7 +11324,7 @@
       <c r="Q134" s="7"/>
       <c r="R134" s="7"/>
     </row>
-    <row r="135" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A135" s="11" t="s">
         <v>30</v>
       </c>
@@ -11914,7 +11372,7 @@
       </c>
       <c r="R135" s="12"/>
     </row>
-    <row r="136" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A136" s="6" t="s">
         <v>145</v>
       </c>
@@ -11954,7 +11412,7 @@
       </c>
       <c r="R136" s="7"/>
     </row>
-    <row r="137" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A137" s="11" t="s">
         <v>18</v>
       </c>
@@ -11996,7 +11454,7 @@
       <c r="Q137" s="12"/>
       <c r="R137" s="12"/>
     </row>
-    <row r="138" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A138" s="6" t="s">
         <v>18</v>
       </c>
@@ -12038,7 +11496,7 @@
       <c r="Q138" s="7"/>
       <c r="R138" s="7"/>
     </row>
-    <row r="139" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A139" s="11" t="s">
         <v>18</v>
       </c>
@@ -12082,7 +11540,7 @@
       <c r="Q139" s="12"/>
       <c r="R139" s="12"/>
     </row>
-    <row r="140" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A140" s="6" t="s">
         <v>18</v>
       </c>
@@ -12124,7 +11582,7 @@
       <c r="Q140" s="7"/>
       <c r="R140" s="7"/>
     </row>
-    <row r="141" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A141" s="11" t="s">
         <v>18</v>
       </c>
@@ -12166,7 +11624,7 @@
       <c r="Q141" s="12"/>
       <c r="R141" s="12"/>
     </row>
-    <row r="142" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A142" s="6" t="s">
         <v>30</v>
       </c>
@@ -12216,7 +11674,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="143" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A143" s="11" t="s">
         <v>145</v>
       </c>
@@ -12256,7 +11714,7 @@
       </c>
       <c r="R143" s="12"/>
     </row>
-    <row r="144" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A144" s="6" t="s">
         <v>18</v>
       </c>
@@ -12298,7 +11756,7 @@
       <c r="Q144" s="7"/>
       <c r="R144" s="7"/>
     </row>
-    <row r="145" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A145" s="11" t="s">
         <v>18</v>
       </c>
@@ -12342,7 +11800,7 @@
       <c r="Q145" s="12"/>
       <c r="R145" s="12"/>
     </row>
-    <row r="146" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A146" s="6" t="s">
         <v>18</v>
       </c>
@@ -12386,7 +11844,7 @@
       <c r="Q146" s="7"/>
       <c r="R146" s="7"/>
     </row>
-    <row r="147" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A147" s="11" t="s">
         <v>30</v>
       </c>
@@ -12436,7 +11894,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="148" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A148" s="6" t="s">
         <v>145</v>
       </c>
@@ -12476,7 +11934,7 @@
       </c>
       <c r="R148" s="7"/>
     </row>
-    <row r="149" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A149" s="11" t="s">
         <v>18</v>
       </c>
@@ -12518,7 +11976,7 @@
       <c r="Q149" s="12"/>
       <c r="R149" s="12"/>
     </row>
-    <row r="150" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A150" s="6" t="s">
         <v>18</v>
       </c>
@@ -12564,7 +12022,7 @@
       <c r="Q150" s="7"/>
       <c r="R150" s="7"/>
     </row>
-    <row r="151" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A151" s="11" t="s">
         <v>30</v>
       </c>
@@ -12614,7 +12072,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="152" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A152" s="6" t="s">
         <v>145</v>
       </c>
@@ -12654,7 +12112,7 @@
       </c>
       <c r="R152" s="7"/>
     </row>
-    <row r="153" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A153" s="11" t="s">
         <v>30</v>
       </c>
@@ -12706,7 +12164,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="154" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A154" s="6" t="s">
         <v>139</v>
       </c>
@@ -12754,7 +12212,7 @@
       </c>
       <c r="R154" s="7"/>
     </row>
-    <row r="155" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A155" s="11" t="s">
         <v>18</v>
       </c>
@@ -12798,7 +12256,7 @@
       <c r="Q155" s="12"/>
       <c r="R155" s="12"/>
     </row>
-    <row r="156" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A156" s="6" t="s">
         <v>30</v>
       </c>
@@ -12844,11 +12302,11 @@
       <c r="Q156" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R156" s="21" t="s">
+      <c r="R156" s="23" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="157" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A157" s="11" t="s">
         <v>145</v>
       </c>
@@ -12888,7 +12346,7 @@
       </c>
       <c r="R157" s="12"/>
     </row>
-    <row r="158" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A158" s="6" t="s">
         <v>18</v>
       </c>
@@ -12932,7 +12390,7 @@
       <c r="Q158" s="7"/>
       <c r="R158" s="7"/>
     </row>
-    <row r="159" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A159" s="11" t="s">
         <v>18</v>
       </c>
@@ -12978,7 +12436,7 @@
       <c r="Q159" s="12"/>
       <c r="R159" s="12"/>
     </row>
-    <row r="160" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>30</v>
       </c>
@@ -13026,7 +12484,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="161" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A161" s="11" t="s">
         <v>139</v>
       </c>
@@ -13072,7 +12530,7 @@
       </c>
       <c r="R161" s="12"/>
     </row>
-    <row r="162" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A162" s="6" t="s">
         <v>18</v>
       </c>
@@ -13108,7 +12566,7 @@
       <c r="Q162" s="7"/>
       <c r="R162" s="7"/>
     </row>
-    <row r="163" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A163" s="11" t="s">
         <v>18</v>
       </c>
@@ -13150,7 +12608,7 @@
       <c r="Q163" s="12"/>
       <c r="R163" s="12"/>
     </row>
-    <row r="164" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A164" s="6" t="s">
         <v>18</v>
       </c>
@@ -13192,7 +12650,7 @@
       <c r="Q164" s="7"/>
       <c r="R164" s="7"/>
     </row>
-    <row r="165" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A165" s="11" t="s">
         <v>18</v>
       </c>
@@ -13236,7 +12694,7 @@
       <c r="Q165" s="12"/>
       <c r="R165" s="12"/>
     </row>
-    <row r="166" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A166" s="6" t="s">
         <v>18</v>
       </c>
@@ -13280,7 +12738,7 @@
       <c r="Q166" s="7"/>
       <c r="R166" s="7"/>
     </row>
-    <row r="167" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A167" s="11" t="s">
         <v>30</v>
       </c>
@@ -13326,7 +12784,7 @@
       <c r="Q167" s="12"/>
       <c r="R167" s="12"/>
     </row>
-    <row r="168" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A168" s="6" t="s">
         <v>18</v>
       </c>
@@ -13360,7 +12818,7 @@
       <c r="Q168" s="7"/>
       <c r="R168" s="7"/>
     </row>
-    <row r="169" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A169" s="11" t="s">
         <v>18</v>
       </c>
@@ -13396,7 +12854,7 @@
       <c r="Q169" s="12"/>
       <c r="R169" s="12"/>
     </row>
-    <row r="170" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A170" s="6" t="s">
         <v>18</v>
       </c>
@@ -13440,7 +12898,7 @@
       <c r="Q170" s="7"/>
       <c r="R170" s="7"/>
     </row>
-    <row r="171" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A171" s="11" t="s">
         <v>18</v>
       </c>
@@ -13474,7 +12932,7 @@
       <c r="Q171" s="12"/>
       <c r="R171" s="12"/>
     </row>
-    <row r="172" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A172" s="6" t="s">
         <v>18</v>
       </c>
@@ -13506,7 +12964,7 @@
       <c r="Q172" s="7"/>
       <c r="R172" s="7"/>
     </row>
-    <row r="173" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A173" s="11" t="s">
         <v>30</v>
       </c>
@@ -13554,7 +13012,7 @@
       </c>
       <c r="R173" s="12"/>
     </row>
-    <row r="174" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A174" s="6" t="s">
         <v>18</v>
       </c>
@@ -13596,7 +13054,7 @@
       <c r="Q174" s="7"/>
       <c r="R174" s="7"/>
     </row>
-    <row r="175" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A175" s="11" t="s">
         <v>18</v>
       </c>
@@ -13638,7 +13096,7 @@
       <c r="Q175" s="12"/>
       <c r="R175" s="12"/>
     </row>
-    <row r="176" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A176" s="6" t="s">
         <v>18</v>
       </c>
@@ -13680,7 +13138,7 @@
       <c r="Q176" s="7"/>
       <c r="R176" s="7"/>
     </row>
-    <row r="177" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A177" s="11" t="s">
         <v>18</v>
       </c>
@@ -13718,7 +13176,7 @@
       <c r="Q177" s="12"/>
       <c r="R177" s="12"/>
     </row>
-    <row r="178" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A178" s="6" t="s">
         <v>18</v>
       </c>
@@ -13760,7 +13218,7 @@
       <c r="Q178" s="7"/>
       <c r="R178" s="7"/>
     </row>
-    <row r="179" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A179" s="11" t="s">
         <v>18</v>
       </c>
@@ -13802,7 +13260,7 @@
       <c r="Q179" s="12"/>
       <c r="R179" s="12"/>
     </row>
-    <row r="180" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A180" s="6" t="s">
         <v>18</v>
       </c>
@@ -13842,7 +13300,7 @@
       <c r="Q180" s="7"/>
       <c r="R180" s="7"/>
     </row>
-    <row r="181" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A181" s="11" t="s">
         <v>18</v>
       </c>
@@ -13876,7 +13334,7 @@
       <c r="Q181" s="12"/>
       <c r="R181" s="12"/>
     </row>
-    <row r="182" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A182" s="6" t="s">
         <v>18</v>
       </c>
@@ -13912,7 +13370,7 @@
       <c r="Q182" s="7"/>
       <c r="R182" s="7"/>
     </row>
-    <row r="183" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A183" s="11" t="s">
         <v>18</v>
       </c>
@@ -13954,7 +13412,7 @@
       <c r="Q183" s="12"/>
       <c r="R183" s="12"/>
     </row>
-    <row r="184" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A184" s="6" t="s">
         <v>18</v>
       </c>
@@ -13996,7 +13454,7 @@
       <c r="Q184" s="7"/>
       <c r="R184" s="7"/>
     </row>
-    <row r="185" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A185" s="11" t="s">
         <v>18</v>
       </c>
@@ -14038,7 +13496,7 @@
       <c r="Q185" s="12"/>
       <c r="R185" s="12"/>
     </row>
-    <row r="186" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A186" s="6" t="s">
         <v>18</v>
       </c>
@@ -14082,7 +13540,7 @@
       <c r="Q186" s="7"/>
       <c r="R186" s="7"/>
     </row>
-    <row r="187" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A187" s="11" t="s">
         <v>18</v>
       </c>
@@ -14118,7 +13576,7 @@
       <c r="Q187" s="12"/>
       <c r="R187" s="12"/>
     </row>
-    <row r="188" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A188" s="6" t="s">
         <v>18</v>
       </c>
@@ -14162,7 +13620,7 @@
       <c r="Q188" s="7"/>
       <c r="R188" s="7"/>
     </row>
-    <row r="189" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A189" s="11" t="s">
         <v>18</v>
       </c>
@@ -14206,7 +13664,7 @@
       <c r="Q189" s="12"/>
       <c r="R189" s="12"/>
     </row>
-    <row r="190" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A190" s="6" t="s">
         <v>18</v>
       </c>
@@ -14250,7 +13708,7 @@
       <c r="Q190" s="7"/>
       <c r="R190" s="7"/>
     </row>
-    <row r="191" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A191" s="11" t="s">
         <v>18</v>
       </c>
@@ -14294,7 +13752,7 @@
       <c r="Q191" s="12"/>
       <c r="R191" s="12"/>
     </row>
-    <row r="192" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A192" s="6" t="s">
         <v>18</v>
       </c>
@@ -14338,7 +13796,7 @@
       <c r="Q192" s="7"/>
       <c r="R192" s="7"/>
     </row>
-    <row r="193" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A193" s="11" t="s">
         <v>30</v>
       </c>
@@ -14384,7 +13842,7 @@
       <c r="Q193" s="12"/>
       <c r="R193" s="12"/>
     </row>
-    <row r="194" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A194" s="6" t="s">
         <v>18</v>
       </c>
@@ -14420,7 +13878,7 @@
       <c r="Q194" s="7"/>
       <c r="R194" s="7"/>
     </row>
-    <row r="195" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A195" s="11" t="s">
         <v>18</v>
       </c>
@@ -14464,7 +13922,7 @@
       <c r="Q195" s="12"/>
       <c r="R195" s="12"/>
     </row>
-    <row r="196" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A196" s="6" t="s">
         <v>18</v>
       </c>
@@ -14508,7 +13966,7 @@
       <c r="Q196" s="7"/>
       <c r="R196" s="7"/>
     </row>
-    <row r="197" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A197" s="11" t="s">
         <v>30</v>
       </c>
@@ -14554,7 +14012,7 @@
       <c r="Q197" s="12"/>
       <c r="R197" s="12"/>
     </row>
-    <row r="198" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A198" s="6" t="s">
         <v>18</v>
       </c>
@@ -14590,7 +14048,7 @@
       <c r="Q198" s="7"/>
       <c r="R198" s="7"/>
     </row>
-    <row r="199" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A199" s="11" t="s">
         <v>18</v>
       </c>
@@ -14632,7 +14090,7 @@
       <c r="Q199" s="12"/>
       <c r="R199" s="12"/>
     </row>
-    <row r="200" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A200" s="6" t="s">
         <v>18</v>
       </c>
@@ -14676,7 +14134,7 @@
       <c r="Q200" s="7"/>
       <c r="R200" s="7"/>
     </row>
-    <row r="201" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A201" s="11" t="s">
         <v>30</v>
       </c>
@@ -14722,7 +14180,7 @@
       <c r="Q201" s="12"/>
       <c r="R201" s="12"/>
     </row>
-    <row r="202" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A202" s="6" t="s">
         <v>18</v>
       </c>
@@ -14762,7 +14220,7 @@
       <c r="Q202" s="7"/>
       <c r="R202" s="7"/>
     </row>
-    <row r="203" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A203" s="11" t="s">
         <v>18</v>
       </c>
@@ -14806,7 +14264,7 @@
       <c r="Q203" s="12"/>
       <c r="R203" s="12"/>
     </row>
-    <row r="204" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A204" s="6" t="s">
         <v>18</v>
       </c>
@@ -14850,7 +14308,7 @@
       <c r="Q204" s="7"/>
       <c r="R204" s="7"/>
     </row>
-    <row r="205" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A205" s="11" t="s">
         <v>30</v>
       </c>
@@ -14898,7 +14356,7 @@
       </c>
       <c r="R205" s="12"/>
     </row>
-    <row r="206" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A206" s="6" t="s">
         <v>18</v>
       </c>
@@ -14942,7 +14400,7 @@
       <c r="Q206" s="7"/>
       <c r="R206" s="7"/>
     </row>
-    <row r="207" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A207" s="11" t="s">
         <v>30</v>
       </c>
@@ -14990,7 +14448,7 @@
       <c r="Q207" s="12"/>
       <c r="R207" s="12"/>
     </row>
-    <row r="208" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A208" s="6" t="s">
         <v>18</v>
       </c>
@@ -15034,7 +14492,7 @@
       <c r="Q208" s="7"/>
       <c r="R208" s="7"/>
     </row>
-    <row r="209" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A209" s="11" t="s">
         <v>18</v>
       </c>
@@ -15078,7 +14536,7 @@
       <c r="Q209" s="12"/>
       <c r="R209" s="12"/>
     </row>
-    <row r="210" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A210" s="6" t="s">
         <v>18</v>
       </c>
@@ -15120,7 +14578,7 @@
       <c r="Q210" s="7"/>
       <c r="R210" s="7"/>
     </row>
-    <row r="211" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A211" s="11" t="s">
         <v>30</v>
       </c>
@@ -15170,7 +14628,7 @@
       </c>
       <c r="R211" s="12"/>
     </row>
-    <row r="212" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A212" s="6" t="s">
         <v>18</v>
       </c>
@@ -15212,7 +14670,7 @@
       <c r="Q212" s="7"/>
       <c r="R212" s="7"/>
     </row>
-    <row r="213" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A213" s="11" t="s">
         <v>18</v>
       </c>
@@ -15258,7 +14716,7 @@
       <c r="Q213" s="12"/>
       <c r="R213" s="12"/>
     </row>
-    <row r="214" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A214" s="6" t="s">
         <v>30</v>
       </c>
@@ -15306,7 +14764,7 @@
       </c>
       <c r="R214" s="7"/>
     </row>
-    <row r="215" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A215" s="11" t="s">
         <v>18</v>
       </c>
@@ -15350,7 +14808,7 @@
       <c r="Q215" s="12"/>
       <c r="R215" s="12"/>
     </row>
-    <row r="216" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A216" s="6" t="s">
         <v>18</v>
       </c>
@@ -15394,7 +14852,7 @@
       <c r="Q216" s="7"/>
       <c r="R216" s="7"/>
     </row>
-    <row r="217" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A217" s="11" t="s">
         <v>18</v>
       </c>
@@ -15438,7 +14896,7 @@
       <c r="Q217" s="12"/>
       <c r="R217" s="12"/>
     </row>
-    <row r="218" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A218" s="6" t="s">
         <v>18</v>
       </c>
@@ -15482,7 +14940,7 @@
       <c r="Q218" s="7"/>
       <c r="R218" s="7"/>
     </row>
-    <row r="219" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A219" s="11" t="s">
         <v>30</v>
       </c>
@@ -15532,7 +14990,7 @@
       </c>
       <c r="R219" s="12"/>
     </row>
-    <row r="220" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A220" s="6" t="s">
         <v>18</v>
       </c>
@@ -15574,7 +15032,7 @@
       <c r="Q220" s="7"/>
       <c r="R220" s="7"/>
     </row>
-    <row r="221" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A221" s="11" t="s">
         <v>18</v>
       </c>
@@ -15618,7 +15076,7 @@
       <c r="Q221" s="12"/>
       <c r="R221" s="12"/>
     </row>
-    <row r="222" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A222" s="6" t="s">
         <v>18</v>
       </c>
@@ -15662,7 +15120,7 @@
       <c r="Q222" s="7"/>
       <c r="R222" s="7"/>
     </row>
-    <row r="223" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A223" s="11" t="s">
         <v>18</v>
       </c>
@@ -15706,7 +15164,7 @@
       <c r="Q223" s="12"/>
       <c r="R223" s="12"/>
     </row>
-    <row r="224" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A224" s="6" t="s">
         <v>30</v>
       </c>
@@ -15758,7 +15216,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="225" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A225" s="11" t="s">
         <v>18</v>
       </c>
@@ -15792,7 +15250,7 @@
       <c r="Q225" s="12"/>
       <c r="R225" s="12"/>
     </row>
-    <row r="226" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A226" s="6" t="s">
         <v>18</v>
       </c>
@@ -15836,7 +15294,7 @@
       <c r="Q226" s="7"/>
       <c r="R226" s="7"/>
     </row>
-    <row r="227" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A227" s="11" t="s">
         <v>18</v>
       </c>
@@ -15880,7 +15338,7 @@
       <c r="Q227" s="12"/>
       <c r="R227" s="12"/>
     </row>
-    <row r="228" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A228" s="6" t="s">
         <v>18</v>
       </c>
@@ -15924,7 +15382,7 @@
       <c r="Q228" s="7"/>
       <c r="R228" s="7"/>
     </row>
-    <row r="229" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A229" s="11" t="s">
         <v>18</v>
       </c>
@@ -15968,7 +15426,7 @@
       <c r="Q229" s="12"/>
       <c r="R229" s="12"/>
     </row>
-    <row r="230" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A230" s="6" t="s">
         <v>30</v>
       </c>
@@ -16014,7 +15472,7 @@
       <c r="Q230" s="7"/>
       <c r="R230" s="7"/>
     </row>
-    <row r="231" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A231" s="11" t="s">
         <v>18</v>
       </c>
@@ -16048,7 +15506,7 @@
       <c r="Q231" s="12"/>
       <c r="R231" s="12"/>
     </row>
-    <row r="232" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A232" s="6" t="s">
         <v>18</v>
       </c>
@@ -16082,7 +15540,7 @@
       <c r="Q232" s="7"/>
       <c r="R232" s="7"/>
     </row>
-    <row r="233" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A233" s="11" t="s">
         <v>18</v>
       </c>
@@ -16124,7 +15582,7 @@
       <c r="Q233" s="12"/>
       <c r="R233" s="12"/>
     </row>
-    <row r="234" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A234" s="6" t="s">
         <v>18</v>
       </c>
@@ -16158,7 +15616,7 @@
       <c r="Q234" s="7"/>
       <c r="R234" s="7"/>
     </row>
-    <row r="235" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A235" s="11" t="s">
         <v>18</v>
       </c>
@@ -16202,7 +15660,7 @@
       <c r="Q235" s="12"/>
       <c r="R235" s="12"/>
     </row>
-    <row r="236" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A236" s="6" t="s">
         <v>18</v>
       </c>
@@ -16240,7 +15698,7 @@
       <c r="Q236" s="7"/>
       <c r="R236" s="7"/>
     </row>
-    <row r="237" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A237" s="11" t="s">
         <v>30</v>
       </c>
@@ -16286,7 +15744,7 @@
       <c r="Q237" s="12"/>
       <c r="R237" s="12"/>
     </row>
-    <row r="238" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A238" s="6" t="s">
         <v>18</v>
       </c>
@@ -16328,7 +15786,7 @@
       <c r="Q238" s="7"/>
       <c r="R238" s="7"/>
     </row>
-    <row r="239" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A239" s="11" t="s">
         <v>18</v>
       </c>
@@ -16370,7 +15828,7 @@
       <c r="Q239" s="12"/>
       <c r="R239" s="12"/>
     </row>
-    <row r="240" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A240" s="6" t="s">
         <v>18</v>
       </c>
@@ -16412,7 +15870,7 @@
       <c r="Q240" s="7"/>
       <c r="R240" s="7"/>
     </row>
-    <row r="241" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A241" s="11" t="s">
         <v>18</v>
       </c>
@@ -16456,7 +15914,7 @@
       <c r="Q241" s="12"/>
       <c r="R241" s="12"/>
     </row>
-    <row r="242" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A242" s="6" t="s">
         <v>18</v>
       </c>
@@ -16502,7 +15960,7 @@
       <c r="Q242" s="7"/>
       <c r="R242" s="7"/>
     </row>
-    <row r="243" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A243" s="11" t="s">
         <v>18</v>
       </c>
@@ -16544,7 +16002,7 @@
       <c r="Q243" s="12"/>
       <c r="R243" s="12"/>
     </row>
-    <row r="244" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A244" s="6" t="s">
         <v>18</v>
       </c>
@@ -16588,7 +16046,7 @@
       <c r="Q244" s="7"/>
       <c r="R244" s="7"/>
     </row>
-    <row r="245" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A245" s="11" t="s">
         <v>18</v>
       </c>
@@ -16632,7 +16090,7 @@
       <c r="Q245" s="12"/>
       <c r="R245" s="12"/>
     </row>
-    <row r="246" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A246" s="6" t="s">
         <v>30</v>
       </c>
@@ -16680,7 +16138,7 @@
       </c>
       <c r="R246" s="7"/>
     </row>
-    <row r="247" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A247" s="11" t="s">
         <v>18</v>
       </c>
@@ -16716,7 +16174,7 @@
       <c r="Q247" s="12"/>
       <c r="R247" s="12"/>
     </row>
-    <row r="248" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A248" s="6" t="s">
         <v>18</v>
       </c>
@@ -16758,7 +16216,7 @@
       <c r="Q248" s="7"/>
       <c r="R248" s="7"/>
     </row>
-    <row r="249" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A249" s="11" t="s">
         <v>18</v>
       </c>
@@ -16804,7 +16262,7 @@
       <c r="Q249" s="12"/>
       <c r="R249" s="12"/>
     </row>
-    <row r="250" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A250" s="6" t="s">
         <v>18</v>
       </c>
@@ -16846,7 +16304,7 @@
       <c r="Q250" s="7"/>
       <c r="R250" s="7"/>
     </row>
-    <row r="251" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A251" s="11" t="s">
         <v>18</v>
       </c>
@@ -16890,7 +16348,7 @@
       <c r="Q251" s="12"/>
       <c r="R251" s="12"/>
     </row>
-    <row r="252" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A252" s="6" t="s">
         <v>30</v>
       </c>
@@ -16938,7 +16396,7 @@
       </c>
       <c r="R252" s="7"/>
     </row>
-    <row r="253" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A253" s="11" t="s">
         <v>18</v>
       </c>
@@ -16982,7 +16440,7 @@
       <c r="Q253" s="12"/>
       <c r="R253" s="12"/>
     </row>
-    <row r="254" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A254" s="6" t="s">
         <v>18</v>
       </c>
@@ -17026,7 +16484,7 @@
       <c r="Q254" s="7"/>
       <c r="R254" s="7"/>
     </row>
-    <row r="255" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A255" s="11" t="s">
         <v>18</v>
       </c>
@@ -17060,7 +16518,7 @@
       <c r="Q255" s="12"/>
       <c r="R255" s="12"/>
     </row>
-    <row r="256" spans="1:18" s="1" customFormat="1" ht="70.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A256" s="6" t="s">
         <v>30</v>
       </c>
@@ -17104,7 +16562,7 @@
       <c r="Q256" s="7"/>
       <c r="R256" s="7"/>
     </row>
-    <row r="257" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A257" s="11" t="s">
         <v>18</v>
       </c>
@@ -17140,7 +16598,7 @@
       <c r="Q257" s="12"/>
       <c r="R257" s="12"/>
     </row>
-    <row r="258" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A258" s="6" t="s">
         <v>18</v>
       </c>
@@ -17174,7 +16632,7 @@
       <c r="Q258" s="7"/>
       <c r="R258" s="7"/>
     </row>
-    <row r="259" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A259" s="11" t="s">
         <v>18</v>
       </c>
@@ -17216,7 +16674,7 @@
       <c r="Q259" s="12"/>
       <c r="R259" s="12"/>
     </row>
-    <row r="260" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A260" s="6" t="s">
         <v>18</v>
       </c>
@@ -17258,7 +16716,7 @@
       <c r="Q260" s="7"/>
       <c r="R260" s="7"/>
     </row>
-    <row r="261" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A261" s="11" t="s">
         <v>18</v>
       </c>
@@ -17294,7 +16752,7 @@
       <c r="Q261" s="12"/>
       <c r="R261" s="12"/>
     </row>
-    <row r="262" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A262" s="6" t="s">
         <v>18</v>
       </c>
@@ -17330,7 +16788,7 @@
       <c r="Q262" s="7"/>
       <c r="R262" s="7"/>
     </row>
-    <row r="263" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A263" s="11" t="s">
         <v>18</v>
       </c>
@@ -17366,7 +16824,7 @@
       <c r="Q263" s="12"/>
       <c r="R263" s="12"/>
     </row>
-    <row r="264" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A264" s="6" t="s">
         <v>18</v>
       </c>
@@ -17408,7 +16866,7 @@
       <c r="Q264" s="7"/>
       <c r="R264" s="7"/>
     </row>
-    <row r="265" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A265" s="11" t="s">
         <v>18</v>
       </c>
@@ -17450,7 +16908,7 @@
       <c r="Q265" s="12"/>
       <c r="R265" s="12"/>
     </row>
-    <row r="266" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A266" s="6" t="s">
         <v>18</v>
       </c>
@@ -17484,7 +16942,7 @@
       <c r="Q266" s="7"/>
       <c r="R266" s="7"/>
     </row>
-    <row r="267" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A267" s="11" t="s">
         <v>18</v>
       </c>
@@ -17526,7 +16984,7 @@
       <c r="Q267" s="12"/>
       <c r="R267" s="12"/>
     </row>
-    <row r="268" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A268" s="6" t="s">
         <v>18</v>
       </c>
@@ -17568,7 +17026,7 @@
       <c r="Q268" s="7"/>
       <c r="R268" s="7"/>
     </row>
-    <row r="269" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A269" s="11" t="s">
         <v>18</v>
       </c>
@@ -17610,7 +17068,7 @@
       <c r="Q269" s="12"/>
       <c r="R269" s="12"/>
     </row>
-    <row r="270" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A270" s="6" t="s">
         <v>18</v>
       </c>
@@ -17654,7 +17112,7 @@
       <c r="Q270" s="7"/>
       <c r="R270" s="7"/>
     </row>
-    <row r="271" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A271" s="11" t="s">
         <v>18</v>
       </c>
@@ -17696,7 +17154,7 @@
       <c r="Q271" s="12"/>
       <c r="R271" s="12"/>
     </row>
-    <row r="272" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A272" s="6" t="s">
         <v>18</v>
       </c>
@@ -17738,7 +17196,7 @@
       <c r="Q272" s="7"/>
       <c r="R272" s="7"/>
     </row>
-    <row r="273" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A273" s="11" t="s">
         <v>18</v>
       </c>
@@ -17780,7 +17238,7 @@
       <c r="Q273" s="12"/>
       <c r="R273" s="12"/>
     </row>
-    <row r="274" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A274" s="6" t="s">
         <v>18</v>
       </c>
@@ -17822,7 +17280,7 @@
       <c r="Q274" s="7"/>
       <c r="R274" s="7"/>
     </row>
-    <row r="275" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A275" s="11" t="s">
         <v>18</v>
       </c>
@@ -17864,7 +17322,7 @@
       <c r="Q275" s="12"/>
       <c r="R275" s="12"/>
     </row>
-    <row r="276" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A276" s="6" t="s">
         <v>18</v>
       </c>
@@ -17906,7 +17364,7 @@
       <c r="Q276" s="7"/>
       <c r="R276" s="7"/>
     </row>
-    <row r="277" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A277" s="11" t="s">
         <v>18</v>
       </c>
@@ -17950,7 +17408,7 @@
       <c r="Q277" s="12"/>
       <c r="R277" s="12"/>
     </row>
-    <row r="278" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A278" s="6" t="s">
         <v>30</v>
       </c>
@@ -17998,7 +17456,7 @@
       </c>
       <c r="R278" s="7"/>
     </row>
-    <row r="279" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A279" s="11" t="s">
         <v>18</v>
       </c>
@@ -18040,7 +17498,7 @@
       <c r="Q279" s="12"/>
       <c r="R279" s="12"/>
     </row>
-    <row r="280" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A280" s="6" t="s">
         <v>18</v>
       </c>
@@ -18082,7 +17540,7 @@
       <c r="Q280" s="7"/>
       <c r="R280" s="7"/>
     </row>
-    <row r="281" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A281" s="11" t="s">
         <v>18</v>
       </c>
@@ -18124,7 +17582,7 @@
       <c r="Q281" s="12"/>
       <c r="R281" s="12"/>
     </row>
-    <row r="282" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A282" s="6" t="s">
         <v>18</v>
       </c>
@@ -18166,7 +17624,7 @@
       <c r="Q282" s="7"/>
       <c r="R282" s="7"/>
     </row>
-    <row r="283" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A283" s="11" t="s">
         <v>18</v>
       </c>
@@ -18208,7 +17666,7 @@
       <c r="Q283" s="12"/>
       <c r="R283" s="12"/>
     </row>
-    <row r="284" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A284" s="6" t="s">
         <v>18</v>
       </c>
@@ -18250,7 +17708,7 @@
       <c r="Q284" s="7"/>
       <c r="R284" s="7"/>
     </row>
-    <row r="285" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A285" s="11" t="s">
         <v>18</v>
       </c>
@@ -18294,7 +17752,7 @@
       <c r="Q285" s="12"/>
       <c r="R285" s="12"/>
     </row>
-    <row r="286" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A286" s="6" t="s">
         <v>30</v>
       </c>
@@ -18342,7 +17800,7 @@
       </c>
       <c r="R286" s="7"/>
     </row>
-    <row r="287" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A287" s="11" t="s">
         <v>18</v>
       </c>
@@ -18384,7 +17842,7 @@
       <c r="Q287" s="12"/>
       <c r="R287" s="12"/>
     </row>
-    <row r="288" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A288" s="6" t="s">
         <v>18</v>
       </c>
@@ -18426,7 +17884,7 @@
       <c r="Q288" s="7"/>
       <c r="R288" s="7"/>
     </row>
-    <row r="289" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A289" s="11" t="s">
         <v>18</v>
       </c>
@@ -18470,7 +17928,7 @@
       <c r="Q289" s="12"/>
       <c r="R289" s="12"/>
     </row>
-    <row r="290" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A290" s="6" t="s">
         <v>18</v>
       </c>
@@ -18512,7 +17970,7 @@
       <c r="Q290" s="7"/>
       <c r="R290" s="7"/>
     </row>
-    <row r="291" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A291" s="11" t="s">
         <v>18</v>
       </c>
@@ -18556,7 +18014,7 @@
       <c r="Q291" s="12"/>
       <c r="R291" s="12"/>
     </row>
-    <row r="292" spans="1:18" s="1" customFormat="1" ht="99.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" s="1" customFormat="1" ht="148.7907" customHeight="1">
       <c r="A292" s="6" t="s">
         <v>18</v>
       </c>
@@ -18592,7 +18050,7 @@
       <c r="Q292" s="7"/>
       <c r="R292" s="7"/>
     </row>
-    <row r="293" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" s="1" customFormat="1" ht="127.4587" customHeight="1">
       <c r="A293" s="11" t="s">
         <v>18</v>
       </c>
@@ -18634,7 +18092,7 @@
       <c r="Q293" s="12"/>
       <c r="R293" s="12"/>
     </row>
-    <row r="294" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" s="1" customFormat="1" ht="127.4587" customHeight="1">
       <c r="A294" s="6" t="s">
         <v>18</v>
       </c>
@@ -18678,7 +18136,7 @@
       <c r="Q294" s="7"/>
       <c r="R294" s="7"/>
     </row>
-    <row r="295" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" s="1" customFormat="1" ht="127.4587" customHeight="1">
       <c r="A295" s="11" t="s">
         <v>18</v>
       </c>
@@ -18712,7 +18170,7 @@
       <c r="Q295" s="12"/>
       <c r="R295" s="12"/>
     </row>
-    <row r="296" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A296" s="6" t="s">
         <v>18</v>
       </c>
@@ -18750,7 +18208,7 @@
       <c r="Q296" s="7"/>
       <c r="R296" s="7"/>
     </row>
-    <row r="297" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A297" s="11" t="s">
         <v>30</v>
       </c>
@@ -18798,7 +18256,7 @@
       </c>
       <c r="R297" s="12"/>
     </row>
-    <row r="298" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A298" s="6" t="s">
         <v>18</v>
       </c>
@@ -18834,7 +18292,7 @@
       <c r="Q298" s="7"/>
       <c r="R298" s="7"/>
     </row>
-    <row r="299" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A299" s="11" t="s">
         <v>18</v>
       </c>
@@ -18876,7 +18334,7 @@
       <c r="Q299" s="12"/>
       <c r="R299" s="12"/>
     </row>
-    <row r="300" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A300" s="6" t="s">
         <v>18</v>
       </c>
@@ -18920,7 +18378,7 @@
       <c r="Q300" s="7"/>
       <c r="R300" s="7"/>
     </row>
-    <row r="301" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A301" s="11" t="s">
         <v>18</v>
       </c>
@@ -18958,7 +18416,7 @@
       <c r="Q301" s="12"/>
       <c r="R301" s="12"/>
     </row>
-    <row r="302" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A302" s="6" t="s">
         <v>18</v>
       </c>
@@ -19002,7 +18460,7 @@
       <c r="Q302" s="7"/>
       <c r="R302" s="7"/>
     </row>
-    <row r="303" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A303" s="11" t="s">
         <v>18</v>
       </c>
@@ -19046,7 +18504,7 @@
       <c r="Q303" s="12"/>
       <c r="R303" s="12"/>
     </row>
-    <row r="304" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A304" s="6" t="s">
         <v>18</v>
       </c>
@@ -19090,7 +18548,7 @@
       <c r="Q304" s="7"/>
       <c r="R304" s="7"/>
     </row>
-    <row r="305" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A305" s="11" t="s">
         <v>30</v>
       </c>
@@ -19138,7 +18596,7 @@
       </c>
       <c r="R305" s="12"/>
     </row>
-    <row r="306" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A306" s="6" t="s">
         <v>18</v>
       </c>
@@ -19172,7 +18630,7 @@
       <c r="Q306" s="7"/>
       <c r="R306" s="7"/>
     </row>
-    <row r="307" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A307" s="11" t="s">
         <v>18</v>
       </c>
@@ -19208,7 +18666,7 @@
       <c r="Q307" s="12"/>
       <c r="R307" s="12"/>
     </row>
-    <row r="308" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A308" s="6" t="s">
         <v>18</v>
       </c>
@@ -19252,7 +18710,7 @@
       <c r="Q308" s="7"/>
       <c r="R308" s="7"/>
     </row>
-    <row r="309" spans="1:18" s="1" customFormat="1" ht="92.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" s="1" customFormat="1" ht="138.1247" customHeight="1">
       <c r="A309" s="11" t="s">
         <v>18</v>
       </c>
@@ -19286,7 +18744,7 @@
       <c r="Q309" s="12"/>
       <c r="R309" s="12"/>
     </row>
-    <row r="310" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A310" s="6" t="s">
         <v>18</v>
       </c>
@@ -19328,7 +18786,7 @@
       <c r="Q310" s="7"/>
       <c r="R310" s="7"/>
     </row>
-    <row r="311" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A311" s="11" t="s">
         <v>18</v>
       </c>
@@ -19372,7 +18830,7 @@
       <c r="Q311" s="12"/>
       <c r="R311" s="12"/>
     </row>
-    <row r="312" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A312" s="6" t="s">
         <v>18</v>
       </c>
@@ -19406,7 +18864,7 @@
       <c r="Q312" s="7"/>
       <c r="R312" s="7"/>
     </row>
-    <row r="313" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A313" s="11" t="s">
         <v>18</v>
       </c>
@@ -19448,7 +18906,7 @@
       <c r="Q313" s="12"/>
       <c r="R313" s="12"/>
     </row>
-    <row r="314" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A314" s="6" t="s">
         <v>18</v>
       </c>
@@ -19490,7 +18948,7 @@
       <c r="Q314" s="7"/>
       <c r="R314" s="7"/>
     </row>
-    <row r="315" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A315" s="11" t="s">
         <v>18</v>
       </c>
@@ -19532,7 +18990,7 @@
       <c r="Q315" s="12"/>
       <c r="R315" s="12"/>
     </row>
-    <row r="316" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A316" s="6" t="s">
         <v>18</v>
       </c>
@@ -19572,7 +19030,7 @@
       <c r="Q316" s="7"/>
       <c r="R316" s="7"/>
     </row>
-    <row r="317" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A317" s="11" t="s">
         <v>18</v>
       </c>
@@ -19616,7 +19074,7 @@
       <c r="Q317" s="12"/>
       <c r="R317" s="12"/>
     </row>
-    <row r="318" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A318" s="6" t="s">
         <v>18</v>
       </c>
@@ -19650,7 +19108,7 @@
       <c r="Q318" s="7"/>
       <c r="R318" s="7"/>
     </row>
-    <row r="319" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A319" s="11" t="s">
         <v>18</v>
       </c>
@@ -19692,7 +19150,7 @@
       <c r="Q319" s="12"/>
       <c r="R319" s="12"/>
     </row>
-    <row r="320" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A320" s="6" t="s">
         <v>18</v>
       </c>
@@ -19730,7 +19188,7 @@
       <c r="Q320" s="7"/>
       <c r="R320" s="7"/>
     </row>
-    <row r="321" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A321" s="11" t="s">
         <v>18</v>
       </c>
@@ -19764,7 +19222,7 @@
       <c r="Q321" s="12"/>
       <c r="R321" s="12"/>
     </row>
-    <row r="322" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A322" s="6" t="s">
         <v>18</v>
       </c>
@@ -19800,7 +19258,7 @@
       <c r="Q322" s="7"/>
       <c r="R322" s="7"/>
     </row>
-    <row r="323" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A323" s="11" t="s">
         <v>18</v>
       </c>
@@ -19834,7 +19292,7 @@
       <c r="Q323" s="12"/>
       <c r="R323" s="12"/>
     </row>
-    <row r="324" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A324" s="6" t="s">
         <v>18</v>
       </c>
@@ -19876,7 +19334,7 @@
       <c r="Q324" s="7"/>
       <c r="R324" s="7"/>
     </row>
-    <row r="325" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A325" s="11" t="s">
         <v>18</v>
       </c>
@@ -19918,7 +19376,7 @@
       <c r="Q325" s="12"/>
       <c r="R325" s="12"/>
     </row>
-    <row r="326" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A326" s="6" t="s">
         <v>18</v>
       </c>
@@ -19960,7 +19418,7 @@
       <c r="Q326" s="7"/>
       <c r="R326" s="7"/>
     </row>
-    <row r="327" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A327" s="11" t="s">
         <v>30</v>
       </c>
@@ -20006,7 +19464,7 @@
       <c r="Q327" s="12"/>
       <c r="R327" s="12"/>
     </row>
-    <row r="328" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A328" s="6" t="s">
         <v>18</v>
       </c>
@@ -20050,7 +19508,7 @@
       <c r="Q328" s="7"/>
       <c r="R328" s="7"/>
     </row>
-    <row r="329" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A329" s="11" t="s">
         <v>30</v>
       </c>
@@ -20098,7 +19556,7 @@
       </c>
       <c r="R329" s="12"/>
     </row>
-    <row r="330" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A330" s="6" t="s">
         <v>18</v>
       </c>
@@ -20142,7 +19600,7 @@
       <c r="Q330" s="7"/>
       <c r="R330" s="7"/>
     </row>
-    <row r="331" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A331" s="11" t="s">
         <v>18</v>
       </c>
@@ -20184,7 +19642,7 @@
       <c r="Q331" s="12"/>
       <c r="R331" s="12"/>
     </row>
-    <row r="332" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A332" s="6" t="s">
         <v>18</v>
       </c>
@@ -20228,7 +19686,7 @@
       <c r="Q332" s="7"/>
       <c r="R332" s="7"/>
     </row>
-    <row r="333" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A333" s="11" t="s">
         <v>30</v>
       </c>
@@ -20272,7 +19730,7 @@
       <c r="Q333" s="12"/>
       <c r="R333" s="12"/>
     </row>
-    <row r="334" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A334" s="6" t="s">
         <v>18</v>
       </c>
@@ -20316,7 +19774,7 @@
       <c r="Q334" s="7"/>
       <c r="R334" s="7"/>
     </row>
-    <row r="335" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A335" s="11" t="s">
         <v>18</v>
       </c>
@@ -20360,7 +19818,7 @@
       <c r="Q335" s="12"/>
       <c r="R335" s="12"/>
     </row>
-    <row r="336" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A336" s="6" t="s">
         <v>30</v>
       </c>
@@ -20408,7 +19866,7 @@
       </c>
       <c r="R336" s="7"/>
     </row>
-    <row r="337" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A337" s="11" t="s">
         <v>18</v>
       </c>
@@ -20452,7 +19910,7 @@
       <c r="Q337" s="12"/>
       <c r="R337" s="12"/>
     </row>
-    <row r="338" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A338" s="6" t="s">
         <v>30</v>
       </c>
@@ -20500,7 +19958,7 @@
       </c>
       <c r="R338" s="7"/>
     </row>
-    <row r="339" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A339" s="11" t="s">
         <v>18</v>
       </c>
@@ -20540,7 +19998,7 @@
       <c r="Q339" s="12"/>
       <c r="R339" s="12"/>
     </row>
-    <row r="340" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A340" s="6" t="s">
         <v>18</v>
       </c>
@@ -20584,7 +20042,7 @@
       <c r="Q340" s="7"/>
       <c r="R340" s="7"/>
     </row>
-    <row r="341" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A341" s="11" t="s">
         <v>18</v>
       </c>
@@ -20630,7 +20088,7 @@
       <c r="Q341" s="12"/>
       <c r="R341" s="12"/>
     </row>
-    <row r="342" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A342" s="6" t="s">
         <v>18</v>
       </c>
@@ -20674,7 +20132,7 @@
       <c r="Q342" s="7"/>
       <c r="R342" s="7"/>
     </row>
-    <row r="343" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A343" s="11" t="s">
         <v>18</v>
       </c>
@@ -20718,7 +20176,7 @@
       <c r="Q343" s="12"/>
       <c r="R343" s="12"/>
     </row>
-    <row r="344" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A344" s="6" t="s">
         <v>30</v>
       </c>
@@ -20768,7 +20226,7 @@
       </c>
       <c r="R344" s="7"/>
     </row>
-    <row r="345" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A345" s="11" t="s">
         <v>139</v>
       </c>
@@ -20814,7 +20272,7 @@
       </c>
       <c r="R345" s="12"/>
     </row>
-    <row r="346" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A346" s="6" t="s">
         <v>18</v>
       </c>
@@ -20858,7 +20316,7 @@
       <c r="Q346" s="7"/>
       <c r="R346" s="7"/>
     </row>
-    <row r="347" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A347" s="11" t="s">
         <v>18</v>
       </c>
@@ -20896,7 +20354,7 @@
       <c r="Q347" s="12"/>
       <c r="R347" s="12"/>
     </row>
-    <row r="348" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A348" s="6" t="s">
         <v>30</v>
       </c>
@@ -20944,7 +20402,7 @@
       </c>
       <c r="R348" s="7"/>
     </row>
-    <row r="349" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A349" s="11" t="s">
         <v>18</v>
       </c>
@@ -20988,7 +20446,7 @@
       <c r="Q349" s="12"/>
       <c r="R349" s="12"/>
     </row>
-    <row r="350" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A350" s="6" t="s">
         <v>18</v>
       </c>
@@ -21032,7 +20490,7 @@
       <c r="Q350" s="7"/>
       <c r="R350" s="7"/>
     </row>
-    <row r="351" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A351" s="11" t="s">
         <v>30</v>
       </c>
@@ -21080,7 +20538,7 @@
       </c>
       <c r="R351" s="12"/>
     </row>
-    <row r="352" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A352" s="6" t="s">
         <v>18</v>
       </c>
@@ -21122,7 +20580,7 @@
       <c r="Q352" s="7"/>
       <c r="R352" s="7"/>
     </row>
-    <row r="353" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A353" s="11" t="s">
         <v>30</v>
       </c>
@@ -21172,7 +20630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="354" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A354" s="6" t="s">
         <v>18</v>
       </c>
@@ -21214,7 +20672,7 @@
       <c r="Q354" s="7"/>
       <c r="R354" s="7"/>
     </row>
-    <row r="355" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A355" s="11" t="s">
         <v>18</v>
       </c>
@@ -21248,7 +20706,7 @@
       <c r="Q355" s="12"/>
       <c r="R355" s="12"/>
     </row>
-    <row r="356" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A356" s="6" t="s">
         <v>18</v>
       </c>
@@ -21288,7 +20746,7 @@
       <c r="Q356" s="7"/>
       <c r="R356" s="7"/>
     </row>
-    <row r="357" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A357" s="11" t="s">
         <v>18</v>
       </c>
@@ -21332,7 +20790,7 @@
       <c r="Q357" s="12"/>
       <c r="R357" s="12"/>
     </row>
-    <row r="358" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A358" s="6" t="s">
         <v>18</v>
       </c>
@@ -21370,7 +20828,7 @@
       <c r="Q358" s="7"/>
       <c r="R358" s="7"/>
     </row>
-    <row r="359" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A359" s="11" t="s">
         <v>18</v>
       </c>
@@ -21404,7 +20862,7 @@
       <c r="Q359" s="12"/>
       <c r="R359" s="12"/>
     </row>
-    <row r="360" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A360" s="6" t="s">
         <v>18</v>
       </c>
@@ -21438,7 +20896,7 @@
       <c r="Q360" s="7"/>
       <c r="R360" s="7"/>
     </row>
-    <row r="361" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A361" s="11" t="s">
         <v>18</v>
       </c>
@@ -21472,7 +20930,7 @@
       <c r="Q361" s="12"/>
       <c r="R361" s="12"/>
     </row>
-    <row r="362" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A362" s="6" t="s">
         <v>18</v>
       </c>
@@ -21516,7 +20974,7 @@
       <c r="Q362" s="7"/>
       <c r="R362" s="7"/>
     </row>
-    <row r="363" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A363" s="11" t="s">
         <v>18</v>
       </c>
@@ -21550,7 +21008,7 @@
       <c r="Q363" s="12"/>
       <c r="R363" s="12"/>
     </row>
-    <row r="364" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A364" s="6" t="s">
         <v>18</v>
       </c>
@@ -21592,7 +21050,7 @@
       <c r="Q364" s="7"/>
       <c r="R364" s="7"/>
     </row>
-    <row r="365" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A365" s="11" t="s">
         <v>18</v>
       </c>
@@ -21634,7 +21092,7 @@
       <c r="Q365" s="12"/>
       <c r="R365" s="12"/>
     </row>
-    <row r="366" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A366" s="6" t="s">
         <v>18</v>
       </c>
@@ -21676,7 +21134,7 @@
       <c r="Q366" s="7"/>
       <c r="R366" s="7"/>
     </row>
-    <row r="367" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A367" s="11" t="s">
         <v>18</v>
       </c>
@@ -21710,7 +21168,7 @@
       <c r="Q367" s="12"/>
       <c r="R367" s="12"/>
     </row>
-    <row r="368" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A368" s="6" t="s">
         <v>18</v>
       </c>
@@ -21754,7 +21212,7 @@
       <c r="Q368" s="7"/>
       <c r="R368" s="7"/>
     </row>
-    <row r="369" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A369" s="11" t="s">
         <v>18</v>
       </c>
@@ -21788,7 +21246,7 @@
       <c r="Q369" s="12"/>
       <c r="R369" s="12"/>
     </row>
-    <row r="370" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A370" s="6" t="s">
         <v>18</v>
       </c>
@@ -21832,7 +21290,7 @@
       <c r="Q370" s="7"/>
       <c r="R370" s="7"/>
     </row>
-    <row r="371" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A371" s="11" t="s">
         <v>18</v>
       </c>
@@ -21870,7 +21328,7 @@
       <c r="Q371" s="12"/>
       <c r="R371" s="12"/>
     </row>
-    <row r="372" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A372" s="6" t="s">
         <v>18</v>
       </c>
@@ -21914,7 +21372,7 @@
       <c r="Q372" s="7"/>
       <c r="R372" s="7"/>
     </row>
-    <row r="373" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A373" s="11" t="s">
         <v>18</v>
       </c>
@@ -21950,7 +21408,7 @@
       <c r="Q373" s="12"/>
       <c r="R373" s="12"/>
     </row>
-    <row r="374" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A374" s="6" t="s">
         <v>18</v>
       </c>
@@ -21988,7 +21446,7 @@
       <c r="Q374" s="7"/>
       <c r="R374" s="7"/>
     </row>
-    <row r="375" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A375" s="11" t="s">
         <v>18</v>
       </c>
@@ -22026,7 +21484,7 @@
       <c r="Q375" s="12"/>
       <c r="R375" s="12"/>
     </row>
-    <row r="376" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A376" s="6" t="s">
         <v>18</v>
       </c>
@@ -22064,7 +21522,7 @@
       <c r="Q376" s="7"/>
       <c r="R376" s="7"/>
     </row>
-    <row r="377" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A377" s="11" t="s">
         <v>18</v>
       </c>
@@ -22100,7 +21558,7 @@
       <c r="Q377" s="12"/>
       <c r="R377" s="12"/>
     </row>
-    <row r="378" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A378" s="6" t="s">
         <v>18</v>
       </c>
@@ -22134,7 +21592,7 @@
       <c r="Q378" s="7"/>
       <c r="R378" s="7"/>
     </row>
-    <row r="379" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A379" s="11" t="s">
         <v>18</v>
       </c>
@@ -22176,7 +21634,7 @@
       <c r="Q379" s="12"/>
       <c r="R379" s="12"/>
     </row>
-    <row r="380" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A380" s="6" t="s">
         <v>18</v>
       </c>
@@ -22220,7 +21678,7 @@
       <c r="Q380" s="7"/>
       <c r="R380" s="7"/>
     </row>
-    <row r="381" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A381" s="11" t="s">
         <v>18</v>
       </c>
@@ -22262,7 +21720,7 @@
       <c r="Q381" s="12"/>
       <c r="R381" s="12"/>
     </row>
-    <row r="382" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A382" s="6" t="s">
         <v>18</v>
       </c>
@@ -22306,7 +21764,7 @@
       <c r="Q382" s="7"/>
       <c r="R382" s="7"/>
     </row>
-    <row r="383" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A383" s="11" t="s">
         <v>18</v>
       </c>
@@ -22350,7 +21808,7 @@
       <c r="Q383" s="12"/>
       <c r="R383" s="12"/>
     </row>
-    <row r="384" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A384" s="6" t="s">
         <v>18</v>
       </c>
@@ -22392,7 +21850,7 @@
       <c r="Q384" s="7"/>
       <c r="R384" s="7"/>
     </row>
-    <row r="385" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A385" s="11" t="s">
         <v>18</v>
       </c>
@@ -22436,7 +21894,7 @@
       <c r="Q385" s="12"/>
       <c r="R385" s="12"/>
     </row>
-    <row r="386" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A386" s="6" t="s">
         <v>18</v>
       </c>
@@ -22480,7 +21938,7 @@
       <c r="Q386" s="7"/>
       <c r="R386" s="7"/>
     </row>
-    <row r="387" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A387" s="11" t="s">
         <v>18</v>
       </c>
@@ -22522,7 +21980,7 @@
       <c r="Q387" s="12"/>
       <c r="R387" s="12"/>
     </row>
-    <row r="388" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A388" s="6" t="s">
         <v>18</v>
       </c>
@@ -22564,7 +22022,7 @@
       <c r="Q388" s="7"/>
       <c r="R388" s="7"/>
     </row>
-    <row r="389" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A389" s="11" t="s">
         <v>18</v>
       </c>
@@ -22608,7 +22066,7 @@
       <c r="Q389" s="12"/>
       <c r="R389" s="12"/>
     </row>
-    <row r="390" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A390" s="6" t="s">
         <v>18</v>
       </c>
@@ -22646,7 +22104,7 @@
       <c r="Q390" s="7"/>
       <c r="R390" s="7"/>
     </row>
-    <row r="391" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A391" s="11" t="s">
         <v>18</v>
       </c>
@@ -22684,7 +22142,7 @@
       <c r="Q391" s="12"/>
       <c r="R391" s="12"/>
     </row>
-    <row r="392" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A392" s="6" t="s">
         <v>30</v>
       </c>
@@ -22730,7 +22188,7 @@
       <c r="Q392" s="7"/>
       <c r="R392" s="7"/>
     </row>
-    <row r="393" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A393" s="11" t="s">
         <v>18</v>
       </c>
@@ -22764,7 +22222,7 @@
       <c r="Q393" s="12"/>
       <c r="R393" s="12"/>
     </row>
-    <row r="394" spans="1:18" s="1" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" s="1" customFormat="1" ht="235.1853" customHeight="1">
       <c r="A394" s="6" t="s">
         <v>30</v>
       </c>
@@ -22814,7 +22272,7 @@
       <c r="Q394" s="7"/>
       <c r="R394" s="7"/>
     </row>
-    <row r="395" spans="1:18" s="1" customFormat="1" ht="192.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" s="1" customFormat="1" ht="289.0486" customHeight="1">
       <c r="A395" s="11" t="s">
         <v>139</v>
       </c>
@@ -22862,7 +22320,7 @@
       </c>
       <c r="R395" s="12"/>
     </row>
-    <row r="396" spans="1:18" s="1" customFormat="1" ht="128" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" s="1" customFormat="1" ht="191.988" customHeight="1">
       <c r="A396" s="6" t="s">
         <v>30</v>
       </c>
@@ -22912,7 +22370,7 @@
       <c r="Q396" s="7"/>
       <c r="R396" s="7"/>
     </row>
-    <row r="397" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A397" s="11" t="s">
         <v>18</v>
       </c>
@@ -22954,7 +22412,7 @@
       <c r="Q397" s="12"/>
       <c r="R397" s="12"/>
     </row>
-    <row r="398" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A398" s="6" t="s">
         <v>18</v>
       </c>
@@ -22998,7 +22456,7 @@
       <c r="Q398" s="7"/>
       <c r="R398" s="7"/>
     </row>
-    <row r="399" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A399" s="11" t="s">
         <v>18</v>
       </c>
@@ -23038,7 +22496,7 @@
       <c r="Q399" s="12"/>
       <c r="R399" s="12"/>
     </row>
-    <row r="400" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A400" s="6" t="s">
         <v>18</v>
       </c>
@@ -23082,7 +22540,7 @@
       <c r="Q400" s="7"/>
       <c r="R400" s="7"/>
     </row>
-    <row r="401" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A401" s="11" t="s">
         <v>18</v>
       </c>
@@ -23126,7 +22584,7 @@
       <c r="Q401" s="12"/>
       <c r="R401" s="12"/>
     </row>
-    <row r="402" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A402" s="6" t="s">
         <v>18</v>
       </c>
@@ -23162,7 +22620,7 @@
       <c r="Q402" s="7"/>
       <c r="R402" s="7"/>
     </row>
-    <row r="403" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A403" s="11" t="s">
         <v>18</v>
       </c>
@@ -23206,7 +22664,7 @@
       <c r="Q403" s="12"/>
       <c r="R403" s="12"/>
     </row>
-    <row r="404" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A404" s="6" t="s">
         <v>18</v>
       </c>
@@ -23250,7 +22708,7 @@
       <c r="Q404" s="7"/>
       <c r="R404" s="7"/>
     </row>
-    <row r="405" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A405" s="11" t="s">
         <v>18</v>
       </c>
@@ -23294,7 +22752,7 @@
       <c r="Q405" s="12"/>
       <c r="R405" s="12"/>
     </row>
-    <row r="406" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A406" s="6" t="s">
         <v>18</v>
       </c>
@@ -23338,7 +22796,7 @@
       <c r="Q406" s="7"/>
       <c r="R406" s="7"/>
     </row>
-    <row r="407" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A407" s="11" t="s">
         <v>30</v>
       </c>
@@ -23384,7 +22842,7 @@
       <c r="Q407" s="12"/>
       <c r="R407" s="12"/>
     </row>
-    <row r="408" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A408" s="6" t="s">
         <v>30</v>
       </c>
@@ -23434,7 +22892,7 @@
       <c r="Q408" s="7"/>
       <c r="R408" s="7"/>
     </row>
-    <row r="409" spans="1:18" s="1" customFormat="1" ht="163.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" s="1" customFormat="1" ht="245.8513" customHeight="1">
       <c r="A409" s="11" t="s">
         <v>139</v>
       </c>
@@ -23482,7 +22940,7 @@
       </c>
       <c r="R409" s="12"/>
     </row>
-    <row r="410" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A410" s="6" t="s">
         <v>18</v>
       </c>
@@ -23526,7 +22984,7 @@
       <c r="Q410" s="7"/>
       <c r="R410" s="7"/>
     </row>
-    <row r="411" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A411" s="11" t="s">
         <v>30</v>
       </c>
@@ -23574,7 +23032,7 @@
       <c r="Q411" s="12"/>
       <c r="R411" s="12"/>
     </row>
-    <row r="412" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A412" s="6" t="s">
         <v>139</v>
       </c>
@@ -23620,7 +23078,7 @@
       </c>
       <c r="R412" s="7"/>
     </row>
-    <row r="413" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A413" s="11" t="s">
         <v>18</v>
       </c>
@@ -23660,7 +23118,7 @@
       <c r="Q413" s="12"/>
       <c r="R413" s="12"/>
     </row>
-    <row r="414" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A414" s="6" t="s">
         <v>18</v>
       </c>
@@ -23702,7 +23160,7 @@
       <c r="Q414" s="7"/>
       <c r="R414" s="7"/>
     </row>
-    <row r="415" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A415" s="11" t="s">
         <v>18</v>
       </c>
@@ -23744,7 +23202,7 @@
       <c r="Q415" s="12"/>
       <c r="R415" s="12"/>
     </row>
-    <row r="416" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A416" s="6" t="s">
         <v>18</v>
       </c>
@@ -23778,7 +23236,7 @@
       <c r="Q416" s="7"/>
       <c r="R416" s="7"/>
     </row>
-    <row r="417" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A417" s="11" t="s">
         <v>18</v>
       </c>
@@ -23822,7 +23280,7 @@
       <c r="Q417" s="12"/>
       <c r="R417" s="12"/>
     </row>
-    <row r="418" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A418" s="6" t="s">
         <v>30</v>
       </c>
@@ -23868,7 +23326,7 @@
       <c r="Q418" s="7"/>
       <c r="R418" s="7"/>
     </row>
-    <row r="419" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A419" s="11" t="s">
         <v>18</v>
       </c>
@@ -23912,7 +23370,7 @@
       <c r="Q419" s="12"/>
       <c r="R419" s="12"/>
     </row>
-    <row r="420" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A420" s="6" t="s">
         <v>18</v>
       </c>
@@ -23954,7 +23412,7 @@
       <c r="Q420" s="7"/>
       <c r="R420" s="7"/>
     </row>
-    <row r="421" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A421" s="11" t="s">
         <v>18</v>
       </c>
@@ -23998,7 +23456,7 @@
       <c r="Q421" s="12"/>
       <c r="R421" s="12"/>
     </row>
-    <row r="422" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A422" s="6" t="s">
         <v>18</v>
       </c>
@@ -24040,7 +23498,7 @@
       <c r="Q422" s="7"/>
       <c r="R422" s="7"/>
     </row>
-    <row r="423" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A423" s="11" t="s">
         <v>18</v>
       </c>
@@ -24084,7 +23542,7 @@
       <c r="Q423" s="12"/>
       <c r="R423" s="12"/>
     </row>
-    <row r="424" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A424" s="6" t="s">
         <v>18</v>
       </c>
@@ -24128,7 +23586,7 @@
       <c r="Q424" s="7"/>
       <c r="R424" s="7"/>
     </row>
-    <row r="425" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A425" s="11" t="s">
         <v>30</v>
       </c>
@@ -24174,7 +23632,7 @@
       <c r="Q425" s="12"/>
       <c r="R425" s="12"/>
     </row>
-    <row r="426" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A426" s="6" t="s">
         <v>18</v>
       </c>
@@ -24210,7 +23668,7 @@
       <c r="Q426" s="7"/>
       <c r="R426" s="7"/>
     </row>
-    <row r="427" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A427" s="11" t="s">
         <v>18</v>
       </c>
@@ -24252,7 +23710,7 @@
       <c r="Q427" s="12"/>
       <c r="R427" s="12"/>
     </row>
-    <row r="428" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A428" s="6" t="s">
         <v>18</v>
       </c>
@@ -24296,7 +23754,7 @@
       <c r="Q428" s="7"/>
       <c r="R428" s="7"/>
     </row>
-    <row r="429" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A429" s="11" t="s">
         <v>18</v>
       </c>
@@ -24340,7 +23798,7 @@
       <c r="Q429" s="12"/>
       <c r="R429" s="12"/>
     </row>
-    <row r="430" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A430" s="6" t="s">
         <v>30</v>
       </c>
@@ -24386,7 +23844,7 @@
       <c r="Q430" s="7"/>
       <c r="R430" s="7"/>
     </row>
-    <row r="431" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A431" s="11" t="s">
         <v>30</v>
       </c>
@@ -24432,7 +23890,7 @@
       <c r="Q431" s="12"/>
       <c r="R431" s="12"/>
     </row>
-    <row r="432" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A432" s="6" t="s">
         <v>18</v>
       </c>
@@ -24470,7 +23928,7 @@
       <c r="Q432" s="7"/>
       <c r="R432" s="7"/>
     </row>
-    <row r="433" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A433" s="11" t="s">
         <v>18</v>
       </c>
@@ -24514,7 +23972,7 @@
       <c r="Q433" s="12"/>
       <c r="R433" s="12"/>
     </row>
-    <row r="434" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A434" s="6" t="s">
         <v>18</v>
       </c>
@@ -24556,7 +24014,7 @@
       <c r="Q434" s="7"/>
       <c r="R434" s="7"/>
     </row>
-    <row r="435" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A435" s="11" t="s">
         <v>18</v>
       </c>
@@ -24600,7 +24058,7 @@
       <c r="Q435" s="12"/>
       <c r="R435" s="12"/>
     </row>
-    <row r="436" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A436" s="6" t="s">
         <v>18</v>
       </c>
@@ -24646,7 +24104,7 @@
       <c r="Q436" s="7"/>
       <c r="R436" s="7"/>
     </row>
-    <row r="437" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A437" s="11" t="s">
         <v>18</v>
       </c>
@@ -24684,7 +24142,7 @@
       <c r="Q437" s="12"/>
       <c r="R437" s="12"/>
     </row>
-    <row r="438" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A438" s="6" t="s">
         <v>18</v>
       </c>
@@ -24722,7 +24180,7 @@
       <c r="Q438" s="7"/>
       <c r="R438" s="7"/>
     </row>
-    <row r="439" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A439" s="11" t="s">
         <v>18</v>
       </c>
@@ -24760,7 +24218,7 @@
       <c r="Q439" s="12"/>
       <c r="R439" s="12"/>
     </row>
-    <row r="440" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A440" s="6" t="s">
         <v>18</v>
       </c>
@@ -24806,7 +24264,7 @@
       <c r="Q440" s="7"/>
       <c r="R440" s="7"/>
     </row>
-    <row r="441" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A441" s="11" t="s">
         <v>18</v>
       </c>
@@ -24850,7 +24308,7 @@
       <c r="Q441" s="12"/>
       <c r="R441" s="12"/>
     </row>
-    <row r="442" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A442" s="6" t="s">
         <v>18</v>
       </c>
@@ -24894,7 +24352,7 @@
       <c r="Q442" s="7"/>
       <c r="R442" s="7"/>
     </row>
-    <row r="443" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A443" s="11" t="s">
         <v>30</v>
       </c>
@@ -24942,7 +24400,7 @@
       </c>
       <c r="R443" s="12"/>
     </row>
-    <row r="444" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A444" s="6" t="s">
         <v>18</v>
       </c>
@@ -24984,7 +24442,7 @@
       <c r="Q444" s="7"/>
       <c r="R444" s="7"/>
     </row>
-    <row r="445" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A445" s="11" t="s">
         <v>18</v>
       </c>
@@ -25018,7 +24476,7 @@
       <c r="Q445" s="12"/>
       <c r="R445" s="12"/>
     </row>
-    <row r="446" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A446" s="6" t="s">
         <v>18</v>
       </c>
@@ -25056,7 +24514,7 @@
       <c r="Q446" s="7"/>
       <c r="R446" s="7"/>
     </row>
-    <row r="447" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A447" s="11" t="s">
         <v>18</v>
       </c>
@@ -25092,7 +24550,7 @@
       <c r="Q447" s="12"/>
       <c r="R447" s="12"/>
     </row>
-    <row r="448" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A448" s="6" t="s">
         <v>18</v>
       </c>
@@ -25136,7 +24594,7 @@
       <c r="Q448" s="7"/>
       <c r="R448" s="7"/>
     </row>
-    <row r="449" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A449" s="11" t="s">
         <v>18</v>
       </c>
@@ -25180,7 +24638,7 @@
       <c r="Q449" s="12"/>
       <c r="R449" s="12"/>
     </row>
-    <row r="450" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A450" s="6" t="s">
         <v>18</v>
       </c>
@@ -25222,7 +24680,7 @@
       <c r="Q450" s="7"/>
       <c r="R450" s="7"/>
     </row>
-    <row r="451" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A451" s="11" t="s">
         <v>18</v>
       </c>
@@ -25266,7 +24724,7 @@
       <c r="Q451" s="12"/>
       <c r="R451" s="12"/>
     </row>
-    <row r="452" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A452" s="6" t="s">
         <v>18</v>
       </c>
@@ -25310,7 +24768,7 @@
       <c r="Q452" s="7"/>
       <c r="R452" s="7"/>
     </row>
-    <row r="453" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A453" s="11" t="s">
         <v>18</v>
       </c>
@@ -25354,7 +24812,7 @@
       <c r="Q453" s="12"/>
       <c r="R453" s="12"/>
     </row>
-    <row r="454" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A454" s="6" t="s">
         <v>18</v>
       </c>
@@ -25398,7 +24856,7 @@
       <c r="Q454" s="7"/>
       <c r="R454" s="7"/>
     </row>
-    <row r="455" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A455" s="11" t="s">
         <v>18</v>
       </c>
@@ -25442,7 +24900,7 @@
       <c r="Q455" s="12"/>
       <c r="R455" s="12"/>
     </row>
-    <row r="456" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A456" s="6" t="s">
         <v>18</v>
       </c>
@@ -25484,7 +24942,7 @@
       <c r="Q456" s="7"/>
       <c r="R456" s="7"/>
     </row>
-    <row r="457" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A457" s="11" t="s">
         <v>18</v>
       </c>
@@ -25528,7 +24986,7 @@
       <c r="Q457" s="12"/>
       <c r="R457" s="12"/>
     </row>
-    <row r="458" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A458" s="6" t="s">
         <v>18</v>
       </c>
@@ -25572,7 +25030,7 @@
       <c r="Q458" s="7"/>
       <c r="R458" s="7"/>
     </row>
-    <row r="459" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A459" s="11" t="s">
         <v>18</v>
       </c>
@@ -25616,7 +25074,7 @@
       <c r="Q459" s="12"/>
       <c r="R459" s="12"/>
     </row>
-    <row r="460" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A460" s="6" t="s">
         <v>30</v>
       </c>
@@ -25664,7 +25122,7 @@
       </c>
       <c r="R460" s="7"/>
     </row>
-    <row r="461" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A461" s="11" t="s">
         <v>18</v>
       </c>
@@ -25708,7 +25166,7 @@
       <c r="Q461" s="12"/>
       <c r="R461" s="12"/>
     </row>
-    <row r="462" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A462" s="6" t="s">
         <v>18</v>
       </c>
@@ -25752,7 +25210,7 @@
       <c r="Q462" s="7"/>
       <c r="R462" s="7"/>
     </row>
-    <row r="463" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A463" s="11" t="s">
         <v>18</v>
       </c>
@@ -25786,7 +25244,7 @@
       <c r="Q463" s="12"/>
       <c r="R463" s="12"/>
     </row>
-    <row r="464" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A464" s="6" t="s">
         <v>18</v>
       </c>
@@ -25828,7 +25286,7 @@
       <c r="Q464" s="7"/>
       <c r="R464" s="7"/>
     </row>
-    <row r="465" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A465" s="11" t="s">
         <v>18</v>
       </c>
@@ -25872,7 +25330,7 @@
       <c r="Q465" s="12"/>
       <c r="R465" s="12"/>
     </row>
-    <row r="466" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A466" s="6" t="s">
         <v>18</v>
       </c>
@@ -25914,7 +25372,7 @@
       <c r="Q466" s="7"/>
       <c r="R466" s="7"/>
     </row>
-    <row r="467" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A467" s="11" t="s">
         <v>18</v>
       </c>
@@ -25956,7 +25414,7 @@
       <c r="Q467" s="12"/>
       <c r="R467" s="12"/>
     </row>
-    <row r="468" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A468" s="6" t="s">
         <v>18</v>
       </c>
@@ -26000,7 +25458,7 @@
       <c r="Q468" s="7"/>
       <c r="R468" s="7"/>
     </row>
-    <row r="469" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A469" s="11" t="s">
         <v>18</v>
       </c>
@@ -26044,7 +25502,7 @@
       <c r="Q469" s="12"/>
       <c r="R469" s="12"/>
     </row>
-    <row r="470" spans="1:18" s="1" customFormat="1" ht="92.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" s="1" customFormat="1" ht="138.1247" customHeight="1">
       <c r="A470" s="6" t="s">
         <v>18</v>
       </c>
@@ -26086,7 +25544,7 @@
       <c r="Q470" s="7"/>
       <c r="R470" s="7"/>
     </row>
-    <row r="471" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A471" s="11" t="s">
         <v>18</v>
       </c>
@@ -26124,7 +25582,7 @@
       <c r="Q471" s="12"/>
       <c r="R471" s="12"/>
     </row>
-    <row r="472" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A472" s="6" t="s">
         <v>18</v>
       </c>
@@ -26162,7 +25620,7 @@
       <c r="Q472" s="7"/>
       <c r="R472" s="7"/>
     </row>
-    <row r="473" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A473" s="11" t="s">
         <v>18</v>
       </c>
@@ -26204,7 +25662,7 @@
       <c r="Q473" s="12"/>
       <c r="R473" s="12"/>
     </row>
-    <row r="474" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A474" s="6" t="s">
         <v>18</v>
       </c>
@@ -26242,7 +25700,7 @@
       <c r="Q474" s="7"/>
       <c r="R474" s="7"/>
     </row>
-    <row r="475" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A475" s="11" t="s">
         <v>18</v>
       </c>
@@ -26282,7 +25740,7 @@
       <c r="Q475" s="12"/>
       <c r="R475" s="12"/>
     </row>
-    <row r="476" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A476" s="6" t="s">
         <v>30</v>
       </c>
@@ -26332,7 +25790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="477" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A477" s="11" t="s">
         <v>18</v>
       </c>
@@ -26368,7 +25826,7 @@
       <c r="Q477" s="12"/>
       <c r="R477" s="12"/>
     </row>
-    <row r="478" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A478" s="6" t="s">
         <v>18</v>
       </c>
@@ -26412,7 +25870,7 @@
       <c r="Q478" s="7"/>
       <c r="R478" s="7"/>
     </row>
-    <row r="479" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A479" s="11" t="s">
         <v>18</v>
       </c>
@@ -26456,7 +25914,7 @@
       <c r="Q479" s="12"/>
       <c r="R479" s="12"/>
     </row>
-    <row r="480" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A480" s="6" t="s">
         <v>18</v>
       </c>
@@ -26500,7 +25958,7 @@
       <c r="Q480" s="7"/>
       <c r="R480" s="7"/>
     </row>
-    <row r="481" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A481" s="11" t="s">
         <v>18</v>
       </c>
@@ -26538,7 +25996,7 @@
       <c r="Q481" s="12"/>
       <c r="R481" s="12"/>
     </row>
-    <row r="482" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A482" s="6" t="s">
         <v>30</v>
       </c>
@@ -26584,7 +26042,7 @@
       <c r="Q482" s="7"/>
       <c r="R482" s="7"/>
     </row>
-    <row r="483" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A483" s="11" t="s">
         <v>18</v>
       </c>
@@ -26628,7 +26086,7 @@
       <c r="Q483" s="12"/>
       <c r="R483" s="12"/>
     </row>
-    <row r="484" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A484" s="6" t="s">
         <v>30</v>
       </c>
@@ -26674,7 +26132,7 @@
       <c r="Q484" s="7"/>
       <c r="R484" s="7"/>
     </row>
-    <row r="485" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A485" s="11" t="s">
         <v>18</v>
       </c>
@@ -26718,7 +26176,7 @@
       <c r="Q485" s="12"/>
       <c r="R485" s="12"/>
     </row>
-    <row r="486" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A486" s="6" t="s">
         <v>18</v>
       </c>
@@ -26762,7 +26220,7 @@
       <c r="Q486" s="7"/>
       <c r="R486" s="7"/>
     </row>
-    <row r="487" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A487" s="11" t="s">
         <v>30</v>
       </c>
@@ -26806,7 +26264,7 @@
       <c r="Q487" s="12"/>
       <c r="R487" s="12"/>
     </row>
-    <row r="488" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A488" s="6" t="s">
         <v>18</v>
       </c>
@@ -26844,7 +26302,7 @@
       <c r="Q488" s="7"/>
       <c r="R488" s="7"/>
     </row>
-    <row r="489" spans="1:18" s="1" customFormat="1" ht="63.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" s="1" customFormat="1" ht="94.9274" customHeight="1">
       <c r="A489" s="11" t="s">
         <v>18</v>
       </c>
@@ -26888,7 +26346,7 @@
       <c r="Q489" s="12"/>
       <c r="R489" s="12"/>
     </row>
-    <row r="490" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A490" s="6" t="s">
         <v>30</v>
       </c>
@@ -26936,7 +26394,7 @@
       <c r="Q490" s="7"/>
       <c r="R490" s="7"/>
     </row>
-    <row r="491" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A491" s="11" t="s">
         <v>18</v>
       </c>
@@ -26980,7 +26438,7 @@
       <c r="Q491" s="12"/>
       <c r="R491" s="12"/>
     </row>
-    <row r="492" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A492" s="6" t="s">
         <v>18</v>
       </c>
@@ -27024,7 +26482,7 @@
       <c r="Q492" s="7"/>
       <c r="R492" s="7"/>
     </row>
-    <row r="493" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A493" s="11" t="s">
         <v>18</v>
       </c>
@@ -27068,7 +26526,7 @@
       <c r="Q493" s="12"/>
       <c r="R493" s="12"/>
     </row>
-    <row r="494" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A494" s="6" t="s">
         <v>30</v>
       </c>
@@ -27114,7 +26572,7 @@
       <c r="Q494" s="7"/>
       <c r="R494" s="7"/>
     </row>
-    <row r="495" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A495" s="11" t="s">
         <v>30</v>
       </c>
@@ -27162,7 +26620,7 @@
       <c r="Q495" s="12"/>
       <c r="R495" s="12"/>
     </row>
-    <row r="496" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A496" s="6" t="s">
         <v>18</v>
       </c>
@@ -27200,7 +26658,7 @@
       <c r="Q496" s="7"/>
       <c r="R496" s="7"/>
     </row>
-    <row r="497" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A497" s="11" t="s">
         <v>18</v>
       </c>
@@ -27238,7 +26696,7 @@
       <c r="Q497" s="12"/>
       <c r="R497" s="12"/>
     </row>
-    <row r="498" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A498" s="6" t="s">
         <v>30</v>
       </c>
@@ -27284,7 +26742,7 @@
       <c r="Q498" s="7"/>
       <c r="R498" s="7"/>
     </row>
-    <row r="499" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A499" s="11" t="s">
         <v>18</v>
       </c>
@@ -27322,7 +26780,7 @@
       <c r="Q499" s="12"/>
       <c r="R499" s="12"/>
     </row>
-    <row r="500" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A500" s="6" t="s">
         <v>18</v>
       </c>
@@ -27360,7 +26818,7 @@
       <c r="Q500" s="7"/>
       <c r="R500" s="7"/>
     </row>
-    <row r="501" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A501" s="11" t="s">
         <v>18</v>
       </c>
@@ -27398,7 +26856,7 @@
       <c r="Q501" s="12"/>
       <c r="R501" s="12"/>
     </row>
-    <row r="502" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A502" s="6" t="s">
         <v>18</v>
       </c>
@@ -27436,7 +26894,7 @@
       <c r="Q502" s="7"/>
       <c r="R502" s="7"/>
     </row>
-    <row r="503" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A503" s="11" t="s">
         <v>18</v>
       </c>
@@ -27480,7 +26938,7 @@
       <c r="Q503" s="12"/>
       <c r="R503" s="12"/>
     </row>
-    <row r="504" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A504" s="6" t="s">
         <v>18</v>
       </c>
@@ -27524,7 +26982,7 @@
       <c r="Q504" s="7"/>
       <c r="R504" s="7"/>
     </row>
-    <row r="505" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A505" s="11" t="s">
         <v>18</v>
       </c>
@@ -27566,7 +27024,7 @@
       <c r="Q505" s="12"/>
       <c r="R505" s="12"/>
     </row>
-    <row r="506" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A506" s="6" t="s">
         <v>18</v>
       </c>
@@ -27610,7 +27068,7 @@
       <c r="Q506" s="7"/>
       <c r="R506" s="7"/>
     </row>
-    <row r="507" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A507" s="11" t="s">
         <v>18</v>
       </c>
@@ -27654,7 +27112,7 @@
       <c r="Q507" s="12"/>
       <c r="R507" s="12"/>
     </row>
-    <row r="508" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A508" s="6" t="s">
         <v>18</v>
       </c>
@@ -27698,7 +27156,7 @@
       <c r="Q508" s="7"/>
       <c r="R508" s="7"/>
     </row>
-    <row r="509" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A509" s="11" t="s">
         <v>30</v>
       </c>
@@ -27746,7 +27204,7 @@
       <c r="Q509" s="12"/>
       <c r="R509" s="12"/>
     </row>
-    <row r="510" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A510" s="6" t="s">
         <v>18</v>
       </c>
@@ -27790,7 +27248,7 @@
       <c r="Q510" s="7"/>
       <c r="R510" s="7"/>
     </row>
-    <row r="511" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A511" s="11" t="s">
         <v>18</v>
       </c>
@@ -27834,7 +27292,7 @@
       <c r="Q511" s="12"/>
       <c r="R511" s="12"/>
     </row>
-    <row r="512" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A512" s="6" t="s">
         <v>30</v>
       </c>
@@ -27882,7 +27340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="513" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A513" s="11" t="s">
         <v>18</v>
       </c>
@@ -27920,7 +27378,7 @@
       <c r="Q513" s="12"/>
       <c r="R513" s="12"/>
     </row>
-    <row r="514" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A514" s="6" t="s">
         <v>18</v>
       </c>
@@ -27956,7 +27414,7 @@
       <c r="Q514" s="7"/>
       <c r="R514" s="7"/>
     </row>
-    <row r="515" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A515" s="11" t="s">
         <v>18</v>
       </c>
@@ -28000,7 +27458,7 @@
       <c r="Q515" s="12"/>
       <c r="R515" s="12"/>
     </row>
-    <row r="516" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A516" s="6" t="s">
         <v>18</v>
       </c>
@@ -28036,7 +27494,7 @@
       <c r="Q516" s="7"/>
       <c r="R516" s="7"/>
     </row>
-    <row r="517" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A517" s="11" t="s">
         <v>18</v>
       </c>
@@ -28080,7 +27538,7 @@
       <c r="Q517" s="12"/>
       <c r="R517" s="12"/>
     </row>
-    <row r="518" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A518" s="6" t="s">
         <v>18</v>
       </c>
@@ -28124,7 +27582,7 @@
       <c r="Q518" s="7"/>
       <c r="R518" s="7"/>
     </row>
-    <row r="519" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A519" s="11" t="s">
         <v>18</v>
       </c>
@@ -28168,7 +27626,7 @@
       <c r="Q519" s="12"/>
       <c r="R519" s="12"/>
     </row>
-    <row r="520" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A520" s="6" t="s">
         <v>18</v>
       </c>
@@ -28212,7 +27670,7 @@
       <c r="Q520" s="7"/>
       <c r="R520" s="7"/>
     </row>
-    <row r="521" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A521" s="11" t="s">
         <v>18</v>
       </c>
@@ -28256,7 +27714,7 @@
       <c r="Q521" s="12"/>
       <c r="R521" s="12"/>
     </row>
-    <row r="522" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A522" s="6" t="s">
         <v>18</v>
       </c>
@@ -28300,7 +27758,7 @@
       <c r="Q522" s="7"/>
       <c r="R522" s="7"/>
     </row>
-    <row r="523" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A523" s="11" t="s">
         <v>30</v>
       </c>
@@ -28346,11 +27804,11 @@
       <c r="Q523" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="R523" s="20" t="s">
+      <c r="R523" s="21" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="524" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A524" s="6" t="s">
         <v>18</v>
       </c>
@@ -28394,7 +27852,7 @@
       <c r="Q524" s="7"/>
       <c r="R524" s="7"/>
     </row>
-    <row r="525" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A525" s="11" t="s">
         <v>18</v>
       </c>
@@ -28438,7 +27896,7 @@
       <c r="Q525" s="12"/>
       <c r="R525" s="12"/>
     </row>
-    <row r="526" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A526" s="6" t="s">
         <v>30</v>
       </c>
@@ -28486,7 +27944,7 @@
       <c r="Q526" s="7"/>
       <c r="R526" s="7"/>
     </row>
-    <row r="527" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A527" s="11" t="s">
         <v>139</v>
       </c>
@@ -28532,7 +27990,7 @@
       </c>
       <c r="R527" s="12"/>
     </row>
-    <row r="528" spans="1:18" s="1" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" s="1" customFormat="1" ht="127.4587" customHeight="1">
       <c r="A528" s="6" t="s">
         <v>18</v>
       </c>
@@ -28576,7 +28034,7 @@
       <c r="Q528" s="7"/>
       <c r="R528" s="7"/>
     </row>
-    <row r="529" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A529" s="11" t="s">
         <v>30</v>
       </c>
@@ -28624,7 +28082,7 @@
       <c r="Q529" s="12"/>
       <c r="R529" s="12"/>
     </row>
-    <row r="530" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A530" s="6" t="s">
         <v>18</v>
       </c>
@@ -28670,7 +28128,7 @@
       <c r="Q530" s="7"/>
       <c r="R530" s="7"/>
     </row>
-    <row r="531" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A531" s="11" t="s">
         <v>30</v>
       </c>
@@ -28718,7 +28176,7 @@
       <c r="Q531" s="12"/>
       <c r="R531" s="12"/>
     </row>
-    <row r="532" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A532" s="6" t="s">
         <v>30</v>
       </c>
@@ -28764,7 +28222,7 @@
       <c r="Q532" s="7"/>
       <c r="R532" s="7"/>
     </row>
-    <row r="533" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A533" s="11" t="s">
         <v>30</v>
       </c>
@@ -28814,7 +28272,7 @@
       </c>
       <c r="R533" s="12"/>
     </row>
-    <row r="534" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A534" s="6" t="s">
         <v>139</v>
       </c>
@@ -28862,7 +28320,7 @@
       </c>
       <c r="R534" s="7"/>
     </row>
-    <row r="535" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A535" s="11" t="s">
         <v>139</v>
       </c>
@@ -28910,7 +28368,7 @@
       </c>
       <c r="R535" s="12"/>
     </row>
-    <row r="536" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A536" s="6" t="s">
         <v>18</v>
       </c>
@@ -28952,7 +28410,7 @@
       <c r="Q536" s="7"/>
       <c r="R536" s="7"/>
     </row>
-    <row r="537" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A537" s="11" t="s">
         <v>18</v>
       </c>
@@ -28994,7 +28452,7 @@
       <c r="Q537" s="12"/>
       <c r="R537" s="12"/>
     </row>
-    <row r="538" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A538" s="6" t="s">
         <v>18</v>
       </c>
@@ -29036,7 +28494,7 @@
       <c r="Q538" s="7"/>
       <c r="R538" s="7"/>
     </row>
-    <row r="539" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A539" s="11" t="s">
         <v>18</v>
       </c>
@@ -29072,7 +28530,7 @@
       <c r="Q539" s="12"/>
       <c r="R539" s="12"/>
     </row>
-    <row r="540" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A540" s="6" t="s">
         <v>18</v>
       </c>
@@ -29114,7 +28572,7 @@
       <c r="Q540" s="7"/>
       <c r="R540" s="7"/>
     </row>
-    <row r="541" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A541" s="11" t="s">
         <v>18</v>
       </c>
@@ -29158,7 +28616,7 @@
       <c r="Q541" s="12"/>
       <c r="R541" s="12"/>
     </row>
-    <row r="542" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A542" s="6" t="s">
         <v>18</v>
       </c>
@@ -29196,7 +28654,7 @@
       <c r="Q542" s="7"/>
       <c r="R542" s="7"/>
     </row>
-    <row r="543" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A543" s="11" t="s">
         <v>18</v>
       </c>
@@ -29240,7 +28698,7 @@
       <c r="Q543" s="12"/>
       <c r="R543" s="12"/>
     </row>
-    <row r="544" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A544" s="6" t="s">
         <v>18</v>
       </c>
@@ -29284,7 +28742,7 @@
       <c r="Q544" s="7"/>
       <c r="R544" s="7"/>
     </row>
-    <row r="545" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A545" s="11" t="s">
         <v>18</v>
       </c>
@@ -29328,7 +28786,7 @@
       <c r="Q545" s="12"/>
       <c r="R545" s="12"/>
     </row>
-    <row r="546" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A546" s="6" t="s">
         <v>30</v>
       </c>
@@ -29376,7 +28834,7 @@
       </c>
       <c r="R546" s="7"/>
     </row>
-    <row r="547" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A547" s="11" t="s">
         <v>18</v>
       </c>
@@ -29412,7 +28870,7 @@
       <c r="Q547" s="12"/>
       <c r="R547" s="12"/>
     </row>
-    <row r="548" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A548" s="6" t="s">
         <v>18</v>
       </c>
@@ -29446,7 +28904,7 @@
       <c r="Q548" s="7"/>
       <c r="R548" s="7"/>
     </row>
-    <row r="549" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A549" s="11" t="s">
         <v>18</v>
       </c>
@@ -29488,7 +28946,7 @@
       <c r="Q549" s="12"/>
       <c r="R549" s="12"/>
     </row>
-    <row r="550" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A550" s="6" t="s">
         <v>18</v>
       </c>
@@ -29532,7 +28990,7 @@
       <c r="Q550" s="7"/>
       <c r="R550" s="7"/>
     </row>
-    <row r="551" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A551" s="11" t="s">
         <v>18</v>
       </c>
@@ -29574,7 +29032,7 @@
       <c r="Q551" s="12"/>
       <c r="R551" s="12"/>
     </row>
-    <row r="552" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A552" s="6" t="s">
         <v>18</v>
       </c>
@@ -29616,7 +29074,7 @@
       <c r="Q552" s="7"/>
       <c r="R552" s="7"/>
     </row>
-    <row r="553" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A553" s="11" t="s">
         <v>18</v>
       </c>
@@ -29654,7 +29112,7 @@
       <c r="Q553" s="12"/>
       <c r="R553" s="12"/>
     </row>
-    <row r="554" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A554" s="6" t="s">
         <v>18</v>
       </c>
@@ -29698,7 +29156,7 @@
       <c r="Q554" s="7"/>
       <c r="R554" s="7"/>
     </row>
-    <row r="555" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A555" s="11" t="s">
         <v>30</v>
       </c>
@@ -29746,7 +29204,7 @@
       </c>
       <c r="R555" s="12"/>
     </row>
-    <row r="556" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A556" s="6" t="s">
         <v>18</v>
       </c>
@@ -29788,7 +29246,7 @@
       <c r="Q556" s="7"/>
       <c r="R556" s="7"/>
     </row>
-    <row r="557" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A557" s="11" t="s">
         <v>18</v>
       </c>
@@ -29832,7 +29290,7 @@
       <c r="Q557" s="12"/>
       <c r="R557" s="12"/>
     </row>
-    <row r="558" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A558" s="6" t="s">
         <v>18</v>
       </c>
@@ -29870,7 +29328,7 @@
       <c r="Q558" s="7"/>
       <c r="R558" s="7"/>
     </row>
-    <row r="559" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A559" s="11" t="s">
         <v>18</v>
       </c>
@@ -29916,7 +29374,7 @@
       <c r="Q559" s="12"/>
       <c r="R559" s="12"/>
     </row>
-    <row r="560" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A560" s="6" t="s">
         <v>18</v>
       </c>
@@ -29960,7 +29418,7 @@
       <c r="Q560" s="7"/>
       <c r="R560" s="7"/>
     </row>
-    <row r="561" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A561" s="11" t="s">
         <v>18</v>
       </c>
@@ -30004,7 +29462,7 @@
       <c r="Q561" s="12"/>
       <c r="R561" s="12"/>
     </row>
-    <row r="562" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A562" s="6" t="s">
         <v>30</v>
       </c>
@@ -30054,7 +29512,7 @@
       </c>
       <c r="R562" s="7"/>
     </row>
-    <row r="563" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A563" s="11" t="s">
         <v>30</v>
       </c>
@@ -30102,7 +29560,7 @@
       </c>
       <c r="R563" s="12"/>
     </row>
-    <row r="564" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A564" s="6" t="s">
         <v>139</v>
       </c>
@@ -30148,7 +29606,7 @@
       </c>
       <c r="R564" s="7"/>
     </row>
-    <row r="565" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A565" s="11" t="s">
         <v>18</v>
       </c>
@@ -30184,7 +29642,7 @@
       <c r="Q565" s="12"/>
       <c r="R565" s="12"/>
     </row>
-    <row r="566" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A566" s="6" t="s">
         <v>18</v>
       </c>
@@ -30226,7 +29684,7 @@
       <c r="Q566" s="7"/>
       <c r="R566" s="7"/>
     </row>
-    <row r="567" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A567" s="11" t="s">
         <v>18</v>
       </c>
@@ -30268,7 +29726,7 @@
       <c r="Q567" s="12"/>
       <c r="R567" s="12"/>
     </row>
-    <row r="568" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A568" s="6" t="s">
         <v>18</v>
       </c>
@@ -30302,7 +29760,7 @@
       <c r="Q568" s="7"/>
       <c r="R568" s="7"/>
     </row>
-    <row r="569" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A569" s="11" t="s">
         <v>18</v>
       </c>
@@ -30344,7 +29802,7 @@
       <c r="Q569" s="12"/>
       <c r="R569" s="12"/>
     </row>
-    <row r="570" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A570" s="6" t="s">
         <v>18</v>
       </c>
@@ -30386,7 +29844,7 @@
       <c r="Q570" s="7"/>
       <c r="R570" s="7"/>
     </row>
-    <row r="571" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A571" s="11" t="s">
         <v>18</v>
       </c>
@@ -30428,7 +29886,7 @@
       <c r="Q571" s="12"/>
       <c r="R571" s="12"/>
     </row>
-    <row r="572" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A572" s="6" t="s">
         <v>18</v>
       </c>
@@ -30468,7 +29926,7 @@
       <c r="Q572" s="7"/>
       <c r="R572" s="7"/>
     </row>
-    <row r="573" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A573" s="11" t="s">
         <v>18</v>
       </c>
@@ -30512,7 +29970,7 @@
       <c r="Q573" s="12"/>
       <c r="R573" s="12"/>
     </row>
-    <row r="574" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A574" s="6" t="s">
         <v>18</v>
       </c>
@@ -30548,7 +30006,7 @@
       <c r="Q574" s="7"/>
       <c r="R574" s="7"/>
     </row>
-    <row r="575" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A575" s="11" t="s">
         <v>18</v>
       </c>
@@ -30584,7 +30042,7 @@
       <c r="Q575" s="12"/>
       <c r="R575" s="12"/>
     </row>
-    <row r="576" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A576" s="6" t="s">
         <v>18</v>
       </c>
@@ -30628,7 +30086,7 @@
       <c r="Q576" s="7"/>
       <c r="R576" s="7"/>
     </row>
-    <row r="577" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A577" s="11" t="s">
         <v>18</v>
       </c>
@@ -30672,7 +30130,7 @@
       <c r="Q577" s="12"/>
       <c r="R577" s="12"/>
     </row>
-    <row r="578" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A578" s="6" t="s">
         <v>18</v>
       </c>
@@ -30710,7 +30168,7 @@
       <c r="Q578" s="7"/>
       <c r="R578" s="7"/>
     </row>
-    <row r="579" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A579" s="11" t="s">
         <v>18</v>
       </c>
@@ -30754,7 +30212,7 @@
       <c r="Q579" s="12"/>
       <c r="R579" s="12"/>
     </row>
-    <row r="580" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A580" s="6" t="s">
         <v>18</v>
       </c>
@@ -30796,7 +30254,7 @@
       <c r="Q580" s="7"/>
       <c r="R580" s="7"/>
     </row>
-    <row r="581" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A581" s="11" t="s">
         <v>18</v>
       </c>
@@ -30840,7 +30298,7 @@
       <c r="Q581" s="12"/>
       <c r="R581" s="12"/>
     </row>
-    <row r="582" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A582" s="6" t="s">
         <v>18</v>
       </c>
@@ -30878,7 +30336,7 @@
       <c r="Q582" s="7"/>
       <c r="R582" s="7"/>
     </row>
-    <row r="583" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A583" s="11" t="s">
         <v>18</v>
       </c>
@@ -30920,7 +30378,7 @@
       <c r="Q583" s="12"/>
       <c r="R583" s="12"/>
     </row>
-    <row r="584" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A584" s="6" t="s">
         <v>18</v>
       </c>
@@ -30962,7 +30420,7 @@
       <c r="Q584" s="7"/>
       <c r="R584" s="7"/>
     </row>
-    <row r="585" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A585" s="11" t="s">
         <v>30</v>
       </c>
@@ -31010,7 +30468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="586" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A586" s="6" t="s">
         <v>18</v>
       </c>
@@ -31052,7 +30510,7 @@
       <c r="Q586" s="7"/>
       <c r="R586" s="7"/>
     </row>
-    <row r="587" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A587" s="11" t="s">
         <v>18</v>
       </c>
@@ -31094,7 +30552,7 @@
       <c r="Q587" s="12"/>
       <c r="R587" s="12"/>
     </row>
-    <row r="588" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A588" s="6" t="s">
         <v>18</v>
       </c>
@@ -31138,7 +30596,7 @@
       <c r="Q588" s="7"/>
       <c r="R588" s="7"/>
     </row>
-    <row r="589" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A589" s="11" t="s">
         <v>18</v>
       </c>
@@ -31180,7 +30638,7 @@
       <c r="Q589" s="12"/>
       <c r="R589" s="12"/>
     </row>
-    <row r="590" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A590" s="6" t="s">
         <v>18</v>
       </c>
@@ -31220,7 +30678,7 @@
       <c r="Q590" s="7"/>
       <c r="R590" s="7"/>
     </row>
-    <row r="591" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A591" s="11" t="s">
         <v>18</v>
       </c>
@@ -31258,7 +30716,7 @@
       <c r="Q591" s="12"/>
       <c r="R591" s="12"/>
     </row>
-    <row r="592" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A592" s="6" t="s">
         <v>18</v>
       </c>
@@ -31296,7 +30754,7 @@
       <c r="Q592" s="7"/>
       <c r="R592" s="7"/>
     </row>
-    <row r="593" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A593" s="11" t="s">
         <v>18</v>
       </c>
@@ -31340,7 +30798,7 @@
       <c r="Q593" s="12"/>
       <c r="R593" s="12"/>
     </row>
-    <row r="594" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A594" s="6" t="s">
         <v>18</v>
       </c>
@@ -31382,7 +30840,7 @@
       <c r="Q594" s="7"/>
       <c r="R594" s="7"/>
     </row>
-    <row r="595" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A595" s="11" t="s">
         <v>30</v>
       </c>
@@ -31432,7 +30890,7 @@
       </c>
       <c r="R595" s="12"/>
     </row>
-    <row r="596" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A596" s="6" t="s">
         <v>18</v>
       </c>
@@ -31476,7 +30934,7 @@
       <c r="Q596" s="7"/>
       <c r="R596" s="7"/>
     </row>
-    <row r="597" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A597" s="11" t="s">
         <v>18</v>
       </c>
@@ -31518,7 +30976,7 @@
       <c r="Q597" s="12"/>
       <c r="R597" s="12"/>
     </row>
-    <row r="598" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A598" s="6" t="s">
         <v>18</v>
       </c>
@@ -31562,7 +31020,7 @@
       <c r="Q598" s="7"/>
       <c r="R598" s="7"/>
     </row>
-    <row r="599" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A599" s="11" t="s">
         <v>18</v>
       </c>
@@ -31604,7 +31062,7 @@
       <c r="Q599" s="12"/>
       <c r="R599" s="12"/>
     </row>
-    <row r="600" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A600" s="6" t="s">
         <v>18</v>
       </c>
@@ -31646,7 +31104,7 @@
       <c r="Q600" s="7"/>
       <c r="R600" s="7"/>
     </row>
-    <row r="601" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A601" s="11" t="s">
         <v>18</v>
       </c>
@@ -31684,7 +31142,7 @@
       <c r="Q601" s="12"/>
       <c r="R601" s="12"/>
     </row>
-    <row r="602" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A602" s="6" t="s">
         <v>18</v>
       </c>
@@ -31728,7 +31186,7 @@
       <c r="Q602" s="7"/>
       <c r="R602" s="7"/>
     </row>
-    <row r="603" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A603" s="11" t="s">
         <v>18</v>
       </c>
@@ -31772,7 +31230,7 @@
       <c r="Q603" s="12"/>
       <c r="R603" s="12"/>
     </row>
-    <row r="604" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A604" s="6" t="s">
         <v>18</v>
       </c>
@@ -31816,7 +31274,7 @@
       <c r="Q604" s="7"/>
       <c r="R604" s="7"/>
     </row>
-    <row r="605" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A605" s="11" t="s">
         <v>18</v>
       </c>
@@ -31858,7 +31316,7 @@
       <c r="Q605" s="12"/>
       <c r="R605" s="12"/>
     </row>
-    <row r="606" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A606" s="6" t="s">
         <v>18</v>
       </c>
@@ -31900,7 +31358,7 @@
       <c r="Q606" s="7"/>
       <c r="R606" s="7"/>
     </row>
-    <row r="607" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A607" s="11" t="s">
         <v>18</v>
       </c>
@@ -31938,7 +31396,7 @@
       <c r="Q607" s="12"/>
       <c r="R607" s="12"/>
     </row>
-    <row r="608" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A608" s="6" t="s">
         <v>18</v>
       </c>
@@ -31976,7 +31434,7 @@
       <c r="Q608" s="7"/>
       <c r="R608" s="7"/>
     </row>
-    <row r="609" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A609" s="11" t="s">
         <v>18</v>
       </c>
@@ -32020,7 +31478,7 @@
       <c r="Q609" s="12"/>
       <c r="R609" s="12"/>
     </row>
-    <row r="610" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A610" s="6" t="s">
         <v>18</v>
       </c>
@@ -32064,7 +31522,7 @@
       <c r="Q610" s="7"/>
       <c r="R610" s="7"/>
     </row>
-    <row r="611" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A611" s="11" t="s">
         <v>18</v>
       </c>
@@ -32106,7 +31564,7 @@
       <c r="Q611" s="12"/>
       <c r="R611" s="12"/>
     </row>
-    <row r="612" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A612" s="6" t="s">
         <v>18</v>
       </c>
@@ -32146,7 +31604,7 @@
       <c r="Q612" s="7"/>
       <c r="R612" s="7"/>
     </row>
-    <row r="613" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A613" s="11" t="s">
         <v>18</v>
       </c>
@@ -32182,7 +31640,7 @@
       <c r="Q613" s="12"/>
       <c r="R613" s="12"/>
     </row>
-    <row r="614" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A614" s="6" t="s">
         <v>18</v>
       </c>
@@ -32220,7 +31678,7 @@
       <c r="Q614" s="7"/>
       <c r="R614" s="7"/>
     </row>
-    <row r="615" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A615" s="11" t="s">
         <v>18</v>
       </c>
@@ -32258,7 +31716,7 @@
       <c r="Q615" s="12"/>
       <c r="R615" s="12"/>
     </row>
-    <row r="616" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A616" s="6" t="s">
         <v>18</v>
       </c>
@@ -32296,7 +31754,7 @@
       <c r="Q616" s="7"/>
       <c r="R616" s="7"/>
     </row>
-    <row r="617" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A617" s="11" t="s">
         <v>18</v>
       </c>
@@ -32332,7 +31790,7 @@
       <c r="Q617" s="12"/>
       <c r="R617" s="12"/>
     </row>
-    <row r="618" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A618" s="6" t="s">
         <v>18</v>
       </c>
@@ -32378,7 +31836,7 @@
       <c r="Q618" s="7"/>
       <c r="R618" s="7"/>
     </row>
-    <row r="619" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A619" s="11" t="s">
         <v>18</v>
       </c>
@@ -32424,7 +31882,7 @@
       <c r="Q619" s="12"/>
       <c r="R619" s="12"/>
     </row>
-    <row r="620" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A620" s="6" t="s">
         <v>18</v>
       </c>
@@ -32470,7 +31928,7 @@
       <c r="Q620" s="7"/>
       <c r="R620" s="7"/>
     </row>
-    <row r="621" spans="1:18" s="1" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" s="1" customFormat="1" ht="84.2614" customHeight="1">
       <c r="A621" s="11" t="s">
         <v>30</v>
       </c>
@@ -32520,7 +31978,7 @@
       </c>
       <c r="R621" s="12"/>
     </row>
-    <row r="622" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A622" s="6" t="s">
         <v>139</v>
       </c>
@@ -32561,7 +32019,7 @@
       <c r="N622" s="15" t="s">
         <v>1715</v>
       </c>
-      <c r="O622" s="22" t="s">
+      <c r="O622" s="25" t="s">
         <v>1716</v>
       </c>
       <c r="P622" s="16" t="s">
@@ -32572,7 +32030,7 @@
       </c>
       <c r="R622" s="7"/>
     </row>
-    <row r="623" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A623" s="11" t="s">
         <v>18</v>
       </c>
@@ -32608,7 +32066,7 @@
       <c r="Q623" s="12"/>
       <c r="R623" s="12"/>
     </row>
-    <row r="624" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A624" s="6" t="s">
         <v>18</v>
       </c>
@@ -32650,7 +32108,7 @@
       <c r="Q624" s="7"/>
       <c r="R624" s="7"/>
     </row>
-    <row r="625" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A625" s="11" t="s">
         <v>18</v>
       </c>
@@ -32684,7 +32142,7 @@
       <c r="Q625" s="12"/>
       <c r="R625" s="12"/>
     </row>
-    <row r="626" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A626" s="6" t="s">
         <v>18</v>
       </c>
@@ -32728,7 +32186,7 @@
       <c r="Q626" s="7"/>
       <c r="R626" s="7"/>
     </row>
-    <row r="627" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A627" s="11" t="s">
         <v>18</v>
       </c>
@@ -32772,7 +32230,7 @@
       <c r="Q627" s="12"/>
       <c r="R627" s="12"/>
     </row>
-    <row r="628" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A628" s="6" t="s">
         <v>18</v>
       </c>
@@ -32816,7 +32274,7 @@
       <c r="Q628" s="7"/>
       <c r="R628" s="7"/>
     </row>
-    <row r="629" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A629" s="11" t="s">
         <v>18</v>
       </c>
@@ -32860,7 +32318,7 @@
       <c r="Q629" s="12"/>
       <c r="R629" s="12"/>
     </row>
-    <row r="630" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A630" s="6" t="s">
         <v>18</v>
       </c>
@@ -32904,7 +32362,7 @@
       <c r="Q630" s="7"/>
       <c r="R630" s="7"/>
     </row>
-    <row r="631" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A631" s="11" t="s">
         <v>30</v>
       </c>
@@ -32948,7 +32406,7 @@
       <c r="Q631" s="12"/>
       <c r="R631" s="12"/>
     </row>
-    <row r="632" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A632" s="6" t="s">
         <v>18</v>
       </c>
@@ -32986,7 +32444,7 @@
       <c r="Q632" s="7"/>
       <c r="R632" s="7"/>
     </row>
-    <row r="633" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A633" s="11" t="s">
         <v>18</v>
       </c>
@@ -33028,7 +32486,7 @@
       <c r="Q633" s="12"/>
       <c r="R633" s="12"/>
     </row>
-    <row r="634" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A634" s="6" t="s">
         <v>18</v>
       </c>
@@ -33070,7 +32528,7 @@
       <c r="Q634" s="7"/>
       <c r="R634" s="7"/>
     </row>
-    <row r="635" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A635" s="11" t="s">
         <v>18</v>
       </c>
@@ -33114,7 +32572,7 @@
       <c r="Q635" s="12"/>
       <c r="R635" s="12"/>
     </row>
-    <row r="636" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A636" s="6" t="s">
         <v>18</v>
       </c>
@@ -33156,7 +32614,7 @@
       <c r="Q636" s="7"/>
       <c r="R636" s="7"/>
     </row>
-    <row r="637" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A637" s="11" t="s">
         <v>18</v>
       </c>
@@ -33200,7 +32658,7 @@
       <c r="Q637" s="12"/>
       <c r="R637" s="12"/>
     </row>
-    <row r="638" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A638" s="6" t="s">
         <v>18</v>
       </c>
@@ -33244,7 +32702,7 @@
       <c r="Q638" s="7"/>
       <c r="R638" s="7"/>
     </row>
-    <row r="639" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A639" s="11" t="s">
         <v>18</v>
       </c>
@@ -33288,7 +32746,7 @@
       <c r="Q639" s="12"/>
       <c r="R639" s="12"/>
     </row>
-    <row r="640" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A640" s="6" t="s">
         <v>30</v>
       </c>
@@ -33334,7 +32792,7 @@
       <c r="Q640" s="7"/>
       <c r="R640" s="7"/>
     </row>
-    <row r="641" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A641" s="11" t="s">
         <v>18</v>
       </c>
@@ -33378,7 +32836,7 @@
       <c r="Q641" s="12"/>
       <c r="R641" s="12"/>
     </row>
-    <row r="642" spans="1:18" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" s="1" customFormat="1" ht="41.0641" customHeight="1">
       <c r="A642" s="6" t="s">
         <v>18</v>
       </c>
@@ -33422,7 +32880,7 @@
       <c r="Q642" s="7"/>
       <c r="R642" s="7"/>
     </row>
-    <row r="643" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A643" s="11" t="s">
         <v>18</v>
       </c>
@@ -33466,7 +32924,7 @@
       <c r="Q643" s="12"/>
       <c r="R643" s="12"/>
     </row>
-    <row r="644" spans="1:18" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" s="1" customFormat="1" ht="30.3981" customHeight="1">
       <c r="A644" s="6" t="s">
         <v>18</v>
       </c>
@@ -33510,7 +32968,7 @@
       <c r="Q644" s="7"/>
       <c r="R644" s="7"/>
     </row>
-    <row r="645" spans="1:18" s="1" customFormat="1" ht="41.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A645" s="11" t="s">
         <v>18</v>
       </c>
@@ -33554,7 +33012,7 @@
       <c r="Q645" s="12"/>
       <c r="R645" s="12"/>
     </row>
-    <row r="646" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A646" s="6" t="s">
         <v>18</v>
       </c>
@@ -33598,7 +33056,7 @@
       <c r="Q646" s="7"/>
       <c r="R646" s="7"/>
     </row>
-    <row r="647" spans="1:18" s="1" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" s="1" customFormat="1" ht="52.2634" customHeight="1">
       <c r="A647" s="11" t="s">
         <v>30</v>
       </c>
@@ -33642,7 +33100,7 @@
       <c r="Q647" s="12"/>
       <c r="R647" s="12"/>
     </row>
-    <row r="648" spans="1:18" s="1" customFormat="1" ht="77.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" s="1" customFormat="1" ht="116.7927" customHeight="1">
       <c r="A648" s="6" t="s">
         <v>18</v>
       </c>
@@ -33684,7 +33142,7 @@
       <c r="Q648" s="7"/>
       <c r="R648" s="7"/>
     </row>
-    <row r="649" spans="1:18" s="1" customFormat="1" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" s="1" customFormat="1" ht="73.5954" customHeight="1">
       <c r="A649" s="11" t="s">
         <v>18</v>
       </c>
@@ -33726,529 +33184,522 @@
       <c r="Q649" s="12"/>
       <c r="R649" s="12"/>
     </row>
-    <row r="650" spans="1:18" s="1" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="P6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="L8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="L14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="P14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="Q14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="L18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B26" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="L26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="P26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N31" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B32" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="L32" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N32" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="L38" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N38" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="P38" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="Q38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B43" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="L43" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="N43" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="Q43" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B44" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="L44" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="N44" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="Q44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B45" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="L45" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="N45" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B63" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L63" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N63" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="P63" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="R63" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B65" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="L65" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="N65" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="Q65" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B66" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="L66" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="N66" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="Q66" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B68" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="L68" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="N68" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="Q68" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="B69" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="L69" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="N69" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="Q69" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B78" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="L78" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="N78" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="P78" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B79" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="L79" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="N79" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="P79" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="Q79" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B89" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="L89" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="N89" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="P89" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="Q89" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="R89" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B90" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="L90" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="N90" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="Q90" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B100" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="L100" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="N100" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="P100" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="Q100" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B101" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="L101" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="N101" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="Q101" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B117" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="L117" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="N117" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="P117" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="R117" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B118" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="L118" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="N118" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="Q118" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B128" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="L128" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="N128" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="P128" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="R128" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B129" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="L129" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="N129" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="Q129" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B135" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="L135" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="N135" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="P135" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="Q135" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B136" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="L136" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="N136" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="Q136" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B142" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="L142" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="N142" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="P142" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="R142" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="B143" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="L143" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="N143" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="Q143" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="B147" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="L147" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="N147" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="P147" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="Q147" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="R147" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="B148" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="L148" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="N148" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="Q148" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="B151" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="L151" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="N151" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="P151" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="Q151" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="R151" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="B152" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="L152" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="N152" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="Q152" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="B153" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="L153" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="N153" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="P153" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="Q153" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="R153" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="B154" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="L154" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="N154" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="P154" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="Q154" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="B156" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="L156" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="N156" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="P156" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="Q156" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="R156" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="B157" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="L157" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="N157" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="Q157" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="B160" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="L160" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="N160" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="P160" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="R160" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="B161" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="L161" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="N161" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="Q161" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="B167" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="L167" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="N167" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="P167" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="B173" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="L173" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="N173" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="P173" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="Q173" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="B193" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="L193" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="N193" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="P193" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="B197" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="L197" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="N197" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="P197" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="B201" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="L201" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="N201" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="P201" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="B205" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="L205" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="N205" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="P205" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="Q205" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="B207" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="L207" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="N207" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="P207" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="B211" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="L211" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="N211" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="P211" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="Q211" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="N213" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="B214" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="L214" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="N214" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="P214" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="Q214" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="B219" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="L219" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="N219" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="P219" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="Q219" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="B224" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="L224" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="N224" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="P224" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="Q224" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="R224" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="B230" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="L230" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="N230" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="P230" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="B237" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="L237" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="N237" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="P237" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="B246" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="L246" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="N246" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="P246" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="Q246" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="B252" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="L252" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="N252" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="P252" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="Q252" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="B256" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="L256" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="N256" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="B278" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="L278" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="N278" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="P278" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="Q278" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="B286" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="L286" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="N286" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="P286" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="Q286" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="B297" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="L297" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="N297" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="P297" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="Q297" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="B305" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="L305" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="N305" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="P305" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="Q305" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="B327" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="L327" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="N327" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="P327" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="B329" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="L329" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="N329" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="P329" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="Q329" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="B333" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="L333" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="N333" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="B336" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="L336" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="N336" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="P336" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="Q336" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="B338" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="L338" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="N338" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="P338" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="Q338" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="B344" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="L344" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="N344" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="P344" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="Q344" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="B345" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="L345" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="N345" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="Q345" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="B348" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="L348" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="N348" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="P348" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="Q348" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="B351" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="L351" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="N351" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="P351" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="Q351" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="B353" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="L353" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="N353" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="P353" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="Q353" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="R353" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="B392" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="L392" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="N392" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="P392" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="B394" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="L394" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="N394" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="P394" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="B395" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="L395" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="N395" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="Q395" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="B396" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="L396" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="N396" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="P396" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="B407" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="L407" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="N407" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="P407" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="B408" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="L408" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="N408" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="P408" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="B409" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="L409" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="N409" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="Q409" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="B411" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="L411" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="N411" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="P411" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="B412" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="L412" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="N412" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="Q412" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="B418" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="L418" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="N418" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="P418" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="B425" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="L425" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="N425" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="P425" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="B430" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="L430" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="N430" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="P430" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="B431" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="L431" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="N431" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="P431" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="B443" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="L443" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="N443" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="P443" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="Q443" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="B460" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="L460" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="N460" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="P460" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="Q460" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="N465" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="B476" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="L476" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="N476" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="P476" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="R476" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="B482" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="L482" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="N482" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="P482" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="B484" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="L484" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="N484" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="B487" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="L487" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="N487" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="B490" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="L490" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="N490" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="P490" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="B494" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="L494" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="N494" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="P494" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="B495" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="L495" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="N495" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="P495" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="B498" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="L498" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="N498" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="P498" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="B509" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="L509" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="N509" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="P509" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="B512" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="L512" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="N512" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="P512" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="R512" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="B523" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="L523" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="N523" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="P523" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="Q523" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="R523" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="B526" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="L526" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="N526" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="P526" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="B527" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="L527" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="N527" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="Q527" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="B529" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="L529" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="N529" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="P529" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="B531" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="L531" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="N531" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="P531" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="B532" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="L532" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="N532" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="P532" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="B533" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="L533" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="N533" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="P533" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="Q533" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="B534" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="L534" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="N534" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="Q534" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="B535" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="L535" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="N535" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="Q535" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="B546" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="L546" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="N546" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="P546" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="Q546" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="N554" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="B555" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="L555" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="N555" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="P555" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="Q555" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="B562" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="L562" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="N562" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="P562" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="Q562" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="B563" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="L563" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="N563" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="Q563" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="B564" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="L564" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="N564" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="Q564" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="B585" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="L585" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="N585" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="P585" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="R585" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="B595" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="L595" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="N595" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="P595" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="Q595" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="B621" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="L621" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="N621" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="P621" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="Q621" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="B622" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="L622" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="N622" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="O622" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="P622" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="Q622" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="B631" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="N631" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="P631" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="B640" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="L640" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="N640" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="P640" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="B647" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="L647" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="N647" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="L6" r:id="rId2"/>
+    <hyperlink ref="N6" r:id="rId3"/>
+    <hyperlink ref="P6" r:id="rId4"/>
+    <hyperlink ref="B8" r:id="rId5"/>
+    <hyperlink ref="L8" r:id="rId6"/>
+    <hyperlink ref="N8" r:id="rId7"/>
+    <hyperlink ref="B14" r:id="rId8"/>
+    <hyperlink ref="L14" r:id="rId9"/>
+    <hyperlink ref="N14" r:id="rId10"/>
+    <hyperlink ref="P14" r:id="rId11"/>
+    <hyperlink ref="Q14" r:id="rId12"/>
+    <hyperlink ref="B18" r:id="rId13"/>
+    <hyperlink ref="L18" r:id="rId14"/>
+    <hyperlink ref="N18" r:id="rId15"/>
+    <hyperlink ref="B26" r:id="rId16"/>
+    <hyperlink ref="L26" r:id="rId17"/>
+    <hyperlink ref="N26" r:id="rId18"/>
+    <hyperlink ref="P26" r:id="rId19"/>
+    <hyperlink ref="N31" r:id="rId20"/>
+    <hyperlink ref="B32" r:id="rId21"/>
+    <hyperlink ref="L32" r:id="rId22"/>
+    <hyperlink ref="N32" r:id="rId23"/>
+    <hyperlink ref="B38" r:id="rId24"/>
+    <hyperlink ref="L38" r:id="rId25"/>
+    <hyperlink ref="N38" r:id="rId26"/>
+    <hyperlink ref="P38" r:id="rId27"/>
+    <hyperlink ref="Q38" r:id="rId28"/>
+    <hyperlink ref="B43" r:id="rId29"/>
+    <hyperlink ref="L43" r:id="rId30"/>
+    <hyperlink ref="N43" r:id="rId31"/>
+    <hyperlink ref="Q43" r:id="rId32"/>
+    <hyperlink ref="B44" r:id="rId33"/>
+    <hyperlink ref="L44" r:id="rId34"/>
+    <hyperlink ref="N44" r:id="rId35"/>
+    <hyperlink ref="Q44" r:id="rId36"/>
+    <hyperlink ref="B45" r:id="rId37"/>
+    <hyperlink ref="L45" r:id="rId38"/>
+    <hyperlink ref="N45" r:id="rId39"/>
+    <hyperlink ref="B63" r:id="rId40"/>
+    <hyperlink ref="L63" r:id="rId41"/>
+    <hyperlink ref="N63" r:id="rId42"/>
+    <hyperlink ref="P63" r:id="rId43"/>
+    <hyperlink ref="R63" r:id="rId44"/>
+    <hyperlink ref="B65" r:id="rId45"/>
+    <hyperlink ref="L65" r:id="rId46"/>
+    <hyperlink ref="N65" r:id="rId47"/>
+    <hyperlink ref="Q65" r:id="rId48"/>
+    <hyperlink ref="B66" r:id="rId49"/>
+    <hyperlink ref="L66" r:id="rId50"/>
+    <hyperlink ref="N66" r:id="rId51"/>
+    <hyperlink ref="Q66" r:id="rId52"/>
+    <hyperlink ref="B68" r:id="rId53"/>
+    <hyperlink ref="L68" r:id="rId54"/>
+    <hyperlink ref="N68" r:id="rId55"/>
+    <hyperlink ref="Q68" r:id="rId56"/>
+    <hyperlink ref="B69" r:id="rId57"/>
+    <hyperlink ref="L69" r:id="rId58"/>
+    <hyperlink ref="N69" r:id="rId59"/>
+    <hyperlink ref="Q69" r:id="rId60"/>
+    <hyperlink ref="B78" r:id="rId61"/>
+    <hyperlink ref="L78" r:id="rId62"/>
+    <hyperlink ref="N78" r:id="rId63"/>
+    <hyperlink ref="P78" r:id="rId64"/>
+    <hyperlink ref="B79" r:id="rId65"/>
+    <hyperlink ref="L79" r:id="rId66"/>
+    <hyperlink ref="N79" r:id="rId67"/>
+    <hyperlink ref="P79" r:id="rId68"/>
+    <hyperlink ref="Q79" r:id="rId69"/>
+    <hyperlink ref="B89" r:id="rId70"/>
+    <hyperlink ref="L89" r:id="rId71"/>
+    <hyperlink ref="N89" r:id="rId72"/>
+    <hyperlink ref="P89" r:id="rId73"/>
+    <hyperlink ref="Q89" r:id="rId74"/>
+    <hyperlink ref="R89" r:id="rId75"/>
+    <hyperlink ref="B90" r:id="rId76"/>
+    <hyperlink ref="L90" r:id="rId77"/>
+    <hyperlink ref="N90" r:id="rId78"/>
+    <hyperlink ref="Q90" r:id="rId79"/>
+    <hyperlink ref="B100" r:id="rId80"/>
+    <hyperlink ref="L100" r:id="rId81"/>
+    <hyperlink ref="N100" r:id="rId82"/>
+    <hyperlink ref="P100" r:id="rId83"/>
+    <hyperlink ref="Q100" r:id="rId84"/>
+    <hyperlink ref="B101" r:id="rId85"/>
+    <hyperlink ref="L101" r:id="rId86"/>
+    <hyperlink ref="N101" r:id="rId87"/>
+    <hyperlink ref="Q101" r:id="rId88"/>
+    <hyperlink ref="B117" r:id="rId89"/>
+    <hyperlink ref="L117" r:id="rId90"/>
+    <hyperlink ref="N117" r:id="rId91"/>
+    <hyperlink ref="P117" r:id="rId92"/>
+    <hyperlink ref="R117" r:id="rId93"/>
+    <hyperlink ref="B118" r:id="rId94"/>
+    <hyperlink ref="L118" r:id="rId95"/>
+    <hyperlink ref="N118" r:id="rId96"/>
+    <hyperlink ref="Q118" r:id="rId97"/>
+    <hyperlink ref="B128" r:id="rId98"/>
+    <hyperlink ref="L128" r:id="rId99"/>
+    <hyperlink ref="N128" r:id="rId100"/>
+    <hyperlink ref="P128" r:id="rId101"/>
+    <hyperlink ref="R128" r:id="rId102"/>
+    <hyperlink ref="B129" r:id="rId103"/>
+    <hyperlink ref="L129" r:id="rId104"/>
+    <hyperlink ref="N129" r:id="rId105"/>
+    <hyperlink ref="Q129" r:id="rId106"/>
+    <hyperlink ref="B135" r:id="rId107"/>
+    <hyperlink ref="L135" r:id="rId108"/>
+    <hyperlink ref="N135" r:id="rId109"/>
+    <hyperlink ref="P135" r:id="rId110"/>
+    <hyperlink ref="Q135" r:id="rId111"/>
+    <hyperlink ref="B136" r:id="rId112"/>
+    <hyperlink ref="L136" r:id="rId113"/>
+    <hyperlink ref="N136" r:id="rId114"/>
+    <hyperlink ref="Q136" r:id="rId115"/>
+    <hyperlink ref="B142" r:id="rId116"/>
+    <hyperlink ref="L142" r:id="rId117"/>
+    <hyperlink ref="N142" r:id="rId118"/>
+    <hyperlink ref="P142" r:id="rId119"/>
+    <hyperlink ref="R142" r:id="rId120"/>
+    <hyperlink ref="B143" r:id="rId121"/>
+    <hyperlink ref="L143" r:id="rId122"/>
+    <hyperlink ref="N143" r:id="rId123"/>
+    <hyperlink ref="Q143" r:id="rId124"/>
+    <hyperlink ref="B147" r:id="rId125"/>
+    <hyperlink ref="L147" r:id="rId126"/>
+    <hyperlink ref="N147" r:id="rId127"/>
+    <hyperlink ref="P147" r:id="rId128"/>
+    <hyperlink ref="Q147" r:id="rId129"/>
+    <hyperlink ref="R147" r:id="rId130"/>
+    <hyperlink ref="B148" r:id="rId131"/>
+    <hyperlink ref="L148" r:id="rId132"/>
+    <hyperlink ref="N148" r:id="rId133"/>
+    <hyperlink ref="Q148" r:id="rId134"/>
+    <hyperlink ref="B151" r:id="rId135"/>
+    <hyperlink ref="L151" r:id="rId136"/>
+    <hyperlink ref="N151" r:id="rId137"/>
+    <hyperlink ref="P151" r:id="rId138"/>
+    <hyperlink ref="Q151" r:id="rId139"/>
+    <hyperlink ref="R151" r:id="rId140"/>
+    <hyperlink ref="B152" r:id="rId141"/>
+    <hyperlink ref="L152" r:id="rId142"/>
+    <hyperlink ref="N152" r:id="rId143"/>
+    <hyperlink ref="Q152" r:id="rId144"/>
+    <hyperlink ref="B153" r:id="rId145"/>
+    <hyperlink ref="L153" r:id="rId146"/>
+    <hyperlink ref="N153" r:id="rId147"/>
+    <hyperlink ref="P153" r:id="rId148"/>
+    <hyperlink ref="Q153" r:id="rId149"/>
+    <hyperlink ref="R153" r:id="rId150"/>
+    <hyperlink ref="B154" r:id="rId151"/>
+    <hyperlink ref="L154" r:id="rId152"/>
+    <hyperlink ref="N154" r:id="rId153"/>
+    <hyperlink ref="P154" r:id="rId154"/>
+    <hyperlink ref="Q154" r:id="rId155"/>
+    <hyperlink ref="B156" r:id="rId156"/>
+    <hyperlink ref="L156" r:id="rId157"/>
+    <hyperlink ref="N156" r:id="rId158"/>
+    <hyperlink ref="P156" r:id="rId159"/>
+    <hyperlink ref="Q156" r:id="rId160"/>
+    <hyperlink ref="R156" r:id="rId161"/>
+    <hyperlink ref="B157" r:id="rId162"/>
+    <hyperlink ref="L157" r:id="rId163"/>
+    <hyperlink ref="N157" r:id="rId164"/>
+    <hyperlink ref="Q157" r:id="rId165"/>
+    <hyperlink ref="B160" r:id="rId166"/>
+    <hyperlink ref="L160" r:id="rId167"/>
+    <hyperlink ref="N160" r:id="rId168"/>
+    <hyperlink ref="P160" r:id="rId169"/>
+    <hyperlink ref="R160" r:id="rId170"/>
+    <hyperlink ref="B161" r:id="rId171"/>
+    <hyperlink ref="L161" r:id="rId172"/>
+    <hyperlink ref="N161" r:id="rId173"/>
+    <hyperlink ref="Q161" r:id="rId174"/>
+    <hyperlink ref="B167" r:id="rId175"/>
+    <hyperlink ref="L167" r:id="rId176"/>
+    <hyperlink ref="N167" r:id="rId177"/>
+    <hyperlink ref="P167" r:id="rId178"/>
+    <hyperlink ref="B173" r:id="rId179"/>
+    <hyperlink ref="L173" r:id="rId180"/>
+    <hyperlink ref="N173" r:id="rId181"/>
+    <hyperlink ref="P173" r:id="rId182"/>
+    <hyperlink ref="Q173" r:id="rId183"/>
+    <hyperlink ref="B193" r:id="rId184"/>
+    <hyperlink ref="L193" r:id="rId185"/>
+    <hyperlink ref="N193" r:id="rId186"/>
+    <hyperlink ref="P193" r:id="rId187"/>
+    <hyperlink ref="B197" r:id="rId188"/>
+    <hyperlink ref="L197" r:id="rId189"/>
+    <hyperlink ref="N197" r:id="rId190"/>
+    <hyperlink ref="P197" r:id="rId191"/>
+    <hyperlink ref="B201" r:id="rId192"/>
+    <hyperlink ref="L201" r:id="rId193"/>
+    <hyperlink ref="N201" r:id="rId194"/>
+    <hyperlink ref="P201" r:id="rId195"/>
+    <hyperlink ref="B205" r:id="rId196"/>
+    <hyperlink ref="L205" r:id="rId197"/>
+    <hyperlink ref="N205" r:id="rId198"/>
+    <hyperlink ref="P205" r:id="rId199"/>
+    <hyperlink ref="Q205" r:id="rId200"/>
+    <hyperlink ref="B207" r:id="rId201"/>
+    <hyperlink ref="L207" r:id="rId202"/>
+    <hyperlink ref="N207" r:id="rId203"/>
+    <hyperlink ref="P207" r:id="rId204"/>
+    <hyperlink ref="B211" r:id="rId205"/>
+    <hyperlink ref="L211" r:id="rId206"/>
+    <hyperlink ref="N211" r:id="rId207"/>
+    <hyperlink ref="P211" r:id="rId208"/>
+    <hyperlink ref="Q211" r:id="rId209"/>
+    <hyperlink ref="N213" r:id="rId210"/>
+    <hyperlink ref="B214" r:id="rId211"/>
+    <hyperlink ref="L214" r:id="rId212"/>
+    <hyperlink ref="N214" r:id="rId213"/>
+    <hyperlink ref="P214" r:id="rId214"/>
+    <hyperlink ref="Q214" r:id="rId215"/>
+    <hyperlink ref="B219" r:id="rId216"/>
+    <hyperlink ref="L219" r:id="rId217"/>
+    <hyperlink ref="N219" r:id="rId218"/>
+    <hyperlink ref="P219" r:id="rId219"/>
+    <hyperlink ref="Q219" r:id="rId220"/>
+    <hyperlink ref="B224" r:id="rId221"/>
+    <hyperlink ref="L224" r:id="rId222"/>
+    <hyperlink ref="N224" r:id="rId223"/>
+    <hyperlink ref="P224" r:id="rId224"/>
+    <hyperlink ref="Q224" r:id="rId225"/>
+    <hyperlink ref="R224" r:id="rId226"/>
+    <hyperlink ref="B230" r:id="rId227"/>
+    <hyperlink ref="L230" r:id="rId228"/>
+    <hyperlink ref="N230" r:id="rId229"/>
+    <hyperlink ref="P230" r:id="rId230"/>
+    <hyperlink ref="B237" r:id="rId231"/>
+    <hyperlink ref="L237" r:id="rId232"/>
+    <hyperlink ref="N237" r:id="rId233"/>
+    <hyperlink ref="P237" r:id="rId234"/>
+    <hyperlink ref="B246" r:id="rId235"/>
+    <hyperlink ref="L246" r:id="rId236"/>
+    <hyperlink ref="N246" r:id="rId237"/>
+    <hyperlink ref="P246" r:id="rId238"/>
+    <hyperlink ref="Q246" r:id="rId239"/>
+    <hyperlink ref="B252" r:id="rId240"/>
+    <hyperlink ref="L252" r:id="rId241"/>
+    <hyperlink ref="N252" r:id="rId242"/>
+    <hyperlink ref="P252" r:id="rId243"/>
+    <hyperlink ref="Q252" r:id="rId244"/>
+    <hyperlink ref="B256" r:id="rId245"/>
+    <hyperlink ref="L256" r:id="rId246"/>
+    <hyperlink ref="N256" r:id="rId247"/>
+    <hyperlink ref="B278" r:id="rId248"/>
+    <hyperlink ref="L278" r:id="rId249"/>
+    <hyperlink ref="N278" r:id="rId250"/>
+    <hyperlink ref="P278" r:id="rId251"/>
+    <hyperlink ref="Q278" r:id="rId252"/>
+    <hyperlink ref="B286" r:id="rId253"/>
+    <hyperlink ref="L286" r:id="rId254"/>
+    <hyperlink ref="N286" r:id="rId255"/>
+    <hyperlink ref="P286" r:id="rId256"/>
+    <hyperlink ref="Q286" r:id="rId257"/>
+    <hyperlink ref="B297" r:id="rId258"/>
+    <hyperlink ref="L297" r:id="rId259"/>
+    <hyperlink ref="N297" r:id="rId260"/>
+    <hyperlink ref="P297" r:id="rId261"/>
+    <hyperlink ref="Q297" r:id="rId262"/>
+    <hyperlink ref="B305" r:id="rId263"/>
+    <hyperlink ref="L305" r:id="rId264"/>
+    <hyperlink ref="N305" r:id="rId265"/>
+    <hyperlink ref="P305" r:id="rId266"/>
+    <hyperlink ref="Q305" r:id="rId267"/>
+    <hyperlink ref="B327" r:id="rId268"/>
+    <hyperlink ref="L327" r:id="rId269"/>
+    <hyperlink ref="N327" r:id="rId270"/>
+    <hyperlink ref="P327" r:id="rId271"/>
+    <hyperlink ref="B329" r:id="rId272"/>
+    <hyperlink ref="L329" r:id="rId273"/>
+    <hyperlink ref="N329" r:id="rId274"/>
+    <hyperlink ref="P329" r:id="rId275"/>
+    <hyperlink ref="Q329" r:id="rId276"/>
+    <hyperlink ref="B333" r:id="rId277"/>
+    <hyperlink ref="L333" r:id="rId278"/>
+    <hyperlink ref="N333" r:id="rId279"/>
+    <hyperlink ref="B336" r:id="rId280"/>
+    <hyperlink ref="L336" r:id="rId281"/>
+    <hyperlink ref="N336" r:id="rId282"/>
+    <hyperlink ref="P336" r:id="rId283"/>
+    <hyperlink ref="Q336" r:id="rId284"/>
+    <hyperlink ref="B338" r:id="rId285"/>
+    <hyperlink ref="L338" r:id="rId286"/>
+    <hyperlink ref="N338" r:id="rId287"/>
+    <hyperlink ref="P338" r:id="rId288"/>
+    <hyperlink ref="Q338" r:id="rId289"/>
+    <hyperlink ref="B344" r:id="rId290"/>
+    <hyperlink ref="L344" r:id="rId291"/>
+    <hyperlink ref="N344" r:id="rId292"/>
+    <hyperlink ref="P344" r:id="rId293"/>
+    <hyperlink ref="Q344" r:id="rId294"/>
+    <hyperlink ref="B345" r:id="rId295"/>
+    <hyperlink ref="L345" r:id="rId296"/>
+    <hyperlink ref="N345" r:id="rId297"/>
+    <hyperlink ref="Q345" r:id="rId298"/>
+    <hyperlink ref="B348" r:id="rId299"/>
+    <hyperlink ref="L348" r:id="rId300"/>
+    <hyperlink ref="N348" r:id="rId301"/>
+    <hyperlink ref="P348" r:id="rId302"/>
+    <hyperlink ref="Q348" r:id="rId303"/>
+    <hyperlink ref="B351" r:id="rId304"/>
+    <hyperlink ref="L351" r:id="rId305"/>
+    <hyperlink ref="N351" r:id="rId306"/>
+    <hyperlink ref="P351" r:id="rId307"/>
+    <hyperlink ref="Q351" r:id="rId308"/>
+    <hyperlink ref="B353" r:id="rId309"/>
+    <hyperlink ref="L353" r:id="rId310"/>
+    <hyperlink ref="N353" r:id="rId311"/>
+    <hyperlink ref="P353" r:id="rId312"/>
+    <hyperlink ref="Q353" r:id="rId313"/>
+    <hyperlink ref="R353" r:id="rId314"/>
+    <hyperlink ref="B392" r:id="rId315"/>
+    <hyperlink ref="L392" r:id="rId316"/>
+    <hyperlink ref="N392" r:id="rId317"/>
+    <hyperlink ref="P392" r:id="rId318"/>
+    <hyperlink ref="B394" r:id="rId319"/>
+    <hyperlink ref="L394" r:id="rId320"/>
+    <hyperlink ref="N394" r:id="rId321"/>
+    <hyperlink ref="P394" r:id="rId322"/>
+    <hyperlink ref="B395" r:id="rId323"/>
+    <hyperlink ref="L395" r:id="rId324"/>
+    <hyperlink ref="N395" r:id="rId325"/>
+    <hyperlink ref="Q395" r:id="rId326"/>
+    <hyperlink ref="B396" r:id="rId327"/>
+    <hyperlink ref="L396" r:id="rId328"/>
+    <hyperlink ref="N396" r:id="rId329"/>
+    <hyperlink ref="P396" r:id="rId330"/>
+    <hyperlink ref="B407" r:id="rId331"/>
+    <hyperlink ref="L407" r:id="rId332"/>
+    <hyperlink ref="N407" r:id="rId333"/>
+    <hyperlink ref="P407" r:id="rId334"/>
+    <hyperlink ref="B408" r:id="rId335"/>
+    <hyperlink ref="L408" r:id="rId336"/>
+    <hyperlink ref="N408" r:id="rId337"/>
+    <hyperlink ref="P408" r:id="rId338"/>
+    <hyperlink ref="B409" r:id="rId339"/>
+    <hyperlink ref="L409" r:id="rId340"/>
+    <hyperlink ref="N409" r:id="rId341"/>
+    <hyperlink ref="Q409" r:id="rId342"/>
+    <hyperlink ref="B411" r:id="rId343"/>
+    <hyperlink ref="L411" r:id="rId344"/>
+    <hyperlink ref="N411" r:id="rId345"/>
+    <hyperlink ref="P411" r:id="rId346"/>
+    <hyperlink ref="B412" r:id="rId347"/>
+    <hyperlink ref="L412" r:id="rId348"/>
+    <hyperlink ref="N412" r:id="rId349"/>
+    <hyperlink ref="Q412" r:id="rId350"/>
+    <hyperlink ref="B418" r:id="rId351"/>
+    <hyperlink ref="L418" r:id="rId352"/>
+    <hyperlink ref="N418" r:id="rId353"/>
+    <hyperlink ref="P418" r:id="rId354"/>
+    <hyperlink ref="B425" r:id="rId355"/>
+    <hyperlink ref="L425" r:id="rId356"/>
+    <hyperlink ref="N425" r:id="rId357"/>
+    <hyperlink ref="P425" r:id="rId358"/>
+    <hyperlink ref="B430" r:id="rId359"/>
+    <hyperlink ref="L430" r:id="rId360"/>
+    <hyperlink ref="N430" r:id="rId361"/>
+    <hyperlink ref="P430" r:id="rId362"/>
+    <hyperlink ref="B431" r:id="rId363"/>
+    <hyperlink ref="L431" r:id="rId364"/>
+    <hyperlink ref="N431" r:id="rId365"/>
+    <hyperlink ref="P431" r:id="rId366"/>
+    <hyperlink ref="B443" r:id="rId367"/>
+    <hyperlink ref="L443" r:id="rId368"/>
+    <hyperlink ref="N443" r:id="rId369"/>
+    <hyperlink ref="P443" r:id="rId370"/>
+    <hyperlink ref="Q443" r:id="rId371"/>
+    <hyperlink ref="B460" r:id="rId372"/>
+    <hyperlink ref="L460" r:id="rId373"/>
+    <hyperlink ref="N460" r:id="rId374"/>
+    <hyperlink ref="P460" r:id="rId375"/>
+    <hyperlink ref="Q460" r:id="rId376"/>
+    <hyperlink ref="N465" r:id="rId377"/>
+    <hyperlink ref="B476" r:id="rId378"/>
+    <hyperlink ref="L476" r:id="rId379"/>
+    <hyperlink ref="N476" r:id="rId380"/>
+    <hyperlink ref="P476" r:id="rId381"/>
+    <hyperlink ref="R476" r:id="rId382"/>
+    <hyperlink ref="B482" r:id="rId383"/>
+    <hyperlink ref="L482" r:id="rId384"/>
+    <hyperlink ref="N482" r:id="rId385"/>
+    <hyperlink ref="P482" r:id="rId386"/>
+    <hyperlink ref="B484" r:id="rId387"/>
+    <hyperlink ref="L484" r:id="rId388"/>
+    <hyperlink ref="N484" r:id="rId389"/>
+    <hyperlink ref="B487" r:id="rId390"/>
+    <hyperlink ref="L487" r:id="rId391"/>
+    <hyperlink ref="N487" r:id="rId392"/>
+    <hyperlink ref="B490" r:id="rId393"/>
+    <hyperlink ref="L490" r:id="rId394"/>
+    <hyperlink ref="N490" r:id="rId395"/>
+    <hyperlink ref="P490" r:id="rId396"/>
+    <hyperlink ref="B494" r:id="rId397"/>
+    <hyperlink ref="L494" r:id="rId398"/>
+    <hyperlink ref="N494" r:id="rId399"/>
+    <hyperlink ref="P494" r:id="rId400"/>
+    <hyperlink ref="B495" r:id="rId401"/>
+    <hyperlink ref="L495" r:id="rId402"/>
+    <hyperlink ref="N495" r:id="rId403"/>
+    <hyperlink ref="P495" r:id="rId404"/>
+    <hyperlink ref="B498" r:id="rId405"/>
+    <hyperlink ref="L498" r:id="rId406"/>
+    <hyperlink ref="N498" r:id="rId407"/>
+    <hyperlink ref="P498" r:id="rId408"/>
+    <hyperlink ref="B509" r:id="rId409"/>
+    <hyperlink ref="L509" r:id="rId410"/>
+    <hyperlink ref="N509" r:id="rId411"/>
+    <hyperlink ref="P509" r:id="rId412"/>
+    <hyperlink ref="B512" r:id="rId413"/>
+    <hyperlink ref="L512" r:id="rId414"/>
+    <hyperlink ref="N512" r:id="rId415"/>
+    <hyperlink ref="P512" r:id="rId416"/>
+    <hyperlink ref="R512" r:id="rId417"/>
+    <hyperlink ref="B523" r:id="rId418"/>
+    <hyperlink ref="L523" r:id="rId419"/>
+    <hyperlink ref="N523" r:id="rId420"/>
+    <hyperlink ref="P523" r:id="rId421"/>
+    <hyperlink ref="Q523" r:id="rId422"/>
+    <hyperlink ref="R523" r:id="rId423"/>
+    <hyperlink ref="B526" r:id="rId424"/>
+    <hyperlink ref="L526" r:id="rId425"/>
+    <hyperlink ref="N526" r:id="rId426"/>
+    <hyperlink ref="P526" r:id="rId427"/>
+    <hyperlink ref="B527" r:id="rId428"/>
+    <hyperlink ref="L527" r:id="rId429"/>
+    <hyperlink ref="N527" r:id="rId430"/>
+    <hyperlink ref="Q527" r:id="rId431"/>
+    <hyperlink ref="B529" r:id="rId432"/>
+    <hyperlink ref="L529" r:id="rId433"/>
+    <hyperlink ref="N529" r:id="rId434"/>
+    <hyperlink ref="P529" r:id="rId435"/>
+    <hyperlink ref="B531" r:id="rId436"/>
+    <hyperlink ref="L531" r:id="rId437"/>
+    <hyperlink ref="N531" r:id="rId438"/>
+    <hyperlink ref="P531" r:id="rId439"/>
+    <hyperlink ref="B532" r:id="rId440"/>
+    <hyperlink ref="L532" r:id="rId441"/>
+    <hyperlink ref="N532" r:id="rId442"/>
+    <hyperlink ref="P532" r:id="rId443"/>
+    <hyperlink ref="B533" r:id="rId444"/>
+    <hyperlink ref="L533" r:id="rId445"/>
+    <hyperlink ref="N533" r:id="rId446"/>
+    <hyperlink ref="P533" r:id="rId447"/>
+    <hyperlink ref="Q533" r:id="rId448"/>
+    <hyperlink ref="B534" r:id="rId449"/>
+    <hyperlink ref="L534" r:id="rId450"/>
+    <hyperlink ref="N534" r:id="rId451"/>
+    <hyperlink ref="Q534" r:id="rId452"/>
+    <hyperlink ref="B535" r:id="rId453"/>
+    <hyperlink ref="L535" r:id="rId454"/>
+    <hyperlink ref="N535" r:id="rId455"/>
+    <hyperlink ref="Q535" r:id="rId456"/>
+    <hyperlink ref="B546" r:id="rId457"/>
+    <hyperlink ref="L546" r:id="rId458"/>
+    <hyperlink ref="N546" r:id="rId459"/>
+    <hyperlink ref="P546" r:id="rId460"/>
+    <hyperlink ref="Q546" r:id="rId461"/>
+    <hyperlink ref="N554" r:id="rId462"/>
+    <hyperlink ref="B555" r:id="rId463"/>
+    <hyperlink ref="L555" r:id="rId464"/>
+    <hyperlink ref="N555" r:id="rId465"/>
+    <hyperlink ref="P555" r:id="rId466"/>
+    <hyperlink ref="Q555" r:id="rId467"/>
+    <hyperlink ref="B562" r:id="rId468"/>
+    <hyperlink ref="L562" r:id="rId469"/>
+    <hyperlink ref="N562" r:id="rId470"/>
+    <hyperlink ref="P562" r:id="rId471"/>
+    <hyperlink ref="Q562" r:id="rId472"/>
+    <hyperlink ref="B563" r:id="rId473"/>
+    <hyperlink ref="L563" r:id="rId474"/>
+    <hyperlink ref="N563" r:id="rId475"/>
+    <hyperlink ref="Q563" r:id="rId476"/>
+    <hyperlink ref="B564" r:id="rId477"/>
+    <hyperlink ref="L564" r:id="rId478"/>
+    <hyperlink ref="N564" r:id="rId479"/>
+    <hyperlink ref="Q564" r:id="rId480"/>
+    <hyperlink ref="B585" r:id="rId481"/>
+    <hyperlink ref="L585" r:id="rId482"/>
+    <hyperlink ref="N585" r:id="rId483"/>
+    <hyperlink ref="P585" r:id="rId484"/>
+    <hyperlink ref="R585" r:id="rId485"/>
+    <hyperlink ref="B595" r:id="rId486"/>
+    <hyperlink ref="L595" r:id="rId487"/>
+    <hyperlink ref="N595" r:id="rId488"/>
+    <hyperlink ref="P595" r:id="rId489"/>
+    <hyperlink ref="Q595" r:id="rId490"/>
+    <hyperlink ref="B621" r:id="rId491"/>
+    <hyperlink ref="L621" r:id="rId492"/>
+    <hyperlink ref="N621" r:id="rId493"/>
+    <hyperlink ref="P621" r:id="rId494"/>
+    <hyperlink ref="Q621" r:id="rId495"/>
+    <hyperlink ref="B622" r:id="rId496"/>
+    <hyperlink ref="L622" r:id="rId497"/>
+    <hyperlink ref="N622" r:id="rId498"/>
+    <hyperlink ref="O622" r:id="rId499"/>
+    <hyperlink ref="P622" r:id="rId500"/>
+    <hyperlink ref="Q622" r:id="rId501"/>
+    <hyperlink ref="B631" r:id="rId502"/>
+    <hyperlink ref="N631" r:id="rId503"/>
+    <hyperlink ref="P631" r:id="rId504"/>
+    <hyperlink ref="B640" r:id="rId505"/>
+    <hyperlink ref="L640" r:id="rId506"/>
+    <hyperlink ref="N640" r:id="rId507"/>
+    <hyperlink ref="P640" r:id="rId508"/>
+    <hyperlink ref="B647" r:id="rId509"/>
+    <hyperlink ref="L647" r:id="rId510"/>
+    <hyperlink ref="N647" r:id="rId511"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="66" orientation="landscape"/>
+  <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{b16d0a29-7bab-41bf-9a27-8bca820ba65b}" enabled="1" method="Privileged" siteId="{a2d34bfa-bd5b-4dc3-9a2e-098f99296771}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -29514,7 +29514,7 @@
     </row>
     <row r="563" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A563" s="11" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="B563" s="18" t="s">
         <v>1582</v>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -5698,7 +5698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R650"/>
+  <dimension ref="A1:Q649"/>
   <cols>
     <col min="1" max="1" width="15.9715986666667" customWidth="1"/>
     <col min="2" max="3" width="24.1017" customWidth="1"/>
@@ -5713,7 +5713,6 @@
     <col min="14" max="16" width="14.1158973333333" customWidth="1"/>
     <col min="17" max="17" width="15.4011986666667" customWidth="1"/>
     <col min="18" max="18" width="16.5419986666667" customWidth="1"/>
-    <col min="19" max="19" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="55.9965" customHeight="1">
@@ -5946,7 +5945,7 @@
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -5972,17 +5971,17 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="N6" s="15" t="s">
+      <c r="N6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="O6" s="9"/>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q6" s="7"/>
@@ -6036,7 +6035,7 @@
       <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -6062,13 +6061,13 @@
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="7" t="s">
         <v>39</v>
       </c>
       <c r="O8" s="9"/>
@@ -6288,7 +6287,7 @@
       <c r="A14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -6314,20 +6313,20 @@
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="N14" s="7" t="s">
         <v>59</v>
       </c>
       <c r="O14" s="9"/>
-      <c r="P14" s="16" t="s">
+      <c r="P14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q14" s="15" t="s">
+      <c r="Q14" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R14" s="7"/>
@@ -6460,7 +6459,7 @@
       <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -6486,13 +6485,13 @@
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="N18" s="15" t="s">
+      <c r="N18" s="7" t="s">
         <v>68</v>
       </c>
       <c r="O18" s="9"/>
@@ -6802,7 +6801,7 @@
       <c r="A26" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -6828,17 +6827,17 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="8"/>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="N26" s="15" t="s">
+      <c r="N26" s="7" t="s">
         <v>93</v>
       </c>
       <c r="O26" s="9"/>
-      <c r="P26" s="16" t="s">
+      <c r="P26" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q26" s="7"/>
@@ -7048,7 +7047,7 @@
       <c r="M31" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="N31" s="18" t="s">
+      <c r="N31" s="12" t="s">
         <v>68</v>
       </c>
       <c r="O31" s="14"/>
@@ -7060,7 +7059,7 @@
       <c r="A32" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="7" t="s">
         <v>110</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -7086,13 +7085,13 @@
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="8"/>
-      <c r="L32" s="15" t="s">
+      <c r="L32" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="N32" s="15" t="s">
+      <c r="N32" s="7" t="s">
         <v>68</v>
       </c>
       <c r="O32" s="9"/>
@@ -7310,7 +7309,7 @@
       <c r="A38" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="7" t="s">
         <v>124</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -7336,20 +7335,20 @@
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="15" t="s">
+      <c r="L38" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="N38" s="15" t="s">
+      <c r="N38" s="7" t="s">
         <v>128</v>
       </c>
       <c r="O38" s="9"/>
-      <c r="P38" s="16" t="s">
+      <c r="P38" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q38" s="15" t="s">
+      <c r="Q38" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R38" s="7"/>
@@ -7522,7 +7521,7 @@
       <c r="A43" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="12" t="s">
         <v>140</v>
       </c>
       <c r="C43" s="12" t="s">
@@ -7548,18 +7547,18 @@
       </c>
       <c r="J43" s="14"/>
       <c r="K43" s="13"/>
-      <c r="L43" s="18" t="s">
+      <c r="L43" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M43" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="N43" s="18" t="s">
+      <c r="N43" s="12" t="s">
         <v>144</v>
       </c>
       <c r="O43" s="14"/>
       <c r="P43" s="14"/>
-      <c r="Q43" s="18" t="s">
+      <c r="Q43" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R43" s="12"/>
@@ -7568,7 +7567,7 @@
       <c r="A44" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="7" t="s">
         <v>146</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -7586,18 +7585,18 @@
       <c r="I44" s="8"/>
       <c r="J44" s="9"/>
       <c r="K44" s="8"/>
-      <c r="L44" s="15" t="s">
+      <c r="L44" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="N44" s="15" t="s">
+      <c r="N44" s="7" t="s">
         <v>144</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="9"/>
-      <c r="Q44" s="15" t="s">
+      <c r="Q44" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R44" s="7"/>
@@ -7606,7 +7605,7 @@
       <c r="A45" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="12" t="s">
         <v>150</v>
       </c>
       <c r="C45" s="12" t="s">
@@ -7632,13 +7631,13 @@
       </c>
       <c r="J45" s="14"/>
       <c r="K45" s="13"/>
-      <c r="L45" s="18" t="s">
+      <c r="L45" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M45" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="18" t="s">
+      <c r="N45" s="12" t="s">
         <v>154</v>
       </c>
       <c r="O45" s="14"/>
@@ -8332,7 +8331,7 @@
       <c r="A63" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="12" t="s">
         <v>206</v>
       </c>
       <c r="C63" s="12" t="s">
@@ -8358,21 +8357,21 @@
       </c>
       <c r="J63" s="14"/>
       <c r="K63" s="13"/>
-      <c r="L63" s="18" t="s">
+      <c r="L63" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M63" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="N63" s="18" t="s">
+      <c r="N63" s="12" t="s">
         <v>208</v>
       </c>
       <c r="O63" s="14"/>
-      <c r="P63" s="19" t="s">
+      <c r="P63" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q63" s="12"/>
-      <c r="R63" s="18" t="s">
+      <c r="R63" s="12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8418,7 +8417,7 @@
       <c r="A65" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="12" t="s">
         <v>214</v>
       </c>
       <c r="C65" s="12" t="s">
@@ -8438,18 +8437,18 @@
       <c r="I65" s="13"/>
       <c r="J65" s="14"/>
       <c r="K65" s="13"/>
-      <c r="L65" s="18" t="s">
+      <c r="L65" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M65" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="N65" s="18" t="s">
+      <c r="N65" s="12" t="s">
         <v>213</v>
       </c>
       <c r="O65" s="14"/>
       <c r="P65" s="14"/>
-      <c r="Q65" s="18" t="s">
+      <c r="Q65" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R65" s="12"/>
@@ -8458,7 +8457,7 @@
       <c r="A66" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="7" t="s">
         <v>217</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -8478,18 +8477,18 @@
       <c r="I66" s="8"/>
       <c r="J66" s="9"/>
       <c r="K66" s="8"/>
-      <c r="L66" s="15" t="s">
+      <c r="L66" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="N66" s="15" t="s">
+      <c r="N66" s="7" t="s">
         <v>220</v>
       </c>
       <c r="O66" s="9"/>
       <c r="P66" s="9"/>
-      <c r="Q66" s="15" t="s">
+      <c r="Q66" s="7" t="s">
         <v>221</v>
       </c>
       <c r="R66" s="7"/>
@@ -8540,7 +8539,7 @@
       <c r="A68" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="7" t="s">
         <v>226</v>
       </c>
       <c r="C68" s="7" t="s">
@@ -8560,18 +8559,18 @@
       <c r="I68" s="8"/>
       <c r="J68" s="9"/>
       <c r="K68" s="8"/>
-      <c r="L68" s="15" t="s">
+      <c r="L68" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="N68" s="15" t="s">
+      <c r="N68" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O68" s="9"/>
       <c r="P68" s="9"/>
-      <c r="Q68" s="15" t="s">
+      <c r="Q68" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R68" s="7"/>
@@ -8580,7 +8579,7 @@
       <c r="A69" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="12" t="s">
         <v>228</v>
       </c>
       <c r="C69" s="12" t="s">
@@ -8600,18 +8599,18 @@
       <c r="I69" s="13"/>
       <c r="J69" s="14"/>
       <c r="K69" s="13"/>
-      <c r="L69" s="18" t="s">
+      <c r="L69" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M69" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="N69" s="18" t="s">
+      <c r="N69" s="12" t="s">
         <v>231</v>
       </c>
       <c r="O69" s="14"/>
       <c r="P69" s="14"/>
-      <c r="Q69" s="18" t="s">
+      <c r="Q69" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R69" s="12"/>
@@ -8950,7 +8949,7 @@
       <c r="A78" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="7" t="s">
         <v>252</v>
       </c>
       <c r="C78" s="7" t="s">
@@ -8978,17 +8977,17 @@
       <c r="K78" s="8">
         <v>46112</v>
       </c>
-      <c r="L78" s="15" t="s">
+      <c r="L78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="N78" s="15" t="s">
+      <c r="N78" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O78" s="9"/>
-      <c r="P78" s="16" t="s">
+      <c r="P78" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q78" s="7"/>
@@ -8998,7 +8997,7 @@
       <c r="A79" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="12" t="s">
         <v>254</v>
       </c>
       <c r="C79" s="12" t="s">
@@ -9024,20 +9023,20 @@
       </c>
       <c r="J79" s="14"/>
       <c r="K79" s="13"/>
-      <c r="L79" s="18" t="s">
+      <c r="L79" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M79" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="N79" s="18" t="s">
+      <c r="N79" s="12" t="s">
         <v>256</v>
       </c>
       <c r="O79" s="14"/>
-      <c r="P79" s="19" t="s">
+      <c r="P79" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q79" s="18" t="s">
+      <c r="Q79" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R79" s="12"/>
@@ -9428,7 +9427,7 @@
       <c r="A89" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="12" t="s">
         <v>280</v>
       </c>
       <c r="C89" s="12" t="s">
@@ -9454,23 +9453,23 @@
       </c>
       <c r="J89" s="14"/>
       <c r="K89" s="13"/>
-      <c r="L89" s="18" t="s">
+      <c r="L89" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M89" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="N89" s="18" t="s">
+      <c r="N89" s="12" t="s">
         <v>283</v>
       </c>
       <c r="O89" s="14"/>
-      <c r="P89" s="19" t="s">
+      <c r="P89" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q89" s="18" t="s">
+      <c r="Q89" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R89" s="18" t="s">
+      <c r="R89" s="12" t="s">
         <v>284</v>
       </c>
     </row>
@@ -9478,7 +9477,7 @@
       <c r="A90" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="7" t="s">
         <v>285</v>
       </c>
       <c r="C90" s="7" t="s">
@@ -9498,18 +9497,18 @@
       <c r="I90" s="8"/>
       <c r="J90" s="9"/>
       <c r="K90" s="8"/>
-      <c r="L90" s="15" t="s">
+      <c r="L90" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="N90" s="15" t="s">
+      <c r="N90" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O90" s="9"/>
       <c r="P90" s="9"/>
-      <c r="Q90" s="15" t="s">
+      <c r="Q90" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R90" s="7"/>
@@ -9894,7 +9893,7 @@
       <c r="A100" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" s="7" t="s">
         <v>309</v>
       </c>
       <c r="C100" s="7" t="s">
@@ -9920,20 +9919,20 @@
       </c>
       <c r="J100" s="9"/>
       <c r="K100" s="8"/>
-      <c r="L100" s="15" t="s">
+      <c r="L100" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="N100" s="15" t="s">
+      <c r="N100" s="7" t="s">
         <v>311</v>
       </c>
       <c r="O100" s="9"/>
-      <c r="P100" s="16" t="s">
+      <c r="P100" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q100" s="15" t="s">
+      <c r="Q100" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R100" s="7"/>
@@ -9942,7 +9941,7 @@
       <c r="A101" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="12" t="s">
         <v>312</v>
       </c>
       <c r="C101" s="12" t="s">
@@ -9962,18 +9961,18 @@
       <c r="I101" s="13"/>
       <c r="J101" s="14"/>
       <c r="K101" s="13"/>
-      <c r="L101" s="18" t="s">
+      <c r="L101" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M101" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="N101" s="18" t="s">
+      <c r="N101" s="12" t="s">
         <v>213</v>
       </c>
       <c r="O101" s="14"/>
       <c r="P101" s="14"/>
-      <c r="Q101" s="18" t="s">
+      <c r="Q101" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R101" s="12"/>
@@ -10576,7 +10575,7 @@
       <c r="A117" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="12" t="s">
         <v>347</v>
       </c>
       <c r="C117" s="12" t="s">
@@ -10604,21 +10603,21 @@
         <v>86</v>
       </c>
       <c r="K117" s="13"/>
-      <c r="L117" s="18" t="s">
+      <c r="L117" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M117" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="N117" s="18" t="s">
+      <c r="N117" s="12" t="s">
         <v>248</v>
       </c>
       <c r="O117" s="14"/>
-      <c r="P117" s="19" t="s">
+      <c r="P117" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q117" s="12"/>
-      <c r="R117" s="21" t="s">
+      <c r="R117" s="20" t="s">
         <v>350</v>
       </c>
     </row>
@@ -10626,7 +10625,7 @@
       <c r="A118" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B118" s="15" t="s">
+      <c r="B118" s="7" t="s">
         <v>351</v>
       </c>
       <c r="C118" s="7" t="s">
@@ -10646,18 +10645,18 @@
       <c r="I118" s="8"/>
       <c r="J118" s="9"/>
       <c r="K118" s="8"/>
-      <c r="L118" s="15" t="s">
+      <c r="L118" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="N118" s="15" t="s">
+      <c r="N118" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O118" s="9"/>
       <c r="P118" s="9"/>
-      <c r="Q118" s="15" t="s">
+      <c r="Q118" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R118" s="7"/>
@@ -11022,7 +11021,7 @@
       <c r="A128" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B128" s="7" t="s">
         <v>373</v>
       </c>
       <c r="C128" s="7" t="s">
@@ -11050,21 +11049,21 @@
         <v>86</v>
       </c>
       <c r="K128" s="8"/>
-      <c r="L128" s="15" t="s">
+      <c r="L128" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M128" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="N128" s="15" t="s">
+      <c r="N128" s="7" t="s">
         <v>248</v>
       </c>
       <c r="O128" s="9"/>
-      <c r="P128" s="16" t="s">
+      <c r="P128" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q128" s="7"/>
-      <c r="R128" s="15" t="s">
+      <c r="R128" s="7" t="s">
         <v>350</v>
       </c>
     </row>
@@ -11072,7 +11071,7 @@
       <c r="A129" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B129" s="18" t="s">
+      <c r="B129" s="12" t="s">
         <v>376</v>
       </c>
       <c r="C129" s="12" t="s">
@@ -11092,18 +11091,18 @@
       <c r="I129" s="13"/>
       <c r="J129" s="14"/>
       <c r="K129" s="13"/>
-      <c r="L129" s="18" t="s">
+      <c r="L129" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M129" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="N129" s="18" t="s">
+      <c r="N129" s="12" t="s">
         <v>213</v>
       </c>
       <c r="O129" s="14"/>
       <c r="P129" s="14"/>
-      <c r="Q129" s="18" t="s">
+      <c r="Q129" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R129" s="12"/>
@@ -11328,7 +11327,7 @@
       <c r="A135" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B135" s="18" t="s">
+      <c r="B135" s="12" t="s">
         <v>389</v>
       </c>
       <c r="C135" s="12" t="s">
@@ -11354,20 +11353,20 @@
       </c>
       <c r="J135" s="14"/>
       <c r="K135" s="13"/>
-      <c r="L135" s="18" t="s">
+      <c r="L135" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M135" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="N135" s="18" t="s">
+      <c r="N135" s="12" t="s">
         <v>391</v>
       </c>
       <c r="O135" s="14"/>
-      <c r="P135" s="19" t="s">
+      <c r="P135" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q135" s="18" t="s">
+      <c r="Q135" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R135" s="12"/>
@@ -11376,7 +11375,7 @@
       <c r="A136" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B136" s="15" t="s">
+      <c r="B136" s="7" t="s">
         <v>392</v>
       </c>
       <c r="C136" s="7" t="s">
@@ -11396,18 +11395,18 @@
       <c r="I136" s="8"/>
       <c r="J136" s="9"/>
       <c r="K136" s="8"/>
-      <c r="L136" s="15" t="s">
+      <c r="L136" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M136" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="N136" s="15" t="s">
+      <c r="N136" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O136" s="9"/>
       <c r="P136" s="9"/>
-      <c r="Q136" s="15" t="s">
+      <c r="Q136" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R136" s="7"/>
@@ -11628,7 +11627,7 @@
       <c r="A142" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B142" s="15" t="s">
+      <c r="B142" s="7" t="s">
         <v>406</v>
       </c>
       <c r="C142" s="7" t="s">
@@ -11656,21 +11655,21 @@
         <v>86</v>
       </c>
       <c r="K142" s="8"/>
-      <c r="L142" s="15" t="s">
+      <c r="L142" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M142" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="N142" s="15" t="s">
+      <c r="N142" s="7" t="s">
         <v>248</v>
       </c>
       <c r="O142" s="9"/>
-      <c r="P142" s="16" t="s">
+      <c r="P142" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q142" s="7"/>
-      <c r="R142" s="15" t="s">
+      <c r="R142" s="7" t="s">
         <v>350</v>
       </c>
     </row>
@@ -11678,7 +11677,7 @@
       <c r="A143" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B143" s="18" t="s">
+      <c r="B143" s="12" t="s">
         <v>408</v>
       </c>
       <c r="C143" s="12" t="s">
@@ -11698,18 +11697,18 @@
       <c r="I143" s="13"/>
       <c r="J143" s="14"/>
       <c r="K143" s="13"/>
-      <c r="L143" s="18" t="s">
+      <c r="L143" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M143" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="N143" s="18" t="s">
+      <c r="N143" s="12" t="s">
         <v>213</v>
       </c>
       <c r="O143" s="14"/>
       <c r="P143" s="14"/>
-      <c r="Q143" s="18" t="s">
+      <c r="Q143" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R143" s="12"/>
@@ -11848,7 +11847,7 @@
       <c r="A147" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B147" s="18" t="s">
+      <c r="B147" s="12" t="s">
         <v>417</v>
       </c>
       <c r="C147" s="12" t="s">
@@ -11874,23 +11873,23 @@
       </c>
       <c r="J147" s="14"/>
       <c r="K147" s="13"/>
-      <c r="L147" s="18" t="s">
+      <c r="L147" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M147" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="N147" s="18" t="s">
+      <c r="N147" s="12" t="s">
         <v>311</v>
       </c>
       <c r="O147" s="14"/>
-      <c r="P147" s="19" t="s">
+      <c r="P147" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q147" s="18" t="s">
+      <c r="Q147" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R147" s="18" t="s">
+      <c r="R147" s="12" t="s">
         <v>419</v>
       </c>
     </row>
@@ -11898,7 +11897,7 @@
       <c r="A148" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B148" s="15" t="s">
+      <c r="B148" s="7" t="s">
         <v>420</v>
       </c>
       <c r="C148" s="7" t="s">
@@ -11918,18 +11917,18 @@
       <c r="I148" s="8"/>
       <c r="J148" s="9"/>
       <c r="K148" s="8"/>
-      <c r="L148" s="15" t="s">
+      <c r="L148" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M148" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="N148" s="15" t="s">
+      <c r="N148" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O148" s="9"/>
       <c r="P148" s="9"/>
-      <c r="Q148" s="15" t="s">
+      <c r="Q148" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R148" s="7"/>
@@ -12026,7 +12025,7 @@
       <c r="A151" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B151" s="18" t="s">
+      <c r="B151" s="12" t="s">
         <v>427</v>
       </c>
       <c r="C151" s="12" t="s">
@@ -12052,23 +12051,23 @@
       </c>
       <c r="J151" s="14"/>
       <c r="K151" s="13"/>
-      <c r="L151" s="18" t="s">
+      <c r="L151" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M151" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="N151" s="18" t="s">
+      <c r="N151" s="12" t="s">
         <v>283</v>
       </c>
       <c r="O151" s="14"/>
-      <c r="P151" s="19" t="s">
+      <c r="P151" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q151" s="18" t="s">
+      <c r="Q151" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R151" s="18" t="s">
+      <c r="R151" s="12" t="s">
         <v>284</v>
       </c>
     </row>
@@ -12076,7 +12075,7 @@
       <c r="A152" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B152" s="15" t="s">
+      <c r="B152" s="7" t="s">
         <v>429</v>
       </c>
       <c r="C152" s="7" t="s">
@@ -12096,18 +12095,18 @@
       <c r="I152" s="8"/>
       <c r="J152" s="9"/>
       <c r="K152" s="8"/>
-      <c r="L152" s="15" t="s">
+      <c r="L152" s="7" t="s">
         <v>431</v>
       </c>
       <c r="M152" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="N152" s="15" t="s">
+      <c r="N152" s="7" t="s">
         <v>213</v>
       </c>
       <c r="O152" s="9"/>
       <c r="P152" s="9"/>
-      <c r="Q152" s="15" t="s">
+      <c r="Q152" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R152" s="7"/>
@@ -12116,7 +12115,7 @@
       <c r="A153" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B153" s="18" t="s">
+      <c r="B153" s="12" t="s">
         <v>432</v>
       </c>
       <c r="C153" s="12" t="s">
@@ -12144,23 +12143,23 @@
       <c r="K153" s="13">
         <v>46203</v>
       </c>
-      <c r="L153" s="18" t="s">
+      <c r="L153" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M153" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="N153" s="18" t="s">
+      <c r="N153" s="12" t="s">
         <v>213</v>
       </c>
       <c r="O153" s="14"/>
-      <c r="P153" s="19" t="s">
+      <c r="P153" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q153" s="18" t="s">
+      <c r="Q153" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R153" s="18" t="s">
+      <c r="R153" s="12" t="s">
         <v>436</v>
       </c>
     </row>
@@ -12168,7 +12167,7 @@
       <c r="A154" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B154" s="15" t="s">
+      <c r="B154" s="7" t="s">
         <v>437</v>
       </c>
       <c r="C154" s="7" t="s">
@@ -12194,20 +12193,20 @@
       </c>
       <c r="J154" s="9"/>
       <c r="K154" s="8"/>
-      <c r="L154" s="15" t="s">
+      <c r="L154" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M154" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="N154" s="15" t="s">
+      <c r="N154" s="7" t="s">
         <v>440</v>
       </c>
       <c r="O154" s="9"/>
-      <c r="P154" s="16" t="s">
+      <c r="P154" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q154" s="15" t="s">
+      <c r="Q154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R154" s="7"/>
@@ -12260,7 +12259,7 @@
       <c r="A156" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B156" s="15" t="s">
+      <c r="B156" s="7" t="s">
         <v>444</v>
       </c>
       <c r="C156" s="7" t="s">
@@ -12286,23 +12285,23 @@
       </c>
       <c r="J156" s="9"/>
       <c r="K156" s="8"/>
-      <c r="L156" s="15" t="s">
+      <c r="L156" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M156" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="N156" s="15" t="s">
+      <c r="N156" s="7" t="s">
         <v>311</v>
       </c>
       <c r="O156" s="9"/>
-      <c r="P156" s="16" t="s">
+      <c r="P156" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q156" s="15" t="s">
+      <c r="Q156" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R156" s="23" t="s">
+      <c r="R156" s="22" t="s">
         <v>445</v>
       </c>
     </row>
@@ -12310,7 +12309,7 @@
       <c r="A157" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B157" s="18" t="s">
+      <c r="B157" s="12" t="s">
         <v>446</v>
       </c>
       <c r="C157" s="12" t="s">
@@ -12330,18 +12329,18 @@
       <c r="I157" s="13"/>
       <c r="J157" s="14"/>
       <c r="K157" s="13"/>
-      <c r="L157" s="18" t="s">
+      <c r="L157" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M157" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="N157" s="18" t="s">
+      <c r="N157" s="12" t="s">
         <v>213</v>
       </c>
       <c r="O157" s="14"/>
       <c r="P157" s="14"/>
-      <c r="Q157" s="18" t="s">
+      <c r="Q157" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R157" s="12"/>
@@ -12440,7 +12439,7 @@
       <c r="A160" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B160" s="15" t="s">
+      <c r="B160" s="7" t="s">
         <v>457</v>
       </c>
       <c r="C160" s="7" t="s">
@@ -12466,21 +12465,21 @@
       </c>
       <c r="J160" s="9"/>
       <c r="K160" s="8"/>
-      <c r="L160" s="15" t="s">
+      <c r="L160" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M160" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="N160" s="15" t="s">
+      <c r="N160" s="7" t="s">
         <v>459</v>
       </c>
       <c r="O160" s="9"/>
-      <c r="P160" s="16" t="s">
+      <c r="P160" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q160" s="7"/>
-      <c r="R160" s="15" t="s">
+      <c r="R160" s="7" t="s">
         <v>460</v>
       </c>
     </row>
@@ -12488,7 +12487,7 @@
       <c r="A161" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B161" s="18" t="s">
+      <c r="B161" s="12" t="s">
         <v>461</v>
       </c>
       <c r="C161" s="12" t="s">
@@ -12514,18 +12513,18 @@
       </c>
       <c r="J161" s="14"/>
       <c r="K161" s="13"/>
-      <c r="L161" s="18" t="s">
+      <c r="L161" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M161" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="N161" s="18" t="s">
+      <c r="N161" s="12" t="s">
         <v>465</v>
       </c>
       <c r="O161" s="14"/>
       <c r="P161" s="14"/>
-      <c r="Q161" s="18" t="s">
+      <c r="Q161" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R161" s="12"/>
@@ -12742,7 +12741,7 @@
       <c r="A167" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B167" s="18" t="s">
+      <c r="B167" s="12" t="s">
         <v>480</v>
       </c>
       <c r="C167" s="12" t="s">
@@ -12768,17 +12767,17 @@
       </c>
       <c r="J167" s="14"/>
       <c r="K167" s="13"/>
-      <c r="L167" s="18" t="s">
+      <c r="L167" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M167" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="N167" s="18" t="s">
+      <c r="N167" s="12" t="s">
         <v>482</v>
       </c>
       <c r="O167" s="14"/>
-      <c r="P167" s="19" t="s">
+      <c r="P167" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q167" s="12"/>
@@ -12968,7 +12967,7 @@
       <c r="A173" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B173" s="18" t="s">
+      <c r="B173" s="12" t="s">
         <v>496</v>
       </c>
       <c r="C173" s="12" t="s">
@@ -12994,20 +12993,20 @@
       </c>
       <c r="J173" s="14"/>
       <c r="K173" s="13"/>
-      <c r="L173" s="18" t="s">
+      <c r="L173" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M173" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="N173" s="18" t="s">
+      <c r="N173" s="12" t="s">
         <v>499</v>
       </c>
       <c r="O173" s="14"/>
-      <c r="P173" s="19" t="s">
+      <c r="P173" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q173" s="18" t="s">
+      <c r="Q173" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R173" s="12"/>
@@ -13800,7 +13799,7 @@
       <c r="A193" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B193" s="18" t="s">
+      <c r="B193" s="12" t="s">
         <v>545</v>
       </c>
       <c r="C193" s="12" t="s">
@@ -13826,17 +13825,17 @@
       </c>
       <c r="J193" s="14"/>
       <c r="K193" s="13"/>
-      <c r="L193" s="18" t="s">
+      <c r="L193" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M193" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="N193" s="18" t="s">
+      <c r="N193" s="12" t="s">
         <v>547</v>
       </c>
       <c r="O193" s="14"/>
-      <c r="P193" s="19" t="s">
+      <c r="P193" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q193" s="12"/>
@@ -13970,7 +13969,7 @@
       <c r="A197" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B197" s="18" t="s">
+      <c r="B197" s="12" t="s">
         <v>560</v>
       </c>
       <c r="C197" s="12" t="s">
@@ -13996,17 +13995,17 @@
       </c>
       <c r="J197" s="14"/>
       <c r="K197" s="13"/>
-      <c r="L197" s="18" t="s">
+      <c r="L197" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M197" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="N197" s="18" t="s">
+      <c r="N197" s="12" t="s">
         <v>547</v>
       </c>
       <c r="O197" s="14"/>
-      <c r="P197" s="19" t="s">
+      <c r="P197" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q197" s="12"/>
@@ -14138,7 +14137,7 @@
       <c r="A201" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B201" s="18" t="s">
+      <c r="B201" s="12" t="s">
         <v>570</v>
       </c>
       <c r="C201" s="12" t="s">
@@ -14164,17 +14163,17 @@
       </c>
       <c r="J201" s="14"/>
       <c r="K201" s="13"/>
-      <c r="L201" s="18" t="s">
+      <c r="L201" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M201" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="N201" s="18" t="s">
+      <c r="N201" s="12" t="s">
         <v>547</v>
       </c>
       <c r="O201" s="14"/>
-      <c r="P201" s="19" t="s">
+      <c r="P201" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q201" s="12"/>
@@ -14312,7 +14311,7 @@
       <c r="A205" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B205" s="18" t="s">
+      <c r="B205" s="12" t="s">
         <v>584</v>
       </c>
       <c r="C205" s="12" t="s">
@@ -14338,20 +14337,20 @@
       </c>
       <c r="J205" s="14"/>
       <c r="K205" s="13"/>
-      <c r="L205" s="18" t="s">
+      <c r="L205" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M205" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="N205" s="18" t="s">
+      <c r="N205" s="12" t="s">
         <v>547</v>
       </c>
       <c r="O205" s="14"/>
-      <c r="P205" s="19" t="s">
+      <c r="P205" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q205" s="18" t="s">
+      <c r="Q205" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R205" s="12"/>
@@ -14404,7 +14403,7 @@
       <c r="A207" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B207" s="18" t="s">
+      <c r="B207" s="12" t="s">
         <v>589</v>
       </c>
       <c r="C207" s="12" t="s">
@@ -14432,17 +14431,17 @@
         <v>86</v>
       </c>
       <c r="K207" s="13"/>
-      <c r="L207" s="18" t="s">
+      <c r="L207" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M207" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="N207" s="18" t="s">
+      <c r="N207" s="12" t="s">
         <v>593</v>
       </c>
       <c r="O207" s="14"/>
-      <c r="P207" s="19" t="s">
+      <c r="P207" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q207" s="12"/>
@@ -14582,7 +14581,7 @@
       <c r="A211" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B211" s="18" t="s">
+      <c r="B211" s="12" t="s">
         <v>608</v>
       </c>
       <c r="C211" s="12" t="s">
@@ -14610,20 +14609,20 @@
         <v>86</v>
       </c>
       <c r="K211" s="13"/>
-      <c r="L211" s="18" t="s">
+      <c r="L211" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M211" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="N211" s="18" t="s">
+      <c r="N211" s="12" t="s">
         <v>610</v>
       </c>
       <c r="O211" s="14"/>
-      <c r="P211" s="19" t="s">
+      <c r="P211" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q211" s="18" t="s">
+      <c r="Q211" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R211" s="12"/>
@@ -14708,7 +14707,7 @@
       <c r="M213" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="N213" s="18" t="s">
+      <c r="N213" s="12" t="s">
         <v>607</v>
       </c>
       <c r="O213" s="14"/>
@@ -14720,7 +14719,7 @@
       <c r="A214" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B214" s="15" t="s">
+      <c r="B214" s="7" t="s">
         <v>617</v>
       </c>
       <c r="C214" s="7" t="s">
@@ -14746,20 +14745,20 @@
       </c>
       <c r="J214" s="9"/>
       <c r="K214" s="8"/>
-      <c r="L214" s="15" t="s">
+      <c r="L214" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M214" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="N214" s="15" t="s">
+      <c r="N214" s="7" t="s">
         <v>619</v>
       </c>
       <c r="O214" s="9"/>
-      <c r="P214" s="16" t="s">
+      <c r="P214" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q214" s="15" t="s">
+      <c r="Q214" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R214" s="7"/>
@@ -14944,7 +14943,7 @@
       <c r="A219" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B219" s="18" t="s">
+      <c r="B219" s="12" t="s">
         <v>634</v>
       </c>
       <c r="C219" s="12" t="s">
@@ -14972,20 +14971,20 @@
         <v>86</v>
       </c>
       <c r="K219" s="13"/>
-      <c r="L219" s="18" t="s">
+      <c r="L219" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M219" s="17" t="s">
         <v>635</v>
       </c>
-      <c r="N219" s="18" t="s">
+      <c r="N219" s="12" t="s">
         <v>636</v>
       </c>
       <c r="O219" s="14"/>
-      <c r="P219" s="19" t="s">
+      <c r="P219" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q219" s="18" t="s">
+      <c r="Q219" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R219" s="12"/>
@@ -15168,7 +15167,7 @@
       <c r="A224" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B224" s="15" t="s">
+      <c r="B224" s="7" t="s">
         <v>648</v>
       </c>
       <c r="C224" s="7" t="s">
@@ -15196,23 +15195,23 @@
         <v>86</v>
       </c>
       <c r="K224" s="8"/>
-      <c r="L224" s="15" t="s">
+      <c r="L224" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M224" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="N224" s="15" t="s">
+      <c r="N224" s="7" t="s">
         <v>636</v>
       </c>
       <c r="O224" s="9"/>
-      <c r="P224" s="16" t="s">
+      <c r="P224" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q224" s="15" t="s">
+      <c r="Q224" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R224" s="15" t="s">
+      <c r="R224" s="7" t="s">
         <v>650</v>
       </c>
     </row>
@@ -15430,7 +15429,7 @@
       <c r="A230" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B230" s="15" t="s">
+      <c r="B230" s="7" t="s">
         <v>668</v>
       </c>
       <c r="C230" s="7" t="s">
@@ -15456,17 +15455,17 @@
       </c>
       <c r="J230" s="9"/>
       <c r="K230" s="8"/>
-      <c r="L230" s="15" t="s">
+      <c r="L230" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M230" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="N230" s="15" t="s">
+      <c r="N230" s="7" t="s">
         <v>671</v>
       </c>
       <c r="O230" s="9"/>
-      <c r="P230" s="16" t="s">
+      <c r="P230" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q230" s="7"/>
@@ -15702,7 +15701,7 @@
       <c r="A237" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B237" s="18" t="s">
+      <c r="B237" s="12" t="s">
         <v>693</v>
       </c>
       <c r="C237" s="12" t="s">
@@ -15728,17 +15727,17 @@
       </c>
       <c r="J237" s="14"/>
       <c r="K237" s="13"/>
-      <c r="L237" s="18" t="s">
+      <c r="L237" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M237" s="11" t="s">
         <v>694</v>
       </c>
-      <c r="N237" s="18" t="s">
+      <c r="N237" s="12" t="s">
         <v>692</v>
       </c>
       <c r="O237" s="14"/>
-      <c r="P237" s="19" t="s">
+      <c r="P237" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q237" s="12"/>
@@ -16094,7 +16093,7 @@
       <c r="A246" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B246" s="15" t="s">
+      <c r="B246" s="7" t="s">
         <v>713</v>
       </c>
       <c r="C246" s="7" t="s">
@@ -16120,20 +16119,20 @@
       </c>
       <c r="J246" s="9"/>
       <c r="K246" s="8"/>
-      <c r="L246" s="15" t="s">
+      <c r="L246" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M246" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="N246" s="15" t="s">
+      <c r="N246" s="7" t="s">
         <v>459</v>
       </c>
       <c r="O246" s="9"/>
-      <c r="P246" s="16" t="s">
+      <c r="P246" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q246" s="15" t="s">
+      <c r="Q246" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R246" s="7"/>
@@ -16352,7 +16351,7 @@
       <c r="A252" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B252" s="15" t="s">
+      <c r="B252" s="7" t="s">
         <v>729</v>
       </c>
       <c r="C252" s="7" t="s">
@@ -16378,20 +16377,20 @@
       </c>
       <c r="J252" s="9"/>
       <c r="K252" s="8"/>
-      <c r="L252" s="15" t="s">
+      <c r="L252" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M252" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="N252" s="15" t="s">
+      <c r="N252" s="7" t="s">
         <v>459</v>
       </c>
       <c r="O252" s="9"/>
-      <c r="P252" s="16" t="s">
+      <c r="P252" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q252" s="15" t="s">
+      <c r="Q252" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R252" s="7"/>
@@ -16522,7 +16521,7 @@
       <c r="A256" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B256" s="15" t="s">
+      <c r="B256" s="7" t="s">
         <v>741</v>
       </c>
       <c r="C256" s="7" t="s">
@@ -16548,13 +16547,13 @@
       </c>
       <c r="J256" s="9"/>
       <c r="K256" s="8"/>
-      <c r="L256" s="15" t="s">
+      <c r="L256" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M256" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="N256" s="15" t="s">
+      <c r="N256" s="7" t="s">
         <v>68</v>
       </c>
       <c r="O256" s="9"/>
@@ -17412,7 +17411,7 @@
       <c r="A278" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B278" s="15" t="s">
+      <c r="B278" s="7" t="s">
         <v>796</v>
       </c>
       <c r="C278" s="7" t="s">
@@ -17438,20 +17437,20 @@
       </c>
       <c r="J278" s="9"/>
       <c r="K278" s="8"/>
-      <c r="L278" s="15" t="s">
+      <c r="L278" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M278" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="N278" s="15" t="s">
+      <c r="N278" s="7" t="s">
         <v>692</v>
       </c>
       <c r="O278" s="9"/>
-      <c r="P278" s="16" t="s">
+      <c r="P278" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q278" s="15" t="s">
+      <c r="Q278" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R278" s="7"/>
@@ -17756,7 +17755,7 @@
       <c r="A286" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B286" s="15" t="s">
+      <c r="B286" s="7" t="s">
         <v>812</v>
       </c>
       <c r="C286" s="7" t="s">
@@ -17782,20 +17781,20 @@
       </c>
       <c r="J286" s="9"/>
       <c r="K286" s="8"/>
-      <c r="L286" s="15" t="s">
+      <c r="L286" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M286" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="N286" s="15" t="s">
+      <c r="N286" s="7" t="s">
         <v>692</v>
       </c>
       <c r="O286" s="9"/>
-      <c r="P286" s="16" t="s">
+      <c r="P286" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q286" s="15" t="s">
+      <c r="Q286" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R286" s="7"/>
@@ -18212,7 +18211,7 @@
       <c r="A297" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B297" s="18" t="s">
+      <c r="B297" s="12" t="s">
         <v>838</v>
       </c>
       <c r="C297" s="12" t="s">
@@ -18238,20 +18237,20 @@
       </c>
       <c r="J297" s="14"/>
       <c r="K297" s="13"/>
-      <c r="L297" s="18" t="s">
+      <c r="L297" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M297" s="11" t="s">
         <v>841</v>
       </c>
-      <c r="N297" s="18" t="s">
+      <c r="N297" s="12" t="s">
         <v>842</v>
       </c>
       <c r="O297" s="14"/>
-      <c r="P297" s="19" t="s">
+      <c r="P297" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q297" s="18" t="s">
+      <c r="Q297" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R297" s="12"/>
@@ -18552,7 +18551,7 @@
       <c r="A305" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B305" s="18" t="s">
+      <c r="B305" s="12" t="s">
         <v>864</v>
       </c>
       <c r="C305" s="12" t="s">
@@ -18578,20 +18577,20 @@
       </c>
       <c r="J305" s="14"/>
       <c r="K305" s="13"/>
-      <c r="L305" s="18" t="s">
+      <c r="L305" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M305" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="N305" s="18" t="s">
+      <c r="N305" s="12" t="s">
         <v>692</v>
       </c>
       <c r="O305" s="14"/>
-      <c r="P305" s="19" t="s">
+      <c r="P305" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q305" s="18" t="s">
+      <c r="Q305" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R305" s="12"/>
@@ -19422,7 +19421,7 @@
       <c r="A327" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B327" s="18" t="s">
+      <c r="B327" s="12" t="s">
         <v>914</v>
       </c>
       <c r="C327" s="12" t="s">
@@ -19448,17 +19447,17 @@
       </c>
       <c r="J327" s="14"/>
       <c r="K327" s="13"/>
-      <c r="L327" s="18" t="s">
+      <c r="L327" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M327" s="11" t="s">
         <v>916</v>
       </c>
-      <c r="N327" s="18" t="s">
+      <c r="N327" s="12" t="s">
         <v>917</v>
       </c>
       <c r="O327" s="14"/>
-      <c r="P327" s="19" t="s">
+      <c r="P327" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q327" s="12"/>
@@ -19512,7 +19511,7 @@
       <c r="A329" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B329" s="18" t="s">
+      <c r="B329" s="12" t="s">
         <v>921</v>
       </c>
       <c r="C329" s="12" t="s">
@@ -19538,20 +19537,20 @@
       </c>
       <c r="J329" s="14"/>
       <c r="K329" s="13"/>
-      <c r="L329" s="18" t="s">
+      <c r="L329" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M329" s="11" t="s">
         <v>923</v>
       </c>
-      <c r="N329" s="18" t="s">
+      <c r="N329" s="12" t="s">
         <v>924</v>
       </c>
       <c r="O329" s="14"/>
-      <c r="P329" s="19" t="s">
+      <c r="P329" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q329" s="18" t="s">
+      <c r="Q329" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R329" s="12"/>
@@ -19690,7 +19689,7 @@
       <c r="A333" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B333" s="18" t="s">
+      <c r="B333" s="12" t="s">
         <v>936</v>
       </c>
       <c r="C333" s="12" t="s">
@@ -19716,13 +19715,13 @@
       </c>
       <c r="J333" s="14"/>
       <c r="K333" s="13"/>
-      <c r="L333" s="18" t="s">
+      <c r="L333" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M333" s="11" t="s">
         <v>939</v>
       </c>
-      <c r="N333" s="18" t="s">
+      <c r="N333" s="12" t="s">
         <v>68</v>
       </c>
       <c r="O333" s="14"/>
@@ -19822,7 +19821,7 @@
       <c r="A336" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B336" s="15" t="s">
+      <c r="B336" s="7" t="s">
         <v>946</v>
       </c>
       <c r="C336" s="7" t="s">
@@ -19848,20 +19847,20 @@
       </c>
       <c r="J336" s="9"/>
       <c r="K336" s="8"/>
-      <c r="L336" s="15" t="s">
+      <c r="L336" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M336" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="N336" s="15" t="s">
+      <c r="N336" s="7" t="s">
         <v>459</v>
       </c>
       <c r="O336" s="9"/>
-      <c r="P336" s="16" t="s">
+      <c r="P336" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q336" s="15" t="s">
+      <c r="Q336" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R336" s="7"/>
@@ -19914,7 +19913,7 @@
       <c r="A338" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B338" s="15" t="s">
+      <c r="B338" s="7" t="s">
         <v>950</v>
       </c>
       <c r="C338" s="7" t="s">
@@ -19940,20 +19939,20 @@
       </c>
       <c r="J338" s="9"/>
       <c r="K338" s="8"/>
-      <c r="L338" s="15" t="s">
+      <c r="L338" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M338" s="6" t="s">
         <v>951</v>
       </c>
-      <c r="N338" s="15" t="s">
+      <c r="N338" s="7" t="s">
         <v>924</v>
       </c>
       <c r="O338" s="9"/>
-      <c r="P338" s="16" t="s">
+      <c r="P338" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q338" s="15" t="s">
+      <c r="Q338" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R338" s="7"/>
@@ -20180,7 +20179,7 @@
       <c r="A344" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B344" s="15" t="s">
+      <c r="B344" s="7" t="s">
         <v>961</v>
       </c>
       <c r="C344" s="7" t="s">
@@ -20208,20 +20207,20 @@
       <c r="K344" s="8">
         <v>47208</v>
       </c>
-      <c r="L344" s="15" t="s">
+      <c r="L344" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M344" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="N344" s="15" t="s">
+      <c r="N344" s="7" t="s">
         <v>965</v>
       </c>
       <c r="O344" s="9"/>
-      <c r="P344" s="16" t="s">
+      <c r="P344" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q344" s="15" t="s">
+      <c r="Q344" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R344" s="7"/>
@@ -20230,7 +20229,7 @@
       <c r="A345" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B345" s="18" t="s">
+      <c r="B345" s="12" t="s">
         <v>966</v>
       </c>
       <c r="C345" s="12" t="s">
@@ -20256,18 +20255,18 @@
       </c>
       <c r="J345" s="14"/>
       <c r="K345" s="13"/>
-      <c r="L345" s="18" t="s">
+      <c r="L345" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M345" s="11" t="s">
         <v>969</v>
       </c>
-      <c r="N345" s="18" t="s">
+      <c r="N345" s="12" t="s">
         <v>970</v>
       </c>
       <c r="O345" s="14"/>
       <c r="P345" s="14"/>
-      <c r="Q345" s="18" t="s">
+      <c r="Q345" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R345" s="12"/>
@@ -20358,7 +20357,7 @@
       <c r="A348" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B348" s="15" t="s">
+      <c r="B348" s="7" t="s">
         <v>977</v>
       </c>
       <c r="C348" s="7" t="s">
@@ -20384,20 +20383,20 @@
       </c>
       <c r="J348" s="9"/>
       <c r="K348" s="8"/>
-      <c r="L348" s="15" t="s">
+      <c r="L348" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M348" s="6" t="s">
         <v>841</v>
       </c>
-      <c r="N348" s="15" t="s">
+      <c r="N348" s="7" t="s">
         <v>842</v>
       </c>
       <c r="O348" s="9"/>
-      <c r="P348" s="16" t="s">
+      <c r="P348" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q348" s="15" t="s">
+      <c r="Q348" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R348" s="7"/>
@@ -20494,7 +20493,7 @@
       <c r="A351" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B351" s="18" t="s">
+      <c r="B351" s="12" t="s">
         <v>984</v>
       </c>
       <c r="C351" s="12" t="s">
@@ -20520,20 +20519,20 @@
       </c>
       <c r="J351" s="14"/>
       <c r="K351" s="13"/>
-      <c r="L351" s="18" t="s">
+      <c r="L351" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M351" s="11" t="s">
         <v>841</v>
       </c>
-      <c r="N351" s="18" t="s">
+      <c r="N351" s="12" t="s">
         <v>842</v>
       </c>
       <c r="O351" s="14"/>
-      <c r="P351" s="19" t="s">
+      <c r="P351" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q351" s="18" t="s">
+      <c r="Q351" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R351" s="12"/>
@@ -20584,7 +20583,7 @@
       <c r="A353" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B353" s="18" t="s">
+      <c r="B353" s="12" t="s">
         <v>992</v>
       </c>
       <c r="C353" s="12" t="s">
@@ -20610,23 +20609,23 @@
       </c>
       <c r="J353" s="14"/>
       <c r="K353" s="13"/>
-      <c r="L353" s="18" t="s">
+      <c r="L353" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M353" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="N353" s="18" t="s">
+      <c r="N353" s="12" t="s">
         <v>991</v>
       </c>
       <c r="O353" s="14"/>
-      <c r="P353" s="19" t="s">
+      <c r="P353" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q353" s="18" t="s">
+      <c r="Q353" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R353" s="18" t="s">
+      <c r="R353" s="12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -22146,7 +22145,7 @@
       <c r="A392" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B392" s="15" t="s">
+      <c r="B392" s="7" t="s">
         <v>1104</v>
       </c>
       <c r="C392" s="7" t="s">
@@ -22172,17 +22171,17 @@
       </c>
       <c r="J392" s="9"/>
       <c r="K392" s="8"/>
-      <c r="L392" s="15" t="s">
+      <c r="L392" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M392" s="10" t="s">
         <v>1107</v>
       </c>
-      <c r="N392" s="15" t="s">
+      <c r="N392" s="7" t="s">
         <v>1108</v>
       </c>
       <c r="O392" s="9"/>
-      <c r="P392" s="16" t="s">
+      <c r="P392" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q392" s="7"/>
@@ -22226,7 +22225,7 @@
       <c r="A394" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B394" s="15" t="s">
+      <c r="B394" s="7" t="s">
         <v>1113</v>
       </c>
       <c r="C394" s="7" t="s">
@@ -22256,17 +22255,17 @@
       <c r="K394" s="8">
         <v>46112</v>
       </c>
-      <c r="L394" s="15" t="s">
+      <c r="L394" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M394" s="10" t="s">
         <v>1116</v>
       </c>
-      <c r="N394" s="15" t="s">
+      <c r="N394" s="7" t="s">
         <v>1108</v>
       </c>
       <c r="O394" s="9"/>
-      <c r="P394" s="16" t="s">
+      <c r="P394" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q394" s="7"/>
@@ -22276,7 +22275,7 @@
       <c r="A395" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B395" s="18" t="s">
+      <c r="B395" s="12" t="s">
         <v>1117</v>
       </c>
       <c r="C395" s="12" t="s">
@@ -22304,18 +22303,18 @@
         <v>86</v>
       </c>
       <c r="K395" s="13"/>
-      <c r="L395" s="18" t="s">
+      <c r="L395" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M395" s="17" t="s">
         <v>1120</v>
       </c>
-      <c r="N395" s="18" t="s">
+      <c r="N395" s="12" t="s">
         <v>1121</v>
       </c>
       <c r="O395" s="14"/>
       <c r="P395" s="14"/>
-      <c r="Q395" s="18" t="s">
+      <c r="Q395" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R395" s="12"/>
@@ -22324,7 +22323,7 @@
       <c r="A396" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B396" s="15" t="s">
+      <c r="B396" s="7" t="s">
         <v>1122</v>
       </c>
       <c r="C396" s="7" t="s">
@@ -22354,17 +22353,17 @@
       <c r="K396" s="8">
         <v>46112</v>
       </c>
-      <c r="L396" s="15" t="s">
+      <c r="L396" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M396" s="6" t="s">
         <v>1125</v>
       </c>
-      <c r="N396" s="15" t="s">
+      <c r="N396" s="7" t="s">
         <v>1108</v>
       </c>
       <c r="O396" s="9"/>
-      <c r="P396" s="16" t="s">
+      <c r="P396" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q396" s="7"/>
@@ -22800,7 +22799,7 @@
       <c r="A407" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B407" s="18" t="s">
+      <c r="B407" s="12" t="s">
         <v>1154</v>
       </c>
       <c r="C407" s="12" t="s">
@@ -22826,17 +22825,17 @@
       </c>
       <c r="J407" s="14"/>
       <c r="K407" s="13"/>
-      <c r="L407" s="18" t="s">
+      <c r="L407" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M407" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="N407" s="18" t="s">
+      <c r="N407" s="12" t="s">
         <v>647</v>
       </c>
       <c r="O407" s="14"/>
-      <c r="P407" s="19" t="s">
+      <c r="P407" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q407" s="12"/>
@@ -22846,7 +22845,7 @@
       <c r="A408" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B408" s="15" t="s">
+      <c r="B408" s="7" t="s">
         <v>1156</v>
       </c>
       <c r="C408" s="7" t="s">
@@ -22876,17 +22875,17 @@
       <c r="K408" s="8">
         <v>46843</v>
       </c>
-      <c r="L408" s="15" t="s">
+      <c r="L408" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M408" s="10" t="s">
         <v>1159</v>
       </c>
-      <c r="N408" s="15" t="s">
+      <c r="N408" s="7" t="s">
         <v>1160</v>
       </c>
       <c r="O408" s="9"/>
-      <c r="P408" s="16" t="s">
+      <c r="P408" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q408" s="7"/>
@@ -22896,7 +22895,7 @@
       <c r="A409" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B409" s="18" t="s">
+      <c r="B409" s="12" t="s">
         <v>1161</v>
       </c>
       <c r="C409" s="12" t="s">
@@ -22924,18 +22923,18 @@
         <v>86</v>
       </c>
       <c r="K409" s="13"/>
-      <c r="L409" s="18" t="s">
+      <c r="L409" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M409" s="17" t="s">
         <v>1163</v>
       </c>
-      <c r="N409" s="18" t="s">
+      <c r="N409" s="12" t="s">
         <v>970</v>
       </c>
       <c r="O409" s="14"/>
       <c r="P409" s="14"/>
-      <c r="Q409" s="18" t="s">
+      <c r="Q409" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R409" s="12"/>
@@ -22988,7 +22987,7 @@
       <c r="A411" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B411" s="18" t="s">
+      <c r="B411" s="12" t="s">
         <v>1168</v>
       </c>
       <c r="C411" s="12" t="s">
@@ -23016,17 +23015,17 @@
       <c r="K411" s="13">
         <v>46112</v>
       </c>
-      <c r="L411" s="18" t="s">
+      <c r="L411" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M411" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="N411" s="18" t="s">
+      <c r="N411" s="12" t="s">
         <v>647</v>
       </c>
       <c r="O411" s="14"/>
-      <c r="P411" s="19" t="s">
+      <c r="P411" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q411" s="12"/>
@@ -23036,7 +23035,7 @@
       <c r="A412" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B412" s="15" t="s">
+      <c r="B412" s="7" t="s">
         <v>1169</v>
       </c>
       <c r="C412" s="7" t="s">
@@ -23062,18 +23061,18 @@
       </c>
       <c r="J412" s="9"/>
       <c r="K412" s="8"/>
-      <c r="L412" s="15" t="s">
+      <c r="L412" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M412" s="6" t="s">
         <v>1171</v>
       </c>
-      <c r="N412" s="15" t="s">
+      <c r="N412" s="7" t="s">
         <v>1172</v>
       </c>
       <c r="O412" s="9"/>
       <c r="P412" s="9"/>
-      <c r="Q412" s="15" t="s">
+      <c r="Q412" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R412" s="7"/>
@@ -23284,7 +23283,7 @@
       <c r="A418" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B418" s="15" t="s">
+      <c r="B418" s="7" t="s">
         <v>1185</v>
       </c>
       <c r="C418" s="7" t="s">
@@ -23310,17 +23309,17 @@
       </c>
       <c r="J418" s="9"/>
       <c r="K418" s="8"/>
-      <c r="L418" s="15" t="s">
+      <c r="L418" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M418" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="N418" s="15" t="s">
+      <c r="N418" s="7" t="s">
         <v>647</v>
       </c>
       <c r="O418" s="9"/>
-      <c r="P418" s="16" t="s">
+      <c r="P418" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q418" s="7"/>
@@ -23590,7 +23589,7 @@
       <c r="A425" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B425" s="18" t="s">
+      <c r="B425" s="12" t="s">
         <v>1203</v>
       </c>
       <c r="C425" s="12" t="s">
@@ -23616,17 +23615,17 @@
       </c>
       <c r="J425" s="14"/>
       <c r="K425" s="13"/>
-      <c r="L425" s="18" t="s">
+      <c r="L425" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M425" s="11" t="s">
         <v>1204</v>
       </c>
-      <c r="N425" s="18" t="s">
+      <c r="N425" s="12" t="s">
         <v>1205</v>
       </c>
       <c r="O425" s="14"/>
-      <c r="P425" s="19" t="s">
+      <c r="P425" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q425" s="12"/>
@@ -23802,7 +23801,7 @@
       <c r="A430" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B430" s="15" t="s">
+      <c r="B430" s="7" t="s">
         <v>1218</v>
       </c>
       <c r="C430" s="7" t="s">
@@ -23828,17 +23827,17 @@
       </c>
       <c r="J430" s="9"/>
       <c r="K430" s="8"/>
-      <c r="L430" s="15" t="s">
+      <c r="L430" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M430" s="6" t="s">
         <v>1221</v>
       </c>
-      <c r="N430" s="15" t="s">
+      <c r="N430" s="7" t="s">
         <v>1222</v>
       </c>
       <c r="O430" s="9"/>
-      <c r="P430" s="16" t="s">
+      <c r="P430" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q430" s="7"/>
@@ -23848,7 +23847,7 @@
       <c r="A431" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B431" s="18" t="s">
+      <c r="B431" s="12" t="s">
         <v>1223</v>
       </c>
       <c r="C431" s="12" t="s">
@@ -23874,17 +23873,17 @@
       </c>
       <c r="J431" s="14"/>
       <c r="K431" s="13"/>
-      <c r="L431" s="18" t="s">
+      <c r="L431" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M431" s="11" t="s">
         <v>1226</v>
       </c>
-      <c r="N431" s="18" t="s">
+      <c r="N431" s="12" t="s">
         <v>1227</v>
       </c>
       <c r="O431" s="14"/>
-      <c r="P431" s="19" t="s">
+      <c r="P431" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q431" s="12"/>
@@ -24356,7 +24355,7 @@
       <c r="A443" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="18" t="s">
+      <c r="B443" s="12" t="s">
         <v>1261</v>
       </c>
       <c r="C443" s="12" t="s">
@@ -24382,20 +24381,20 @@
       </c>
       <c r="J443" s="14"/>
       <c r="K443" s="13"/>
-      <c r="L443" s="18" t="s">
+      <c r="L443" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M443" s="11" t="s">
         <v>1262</v>
       </c>
-      <c r="N443" s="18" t="s">
+      <c r="N443" s="12" t="s">
         <v>1260</v>
       </c>
       <c r="O443" s="14"/>
-      <c r="P443" s="19" t="s">
+      <c r="P443" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q443" s="18" t="s">
+      <c r="Q443" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R443" s="12"/>
@@ -25078,7 +25077,7 @@
       <c r="A460" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B460" s="15" t="s">
+      <c r="B460" s="7" t="s">
         <v>1307</v>
       </c>
       <c r="C460" s="7" t="s">
@@ -25104,20 +25103,20 @@
       </c>
       <c r="J460" s="9"/>
       <c r="K460" s="8"/>
-      <c r="L460" s="15" t="s">
+      <c r="L460" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M460" s="6" t="s">
         <v>1308</v>
       </c>
-      <c r="N460" s="15" t="s">
+      <c r="N460" s="7" t="s">
         <v>692</v>
       </c>
       <c r="O460" s="9"/>
-      <c r="P460" s="16" t="s">
+      <c r="P460" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q460" s="15" t="s">
+      <c r="Q460" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R460" s="7"/>
@@ -25322,7 +25321,7 @@
       <c r="M465" s="11" t="s">
         <v>1286</v>
       </c>
-      <c r="N465" s="18" t="s">
+      <c r="N465" s="12" t="s">
         <v>1321</v>
       </c>
       <c r="O465" s="14"/>
@@ -25744,7 +25743,7 @@
       <c r="A476" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B476" s="15" t="s">
+      <c r="B476" s="7" t="s">
         <v>1348</v>
       </c>
       <c r="C476" s="7" t="s">
@@ -25772,21 +25771,21 @@
         <v>86</v>
       </c>
       <c r="K476" s="8"/>
-      <c r="L476" s="15" t="s">
+      <c r="L476" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M476" s="10" t="s">
         <v>1349</v>
       </c>
-      <c r="N476" s="15" t="s">
+      <c r="N476" s="7" t="s">
         <v>1350</v>
       </c>
       <c r="O476" s="9"/>
-      <c r="P476" s="16" t="s">
+      <c r="P476" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q476" s="7"/>
-      <c r="R476" s="15" t="s">
+      <c r="R476" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -26000,7 +25999,7 @@
       <c r="A482" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B482" s="15" t="s">
+      <c r="B482" s="7" t="s">
         <v>1363</v>
       </c>
       <c r="C482" s="7" t="s">
@@ -26026,17 +26025,17 @@
       </c>
       <c r="J482" s="9"/>
       <c r="K482" s="8"/>
-      <c r="L482" s="15" t="s">
+      <c r="L482" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M482" s="6" t="s">
         <v>1364</v>
       </c>
-      <c r="N482" s="15" t="s">
+      <c r="N482" s="7" t="s">
         <v>68</v>
       </c>
       <c r="O482" s="9"/>
-      <c r="P482" s="16" t="s">
+      <c r="P482" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q482" s="7"/>
@@ -26090,7 +26089,7 @@
       <c r="A484" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B484" s="15" t="s">
+      <c r="B484" s="7" t="s">
         <v>1368</v>
       </c>
       <c r="C484" s="7" t="s">
@@ -26118,13 +26117,13 @@
         <v>86</v>
       </c>
       <c r="K484" s="8"/>
-      <c r="L484" s="15" t="s">
+      <c r="L484" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M484" s="6" t="s">
         <v>1370</v>
       </c>
-      <c r="N484" s="15" t="s">
+      <c r="N484" s="7" t="s">
         <v>1367</v>
       </c>
       <c r="O484" s="9"/>
@@ -26224,7 +26223,7 @@
       <c r="A487" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B487" s="18" t="s">
+      <c r="B487" s="12" t="s">
         <v>1378</v>
       </c>
       <c r="C487" s="12" t="s">
@@ -26250,13 +26249,13 @@
       </c>
       <c r="J487" s="14"/>
       <c r="K487" s="13"/>
-      <c r="L487" s="18" t="s">
+      <c r="L487" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M487" s="11" t="s">
         <v>1380</v>
       </c>
-      <c r="N487" s="18" t="s">
+      <c r="N487" s="12" t="s">
         <v>1375</v>
       </c>
       <c r="O487" s="14"/>
@@ -26350,7 +26349,7 @@
       <c r="A490" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B490" s="15" t="s">
+      <c r="B490" s="7" t="s">
         <v>1389</v>
       </c>
       <c r="C490" s="7" t="s">
@@ -26378,17 +26377,17 @@
       <c r="K490" s="8">
         <v>46477</v>
       </c>
-      <c r="L490" s="15" t="s">
+      <c r="L490" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M490" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N490" s="15" t="s">
+      <c r="N490" s="7" t="s">
         <v>1050</v>
       </c>
       <c r="O490" s="9"/>
-      <c r="P490" s="16" t="s">
+      <c r="P490" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q490" s="7"/>
@@ -26530,7 +26529,7 @@
       <c r="A494" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B494" s="15" t="s">
+      <c r="B494" s="7" t="s">
         <v>1400</v>
       </c>
       <c r="C494" s="7" t="s">
@@ -26556,17 +26555,17 @@
       </c>
       <c r="J494" s="9"/>
       <c r="K494" s="8"/>
-      <c r="L494" s="15" t="s">
+      <c r="L494" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M494" s="6" t="s">
         <v>1401</v>
       </c>
-      <c r="N494" s="15" t="s">
+      <c r="N494" s="7" t="s">
         <v>1304</v>
       </c>
       <c r="O494" s="9"/>
-      <c r="P494" s="16" t="s">
+      <c r="P494" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q494" s="7"/>
@@ -26576,7 +26575,7 @@
       <c r="A495" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B495" s="18" t="s">
+      <c r="B495" s="12" t="s">
         <v>1402</v>
       </c>
       <c r="C495" s="12" t="s">
@@ -26604,17 +26603,17 @@
       <c r="K495" s="13">
         <v>46477</v>
       </c>
-      <c r="L495" s="18" t="s">
+      <c r="L495" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M495" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N495" s="18" t="s">
+      <c r="N495" s="12" t="s">
         <v>1050</v>
       </c>
       <c r="O495" s="14"/>
-      <c r="P495" s="19" t="s">
+      <c r="P495" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q495" s="12"/>
@@ -26700,7 +26699,7 @@
       <c r="A498" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B498" s="15" t="s">
+      <c r="B498" s="7" t="s">
         <v>1411</v>
       </c>
       <c r="C498" s="7" t="s">
@@ -26726,17 +26725,17 @@
       </c>
       <c r="J498" s="9"/>
       <c r="K498" s="8"/>
-      <c r="L498" s="15" t="s">
+      <c r="L498" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M498" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="N498" s="15" t="s">
+      <c r="N498" s="7" t="s">
         <v>1415</v>
       </c>
       <c r="O498" s="9"/>
-      <c r="P498" s="16" t="s">
+      <c r="P498" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q498" s="7"/>
@@ -27160,7 +27159,7 @@
       <c r="A509" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B509" s="18" t="s">
+      <c r="B509" s="12" t="s">
         <v>1439</v>
       </c>
       <c r="C509" s="12" t="s">
@@ -27188,17 +27187,17 @@
       <c r="K509" s="13">
         <v>46477</v>
       </c>
-      <c r="L509" s="18" t="s">
+      <c r="L509" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M509" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="N509" s="18" t="s">
+      <c r="N509" s="12" t="s">
         <v>191</v>
       </c>
       <c r="O509" s="14"/>
-      <c r="P509" s="19" t="s">
+      <c r="P509" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q509" s="12"/>
@@ -27296,7 +27295,7 @@
       <c r="A512" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B512" s="15" t="s">
+      <c r="B512" s="7" t="s">
         <v>1449</v>
       </c>
       <c r="C512" s="7" t="s">
@@ -27322,21 +27321,21 @@
       </c>
       <c r="J512" s="9"/>
       <c r="K512" s="8"/>
-      <c r="L512" s="15" t="s">
+      <c r="L512" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M512" s="10" t="s">
         <v>1451</v>
       </c>
-      <c r="N512" s="15" t="s">
+      <c r="N512" s="7" t="s">
         <v>1238</v>
       </c>
       <c r="O512" s="9"/>
-      <c r="P512" s="16" t="s">
+      <c r="P512" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q512" s="7"/>
-      <c r="R512" s="15" t="s">
+      <c r="R512" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -27762,7 +27761,7 @@
       <c r="A523" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B523" s="18" t="s">
+      <c r="B523" s="12" t="s">
         <v>1476</v>
       </c>
       <c r="C523" s="12" t="s">
@@ -27788,23 +27787,23 @@
       </c>
       <c r="J523" s="14"/>
       <c r="K523" s="13"/>
-      <c r="L523" s="18" t="s">
+      <c r="L523" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M523" s="17" t="s">
         <v>1478</v>
       </c>
-      <c r="N523" s="18" t="s">
+      <c r="N523" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="O523" s="14"/>
-      <c r="P523" s="19" t="s">
+      <c r="P523" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q523" s="18" t="s">
+      <c r="Q523" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R523" s="21" t="s">
+      <c r="R523" s="20" t="s">
         <v>284</v>
       </c>
     </row>
@@ -27900,7 +27899,7 @@
       <c r="A526" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B526" s="15" t="s">
+      <c r="B526" s="7" t="s">
         <v>1486</v>
       </c>
       <c r="C526" s="7" t="s">
@@ -27928,17 +27927,17 @@
       <c r="K526" s="8">
         <v>46295</v>
       </c>
-      <c r="L526" s="15" t="s">
+      <c r="L526" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M526" s="6" t="s">
         <v>1489</v>
       </c>
-      <c r="N526" s="15" t="s">
+      <c r="N526" s="7" t="s">
         <v>1490</v>
       </c>
       <c r="O526" s="9"/>
-      <c r="P526" s="16" t="s">
+      <c r="P526" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q526" s="7"/>
@@ -27948,7 +27947,7 @@
       <c r="A527" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B527" s="18" t="s">
+      <c r="B527" s="12" t="s">
         <v>1491</v>
       </c>
       <c r="C527" s="12" t="s">
@@ -27974,18 +27973,18 @@
       </c>
       <c r="J527" s="14"/>
       <c r="K527" s="13"/>
-      <c r="L527" s="18" t="s">
+      <c r="L527" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M527" s="17" t="s">
         <v>1494</v>
       </c>
-      <c r="N527" s="18" t="s">
+      <c r="N527" s="12" t="s">
         <v>1495</v>
       </c>
       <c r="O527" s="14"/>
       <c r="P527" s="14"/>
-      <c r="Q527" s="18" t="s">
+      <c r="Q527" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R527" s="12"/>
@@ -28038,7 +28037,7 @@
       <c r="A529" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B529" s="18" t="s">
+      <c r="B529" s="12" t="s">
         <v>1500</v>
       </c>
       <c r="C529" s="12" t="s">
@@ -28066,17 +28065,17 @@
         <v>86</v>
       </c>
       <c r="K529" s="13"/>
-      <c r="L529" s="18" t="s">
+      <c r="L529" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M529" s="11" t="s">
         <v>1501</v>
       </c>
-      <c r="N529" s="18" t="s">
+      <c r="N529" s="12" t="s">
         <v>1502</v>
       </c>
       <c r="O529" s="14"/>
-      <c r="P529" s="19" t="s">
+      <c r="P529" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q529" s="12"/>
@@ -28132,7 +28131,7 @@
       <c r="A531" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B531" s="18" t="s">
+      <c r="B531" s="12" t="s">
         <v>1507</v>
       </c>
       <c r="C531" s="12" t="s">
@@ -28160,17 +28159,17 @@
         <v>86</v>
       </c>
       <c r="K531" s="13"/>
-      <c r="L531" s="18" t="s">
+      <c r="L531" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M531" s="11" t="s">
         <v>1256</v>
       </c>
-      <c r="N531" s="18" t="s">
+      <c r="N531" s="12" t="s">
         <v>459</v>
       </c>
       <c r="O531" s="14"/>
-      <c r="P531" s="19" t="s">
+      <c r="P531" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q531" s="12"/>
@@ -28180,7 +28179,7 @@
       <c r="A532" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B532" s="15" t="s">
+      <c r="B532" s="7" t="s">
         <v>1508</v>
       </c>
       <c r="C532" s="7" t="s">
@@ -28206,17 +28205,17 @@
       </c>
       <c r="J532" s="9"/>
       <c r="K532" s="8"/>
-      <c r="L532" s="15" t="s">
+      <c r="L532" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M532" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="N532" s="15" t="s">
+      <c r="N532" s="7" t="s">
         <v>1511</v>
       </c>
       <c r="O532" s="9"/>
-      <c r="P532" s="16" t="s">
+      <c r="P532" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q532" s="7"/>
@@ -28226,7 +28225,7 @@
       <c r="A533" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B533" s="18" t="s">
+      <c r="B533" s="12" t="s">
         <v>1512</v>
       </c>
       <c r="C533" s="12" t="s">
@@ -28254,20 +28253,20 @@
         <v>86</v>
       </c>
       <c r="K533" s="13"/>
-      <c r="L533" s="18" t="s">
+      <c r="L533" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M533" s="11" t="s">
         <v>1262</v>
       </c>
-      <c r="N533" s="18" t="s">
+      <c r="N533" s="12" t="s">
         <v>1260</v>
       </c>
       <c r="O533" s="14"/>
-      <c r="P533" s="19" t="s">
+      <c r="P533" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q533" s="18" t="s">
+      <c r="Q533" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R533" s="12"/>
@@ -28276,7 +28275,7 @@
       <c r="A534" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B534" s="15" t="s">
+      <c r="B534" s="7" t="s">
         <v>1515</v>
       </c>
       <c r="C534" s="7" t="s">
@@ -28304,18 +28303,18 @@
         <v>86</v>
       </c>
       <c r="K534" s="8"/>
-      <c r="L534" s="15" t="s">
+      <c r="L534" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M534" s="10" t="s">
         <v>1494</v>
       </c>
-      <c r="N534" s="15" t="s">
+      <c r="N534" s="7" t="s">
         <v>1495</v>
       </c>
       <c r="O534" s="9"/>
       <c r="P534" s="9"/>
-      <c r="Q534" s="15" t="s">
+      <c r="Q534" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R534" s="7"/>
@@ -28324,7 +28323,7 @@
       <c r="A535" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B535" s="18" t="s">
+      <c r="B535" s="12" t="s">
         <v>1518</v>
       </c>
       <c r="C535" s="12" t="s">
@@ -28352,18 +28351,18 @@
         <v>86</v>
       </c>
       <c r="K535" s="13"/>
-      <c r="L535" s="18" t="s">
+      <c r="L535" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M535" s="17" t="s">
         <v>1521</v>
       </c>
-      <c r="N535" s="18" t="s">
+      <c r="N535" s="12" t="s">
         <v>1522</v>
       </c>
       <c r="O535" s="14"/>
       <c r="P535" s="14"/>
-      <c r="Q535" s="18" t="s">
+      <c r="Q535" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R535" s="12"/>
@@ -28790,7 +28789,7 @@
       <c r="A546" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B546" s="15" t="s">
+      <c r="B546" s="7" t="s">
         <v>1548</v>
       </c>
       <c r="C546" s="7" t="s">
@@ -28816,20 +28815,20 @@
       </c>
       <c r="J546" s="9"/>
       <c r="K546" s="8"/>
-      <c r="L546" s="15" t="s">
+      <c r="L546" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M546" s="6" t="s">
         <v>1256</v>
       </c>
-      <c r="N546" s="15" t="s">
+      <c r="N546" s="7" t="s">
         <v>459</v>
       </c>
       <c r="O546" s="9"/>
-      <c r="P546" s="16" t="s">
+      <c r="P546" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q546" s="15" t="s">
+      <c r="Q546" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R546" s="7"/>
@@ -29148,7 +29147,7 @@
       <c r="M554" s="6" t="s">
         <v>841</v>
       </c>
-      <c r="N554" s="15" t="s">
+      <c r="N554" s="7" t="s">
         <v>842</v>
       </c>
       <c r="O554" s="9"/>
@@ -29160,7 +29159,7 @@
       <c r="A555" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B555" s="18" t="s">
+      <c r="B555" s="12" t="s">
         <v>1564</v>
       </c>
       <c r="C555" s="12" t="s">
@@ -29186,20 +29185,20 @@
       </c>
       <c r="J555" s="14"/>
       <c r="K555" s="13"/>
-      <c r="L555" s="18" t="s">
+      <c r="L555" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M555" s="11" t="s">
         <v>1565</v>
       </c>
-      <c r="N555" s="18" t="s">
+      <c r="N555" s="12" t="s">
         <v>607</v>
       </c>
       <c r="O555" s="14"/>
-      <c r="P555" s="19" t="s">
+      <c r="P555" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q555" s="18" t="s">
+      <c r="Q555" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R555" s="12"/>
@@ -29466,7 +29465,7 @@
       <c r="A562" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B562" s="15" t="s">
+      <c r="B562" s="7" t="s">
         <v>1578</v>
       </c>
       <c r="C562" s="7" t="s">
@@ -29494,20 +29493,20 @@
       <c r="K562" s="8">
         <v>46295</v>
       </c>
-      <c r="L562" s="15" t="s">
+      <c r="L562" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M562" s="6" t="s">
         <v>1581</v>
       </c>
-      <c r="N562" s="15" t="s">
+      <c r="N562" s="7" t="s">
         <v>965</v>
       </c>
       <c r="O562" s="9"/>
-      <c r="P562" s="16" t="s">
+      <c r="P562" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q562" s="15" t="s">
+      <c r="Q562" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R562" s="7"/>
@@ -29516,7 +29515,7 @@
       <c r="A563" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B563" s="18" t="s">
+      <c r="B563" s="12" t="s">
         <v>1582</v>
       </c>
       <c r="C563" s="12" t="s">
@@ -29544,18 +29543,18 @@
       <c r="K563" s="13">
         <v>47208</v>
       </c>
-      <c r="L563" s="18" t="s">
+      <c r="L563" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M563" s="11" t="s">
         <v>1585</v>
       </c>
-      <c r="N563" s="18" t="s">
+      <c r="N563" s="12" t="s">
         <v>144</v>
       </c>
       <c r="O563" s="14"/>
       <c r="P563" s="14"/>
-      <c r="Q563" s="18" t="s">
+      <c r="Q563" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R563" s="12"/>
@@ -29564,7 +29563,7 @@
       <c r="A564" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B564" s="15" t="s">
+      <c r="B564" s="7" t="s">
         <v>1586</v>
       </c>
       <c r="C564" s="7" t="s">
@@ -29590,18 +29589,18 @@
       </c>
       <c r="J564" s="9"/>
       <c r="K564" s="8"/>
-      <c r="L564" s="15" t="s">
+      <c r="L564" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M564" s="6" t="s">
         <v>969</v>
       </c>
-      <c r="N564" s="15" t="s">
+      <c r="N564" s="7" t="s">
         <v>970</v>
       </c>
       <c r="O564" s="9"/>
       <c r="P564" s="9"/>
-      <c r="Q564" s="15" t="s">
+      <c r="Q564" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R564" s="7"/>
@@ -30424,7 +30423,7 @@
       <c r="A585" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B585" s="18" t="s">
+      <c r="B585" s="12" t="s">
         <v>1631</v>
       </c>
       <c r="C585" s="12" t="s">
@@ -30450,21 +30449,21 @@
       </c>
       <c r="J585" s="14"/>
       <c r="K585" s="13"/>
-      <c r="L585" s="18" t="s">
+      <c r="L585" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M585" s="11" t="s">
         <v>1632</v>
       </c>
-      <c r="N585" s="18" t="s">
+      <c r="N585" s="12" t="s">
         <v>991</v>
       </c>
       <c r="O585" s="14"/>
-      <c r="P585" s="19" t="s">
+      <c r="P585" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q585" s="12"/>
-      <c r="R585" s="18" t="s">
+      <c r="R585" s="12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -30844,7 +30843,7 @@
       <c r="A595" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B595" s="18" t="s">
+      <c r="B595" s="12" t="s">
         <v>1655</v>
       </c>
       <c r="C595" s="12" t="s">
@@ -30872,20 +30871,20 @@
         <v>86</v>
       </c>
       <c r="K595" s="13"/>
-      <c r="L595" s="18" t="s">
+      <c r="L595" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M595" s="11" t="s">
         <v>1656</v>
       </c>
-      <c r="N595" s="18" t="s">
+      <c r="N595" s="12" t="s">
         <v>1654</v>
       </c>
       <c r="O595" s="14"/>
-      <c r="P595" s="19" t="s">
+      <c r="P595" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q595" s="18" t="s">
+      <c r="Q595" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R595" s="12"/>
@@ -31932,7 +31931,7 @@
       <c r="A621" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B621" s="18" t="s">
+      <c r="B621" s="12" t="s">
         <v>1708</v>
       </c>
       <c r="C621" s="12" t="s">
@@ -31960,20 +31959,20 @@
         <v>86</v>
       </c>
       <c r="K621" s="13"/>
-      <c r="L621" s="18" t="s">
+      <c r="L621" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M621" s="17" t="s">
         <v>1709</v>
       </c>
-      <c r="N621" s="18" t="s">
+      <c r="N621" s="12" t="s">
         <v>1710</v>
       </c>
       <c r="O621" s="14"/>
-      <c r="P621" s="19" t="s">
+      <c r="P621" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q621" s="18" t="s">
+      <c r="Q621" s="12" t="s">
         <v>16</v>
       </c>
       <c r="R621" s="12"/>
@@ -31982,7 +31981,7 @@
       <c r="A622" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B622" s="15" t="s">
+      <c r="B622" s="7" t="s">
         <v>1711</v>
       </c>
       <c r="C622" s="7" t="s">
@@ -32010,22 +32009,22 @@
         <v>86</v>
       </c>
       <c r="K622" s="8"/>
-      <c r="L622" s="15" t="s">
+      <c r="L622" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M622" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="N622" s="15" t="s">
+      <c r="N622" s="7" t="s">
         <v>1715</v>
       </c>
-      <c r="O622" s="25" t="s">
+      <c r="O622" s="24" t="s">
         <v>1716</v>
       </c>
-      <c r="P622" s="16" t="s">
+      <c r="P622" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q622" s="15" t="s">
+      <c r="Q622" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R622" s="7"/>
@@ -32366,7 +32365,7 @@
       <c r="A631" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B631" s="18" t="s">
+      <c r="B631" s="12" t="s">
         <v>1736</v>
       </c>
       <c r="C631" s="12" t="s">
@@ -32396,11 +32395,11 @@
       <c r="M631" s="11" t="s">
         <v>1737</v>
       </c>
-      <c r="N631" s="18" t="s">
+      <c r="N631" s="12" t="s">
         <v>68</v>
       </c>
       <c r="O631" s="14"/>
-      <c r="P631" s="19" t="s">
+      <c r="P631" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Q631" s="12"/>
@@ -32750,7 +32749,7 @@
       <c r="A640" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B640" s="15" t="s">
+      <c r="B640" s="7" t="s">
         <v>1754</v>
       </c>
       <c r="C640" s="7" t="s">
@@ -32776,17 +32775,17 @@
       </c>
       <c r="J640" s="9"/>
       <c r="K640" s="8"/>
-      <c r="L640" s="15" t="s">
+      <c r="L640" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M640" s="10" t="s">
         <v>1755</v>
       </c>
-      <c r="N640" s="15" t="s">
+      <c r="N640" s="7" t="s">
         <v>1735</v>
       </c>
       <c r="O640" s="9"/>
-      <c r="P640" s="16" t="s">
+      <c r="P640" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q640" s="7"/>
@@ -33060,7 +33059,7 @@
       <c r="A647" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B647" s="18" t="s">
+      <c r="B647" s="12" t="s">
         <v>1771</v>
       </c>
       <c r="C647" s="12" t="s">
@@ -33086,13 +33085,13 @@
       </c>
       <c r="J647" s="14"/>
       <c r="K647" s="13"/>
-      <c r="L647" s="18" t="s">
+      <c r="L647" s="12" t="s">
         <v>11</v>
       </c>
       <c r="M647" s="11" t="s">
         <v>1772</v>
       </c>
-      <c r="N647" s="18" t="s">
+      <c r="N647" s="12" t="s">
         <v>68</v>
       </c>
       <c r="O647" s="14"/>
@@ -33184,521 +33183,7 @@
       <c r="Q649" s="12"/>
       <c r="R649" s="12"/>
     </row>
-    <row r="650" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-    <hyperlink ref="L6" r:id="rId2"/>
-    <hyperlink ref="N6" r:id="rId3"/>
-    <hyperlink ref="P6" r:id="rId4"/>
-    <hyperlink ref="B8" r:id="rId5"/>
-    <hyperlink ref="L8" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="B14" r:id="rId8"/>
-    <hyperlink ref="L14" r:id="rId9"/>
-    <hyperlink ref="N14" r:id="rId10"/>
-    <hyperlink ref="P14" r:id="rId11"/>
-    <hyperlink ref="Q14" r:id="rId12"/>
-    <hyperlink ref="B18" r:id="rId13"/>
-    <hyperlink ref="L18" r:id="rId14"/>
-    <hyperlink ref="N18" r:id="rId15"/>
-    <hyperlink ref="B26" r:id="rId16"/>
-    <hyperlink ref="L26" r:id="rId17"/>
-    <hyperlink ref="N26" r:id="rId18"/>
-    <hyperlink ref="P26" r:id="rId19"/>
-    <hyperlink ref="N31" r:id="rId20"/>
-    <hyperlink ref="B32" r:id="rId21"/>
-    <hyperlink ref="L32" r:id="rId22"/>
-    <hyperlink ref="N32" r:id="rId23"/>
-    <hyperlink ref="B38" r:id="rId24"/>
-    <hyperlink ref="L38" r:id="rId25"/>
-    <hyperlink ref="N38" r:id="rId26"/>
-    <hyperlink ref="P38" r:id="rId27"/>
-    <hyperlink ref="Q38" r:id="rId28"/>
-    <hyperlink ref="B43" r:id="rId29"/>
-    <hyperlink ref="L43" r:id="rId30"/>
-    <hyperlink ref="N43" r:id="rId31"/>
-    <hyperlink ref="Q43" r:id="rId32"/>
-    <hyperlink ref="B44" r:id="rId33"/>
-    <hyperlink ref="L44" r:id="rId34"/>
-    <hyperlink ref="N44" r:id="rId35"/>
-    <hyperlink ref="Q44" r:id="rId36"/>
-    <hyperlink ref="B45" r:id="rId37"/>
-    <hyperlink ref="L45" r:id="rId38"/>
-    <hyperlink ref="N45" r:id="rId39"/>
-    <hyperlink ref="B63" r:id="rId40"/>
-    <hyperlink ref="L63" r:id="rId41"/>
-    <hyperlink ref="N63" r:id="rId42"/>
-    <hyperlink ref="P63" r:id="rId43"/>
-    <hyperlink ref="R63" r:id="rId44"/>
-    <hyperlink ref="B65" r:id="rId45"/>
-    <hyperlink ref="L65" r:id="rId46"/>
-    <hyperlink ref="N65" r:id="rId47"/>
-    <hyperlink ref="Q65" r:id="rId48"/>
-    <hyperlink ref="B66" r:id="rId49"/>
-    <hyperlink ref="L66" r:id="rId50"/>
-    <hyperlink ref="N66" r:id="rId51"/>
-    <hyperlink ref="Q66" r:id="rId52"/>
-    <hyperlink ref="B68" r:id="rId53"/>
-    <hyperlink ref="L68" r:id="rId54"/>
-    <hyperlink ref="N68" r:id="rId55"/>
-    <hyperlink ref="Q68" r:id="rId56"/>
-    <hyperlink ref="B69" r:id="rId57"/>
-    <hyperlink ref="L69" r:id="rId58"/>
-    <hyperlink ref="N69" r:id="rId59"/>
-    <hyperlink ref="Q69" r:id="rId60"/>
-    <hyperlink ref="B78" r:id="rId61"/>
-    <hyperlink ref="L78" r:id="rId62"/>
-    <hyperlink ref="N78" r:id="rId63"/>
-    <hyperlink ref="P78" r:id="rId64"/>
-    <hyperlink ref="B79" r:id="rId65"/>
-    <hyperlink ref="L79" r:id="rId66"/>
-    <hyperlink ref="N79" r:id="rId67"/>
-    <hyperlink ref="P79" r:id="rId68"/>
-    <hyperlink ref="Q79" r:id="rId69"/>
-    <hyperlink ref="B89" r:id="rId70"/>
-    <hyperlink ref="L89" r:id="rId71"/>
-    <hyperlink ref="N89" r:id="rId72"/>
-    <hyperlink ref="P89" r:id="rId73"/>
-    <hyperlink ref="Q89" r:id="rId74"/>
-    <hyperlink ref="R89" r:id="rId75"/>
-    <hyperlink ref="B90" r:id="rId76"/>
-    <hyperlink ref="L90" r:id="rId77"/>
-    <hyperlink ref="N90" r:id="rId78"/>
-    <hyperlink ref="Q90" r:id="rId79"/>
-    <hyperlink ref="B100" r:id="rId80"/>
-    <hyperlink ref="L100" r:id="rId81"/>
-    <hyperlink ref="N100" r:id="rId82"/>
-    <hyperlink ref="P100" r:id="rId83"/>
-    <hyperlink ref="Q100" r:id="rId84"/>
-    <hyperlink ref="B101" r:id="rId85"/>
-    <hyperlink ref="L101" r:id="rId86"/>
-    <hyperlink ref="N101" r:id="rId87"/>
-    <hyperlink ref="Q101" r:id="rId88"/>
-    <hyperlink ref="B117" r:id="rId89"/>
-    <hyperlink ref="L117" r:id="rId90"/>
-    <hyperlink ref="N117" r:id="rId91"/>
-    <hyperlink ref="P117" r:id="rId92"/>
-    <hyperlink ref="R117" r:id="rId93"/>
-    <hyperlink ref="B118" r:id="rId94"/>
-    <hyperlink ref="L118" r:id="rId95"/>
-    <hyperlink ref="N118" r:id="rId96"/>
-    <hyperlink ref="Q118" r:id="rId97"/>
-    <hyperlink ref="B128" r:id="rId98"/>
-    <hyperlink ref="L128" r:id="rId99"/>
-    <hyperlink ref="N128" r:id="rId100"/>
-    <hyperlink ref="P128" r:id="rId101"/>
-    <hyperlink ref="R128" r:id="rId102"/>
-    <hyperlink ref="B129" r:id="rId103"/>
-    <hyperlink ref="L129" r:id="rId104"/>
-    <hyperlink ref="N129" r:id="rId105"/>
-    <hyperlink ref="Q129" r:id="rId106"/>
-    <hyperlink ref="B135" r:id="rId107"/>
-    <hyperlink ref="L135" r:id="rId108"/>
-    <hyperlink ref="N135" r:id="rId109"/>
-    <hyperlink ref="P135" r:id="rId110"/>
-    <hyperlink ref="Q135" r:id="rId111"/>
-    <hyperlink ref="B136" r:id="rId112"/>
-    <hyperlink ref="L136" r:id="rId113"/>
-    <hyperlink ref="N136" r:id="rId114"/>
-    <hyperlink ref="Q136" r:id="rId115"/>
-    <hyperlink ref="B142" r:id="rId116"/>
-    <hyperlink ref="L142" r:id="rId117"/>
-    <hyperlink ref="N142" r:id="rId118"/>
-    <hyperlink ref="P142" r:id="rId119"/>
-    <hyperlink ref="R142" r:id="rId120"/>
-    <hyperlink ref="B143" r:id="rId121"/>
-    <hyperlink ref="L143" r:id="rId122"/>
-    <hyperlink ref="N143" r:id="rId123"/>
-    <hyperlink ref="Q143" r:id="rId124"/>
-    <hyperlink ref="B147" r:id="rId125"/>
-    <hyperlink ref="L147" r:id="rId126"/>
-    <hyperlink ref="N147" r:id="rId127"/>
-    <hyperlink ref="P147" r:id="rId128"/>
-    <hyperlink ref="Q147" r:id="rId129"/>
-    <hyperlink ref="R147" r:id="rId130"/>
-    <hyperlink ref="B148" r:id="rId131"/>
-    <hyperlink ref="L148" r:id="rId132"/>
-    <hyperlink ref="N148" r:id="rId133"/>
-    <hyperlink ref="Q148" r:id="rId134"/>
-    <hyperlink ref="B151" r:id="rId135"/>
-    <hyperlink ref="L151" r:id="rId136"/>
-    <hyperlink ref="N151" r:id="rId137"/>
-    <hyperlink ref="P151" r:id="rId138"/>
-    <hyperlink ref="Q151" r:id="rId139"/>
-    <hyperlink ref="R151" r:id="rId140"/>
-    <hyperlink ref="B152" r:id="rId141"/>
-    <hyperlink ref="L152" r:id="rId142"/>
-    <hyperlink ref="N152" r:id="rId143"/>
-    <hyperlink ref="Q152" r:id="rId144"/>
-    <hyperlink ref="B153" r:id="rId145"/>
-    <hyperlink ref="L153" r:id="rId146"/>
-    <hyperlink ref="N153" r:id="rId147"/>
-    <hyperlink ref="P153" r:id="rId148"/>
-    <hyperlink ref="Q153" r:id="rId149"/>
-    <hyperlink ref="R153" r:id="rId150"/>
-    <hyperlink ref="B154" r:id="rId151"/>
-    <hyperlink ref="L154" r:id="rId152"/>
-    <hyperlink ref="N154" r:id="rId153"/>
-    <hyperlink ref="P154" r:id="rId154"/>
-    <hyperlink ref="Q154" r:id="rId155"/>
-    <hyperlink ref="B156" r:id="rId156"/>
-    <hyperlink ref="L156" r:id="rId157"/>
-    <hyperlink ref="N156" r:id="rId158"/>
-    <hyperlink ref="P156" r:id="rId159"/>
-    <hyperlink ref="Q156" r:id="rId160"/>
-    <hyperlink ref="R156" r:id="rId161"/>
-    <hyperlink ref="B157" r:id="rId162"/>
-    <hyperlink ref="L157" r:id="rId163"/>
-    <hyperlink ref="N157" r:id="rId164"/>
-    <hyperlink ref="Q157" r:id="rId165"/>
-    <hyperlink ref="B160" r:id="rId166"/>
-    <hyperlink ref="L160" r:id="rId167"/>
-    <hyperlink ref="N160" r:id="rId168"/>
-    <hyperlink ref="P160" r:id="rId169"/>
-    <hyperlink ref="R160" r:id="rId170"/>
-    <hyperlink ref="B161" r:id="rId171"/>
-    <hyperlink ref="L161" r:id="rId172"/>
-    <hyperlink ref="N161" r:id="rId173"/>
-    <hyperlink ref="Q161" r:id="rId174"/>
-    <hyperlink ref="B167" r:id="rId175"/>
-    <hyperlink ref="L167" r:id="rId176"/>
-    <hyperlink ref="N167" r:id="rId177"/>
-    <hyperlink ref="P167" r:id="rId178"/>
-    <hyperlink ref="B173" r:id="rId179"/>
-    <hyperlink ref="L173" r:id="rId180"/>
-    <hyperlink ref="N173" r:id="rId181"/>
-    <hyperlink ref="P173" r:id="rId182"/>
-    <hyperlink ref="Q173" r:id="rId183"/>
-    <hyperlink ref="B193" r:id="rId184"/>
-    <hyperlink ref="L193" r:id="rId185"/>
-    <hyperlink ref="N193" r:id="rId186"/>
-    <hyperlink ref="P193" r:id="rId187"/>
-    <hyperlink ref="B197" r:id="rId188"/>
-    <hyperlink ref="L197" r:id="rId189"/>
-    <hyperlink ref="N197" r:id="rId190"/>
-    <hyperlink ref="P197" r:id="rId191"/>
-    <hyperlink ref="B201" r:id="rId192"/>
-    <hyperlink ref="L201" r:id="rId193"/>
-    <hyperlink ref="N201" r:id="rId194"/>
-    <hyperlink ref="P201" r:id="rId195"/>
-    <hyperlink ref="B205" r:id="rId196"/>
-    <hyperlink ref="L205" r:id="rId197"/>
-    <hyperlink ref="N205" r:id="rId198"/>
-    <hyperlink ref="P205" r:id="rId199"/>
-    <hyperlink ref="Q205" r:id="rId200"/>
-    <hyperlink ref="B207" r:id="rId201"/>
-    <hyperlink ref="L207" r:id="rId202"/>
-    <hyperlink ref="N207" r:id="rId203"/>
-    <hyperlink ref="P207" r:id="rId204"/>
-    <hyperlink ref="B211" r:id="rId205"/>
-    <hyperlink ref="L211" r:id="rId206"/>
-    <hyperlink ref="N211" r:id="rId207"/>
-    <hyperlink ref="P211" r:id="rId208"/>
-    <hyperlink ref="Q211" r:id="rId209"/>
-    <hyperlink ref="N213" r:id="rId210"/>
-    <hyperlink ref="B214" r:id="rId211"/>
-    <hyperlink ref="L214" r:id="rId212"/>
-    <hyperlink ref="N214" r:id="rId213"/>
-    <hyperlink ref="P214" r:id="rId214"/>
-    <hyperlink ref="Q214" r:id="rId215"/>
-    <hyperlink ref="B219" r:id="rId216"/>
-    <hyperlink ref="L219" r:id="rId217"/>
-    <hyperlink ref="N219" r:id="rId218"/>
-    <hyperlink ref="P219" r:id="rId219"/>
-    <hyperlink ref="Q219" r:id="rId220"/>
-    <hyperlink ref="B224" r:id="rId221"/>
-    <hyperlink ref="L224" r:id="rId222"/>
-    <hyperlink ref="N224" r:id="rId223"/>
-    <hyperlink ref="P224" r:id="rId224"/>
-    <hyperlink ref="Q224" r:id="rId225"/>
-    <hyperlink ref="R224" r:id="rId226"/>
-    <hyperlink ref="B230" r:id="rId227"/>
-    <hyperlink ref="L230" r:id="rId228"/>
-    <hyperlink ref="N230" r:id="rId229"/>
-    <hyperlink ref="P230" r:id="rId230"/>
-    <hyperlink ref="B237" r:id="rId231"/>
-    <hyperlink ref="L237" r:id="rId232"/>
-    <hyperlink ref="N237" r:id="rId233"/>
-    <hyperlink ref="P237" r:id="rId234"/>
-    <hyperlink ref="B246" r:id="rId235"/>
-    <hyperlink ref="L246" r:id="rId236"/>
-    <hyperlink ref="N246" r:id="rId237"/>
-    <hyperlink ref="P246" r:id="rId238"/>
-    <hyperlink ref="Q246" r:id="rId239"/>
-    <hyperlink ref="B252" r:id="rId240"/>
-    <hyperlink ref="L252" r:id="rId241"/>
-    <hyperlink ref="N252" r:id="rId242"/>
-    <hyperlink ref="P252" r:id="rId243"/>
-    <hyperlink ref="Q252" r:id="rId244"/>
-    <hyperlink ref="B256" r:id="rId245"/>
-    <hyperlink ref="L256" r:id="rId246"/>
-    <hyperlink ref="N256" r:id="rId247"/>
-    <hyperlink ref="B278" r:id="rId248"/>
-    <hyperlink ref="L278" r:id="rId249"/>
-    <hyperlink ref="N278" r:id="rId250"/>
-    <hyperlink ref="P278" r:id="rId251"/>
-    <hyperlink ref="Q278" r:id="rId252"/>
-    <hyperlink ref="B286" r:id="rId253"/>
-    <hyperlink ref="L286" r:id="rId254"/>
-    <hyperlink ref="N286" r:id="rId255"/>
-    <hyperlink ref="P286" r:id="rId256"/>
-    <hyperlink ref="Q286" r:id="rId257"/>
-    <hyperlink ref="B297" r:id="rId258"/>
-    <hyperlink ref="L297" r:id="rId259"/>
-    <hyperlink ref="N297" r:id="rId260"/>
-    <hyperlink ref="P297" r:id="rId261"/>
-    <hyperlink ref="Q297" r:id="rId262"/>
-    <hyperlink ref="B305" r:id="rId263"/>
-    <hyperlink ref="L305" r:id="rId264"/>
-    <hyperlink ref="N305" r:id="rId265"/>
-    <hyperlink ref="P305" r:id="rId266"/>
-    <hyperlink ref="Q305" r:id="rId267"/>
-    <hyperlink ref="B327" r:id="rId268"/>
-    <hyperlink ref="L327" r:id="rId269"/>
-    <hyperlink ref="N327" r:id="rId270"/>
-    <hyperlink ref="P327" r:id="rId271"/>
-    <hyperlink ref="B329" r:id="rId272"/>
-    <hyperlink ref="L329" r:id="rId273"/>
-    <hyperlink ref="N329" r:id="rId274"/>
-    <hyperlink ref="P329" r:id="rId275"/>
-    <hyperlink ref="Q329" r:id="rId276"/>
-    <hyperlink ref="B333" r:id="rId277"/>
-    <hyperlink ref="L333" r:id="rId278"/>
-    <hyperlink ref="N333" r:id="rId279"/>
-    <hyperlink ref="B336" r:id="rId280"/>
-    <hyperlink ref="L336" r:id="rId281"/>
-    <hyperlink ref="N336" r:id="rId282"/>
-    <hyperlink ref="P336" r:id="rId283"/>
-    <hyperlink ref="Q336" r:id="rId284"/>
-    <hyperlink ref="B338" r:id="rId285"/>
-    <hyperlink ref="L338" r:id="rId286"/>
-    <hyperlink ref="N338" r:id="rId287"/>
-    <hyperlink ref="P338" r:id="rId288"/>
-    <hyperlink ref="Q338" r:id="rId289"/>
-    <hyperlink ref="B344" r:id="rId290"/>
-    <hyperlink ref="L344" r:id="rId291"/>
-    <hyperlink ref="N344" r:id="rId292"/>
-    <hyperlink ref="P344" r:id="rId293"/>
-    <hyperlink ref="Q344" r:id="rId294"/>
-    <hyperlink ref="B345" r:id="rId295"/>
-    <hyperlink ref="L345" r:id="rId296"/>
-    <hyperlink ref="N345" r:id="rId297"/>
-    <hyperlink ref="Q345" r:id="rId298"/>
-    <hyperlink ref="B348" r:id="rId299"/>
-    <hyperlink ref="L348" r:id="rId300"/>
-    <hyperlink ref="N348" r:id="rId301"/>
-    <hyperlink ref="P348" r:id="rId302"/>
-    <hyperlink ref="Q348" r:id="rId303"/>
-    <hyperlink ref="B351" r:id="rId304"/>
-    <hyperlink ref="L351" r:id="rId305"/>
-    <hyperlink ref="N351" r:id="rId306"/>
-    <hyperlink ref="P351" r:id="rId307"/>
-    <hyperlink ref="Q351" r:id="rId308"/>
-    <hyperlink ref="B353" r:id="rId309"/>
-    <hyperlink ref="L353" r:id="rId310"/>
-    <hyperlink ref="N353" r:id="rId311"/>
-    <hyperlink ref="P353" r:id="rId312"/>
-    <hyperlink ref="Q353" r:id="rId313"/>
-    <hyperlink ref="R353" r:id="rId314"/>
-    <hyperlink ref="B392" r:id="rId315"/>
-    <hyperlink ref="L392" r:id="rId316"/>
-    <hyperlink ref="N392" r:id="rId317"/>
-    <hyperlink ref="P392" r:id="rId318"/>
-    <hyperlink ref="B394" r:id="rId319"/>
-    <hyperlink ref="L394" r:id="rId320"/>
-    <hyperlink ref="N394" r:id="rId321"/>
-    <hyperlink ref="P394" r:id="rId322"/>
-    <hyperlink ref="B395" r:id="rId323"/>
-    <hyperlink ref="L395" r:id="rId324"/>
-    <hyperlink ref="N395" r:id="rId325"/>
-    <hyperlink ref="Q395" r:id="rId326"/>
-    <hyperlink ref="B396" r:id="rId327"/>
-    <hyperlink ref="L396" r:id="rId328"/>
-    <hyperlink ref="N396" r:id="rId329"/>
-    <hyperlink ref="P396" r:id="rId330"/>
-    <hyperlink ref="B407" r:id="rId331"/>
-    <hyperlink ref="L407" r:id="rId332"/>
-    <hyperlink ref="N407" r:id="rId333"/>
-    <hyperlink ref="P407" r:id="rId334"/>
-    <hyperlink ref="B408" r:id="rId335"/>
-    <hyperlink ref="L408" r:id="rId336"/>
-    <hyperlink ref="N408" r:id="rId337"/>
-    <hyperlink ref="P408" r:id="rId338"/>
-    <hyperlink ref="B409" r:id="rId339"/>
-    <hyperlink ref="L409" r:id="rId340"/>
-    <hyperlink ref="N409" r:id="rId341"/>
-    <hyperlink ref="Q409" r:id="rId342"/>
-    <hyperlink ref="B411" r:id="rId343"/>
-    <hyperlink ref="L411" r:id="rId344"/>
-    <hyperlink ref="N411" r:id="rId345"/>
-    <hyperlink ref="P411" r:id="rId346"/>
-    <hyperlink ref="B412" r:id="rId347"/>
-    <hyperlink ref="L412" r:id="rId348"/>
-    <hyperlink ref="N412" r:id="rId349"/>
-    <hyperlink ref="Q412" r:id="rId350"/>
-    <hyperlink ref="B418" r:id="rId351"/>
-    <hyperlink ref="L418" r:id="rId352"/>
-    <hyperlink ref="N418" r:id="rId353"/>
-    <hyperlink ref="P418" r:id="rId354"/>
-    <hyperlink ref="B425" r:id="rId355"/>
-    <hyperlink ref="L425" r:id="rId356"/>
-    <hyperlink ref="N425" r:id="rId357"/>
-    <hyperlink ref="P425" r:id="rId358"/>
-    <hyperlink ref="B430" r:id="rId359"/>
-    <hyperlink ref="L430" r:id="rId360"/>
-    <hyperlink ref="N430" r:id="rId361"/>
-    <hyperlink ref="P430" r:id="rId362"/>
-    <hyperlink ref="B431" r:id="rId363"/>
-    <hyperlink ref="L431" r:id="rId364"/>
-    <hyperlink ref="N431" r:id="rId365"/>
-    <hyperlink ref="P431" r:id="rId366"/>
-    <hyperlink ref="B443" r:id="rId367"/>
-    <hyperlink ref="L443" r:id="rId368"/>
-    <hyperlink ref="N443" r:id="rId369"/>
-    <hyperlink ref="P443" r:id="rId370"/>
-    <hyperlink ref="Q443" r:id="rId371"/>
-    <hyperlink ref="B460" r:id="rId372"/>
-    <hyperlink ref="L460" r:id="rId373"/>
-    <hyperlink ref="N460" r:id="rId374"/>
-    <hyperlink ref="P460" r:id="rId375"/>
-    <hyperlink ref="Q460" r:id="rId376"/>
-    <hyperlink ref="N465" r:id="rId377"/>
-    <hyperlink ref="B476" r:id="rId378"/>
-    <hyperlink ref="L476" r:id="rId379"/>
-    <hyperlink ref="N476" r:id="rId380"/>
-    <hyperlink ref="P476" r:id="rId381"/>
-    <hyperlink ref="R476" r:id="rId382"/>
-    <hyperlink ref="B482" r:id="rId383"/>
-    <hyperlink ref="L482" r:id="rId384"/>
-    <hyperlink ref="N482" r:id="rId385"/>
-    <hyperlink ref="P482" r:id="rId386"/>
-    <hyperlink ref="B484" r:id="rId387"/>
-    <hyperlink ref="L484" r:id="rId388"/>
-    <hyperlink ref="N484" r:id="rId389"/>
-    <hyperlink ref="B487" r:id="rId390"/>
-    <hyperlink ref="L487" r:id="rId391"/>
-    <hyperlink ref="N487" r:id="rId392"/>
-    <hyperlink ref="B490" r:id="rId393"/>
-    <hyperlink ref="L490" r:id="rId394"/>
-    <hyperlink ref="N490" r:id="rId395"/>
-    <hyperlink ref="P490" r:id="rId396"/>
-    <hyperlink ref="B494" r:id="rId397"/>
-    <hyperlink ref="L494" r:id="rId398"/>
-    <hyperlink ref="N494" r:id="rId399"/>
-    <hyperlink ref="P494" r:id="rId400"/>
-    <hyperlink ref="B495" r:id="rId401"/>
-    <hyperlink ref="L495" r:id="rId402"/>
-    <hyperlink ref="N495" r:id="rId403"/>
-    <hyperlink ref="P495" r:id="rId404"/>
-    <hyperlink ref="B498" r:id="rId405"/>
-    <hyperlink ref="L498" r:id="rId406"/>
-    <hyperlink ref="N498" r:id="rId407"/>
-    <hyperlink ref="P498" r:id="rId408"/>
-    <hyperlink ref="B509" r:id="rId409"/>
-    <hyperlink ref="L509" r:id="rId410"/>
-    <hyperlink ref="N509" r:id="rId411"/>
-    <hyperlink ref="P509" r:id="rId412"/>
-    <hyperlink ref="B512" r:id="rId413"/>
-    <hyperlink ref="L512" r:id="rId414"/>
-    <hyperlink ref="N512" r:id="rId415"/>
-    <hyperlink ref="P512" r:id="rId416"/>
-    <hyperlink ref="R512" r:id="rId417"/>
-    <hyperlink ref="B523" r:id="rId418"/>
-    <hyperlink ref="L523" r:id="rId419"/>
-    <hyperlink ref="N523" r:id="rId420"/>
-    <hyperlink ref="P523" r:id="rId421"/>
-    <hyperlink ref="Q523" r:id="rId422"/>
-    <hyperlink ref="R523" r:id="rId423"/>
-    <hyperlink ref="B526" r:id="rId424"/>
-    <hyperlink ref="L526" r:id="rId425"/>
-    <hyperlink ref="N526" r:id="rId426"/>
-    <hyperlink ref="P526" r:id="rId427"/>
-    <hyperlink ref="B527" r:id="rId428"/>
-    <hyperlink ref="L527" r:id="rId429"/>
-    <hyperlink ref="N527" r:id="rId430"/>
-    <hyperlink ref="Q527" r:id="rId431"/>
-    <hyperlink ref="B529" r:id="rId432"/>
-    <hyperlink ref="L529" r:id="rId433"/>
-    <hyperlink ref="N529" r:id="rId434"/>
-    <hyperlink ref="P529" r:id="rId435"/>
-    <hyperlink ref="B531" r:id="rId436"/>
-    <hyperlink ref="L531" r:id="rId437"/>
-    <hyperlink ref="N531" r:id="rId438"/>
-    <hyperlink ref="P531" r:id="rId439"/>
-    <hyperlink ref="B532" r:id="rId440"/>
-    <hyperlink ref="L532" r:id="rId441"/>
-    <hyperlink ref="N532" r:id="rId442"/>
-    <hyperlink ref="P532" r:id="rId443"/>
-    <hyperlink ref="B533" r:id="rId444"/>
-    <hyperlink ref="L533" r:id="rId445"/>
-    <hyperlink ref="N533" r:id="rId446"/>
-    <hyperlink ref="P533" r:id="rId447"/>
-    <hyperlink ref="Q533" r:id="rId448"/>
-    <hyperlink ref="B534" r:id="rId449"/>
-    <hyperlink ref="L534" r:id="rId450"/>
-    <hyperlink ref="N534" r:id="rId451"/>
-    <hyperlink ref="Q534" r:id="rId452"/>
-    <hyperlink ref="B535" r:id="rId453"/>
-    <hyperlink ref="L535" r:id="rId454"/>
-    <hyperlink ref="N535" r:id="rId455"/>
-    <hyperlink ref="Q535" r:id="rId456"/>
-    <hyperlink ref="B546" r:id="rId457"/>
-    <hyperlink ref="L546" r:id="rId458"/>
-    <hyperlink ref="N546" r:id="rId459"/>
-    <hyperlink ref="P546" r:id="rId460"/>
-    <hyperlink ref="Q546" r:id="rId461"/>
-    <hyperlink ref="N554" r:id="rId462"/>
-    <hyperlink ref="B555" r:id="rId463"/>
-    <hyperlink ref="L555" r:id="rId464"/>
-    <hyperlink ref="N555" r:id="rId465"/>
-    <hyperlink ref="P555" r:id="rId466"/>
-    <hyperlink ref="Q555" r:id="rId467"/>
-    <hyperlink ref="B562" r:id="rId468"/>
-    <hyperlink ref="L562" r:id="rId469"/>
-    <hyperlink ref="N562" r:id="rId470"/>
-    <hyperlink ref="P562" r:id="rId471"/>
-    <hyperlink ref="Q562" r:id="rId472"/>
-    <hyperlink ref="B563" r:id="rId473"/>
-    <hyperlink ref="L563" r:id="rId474"/>
-    <hyperlink ref="N563" r:id="rId475"/>
-    <hyperlink ref="Q563" r:id="rId476"/>
-    <hyperlink ref="B564" r:id="rId477"/>
-    <hyperlink ref="L564" r:id="rId478"/>
-    <hyperlink ref="N564" r:id="rId479"/>
-    <hyperlink ref="Q564" r:id="rId480"/>
-    <hyperlink ref="B585" r:id="rId481"/>
-    <hyperlink ref="L585" r:id="rId482"/>
-    <hyperlink ref="N585" r:id="rId483"/>
-    <hyperlink ref="P585" r:id="rId484"/>
-    <hyperlink ref="R585" r:id="rId485"/>
-    <hyperlink ref="B595" r:id="rId486"/>
-    <hyperlink ref="L595" r:id="rId487"/>
-    <hyperlink ref="N595" r:id="rId488"/>
-    <hyperlink ref="P595" r:id="rId489"/>
-    <hyperlink ref="Q595" r:id="rId490"/>
-    <hyperlink ref="B621" r:id="rId491"/>
-    <hyperlink ref="L621" r:id="rId492"/>
-    <hyperlink ref="N621" r:id="rId493"/>
-    <hyperlink ref="P621" r:id="rId494"/>
-    <hyperlink ref="Q621" r:id="rId495"/>
-    <hyperlink ref="B622" r:id="rId496"/>
-    <hyperlink ref="L622" r:id="rId497"/>
-    <hyperlink ref="N622" r:id="rId498"/>
-    <hyperlink ref="O622" r:id="rId499"/>
-    <hyperlink ref="P622" r:id="rId500"/>
-    <hyperlink ref="Q622" r:id="rId501"/>
-    <hyperlink ref="B631" r:id="rId502"/>
-    <hyperlink ref="N631" r:id="rId503"/>
-    <hyperlink ref="P631" r:id="rId504"/>
-    <hyperlink ref="B640" r:id="rId505"/>
-    <hyperlink ref="L640" r:id="rId506"/>
-    <hyperlink ref="N640" r:id="rId507"/>
-    <hyperlink ref="P640" r:id="rId508"/>
-    <hyperlink ref="B647" r:id="rId509"/>
-    <hyperlink ref="L647" r:id="rId510"/>
-    <hyperlink ref="N647" r:id="rId511"/>
-  </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4018" uniqueCount="1794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4020" uniqueCount="1794">
   <si>
     <t>Status</t>
   </si>
@@ -8475,9 +8475,9 @@
     </row>
     <row r="65" s="1" customFormat="1" ht="106.1267" customHeight="1">
       <c r="A65" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B65" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>213</v>
       </c>
       <c r="C65" s="13" t="s">
@@ -8498,12 +8498,14 @@
       <c r="H65" s="14">
         <v>46100</v>
       </c>
-      <c r="I65" s="14"/>
+      <c r="I65" s="14">
+        <v>46935</v>
+      </c>
       <c r="J65" s="12"/>
-      <c r="K65" s="14">
-        <v>46100</v>
-      </c>
-      <c r="L65" s="13"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="18" t="s">
+        <v>11</v>
+      </c>
       <c r="M65" s="17" t="s">
         <v>215</v>
       </c>
@@ -8512,7 +8514,9 @@
       </c>
       <c r="O65" s="12"/>
       <c r="P65" s="12"/>
-      <c r="Q65" s="12"/>
+      <c r="Q65" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="R65" s="12"/>
     </row>
     <row r="66" s="1" customFormat="1" ht="106.1267" customHeight="1">
@@ -33556,462 +33560,465 @@
     <hyperlink ref="N63" r:id="rId39"/>
     <hyperlink ref="P63" r:id="rId40"/>
     <hyperlink ref="R63" r:id="rId41"/>
-    <hyperlink ref="N65" r:id="rId42"/>
-    <hyperlink ref="B66" r:id="rId43"/>
-    <hyperlink ref="L66" r:id="rId44"/>
-    <hyperlink ref="N66" r:id="rId45"/>
-    <hyperlink ref="Q66" r:id="rId46"/>
-    <hyperlink ref="B68" r:id="rId47"/>
-    <hyperlink ref="L68" r:id="rId48"/>
-    <hyperlink ref="N68" r:id="rId49"/>
-    <hyperlink ref="Q68" r:id="rId50"/>
-    <hyperlink ref="B69" r:id="rId51"/>
-    <hyperlink ref="L69" r:id="rId52"/>
-    <hyperlink ref="N69" r:id="rId53"/>
-    <hyperlink ref="Q69" r:id="rId54"/>
-    <hyperlink ref="N78" r:id="rId55"/>
-    <hyperlink ref="B79" r:id="rId56"/>
-    <hyperlink ref="L79" r:id="rId57"/>
-    <hyperlink ref="N79" r:id="rId58"/>
-    <hyperlink ref="P79" r:id="rId59"/>
-    <hyperlink ref="Q79" r:id="rId60"/>
-    <hyperlink ref="B89" r:id="rId61"/>
-    <hyperlink ref="L89" r:id="rId62"/>
-    <hyperlink ref="N89" r:id="rId63"/>
-    <hyperlink ref="P89" r:id="rId64"/>
-    <hyperlink ref="Q89" r:id="rId65"/>
-    <hyperlink ref="R89" r:id="rId66"/>
-    <hyperlink ref="B90" r:id="rId67"/>
-    <hyperlink ref="L90" r:id="rId68"/>
-    <hyperlink ref="N90" r:id="rId69"/>
-    <hyperlink ref="Q90" r:id="rId70"/>
-    <hyperlink ref="B100" r:id="rId71"/>
-    <hyperlink ref="L100" r:id="rId72"/>
-    <hyperlink ref="N100" r:id="rId73"/>
-    <hyperlink ref="P100" r:id="rId74"/>
-    <hyperlink ref="Q100" r:id="rId75"/>
-    <hyperlink ref="B101" r:id="rId76"/>
-    <hyperlink ref="L101" r:id="rId77"/>
-    <hyperlink ref="N101" r:id="rId78"/>
-    <hyperlink ref="Q101" r:id="rId79"/>
-    <hyperlink ref="B117" r:id="rId80"/>
-    <hyperlink ref="L117" r:id="rId81"/>
-    <hyperlink ref="N117" r:id="rId82"/>
-    <hyperlink ref="P117" r:id="rId83"/>
-    <hyperlink ref="R117" r:id="rId84"/>
-    <hyperlink ref="N118" r:id="rId85"/>
-    <hyperlink ref="B119" r:id="rId86"/>
-    <hyperlink ref="L119" r:id="rId87"/>
-    <hyperlink ref="N119" r:id="rId88"/>
-    <hyperlink ref="Q119" r:id="rId89"/>
-    <hyperlink ref="B129" r:id="rId90"/>
-    <hyperlink ref="L129" r:id="rId91"/>
-    <hyperlink ref="N129" r:id="rId92"/>
-    <hyperlink ref="P129" r:id="rId93"/>
-    <hyperlink ref="R129" r:id="rId94"/>
-    <hyperlink ref="N130" r:id="rId95"/>
-    <hyperlink ref="B131" r:id="rId96"/>
-    <hyperlink ref="L131" r:id="rId97"/>
-    <hyperlink ref="N131" r:id="rId98"/>
-    <hyperlink ref="Q131" r:id="rId99"/>
-    <hyperlink ref="B137" r:id="rId100"/>
-    <hyperlink ref="L137" r:id="rId101"/>
-    <hyperlink ref="N137" r:id="rId102"/>
-    <hyperlink ref="P137" r:id="rId103"/>
-    <hyperlink ref="Q137" r:id="rId104"/>
-    <hyperlink ref="N138" r:id="rId105"/>
-    <hyperlink ref="B139" r:id="rId106"/>
-    <hyperlink ref="L139" r:id="rId107"/>
-    <hyperlink ref="N139" r:id="rId108"/>
-    <hyperlink ref="Q139" r:id="rId109"/>
-    <hyperlink ref="B145" r:id="rId110"/>
-    <hyperlink ref="L145" r:id="rId111"/>
-    <hyperlink ref="N145" r:id="rId112"/>
-    <hyperlink ref="P145" r:id="rId113"/>
-    <hyperlink ref="R145" r:id="rId114"/>
-    <hyperlink ref="N146" r:id="rId115"/>
-    <hyperlink ref="B147" r:id="rId116"/>
-    <hyperlink ref="L147" r:id="rId117"/>
-    <hyperlink ref="N147" r:id="rId118"/>
-    <hyperlink ref="Q147" r:id="rId119"/>
-    <hyperlink ref="B151" r:id="rId120"/>
-    <hyperlink ref="L151" r:id="rId121"/>
-    <hyperlink ref="N151" r:id="rId122"/>
-    <hyperlink ref="P151" r:id="rId123"/>
-    <hyperlink ref="Q151" r:id="rId124"/>
-    <hyperlink ref="R151" r:id="rId125"/>
-    <hyperlink ref="B152" r:id="rId126"/>
-    <hyperlink ref="L152" r:id="rId127"/>
-    <hyperlink ref="N152" r:id="rId128"/>
-    <hyperlink ref="Q152" r:id="rId129"/>
-    <hyperlink ref="B155" r:id="rId130"/>
-    <hyperlink ref="L155" r:id="rId131"/>
-    <hyperlink ref="N155" r:id="rId132"/>
-    <hyperlink ref="P155" r:id="rId133"/>
-    <hyperlink ref="Q155" r:id="rId134"/>
-    <hyperlink ref="R155" r:id="rId135"/>
-    <hyperlink ref="N156" r:id="rId136"/>
-    <hyperlink ref="B157" r:id="rId137"/>
-    <hyperlink ref="L157" r:id="rId138"/>
-    <hyperlink ref="N157" r:id="rId139"/>
-    <hyperlink ref="Q157" r:id="rId140"/>
-    <hyperlink ref="B158" r:id="rId141"/>
-    <hyperlink ref="L158" r:id="rId142"/>
-    <hyperlink ref="N158" r:id="rId143"/>
-    <hyperlink ref="P158" r:id="rId144"/>
-    <hyperlink ref="Q158" r:id="rId145"/>
-    <hyperlink ref="R158" r:id="rId146"/>
-    <hyperlink ref="B159" r:id="rId147"/>
-    <hyperlink ref="L159" r:id="rId148"/>
-    <hyperlink ref="N159" r:id="rId149"/>
-    <hyperlink ref="P159" r:id="rId150"/>
-    <hyperlink ref="Q159" r:id="rId151"/>
-    <hyperlink ref="B161" r:id="rId152"/>
-    <hyperlink ref="L161" r:id="rId153"/>
-    <hyperlink ref="N161" r:id="rId154"/>
-    <hyperlink ref="P161" r:id="rId155"/>
-    <hyperlink ref="Q161" r:id="rId156"/>
-    <hyperlink ref="R161" r:id="rId157"/>
-    <hyperlink ref="B162" r:id="rId158"/>
-    <hyperlink ref="L162" r:id="rId159"/>
-    <hyperlink ref="N162" r:id="rId160"/>
-    <hyperlink ref="Q162" r:id="rId161"/>
-    <hyperlink ref="B165" r:id="rId162"/>
-    <hyperlink ref="L165" r:id="rId163"/>
-    <hyperlink ref="N165" r:id="rId164"/>
-    <hyperlink ref="P165" r:id="rId165"/>
-    <hyperlink ref="R165" r:id="rId166"/>
-    <hyperlink ref="B166" r:id="rId167"/>
-    <hyperlink ref="L166" r:id="rId168"/>
-    <hyperlink ref="N166" r:id="rId169"/>
-    <hyperlink ref="Q166" r:id="rId170"/>
-    <hyperlink ref="B172" r:id="rId171"/>
-    <hyperlink ref="L172" r:id="rId172"/>
-    <hyperlink ref="N172" r:id="rId173"/>
-    <hyperlink ref="P172" r:id="rId174"/>
-    <hyperlink ref="B178" r:id="rId175"/>
-    <hyperlink ref="L178" r:id="rId176"/>
-    <hyperlink ref="N178" r:id="rId177"/>
-    <hyperlink ref="P178" r:id="rId178"/>
-    <hyperlink ref="Q178" r:id="rId179"/>
-    <hyperlink ref="B198" r:id="rId180"/>
-    <hyperlink ref="L198" r:id="rId181"/>
-    <hyperlink ref="N198" r:id="rId182"/>
-    <hyperlink ref="P198" r:id="rId183"/>
-    <hyperlink ref="B202" r:id="rId184"/>
-    <hyperlink ref="L202" r:id="rId185"/>
-    <hyperlink ref="N202" r:id="rId186"/>
-    <hyperlink ref="P202" r:id="rId187"/>
-    <hyperlink ref="B206" r:id="rId188"/>
-    <hyperlink ref="L206" r:id="rId189"/>
-    <hyperlink ref="N206" r:id="rId190"/>
-    <hyperlink ref="P206" r:id="rId191"/>
-    <hyperlink ref="B210" r:id="rId192"/>
-    <hyperlink ref="L210" r:id="rId193"/>
-    <hyperlink ref="N210" r:id="rId194"/>
-    <hyperlink ref="P210" r:id="rId195"/>
-    <hyperlink ref="Q210" r:id="rId196"/>
-    <hyperlink ref="B212" r:id="rId197"/>
-    <hyperlink ref="L212" r:id="rId198"/>
-    <hyperlink ref="N212" r:id="rId199"/>
-    <hyperlink ref="P212" r:id="rId200"/>
-    <hyperlink ref="B216" r:id="rId201"/>
-    <hyperlink ref="L216" r:id="rId202"/>
-    <hyperlink ref="N216" r:id="rId203"/>
-    <hyperlink ref="P216" r:id="rId204"/>
-    <hyperlink ref="Q216" r:id="rId205"/>
-    <hyperlink ref="N218" r:id="rId206"/>
-    <hyperlink ref="B219" r:id="rId207"/>
-    <hyperlink ref="L219" r:id="rId208"/>
-    <hyperlink ref="N219" r:id="rId209"/>
-    <hyperlink ref="P219" r:id="rId210"/>
-    <hyperlink ref="Q219" r:id="rId211"/>
-    <hyperlink ref="B224" r:id="rId212"/>
-    <hyperlink ref="L224" r:id="rId213"/>
-    <hyperlink ref="N224" r:id="rId214"/>
-    <hyperlink ref="P224" r:id="rId215"/>
-    <hyperlink ref="Q224" r:id="rId216"/>
-    <hyperlink ref="B229" r:id="rId217"/>
-    <hyperlink ref="L229" r:id="rId218"/>
-    <hyperlink ref="N229" r:id="rId219"/>
-    <hyperlink ref="P229" r:id="rId220"/>
-    <hyperlink ref="Q229" r:id="rId221"/>
-    <hyperlink ref="R229" r:id="rId222"/>
-    <hyperlink ref="B235" r:id="rId223"/>
-    <hyperlink ref="L235" r:id="rId224"/>
-    <hyperlink ref="N235" r:id="rId225"/>
-    <hyperlink ref="P235" r:id="rId226"/>
-    <hyperlink ref="B242" r:id="rId227"/>
-    <hyperlink ref="L242" r:id="rId228"/>
-    <hyperlink ref="N242" r:id="rId229"/>
-    <hyperlink ref="P242" r:id="rId230"/>
-    <hyperlink ref="B251" r:id="rId231"/>
-    <hyperlink ref="L251" r:id="rId232"/>
-    <hyperlink ref="N251" r:id="rId233"/>
-    <hyperlink ref="P251" r:id="rId234"/>
-    <hyperlink ref="Q251" r:id="rId235"/>
-    <hyperlink ref="B257" r:id="rId236"/>
-    <hyperlink ref="L257" r:id="rId237"/>
-    <hyperlink ref="N257" r:id="rId238"/>
-    <hyperlink ref="P257" r:id="rId239"/>
-    <hyperlink ref="Q257" r:id="rId240"/>
-    <hyperlink ref="B261" r:id="rId241"/>
-    <hyperlink ref="L261" r:id="rId242"/>
-    <hyperlink ref="N261" r:id="rId243"/>
-    <hyperlink ref="B283" r:id="rId244"/>
-    <hyperlink ref="L283" r:id="rId245"/>
-    <hyperlink ref="N283" r:id="rId246"/>
-    <hyperlink ref="P283" r:id="rId247"/>
-    <hyperlink ref="Q283" r:id="rId248"/>
-    <hyperlink ref="B291" r:id="rId249"/>
-    <hyperlink ref="L291" r:id="rId250"/>
-    <hyperlink ref="N291" r:id="rId251"/>
-    <hyperlink ref="P291" r:id="rId252"/>
-    <hyperlink ref="Q291" r:id="rId253"/>
-    <hyperlink ref="B302" r:id="rId254"/>
-    <hyperlink ref="L302" r:id="rId255"/>
-    <hyperlink ref="N302" r:id="rId256"/>
-    <hyperlink ref="P302" r:id="rId257"/>
-    <hyperlink ref="Q302" r:id="rId258"/>
-    <hyperlink ref="B310" r:id="rId259"/>
-    <hyperlink ref="L310" r:id="rId260"/>
-    <hyperlink ref="N310" r:id="rId261"/>
-    <hyperlink ref="P310" r:id="rId262"/>
-    <hyperlink ref="Q310" r:id="rId263"/>
-    <hyperlink ref="B332" r:id="rId264"/>
-    <hyperlink ref="L332" r:id="rId265"/>
-    <hyperlink ref="N332" r:id="rId266"/>
-    <hyperlink ref="P332" r:id="rId267"/>
-    <hyperlink ref="B334" r:id="rId268"/>
-    <hyperlink ref="L334" r:id="rId269"/>
-    <hyperlink ref="N334" r:id="rId270"/>
-    <hyperlink ref="P334" r:id="rId271"/>
-    <hyperlink ref="Q334" r:id="rId272"/>
-    <hyperlink ref="B338" r:id="rId273"/>
-    <hyperlink ref="L338" r:id="rId274"/>
-    <hyperlink ref="N338" r:id="rId275"/>
-    <hyperlink ref="B341" r:id="rId276"/>
-    <hyperlink ref="L341" r:id="rId277"/>
-    <hyperlink ref="N341" r:id="rId278"/>
-    <hyperlink ref="P341" r:id="rId279"/>
-    <hyperlink ref="Q341" r:id="rId280"/>
-    <hyperlink ref="B343" r:id="rId281"/>
-    <hyperlink ref="L343" r:id="rId282"/>
-    <hyperlink ref="N343" r:id="rId283"/>
-    <hyperlink ref="P343" r:id="rId284"/>
-    <hyperlink ref="Q343" r:id="rId285"/>
-    <hyperlink ref="B349" r:id="rId286"/>
-    <hyperlink ref="L349" r:id="rId287"/>
-    <hyperlink ref="N349" r:id="rId288"/>
-    <hyperlink ref="P349" r:id="rId289"/>
-    <hyperlink ref="Q349" r:id="rId290"/>
-    <hyperlink ref="B350" r:id="rId291"/>
-    <hyperlink ref="L350" r:id="rId292"/>
-    <hyperlink ref="N350" r:id="rId293"/>
-    <hyperlink ref="Q350" r:id="rId294"/>
-    <hyperlink ref="B353" r:id="rId295"/>
-    <hyperlink ref="L353" r:id="rId296"/>
-    <hyperlink ref="N353" r:id="rId297"/>
-    <hyperlink ref="P353" r:id="rId298"/>
-    <hyperlink ref="Q353" r:id="rId299"/>
-    <hyperlink ref="B356" r:id="rId300"/>
-    <hyperlink ref="L356" r:id="rId301"/>
-    <hyperlink ref="N356" r:id="rId302"/>
-    <hyperlink ref="P356" r:id="rId303"/>
-    <hyperlink ref="Q356" r:id="rId304"/>
-    <hyperlink ref="B358" r:id="rId305"/>
-    <hyperlink ref="L358" r:id="rId306"/>
-    <hyperlink ref="N358" r:id="rId307"/>
-    <hyperlink ref="P358" r:id="rId308"/>
-    <hyperlink ref="Q358" r:id="rId309"/>
-    <hyperlink ref="R358" r:id="rId310"/>
-    <hyperlink ref="B397" r:id="rId311"/>
-    <hyperlink ref="L397" r:id="rId312"/>
-    <hyperlink ref="N397" r:id="rId313"/>
-    <hyperlink ref="P397" r:id="rId314"/>
-    <hyperlink ref="N399" r:id="rId315"/>
-    <hyperlink ref="B400" r:id="rId316"/>
-    <hyperlink ref="L400" r:id="rId317"/>
-    <hyperlink ref="N400" r:id="rId318"/>
-    <hyperlink ref="Q400" r:id="rId319"/>
-    <hyperlink ref="N401" r:id="rId320"/>
-    <hyperlink ref="B412" r:id="rId321"/>
-    <hyperlink ref="L412" r:id="rId322"/>
-    <hyperlink ref="N412" r:id="rId323"/>
-    <hyperlink ref="P412" r:id="rId324"/>
-    <hyperlink ref="B413" r:id="rId325"/>
-    <hyperlink ref="L413" r:id="rId326"/>
-    <hyperlink ref="N413" r:id="rId327"/>
-    <hyperlink ref="P413" r:id="rId328"/>
-    <hyperlink ref="B414" r:id="rId329"/>
-    <hyperlink ref="L414" r:id="rId330"/>
-    <hyperlink ref="N414" r:id="rId331"/>
-    <hyperlink ref="Q414" r:id="rId332"/>
-    <hyperlink ref="N416" r:id="rId333"/>
-    <hyperlink ref="B417" r:id="rId334"/>
-    <hyperlink ref="L417" r:id="rId335"/>
-    <hyperlink ref="N417" r:id="rId336"/>
-    <hyperlink ref="Q417" r:id="rId337"/>
-    <hyperlink ref="B423" r:id="rId338"/>
-    <hyperlink ref="L423" r:id="rId339"/>
-    <hyperlink ref="N423" r:id="rId340"/>
-    <hyperlink ref="P423" r:id="rId341"/>
-    <hyperlink ref="B430" r:id="rId342"/>
-    <hyperlink ref="L430" r:id="rId343"/>
-    <hyperlink ref="N430" r:id="rId344"/>
-    <hyperlink ref="P430" r:id="rId345"/>
-    <hyperlink ref="B435" r:id="rId346"/>
-    <hyperlink ref="L435" r:id="rId347"/>
-    <hyperlink ref="N435" r:id="rId348"/>
-    <hyperlink ref="P435" r:id="rId349"/>
-    <hyperlink ref="B436" r:id="rId350"/>
-    <hyperlink ref="L436" r:id="rId351"/>
-    <hyperlink ref="N436" r:id="rId352"/>
-    <hyperlink ref="P436" r:id="rId353"/>
-    <hyperlink ref="B448" r:id="rId354"/>
-    <hyperlink ref="L448" r:id="rId355"/>
-    <hyperlink ref="N448" r:id="rId356"/>
-    <hyperlink ref="P448" r:id="rId357"/>
-    <hyperlink ref="Q448" r:id="rId358"/>
-    <hyperlink ref="B465" r:id="rId359"/>
-    <hyperlink ref="L465" r:id="rId360"/>
-    <hyperlink ref="N465" r:id="rId361"/>
-    <hyperlink ref="P465" r:id="rId362"/>
-    <hyperlink ref="Q465" r:id="rId363"/>
-    <hyperlink ref="N470" r:id="rId364"/>
-    <hyperlink ref="B481" r:id="rId365"/>
-    <hyperlink ref="L481" r:id="rId366"/>
-    <hyperlink ref="N481" r:id="rId367"/>
-    <hyperlink ref="P481" r:id="rId368"/>
-    <hyperlink ref="R481" r:id="rId369"/>
-    <hyperlink ref="B487" r:id="rId370"/>
-    <hyperlink ref="L487" r:id="rId371"/>
-    <hyperlink ref="N487" r:id="rId372"/>
-    <hyperlink ref="P487" r:id="rId373"/>
-    <hyperlink ref="B489" r:id="rId374"/>
-    <hyperlink ref="L489" r:id="rId375"/>
-    <hyperlink ref="N489" r:id="rId376"/>
-    <hyperlink ref="B492" r:id="rId377"/>
-    <hyperlink ref="L492" r:id="rId378"/>
-    <hyperlink ref="N492" r:id="rId379"/>
-    <hyperlink ref="B495" r:id="rId380"/>
-    <hyperlink ref="L495" r:id="rId381"/>
-    <hyperlink ref="N495" r:id="rId382"/>
-    <hyperlink ref="P495" r:id="rId383"/>
-    <hyperlink ref="B499" r:id="rId384"/>
-    <hyperlink ref="L499" r:id="rId385"/>
-    <hyperlink ref="N499" r:id="rId386"/>
-    <hyperlink ref="P499" r:id="rId387"/>
-    <hyperlink ref="B500" r:id="rId388"/>
-    <hyperlink ref="L500" r:id="rId389"/>
-    <hyperlink ref="N500" r:id="rId390"/>
-    <hyperlink ref="P500" r:id="rId391"/>
-    <hyperlink ref="B503" r:id="rId392"/>
-    <hyperlink ref="L503" r:id="rId393"/>
-    <hyperlink ref="N503" r:id="rId394"/>
-    <hyperlink ref="P503" r:id="rId395"/>
-    <hyperlink ref="B514" r:id="rId396"/>
-    <hyperlink ref="L514" r:id="rId397"/>
-    <hyperlink ref="N514" r:id="rId398"/>
-    <hyperlink ref="P514" r:id="rId399"/>
-    <hyperlink ref="B517" r:id="rId400"/>
-    <hyperlink ref="L517" r:id="rId401"/>
-    <hyperlink ref="N517" r:id="rId402"/>
-    <hyperlink ref="P517" r:id="rId403"/>
-    <hyperlink ref="R517" r:id="rId404"/>
-    <hyperlink ref="B528" r:id="rId405"/>
-    <hyperlink ref="L528" r:id="rId406"/>
-    <hyperlink ref="N528" r:id="rId407"/>
-    <hyperlink ref="P528" r:id="rId408"/>
-    <hyperlink ref="Q528" r:id="rId409"/>
-    <hyperlink ref="R528" r:id="rId410"/>
-    <hyperlink ref="B531" r:id="rId411"/>
-    <hyperlink ref="L531" r:id="rId412"/>
-    <hyperlink ref="N531" r:id="rId413"/>
-    <hyperlink ref="P531" r:id="rId414"/>
-    <hyperlink ref="B532" r:id="rId415"/>
-    <hyperlink ref="L532" r:id="rId416"/>
-    <hyperlink ref="N532" r:id="rId417"/>
-    <hyperlink ref="Q532" r:id="rId418"/>
-    <hyperlink ref="B534" r:id="rId419"/>
-    <hyperlink ref="L534" r:id="rId420"/>
-    <hyperlink ref="N534" r:id="rId421"/>
-    <hyperlink ref="P534" r:id="rId422"/>
-    <hyperlink ref="B536" r:id="rId423"/>
-    <hyperlink ref="L536" r:id="rId424"/>
-    <hyperlink ref="N536" r:id="rId425"/>
-    <hyperlink ref="P536" r:id="rId426"/>
-    <hyperlink ref="B537" r:id="rId427"/>
-    <hyperlink ref="L537" r:id="rId428"/>
-    <hyperlink ref="N537" r:id="rId429"/>
-    <hyperlink ref="P537" r:id="rId430"/>
-    <hyperlink ref="B538" r:id="rId431"/>
-    <hyperlink ref="L538" r:id="rId432"/>
-    <hyperlink ref="N538" r:id="rId433"/>
-    <hyperlink ref="P538" r:id="rId434"/>
-    <hyperlink ref="Q538" r:id="rId435"/>
-    <hyperlink ref="B539" r:id="rId436"/>
-    <hyperlink ref="L539" r:id="rId437"/>
-    <hyperlink ref="N539" r:id="rId438"/>
-    <hyperlink ref="Q539" r:id="rId439"/>
-    <hyperlink ref="B540" r:id="rId440"/>
-    <hyperlink ref="L540" r:id="rId441"/>
-    <hyperlink ref="N540" r:id="rId442"/>
-    <hyperlink ref="Q540" r:id="rId443"/>
-    <hyperlink ref="B551" r:id="rId444"/>
-    <hyperlink ref="L551" r:id="rId445"/>
-    <hyperlink ref="N551" r:id="rId446"/>
-    <hyperlink ref="P551" r:id="rId447"/>
-    <hyperlink ref="Q551" r:id="rId448"/>
-    <hyperlink ref="N559" r:id="rId449"/>
-    <hyperlink ref="B560" r:id="rId450"/>
-    <hyperlink ref="L560" r:id="rId451"/>
-    <hyperlink ref="N560" r:id="rId452"/>
-    <hyperlink ref="P560" r:id="rId453"/>
-    <hyperlink ref="Q560" r:id="rId454"/>
-    <hyperlink ref="B567" r:id="rId455"/>
-    <hyperlink ref="L567" r:id="rId456"/>
-    <hyperlink ref="N567" r:id="rId457"/>
-    <hyperlink ref="P567" r:id="rId458"/>
-    <hyperlink ref="Q567" r:id="rId459"/>
-    <hyperlink ref="B568" r:id="rId460"/>
-    <hyperlink ref="L568" r:id="rId461"/>
-    <hyperlink ref="N568" r:id="rId462"/>
-    <hyperlink ref="Q568" r:id="rId463"/>
-    <hyperlink ref="B569" r:id="rId464"/>
-    <hyperlink ref="L569" r:id="rId465"/>
-    <hyperlink ref="N569" r:id="rId466"/>
-    <hyperlink ref="Q569" r:id="rId467"/>
-    <hyperlink ref="B590" r:id="rId468"/>
-    <hyperlink ref="L590" r:id="rId469"/>
-    <hyperlink ref="N590" r:id="rId470"/>
-    <hyperlink ref="P590" r:id="rId471"/>
-    <hyperlink ref="R590" r:id="rId472"/>
-    <hyperlink ref="B600" r:id="rId473"/>
-    <hyperlink ref="L600" r:id="rId474"/>
-    <hyperlink ref="N600" r:id="rId475"/>
-    <hyperlink ref="P600" r:id="rId476"/>
-    <hyperlink ref="Q600" r:id="rId477"/>
-    <hyperlink ref="B626" r:id="rId478"/>
-    <hyperlink ref="L626" r:id="rId479"/>
-    <hyperlink ref="N626" r:id="rId480"/>
-    <hyperlink ref="P626" r:id="rId481"/>
-    <hyperlink ref="Q626" r:id="rId482"/>
-    <hyperlink ref="B627" r:id="rId483"/>
-    <hyperlink ref="L627" r:id="rId484"/>
-    <hyperlink ref="N627" r:id="rId485"/>
-    <hyperlink ref="P627" r:id="rId486"/>
-    <hyperlink ref="Q627" r:id="rId487"/>
-    <hyperlink ref="B636" r:id="rId488"/>
-    <hyperlink ref="N636" r:id="rId489"/>
-    <hyperlink ref="P636" r:id="rId490"/>
-    <hyperlink ref="B645" r:id="rId491"/>
-    <hyperlink ref="L645" r:id="rId492"/>
-    <hyperlink ref="N645" r:id="rId493"/>
-    <hyperlink ref="P645" r:id="rId494"/>
-    <hyperlink ref="B652" r:id="rId495"/>
-    <hyperlink ref="L652" r:id="rId496"/>
-    <hyperlink ref="N652" r:id="rId497"/>
+    <hyperlink ref="B65" r:id="rId42"/>
+    <hyperlink ref="L65" r:id="rId43"/>
+    <hyperlink ref="N65" r:id="rId44"/>
+    <hyperlink ref="Q65" r:id="rId45"/>
+    <hyperlink ref="B66" r:id="rId46"/>
+    <hyperlink ref="L66" r:id="rId47"/>
+    <hyperlink ref="N66" r:id="rId48"/>
+    <hyperlink ref="Q66" r:id="rId49"/>
+    <hyperlink ref="B68" r:id="rId50"/>
+    <hyperlink ref="L68" r:id="rId51"/>
+    <hyperlink ref="N68" r:id="rId52"/>
+    <hyperlink ref="Q68" r:id="rId53"/>
+    <hyperlink ref="B69" r:id="rId54"/>
+    <hyperlink ref="L69" r:id="rId55"/>
+    <hyperlink ref="N69" r:id="rId56"/>
+    <hyperlink ref="Q69" r:id="rId57"/>
+    <hyperlink ref="N78" r:id="rId58"/>
+    <hyperlink ref="B79" r:id="rId59"/>
+    <hyperlink ref="L79" r:id="rId60"/>
+    <hyperlink ref="N79" r:id="rId61"/>
+    <hyperlink ref="P79" r:id="rId62"/>
+    <hyperlink ref="Q79" r:id="rId63"/>
+    <hyperlink ref="B89" r:id="rId64"/>
+    <hyperlink ref="L89" r:id="rId65"/>
+    <hyperlink ref="N89" r:id="rId66"/>
+    <hyperlink ref="P89" r:id="rId67"/>
+    <hyperlink ref="Q89" r:id="rId68"/>
+    <hyperlink ref="R89" r:id="rId69"/>
+    <hyperlink ref="B90" r:id="rId70"/>
+    <hyperlink ref="L90" r:id="rId71"/>
+    <hyperlink ref="N90" r:id="rId72"/>
+    <hyperlink ref="Q90" r:id="rId73"/>
+    <hyperlink ref="B100" r:id="rId74"/>
+    <hyperlink ref="L100" r:id="rId75"/>
+    <hyperlink ref="N100" r:id="rId76"/>
+    <hyperlink ref="P100" r:id="rId77"/>
+    <hyperlink ref="Q100" r:id="rId78"/>
+    <hyperlink ref="B101" r:id="rId79"/>
+    <hyperlink ref="L101" r:id="rId80"/>
+    <hyperlink ref="N101" r:id="rId81"/>
+    <hyperlink ref="Q101" r:id="rId82"/>
+    <hyperlink ref="B117" r:id="rId83"/>
+    <hyperlink ref="L117" r:id="rId84"/>
+    <hyperlink ref="N117" r:id="rId85"/>
+    <hyperlink ref="P117" r:id="rId86"/>
+    <hyperlink ref="R117" r:id="rId87"/>
+    <hyperlink ref="N118" r:id="rId88"/>
+    <hyperlink ref="B119" r:id="rId89"/>
+    <hyperlink ref="L119" r:id="rId90"/>
+    <hyperlink ref="N119" r:id="rId91"/>
+    <hyperlink ref="Q119" r:id="rId92"/>
+    <hyperlink ref="B129" r:id="rId93"/>
+    <hyperlink ref="L129" r:id="rId94"/>
+    <hyperlink ref="N129" r:id="rId95"/>
+    <hyperlink ref="P129" r:id="rId96"/>
+    <hyperlink ref="R129" r:id="rId97"/>
+    <hyperlink ref="N130" r:id="rId98"/>
+    <hyperlink ref="B131" r:id="rId99"/>
+    <hyperlink ref="L131" r:id="rId100"/>
+    <hyperlink ref="N131" r:id="rId101"/>
+    <hyperlink ref="Q131" r:id="rId102"/>
+    <hyperlink ref="B137" r:id="rId103"/>
+    <hyperlink ref="L137" r:id="rId104"/>
+    <hyperlink ref="N137" r:id="rId105"/>
+    <hyperlink ref="P137" r:id="rId106"/>
+    <hyperlink ref="Q137" r:id="rId107"/>
+    <hyperlink ref="N138" r:id="rId108"/>
+    <hyperlink ref="B139" r:id="rId109"/>
+    <hyperlink ref="L139" r:id="rId110"/>
+    <hyperlink ref="N139" r:id="rId111"/>
+    <hyperlink ref="Q139" r:id="rId112"/>
+    <hyperlink ref="B145" r:id="rId113"/>
+    <hyperlink ref="L145" r:id="rId114"/>
+    <hyperlink ref="N145" r:id="rId115"/>
+    <hyperlink ref="P145" r:id="rId116"/>
+    <hyperlink ref="R145" r:id="rId117"/>
+    <hyperlink ref="N146" r:id="rId118"/>
+    <hyperlink ref="B147" r:id="rId119"/>
+    <hyperlink ref="L147" r:id="rId120"/>
+    <hyperlink ref="N147" r:id="rId121"/>
+    <hyperlink ref="Q147" r:id="rId122"/>
+    <hyperlink ref="B151" r:id="rId123"/>
+    <hyperlink ref="L151" r:id="rId124"/>
+    <hyperlink ref="N151" r:id="rId125"/>
+    <hyperlink ref="P151" r:id="rId126"/>
+    <hyperlink ref="Q151" r:id="rId127"/>
+    <hyperlink ref="R151" r:id="rId128"/>
+    <hyperlink ref="B152" r:id="rId129"/>
+    <hyperlink ref="L152" r:id="rId130"/>
+    <hyperlink ref="N152" r:id="rId131"/>
+    <hyperlink ref="Q152" r:id="rId132"/>
+    <hyperlink ref="B155" r:id="rId133"/>
+    <hyperlink ref="L155" r:id="rId134"/>
+    <hyperlink ref="N155" r:id="rId135"/>
+    <hyperlink ref="P155" r:id="rId136"/>
+    <hyperlink ref="Q155" r:id="rId137"/>
+    <hyperlink ref="R155" r:id="rId138"/>
+    <hyperlink ref="N156" r:id="rId139"/>
+    <hyperlink ref="B157" r:id="rId140"/>
+    <hyperlink ref="L157" r:id="rId141"/>
+    <hyperlink ref="N157" r:id="rId142"/>
+    <hyperlink ref="Q157" r:id="rId143"/>
+    <hyperlink ref="B158" r:id="rId144"/>
+    <hyperlink ref="L158" r:id="rId145"/>
+    <hyperlink ref="N158" r:id="rId146"/>
+    <hyperlink ref="P158" r:id="rId147"/>
+    <hyperlink ref="Q158" r:id="rId148"/>
+    <hyperlink ref="R158" r:id="rId149"/>
+    <hyperlink ref="B159" r:id="rId150"/>
+    <hyperlink ref="L159" r:id="rId151"/>
+    <hyperlink ref="N159" r:id="rId152"/>
+    <hyperlink ref="P159" r:id="rId153"/>
+    <hyperlink ref="Q159" r:id="rId154"/>
+    <hyperlink ref="B161" r:id="rId155"/>
+    <hyperlink ref="L161" r:id="rId156"/>
+    <hyperlink ref="N161" r:id="rId157"/>
+    <hyperlink ref="P161" r:id="rId158"/>
+    <hyperlink ref="Q161" r:id="rId159"/>
+    <hyperlink ref="R161" r:id="rId160"/>
+    <hyperlink ref="B162" r:id="rId161"/>
+    <hyperlink ref="L162" r:id="rId162"/>
+    <hyperlink ref="N162" r:id="rId163"/>
+    <hyperlink ref="Q162" r:id="rId164"/>
+    <hyperlink ref="B165" r:id="rId165"/>
+    <hyperlink ref="L165" r:id="rId166"/>
+    <hyperlink ref="N165" r:id="rId167"/>
+    <hyperlink ref="P165" r:id="rId168"/>
+    <hyperlink ref="R165" r:id="rId169"/>
+    <hyperlink ref="B166" r:id="rId170"/>
+    <hyperlink ref="L166" r:id="rId171"/>
+    <hyperlink ref="N166" r:id="rId172"/>
+    <hyperlink ref="Q166" r:id="rId173"/>
+    <hyperlink ref="B172" r:id="rId174"/>
+    <hyperlink ref="L172" r:id="rId175"/>
+    <hyperlink ref="N172" r:id="rId176"/>
+    <hyperlink ref="P172" r:id="rId177"/>
+    <hyperlink ref="B178" r:id="rId178"/>
+    <hyperlink ref="L178" r:id="rId179"/>
+    <hyperlink ref="N178" r:id="rId180"/>
+    <hyperlink ref="P178" r:id="rId181"/>
+    <hyperlink ref="Q178" r:id="rId182"/>
+    <hyperlink ref="B198" r:id="rId183"/>
+    <hyperlink ref="L198" r:id="rId184"/>
+    <hyperlink ref="N198" r:id="rId185"/>
+    <hyperlink ref="P198" r:id="rId186"/>
+    <hyperlink ref="B202" r:id="rId187"/>
+    <hyperlink ref="L202" r:id="rId188"/>
+    <hyperlink ref="N202" r:id="rId189"/>
+    <hyperlink ref="P202" r:id="rId190"/>
+    <hyperlink ref="B206" r:id="rId191"/>
+    <hyperlink ref="L206" r:id="rId192"/>
+    <hyperlink ref="N206" r:id="rId193"/>
+    <hyperlink ref="P206" r:id="rId194"/>
+    <hyperlink ref="B210" r:id="rId195"/>
+    <hyperlink ref="L210" r:id="rId196"/>
+    <hyperlink ref="N210" r:id="rId197"/>
+    <hyperlink ref="P210" r:id="rId198"/>
+    <hyperlink ref="Q210" r:id="rId199"/>
+    <hyperlink ref="B212" r:id="rId200"/>
+    <hyperlink ref="L212" r:id="rId201"/>
+    <hyperlink ref="N212" r:id="rId202"/>
+    <hyperlink ref="P212" r:id="rId203"/>
+    <hyperlink ref="B216" r:id="rId204"/>
+    <hyperlink ref="L216" r:id="rId205"/>
+    <hyperlink ref="N216" r:id="rId206"/>
+    <hyperlink ref="P216" r:id="rId207"/>
+    <hyperlink ref="Q216" r:id="rId208"/>
+    <hyperlink ref="N218" r:id="rId209"/>
+    <hyperlink ref="B219" r:id="rId210"/>
+    <hyperlink ref="L219" r:id="rId211"/>
+    <hyperlink ref="N219" r:id="rId212"/>
+    <hyperlink ref="P219" r:id="rId213"/>
+    <hyperlink ref="Q219" r:id="rId214"/>
+    <hyperlink ref="B224" r:id="rId215"/>
+    <hyperlink ref="L224" r:id="rId216"/>
+    <hyperlink ref="N224" r:id="rId217"/>
+    <hyperlink ref="P224" r:id="rId218"/>
+    <hyperlink ref="Q224" r:id="rId219"/>
+    <hyperlink ref="B229" r:id="rId220"/>
+    <hyperlink ref="L229" r:id="rId221"/>
+    <hyperlink ref="N229" r:id="rId222"/>
+    <hyperlink ref="P229" r:id="rId223"/>
+    <hyperlink ref="Q229" r:id="rId224"/>
+    <hyperlink ref="R229" r:id="rId225"/>
+    <hyperlink ref="B235" r:id="rId226"/>
+    <hyperlink ref="L235" r:id="rId227"/>
+    <hyperlink ref="N235" r:id="rId228"/>
+    <hyperlink ref="P235" r:id="rId229"/>
+    <hyperlink ref="B242" r:id="rId230"/>
+    <hyperlink ref="L242" r:id="rId231"/>
+    <hyperlink ref="N242" r:id="rId232"/>
+    <hyperlink ref="P242" r:id="rId233"/>
+    <hyperlink ref="B251" r:id="rId234"/>
+    <hyperlink ref="L251" r:id="rId235"/>
+    <hyperlink ref="N251" r:id="rId236"/>
+    <hyperlink ref="P251" r:id="rId237"/>
+    <hyperlink ref="Q251" r:id="rId238"/>
+    <hyperlink ref="B257" r:id="rId239"/>
+    <hyperlink ref="L257" r:id="rId240"/>
+    <hyperlink ref="N257" r:id="rId241"/>
+    <hyperlink ref="P257" r:id="rId242"/>
+    <hyperlink ref="Q257" r:id="rId243"/>
+    <hyperlink ref="B261" r:id="rId244"/>
+    <hyperlink ref="L261" r:id="rId245"/>
+    <hyperlink ref="N261" r:id="rId246"/>
+    <hyperlink ref="B283" r:id="rId247"/>
+    <hyperlink ref="L283" r:id="rId248"/>
+    <hyperlink ref="N283" r:id="rId249"/>
+    <hyperlink ref="P283" r:id="rId250"/>
+    <hyperlink ref="Q283" r:id="rId251"/>
+    <hyperlink ref="B291" r:id="rId252"/>
+    <hyperlink ref="L291" r:id="rId253"/>
+    <hyperlink ref="N291" r:id="rId254"/>
+    <hyperlink ref="P291" r:id="rId255"/>
+    <hyperlink ref="Q291" r:id="rId256"/>
+    <hyperlink ref="B302" r:id="rId257"/>
+    <hyperlink ref="L302" r:id="rId258"/>
+    <hyperlink ref="N302" r:id="rId259"/>
+    <hyperlink ref="P302" r:id="rId260"/>
+    <hyperlink ref="Q302" r:id="rId261"/>
+    <hyperlink ref="B310" r:id="rId262"/>
+    <hyperlink ref="L310" r:id="rId263"/>
+    <hyperlink ref="N310" r:id="rId264"/>
+    <hyperlink ref="P310" r:id="rId265"/>
+    <hyperlink ref="Q310" r:id="rId266"/>
+    <hyperlink ref="B332" r:id="rId267"/>
+    <hyperlink ref="L332" r:id="rId268"/>
+    <hyperlink ref="N332" r:id="rId269"/>
+    <hyperlink ref="P332" r:id="rId270"/>
+    <hyperlink ref="B334" r:id="rId271"/>
+    <hyperlink ref="L334" r:id="rId272"/>
+    <hyperlink ref="N334" r:id="rId273"/>
+    <hyperlink ref="P334" r:id="rId274"/>
+    <hyperlink ref="Q334" r:id="rId275"/>
+    <hyperlink ref="B338" r:id="rId276"/>
+    <hyperlink ref="L338" r:id="rId277"/>
+    <hyperlink ref="N338" r:id="rId278"/>
+    <hyperlink ref="B341" r:id="rId279"/>
+    <hyperlink ref="L341" r:id="rId280"/>
+    <hyperlink ref="N341" r:id="rId281"/>
+    <hyperlink ref="P341" r:id="rId282"/>
+    <hyperlink ref="Q341" r:id="rId283"/>
+    <hyperlink ref="B343" r:id="rId284"/>
+    <hyperlink ref="L343" r:id="rId285"/>
+    <hyperlink ref="N343" r:id="rId286"/>
+    <hyperlink ref="P343" r:id="rId287"/>
+    <hyperlink ref="Q343" r:id="rId288"/>
+    <hyperlink ref="B349" r:id="rId289"/>
+    <hyperlink ref="L349" r:id="rId290"/>
+    <hyperlink ref="N349" r:id="rId291"/>
+    <hyperlink ref="P349" r:id="rId292"/>
+    <hyperlink ref="Q349" r:id="rId293"/>
+    <hyperlink ref="B350" r:id="rId294"/>
+    <hyperlink ref="L350" r:id="rId295"/>
+    <hyperlink ref="N350" r:id="rId296"/>
+    <hyperlink ref="Q350" r:id="rId297"/>
+    <hyperlink ref="B353" r:id="rId298"/>
+    <hyperlink ref="L353" r:id="rId299"/>
+    <hyperlink ref="N353" r:id="rId300"/>
+    <hyperlink ref="P353" r:id="rId301"/>
+    <hyperlink ref="Q353" r:id="rId302"/>
+    <hyperlink ref="B356" r:id="rId303"/>
+    <hyperlink ref="L356" r:id="rId304"/>
+    <hyperlink ref="N356" r:id="rId305"/>
+    <hyperlink ref="P356" r:id="rId306"/>
+    <hyperlink ref="Q356" r:id="rId307"/>
+    <hyperlink ref="B358" r:id="rId308"/>
+    <hyperlink ref="L358" r:id="rId309"/>
+    <hyperlink ref="N358" r:id="rId310"/>
+    <hyperlink ref="P358" r:id="rId311"/>
+    <hyperlink ref="Q358" r:id="rId312"/>
+    <hyperlink ref="R358" r:id="rId313"/>
+    <hyperlink ref="B397" r:id="rId314"/>
+    <hyperlink ref="L397" r:id="rId315"/>
+    <hyperlink ref="N397" r:id="rId316"/>
+    <hyperlink ref="P397" r:id="rId317"/>
+    <hyperlink ref="N399" r:id="rId318"/>
+    <hyperlink ref="B400" r:id="rId319"/>
+    <hyperlink ref="L400" r:id="rId320"/>
+    <hyperlink ref="N400" r:id="rId321"/>
+    <hyperlink ref="Q400" r:id="rId322"/>
+    <hyperlink ref="N401" r:id="rId323"/>
+    <hyperlink ref="B412" r:id="rId324"/>
+    <hyperlink ref="L412" r:id="rId325"/>
+    <hyperlink ref="N412" r:id="rId326"/>
+    <hyperlink ref="P412" r:id="rId327"/>
+    <hyperlink ref="B413" r:id="rId328"/>
+    <hyperlink ref="L413" r:id="rId329"/>
+    <hyperlink ref="N413" r:id="rId330"/>
+    <hyperlink ref="P413" r:id="rId331"/>
+    <hyperlink ref="B414" r:id="rId332"/>
+    <hyperlink ref="L414" r:id="rId333"/>
+    <hyperlink ref="N414" r:id="rId334"/>
+    <hyperlink ref="Q414" r:id="rId335"/>
+    <hyperlink ref="N416" r:id="rId336"/>
+    <hyperlink ref="B417" r:id="rId337"/>
+    <hyperlink ref="L417" r:id="rId338"/>
+    <hyperlink ref="N417" r:id="rId339"/>
+    <hyperlink ref="Q417" r:id="rId340"/>
+    <hyperlink ref="B423" r:id="rId341"/>
+    <hyperlink ref="L423" r:id="rId342"/>
+    <hyperlink ref="N423" r:id="rId343"/>
+    <hyperlink ref="P423" r:id="rId344"/>
+    <hyperlink ref="B430" r:id="rId345"/>
+    <hyperlink ref="L430" r:id="rId346"/>
+    <hyperlink ref="N430" r:id="rId347"/>
+    <hyperlink ref="P430" r:id="rId348"/>
+    <hyperlink ref="B435" r:id="rId349"/>
+    <hyperlink ref="L435" r:id="rId350"/>
+    <hyperlink ref="N435" r:id="rId351"/>
+    <hyperlink ref="P435" r:id="rId352"/>
+    <hyperlink ref="B436" r:id="rId353"/>
+    <hyperlink ref="L436" r:id="rId354"/>
+    <hyperlink ref="N436" r:id="rId355"/>
+    <hyperlink ref="P436" r:id="rId356"/>
+    <hyperlink ref="B448" r:id="rId357"/>
+    <hyperlink ref="L448" r:id="rId358"/>
+    <hyperlink ref="N448" r:id="rId359"/>
+    <hyperlink ref="P448" r:id="rId360"/>
+    <hyperlink ref="Q448" r:id="rId361"/>
+    <hyperlink ref="B465" r:id="rId362"/>
+    <hyperlink ref="L465" r:id="rId363"/>
+    <hyperlink ref="N465" r:id="rId364"/>
+    <hyperlink ref="P465" r:id="rId365"/>
+    <hyperlink ref="Q465" r:id="rId366"/>
+    <hyperlink ref="N470" r:id="rId367"/>
+    <hyperlink ref="B481" r:id="rId368"/>
+    <hyperlink ref="L481" r:id="rId369"/>
+    <hyperlink ref="N481" r:id="rId370"/>
+    <hyperlink ref="P481" r:id="rId371"/>
+    <hyperlink ref="R481" r:id="rId372"/>
+    <hyperlink ref="B487" r:id="rId373"/>
+    <hyperlink ref="L487" r:id="rId374"/>
+    <hyperlink ref="N487" r:id="rId375"/>
+    <hyperlink ref="P487" r:id="rId376"/>
+    <hyperlink ref="B489" r:id="rId377"/>
+    <hyperlink ref="L489" r:id="rId378"/>
+    <hyperlink ref="N489" r:id="rId379"/>
+    <hyperlink ref="B492" r:id="rId380"/>
+    <hyperlink ref="L492" r:id="rId381"/>
+    <hyperlink ref="N492" r:id="rId382"/>
+    <hyperlink ref="B495" r:id="rId383"/>
+    <hyperlink ref="L495" r:id="rId384"/>
+    <hyperlink ref="N495" r:id="rId385"/>
+    <hyperlink ref="P495" r:id="rId386"/>
+    <hyperlink ref="B499" r:id="rId387"/>
+    <hyperlink ref="L499" r:id="rId388"/>
+    <hyperlink ref="N499" r:id="rId389"/>
+    <hyperlink ref="P499" r:id="rId390"/>
+    <hyperlink ref="B500" r:id="rId391"/>
+    <hyperlink ref="L500" r:id="rId392"/>
+    <hyperlink ref="N500" r:id="rId393"/>
+    <hyperlink ref="P500" r:id="rId394"/>
+    <hyperlink ref="B503" r:id="rId395"/>
+    <hyperlink ref="L503" r:id="rId396"/>
+    <hyperlink ref="N503" r:id="rId397"/>
+    <hyperlink ref="P503" r:id="rId398"/>
+    <hyperlink ref="B514" r:id="rId399"/>
+    <hyperlink ref="L514" r:id="rId400"/>
+    <hyperlink ref="N514" r:id="rId401"/>
+    <hyperlink ref="P514" r:id="rId402"/>
+    <hyperlink ref="B517" r:id="rId403"/>
+    <hyperlink ref="L517" r:id="rId404"/>
+    <hyperlink ref="N517" r:id="rId405"/>
+    <hyperlink ref="P517" r:id="rId406"/>
+    <hyperlink ref="R517" r:id="rId407"/>
+    <hyperlink ref="B528" r:id="rId408"/>
+    <hyperlink ref="L528" r:id="rId409"/>
+    <hyperlink ref="N528" r:id="rId410"/>
+    <hyperlink ref="P528" r:id="rId411"/>
+    <hyperlink ref="Q528" r:id="rId412"/>
+    <hyperlink ref="R528" r:id="rId413"/>
+    <hyperlink ref="B531" r:id="rId414"/>
+    <hyperlink ref="L531" r:id="rId415"/>
+    <hyperlink ref="N531" r:id="rId416"/>
+    <hyperlink ref="P531" r:id="rId417"/>
+    <hyperlink ref="B532" r:id="rId418"/>
+    <hyperlink ref="L532" r:id="rId419"/>
+    <hyperlink ref="N532" r:id="rId420"/>
+    <hyperlink ref="Q532" r:id="rId421"/>
+    <hyperlink ref="B534" r:id="rId422"/>
+    <hyperlink ref="L534" r:id="rId423"/>
+    <hyperlink ref="N534" r:id="rId424"/>
+    <hyperlink ref="P534" r:id="rId425"/>
+    <hyperlink ref="B536" r:id="rId426"/>
+    <hyperlink ref="L536" r:id="rId427"/>
+    <hyperlink ref="N536" r:id="rId428"/>
+    <hyperlink ref="P536" r:id="rId429"/>
+    <hyperlink ref="B537" r:id="rId430"/>
+    <hyperlink ref="L537" r:id="rId431"/>
+    <hyperlink ref="N537" r:id="rId432"/>
+    <hyperlink ref="P537" r:id="rId433"/>
+    <hyperlink ref="B538" r:id="rId434"/>
+    <hyperlink ref="L538" r:id="rId435"/>
+    <hyperlink ref="N538" r:id="rId436"/>
+    <hyperlink ref="P538" r:id="rId437"/>
+    <hyperlink ref="Q538" r:id="rId438"/>
+    <hyperlink ref="B539" r:id="rId439"/>
+    <hyperlink ref="L539" r:id="rId440"/>
+    <hyperlink ref="N539" r:id="rId441"/>
+    <hyperlink ref="Q539" r:id="rId442"/>
+    <hyperlink ref="B540" r:id="rId443"/>
+    <hyperlink ref="L540" r:id="rId444"/>
+    <hyperlink ref="N540" r:id="rId445"/>
+    <hyperlink ref="Q540" r:id="rId446"/>
+    <hyperlink ref="B551" r:id="rId447"/>
+    <hyperlink ref="L551" r:id="rId448"/>
+    <hyperlink ref="N551" r:id="rId449"/>
+    <hyperlink ref="P551" r:id="rId450"/>
+    <hyperlink ref="Q551" r:id="rId451"/>
+    <hyperlink ref="N559" r:id="rId452"/>
+    <hyperlink ref="B560" r:id="rId453"/>
+    <hyperlink ref="L560" r:id="rId454"/>
+    <hyperlink ref="N560" r:id="rId455"/>
+    <hyperlink ref="P560" r:id="rId456"/>
+    <hyperlink ref="Q560" r:id="rId457"/>
+    <hyperlink ref="B567" r:id="rId458"/>
+    <hyperlink ref="L567" r:id="rId459"/>
+    <hyperlink ref="N567" r:id="rId460"/>
+    <hyperlink ref="P567" r:id="rId461"/>
+    <hyperlink ref="Q567" r:id="rId462"/>
+    <hyperlink ref="B568" r:id="rId463"/>
+    <hyperlink ref="L568" r:id="rId464"/>
+    <hyperlink ref="N568" r:id="rId465"/>
+    <hyperlink ref="Q568" r:id="rId466"/>
+    <hyperlink ref="B569" r:id="rId467"/>
+    <hyperlink ref="L569" r:id="rId468"/>
+    <hyperlink ref="N569" r:id="rId469"/>
+    <hyperlink ref="Q569" r:id="rId470"/>
+    <hyperlink ref="B590" r:id="rId471"/>
+    <hyperlink ref="L590" r:id="rId472"/>
+    <hyperlink ref="N590" r:id="rId473"/>
+    <hyperlink ref="P590" r:id="rId474"/>
+    <hyperlink ref="R590" r:id="rId475"/>
+    <hyperlink ref="B600" r:id="rId476"/>
+    <hyperlink ref="L600" r:id="rId477"/>
+    <hyperlink ref="N600" r:id="rId478"/>
+    <hyperlink ref="P600" r:id="rId479"/>
+    <hyperlink ref="Q600" r:id="rId480"/>
+    <hyperlink ref="B626" r:id="rId481"/>
+    <hyperlink ref="L626" r:id="rId482"/>
+    <hyperlink ref="N626" r:id="rId483"/>
+    <hyperlink ref="P626" r:id="rId484"/>
+    <hyperlink ref="Q626" r:id="rId485"/>
+    <hyperlink ref="B627" r:id="rId486"/>
+    <hyperlink ref="L627" r:id="rId487"/>
+    <hyperlink ref="N627" r:id="rId488"/>
+    <hyperlink ref="P627" r:id="rId489"/>
+    <hyperlink ref="Q627" r:id="rId490"/>
+    <hyperlink ref="B636" r:id="rId491"/>
+    <hyperlink ref="N636" r:id="rId492"/>
+    <hyperlink ref="P636" r:id="rId493"/>
+    <hyperlink ref="B645" r:id="rId494"/>
+    <hyperlink ref="L645" r:id="rId495"/>
+    <hyperlink ref="N645" r:id="rId496"/>
+    <hyperlink ref="P645" r:id="rId497"/>
+    <hyperlink ref="B652" r:id="rId498"/>
+    <hyperlink ref="L652" r:id="rId499"/>
+    <hyperlink ref="N652" r:id="rId500"/>
   </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -463,7 +463,7 @@
   </si>
   <si>
     <t xml:space="preserve">Filing/Order Docket No. RD26-4-000
-Replaces BAL-007-1 - Errata</t>
+Replaces BAL-007-1 (Errata)</t>
   </si>
   <si>
     <t>BAL-502-RF-03</t>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -230,7 +230,8 @@
     <t>BAL-002-WECC-3</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. ​RM19-20-000</t>
+    <t xml:space="preserve">Filing/Order Docket No. ​RM19-20-000
+FERC approved the retirement of the standard 4/14/2026 - RD26-5-000</t>
   </si>
   <si>
     <t>BAL-003-0</t>
@@ -6511,7 +6512,7 @@
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="41.0641" customHeight="1">
+    <row r="18" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
@@ -6540,11 +6541,13 @@
         <v>44375</v>
       </c>
       <c r="J18" s="7"/>
-      <c r="K18" s="9"/>
+      <c r="K18" s="9">
+        <v>46204</v>
+      </c>
       <c r="L18" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="10" t="s">
         <v>72</v>
       </c>
       <c r="N18" s="16" t="s">

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -5371,7 +5371,8 @@
     <t>Establish Transmission system planning performance requirements to develop a Bulk Power System (BPS) that will operate reliably during extreme heat and extreme cold temperature events.</t>
   </si>
   <si>
-    <t>Filing/Order Docket No. RD25-4-000</t>
+    <t xml:space="preserve">Filing/Order Docket No. RD25-4-000
+See the bottom of the TPL-008-1 Reliability Standards page for related documents</t>
   </si>
   <si>
     <t>Project 2023-07</t>
@@ -32314,7 +32315,7 @@
       </c>
       <c r="R626" s="7"/>
     </row>
-    <row r="627" s="1" customFormat="1" ht="52.2634" customHeight="1">
+    <row r="627" s="1" customFormat="1" ht="62.9294" customHeight="1">
       <c r="A627" s="11" t="s">
         <v>30</v>
       </c>
@@ -32349,7 +32350,7 @@
       <c r="L627" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M627" s="11" t="s">
+      <c r="M627" s="17" t="s">
         <v>1729</v>
       </c>
       <c r="N627" s="18" t="s">

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4020" uniqueCount="1793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="1793">
   <si>
     <t>Status</t>
   </si>
@@ -28318,7 +28318,9 @@
         <v>1509</v>
       </c>
       <c r="O532" s="7"/>
-      <c r="P532" s="7"/>
+      <c r="P532" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q532" s="15" t="s">
         <v>16</v>
       </c>
@@ -28648,7 +28650,9 @@
         <v>1509</v>
       </c>
       <c r="O539" s="12"/>
-      <c r="P539" s="12"/>
+      <c r="P539" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q539" s="19" t="s">
         <v>16</v>
       </c>
@@ -28696,7 +28700,9 @@
         <v>1536</v>
       </c>
       <c r="O540" s="7"/>
-      <c r="P540" s="7"/>
+      <c r="P540" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q540" s="15" t="s">
         <v>16</v>
       </c>
@@ -29888,7 +29894,9 @@
         <v>143</v>
       </c>
       <c r="O568" s="7"/>
-      <c r="P568" s="7"/>
+      <c r="P568" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q568" s="15" t="s">
         <v>16</v>
       </c>
@@ -33940,86 +33948,90 @@
     <hyperlink ref="B532" r:id="rId418"/>
     <hyperlink ref="L532" r:id="rId419"/>
     <hyperlink ref="N532" r:id="rId420"/>
-    <hyperlink ref="Q532" r:id="rId421"/>
-    <hyperlink ref="B534" r:id="rId422"/>
-    <hyperlink ref="L534" r:id="rId423"/>
-    <hyperlink ref="N534" r:id="rId424"/>
-    <hyperlink ref="P534" r:id="rId425"/>
-    <hyperlink ref="B536" r:id="rId426"/>
-    <hyperlink ref="L536" r:id="rId427"/>
-    <hyperlink ref="N536" r:id="rId428"/>
-    <hyperlink ref="P536" r:id="rId429"/>
-    <hyperlink ref="B537" r:id="rId430"/>
-    <hyperlink ref="L537" r:id="rId431"/>
-    <hyperlink ref="N537" r:id="rId432"/>
-    <hyperlink ref="P537" r:id="rId433"/>
-    <hyperlink ref="B538" r:id="rId434"/>
-    <hyperlink ref="L538" r:id="rId435"/>
-    <hyperlink ref="N538" r:id="rId436"/>
-    <hyperlink ref="P538" r:id="rId437"/>
-    <hyperlink ref="Q538" r:id="rId438"/>
-    <hyperlink ref="B539" r:id="rId439"/>
-    <hyperlink ref="L539" r:id="rId440"/>
-    <hyperlink ref="N539" r:id="rId441"/>
-    <hyperlink ref="Q539" r:id="rId442"/>
-    <hyperlink ref="B540" r:id="rId443"/>
-    <hyperlink ref="L540" r:id="rId444"/>
-    <hyperlink ref="N540" r:id="rId445"/>
-    <hyperlink ref="Q540" r:id="rId446"/>
-    <hyperlink ref="B551" r:id="rId447"/>
-    <hyperlink ref="L551" r:id="rId448"/>
-    <hyperlink ref="N551" r:id="rId449"/>
-    <hyperlink ref="P551" r:id="rId450"/>
-    <hyperlink ref="Q551" r:id="rId451"/>
-    <hyperlink ref="N559" r:id="rId452"/>
-    <hyperlink ref="B560" r:id="rId453"/>
-    <hyperlink ref="L560" r:id="rId454"/>
-    <hyperlink ref="N560" r:id="rId455"/>
-    <hyperlink ref="P560" r:id="rId456"/>
-    <hyperlink ref="Q560" r:id="rId457"/>
-    <hyperlink ref="B567" r:id="rId458"/>
-    <hyperlink ref="L567" r:id="rId459"/>
-    <hyperlink ref="N567" r:id="rId460"/>
-    <hyperlink ref="P567" r:id="rId461"/>
-    <hyperlink ref="Q567" r:id="rId462"/>
-    <hyperlink ref="B568" r:id="rId463"/>
-    <hyperlink ref="L568" r:id="rId464"/>
-    <hyperlink ref="N568" r:id="rId465"/>
-    <hyperlink ref="Q568" r:id="rId466"/>
-    <hyperlink ref="B569" r:id="rId467"/>
-    <hyperlink ref="L569" r:id="rId468"/>
-    <hyperlink ref="N569" r:id="rId469"/>
-    <hyperlink ref="Q569" r:id="rId470"/>
-    <hyperlink ref="B590" r:id="rId471"/>
-    <hyperlink ref="L590" r:id="rId472"/>
-    <hyperlink ref="N590" r:id="rId473"/>
-    <hyperlink ref="P590" r:id="rId474"/>
-    <hyperlink ref="R590" r:id="rId475"/>
-    <hyperlink ref="B600" r:id="rId476"/>
-    <hyperlink ref="L600" r:id="rId477"/>
-    <hyperlink ref="N600" r:id="rId478"/>
-    <hyperlink ref="P600" r:id="rId479"/>
-    <hyperlink ref="Q600" r:id="rId480"/>
-    <hyperlink ref="B626" r:id="rId481"/>
-    <hyperlink ref="L626" r:id="rId482"/>
-    <hyperlink ref="N626" r:id="rId483"/>
-    <hyperlink ref="P626" r:id="rId484"/>
-    <hyperlink ref="Q626" r:id="rId485"/>
-    <hyperlink ref="B627" r:id="rId486"/>
-    <hyperlink ref="L627" r:id="rId487"/>
-    <hyperlink ref="N627" r:id="rId488"/>
-    <hyperlink ref="P627" r:id="rId489"/>
-    <hyperlink ref="Q627" r:id="rId490"/>
-    <hyperlink ref="B636" r:id="rId491"/>
-    <hyperlink ref="N636" r:id="rId492"/>
-    <hyperlink ref="P636" r:id="rId493"/>
-    <hyperlink ref="B645" r:id="rId494"/>
-    <hyperlink ref="L645" r:id="rId495"/>
-    <hyperlink ref="N645" r:id="rId496"/>
-    <hyperlink ref="P645" r:id="rId497"/>
-    <hyperlink ref="B652" r:id="rId498"/>
-    <hyperlink ref="L652" r:id="rId499"/>
-    <hyperlink ref="N652" r:id="rId500"/>
+    <hyperlink ref="P532" r:id="rId421"/>
+    <hyperlink ref="Q532" r:id="rId422"/>
+    <hyperlink ref="B534" r:id="rId423"/>
+    <hyperlink ref="L534" r:id="rId424"/>
+    <hyperlink ref="N534" r:id="rId425"/>
+    <hyperlink ref="P534" r:id="rId426"/>
+    <hyperlink ref="B536" r:id="rId427"/>
+    <hyperlink ref="L536" r:id="rId428"/>
+    <hyperlink ref="N536" r:id="rId429"/>
+    <hyperlink ref="P536" r:id="rId430"/>
+    <hyperlink ref="B537" r:id="rId431"/>
+    <hyperlink ref="L537" r:id="rId432"/>
+    <hyperlink ref="N537" r:id="rId433"/>
+    <hyperlink ref="P537" r:id="rId434"/>
+    <hyperlink ref="B538" r:id="rId435"/>
+    <hyperlink ref="L538" r:id="rId436"/>
+    <hyperlink ref="N538" r:id="rId437"/>
+    <hyperlink ref="P538" r:id="rId438"/>
+    <hyperlink ref="Q538" r:id="rId439"/>
+    <hyperlink ref="B539" r:id="rId440"/>
+    <hyperlink ref="L539" r:id="rId441"/>
+    <hyperlink ref="N539" r:id="rId442"/>
+    <hyperlink ref="P539" r:id="rId443"/>
+    <hyperlink ref="Q539" r:id="rId444"/>
+    <hyperlink ref="B540" r:id="rId445"/>
+    <hyperlink ref="L540" r:id="rId446"/>
+    <hyperlink ref="N540" r:id="rId447"/>
+    <hyperlink ref="P540" r:id="rId448"/>
+    <hyperlink ref="Q540" r:id="rId449"/>
+    <hyperlink ref="B551" r:id="rId450"/>
+    <hyperlink ref="L551" r:id="rId451"/>
+    <hyperlink ref="N551" r:id="rId452"/>
+    <hyperlink ref="P551" r:id="rId453"/>
+    <hyperlink ref="Q551" r:id="rId454"/>
+    <hyperlink ref="N559" r:id="rId455"/>
+    <hyperlink ref="B560" r:id="rId456"/>
+    <hyperlink ref="L560" r:id="rId457"/>
+    <hyperlink ref="N560" r:id="rId458"/>
+    <hyperlink ref="P560" r:id="rId459"/>
+    <hyperlink ref="Q560" r:id="rId460"/>
+    <hyperlink ref="B567" r:id="rId461"/>
+    <hyperlink ref="L567" r:id="rId462"/>
+    <hyperlink ref="N567" r:id="rId463"/>
+    <hyperlink ref="P567" r:id="rId464"/>
+    <hyperlink ref="Q567" r:id="rId465"/>
+    <hyperlink ref="B568" r:id="rId466"/>
+    <hyperlink ref="L568" r:id="rId467"/>
+    <hyperlink ref="N568" r:id="rId468"/>
+    <hyperlink ref="P568" r:id="rId469"/>
+    <hyperlink ref="Q568" r:id="rId470"/>
+    <hyperlink ref="B569" r:id="rId471"/>
+    <hyperlink ref="L569" r:id="rId472"/>
+    <hyperlink ref="N569" r:id="rId473"/>
+    <hyperlink ref="Q569" r:id="rId474"/>
+    <hyperlink ref="B590" r:id="rId475"/>
+    <hyperlink ref="L590" r:id="rId476"/>
+    <hyperlink ref="N590" r:id="rId477"/>
+    <hyperlink ref="P590" r:id="rId478"/>
+    <hyperlink ref="R590" r:id="rId479"/>
+    <hyperlink ref="B600" r:id="rId480"/>
+    <hyperlink ref="L600" r:id="rId481"/>
+    <hyperlink ref="N600" r:id="rId482"/>
+    <hyperlink ref="P600" r:id="rId483"/>
+    <hyperlink ref="Q600" r:id="rId484"/>
+    <hyperlink ref="B626" r:id="rId485"/>
+    <hyperlink ref="L626" r:id="rId486"/>
+    <hyperlink ref="N626" r:id="rId487"/>
+    <hyperlink ref="P626" r:id="rId488"/>
+    <hyperlink ref="Q626" r:id="rId489"/>
+    <hyperlink ref="B627" r:id="rId490"/>
+    <hyperlink ref="L627" r:id="rId491"/>
+    <hyperlink ref="N627" r:id="rId492"/>
+    <hyperlink ref="P627" r:id="rId493"/>
+    <hyperlink ref="Q627" r:id="rId494"/>
+    <hyperlink ref="B636" r:id="rId495"/>
+    <hyperlink ref="N636" r:id="rId496"/>
+    <hyperlink ref="P636" r:id="rId497"/>
+    <hyperlink ref="B645" r:id="rId498"/>
+    <hyperlink ref="L645" r:id="rId499"/>
+    <hyperlink ref="N645" r:id="rId500"/>
+    <hyperlink ref="P645" r:id="rId501"/>
+    <hyperlink ref="B652" r:id="rId502"/>
+    <hyperlink ref="L652" r:id="rId503"/>
+    <hyperlink ref="N652" r:id="rId504"/>
   </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="1793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="1793">
   <si>
     <t>Status</t>
   </si>
@@ -22656,7 +22656,9 @@
         <v>1135</v>
       </c>
       <c r="O400" s="7"/>
-      <c r="P400" s="7"/>
+      <c r="P400" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q400" s="15" t="s">
         <v>16</v>
       </c>
@@ -33849,189 +33851,190 @@
     <hyperlink ref="B400" r:id="rId319"/>
     <hyperlink ref="L400" r:id="rId320"/>
     <hyperlink ref="N400" r:id="rId321"/>
-    <hyperlink ref="Q400" r:id="rId322"/>
-    <hyperlink ref="N401" r:id="rId323"/>
-    <hyperlink ref="B412" r:id="rId324"/>
-    <hyperlink ref="L412" r:id="rId325"/>
-    <hyperlink ref="N412" r:id="rId326"/>
-    <hyperlink ref="P412" r:id="rId327"/>
-    <hyperlink ref="B413" r:id="rId328"/>
-    <hyperlink ref="L413" r:id="rId329"/>
-    <hyperlink ref="N413" r:id="rId330"/>
-    <hyperlink ref="P413" r:id="rId331"/>
-    <hyperlink ref="B414" r:id="rId332"/>
-    <hyperlink ref="L414" r:id="rId333"/>
-    <hyperlink ref="N414" r:id="rId334"/>
-    <hyperlink ref="Q414" r:id="rId335"/>
-    <hyperlink ref="N416" r:id="rId336"/>
-    <hyperlink ref="B417" r:id="rId337"/>
-    <hyperlink ref="L417" r:id="rId338"/>
-    <hyperlink ref="N417" r:id="rId339"/>
-    <hyperlink ref="Q417" r:id="rId340"/>
-    <hyperlink ref="B423" r:id="rId341"/>
-    <hyperlink ref="L423" r:id="rId342"/>
-    <hyperlink ref="N423" r:id="rId343"/>
-    <hyperlink ref="P423" r:id="rId344"/>
-    <hyperlink ref="B430" r:id="rId345"/>
-    <hyperlink ref="L430" r:id="rId346"/>
-    <hyperlink ref="N430" r:id="rId347"/>
-    <hyperlink ref="P430" r:id="rId348"/>
-    <hyperlink ref="B435" r:id="rId349"/>
-    <hyperlink ref="L435" r:id="rId350"/>
-    <hyperlink ref="N435" r:id="rId351"/>
-    <hyperlink ref="P435" r:id="rId352"/>
-    <hyperlink ref="B436" r:id="rId353"/>
-    <hyperlink ref="L436" r:id="rId354"/>
-    <hyperlink ref="N436" r:id="rId355"/>
-    <hyperlink ref="P436" r:id="rId356"/>
-    <hyperlink ref="B448" r:id="rId357"/>
-    <hyperlink ref="L448" r:id="rId358"/>
-    <hyperlink ref="N448" r:id="rId359"/>
-    <hyperlink ref="P448" r:id="rId360"/>
-    <hyperlink ref="Q448" r:id="rId361"/>
-    <hyperlink ref="B465" r:id="rId362"/>
-    <hyperlink ref="L465" r:id="rId363"/>
-    <hyperlink ref="N465" r:id="rId364"/>
-    <hyperlink ref="P465" r:id="rId365"/>
-    <hyperlink ref="Q465" r:id="rId366"/>
-    <hyperlink ref="N470" r:id="rId367"/>
-    <hyperlink ref="B481" r:id="rId368"/>
-    <hyperlink ref="L481" r:id="rId369"/>
-    <hyperlink ref="N481" r:id="rId370"/>
-    <hyperlink ref="P481" r:id="rId371"/>
-    <hyperlink ref="R481" r:id="rId372"/>
-    <hyperlink ref="B487" r:id="rId373"/>
-    <hyperlink ref="L487" r:id="rId374"/>
-    <hyperlink ref="N487" r:id="rId375"/>
-    <hyperlink ref="P487" r:id="rId376"/>
-    <hyperlink ref="B489" r:id="rId377"/>
-    <hyperlink ref="L489" r:id="rId378"/>
-    <hyperlink ref="N489" r:id="rId379"/>
-    <hyperlink ref="B492" r:id="rId380"/>
-    <hyperlink ref="L492" r:id="rId381"/>
-    <hyperlink ref="N492" r:id="rId382"/>
-    <hyperlink ref="B495" r:id="rId383"/>
-    <hyperlink ref="L495" r:id="rId384"/>
-    <hyperlink ref="N495" r:id="rId385"/>
-    <hyperlink ref="P495" r:id="rId386"/>
-    <hyperlink ref="B499" r:id="rId387"/>
-    <hyperlink ref="L499" r:id="rId388"/>
-    <hyperlink ref="N499" r:id="rId389"/>
-    <hyperlink ref="P499" r:id="rId390"/>
-    <hyperlink ref="B500" r:id="rId391"/>
-    <hyperlink ref="L500" r:id="rId392"/>
-    <hyperlink ref="N500" r:id="rId393"/>
-    <hyperlink ref="P500" r:id="rId394"/>
-    <hyperlink ref="B503" r:id="rId395"/>
-    <hyperlink ref="L503" r:id="rId396"/>
-    <hyperlink ref="N503" r:id="rId397"/>
-    <hyperlink ref="P503" r:id="rId398"/>
-    <hyperlink ref="B514" r:id="rId399"/>
-    <hyperlink ref="L514" r:id="rId400"/>
-    <hyperlink ref="N514" r:id="rId401"/>
-    <hyperlink ref="P514" r:id="rId402"/>
-    <hyperlink ref="B517" r:id="rId403"/>
-    <hyperlink ref="L517" r:id="rId404"/>
-    <hyperlink ref="N517" r:id="rId405"/>
-    <hyperlink ref="P517" r:id="rId406"/>
-    <hyperlink ref="R517" r:id="rId407"/>
-    <hyperlink ref="B528" r:id="rId408"/>
-    <hyperlink ref="L528" r:id="rId409"/>
-    <hyperlink ref="N528" r:id="rId410"/>
-    <hyperlink ref="P528" r:id="rId411"/>
-    <hyperlink ref="Q528" r:id="rId412"/>
-    <hyperlink ref="R528" r:id="rId413"/>
-    <hyperlink ref="B531" r:id="rId414"/>
-    <hyperlink ref="L531" r:id="rId415"/>
-    <hyperlink ref="N531" r:id="rId416"/>
-    <hyperlink ref="P531" r:id="rId417"/>
-    <hyperlink ref="B532" r:id="rId418"/>
-    <hyperlink ref="L532" r:id="rId419"/>
-    <hyperlink ref="N532" r:id="rId420"/>
-    <hyperlink ref="P532" r:id="rId421"/>
-    <hyperlink ref="Q532" r:id="rId422"/>
-    <hyperlink ref="B534" r:id="rId423"/>
-    <hyperlink ref="L534" r:id="rId424"/>
-    <hyperlink ref="N534" r:id="rId425"/>
-    <hyperlink ref="P534" r:id="rId426"/>
-    <hyperlink ref="B536" r:id="rId427"/>
-    <hyperlink ref="L536" r:id="rId428"/>
-    <hyperlink ref="N536" r:id="rId429"/>
-    <hyperlink ref="P536" r:id="rId430"/>
-    <hyperlink ref="B537" r:id="rId431"/>
-    <hyperlink ref="L537" r:id="rId432"/>
-    <hyperlink ref="N537" r:id="rId433"/>
-    <hyperlink ref="P537" r:id="rId434"/>
-    <hyperlink ref="B538" r:id="rId435"/>
-    <hyperlink ref="L538" r:id="rId436"/>
-    <hyperlink ref="N538" r:id="rId437"/>
-    <hyperlink ref="P538" r:id="rId438"/>
-    <hyperlink ref="Q538" r:id="rId439"/>
-    <hyperlink ref="B539" r:id="rId440"/>
-    <hyperlink ref="L539" r:id="rId441"/>
-    <hyperlink ref="N539" r:id="rId442"/>
-    <hyperlink ref="P539" r:id="rId443"/>
-    <hyperlink ref="Q539" r:id="rId444"/>
-    <hyperlink ref="B540" r:id="rId445"/>
-    <hyperlink ref="L540" r:id="rId446"/>
-    <hyperlink ref="N540" r:id="rId447"/>
-    <hyperlink ref="P540" r:id="rId448"/>
-    <hyperlink ref="Q540" r:id="rId449"/>
-    <hyperlink ref="B551" r:id="rId450"/>
-    <hyperlink ref="L551" r:id="rId451"/>
-    <hyperlink ref="N551" r:id="rId452"/>
-    <hyperlink ref="P551" r:id="rId453"/>
-    <hyperlink ref="Q551" r:id="rId454"/>
-    <hyperlink ref="N559" r:id="rId455"/>
-    <hyperlink ref="B560" r:id="rId456"/>
-    <hyperlink ref="L560" r:id="rId457"/>
-    <hyperlink ref="N560" r:id="rId458"/>
-    <hyperlink ref="P560" r:id="rId459"/>
-    <hyperlink ref="Q560" r:id="rId460"/>
-    <hyperlink ref="B567" r:id="rId461"/>
-    <hyperlink ref="L567" r:id="rId462"/>
-    <hyperlink ref="N567" r:id="rId463"/>
-    <hyperlink ref="P567" r:id="rId464"/>
-    <hyperlink ref="Q567" r:id="rId465"/>
-    <hyperlink ref="B568" r:id="rId466"/>
-    <hyperlink ref="L568" r:id="rId467"/>
-    <hyperlink ref="N568" r:id="rId468"/>
-    <hyperlink ref="P568" r:id="rId469"/>
-    <hyperlink ref="Q568" r:id="rId470"/>
-    <hyperlink ref="B569" r:id="rId471"/>
-    <hyperlink ref="L569" r:id="rId472"/>
-    <hyperlink ref="N569" r:id="rId473"/>
-    <hyperlink ref="Q569" r:id="rId474"/>
-    <hyperlink ref="B590" r:id="rId475"/>
-    <hyperlink ref="L590" r:id="rId476"/>
-    <hyperlink ref="N590" r:id="rId477"/>
-    <hyperlink ref="P590" r:id="rId478"/>
-    <hyperlink ref="R590" r:id="rId479"/>
-    <hyperlink ref="B600" r:id="rId480"/>
-    <hyperlink ref="L600" r:id="rId481"/>
-    <hyperlink ref="N600" r:id="rId482"/>
-    <hyperlink ref="P600" r:id="rId483"/>
-    <hyperlink ref="Q600" r:id="rId484"/>
-    <hyperlink ref="B626" r:id="rId485"/>
-    <hyperlink ref="L626" r:id="rId486"/>
-    <hyperlink ref="N626" r:id="rId487"/>
-    <hyperlink ref="P626" r:id="rId488"/>
-    <hyperlink ref="Q626" r:id="rId489"/>
-    <hyperlink ref="B627" r:id="rId490"/>
-    <hyperlink ref="L627" r:id="rId491"/>
-    <hyperlink ref="N627" r:id="rId492"/>
-    <hyperlink ref="P627" r:id="rId493"/>
-    <hyperlink ref="Q627" r:id="rId494"/>
-    <hyperlink ref="B636" r:id="rId495"/>
-    <hyperlink ref="N636" r:id="rId496"/>
-    <hyperlink ref="P636" r:id="rId497"/>
-    <hyperlink ref="B645" r:id="rId498"/>
-    <hyperlink ref="L645" r:id="rId499"/>
-    <hyperlink ref="N645" r:id="rId500"/>
-    <hyperlink ref="P645" r:id="rId501"/>
-    <hyperlink ref="B652" r:id="rId502"/>
-    <hyperlink ref="L652" r:id="rId503"/>
-    <hyperlink ref="N652" r:id="rId504"/>
+    <hyperlink ref="P400" r:id="rId322"/>
+    <hyperlink ref="Q400" r:id="rId323"/>
+    <hyperlink ref="N401" r:id="rId324"/>
+    <hyperlink ref="B412" r:id="rId325"/>
+    <hyperlink ref="L412" r:id="rId326"/>
+    <hyperlink ref="N412" r:id="rId327"/>
+    <hyperlink ref="P412" r:id="rId328"/>
+    <hyperlink ref="B413" r:id="rId329"/>
+    <hyperlink ref="L413" r:id="rId330"/>
+    <hyperlink ref="N413" r:id="rId331"/>
+    <hyperlink ref="P413" r:id="rId332"/>
+    <hyperlink ref="B414" r:id="rId333"/>
+    <hyperlink ref="L414" r:id="rId334"/>
+    <hyperlink ref="N414" r:id="rId335"/>
+    <hyperlink ref="Q414" r:id="rId336"/>
+    <hyperlink ref="N416" r:id="rId337"/>
+    <hyperlink ref="B417" r:id="rId338"/>
+    <hyperlink ref="L417" r:id="rId339"/>
+    <hyperlink ref="N417" r:id="rId340"/>
+    <hyperlink ref="Q417" r:id="rId341"/>
+    <hyperlink ref="B423" r:id="rId342"/>
+    <hyperlink ref="L423" r:id="rId343"/>
+    <hyperlink ref="N423" r:id="rId344"/>
+    <hyperlink ref="P423" r:id="rId345"/>
+    <hyperlink ref="B430" r:id="rId346"/>
+    <hyperlink ref="L430" r:id="rId347"/>
+    <hyperlink ref="N430" r:id="rId348"/>
+    <hyperlink ref="P430" r:id="rId349"/>
+    <hyperlink ref="B435" r:id="rId350"/>
+    <hyperlink ref="L435" r:id="rId351"/>
+    <hyperlink ref="N435" r:id="rId352"/>
+    <hyperlink ref="P435" r:id="rId353"/>
+    <hyperlink ref="B436" r:id="rId354"/>
+    <hyperlink ref="L436" r:id="rId355"/>
+    <hyperlink ref="N436" r:id="rId356"/>
+    <hyperlink ref="P436" r:id="rId357"/>
+    <hyperlink ref="B448" r:id="rId358"/>
+    <hyperlink ref="L448" r:id="rId359"/>
+    <hyperlink ref="N448" r:id="rId360"/>
+    <hyperlink ref="P448" r:id="rId361"/>
+    <hyperlink ref="Q448" r:id="rId362"/>
+    <hyperlink ref="B465" r:id="rId363"/>
+    <hyperlink ref="L465" r:id="rId364"/>
+    <hyperlink ref="N465" r:id="rId365"/>
+    <hyperlink ref="P465" r:id="rId366"/>
+    <hyperlink ref="Q465" r:id="rId367"/>
+    <hyperlink ref="N470" r:id="rId368"/>
+    <hyperlink ref="B481" r:id="rId369"/>
+    <hyperlink ref="L481" r:id="rId370"/>
+    <hyperlink ref="N481" r:id="rId371"/>
+    <hyperlink ref="P481" r:id="rId372"/>
+    <hyperlink ref="R481" r:id="rId373"/>
+    <hyperlink ref="B487" r:id="rId374"/>
+    <hyperlink ref="L487" r:id="rId375"/>
+    <hyperlink ref="N487" r:id="rId376"/>
+    <hyperlink ref="P487" r:id="rId377"/>
+    <hyperlink ref="B489" r:id="rId378"/>
+    <hyperlink ref="L489" r:id="rId379"/>
+    <hyperlink ref="N489" r:id="rId380"/>
+    <hyperlink ref="B492" r:id="rId381"/>
+    <hyperlink ref="L492" r:id="rId382"/>
+    <hyperlink ref="N492" r:id="rId383"/>
+    <hyperlink ref="B495" r:id="rId384"/>
+    <hyperlink ref="L495" r:id="rId385"/>
+    <hyperlink ref="N495" r:id="rId386"/>
+    <hyperlink ref="P495" r:id="rId387"/>
+    <hyperlink ref="B499" r:id="rId388"/>
+    <hyperlink ref="L499" r:id="rId389"/>
+    <hyperlink ref="N499" r:id="rId390"/>
+    <hyperlink ref="P499" r:id="rId391"/>
+    <hyperlink ref="B500" r:id="rId392"/>
+    <hyperlink ref="L500" r:id="rId393"/>
+    <hyperlink ref="N500" r:id="rId394"/>
+    <hyperlink ref="P500" r:id="rId395"/>
+    <hyperlink ref="B503" r:id="rId396"/>
+    <hyperlink ref="L503" r:id="rId397"/>
+    <hyperlink ref="N503" r:id="rId398"/>
+    <hyperlink ref="P503" r:id="rId399"/>
+    <hyperlink ref="B514" r:id="rId400"/>
+    <hyperlink ref="L514" r:id="rId401"/>
+    <hyperlink ref="N514" r:id="rId402"/>
+    <hyperlink ref="P514" r:id="rId403"/>
+    <hyperlink ref="B517" r:id="rId404"/>
+    <hyperlink ref="L517" r:id="rId405"/>
+    <hyperlink ref="N517" r:id="rId406"/>
+    <hyperlink ref="P517" r:id="rId407"/>
+    <hyperlink ref="R517" r:id="rId408"/>
+    <hyperlink ref="B528" r:id="rId409"/>
+    <hyperlink ref="L528" r:id="rId410"/>
+    <hyperlink ref="N528" r:id="rId411"/>
+    <hyperlink ref="P528" r:id="rId412"/>
+    <hyperlink ref="Q528" r:id="rId413"/>
+    <hyperlink ref="R528" r:id="rId414"/>
+    <hyperlink ref="B531" r:id="rId415"/>
+    <hyperlink ref="L531" r:id="rId416"/>
+    <hyperlink ref="N531" r:id="rId417"/>
+    <hyperlink ref="P531" r:id="rId418"/>
+    <hyperlink ref="B532" r:id="rId419"/>
+    <hyperlink ref="L532" r:id="rId420"/>
+    <hyperlink ref="N532" r:id="rId421"/>
+    <hyperlink ref="P532" r:id="rId422"/>
+    <hyperlink ref="Q532" r:id="rId423"/>
+    <hyperlink ref="B534" r:id="rId424"/>
+    <hyperlink ref="L534" r:id="rId425"/>
+    <hyperlink ref="N534" r:id="rId426"/>
+    <hyperlink ref="P534" r:id="rId427"/>
+    <hyperlink ref="B536" r:id="rId428"/>
+    <hyperlink ref="L536" r:id="rId429"/>
+    <hyperlink ref="N536" r:id="rId430"/>
+    <hyperlink ref="P536" r:id="rId431"/>
+    <hyperlink ref="B537" r:id="rId432"/>
+    <hyperlink ref="L537" r:id="rId433"/>
+    <hyperlink ref="N537" r:id="rId434"/>
+    <hyperlink ref="P537" r:id="rId435"/>
+    <hyperlink ref="B538" r:id="rId436"/>
+    <hyperlink ref="L538" r:id="rId437"/>
+    <hyperlink ref="N538" r:id="rId438"/>
+    <hyperlink ref="P538" r:id="rId439"/>
+    <hyperlink ref="Q538" r:id="rId440"/>
+    <hyperlink ref="B539" r:id="rId441"/>
+    <hyperlink ref="L539" r:id="rId442"/>
+    <hyperlink ref="N539" r:id="rId443"/>
+    <hyperlink ref="P539" r:id="rId444"/>
+    <hyperlink ref="Q539" r:id="rId445"/>
+    <hyperlink ref="B540" r:id="rId446"/>
+    <hyperlink ref="L540" r:id="rId447"/>
+    <hyperlink ref="N540" r:id="rId448"/>
+    <hyperlink ref="P540" r:id="rId449"/>
+    <hyperlink ref="Q540" r:id="rId450"/>
+    <hyperlink ref="B551" r:id="rId451"/>
+    <hyperlink ref="L551" r:id="rId452"/>
+    <hyperlink ref="N551" r:id="rId453"/>
+    <hyperlink ref="P551" r:id="rId454"/>
+    <hyperlink ref="Q551" r:id="rId455"/>
+    <hyperlink ref="N559" r:id="rId456"/>
+    <hyperlink ref="B560" r:id="rId457"/>
+    <hyperlink ref="L560" r:id="rId458"/>
+    <hyperlink ref="N560" r:id="rId459"/>
+    <hyperlink ref="P560" r:id="rId460"/>
+    <hyperlink ref="Q560" r:id="rId461"/>
+    <hyperlink ref="B567" r:id="rId462"/>
+    <hyperlink ref="L567" r:id="rId463"/>
+    <hyperlink ref="N567" r:id="rId464"/>
+    <hyperlink ref="P567" r:id="rId465"/>
+    <hyperlink ref="Q567" r:id="rId466"/>
+    <hyperlink ref="B568" r:id="rId467"/>
+    <hyperlink ref="L568" r:id="rId468"/>
+    <hyperlink ref="N568" r:id="rId469"/>
+    <hyperlink ref="P568" r:id="rId470"/>
+    <hyperlink ref="Q568" r:id="rId471"/>
+    <hyperlink ref="B569" r:id="rId472"/>
+    <hyperlink ref="L569" r:id="rId473"/>
+    <hyperlink ref="N569" r:id="rId474"/>
+    <hyperlink ref="Q569" r:id="rId475"/>
+    <hyperlink ref="B590" r:id="rId476"/>
+    <hyperlink ref="L590" r:id="rId477"/>
+    <hyperlink ref="N590" r:id="rId478"/>
+    <hyperlink ref="P590" r:id="rId479"/>
+    <hyperlink ref="R590" r:id="rId480"/>
+    <hyperlink ref="B600" r:id="rId481"/>
+    <hyperlink ref="L600" r:id="rId482"/>
+    <hyperlink ref="N600" r:id="rId483"/>
+    <hyperlink ref="P600" r:id="rId484"/>
+    <hyperlink ref="Q600" r:id="rId485"/>
+    <hyperlink ref="B626" r:id="rId486"/>
+    <hyperlink ref="L626" r:id="rId487"/>
+    <hyperlink ref="N626" r:id="rId488"/>
+    <hyperlink ref="P626" r:id="rId489"/>
+    <hyperlink ref="Q626" r:id="rId490"/>
+    <hyperlink ref="B627" r:id="rId491"/>
+    <hyperlink ref="L627" r:id="rId492"/>
+    <hyperlink ref="N627" r:id="rId493"/>
+    <hyperlink ref="P627" r:id="rId494"/>
+    <hyperlink ref="Q627" r:id="rId495"/>
+    <hyperlink ref="B636" r:id="rId496"/>
+    <hyperlink ref="N636" r:id="rId497"/>
+    <hyperlink ref="P636" r:id="rId498"/>
+    <hyperlink ref="B645" r:id="rId499"/>
+    <hyperlink ref="L645" r:id="rId500"/>
+    <hyperlink ref="N645" r:id="rId501"/>
+    <hyperlink ref="P645" r:id="rId502"/>
+    <hyperlink ref="B652" r:id="rId503"/>
+    <hyperlink ref="L652" r:id="rId504"/>
+    <hyperlink ref="N652" r:id="rId505"/>
   </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -10055,7 +10055,7 @@
         <v>46100</v>
       </c>
       <c r="H101" s="14">
-        <v>46899</v>
+        <v>46168</v>
       </c>
       <c r="I101" s="14">
         <v>46935</v>
@@ -12669,7 +12669,7 @@
         <v>46100</v>
       </c>
       <c r="H162" s="9">
-        <v>46107</v>
+        <v>46168</v>
       </c>
       <c r="I162" s="9">
         <v>46935</v>

--- a/last_snapshot.xlsx
+++ b/last_snapshot.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4042" uniqueCount="1806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4053" uniqueCount="1806">
   <si>
     <t>Status</t>
   </si>
@@ -8547,7 +8547,9 @@
         <v>213</v>
       </c>
       <c r="O65" s="12"/>
-      <c r="P65" s="12"/>
+      <c r="P65" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q65" s="19" t="s">
         <v>16</v>
       </c>
@@ -8683,7 +8685,9 @@
         <v>213</v>
       </c>
       <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
+      <c r="P68" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q68" s="15" t="s">
         <v>16</v>
       </c>
@@ -9633,7 +9637,9 @@
         <v>213</v>
       </c>
       <c r="O90" s="7"/>
-      <c r="P90" s="7"/>
+      <c r="P90" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q90" s="15" t="s">
         <v>16</v>
       </c>
@@ -10105,7 +10111,9 @@
         <v>213</v>
       </c>
       <c r="O101" s="12"/>
-      <c r="P101" s="12"/>
+      <c r="P101" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q101" s="19" t="s">
         <v>16</v>
       </c>
@@ -10835,7 +10843,9 @@
         <v>213</v>
       </c>
       <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
+      <c r="P119" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q119" s="19" t="s">
         <v>16</v>
       </c>
@@ -11327,7 +11337,9 @@
         <v>213</v>
       </c>
       <c r="O131" s="12"/>
-      <c r="P131" s="12"/>
+      <c r="P131" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q131" s="19" t="s">
         <v>16</v>
       </c>
@@ -11677,7 +11689,9 @@
         <v>402</v>
       </c>
       <c r="O139" s="12"/>
-      <c r="P139" s="12"/>
+      <c r="P139" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q139" s="19" t="s">
         <v>16</v>
       </c>
@@ -12025,7 +12039,9 @@
         <v>402</v>
       </c>
       <c r="O147" s="12"/>
-      <c r="P147" s="12"/>
+      <c r="P147" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q147" s="19" t="s">
         <v>16</v>
       </c>
@@ -12253,7 +12269,9 @@
         <v>213</v>
       </c>
       <c r="O152" s="7"/>
-      <c r="P152" s="7"/>
+      <c r="P152" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q152" s="15" t="s">
         <v>16</v>
       </c>
@@ -12477,7 +12495,9 @@
         <v>402</v>
       </c>
       <c r="O157" s="12"/>
-      <c r="P157" s="12"/>
+      <c r="P157" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="Q157" s="19" t="s">
         <v>16</v>
       </c>
@@ -12711,7 +12731,9 @@
         <v>213</v>
       </c>
       <c r="O162" s="7"/>
-      <c r="P162" s="7"/>
+      <c r="P162" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="Q162" s="15" t="s">
         <v>16</v>
       </c>
@@ -33710,473 +33732,484 @@
     <hyperlink ref="B65" r:id="rId39"/>
     <hyperlink ref="L65" r:id="rId40"/>
     <hyperlink ref="N65" r:id="rId41"/>
-    <hyperlink ref="Q65" r:id="rId42"/>
-    <hyperlink ref="B66" r:id="rId43"/>
-    <hyperlink ref="L66" r:id="rId44"/>
-    <hyperlink ref="N66" r:id="rId45"/>
-    <hyperlink ref="Q66" r:id="rId46"/>
-    <hyperlink ref="B68" r:id="rId47"/>
-    <hyperlink ref="L68" r:id="rId48"/>
-    <hyperlink ref="N68" r:id="rId49"/>
-    <hyperlink ref="Q68" r:id="rId50"/>
-    <hyperlink ref="B69" r:id="rId51"/>
-    <hyperlink ref="L69" r:id="rId52"/>
-    <hyperlink ref="N69" r:id="rId53"/>
-    <hyperlink ref="Q69" r:id="rId54"/>
-    <hyperlink ref="N78" r:id="rId55"/>
-    <hyperlink ref="B79" r:id="rId56"/>
-    <hyperlink ref="L79" r:id="rId57"/>
-    <hyperlink ref="N79" r:id="rId58"/>
-    <hyperlink ref="P79" r:id="rId59"/>
-    <hyperlink ref="Q79" r:id="rId60"/>
-    <hyperlink ref="B89" r:id="rId61"/>
-    <hyperlink ref="L89" r:id="rId62"/>
-    <hyperlink ref="N89" r:id="rId63"/>
-    <hyperlink ref="P89" r:id="rId64"/>
-    <hyperlink ref="Q89" r:id="rId65"/>
-    <hyperlink ref="R89" r:id="rId66"/>
-    <hyperlink ref="B90" r:id="rId67"/>
-    <hyperlink ref="L90" r:id="rId68"/>
-    <hyperlink ref="N90" r:id="rId69"/>
-    <hyperlink ref="Q90" r:id="rId70"/>
-    <hyperlink ref="B100" r:id="rId71"/>
-    <hyperlink ref="L100" r:id="rId72"/>
-    <hyperlink ref="N100" r:id="rId73"/>
-    <hyperlink ref="P100" r:id="rId74"/>
-    <hyperlink ref="Q100" r:id="rId75"/>
-    <hyperlink ref="B101" r:id="rId76"/>
-    <hyperlink ref="L101" r:id="rId77"/>
-    <hyperlink ref="N101" r:id="rId78"/>
-    <hyperlink ref="Q101" r:id="rId79"/>
-    <hyperlink ref="B117" r:id="rId80"/>
-    <hyperlink ref="L117" r:id="rId81"/>
-    <hyperlink ref="N117" r:id="rId82"/>
-    <hyperlink ref="P117" r:id="rId83"/>
-    <hyperlink ref="R117" r:id="rId84"/>
-    <hyperlink ref="N118" r:id="rId85"/>
-    <hyperlink ref="B119" r:id="rId86"/>
-    <hyperlink ref="L119" r:id="rId87"/>
-    <hyperlink ref="N119" r:id="rId88"/>
-    <hyperlink ref="Q119" r:id="rId89"/>
-    <hyperlink ref="B129" r:id="rId90"/>
-    <hyperlink ref="L129" r:id="rId91"/>
-    <hyperlink ref="N129" r:id="rId92"/>
-    <hyperlink ref="P129" r:id="rId93"/>
-    <hyperlink ref="R129" r:id="rId94"/>
-    <hyperlink ref="N130" r:id="rId95"/>
-    <hyperlink ref="B131" r:id="rId96"/>
-    <hyperlink ref="L131" r:id="rId97"/>
-    <hyperlink ref="N131" r:id="rId98"/>
-    <hyperlink ref="Q131" r:id="rId99"/>
-    <hyperlink ref="B137" r:id="rId100"/>
-    <hyperlink ref="L137" r:id="rId101"/>
-    <hyperlink ref="N137" r:id="rId102"/>
-    <hyperlink ref="P137" r:id="rId103"/>
-    <hyperlink ref="Q137" r:id="rId104"/>
-    <hyperlink ref="N138" r:id="rId105"/>
-    <hyperlink ref="B139" r:id="rId106"/>
-    <hyperlink ref="L139" r:id="rId107"/>
-    <hyperlink ref="N139" r:id="rId108"/>
-    <hyperlink ref="Q139" r:id="rId109"/>
-    <hyperlink ref="B145" r:id="rId110"/>
-    <hyperlink ref="L145" r:id="rId111"/>
-    <hyperlink ref="N145" r:id="rId112"/>
-    <hyperlink ref="P145" r:id="rId113"/>
-    <hyperlink ref="R145" r:id="rId114"/>
-    <hyperlink ref="N146" r:id="rId115"/>
-    <hyperlink ref="B147" r:id="rId116"/>
-    <hyperlink ref="L147" r:id="rId117"/>
-    <hyperlink ref="N147" r:id="rId118"/>
-    <hyperlink ref="Q147" r:id="rId119"/>
-    <hyperlink ref="B151" r:id="rId120"/>
-    <hyperlink ref="L151" r:id="rId121"/>
-    <hyperlink ref="N151" r:id="rId122"/>
-    <hyperlink ref="P151" r:id="rId123"/>
-    <hyperlink ref="Q151" r:id="rId124"/>
-    <hyperlink ref="R151" r:id="rId125"/>
-    <hyperlink ref="B152" r:id="rId126"/>
-    <hyperlink ref="L152" r:id="rId127"/>
-    <hyperlink ref="N152" r:id="rId128"/>
-    <hyperlink ref="Q152" r:id="rId129"/>
-    <hyperlink ref="B155" r:id="rId130"/>
-    <hyperlink ref="L155" r:id="rId131"/>
-    <hyperlink ref="N155" r:id="rId132"/>
-    <hyperlink ref="P155" r:id="rId133"/>
-    <hyperlink ref="Q155" r:id="rId134"/>
-    <hyperlink ref="R155" r:id="rId135"/>
-    <hyperlink ref="N156" r:id="rId136"/>
-    <hyperlink ref="B157" r:id="rId137"/>
-    <hyperlink ref="L157" r:id="rId138"/>
-    <hyperlink ref="N157" r:id="rId139"/>
-    <hyperlink ref="Q157" r:id="rId140"/>
-    <hyperlink ref="B159" r:id="rId141"/>
-    <hyperlink ref="L159" r:id="rId142"/>
-    <hyperlink ref="N159" r:id="rId143"/>
-    <hyperlink ref="P159" r:id="rId144"/>
-    <hyperlink ref="Q159" r:id="rId145"/>
-    <hyperlink ref="B161" r:id="rId146"/>
-    <hyperlink ref="L161" r:id="rId147"/>
-    <hyperlink ref="N161" r:id="rId148"/>
-    <hyperlink ref="P161" r:id="rId149"/>
-    <hyperlink ref="Q161" r:id="rId150"/>
-    <hyperlink ref="R161" r:id="rId151"/>
-    <hyperlink ref="B162" r:id="rId152"/>
-    <hyperlink ref="L162" r:id="rId153"/>
-    <hyperlink ref="N162" r:id="rId154"/>
-    <hyperlink ref="Q162" r:id="rId155"/>
-    <hyperlink ref="B165" r:id="rId156"/>
-    <hyperlink ref="L165" r:id="rId157"/>
-    <hyperlink ref="N165" r:id="rId158"/>
-    <hyperlink ref="P165" r:id="rId159"/>
-    <hyperlink ref="R165" r:id="rId160"/>
-    <hyperlink ref="B166" r:id="rId161"/>
-    <hyperlink ref="L166" r:id="rId162"/>
-    <hyperlink ref="N166" r:id="rId163"/>
-    <hyperlink ref="Q166" r:id="rId164"/>
-    <hyperlink ref="B167" r:id="rId165"/>
-    <hyperlink ref="L167" r:id="rId166"/>
-    <hyperlink ref="N167" r:id="rId167"/>
-    <hyperlink ref="Q167" r:id="rId168"/>
-    <hyperlink ref="B168" r:id="rId169"/>
-    <hyperlink ref="L168" r:id="rId170"/>
-    <hyperlink ref="N168" r:id="rId171"/>
-    <hyperlink ref="Q168" r:id="rId172"/>
-    <hyperlink ref="B174" r:id="rId173"/>
-    <hyperlink ref="L174" r:id="rId174"/>
-    <hyperlink ref="N174" r:id="rId175"/>
-    <hyperlink ref="P174" r:id="rId176"/>
-    <hyperlink ref="B180" r:id="rId177"/>
-    <hyperlink ref="L180" r:id="rId178"/>
-    <hyperlink ref="N180" r:id="rId179"/>
-    <hyperlink ref="P180" r:id="rId180"/>
-    <hyperlink ref="Q180" r:id="rId181"/>
-    <hyperlink ref="B200" r:id="rId182"/>
-    <hyperlink ref="L200" r:id="rId183"/>
-    <hyperlink ref="N200" r:id="rId184"/>
-    <hyperlink ref="P200" r:id="rId185"/>
-    <hyperlink ref="B201" r:id="rId186"/>
-    <hyperlink ref="L201" r:id="rId187"/>
-    <hyperlink ref="N201" r:id="rId188"/>
-    <hyperlink ref="Q201" r:id="rId189"/>
-    <hyperlink ref="B205" r:id="rId190"/>
-    <hyperlink ref="L205" r:id="rId191"/>
-    <hyperlink ref="N205" r:id="rId192"/>
-    <hyperlink ref="P205" r:id="rId193"/>
-    <hyperlink ref="B209" r:id="rId194"/>
-    <hyperlink ref="L209" r:id="rId195"/>
-    <hyperlink ref="N209" r:id="rId196"/>
-    <hyperlink ref="P209" r:id="rId197"/>
-    <hyperlink ref="B213" r:id="rId198"/>
-    <hyperlink ref="L213" r:id="rId199"/>
-    <hyperlink ref="N213" r:id="rId200"/>
-    <hyperlink ref="P213" r:id="rId201"/>
-    <hyperlink ref="Q213" r:id="rId202"/>
-    <hyperlink ref="B215" r:id="rId203"/>
-    <hyperlink ref="L215" r:id="rId204"/>
-    <hyperlink ref="N215" r:id="rId205"/>
-    <hyperlink ref="P215" r:id="rId206"/>
-    <hyperlink ref="B219" r:id="rId207"/>
-    <hyperlink ref="L219" r:id="rId208"/>
-    <hyperlink ref="N219" r:id="rId209"/>
-    <hyperlink ref="P219" r:id="rId210"/>
-    <hyperlink ref="Q219" r:id="rId211"/>
-    <hyperlink ref="N221" r:id="rId212"/>
-    <hyperlink ref="B222" r:id="rId213"/>
-    <hyperlink ref="L222" r:id="rId214"/>
-    <hyperlink ref="N222" r:id="rId215"/>
-    <hyperlink ref="P222" r:id="rId216"/>
-    <hyperlink ref="Q222" r:id="rId217"/>
-    <hyperlink ref="B227" r:id="rId218"/>
-    <hyperlink ref="L227" r:id="rId219"/>
-    <hyperlink ref="N227" r:id="rId220"/>
-    <hyperlink ref="P227" r:id="rId221"/>
-    <hyperlink ref="Q227" r:id="rId222"/>
-    <hyperlink ref="B232" r:id="rId223"/>
-    <hyperlink ref="L232" r:id="rId224"/>
-    <hyperlink ref="N232" r:id="rId225"/>
-    <hyperlink ref="P232" r:id="rId226"/>
-    <hyperlink ref="Q232" r:id="rId227"/>
-    <hyperlink ref="R232" r:id="rId228"/>
-    <hyperlink ref="B238" r:id="rId229"/>
-    <hyperlink ref="L238" r:id="rId230"/>
-    <hyperlink ref="N238" r:id="rId231"/>
-    <hyperlink ref="P238" r:id="rId232"/>
-    <hyperlink ref="B245" r:id="rId233"/>
-    <hyperlink ref="L245" r:id="rId234"/>
-    <hyperlink ref="N245" r:id="rId235"/>
-    <hyperlink ref="P245" r:id="rId236"/>
-    <hyperlink ref="B254" r:id="rId237"/>
-    <hyperlink ref="L254" r:id="rId238"/>
-    <hyperlink ref="N254" r:id="rId239"/>
-    <hyperlink ref="P254" r:id="rId240"/>
-    <hyperlink ref="Q254" r:id="rId241"/>
-    <hyperlink ref="B260" r:id="rId242"/>
-    <hyperlink ref="L260" r:id="rId243"/>
-    <hyperlink ref="N260" r:id="rId244"/>
-    <hyperlink ref="P260" r:id="rId245"/>
-    <hyperlink ref="Q260" r:id="rId246"/>
-    <hyperlink ref="B264" r:id="rId247"/>
-    <hyperlink ref="L264" r:id="rId248"/>
-    <hyperlink ref="N264" r:id="rId249"/>
-    <hyperlink ref="B286" r:id="rId250"/>
-    <hyperlink ref="L286" r:id="rId251"/>
-    <hyperlink ref="N286" r:id="rId252"/>
-    <hyperlink ref="P286" r:id="rId253"/>
-    <hyperlink ref="Q286" r:id="rId254"/>
-    <hyperlink ref="B294" r:id="rId255"/>
-    <hyperlink ref="L294" r:id="rId256"/>
-    <hyperlink ref="N294" r:id="rId257"/>
-    <hyperlink ref="P294" r:id="rId258"/>
-    <hyperlink ref="Q294" r:id="rId259"/>
-    <hyperlink ref="B305" r:id="rId260"/>
-    <hyperlink ref="L305" r:id="rId261"/>
-    <hyperlink ref="N305" r:id="rId262"/>
-    <hyperlink ref="P305" r:id="rId263"/>
-    <hyperlink ref="Q305" r:id="rId264"/>
-    <hyperlink ref="B313" r:id="rId265"/>
-    <hyperlink ref="L313" r:id="rId266"/>
-    <hyperlink ref="N313" r:id="rId267"/>
-    <hyperlink ref="P313" r:id="rId268"/>
-    <hyperlink ref="Q313" r:id="rId269"/>
-    <hyperlink ref="B335" r:id="rId270"/>
-    <hyperlink ref="L335" r:id="rId271"/>
-    <hyperlink ref="N335" r:id="rId272"/>
-    <hyperlink ref="P335" r:id="rId273"/>
-    <hyperlink ref="B337" r:id="rId274"/>
-    <hyperlink ref="L337" r:id="rId275"/>
-    <hyperlink ref="N337" r:id="rId276"/>
-    <hyperlink ref="P337" r:id="rId277"/>
-    <hyperlink ref="Q337" r:id="rId278"/>
-    <hyperlink ref="B341" r:id="rId279"/>
-    <hyperlink ref="L341" r:id="rId280"/>
-    <hyperlink ref="N341" r:id="rId281"/>
-    <hyperlink ref="B344" r:id="rId282"/>
-    <hyperlink ref="L344" r:id="rId283"/>
-    <hyperlink ref="N344" r:id="rId284"/>
-    <hyperlink ref="P344" r:id="rId285"/>
-    <hyperlink ref="Q344" r:id="rId286"/>
-    <hyperlink ref="B346" r:id="rId287"/>
-    <hyperlink ref="L346" r:id="rId288"/>
-    <hyperlink ref="N346" r:id="rId289"/>
-    <hyperlink ref="P346" r:id="rId290"/>
-    <hyperlink ref="Q346" r:id="rId291"/>
-    <hyperlink ref="B352" r:id="rId292"/>
-    <hyperlink ref="L352" r:id="rId293"/>
-    <hyperlink ref="N352" r:id="rId294"/>
-    <hyperlink ref="P352" r:id="rId295"/>
-    <hyperlink ref="Q352" r:id="rId296"/>
-    <hyperlink ref="B353" r:id="rId297"/>
-    <hyperlink ref="L353" r:id="rId298"/>
-    <hyperlink ref="N353" r:id="rId299"/>
-    <hyperlink ref="Q353" r:id="rId300"/>
-    <hyperlink ref="B356" r:id="rId301"/>
-    <hyperlink ref="L356" r:id="rId302"/>
-    <hyperlink ref="N356" r:id="rId303"/>
-    <hyperlink ref="P356" r:id="rId304"/>
-    <hyperlink ref="Q356" r:id="rId305"/>
-    <hyperlink ref="B359" r:id="rId306"/>
-    <hyperlink ref="L359" r:id="rId307"/>
-    <hyperlink ref="N359" r:id="rId308"/>
-    <hyperlink ref="P359" r:id="rId309"/>
-    <hyperlink ref="Q359" r:id="rId310"/>
-    <hyperlink ref="B361" r:id="rId311"/>
-    <hyperlink ref="L361" r:id="rId312"/>
-    <hyperlink ref="N361" r:id="rId313"/>
-    <hyperlink ref="P361" r:id="rId314"/>
-    <hyperlink ref="Q361" r:id="rId315"/>
-    <hyperlink ref="R361" r:id="rId316"/>
-    <hyperlink ref="B400" r:id="rId317"/>
-    <hyperlink ref="L400" r:id="rId318"/>
-    <hyperlink ref="N400" r:id="rId319"/>
-    <hyperlink ref="P400" r:id="rId320"/>
-    <hyperlink ref="N402" r:id="rId321"/>
-    <hyperlink ref="B403" r:id="rId322"/>
-    <hyperlink ref="L403" r:id="rId323"/>
-    <hyperlink ref="N403" r:id="rId324"/>
-    <hyperlink ref="P403" r:id="rId325"/>
-    <hyperlink ref="Q403" r:id="rId326"/>
-    <hyperlink ref="N404" r:id="rId327"/>
-    <hyperlink ref="B415" r:id="rId328"/>
-    <hyperlink ref="L415" r:id="rId329"/>
-    <hyperlink ref="N415" r:id="rId330"/>
-    <hyperlink ref="P415" r:id="rId331"/>
-    <hyperlink ref="B416" r:id="rId332"/>
-    <hyperlink ref="L416" r:id="rId333"/>
-    <hyperlink ref="N416" r:id="rId334"/>
-    <hyperlink ref="P416" r:id="rId335"/>
-    <hyperlink ref="B417" r:id="rId336"/>
-    <hyperlink ref="L417" r:id="rId337"/>
-    <hyperlink ref="N417" r:id="rId338"/>
-    <hyperlink ref="Q417" r:id="rId339"/>
-    <hyperlink ref="N419" r:id="rId340"/>
-    <hyperlink ref="B420" r:id="rId341"/>
-    <hyperlink ref="L420" r:id="rId342"/>
-    <hyperlink ref="N420" r:id="rId343"/>
-    <hyperlink ref="Q420" r:id="rId344"/>
-    <hyperlink ref="B426" r:id="rId345"/>
-    <hyperlink ref="L426" r:id="rId346"/>
-    <hyperlink ref="N426" r:id="rId347"/>
-    <hyperlink ref="P426" r:id="rId348"/>
-    <hyperlink ref="B433" r:id="rId349"/>
-    <hyperlink ref="L433" r:id="rId350"/>
-    <hyperlink ref="N433" r:id="rId351"/>
-    <hyperlink ref="P433" r:id="rId352"/>
-    <hyperlink ref="B438" r:id="rId353"/>
-    <hyperlink ref="L438" r:id="rId354"/>
-    <hyperlink ref="N438" r:id="rId355"/>
-    <hyperlink ref="P438" r:id="rId356"/>
-    <hyperlink ref="B439" r:id="rId357"/>
-    <hyperlink ref="L439" r:id="rId358"/>
-    <hyperlink ref="N439" r:id="rId359"/>
-    <hyperlink ref="P439" r:id="rId360"/>
-    <hyperlink ref="B451" r:id="rId361"/>
-    <hyperlink ref="L451" r:id="rId362"/>
-    <hyperlink ref="N451" r:id="rId363"/>
-    <hyperlink ref="P451" r:id="rId364"/>
-    <hyperlink ref="Q451" r:id="rId365"/>
-    <hyperlink ref="B468" r:id="rId366"/>
-    <hyperlink ref="L468" r:id="rId367"/>
-    <hyperlink ref="N468" r:id="rId368"/>
-    <hyperlink ref="P468" r:id="rId369"/>
-    <hyperlink ref="Q468" r:id="rId370"/>
-    <hyperlink ref="N473" r:id="rId371"/>
-    <hyperlink ref="B484" r:id="rId372"/>
-    <hyperlink ref="L484" r:id="rId373"/>
-    <hyperlink ref="N484" r:id="rId374"/>
-    <hyperlink ref="P484" r:id="rId375"/>
-    <hyperlink ref="R484" r:id="rId376"/>
-    <hyperlink ref="B490" r:id="rId377"/>
-    <hyperlink ref="L490" r:id="rId378"/>
-    <hyperlink ref="N490" r:id="rId379"/>
-    <hyperlink ref="P490" r:id="rId380"/>
-    <hyperlink ref="B492" r:id="rId381"/>
-    <hyperlink ref="L492" r:id="rId382"/>
-    <hyperlink ref="N492" r:id="rId383"/>
-    <hyperlink ref="B495" r:id="rId384"/>
-    <hyperlink ref="L495" r:id="rId385"/>
-    <hyperlink ref="N495" r:id="rId386"/>
-    <hyperlink ref="B498" r:id="rId387"/>
-    <hyperlink ref="L498" r:id="rId388"/>
-    <hyperlink ref="N498" r:id="rId389"/>
-    <hyperlink ref="P498" r:id="rId390"/>
-    <hyperlink ref="B502" r:id="rId391"/>
-    <hyperlink ref="L502" r:id="rId392"/>
-    <hyperlink ref="N502" r:id="rId393"/>
-    <hyperlink ref="P502" r:id="rId394"/>
-    <hyperlink ref="B503" r:id="rId395"/>
-    <hyperlink ref="L503" r:id="rId396"/>
-    <hyperlink ref="N503" r:id="rId397"/>
-    <hyperlink ref="P503" r:id="rId398"/>
-    <hyperlink ref="B506" r:id="rId399"/>
-    <hyperlink ref="L506" r:id="rId400"/>
-    <hyperlink ref="N506" r:id="rId401"/>
-    <hyperlink ref="P506" r:id="rId402"/>
-    <hyperlink ref="B517" r:id="rId403"/>
-    <hyperlink ref="L517" r:id="rId404"/>
-    <hyperlink ref="N517" r:id="rId405"/>
-    <hyperlink ref="P517" r:id="rId406"/>
-    <hyperlink ref="B520" r:id="rId407"/>
-    <hyperlink ref="L520" r:id="rId408"/>
-    <hyperlink ref="N520" r:id="rId409"/>
-    <hyperlink ref="P520" r:id="rId410"/>
-    <hyperlink ref="R520" r:id="rId411"/>
-    <hyperlink ref="B531" r:id="rId412"/>
-    <hyperlink ref="L531" r:id="rId413"/>
-    <hyperlink ref="N531" r:id="rId414"/>
-    <hyperlink ref="P531" r:id="rId415"/>
-    <hyperlink ref="Q531" r:id="rId416"/>
-    <hyperlink ref="R531" r:id="rId417"/>
-    <hyperlink ref="B534" r:id="rId418"/>
-    <hyperlink ref="L534" r:id="rId419"/>
-    <hyperlink ref="N534" r:id="rId420"/>
-    <hyperlink ref="P534" r:id="rId421"/>
-    <hyperlink ref="B535" r:id="rId422"/>
-    <hyperlink ref="L535" r:id="rId423"/>
-    <hyperlink ref="N535" r:id="rId424"/>
-    <hyperlink ref="P535" r:id="rId425"/>
-    <hyperlink ref="Q535" r:id="rId426"/>
-    <hyperlink ref="B537" r:id="rId427"/>
-    <hyperlink ref="L537" r:id="rId428"/>
-    <hyperlink ref="N537" r:id="rId429"/>
-    <hyperlink ref="P537" r:id="rId430"/>
-    <hyperlink ref="B539" r:id="rId431"/>
-    <hyperlink ref="L539" r:id="rId432"/>
-    <hyperlink ref="N539" r:id="rId433"/>
-    <hyperlink ref="P539" r:id="rId434"/>
-    <hyperlink ref="B540" r:id="rId435"/>
-    <hyperlink ref="L540" r:id="rId436"/>
-    <hyperlink ref="N540" r:id="rId437"/>
-    <hyperlink ref="P540" r:id="rId438"/>
-    <hyperlink ref="B541" r:id="rId439"/>
-    <hyperlink ref="L541" r:id="rId440"/>
-    <hyperlink ref="N541" r:id="rId441"/>
-    <hyperlink ref="P541" r:id="rId442"/>
-    <hyperlink ref="Q541" r:id="rId443"/>
-    <hyperlink ref="B542" r:id="rId444"/>
-    <hyperlink ref="L542" r:id="rId445"/>
-    <hyperlink ref="N542" r:id="rId446"/>
-    <hyperlink ref="P542" r:id="rId447"/>
-    <hyperlink ref="Q542" r:id="rId448"/>
-    <hyperlink ref="B543" r:id="rId449"/>
-    <hyperlink ref="L543" r:id="rId450"/>
-    <hyperlink ref="N543" r:id="rId451"/>
-    <hyperlink ref="P543" r:id="rId452"/>
-    <hyperlink ref="Q543" r:id="rId453"/>
-    <hyperlink ref="B554" r:id="rId454"/>
-    <hyperlink ref="L554" r:id="rId455"/>
-    <hyperlink ref="N554" r:id="rId456"/>
-    <hyperlink ref="P554" r:id="rId457"/>
-    <hyperlink ref="Q554" r:id="rId458"/>
-    <hyperlink ref="N562" r:id="rId459"/>
-    <hyperlink ref="B563" r:id="rId460"/>
-    <hyperlink ref="L563" r:id="rId461"/>
-    <hyperlink ref="N563" r:id="rId462"/>
-    <hyperlink ref="P563" r:id="rId463"/>
-    <hyperlink ref="Q563" r:id="rId464"/>
-    <hyperlink ref="B570" r:id="rId465"/>
-    <hyperlink ref="L570" r:id="rId466"/>
-    <hyperlink ref="N570" r:id="rId467"/>
-    <hyperlink ref="P570" r:id="rId468"/>
-    <hyperlink ref="Q570" r:id="rId469"/>
-    <hyperlink ref="B571" r:id="rId470"/>
-    <hyperlink ref="L571" r:id="rId471"/>
-    <hyperlink ref="N571" r:id="rId472"/>
-    <hyperlink ref="P571" r:id="rId473"/>
-    <hyperlink ref="Q571" r:id="rId474"/>
-    <hyperlink ref="B572" r:id="rId475"/>
-    <hyperlink ref="L572" r:id="rId476"/>
-    <hyperlink ref="N572" r:id="rId477"/>
-    <hyperlink ref="Q572" r:id="rId478"/>
-    <hyperlink ref="B593" r:id="rId479"/>
-    <hyperlink ref="L593" r:id="rId480"/>
-    <hyperlink ref="N593" r:id="rId481"/>
-    <hyperlink ref="P593" r:id="rId482"/>
-    <hyperlink ref="R593" r:id="rId483"/>
-    <hyperlink ref="B603" r:id="rId484"/>
-    <hyperlink ref="L603" r:id="rId485"/>
-    <hyperlink ref="N603" r:id="rId486"/>
-    <hyperlink ref="P603" r:id="rId487"/>
-    <hyperlink ref="Q603" r:id="rId488"/>
-    <hyperlink ref="B629" r:id="rId489"/>
-    <hyperlink ref="L629" r:id="rId490"/>
-    <hyperlink ref="N629" r:id="rId491"/>
-    <hyperlink ref="P629" r:id="rId492"/>
-    <hyperlink ref="Q629" r:id="rId493"/>
-    <hyperlink ref="B630" r:id="rId494"/>
-    <hyperlink ref="L630" r:id="rId495"/>
-    <hyperlink ref="N630" r:id="rId496"/>
-    <hyperlink ref="P630" r:id="rId497"/>
-    <hyperlink ref="Q630" r:id="rId498"/>
-    <hyperlink ref="B639" r:id="rId499"/>
-    <hyperlink ref="N639" r:id="rId500"/>
-    <hyperlink ref="P639" r:id="rId501"/>
-    <hyperlink ref="B648" r:id="rId502"/>
-    <hyperlink ref="L648" r:id="rId503"/>
-    <hyperlink ref="N648" r:id="rId504"/>
-    <hyperlink ref="P648" r:id="rId505"/>
-    <hyperlink ref="B655" r:id="rId506"/>
-    <hyperlink ref="L655" r:id="rId507"/>
-    <hyperlink ref="N655" r:id="rId508"/>
+    <hyperlink ref="P65" r:id="rId42"/>
+    <hyperlink ref="Q65" r:id="rId43"/>
+    <hyperlink ref="B66" r:id="rId44"/>
+    <hyperlink ref="L66" r:id="rId45"/>
+    <hyperlink ref="N66" r:id="rId46"/>
+    <hyperlink ref="Q66" r:id="rId47"/>
+    <hyperlink ref="B68" r:id="rId48"/>
+    <hyperlink ref="L68" r:id="rId49"/>
+    <hyperlink ref="N68" r:id="rId50"/>
+    <hyperlink ref="P68" r:id="rId51"/>
+    <hyperlink ref="Q68" r:id="rId52"/>
+    <hyperlink ref="B69" r:id="rId53"/>
+    <hyperlink ref="L69" r:id="rId54"/>
+    <hyperlink ref="N69" r:id="rId55"/>
+    <hyperlink ref="Q69" r:id="rId56"/>
+    <hyperlink ref="N78" r:id="rId57"/>
+    <hyperlink ref="B79" r:id="rId58"/>
+    <hyperlink ref="L79" r:id="rId59"/>
+    <hyperlink ref="N79" r:id="rId60"/>
+    <hyperlink ref="P79" r:id="rId61"/>
+    <hyperlink ref="Q79" r:id="rId62"/>
+    <hyperlink ref="B89" r:id="rId63"/>
+    <hyperlink ref="L89" r:id="rId64"/>
+    <hyperlink ref="N89" r:id="rId65"/>
+    <hyperlink ref="P89" r:id="rId66"/>
+    <hyperlink ref="Q89" r:id="rId67"/>
+    <hyperlink ref="R89" r:id="rId68"/>
+    <hyperlink ref="B90" r:id="rId69"/>
+    <hyperlink ref="L90" r:id="rId70"/>
+    <hyperlink ref="N90" r:id="rId71"/>
+    <hyperlink ref="P90" r:id="rId72"/>
+    <hyperlink ref="Q90" r:id="rId73"/>
+    <hyperlink ref="B100" r:id="rId74"/>
+    <hyperlink ref="L100" r:id="rId75"/>
+    <hyperlink ref="N100" r:id="rId76"/>
+    <hyperlink ref="P100" r:id="rId77"/>
+    <hyperlink ref="Q100" r:id="rId78"/>
+    <hyperlink ref="B101" r:id="rId79"/>
+    <hyperlink ref="L101" r:id="rId80"/>
+    <hyperlink ref="N101" r:id="rId81"/>
+    <hyperlink ref="P101" r:id="rId82"/>
+    <hyperlink ref="Q101" r:id="rId83"/>
+    <hyperlink ref="B117" r:id="rId84"/>
+    <hyperlink ref="L117" r:id="rId85"/>
+    <hyperlink ref="N117" r:id="rId86"/>
+    <hyperlink ref="P117" r:id="rId87"/>
+    <hyperlink ref="R117" r:id="rId88"/>
+    <hyperlink ref="N118" r:id="rId89"/>
+    <hyperlink ref="B119" r:id="rId90"/>
+    <hyperlink ref="L119" r:id="rId91"/>
+    <hyperlink ref="N119" r:id="rId92"/>
+    <hyperlink ref="P119" r:id="rId93"/>
+    <hyperlink ref="Q119" r:id="rId94"/>
+    <hyperlink ref="B129" r:id="rId95"/>
+    <hyperlink ref="L129" r:id="rId96"/>
+    <hyperlink ref="N129" r:id="rId97"/>
+    <hyperlink ref="P129" r:id="rId98"/>
+    <hyperlink ref="R129" r:id="rId99"/>
+    <hyperlink ref="N130" r:id="rId100"/>
+    <hyperlink ref="B131" r:id="rId101"/>
+    <hyperlink ref="L131" r:id="rId102"/>
+    <hyperlink ref="N131" r:id="rId103"/>
+    <hyperlink ref="P131" r:id="rId104"/>
+    <hyperlink ref="Q131" r:id="rId105"/>
+    <hyperlink ref="B137" r:id="rId106"/>
+    <hyperlink ref="L137" r:id="rId107"/>
+    <hyperlink ref="N137" r:id="rId108"/>
+    <hyperlink ref="P137" r:id="rId109"/>
+    <hyperlink ref="Q137" r:id="rId110"/>
+    <hyperlink ref="N138" r:id="rId111"/>
+    <hyperlink ref="B139" r:id="rId112"/>
+    <hyperlink ref="L139" r:id="rId113"/>
+    <hyperlink ref="N139" r:id="rId114"/>
+    <hyperlink ref="P139" r:id="rId115"/>
+    <hyperlink ref="Q139" r:id="rId116"/>
+    <hyperlink ref="B145" r:id="rId117"/>
+    <hyperlink ref="L145" r:id="rId118"/>
+    <hyperlink ref="N145" r:id="rId119"/>
+    <hyperlink ref="P145" r:id="rId120"/>
+    <hyperlink ref="R145" r:id="rId121"/>
+    <hyperlink ref="N146" r:id="rId122"/>
+    <hyperlink ref="B147" r:id="rId123"/>
+    <hyperlink ref="L147" r:id="rId124"/>
+    <hyperlink ref="N147" r:id="rId125"/>
+    <hyperlink ref="P147" r:id="rId126"/>
+    <hyperlink ref="Q147" r:id="rId127"/>
+    <hyperlink ref="B151" r:id="rId128"/>
+    <hyperlink ref="L151" r:id="rId129"/>
+    <hyperlink ref="N151" r:id="rId130"/>
+    <hyperlink ref="P151" r:id="rId131"/>
+    <hyperlink ref="Q151" r:id="rId132"/>
+    <hyperlink ref="R151" r:id="rId133"/>
+    <hyperlink ref="B152" r:id="rId134"/>
+    <hyperlink ref="L152" r:id="rId135"/>
+    <hyperlink ref="N152" r:id="rId136"/>
+    <hyperlink ref="P152" r:id="rId137"/>
+    <hyperlink ref="Q152" r:id="rId138"/>
+    <hyperlink ref="B155" r:id="rId139"/>
+    <hyperlink ref="L155" r:id="rId140"/>
+    <hyperlink ref="N155" r:id="rId141"/>
+    <hyperlink ref="P155" r:id="rId142"/>
+    <hyperlink ref="Q155" r:id="rId143"/>
+    <hyperlink ref="R155" r:id="rId144"/>
+    <hyperlink ref="N156" r:id="rId145"/>
+    <hyperlink ref="B157" r:id="rId146"/>
+    <hyperlink ref="L157" r:id="rId147"/>
+    <hyperlink ref="N157" r:id="rId148"/>
+    <hyperlink ref="P157" r:id="rId149"/>
+    <hyperlink ref="Q157" r:id="rId150"/>
+    <hyperlink ref="B159" r:id="rId151"/>
+    <hyperlink ref="L159" r:id="rId152"/>
+    <hyperlink ref="N159" r:id="rId153"/>
+    <hyperlink ref="P159" r:id="rId154"/>
+    <hyperlink ref="Q159" r:id="rId155"/>
+    <hyperlink ref="B161" r:id="rId156"/>
+    <hyperlink ref="L161" r:id="rId157"/>
+    <hyperlink ref="N161" r:id="rId158"/>
+    <hyperlink ref="P161" r:id="rId159"/>
+    <hyperlink ref="Q161" r:id="rId160"/>
+    <hyperlink ref="R161" r:id="rId161"/>
+    <hyperlink ref="B162" r:id="rId162"/>
+    <hyperlink ref="L162" r:id="rId163"/>
+    <hyperlink ref="N162" r:id="rId164"/>
+    <hyperlink ref="P162" r:id="rId165"/>
+    <hyperlink ref="Q162" r:id="rId166"/>
+    <hyperlink ref="B165" r:id="rId167"/>
+    <hyperlink ref="L165" r:id="rId168"/>
+    <hyperlink ref="N165" r:id="rId169"/>
+    <hyperlink ref="P165" r:id="rId170"/>
+    <hyperlink ref="R165" r:id="rId171"/>
+    <hyperlink ref="B166" r:id="rId172"/>
+    <hyperlink ref="L166" r:id="rId173"/>
+    <hyperlink ref="N166" r:id="rId174"/>
+    <hyperlink ref="Q166" r:id="rId175"/>
+    <hyperlink ref="B167" r:id="rId176"/>
+    <hyperlink ref="L167" r:id="rId177"/>
+    <hyperlink ref="N167" r:id="rId178"/>
+    <hyperlink ref="Q167" r:id="rId179"/>
+    <hyperlink ref="B168" r:id="rId180"/>
+    <hyperlink ref="L168" r:id="rId181"/>
+    <hyperlink ref="N168" r:id="rId182"/>
+    <hyperlink ref="Q168" r:id="rId183"/>
+    <hyperlink ref="B174" r:id="rId184"/>
+    <hyperlink ref="L174" r:id="rId185"/>
+    <hyperlink ref="N174" r:id="rId186"/>
+    <hyperlink ref="P174" r:id="rId187"/>
+    <hyperlink ref="B180" r:id="rId188"/>
+    <hyperlink ref="L180" r:id="rId189"/>
+    <hyperlink ref="N180" r:id="rId190"/>
+    <hyperlink ref="P180" r:id="rId191"/>
+    <hyperlink ref="Q180" r:id="rId192"/>
+    <hyperlink ref="B200" r:id="rId193"/>
+    <hyperlink ref="L200" r:id="rId194"/>
+    <hyperlink ref="N200" r:id="rId195"/>
+    <hyperlink ref="P200" r:id="rId196"/>
+    <hyperlink ref="B201" r:id="rId197"/>
+    <hyperlink ref="L201" r:id="rId198"/>
+    <hyperlink ref="N201" r:id="rId199"/>
+    <hyperlink ref="Q201" r:id="rId200"/>
+    <hyperlink ref="B205" r:id="rId201"/>
+    <hyperlink ref="L205" r:id="rId202"/>
+    <hyperlink ref="N205" r:id="rId203"/>
+    <hyperlink ref="P205" r:id="rId204"/>
+    <hyperlink ref="B209" r:id="rId205"/>
+    <hyperlink ref="L209" r:id="rId206"/>
+    <hyperlink ref="N209" r:id="rId207"/>
+    <hyperlink ref="P209" r:id="rId208"/>
+    <hyperlink ref="B213" r:id="rId209"/>
+    <hyperlink ref="L213" r:id="rId210"/>
+    <hyperlink ref="N213" r:id="rId211"/>
+    <hyperlink ref="P213" r:id="rId212"/>
+    <hyperlink ref="Q213" r:id="rId213"/>
+    <hyperlink ref="B215" r:id="rId214"/>
+    <hyperlink ref="L215" r:id="rId215"/>
+    <hyperlink ref="N215" r:id="rId216"/>
+    <hyperlink ref="P215" r:id="rId217"/>
+    <hyperlink ref="B219" r:id="rId218"/>
+    <hyperlink ref="L219" r:id="rId219"/>
+    <hyperlink ref="N219" r:id="rId220"/>
+    <hyperlink ref="P219" r:id="rId221"/>
+    <hyperlink ref="Q219" r:id="rId222"/>
+    <hyperlink ref="N221" r:id="rId223"/>
+    <hyperlink ref="B222" r:id="rId224"/>
+    <hyperlink ref="L222" r:id="rId225"/>
+    <hyperlink ref="N222" r:id="rId226"/>
+    <hyperlink ref="P222" r:id="rId227"/>
+    <hyperlink ref="Q222" r:id="rId228"/>
+    <hyperlink ref="B227" r:id="rId229"/>
+    <hyperlink ref="L227" r:id="rId230"/>
+    <hyperlink ref="N227" r:id="rId231"/>
+    <hyperlink ref="P227" r:id="rId232"/>
+    <hyperlink ref="Q227" r:id="rId233"/>
+    <hyperlink ref="B232" r:id="rId234"/>
+    <hyperlink ref="L232" r:id="rId235"/>
+    <hyperlink ref="N232" r:id="rId236"/>
+    <hyperlink ref="P232" r:id="rId237"/>
+    <hyperlink ref="Q232" r:id="rId238"/>
+    <hyperlink ref="R232" r:id="rId239"/>
+    <hyperlink ref="B238" r:id="rId240"/>
+    <hyperlink ref="L238" r:id="rId241"/>
+    <hyperlink ref="N238" r:id="rId242"/>
+    <hyperlink ref="P238" r:id="rId243"/>
+    <hyperlink ref="B245" r:id="rId244"/>
+    <hyperlink ref="L245" r:id="rId245"/>
+    <hyperlink ref="N245" r:id="rId246"/>
+    <hyperlink ref="P245" r:id="rId247"/>
+    <hyperlink ref="B254" r:id="rId248"/>
+    <hyperlink ref="L254" r:id="rId249"/>
+    <hyperlink ref="N254" r:id="rId250"/>
+    <hyperlink ref="P254" r:id="rId251"/>
+    <hyperlink ref="Q254" r:id="rId252"/>
+    <hyperlink ref="B260" r:id="rId253"/>
+    <hyperlink ref="L260" r:id="rId254"/>
+    <hyperlink ref="N260" r:id="rId255"/>
+    <hyperlink ref="P260" r:id="rId256"/>
+    <hyperlink ref="Q260" r:id="rId257"/>
+    <hyperlink ref="B264" r:id="rId258"/>
+    <hyperlink ref="L264" r:id="rId259"/>
+    <hyperlink ref="N264" r:id="rId260"/>
+    <hyperlink ref="B286" r:id="rId261"/>
+    <hyperlink ref="L286" r:id="rId262"/>
+    <hyperlink ref="N286" r:id="rId263"/>
+    <hyperlink ref="P286" r:id="rId264"/>
+    <hyperlink ref="Q286" r:id="rId265"/>
+    <hyperlink ref="B294" r:id="rId266"/>
+    <hyperlink ref="L294" r:id="rId267"/>
+    <hyperlink ref="N294" r:id="rId268"/>
+    <hyperlink ref="P294" r:id="rId269"/>
+    <hyperlink ref="Q294" r:id="rId270"/>
+    <hyperlink ref="B305" r:id="rId271"/>
+    <hyperlink ref="L305" r:id="rId272"/>
+    <hyperlink ref="N305" r:id="rId273"/>
+    <hyperlink ref="P305" r:id="rId274"/>
+    <hyperlink ref="Q305" r:id="rId275"/>
+    <hyperlink ref="B313" r:id="rId276"/>
+    <hyperlink ref="L313" r:id="rId277"/>
+    <hyperlink ref="N313" r:id="rId278"/>
+    <hyperlink ref="P313" r:id="rId279"/>
+    <hyperlink ref="Q313" r:id="rId280"/>
+    <hyperlink ref="B335" r:id="rId281"/>
+    <hyperlink ref="L335" r:id="rId282"/>
+    <hyperlink ref="N335" r:id="rId283"/>
+    <hyperlink ref="P335" r:id="rId284"/>
+    <hyperlink ref="B337" r:id="rId285"/>
+    <hyperlink ref="L337" r:id="rId286"/>
+    <hyperlink ref="N337" r:id="rId287"/>
+    <hyperlink ref="P337" r:id="rId288"/>
+    <hyperlink ref="Q337" r:id="rId289"/>
+    <hyperlink ref="B341" r:id="rId290"/>
+    <hyperlink ref="L341" r:id="rId291"/>
+    <hyperlink ref="N341" r:id="rId292"/>
+    <hyperlink ref="B344" r:id="rId293"/>
+    <hyperlink ref="L344" r:id="rId294"/>
+    <hyperlink ref="N344" r:id="rId295"/>
+    <hyperlink ref="P344" r:id="rId296"/>
+    <hyperlink ref="Q344" r:id="rId297"/>
+    <hyperlink ref="B346" r:id="rId298"/>
+    <hyperlink ref="L346" r:id="rId299"/>
+    <hyperlink ref="N346" r:id="rId300"/>
+    <hyperlink ref="P346" r:id="rId301"/>
+    <hyperlink ref="Q346" r:id="rId302"/>
+    <hyperlink ref="B352" r:id="rId303"/>
+    <hyperlink ref="L352" r:id="rId304"/>
+    <hyperlink ref="N352" r:id="rId305"/>
+    <hyperlink ref="P352" r:id="rId306"/>
+    <hyperlink ref="Q352" r:id="rId307"/>
+    <hyperlink ref="B353" r:id="rId308"/>
+    <hyperlink ref="L353" r:id="rId309"/>
+    <hyperlink ref="N353" r:id="rId310"/>
+    <hyperlink ref="Q353" r:id="rId311"/>
+    <hyperlink ref="B356" r:id="rId312"/>
+    <hyperlink ref="L356" r:id="rId313"/>
+    <hyperlink ref="N356" r:id="rId314"/>
+    <hyperlink ref="P356" r:id="rId315"/>
+    <hyperlink ref="Q356" r:id="rId316"/>
+    <hyperlink ref="B359" r:id="rId317"/>
+    <hyperlink ref="L359" r:id="rId318"/>
+    <hyperlink ref="N359" r:id="rId319"/>
+    <hyperlink ref="P359" r:id="rId320"/>
+    <hyperlink ref="Q359" r:id="rId321"/>
+    <hyperlink ref="B361" r:id="rId322"/>
+    <hyperlink ref="L361" r:id="rId323"/>
+    <hyperlink ref="N361" r:id="rId324"/>
+    <hyperlink ref="P361" r:id="rId325"/>
+    <hyperlink ref="Q361" r:id="rId326"/>
+    <hyperlink ref="R361" r:id="rId327"/>
+    <hyperlink ref="B400" r:id="rId328"/>
+    <hyperlink ref="L400" r:id="rId329"/>
+    <hyperlink ref="N400" r:id="rId330"/>
+    <hyperlink ref="P400" r:id="rId331"/>
+    <hyperlink ref="N402" r:id="rId332"/>
+    <hyperlink ref="B403" r:id="rId333"/>
+    <hyperlink ref="L403" r:id="rId334"/>
+    <hyperlink ref="N403" r:id="rId335"/>
+    <hyperlink ref="P403" r:id="rId336"/>
+    <hyperlink ref="Q403" r:id="rId337"/>
+    <hyperlink ref="N404" r:id="rId338"/>
+    <hyperlink ref="B415" r:id="rId339"/>
+    <hyperlink ref="L415" r:id="rId340"/>
+    <hyperlink ref="N415" r:id="rId341"/>
+    <hyperlink ref="P415" r:id="rId342"/>
+    <hyperlink ref="B416" r:id="rId343"/>
+    <hyperlink ref="L416" r:id="rId344"/>
+    <hyperlink ref="N416" r:id="rId345"/>
+    <hyperlink ref="P416" r:id="rId346"/>
+    <hyperlink ref="B417" r:id="rId347"/>
+    <hyperlink ref="L417" r:id="rId348"/>
+    <hyperlink ref="N417" r:id="rId349"/>
+    <hyperlink ref="Q417" r:id="rId350"/>
+    <hyperlink ref="N419" r:id="rId351"/>
+    <hyperlink ref="B420" r:id="rId352"/>
+    <hyperlink ref="L420" r:id="rId353"/>
+    <hyperlink ref="N420" r:id="rId354"/>
+    <hyperlink ref="Q420" r:id="rId355"/>
+    <hyperlink ref="B426" r:id="rId356"/>
+    <hyperlink ref="L426" r:id="rId357"/>
+    <hyperlink ref="N426" r:id="rId358"/>
+    <hyperlink ref="P426" r:id="rId359"/>
+    <hyperlink ref="B433" r:id="rId360"/>
+    <hyperlink ref="L433" r:id="rId361"/>
+    <hyperlink ref="N433" r:id="rId362"/>
+    <hyperlink ref="P433" r:id="rId363"/>
+    <hyperlink ref="B438" r:id="rId364"/>
+    <hyperlink ref="L438" r:id="rId365"/>
+    <hyperlink ref="N438" r:id="rId366"/>
+    <hyperlink ref="P438" r:id="rId367"/>
+    <hyperlink ref="B439" r:id="rId368"/>
+    <hyperlink ref="L439" r:id="rId369"/>
+    <hyperlink ref="N439" r:id="rId370"/>
+    <hyperlink ref="P439" r:id="rId371"/>
+    <hyperlink ref="B451" r:id="rId372"/>
+    <hyperlink ref="L451" r:id="rId373"/>
+    <hyperlink ref="N451" r:id="rId374"/>
+    <hyperlink ref="P451" r:id="rId375"/>
+    <hyperlink ref="Q451" r:id="rId376"/>
+    <hyperlink ref="B468" r:id="rId377"/>
+    <hyperlink ref="L468" r:id="rId378"/>
+    <hyperlink ref="N468" r:id="rId379"/>
+    <hyperlink ref="P468" r:id="rId380"/>
+    <hyperlink ref="Q468" r:id="rId381"/>
+    <hyperlink ref="N473" r:id="rId382"/>
+    <hyperlink ref="B484" r:id="rId383"/>
+    <hyperlink ref="L484" r:id="rId384"/>
+    <hyperlink ref="N484" r:id="rId385"/>
+    <hyperlink ref="P484" r:id="rId386"/>
+    <hyperlink ref="R484" r:id="rId387"/>
+    <hyperlink ref="B490" r:id="rId388"/>
+    <hyperlink ref="L490" r:id="rId389"/>
+    <hyperlink ref="N490" r:id="rId390"/>
+    <hyperlink ref="P490" r:id="rId391"/>
+    <hyperlink ref="B492" r:id="rId392"/>
+    <hyperlink ref="L492" r:id="rId393"/>
+    <hyperlink ref="N492" r:id="rId394"/>
+    <hyperlink ref="B495" r:id="rId395"/>
+    <hyperlink ref="L495" r:id="rId396"/>
+    <hyperlink ref="N495" r:id="rId397"/>
+    <hyperlink ref="B498" r:id="rId398"/>
+    <hyperlink ref="L498" r:id="rId399"/>
+    <hyperlink ref="N498" r:id="rId400"/>
+    <hyperlink ref="P498" r:id="rId401"/>
+    <hyperlink ref="B502" r:id="rId402"/>
+    <hyperlink ref="L502" r:id="rId403"/>
+    <hyperlink ref="N502" r:id="rId404"/>
+    <hyperlink ref="P502" r:id="rId405"/>
+    <hyperlink ref="B503" r:id="rId406"/>
+    <hyperlink ref="L503" r:id="rId407"/>
+    <hyperlink ref="N503" r:id="rId408"/>
+    <hyperlink ref="P503" r:id="rId409"/>
+    <hyperlink ref="B506" r:id="rId410"/>
+    <hyperlink ref="L506" r:id="rId411"/>
+    <hyperlink ref="N506" r:id="rId412"/>
+    <hyperlink ref="P506" r:id="rId413"/>
+    <hyperlink ref="B517" r:id="rId414"/>
+    <hyperlink ref="L517" r:id="rId415"/>
+    <hyperlink ref="N517" r:id="rId416"/>
+    <hyperlink ref="P517" r:id="rId417"/>
+    <hyperlink ref="B520" r:id="rId418"/>
+    <hyperlink ref="L520" r:id="rId419"/>
+    <hyperlink ref="N520" r:id="rId420"/>
+    <hyperlink ref="P520" r:id="rId421"/>
+    <hyperlink ref="R520" r:id="rId422"/>
+    <hyperlink ref="B531" r:id="rId423"/>
+    <hyperlink ref="L531" r:id="rId424"/>
+    <hyperlink ref="N531" r:id="rId425"/>
+    <hyperlink ref="P531" r:id="rId426"/>
+    <hyperlink ref="Q531" r:id="rId427"/>
+    <hyperlink ref="R531" r:id="rId428"/>
+    <hyperlink ref="B534" r:id="rId429"/>
+    <hyperlink ref="L534" r:id="rId430"/>
+    <hyperlink ref="N534" r:id="rId431"/>
+    <hyperlink ref="P534" r:id="rId432"/>
+    <hyperlink ref="B535" r:id="rId433"/>
+    <hyperlink ref="L535" r:id="rId434"/>
+    <hyperlink ref="N535" r:id="rId435"/>
+    <hyperlink ref="P535" r:id="rId436"/>
+    <hyperlink ref="Q535" r:id="rId437"/>
+    <hyperlink ref="B537" r:id="rId438"/>
+    <hyperlink ref="L537" r:id="rId439"/>
+    <hyperlink ref="N537" r:id="rId440"/>
+    <hyperlink ref="P537" r:id="rId441"/>
+    <hyperlink ref="B539" r:id="rId442"/>
+    <hyperlink ref="L539" r:id="rId443"/>
+    <hyperlink ref="N539" r:id="rId444"/>
+    <hyperlink ref="P539" r:id="rId445"/>
+    <hyperlink ref="B540" r:id="rId446"/>
+    <hyperlink ref="L540" r:id="rId447"/>
+    <hyperlink ref="N540" r:id="rId448"/>
+    <hyperlink ref="P540" r:id="rId449"/>
+    <hyperlink ref="B541" r:id="rId450"/>
+    <hyperlink ref="L541" r:id="rId451"/>
+    <hyperlink ref="N541" r:id="rId452"/>
+    <hyperlink ref="P541" r:id="rId453"/>
+    <hyperlink ref="Q541" r:id="rId454"/>
+    <hyperlink ref="B542" r:id="rId455"/>
+    <hyperlink ref="L542" r:id="rId456"/>
+    <hyperlink ref="N542" r:id="rId457"/>
+    <hyperlink ref="P542" r:id="rId458"/>
+    <hyperlink ref="Q542" r:id="rId459"/>
+    <hyperlink ref="B543" r:id="rId460"/>
+    <hyperlink ref="L543" r:id="rId461"/>
+    <hyperlink ref="N543" r:id="rId462"/>
+    <hyperlink ref="P543" r:id="rId463"/>
+    <hyperlink ref="Q543" r:id="rId464"/>
+    <hyperlink ref="B554" r:id="rId465"/>
+    <hyperlink ref="L554" r:id="rId466"/>
+    <hyperlink ref="N554" r:id="rId467"/>
+    <hyperlink ref="P554" r:id="rId468"/>
+    <hyperlink ref="Q554" r:id="rId469"/>
+    <hyperlink ref="N562" r:id="rId470"/>
+    <hyperlink ref="B563" r:id="rId471"/>
+    <hyperlink ref="L563" r:id="rId472"/>
+    <hyperlink ref="N563" r:id="rId473"/>
+    <hyperlink ref="P563" r:id="rId474"/>
+    <hyperlink ref="Q563" r:id="rId475"/>
+    <hyperlink ref="B570" r:id="rId476"/>
+    <hyperlink ref="L570" r:id="rId477"/>
+    <hyperlink ref="N570" r:id="rId478"/>
+    <hyperlink ref="P570" r:id="rId479"/>
+    <hyperlink ref="Q570" r:id="rId480"/>
+    <hyperlink ref="B571" r:id="rId481"/>
+    <hyperlink ref="L571" r:id="rId482"/>
+    <hyperlink ref="N571" r:id="rId483"/>
+    <hyperlink ref="P571" r:id="rId484"/>
+    <hyperlink ref="Q571" r:id="rId485"/>
+    <hyperlink ref="B572" r:id="rId486"/>
+    <hyperlink ref="L572" r:id="rId487"/>
+    <hyperlink ref="N572" r:id="rId488"/>
+    <hyperlink ref="Q572" r:id="rId489"/>
+    <hyperlink ref="B593" r:id="rId490"/>
+    <hyperlink ref="L593" r:id="rId491"/>
+    <hyperlink ref="N593" r:id="rId492"/>
+    <hyperlink ref="P593" r:id="rId493"/>
+    <hyperlink ref="R593" r:id="rId494"/>
+    <hyperlink ref="B603" r:id="rId495"/>
+    <hyperlink ref="L603" r:id="rId496"/>
+    <hyperlink ref="N603" r:id="rId497"/>
+    <hyperlink ref="P603" r:id="rId498"/>
+    <hyperlink ref="Q603" r:id="rId499"/>
+    <hyperlink ref="B629" r:id="rId500"/>
+    <hyperlink ref="L629" r:id="rId501"/>
+    <hyperlink ref="N629" r:id="rId502"/>
+    <hyperlink ref="P629" r:id="rId503"/>
+    <hyperlink ref="Q629" r:id="rId504"/>
+    <hyperlink ref="B630" r:id="rId505"/>
+    <hyperlink ref="L630" r:id="rId506"/>
+    <hyperlink ref="N630" r:id="rId507"/>
+    <hyperlink ref="P630" r:id="rId508"/>
+    <hyperlink ref="Q630" r:id="rId509"/>
+    <hyperlink ref="B639" r:id="rId510"/>
+    <hyperlink ref="N639" r:id="rId511"/>
+    <hyperlink ref="P639" r:id="rId512"/>
+    <hyperlink ref="B648" r:id="rId513"/>
+    <hyperlink ref="L648" r:id="rId514"/>
+    <hyperlink ref="N648" r:id="rId515"/>
+    <hyperlink ref="P648" r:id="rId516"/>
+    <hyperlink ref="B655" r:id="rId517"/>
+    <hyperlink ref="L655" r:id="rId518"/>
+    <hyperlink ref="N655" r:id="rId519"/>
   </hyperlinks>
   <pageSetup paperSize="66" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
